--- a/test-data/TEST_Sheohar_Project.xlsx
+++ b/test-data/TEST_Sheohar_Project.xlsx
@@ -577,7 +577,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B17"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -612,7 +612,7 @@
         <v>Saved at</v>
       </c>
       <c r="B4" t="str">
-        <v>12-10-2026 17:53:11</v>
+        <v>12-10-2026 18:19:44</v>
       </c>
     </row>
     <row r="5">
@@ -671,9 +671,57 @@
         <v>No</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>part.second.polling</v>
+      </c>
+      <c r="B12" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>part.second.pccp</v>
+      </c>
+      <c r="B13" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>part.second.micro</v>
+      </c>
+      <c r="B14" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>part.final.polling</v>
+      </c>
+      <c r="B15" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>part.final.pccp</v>
+      </c>
+      <c r="B16" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>part.final.micro</v>
+      </c>
+      <c r="B17" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B17"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -696,7 +744,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12-10-2026 17:53:11</v>
+        <v>12-10-2026 18:19:44</v>
       </c>
       <c r="B2" t="str">
         <v>Test data generated (Small — Sheohar style (5 blocks, 6 TC + 6 GC booths))</v>
@@ -1487,34 +1535,34 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0300003</v>
+        <v>0300012</v>
       </c>
       <c r="B2" t="str">
-        <v>PRIYANKA THAKUR</v>
+        <v>USHA SINGH</v>
       </c>
       <c r="C2" t="str">
-        <v>Section Officer</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D2" t="str">
-        <v>Project Girls High School Sheohar No.3</v>
+        <v>Block Education Office Piprahi No.2</v>
       </c>
       <c r="E2" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F2" t="str">
-        <v>9003000003</v>
+        <v>9003000012</v>
       </c>
       <c r="G2" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="H2" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="I2" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J2" t="str">
-        <v>30000023757</v>
+        <v>30000095028</v>
       </c>
       <c r="K2" t="str">
         <v>State Bank of India</v>
@@ -1523,39 +1571,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M2" t="str">
-        <v>SBIN0004239</v>
+        <v>SBIN0004474</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0300028</v>
+        <v>0300004</v>
       </c>
       <c r="B3" t="str">
-        <v>RAKESH MAHTO</v>
+        <v>MAMTA THAKUR</v>
       </c>
       <c r="C3" t="str">
-        <v>Head Clerk</v>
+        <v>Headmaster</v>
       </c>
       <c r="D3" t="str">
-        <v>Kanya Middle School Purnahiya No.2</v>
+        <v>High School Dumri Katsari No.4</v>
       </c>
       <c r="E3" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F3" t="str">
-        <v>9003000028</v>
+        <v>9003000004</v>
       </c>
       <c r="G3" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H3" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="I3" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J3" t="str">
-        <v>30000221732</v>
+        <v>30000031676</v>
       </c>
       <c r="K3" t="str">
         <v>State Bank of India</v>
@@ -1564,39 +1612,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M3" t="str">
-        <v>SBIN0004432</v>
+        <v>SBIN0003675</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0300106</v>
+        <v>0300114</v>
       </c>
       <c r="B4" t="str">
-        <v>ALOK GUPTA</v>
+        <v>SAVITA PANDEY</v>
       </c>
       <c r="C4" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D4" t="str">
-        <v>Bank of India, Tariyani</v>
+        <v>Head Post Office, Purnahiya</v>
       </c>
       <c r="E4" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F4" t="str">
-        <v>9003000106</v>
+        <v>9003000114</v>
       </c>
       <c r="G4" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="H4" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I4" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J4" t="str">
-        <v>30000839414</v>
+        <v>30000902766</v>
       </c>
       <c r="K4" t="str">
         <v>State Bank of India</v>
@@ -1605,39 +1653,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M4" t="str">
-        <v>SBIN0002059</v>
+        <v>SBIN0003704</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0300045</v>
+        <v>0300060</v>
       </c>
       <c r="B5" t="str">
-        <v>NASREEN ALAM</v>
+        <v>MUKESH KUMAR</v>
       </c>
       <c r="C5" t="str">
         <v>Clerk</v>
       </c>
       <c r="D5" t="str">
-        <v>Middle School Tariyani</v>
+        <v>District Treasury Sheohar</v>
       </c>
       <c r="E5" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F5" t="str">
-        <v>9003000045</v>
+        <v>9003000060</v>
       </c>
       <c r="G5" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="H5" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I5" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="J5" t="str">
-        <v>30000356355</v>
+        <v>30000475140</v>
       </c>
       <c r="K5" t="str">
         <v>State Bank of India</v>
@@ -1646,39 +1694,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M5" t="str">
-        <v>SBIN0001508</v>
+        <v>SBIN0009610</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0300023</v>
+        <v>0300100</v>
       </c>
       <c r="B6" t="str">
-        <v>ALOK KUMAR</v>
+        <v>ASHA JHA</v>
       </c>
       <c r="C6" t="str">
-        <v>Senior Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D6" t="str">
-        <v>Block Office Tariyani No.4</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="E6" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F6" t="str">
-        <v>9003000023</v>
+        <v>9003000100</v>
       </c>
       <c r="G6" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H6" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I6" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="J6" t="str">
-        <v>30000182137</v>
+        <v>30000791900</v>
       </c>
       <c r="K6" t="str">
         <v>State Bank of India</v>
@@ -1687,39 +1735,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M6" t="str">
-        <v>SBIN0006316</v>
+        <v>SBIN0002940</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>0300091</v>
+        <v>0300031</v>
       </c>
       <c r="B7" t="str">
-        <v>RANJIT ALAM</v>
+        <v>AMIT SHARMA</v>
       </c>
       <c r="C7" t="str">
-        <v>Assistant Engineer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D7" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>Primary School Dumri Katsari No.1</v>
       </c>
       <c r="E7" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F7" t="str">
-        <v>9003000091</v>
+        <v>9003000031</v>
       </c>
       <c r="G7" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H7" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I7" t="str">
         <v>Dumri Katsari</v>
       </c>
       <c r="J7" t="str">
-        <v>30000720629</v>
+        <v>30000245489</v>
       </c>
       <c r="K7" t="str">
         <v>State Bank of India</v>
@@ -1728,39 +1776,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M7" t="str">
-        <v>SBIN0008490</v>
+        <v>SBIN0008556</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0300097</v>
+        <v>0300110</v>
       </c>
       <c r="B8" t="str">
-        <v>RAKESH RAM</v>
+        <v>SAVITA DEVI C</v>
       </c>
       <c r="C8" t="str">
-        <v>Assistant Engineer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D8" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>Bank of India, Sheohar</v>
       </c>
       <c r="E8" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F8" t="str">
-        <v>9003000097</v>
+        <v>9003000110</v>
       </c>
       <c r="G8" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H8" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I8" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="J8" t="str">
-        <v>30000768143</v>
+        <v>30000871090</v>
       </c>
       <c r="K8" t="str">
         <v>State Bank of India</v>
@@ -1769,39 +1817,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M8" t="str">
-        <v>SBIN0009702</v>
+        <v>SBIN0003602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0300123</v>
+        <v>0300101</v>
       </c>
       <c r="B9" t="str">
-        <v>AMIT RAI L</v>
+        <v>ANITA MISHRA</v>
       </c>
       <c r="C9" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D9" t="str">
-        <v>Punjab National Bank, Sheohar</v>
+        <v>Minor Irrigation Office Tariyani</v>
       </c>
       <c r="E9" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F9" t="str">
-        <v>9003000123</v>
+        <v>9003000101</v>
       </c>
       <c r="G9" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H9" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I9" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="J9" t="str">
-        <v>30000974037</v>
+        <v>30000799819</v>
       </c>
       <c r="K9" t="str">
         <v>State Bank of India</v>
@@ -1810,39 +1858,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M9" t="str">
-        <v>SBIN0008649</v>
+        <v>SBIN0006645</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0300116</v>
+        <v>0300121</v>
       </c>
       <c r="B10" t="str">
-        <v>ANITA RAM</v>
+        <v>KIRAN KUMAR</v>
       </c>
       <c r="C10" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D10" t="str">
-        <v>LIC Branch Office, Sheohar</v>
+        <v>Head Post Office, Sheohar</v>
       </c>
       <c r="E10" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F10" t="str">
-        <v>9003000116</v>
+        <v>9003000121</v>
       </c>
       <c r="G10" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="H10" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I10" t="str">
         <v>Sheohar</v>
       </c>
       <c r="J10" t="str">
-        <v>30000918604</v>
+        <v>30000958199</v>
       </c>
       <c r="K10" t="str">
         <v>State Bank of India</v>
@@ -1851,39 +1899,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M10" t="str">
-        <v>SBIN0008202</v>
+        <v>SBIN0005457</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>0300010</v>
+        <v>0300079</v>
       </c>
       <c r="B11" t="str">
-        <v>KIRAN RAM</v>
+        <v>FARHAT PRASAD</v>
       </c>
       <c r="C11" t="str">
-        <v>Headmaster</v>
+        <v>Clerk</v>
       </c>
       <c r="D11" t="str">
-        <v>Block Education Office Tariyani No.4</v>
+        <v>Kanya Middle School Purnahiya</v>
       </c>
       <c r="E11" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F11" t="str">
-        <v>9003000010</v>
+        <v>9003000079</v>
       </c>
       <c r="G11" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H11" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I11" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J11" t="str">
-        <v>30000079190</v>
+        <v>30000625601</v>
       </c>
       <c r="K11" t="str">
         <v>State Bank of India</v>
@@ -1892,39 +1940,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M11" t="str">
-        <v>SBIN0009534</v>
+        <v>SBIN0007441</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>0300093</v>
+        <v>0300123</v>
       </c>
       <c r="B12" t="str">
-        <v>RINKU KHATUN</v>
+        <v>RAVI JHA M</v>
       </c>
       <c r="C12" t="str">
-        <v>Revenue Officer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D12" t="str">
-        <v>Minor Irrigation Office Sheohar</v>
+        <v>UCO Bank, Piprahi</v>
       </c>
       <c r="E12" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F12" t="str">
-        <v>9003000093</v>
+        <v>9003000123</v>
       </c>
       <c r="G12" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H12" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="I12" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J12" t="str">
-        <v>30000736467</v>
+        <v>30000974037</v>
       </c>
       <c r="K12" t="str">
         <v>State Bank of India</v>
@@ -1933,39 +1981,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M12" t="str">
-        <v>SBIN0007199</v>
+        <v>SBIN0003472</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0300052</v>
+        <v>0300113</v>
       </c>
       <c r="B13" t="str">
-        <v>MANOJ SAH</v>
+        <v>SURESH PRASAD J</v>
       </c>
       <c r="C13" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Postmaster</v>
       </c>
       <c r="D13" t="str">
-        <v>CDPO Office Dumri Katsari No.3</v>
+        <v>Punjab National Bank, Dumri Katsari</v>
       </c>
       <c r="E13" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F13" t="str">
-        <v>9003000052</v>
+        <v>9003000113</v>
       </c>
       <c r="G13" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H13" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I13" t="str">
         <v>Dumri Katsari</v>
       </c>
       <c r="J13" t="str">
-        <v>30000411788</v>
+        <v>30000894847</v>
       </c>
       <c r="K13" t="str">
         <v>State Bank of India</v>
@@ -1974,30 +2022,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M13" t="str">
-        <v>SBIN0007411</v>
+        <v>SBIN0002154</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0300070</v>
+        <v>0300050</v>
       </c>
       <c r="B14" t="str">
-        <v>RINKU THAKUR</v>
+        <v>RAVI PRASAD</v>
       </c>
       <c r="C14" t="str">
-        <v>Office Assistant</v>
+        <v>Accountant</v>
       </c>
       <c r="D14" t="str">
-        <v>CDPO Office Tariyani</v>
+        <v>High School Tariyani</v>
       </c>
       <c r="E14" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="F14" t="str">
-        <v>9003000070</v>
+        <v>9003000050</v>
       </c>
       <c r="G14" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H14" t="str">
         <v>Tariyani</v>
@@ -2006,7 +2054,7 @@
         <v>Tariyani</v>
       </c>
       <c r="J14" t="str">
-        <v>30000554330</v>
+        <v>30000395950</v>
       </c>
       <c r="K14" t="str">
         <v>State Bank of India</v>
@@ -2015,39 +2063,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M14" t="str">
-        <v>SBIN0008480</v>
+        <v>SBIN0002852</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>0300111</v>
+        <v>0300062</v>
       </c>
       <c r="B15" t="str">
-        <v>MUKESH RAI</v>
+        <v>ARVIND SHARMA</v>
       </c>
       <c r="C15" t="str">
-        <v>Branch Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D15" t="str">
-        <v>Bank of India, Piprahi</v>
+        <v>Panchayat Bhawan Purnahiya No.1</v>
       </c>
       <c r="E15" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F15" t="str">
-        <v>9003000111</v>
+        <v>9003000062</v>
       </c>
       <c r="G15" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H15" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I15" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J15" t="str">
-        <v>30000879009</v>
+        <v>30000490978</v>
       </c>
       <c r="K15" t="str">
         <v>State Bank of India</v>
@@ -2056,39 +2104,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M15" t="str">
-        <v>SBIN0004241</v>
+        <v>SBIN0002294</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>0300064</v>
+        <v>0300059</v>
       </c>
       <c r="B16" t="str">
-        <v>PRIYANKA MAHTO</v>
+        <v>RAVI GUPTA</v>
       </c>
       <c r="C16" t="str">
         <v>Clerk</v>
       </c>
       <c r="D16" t="str">
-        <v>High School Sheohar No.2</v>
+        <v>Project Girls High School Dumri Katsari</v>
       </c>
       <c r="E16" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F16" t="str">
-        <v>9003000064</v>
+        <v>9003000059</v>
       </c>
       <c r="G16" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H16" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="I16" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I16" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="J16" t="str">
-        <v>30000506816</v>
+        <v>30000467221</v>
       </c>
       <c r="K16" t="str">
         <v>State Bank of India</v>
@@ -2097,39 +2145,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M16" t="str">
-        <v>SBIN0009860</v>
+        <v>SBIN0003004</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>0300108</v>
+        <v>0300075</v>
       </c>
       <c r="B17" t="str">
-        <v>SURESH RAI L</v>
+        <v>REKHA JHA</v>
       </c>
       <c r="C17" t="str">
-        <v>Postmaster</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D17" t="str">
-        <v>Head Post Office, Tariyani</v>
+        <v>High School Tariyani No.3</v>
       </c>
       <c r="E17" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="F17" t="str">
-        <v>9003000108</v>
+        <v>9003000075</v>
       </c>
       <c r="G17" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H17" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I17" t="str">
         <v>Tariyani</v>
       </c>
       <c r="J17" t="str">
-        <v>30000855252</v>
+        <v>30000593925</v>
       </c>
       <c r="K17" t="str">
         <v>State Bank of India</v>
@@ -2138,39 +2186,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M17" t="str">
-        <v>SBIN0003467</v>
+        <v>SBIN0006523</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>0300099</v>
+        <v>0300021</v>
       </c>
       <c r="B18" t="str">
-        <v>MD. IRFAN MISHRA</v>
+        <v>NASREEN OJHA</v>
       </c>
       <c r="C18" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D18" t="str">
-        <v>RWD Sub-Division Sheohar</v>
+        <v>Middle School Sheohar No.1</v>
       </c>
       <c r="E18" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F18" t="str">
-        <v>9003000099</v>
+        <v>9003000021</v>
       </c>
       <c r="G18" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H18" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I18" t="str">
         <v>Sheohar</v>
       </c>
       <c r="J18" t="str">
-        <v>30000783981</v>
+        <v>30000166299</v>
       </c>
       <c r="K18" t="str">
         <v>State Bank of India</v>
@@ -2179,39 +2227,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M18" t="str">
-        <v>SBIN0005612</v>
+        <v>SBIN0001449</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>0300079</v>
+        <v>0300045</v>
       </c>
       <c r="B19" t="str">
-        <v>SURESH RAI T</v>
+        <v>SANJAY JHA</v>
       </c>
       <c r="C19" t="str">
         <v>Teacher</v>
       </c>
       <c r="D19" t="str">
-        <v>High School Tariyani</v>
+        <v>Primary School Tariyani No.4</v>
       </c>
       <c r="E19" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="F19" t="str">
-        <v>9003000079</v>
+        <v>9003000045</v>
       </c>
       <c r="G19" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H19" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I19" t="str">
         <v>Tariyani</v>
       </c>
       <c r="J19" t="str">
-        <v>30000625601</v>
+        <v>30000356355</v>
       </c>
       <c r="K19" t="str">
         <v>State Bank of India</v>
@@ -2220,39 +2268,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M19" t="str">
-        <v>SBIN0005188</v>
+        <v>SBIN0001347</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>0300095</v>
+        <v>0300023</v>
       </c>
       <c r="B20" t="str">
-        <v>VIJAY RAM</v>
+        <v>SANTOSH RAI</v>
       </c>
       <c r="C20" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D20" t="str">
-        <v>Block Office Tariyani</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="E20" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F20" t="str">
-        <v>9003000095</v>
+        <v>9003000023</v>
       </c>
       <c r="G20" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H20" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I20" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="J20" t="str">
-        <v>30000752305</v>
+        <v>30000182137</v>
       </c>
       <c r="K20" t="str">
         <v>State Bank of India</v>
@@ -2261,39 +2309,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M20" t="str">
-        <v>SBIN0008933</v>
+        <v>SBIN0004786</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>0300080</v>
+        <v>0300066</v>
       </c>
       <c r="B21" t="str">
-        <v>MAHESH OJHA</v>
+        <v>RINKU DEVI</v>
       </c>
       <c r="C21" t="str">
-        <v>Office Assistant</v>
+        <v>Clerk</v>
       </c>
       <c r="D21" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="E21" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F21" t="str">
-        <v>9003000080</v>
+        <v>9003000066</v>
       </c>
       <c r="G21" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="H21" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I21" t="str">
         <v>Sheohar</v>
       </c>
       <c r="J21" t="str">
-        <v>30000633520</v>
+        <v>30000522654</v>
       </c>
       <c r="K21" t="str">
         <v>State Bank of India</v>
@@ -2302,39 +2350,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M21" t="str">
-        <v>SBIN0005792</v>
+        <v>SBIN0003668</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>0300002</v>
+        <v>0300037</v>
       </c>
       <c r="B22" t="str">
-        <v>ABDUL KALAM PANDEY</v>
+        <v>RAMESH OJHA</v>
       </c>
       <c r="C22" t="str">
-        <v>Senior Teacher</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D22" t="str">
-        <v>Block Agriculture Office Purnahiya No.4</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="E22" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F22" t="str">
-        <v>9003000002</v>
+        <v>9003000037</v>
       </c>
       <c r="G22" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H22" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I22" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J22" t="str">
-        <v>30000015838</v>
+        <v>30000293003</v>
       </c>
       <c r="K22" t="str">
         <v>State Bank of India</v>
@@ -2343,39 +2391,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M22" t="str">
-        <v>SBIN0002382</v>
+        <v>SBIN0006367</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>0300026</v>
+        <v>0300020</v>
       </c>
       <c r="B23" t="str">
-        <v>MANOJ ALAM</v>
+        <v>NITISH SINGH</v>
       </c>
       <c r="C23" t="str">
-        <v>Head Clerk</v>
+        <v>Lecturer</v>
       </c>
       <c r="D23" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="E23" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F23" t="str">
-        <v>9003000026</v>
+        <v>9003000020</v>
       </c>
       <c r="G23" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H23" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I23" t="str">
         <v>Sheohar</v>
       </c>
       <c r="J23" t="str">
-        <v>30000205894</v>
+        <v>30000158380</v>
       </c>
       <c r="K23" t="str">
         <v>State Bank of India</v>
@@ -2384,39 +2432,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M23" t="str">
-        <v>SBIN0008069</v>
+        <v>SBIN0003881</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>0300105</v>
+        <v>0300070</v>
       </c>
       <c r="B24" t="str">
-        <v>PANKAJ RAM</v>
+        <v>SANJAY OJHA</v>
       </c>
       <c r="C24" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D24" t="str">
-        <v>Minor Irrigation Office Purnahiya</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="E24" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F24" t="str">
-        <v>9003000105</v>
+        <v>9003000070</v>
       </c>
       <c r="G24" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H24" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I24" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J24" t="str">
-        <v>30000831495</v>
+        <v>30000554330</v>
       </c>
       <c r="K24" t="str">
         <v>State Bank of India</v>
@@ -2425,39 +2473,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M24" t="str">
-        <v>SBIN0002802</v>
+        <v>SBIN0004984</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0300044</v>
+        <v>0300002</v>
       </c>
       <c r="B25" t="str">
-        <v>ARVIND CHAUDHARY</v>
+        <v>NIRMALA OJHA</v>
       </c>
       <c r="C25" t="str">
-        <v>Teacher</v>
+        <v>Lecturer</v>
       </c>
       <c r="D25" t="str">
-        <v>High School Piprahi No.4</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="E25" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F25" t="str">
-        <v>9003000044</v>
+        <v>9003000002</v>
       </c>
       <c r="G25" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H25" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I25" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="J25" t="str">
-        <v>30000348436</v>
+        <v>30000015838</v>
       </c>
       <c r="K25" t="str">
         <v>State Bank of India</v>
@@ -2466,39 +2514,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M25" t="str">
-        <v>SBIN0001712</v>
+        <v>SBIN0003827</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>0300096</v>
+        <v>0300076</v>
       </c>
       <c r="B26" t="str">
-        <v>PANKAJ KHATUN</v>
+        <v>POONAM SINHA</v>
       </c>
       <c r="C26" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D26" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Kanya Middle School Dumri Katsari No.2</v>
       </c>
       <c r="E26" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F26" t="str">
-        <v>9003000096</v>
+        <v>9003000076</v>
       </c>
       <c r="G26" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H26" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I26" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J26" t="str">
-        <v>30000760224</v>
+        <v>30000601844</v>
       </c>
       <c r="K26" t="str">
         <v>State Bank of India</v>
@@ -2507,39 +2555,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M26" t="str">
-        <v>SBIN0006697</v>
+        <v>SBIN0005783</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>0300061</v>
+        <v>0300008</v>
       </c>
       <c r="B27" t="str">
-        <v>REKHA GUPTA</v>
+        <v>ANITA PRASAD</v>
       </c>
       <c r="C27" t="str">
-        <v>Accountant</v>
+        <v>Lecturer</v>
       </c>
       <c r="D27" t="str">
-        <v>Middle School Tariyani No.4</v>
+        <v>Block Education Office Sheohar No.4</v>
       </c>
       <c r="E27" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F27" t="str">
-        <v>9003000061</v>
+        <v>9003000008</v>
       </c>
       <c r="G27" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H27" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="I27" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="J27" t="str">
-        <v>30000483059</v>
+        <v>30000063352</v>
       </c>
       <c r="K27" t="str">
         <v>State Bank of India</v>
@@ -2548,39 +2596,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M27" t="str">
-        <v>SBIN0002019</v>
+        <v>SBIN0007356</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>0300081</v>
+        <v>0300024</v>
       </c>
       <c r="B28" t="str">
-        <v>SUNIL DEVI</v>
+        <v>USHA KUMAR</v>
       </c>
       <c r="C28" t="str">
-        <v>Data Entry Operator</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D28" t="str">
-        <v>Block Office Piprahi No.3</v>
+        <v>Middle School Dumri Katsari No.2</v>
       </c>
       <c r="E28" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F28" t="str">
-        <v>9003000081</v>
+        <v>9003000024</v>
       </c>
       <c r="G28" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H28" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="I28" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I28" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="J28" t="str">
-        <v>30000641439</v>
+        <v>30000190056</v>
       </c>
       <c r="K28" t="str">
         <v>State Bank of India</v>
@@ -2589,39 +2637,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M28" t="str">
-        <v>SBIN0009718</v>
+        <v>SBIN0007097</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>0300054</v>
+        <v>0300092</v>
       </c>
       <c r="B29" t="str">
-        <v>ABDUL KALAM ALAM</v>
+        <v>RANJIT KUMAR</v>
       </c>
       <c r="C29" t="str">
-        <v>Accountant</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D29" t="str">
-        <v>CDPO Office Dumri Katsari</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="E29" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F29" t="str">
-        <v>9003000054</v>
+        <v>9003000092</v>
       </c>
       <c r="G29" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H29" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I29" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="J29" t="str">
-        <v>30000427626</v>
+        <v>30000728548</v>
       </c>
       <c r="K29" t="str">
         <v>State Bank of India</v>
@@ -2630,39 +2678,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M29" t="str">
-        <v>SBIN0006878</v>
+        <v>SBIN0004854</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>0300056</v>
+        <v>0300093</v>
       </c>
       <c r="B30" t="str">
-        <v>PRIYANKA VERMA</v>
+        <v>ANIL MAHTO</v>
       </c>
       <c r="C30" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D30" t="str">
-        <v>PHC Purnahiya No.2</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="E30" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F30" t="str">
-        <v>9003000056</v>
+        <v>9003000093</v>
       </c>
       <c r="G30" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H30" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I30" t="str">
         <v>Purnahiya</v>
       </c>
       <c r="J30" t="str">
-        <v>30000443464</v>
+        <v>30000736467</v>
       </c>
       <c r="K30" t="str">
         <v>State Bank of India</v>
@@ -2671,39 +2719,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M30" t="str">
-        <v>SBIN0007805</v>
+        <v>SBIN0002484</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>0300033</v>
+        <v>0300058</v>
       </c>
       <c r="B31" t="str">
-        <v>MANOJ THAKUR</v>
+        <v>USHA GUPTA</v>
       </c>
       <c r="C31" t="str">
-        <v>Head Clerk</v>
+        <v>Clerk</v>
       </c>
       <c r="D31" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>High School Piprahi No.2</v>
       </c>
       <c r="E31" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F31" t="str">
-        <v>9003000033</v>
+        <v>9003000058</v>
       </c>
       <c r="G31" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H31" t="str">
         <v>Sheohar</v>
       </c>
       <c r="I31" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J31" t="str">
-        <v>30000261327</v>
+        <v>30000459302</v>
       </c>
       <c r="K31" t="str">
         <v>State Bank of India</v>
@@ -2712,39 +2760,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M31" t="str">
-        <v>SBIN0003782</v>
+        <v>SBIN0001717</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>0300121</v>
+        <v>0300116</v>
       </c>
       <c r="B32" t="str">
-        <v>AMIT ANSARI</v>
+        <v>AJAY DEVI</v>
       </c>
       <c r="C32" t="str">
-        <v>Branch Manager</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D32" t="str">
-        <v>UCO Bank, Dumri Katsari</v>
+        <v>Bank of India, Purnahiya</v>
       </c>
       <c r="E32" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F32" t="str">
-        <v>9003000121</v>
+        <v>9003000116</v>
       </c>
       <c r="G32" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="H32" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="I32" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J32" t="str">
-        <v>30000958199</v>
+        <v>30000918604</v>
       </c>
       <c r="K32" t="str">
         <v>State Bank of India</v>
@@ -2753,39 +2801,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M32" t="str">
-        <v>SBIN0001577</v>
+        <v>SBIN0009492</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>0300047</v>
+        <v>0300081</v>
       </c>
       <c r="B33" t="str">
-        <v>MAMTA SINHA</v>
+        <v>DINESH MAHTO</v>
       </c>
       <c r="C33" t="str">
-        <v>Accountant</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D33" t="str">
-        <v>PHC Purnahiya No.3</v>
+        <v>District Treasury Sheohar</v>
       </c>
       <c r="E33" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F33" t="str">
-        <v>9003000047</v>
+        <v>9003000081</v>
       </c>
       <c r="G33" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H33" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I33" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J33" t="str">
-        <v>30000372193</v>
+        <v>30000641439</v>
       </c>
       <c r="K33" t="str">
         <v>State Bank of India</v>
@@ -2794,39 +2842,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M33" t="str">
-        <v>SBIN0007816</v>
+        <v>SBIN0004911</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>0300038</v>
+        <v>0300080</v>
       </c>
       <c r="B34" t="str">
-        <v>RAMESH RAI</v>
+        <v>PANKAJ TIWARI</v>
       </c>
       <c r="C34" t="str">
-        <v>Senior Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D34" t="str">
-        <v>Block Office Sheohar</v>
+        <v>PHC Dumri Katsari No.3</v>
       </c>
       <c r="E34" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F34" t="str">
-        <v>9003000038</v>
+        <v>9003000080</v>
       </c>
       <c r="G34" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H34" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="I34" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J34" t="str">
-        <v>30000300922</v>
+        <v>30000633520</v>
       </c>
       <c r="K34" t="str">
         <v>State Bank of India</v>
@@ -2835,39 +2883,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M34" t="str">
-        <v>SBIN0005919</v>
+        <v>SBIN0002681</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>0300078</v>
+        <v>0300056</v>
       </c>
       <c r="B35" t="str">
-        <v>DEEPAK ALAM I</v>
+        <v>RAVI OJHA</v>
       </c>
       <c r="C35" t="str">
-        <v>Office Assistant</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D35" t="str">
-        <v>Block Education Office Piprahi</v>
+        <v>CDPO Office Sheohar</v>
       </c>
       <c r="E35" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F35" t="str">
-        <v>9003000078</v>
+        <v>9003000056</v>
       </c>
       <c r="G35" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H35" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="I35" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J35" t="str">
-        <v>30000617682</v>
+        <v>30000443464</v>
       </c>
       <c r="K35" t="str">
         <v>State Bank of India</v>
@@ -2876,39 +2924,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M35" t="str">
-        <v>SBIN0006165</v>
+        <v>SBIN0006139</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>0300100</v>
+        <v>0300010</v>
       </c>
       <c r="B36" t="str">
-        <v>KUMARI ANJALI GUPTA</v>
+        <v>SURESH KHATUN</v>
       </c>
       <c r="C36" t="str">
-        <v>Junior Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D36" t="str">
-        <v>Minor Irrigation Office Sheohar</v>
+        <v>Middle School Tariyani No.1</v>
       </c>
       <c r="E36" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F36" t="str">
-        <v>9003000100</v>
+        <v>9003000010</v>
       </c>
       <c r="G36" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H36" t="str">
         <v>Sheohar</v>
       </c>
       <c r="I36" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="J36" t="str">
-        <v>30000791900</v>
+        <v>30000079190</v>
       </c>
       <c r="K36" t="str">
         <v>State Bank of India</v>
@@ -2917,39 +2965,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M36" t="str">
-        <v>SBIN0002309</v>
+        <v>SBIN0005392</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>0300043</v>
+        <v>0300039</v>
       </c>
       <c r="B37" t="str">
-        <v>NIRMALA PASWAN</v>
+        <v>RAKESH MISHRA</v>
       </c>
       <c r="C37" t="str">
-        <v>Clerk</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D37" t="str">
-        <v>CDPO Office Purnahiya No.4</v>
+        <v>Middle School Dumri Katsari No.4</v>
       </c>
       <c r="E37" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F37" t="str">
-        <v>9003000043</v>
+        <v>9003000039</v>
       </c>
       <c r="G37" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H37" t="str">
         <v>Sheohar</v>
       </c>
       <c r="I37" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J37" t="str">
-        <v>30000340517</v>
+        <v>30000308841</v>
       </c>
       <c r="K37" t="str">
         <v>State Bank of India</v>
@@ -2958,39 +3006,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M37" t="str">
-        <v>SBIN0004230</v>
+        <v>SBIN0002214</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>0300037</v>
+        <v>0300011</v>
       </c>
       <c r="B38" t="str">
-        <v>MD. IRFAN RAM</v>
+        <v>SHAILESH SINHA</v>
       </c>
       <c r="C38" t="str">
-        <v>Assistant Teacher</v>
+        <v>Section Officer</v>
       </c>
       <c r="D38" t="str">
-        <v>Block Education Office Piprahi</v>
+        <v>Block Office Sheohar</v>
       </c>
       <c r="E38" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F38" t="str">
-        <v>9003000037</v>
+        <v>9003000011</v>
       </c>
       <c r="G38" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H38" t="str">
         <v>Sheohar</v>
       </c>
       <c r="I38" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J38" t="str">
-        <v>30000293003</v>
+        <v>30000087109</v>
       </c>
       <c r="K38" t="str">
         <v>State Bank of India</v>
@@ -2999,39 +3047,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M38" t="str">
-        <v>SBIN0009728</v>
+        <v>SBIN0008478</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>0300040</v>
+        <v>0300094</v>
       </c>
       <c r="B39" t="str">
-        <v>SHAILESH PRASAD</v>
+        <v>SUNITA OJHA</v>
       </c>
       <c r="C39" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D39" t="str">
-        <v>Circle Office Purnahiya No.4</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="E39" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F39" t="str">
-        <v>9003000040</v>
+        <v>9003000094</v>
       </c>
       <c r="G39" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H39" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="I39" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="J39" t="str">
-        <v>30000316760</v>
+        <v>30000744386</v>
       </c>
       <c r="K39" t="str">
         <v>State Bank of India</v>
@@ -3040,39 +3088,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M39" t="str">
-        <v>SBIN0002364</v>
+        <v>SBIN0007434</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>0300017</v>
+        <v>0300104</v>
       </c>
       <c r="B40" t="str">
-        <v>AJAY SINHA</v>
+        <v>SUNITA PANDEY</v>
       </c>
       <c r="C40" t="str">
-        <v>Section Officer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D40" t="str">
-        <v>Block Office Sheohar No.2</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="E40" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F40" t="str">
-        <v>9003000017</v>
+        <v>9003000104</v>
       </c>
       <c r="G40" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H40" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I40" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J40" t="str">
-        <v>30000134623</v>
+        <v>30000823576</v>
       </c>
       <c r="K40" t="str">
         <v>State Bank of India</v>
@@ -3081,39 +3129,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M40" t="str">
-        <v>SBIN0004824</v>
+        <v>SBIN0005687</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>0300016</v>
+        <v>0300112</v>
       </c>
       <c r="B41" t="str">
-        <v>RAVI SINHA</v>
+        <v>PANKAJ GUPTA</v>
       </c>
       <c r="C41" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D41" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>State Bank of India, Dumri Katsari</v>
       </c>
       <c r="E41" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F41" t="str">
-        <v>9003000016</v>
+        <v>9003000112</v>
       </c>
       <c r="G41" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H41" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I41" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J41" t="str">
-        <v>30000126704</v>
+        <v>30000886928</v>
       </c>
       <c r="K41" t="str">
         <v>State Bank of India</v>
@@ -3122,39 +3170,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M41" t="str">
-        <v>SBIN0001778</v>
+        <v>SBIN0001601</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>0300039</v>
+        <v>0300074</v>
       </c>
       <c r="B42" t="str">
-        <v>REKHA ANSARI</v>
+        <v>NEHA SAH</v>
       </c>
       <c r="C42" t="str">
-        <v>Assistant Teacher</v>
+        <v>Teacher</v>
       </c>
       <c r="D42" t="str">
-        <v>Middle School Tariyani</v>
+        <v>Circle Office Dumri Katsari No.4</v>
       </c>
       <c r="E42" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F42" t="str">
-        <v>9003000039</v>
+        <v>9003000074</v>
       </c>
       <c r="G42" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H42" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I42" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J42" t="str">
-        <v>30000308841</v>
+        <v>30000586006</v>
       </c>
       <c r="K42" t="str">
         <v>State Bank of India</v>
@@ -3163,39 +3211,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M42" t="str">
-        <v>SBIN0004529</v>
+        <v>SBIN0009102</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>0300104</v>
+        <v>0300088</v>
       </c>
       <c r="B43" t="str">
-        <v>MUKESH SHARMA</v>
+        <v>KIRAN VERMA</v>
       </c>
       <c r="C43" t="str">
-        <v>Revenue Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D43" t="str">
-        <v>Block Office Sheohar</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="E43" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F43" t="str">
-        <v>9003000104</v>
+        <v>9003000088</v>
       </c>
       <c r="G43" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H43" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I43" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="J43" t="str">
-        <v>30000823576</v>
+        <v>30000696872</v>
       </c>
       <c r="K43" t="str">
         <v>State Bank of India</v>
@@ -3204,39 +3252,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M43" t="str">
-        <v>SBIN0002246</v>
+        <v>SBIN0007139</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>0300005</v>
+        <v>0300107</v>
       </c>
       <c r="B44" t="str">
-        <v>MAMTA YADAV</v>
+        <v>UMESH ANSARI</v>
       </c>
       <c r="C44" t="str">
-        <v>Headmaster</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D44" t="str">
-        <v>High School Purnahiya No.1</v>
+        <v>Punjab National Bank, Dumri Katsari</v>
       </c>
       <c r="E44" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F44" t="str">
-        <v>9003000005</v>
+        <v>9003000107</v>
       </c>
       <c r="G44" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H44" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I44" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J44" t="str">
-        <v>30000039595</v>
+        <v>30000847333</v>
       </c>
       <c r="K44" t="str">
         <v>State Bank of India</v>
@@ -3245,39 +3293,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M44" t="str">
-        <v>SBIN0004279</v>
+        <v>SBIN0001860</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>0300020</v>
+        <v>0300084</v>
       </c>
       <c r="B45" t="str">
-        <v>SAVITA YADAV</v>
+        <v>KUMARI ANJALI ANSARI</v>
       </c>
       <c r="C45" t="str">
-        <v>Headmaster</v>
+        <v>Clerk</v>
       </c>
       <c r="D45" t="str">
-        <v>Project Girls High School Tariyani No.2</v>
+        <v>Middle School Purnahiya No.4</v>
       </c>
       <c r="E45" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F45" t="str">
-        <v>9003000020</v>
+        <v>9003000084</v>
       </c>
       <c r="G45" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H45" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I45" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J45" t="str">
-        <v>30000158380</v>
+        <v>30000665196</v>
       </c>
       <c r="K45" t="str">
         <v>State Bank of India</v>
@@ -3286,39 +3334,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M45" t="str">
-        <v>SBIN0008241</v>
+        <v>SBIN0004505</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>0300107</v>
+        <v>0300082</v>
       </c>
       <c r="B46" t="str">
-        <v>POONAM TIWARI</v>
+        <v>ANITA MAHTO</v>
       </c>
       <c r="C46" t="str">
-        <v>Administrative Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D46" t="str">
-        <v>BSNL Exchange, Piprahi</v>
+        <v>PHC Dumri Katsari No.4</v>
       </c>
       <c r="E46" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F46" t="str">
-        <v>9003000107</v>
+        <v>9003000082</v>
       </c>
       <c r="G46" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H46" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I46" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J46" t="str">
-        <v>30000847333</v>
+        <v>30000649358</v>
       </c>
       <c r="K46" t="str">
         <v>State Bank of India</v>
@@ -3327,39 +3375,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M46" t="str">
-        <v>SBIN0002740</v>
+        <v>SBIN0003052</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0300072</v>
+        <v>0300085</v>
       </c>
       <c r="B47" t="str">
-        <v>AJAY SINHA L</v>
+        <v>MD. IRFAN GUPTA</v>
       </c>
       <c r="C47" t="str">
-        <v>Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D47" t="str">
-        <v>Block Office Tariyani</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="E47" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F47" t="str">
-        <v>9003000072</v>
+        <v>9003000085</v>
       </c>
       <c r="G47" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H47" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I47" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J47" t="str">
-        <v>30000570168</v>
+        <v>30000673115</v>
       </c>
       <c r="K47" t="str">
         <v>State Bank of India</v>
@@ -3368,39 +3416,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M47" t="str">
-        <v>SBIN0001790</v>
+        <v>SBIN0001827</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0300025</v>
+        <v>0300017</v>
       </c>
       <c r="B48" t="str">
-        <v>POONAM PRASAD</v>
+        <v>PANKAJ MISHRA</v>
       </c>
       <c r="C48" t="str">
-        <v>Assistant Teacher</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D48" t="str">
-        <v>Block Office Purnahiya No.2</v>
+        <v>Panchayat Bhawan Piprahi No.4</v>
       </c>
       <c r="E48" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F48" t="str">
-        <v>9003000025</v>
+        <v>9003000017</v>
       </c>
       <c r="G48" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H48" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="I48" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="J48" t="str">
-        <v>30000197975</v>
+        <v>30000134623</v>
       </c>
       <c r="K48" t="str">
         <v>State Bank of India</v>
@@ -3409,39 +3457,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M48" t="str">
-        <v>SBIN0006441</v>
+        <v>SBIN0005930</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0300065</v>
+        <v>0300091</v>
       </c>
       <c r="B49" t="str">
-        <v>MUKESH ALAM</v>
+        <v>NEHA RAI</v>
       </c>
       <c r="C49" t="str">
-        <v>Teacher</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D49" t="str">
-        <v>Block Education Office Purnahiya No.1</v>
+        <v>RWD Sub-Division Sheohar</v>
       </c>
       <c r="E49" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F49" t="str">
-        <v>9003000065</v>
+        <v>9003000091</v>
       </c>
       <c r="G49" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H49" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I49" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J49" t="str">
-        <v>30000514735</v>
+        <v>30000720629</v>
       </c>
       <c r="K49" t="str">
         <v>State Bank of India</v>
@@ -3450,39 +3498,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M49" t="str">
-        <v>SBIN0007309</v>
+        <v>SBIN0007316</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0300004</v>
+        <v>0300048</v>
       </c>
       <c r="B50" t="str">
-        <v>MAMTA PANDEY</v>
+        <v>NITISH GUPTA</v>
       </c>
       <c r="C50" t="str">
-        <v>Headmaster</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D50" t="str">
-        <v>CDPO Office Tariyani No.2</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="E50" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F50" t="str">
-        <v>9003000004</v>
+        <v>9003000048</v>
       </c>
       <c r="G50" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H50" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="I50" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="J50" t="str">
-        <v>30000031676</v>
+        <v>30000380112</v>
       </c>
       <c r="K50" t="str">
         <v>State Bank of India</v>
@@ -3491,39 +3539,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M50" t="str">
-        <v>SBIN0001546</v>
+        <v>SBIN0006386</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>0300086</v>
+        <v>0300034</v>
       </c>
       <c r="B51" t="str">
-        <v>RAVI KHATUN</v>
+        <v>NIRMALA SAH</v>
       </c>
       <c r="C51" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D51" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>Panchayat Bhawan Piprahi</v>
       </c>
       <c r="E51" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="F51" t="str">
-        <v>9003000086</v>
+        <v>9003000034</v>
       </c>
       <c r="G51" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H51" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="I51" t="str">
         <v>Piprahi</v>
       </c>
       <c r="J51" t="str">
-        <v>30000681034</v>
+        <v>30000269246</v>
       </c>
       <c r="K51" t="str">
         <v>State Bank of India</v>
@@ -3532,27 +3580,27 @@
         <v>Sheohar</v>
       </c>
       <c r="M51" t="str">
-        <v>SBIN0004569</v>
+        <v>SBIN0003356</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>0300050</v>
+        <v>0300053</v>
       </c>
       <c r="B52" t="str">
-        <v>NIRMALA MAHTO</v>
+        <v>VINOD SAH</v>
       </c>
       <c r="C52" t="str">
         <v>Revenue Karmachari</v>
       </c>
       <c r="D52" t="str">
-        <v>Project Girls High School Piprahi</v>
+        <v>Block Office Dumri Katsari</v>
       </c>
       <c r="E52" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F52" t="str">
-        <v>9003000050</v>
+        <v>9003000053</v>
       </c>
       <c r="G52" t="str">
         <v>POLLING OFFICER-2</v>
@@ -3561,10 +3609,10 @@
         <v>Purnahiya</v>
       </c>
       <c r="I52" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J52" t="str">
-        <v>30000395950</v>
+        <v>30000419707</v>
       </c>
       <c r="K52" t="str">
         <v>State Bank of India</v>
@@ -3573,39 +3621,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M52" t="str">
-        <v>SBIN0001076</v>
+        <v>SBIN0003196</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>0300058</v>
+        <v>0300003</v>
       </c>
       <c r="B53" t="str">
-        <v>PRIYANKA RAI</v>
+        <v>PRAMOD JHA</v>
       </c>
       <c r="C53" t="str">
-        <v>Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D53" t="str">
-        <v>Block Agriculture Office Purnahiya No.4</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="E53" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F53" t="str">
-        <v>9003000058</v>
+        <v>9003000003</v>
       </c>
       <c r="G53" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H53" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I53" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J53" t="str">
-        <v>30000459302</v>
+        <v>30000023757</v>
       </c>
       <c r="K53" t="str">
         <v>State Bank of India</v>
@@ -3614,39 +3662,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M53" t="str">
-        <v>SBIN0006203</v>
+        <v>SBIN0003273</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>0300092</v>
+        <v>0300036</v>
       </c>
       <c r="B54" t="str">
-        <v>UMESH GUPTA</v>
+        <v>MAHESH MAHTO</v>
       </c>
       <c r="C54" t="str">
-        <v>Assistant Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D54" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Project Girls High School Purnahiya No.2</v>
       </c>
       <c r="E54" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F54" t="str">
-        <v>9003000092</v>
+        <v>9003000036</v>
       </c>
       <c r="G54" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H54" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I54" t="str">
         <v>Purnahiya</v>
       </c>
       <c r="J54" t="str">
-        <v>30000728548</v>
+        <v>30000285084</v>
       </c>
       <c r="K54" t="str">
         <v>State Bank of India</v>
@@ -3655,39 +3703,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M54" t="str">
-        <v>SBIN0004044</v>
+        <v>SBIN0006757</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>0300063</v>
+        <v>0300122</v>
       </c>
       <c r="B55" t="str">
-        <v>KUMARI ANJALI KHATUN</v>
+        <v>NIRMALA RAI</v>
       </c>
       <c r="C55" t="str">
-        <v>Teacher</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D55" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>UCO Bank, Purnahiya</v>
       </c>
       <c r="E55" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F55" t="str">
-        <v>9003000063</v>
+        <v>9003000122</v>
       </c>
       <c r="G55" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H55" t="str">
         <v>Purnahiya</v>
       </c>
       <c r="I55" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J55" t="str">
-        <v>30000498897</v>
+        <v>30000966118</v>
       </c>
       <c r="K55" t="str">
         <v>State Bank of India</v>
@@ -3696,27 +3744,27 @@
         <v>Sheohar</v>
       </c>
       <c r="M55" t="str">
-        <v>SBIN0001393</v>
+        <v>SBIN0003736</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>0300008</v>
+        <v>0300009</v>
       </c>
       <c r="B56" t="str">
-        <v>USHA OJHA</v>
+        <v>NASREEN VERMA</v>
       </c>
       <c r="C56" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D56" t="str">
-        <v>PHC Piprahi No.3</v>
+        <v>CDPO Office Piprahi</v>
       </c>
       <c r="E56" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="F56" t="str">
-        <v>9003000008</v>
+        <v>9003000009</v>
       </c>
       <c r="G56" t="str">
         <v>PRESIDING OFFICER</v>
@@ -3728,7 +3776,7 @@
         <v>Piprahi</v>
       </c>
       <c r="J56" t="str">
-        <v>30000063352</v>
+        <v>30000071271</v>
       </c>
       <c r="K56" t="str">
         <v>State Bank of India</v>
@@ -3737,39 +3785,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M56" t="str">
-        <v>SBIN0004343</v>
+        <v>SBIN0009883</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>0300067</v>
+        <v>0300033</v>
       </c>
       <c r="B57" t="str">
-        <v>SURESH RAI</v>
+        <v>MD. IRFAN PRASAD</v>
       </c>
       <c r="C57" t="str">
-        <v>Clerk</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D57" t="str">
-        <v>High School Sheohar No.2</v>
+        <v>Panchayat Bhawan Dumri Katsari</v>
       </c>
       <c r="E57" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F57" t="str">
-        <v>9003000067</v>
+        <v>9003000033</v>
       </c>
       <c r="G57" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H57" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I57" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J57" t="str">
-        <v>30000530573</v>
+        <v>30000261327</v>
       </c>
       <c r="K57" t="str">
         <v>State Bank of India</v>
@@ -3778,39 +3826,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M57" t="str">
-        <v>SBIN0002093</v>
+        <v>SBIN0008331</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>0300022</v>
+        <v>0300007</v>
       </c>
       <c r="B58" t="str">
-        <v>DEEPAK RAI</v>
+        <v>NITISH VERMA</v>
       </c>
       <c r="C58" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D58" t="str">
-        <v>Primary School Tariyani</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="E58" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F58" t="str">
-        <v>9003000022</v>
+        <v>9003000007</v>
       </c>
       <c r="G58" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H58" t="str">
         <v>Sheohar</v>
       </c>
       <c r="I58" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="J58" t="str">
-        <v>30000174218</v>
+        <v>30000055433</v>
       </c>
       <c r="K58" t="str">
         <v>State Bank of India</v>
@@ -3819,30 +3867,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M58" t="str">
-        <v>SBIN0004758</v>
+        <v>SBIN0001123</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>0300014</v>
+        <v>0300065</v>
       </c>
       <c r="B59" t="str">
-        <v>PRAMOD RAI</v>
+        <v>ANIL TIWARI</v>
       </c>
       <c r="C59" t="str">
-        <v>Assistant Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D59" t="str">
-        <v>Middle School Piprahi</v>
+        <v>Panchayat Bhawan Piprahi No.3</v>
       </c>
       <c r="E59" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="F59" t="str">
-        <v>9003000014</v>
+        <v>9003000065</v>
       </c>
       <c r="G59" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H59" t="str">
         <v>Piprahi</v>
@@ -3851,7 +3899,7 @@
         <v>Piprahi</v>
       </c>
       <c r="J59" t="str">
-        <v>30000110866</v>
+        <v>30000514735</v>
       </c>
       <c r="K59" t="str">
         <v>State Bank of India</v>
@@ -3860,39 +3908,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M59" t="str">
-        <v>SBIN0006689</v>
+        <v>SBIN0009027</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>0300036</v>
+        <v>0300087</v>
       </c>
       <c r="B60" t="str">
-        <v>SAVITA ANSARI</v>
+        <v>RAVI PRASAD P</v>
       </c>
       <c r="C60" t="str">
-        <v>Senior Clerk</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D60" t="str">
-        <v>Block Agriculture Office Piprahi No.3</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="E60" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F60" t="str">
-        <v>9003000036</v>
+        <v>9003000087</v>
       </c>
       <c r="G60" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H60" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="I60" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="J60" t="str">
-        <v>30000285084</v>
+        <v>30000688953</v>
       </c>
       <c r="K60" t="str">
         <v>State Bank of India</v>
@@ -3901,39 +3949,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M60" t="str">
-        <v>SBIN0007179</v>
+        <v>SBIN0002985</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>0300027</v>
+        <v>0300057</v>
       </c>
       <c r="B61" t="str">
-        <v>RAKESH PANDEY</v>
+        <v>KIRAN MISHRA</v>
       </c>
       <c r="C61" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Teacher</v>
       </c>
       <c r="D61" t="str">
-        <v>Middle School Dumri Katsari No.4</v>
+        <v>PHC Dumri Katsari</v>
       </c>
       <c r="E61" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F61" t="str">
-        <v>9003000027</v>
+        <v>9003000057</v>
       </c>
       <c r="G61" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H61" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="I61" t="str">
         <v>Dumri Katsari</v>
       </c>
       <c r="J61" t="str">
-        <v>30000213813</v>
+        <v>30000451383</v>
       </c>
       <c r="K61" t="str">
         <v>State Bank of India</v>
@@ -3942,39 +3990,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M61" t="str">
-        <v>SBIN0006627</v>
+        <v>SBIN0004889</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>0300077</v>
+        <v>0300016</v>
       </c>
       <c r="B62" t="str">
-        <v>NASREEN MISHRA</v>
+        <v>MAHESH SHARMA</v>
       </c>
       <c r="C62" t="str">
-        <v>Office Assistant</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D62" t="str">
-        <v>Panchayat Bhawan Piprahi No.1</v>
+        <v>Kanya Middle School Piprahi No.3</v>
       </c>
       <c r="E62" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="F62" t="str">
-        <v>9003000077</v>
+        <v>9003000016</v>
       </c>
       <c r="G62" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H62" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I62" t="str">
         <v>Piprahi</v>
       </c>
       <c r="J62" t="str">
-        <v>30000609763</v>
+        <v>30000126704</v>
       </c>
       <c r="K62" t="str">
         <v>State Bank of India</v>
@@ -3983,39 +4031,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M62" t="str">
-        <v>SBIN0002491</v>
+        <v>SBIN0008116</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>0300049</v>
+        <v>0300041</v>
       </c>
       <c r="B63" t="str">
-        <v>PANKAJ MAHTO</v>
+        <v>AMIT ALAM</v>
       </c>
       <c r="C63" t="str">
-        <v>Clerk</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D63" t="str">
-        <v>Primary School Purnahiya</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="E63" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F63" t="str">
-        <v>9003000049</v>
+        <v>9003000041</v>
       </c>
       <c r="G63" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H63" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I63" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="J63" t="str">
-        <v>30000388031</v>
+        <v>30000324679</v>
       </c>
       <c r="K63" t="str">
         <v>State Bank of India</v>
@@ -4024,39 +4072,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M63" t="str">
-        <v>SBIN0008227</v>
+        <v>SBIN0004282</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>0300006</v>
+        <v>0300046</v>
       </c>
       <c r="B64" t="str">
-        <v>AMIT RAI</v>
+        <v>RAKESH MISHRA T</v>
       </c>
       <c r="C64" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D64" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>CDPO Office Sheohar No.1</v>
       </c>
       <c r="E64" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F64" t="str">
-        <v>9003000006</v>
+        <v>9003000046</v>
       </c>
       <c r="G64" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H64" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="I64" t="str">
         <v>Sheohar</v>
       </c>
       <c r="J64" t="str">
-        <v>30000047514</v>
+        <v>30000364274</v>
       </c>
       <c r="K64" t="str">
         <v>State Bank of India</v>
@@ -4065,30 +4113,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M64" t="str">
-        <v>SBIN0007649</v>
+        <v>SBIN0002320</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>0300055</v>
+        <v>0300090</v>
       </c>
       <c r="B65" t="str">
-        <v>MD. SHAHID SHARMA</v>
+        <v>RAMESH ALAM</v>
       </c>
       <c r="C65" t="str">
-        <v>Accountant</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D65" t="str">
-        <v>Block Agriculture Office Dumri Katsari No.1</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="E65" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F65" t="str">
-        <v>9003000055</v>
+        <v>9003000090</v>
       </c>
       <c r="G65" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H65" t="str">
         <v>Dumri Katsari</v>
@@ -4097,7 +4145,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="J65" t="str">
-        <v>30000435545</v>
+        <v>30000712710</v>
       </c>
       <c r="K65" t="str">
         <v>State Bank of India</v>
@@ -4106,39 +4154,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M65" t="str">
-        <v>SBIN0007638</v>
+        <v>SBIN0007828</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>0300032</v>
+        <v>0300054</v>
       </c>
       <c r="B66" t="str">
-        <v>SHAILESH MAHTO</v>
+        <v>RAMESH MISHRA</v>
       </c>
       <c r="C66" t="str">
-        <v>Assistant Teacher</v>
+        <v>Accountant</v>
       </c>
       <c r="D66" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>Block Office Sheohar No.1</v>
       </c>
       <c r="E66" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F66" t="str">
-        <v>9003000032</v>
+        <v>9003000054</v>
       </c>
       <c r="G66" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H66" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="I66" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J66" t="str">
-        <v>30000253408</v>
+        <v>30000427626</v>
       </c>
       <c r="K66" t="str">
         <v>State Bank of India</v>
@@ -4147,39 +4195,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M66" t="str">
-        <v>SBIN0002494</v>
+        <v>SBIN0004560</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>0300087</v>
+        <v>0300115</v>
       </c>
       <c r="B67" t="str">
-        <v>RAKESH OJHA</v>
+        <v>MD. IRFAN PRASAD M</v>
       </c>
       <c r="C67" t="str">
-        <v>Revenue Officer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D67" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Punjab National Bank, Dumri Katsari</v>
       </c>
       <c r="E67" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F67" t="str">
-        <v>9003000087</v>
+        <v>9003000115</v>
       </c>
       <c r="G67" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H67" t="str">
         <v>Piprahi</v>
       </c>
       <c r="I67" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J67" t="str">
-        <v>30000688953</v>
+        <v>30000910685</v>
       </c>
       <c r="K67" t="str">
         <v>State Bank of India</v>
@@ -4188,39 +4236,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M67" t="str">
-        <v>SBIN0003524</v>
+        <v>SBIN0009397</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>0300094</v>
+        <v>0300005</v>
       </c>
       <c r="B68" t="str">
-        <v>PANKAJ DEVI</v>
+        <v>ASHA OJHA</v>
       </c>
       <c r="C68" t="str">
-        <v>Junior Engineer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D68" t="str">
-        <v>Block Office Tariyani</v>
+        <v>Kanya Middle School Piprahi No.3</v>
       </c>
       <c r="E68" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F68" t="str">
-        <v>9003000094</v>
+        <v>9003000005</v>
       </c>
       <c r="G68" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H68" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="I68" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="J68" t="str">
-        <v>30000744386</v>
+        <v>30000039595</v>
       </c>
       <c r="K68" t="str">
         <v>State Bank of India</v>
@@ -4229,30 +4277,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M68" t="str">
-        <v>SBIN0006690</v>
+        <v>SBIN0004909</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>0300053</v>
+        <v>0300006</v>
       </c>
       <c r="B69" t="str">
-        <v>DEEPAK ALAM</v>
+        <v>SURESH PRASAD</v>
       </c>
       <c r="C69" t="str">
-        <v>Teacher</v>
+        <v>Headmaster</v>
       </c>
       <c r="D69" t="str">
-        <v>High School Piprahi No.1</v>
+        <v>CDPO Office Piprahi No.3</v>
       </c>
       <c r="E69" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="F69" t="str">
-        <v>9003000053</v>
+        <v>9003000006</v>
       </c>
       <c r="G69" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H69" t="str">
         <v>Piprahi</v>
@@ -4261,7 +4309,7 @@
         <v>Piprahi</v>
       </c>
       <c r="J69" t="str">
-        <v>30000419707</v>
+        <v>30000047514</v>
       </c>
       <c r="K69" t="str">
         <v>State Bank of India</v>
@@ -4270,39 +4318,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M69" t="str">
-        <v>SBIN0004061</v>
+        <v>SBIN0008480</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>0300018</v>
+        <v>0300042</v>
       </c>
       <c r="B70" t="str">
-        <v>SANJAY ALAM</v>
+        <v>SUNITA SINGH</v>
       </c>
       <c r="C70" t="str">
-        <v>Section Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D70" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>Block Education Office Sheohar</v>
       </c>
       <c r="E70" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F70" t="str">
-        <v>9003000018</v>
+        <v>9003000042</v>
       </c>
       <c r="G70" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H70" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I70" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="J70" t="str">
-        <v>30000142542</v>
+        <v>30000332598</v>
       </c>
       <c r="K70" t="str">
         <v>State Bank of India</v>
@@ -4311,39 +4359,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M70" t="str">
-        <v>SBIN0007179</v>
+        <v>SBIN0001203</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>0300011</v>
+        <v>0300073</v>
       </c>
       <c r="B71" t="str">
-        <v>RAMESH PRASAD</v>
+        <v>NEHA PRASAD</v>
       </c>
       <c r="C71" t="str">
-        <v>Lecturer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D71" t="str">
-        <v>High School Sheohar</v>
+        <v>Middle School Dumri Katsari No.3</v>
       </c>
       <c r="E71" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F71" t="str">
-        <v>9003000011</v>
+        <v>9003000073</v>
       </c>
       <c r="G71" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H71" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I71" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J71" t="str">
-        <v>30000087109</v>
+        <v>30000578087</v>
       </c>
       <c r="K71" t="str">
         <v>State Bank of India</v>
@@ -4352,39 +4400,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M71" t="str">
-        <v>SBIN0006874</v>
+        <v>SBIN0007924</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>0300057</v>
+        <v>0300051</v>
       </c>
       <c r="B72" t="str">
-        <v>FARHAT KHATUN</v>
+        <v>KIRAN OJHA</v>
       </c>
       <c r="C72" t="str">
-        <v>Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D72" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>CDPO Office Purnahiya</v>
       </c>
       <c r="E72" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F72" t="str">
-        <v>9003000057</v>
+        <v>9003000051</v>
       </c>
       <c r="G72" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="H72" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I72" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J72" t="str">
-        <v>30000451383</v>
+        <v>30000403869</v>
       </c>
       <c r="K72" t="str">
         <v>State Bank of India</v>
@@ -4393,39 +4441,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M72" t="str">
-        <v>SBIN0005285</v>
+        <v>SBIN0009725</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>0300112</v>
+        <v>0300103</v>
       </c>
       <c r="B73" t="str">
-        <v>ANITA KHATUN</v>
+        <v>RAKESH SINGH</v>
       </c>
       <c r="C73" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D73" t="str">
-        <v>Bank of India, Dumri Katsari</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="E73" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F73" t="str">
-        <v>9003000112</v>
+        <v>9003000103</v>
       </c>
       <c r="G73" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H73" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I73" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="J73" t="str">
-        <v>30000886928</v>
+        <v>30000815657</v>
       </c>
       <c r="K73" t="str">
         <v>State Bank of India</v>
@@ -4434,39 +4482,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M73" t="str">
-        <v>SBIN0006817</v>
+        <v>SBIN0002976</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>0300042</v>
+        <v>0300038</v>
       </c>
       <c r="B74" t="str">
-        <v>PANKAJ THAKUR</v>
+        <v>DEEPAK JHA</v>
       </c>
       <c r="C74" t="str">
-        <v>Assistant Teacher</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D74" t="str">
-        <v>Kanya Middle School Dumri Katsari No.4</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="E74" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F74" t="str">
-        <v>9003000042</v>
+        <v>9003000038</v>
       </c>
       <c r="G74" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="H74" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I74" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="J74" t="str">
-        <v>30000332598</v>
+        <v>30000300922</v>
       </c>
       <c r="K74" t="str">
         <v>State Bank of India</v>
@@ -4475,39 +4523,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M74" t="str">
-        <v>SBIN0009328</v>
+        <v>SBIN0005616</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>0300015</v>
+        <v>0300120</v>
       </c>
       <c r="B75" t="str">
-        <v>POONAM MAHTO</v>
+        <v>MAHESH SAH</v>
       </c>
       <c r="C75" t="str">
-        <v>Assistant Engineer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D75" t="str">
-        <v>CDPO Office Piprahi No.2</v>
+        <v>UCO Bank, Piprahi</v>
       </c>
       <c r="E75" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="F75" t="str">
-        <v>9003000015</v>
+        <v>9003000120</v>
       </c>
       <c r="G75" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H75" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="I75" t="str">
         <v>Piprahi</v>
       </c>
       <c r="J75" t="str">
-        <v>30000118785</v>
+        <v>30000950280</v>
       </c>
       <c r="K75" t="str">
         <v>State Bank of India</v>
@@ -4516,39 +4564,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M75" t="str">
-        <v>SBIN0008944</v>
+        <v>SBIN0003150</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>0300102</v>
+        <v>0300013</v>
       </c>
       <c r="B76" t="str">
-        <v>ANIL SAH</v>
+        <v>SHAILESH ALAM</v>
       </c>
       <c r="C76" t="str">
-        <v>Junior Engineer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D76" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="E76" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F76" t="str">
-        <v>9003000102</v>
+        <v>9003000013</v>
       </c>
       <c r="G76" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H76" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="I76" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J76" t="str">
-        <v>30000807738</v>
+        <v>30000102947</v>
       </c>
       <c r="K76" t="str">
         <v>State Bank of India</v>
@@ -4557,39 +4605,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M76" t="str">
-        <v>SBIN0005286</v>
+        <v>SBIN0008023</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>0300029</v>
+        <v>0300077</v>
       </c>
       <c r="B77" t="str">
-        <v>SUNIL THAKUR</v>
+        <v>REKHA GUPTA</v>
       </c>
       <c r="C77" t="str">
-        <v>Assistant Teacher</v>
+        <v>Teacher</v>
       </c>
       <c r="D77" t="str">
-        <v>Panchayat Bhawan Dumri Katsari No.3</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="E77" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F77" t="str">
-        <v>9003000029</v>
+        <v>9003000077</v>
       </c>
       <c r="G77" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H77" t="str">
         <v>Purnahiya</v>
       </c>
       <c r="I77" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="J77" t="str">
-        <v>30000229651</v>
+        <v>30000609763</v>
       </c>
       <c r="K77" t="str">
         <v>State Bank of India</v>
@@ -4598,39 +4646,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M77" t="str">
-        <v>SBIN0009660</v>
+        <v>SBIN0005667</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>0300084</v>
+        <v>0300109</v>
       </c>
       <c r="B78" t="str">
-        <v>MD. IRFAN ALAM</v>
+        <v>POONAM PANDEY</v>
       </c>
       <c r="C78" t="str">
-        <v>Clerk</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D78" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>State Bank of India, Purnahiya</v>
       </c>
       <c r="E78" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F78" t="str">
-        <v>9003000084</v>
+        <v>9003000109</v>
       </c>
       <c r="G78" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H78" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="I78" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="I78" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="J78" t="str">
-        <v>30000665196</v>
+        <v>30000863171</v>
       </c>
       <c r="K78" t="str">
         <v>State Bank of India</v>
@@ -4639,39 +4687,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M78" t="str">
-        <v>SBIN0007723</v>
+        <v>SBIN0002365</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0300083</v>
+        <v>0300119</v>
       </c>
       <c r="B79" t="str">
-        <v>MAHESH ANSARI</v>
+        <v>PRIYANKA SHARMA</v>
       </c>
       <c r="C79" t="str">
-        <v>Office Assistant</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D79" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>BSNL Exchange, Purnahiya</v>
       </c>
       <c r="E79" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F79" t="str">
-        <v>9003000083</v>
+        <v>9003000119</v>
       </c>
       <c r="G79" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H79" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I79" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J79" t="str">
-        <v>30000657277</v>
+        <v>30000942361</v>
       </c>
       <c r="K79" t="str">
         <v>State Bank of India</v>
@@ -4680,39 +4728,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M79" t="str">
-        <v>SBIN0006979</v>
+        <v>SBIN0008612</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>0300021</v>
+        <v>0300105</v>
       </c>
       <c r="B80" t="str">
-        <v>KUMARI ANJALI VERMA</v>
+        <v>SANJAY PANDEY</v>
       </c>
       <c r="C80" t="str">
-        <v>Senior Teacher</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D80" t="str">
-        <v>CDPO Office Sheohar No.4</v>
+        <v>RWD Sub-Division Tariyani</v>
       </c>
       <c r="E80" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F80" t="str">
-        <v>9003000021</v>
+        <v>9003000105</v>
       </c>
       <c r="G80" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H80" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I80" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="J80" t="str">
-        <v>30000166299</v>
+        <v>30000831495</v>
       </c>
       <c r="K80" t="str">
         <v>State Bank of India</v>
@@ -4721,39 +4769,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M80" t="str">
-        <v>SBIN0004864</v>
+        <v>SBIN0001798</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>0300030</v>
+        <v>0300001</v>
       </c>
       <c r="B81" t="str">
-        <v>SUNIL PANDEY</v>
+        <v>SANJAY MISHRA</v>
       </c>
       <c r="C81" t="str">
-        <v>Assistant Teacher</v>
+        <v>Headmaster</v>
       </c>
       <c r="D81" t="str">
-        <v>Block Education Office Sheohar No.3</v>
+        <v>CDPO Office Purnahiya No.2</v>
       </c>
       <c r="E81" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F81" t="str">
-        <v>9003000030</v>
+        <v>9003000001</v>
       </c>
       <c r="G81" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H81" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I81" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J81" t="str">
-        <v>30000237570</v>
+        <v>30000007919</v>
       </c>
       <c r="K81" t="str">
         <v>State Bank of India</v>
@@ -4762,39 +4810,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M81" t="str">
-        <v>SBIN0002783</v>
+        <v>SBIN0001721</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>0300103</v>
+        <v>0300124</v>
       </c>
       <c r="B82" t="str">
-        <v>VIJAY CHAUDHARY</v>
+        <v>USHA YADAV</v>
       </c>
       <c r="C82" t="str">
-        <v>Revenue Officer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D82" t="str">
-        <v>Block Office Sheohar</v>
+        <v>Central Bank of India, Piprahi</v>
       </c>
       <c r="E82" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F82" t="str">
-        <v>9003000103</v>
+        <v>9003000124</v>
       </c>
       <c r="G82" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H82" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I82" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J82" t="str">
-        <v>30000815657</v>
+        <v>30000981956</v>
       </c>
       <c r="K82" t="str">
         <v>State Bank of India</v>
@@ -4803,39 +4851,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M82" t="str">
-        <v>SBIN0008904</v>
+        <v>SBIN0001802</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>0300088</v>
+        <v>0300096</v>
       </c>
       <c r="B83" t="str">
-        <v>ANIL MAHTO</v>
+        <v>DEEPAK MISHRA</v>
       </c>
       <c r="C83" t="str">
-        <v>Assistant Engineer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D83" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="E83" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F83" t="str">
-        <v>9003000088</v>
+        <v>9003000096</v>
       </c>
       <c r="G83" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H83" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="I83" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="J83" t="str">
-        <v>30000696872</v>
+        <v>30000760224</v>
       </c>
       <c r="K83" t="str">
         <v>State Bank of India</v>
@@ -4844,39 +4892,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M83" t="str">
-        <v>SBIN0006112</v>
+        <v>SBIN0002481</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>0300085</v>
+        <v>0300083</v>
       </c>
       <c r="B84" t="str">
-        <v>RAVI CHAUDHARY</v>
+        <v>ANITA RAM</v>
       </c>
       <c r="C84" t="str">
-        <v>Revenue Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D84" t="str">
-        <v>Block Office Tariyani</v>
+        <v>Primary School Piprahi No.2</v>
       </c>
       <c r="E84" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F84" t="str">
-        <v>9003000085</v>
+        <v>9003000083</v>
       </c>
       <c r="G84" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H84" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I84" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="J84" t="str">
-        <v>30000673115</v>
+        <v>30000657277</v>
       </c>
       <c r="K84" t="str">
         <v>State Bank of India</v>
@@ -4885,39 +4933,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M84" t="str">
-        <v>SBIN0006691</v>
+        <v>SBIN0002527</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>0300074</v>
+        <v>0300019</v>
       </c>
       <c r="B85" t="str">
-        <v>MAMTA SHARMA</v>
+        <v>MD. SHAHID GUPTA</v>
       </c>
       <c r="C85" t="str">
-        <v>Data Entry Operator</v>
+        <v>Section Officer</v>
       </c>
       <c r="D85" t="str">
-        <v>CDPO Office Piprahi No.4</v>
+        <v>PHC Purnahiya</v>
       </c>
       <c r="E85" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F85" t="str">
-        <v>9003000074</v>
+        <v>9003000019</v>
       </c>
       <c r="G85" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H85" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I85" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J85" t="str">
-        <v>30000586006</v>
+        <v>30000150461</v>
       </c>
       <c r="K85" t="str">
         <v>State Bank of India</v>
@@ -4926,39 +4974,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M85" t="str">
-        <v>SBIN0004439</v>
+        <v>SBIN0004236</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>0300089</v>
+        <v>0300027</v>
       </c>
       <c r="B86" t="str">
-        <v>RAJESH VERMA</v>
+        <v>SURESH ANSARI</v>
       </c>
       <c r="C86" t="str">
-        <v>Revenue Officer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D86" t="str">
-        <v>RWD Sub-Division Sheohar</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="E86" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F86" t="str">
-        <v>9003000089</v>
+        <v>9003000027</v>
       </c>
       <c r="G86" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H86" t="str">
         <v>Sheohar</v>
       </c>
       <c r="I86" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J86" t="str">
-        <v>30000704791</v>
+        <v>30000213813</v>
       </c>
       <c r="K86" t="str">
         <v>State Bank of India</v>
@@ -4967,27 +5015,27 @@
         <v>Sheohar</v>
       </c>
       <c r="M86" t="str">
-        <v>SBIN0005718</v>
+        <v>SBIN0003252</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>0300119</v>
+        <v>0300126</v>
       </c>
       <c r="B87" t="str">
-        <v>MD. SHAHID KUMAR</v>
+        <v>MD. IRFAN DEVI</v>
       </c>
       <c r="C87" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D87" t="str">
-        <v>Head Post Office, Dumri Katsari</v>
+        <v>Central Bank of India, Piprahi</v>
       </c>
       <c r="E87" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F87" t="str">
-        <v>9003000119</v>
+        <v>9003000126</v>
       </c>
       <c r="G87" t="str">
         <v>MICRO OBSERVER</v>
@@ -4996,10 +5044,10 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="I87" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="J87" t="str">
-        <v>30000942361</v>
+        <v>30000997794</v>
       </c>
       <c r="K87" t="str">
         <v>State Bank of India</v>
@@ -5008,39 +5056,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M87" t="str">
-        <v>SBIN0009211</v>
+        <v>SBIN0001441</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>0300076</v>
+        <v>0300099</v>
       </c>
       <c r="B88" t="str">
-        <v>SANJAY SINHA</v>
+        <v>RAMESH MAHTO</v>
       </c>
       <c r="C88" t="str">
-        <v>Office Assistant</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D88" t="str">
-        <v>Block Office Dumri Katsari No.2</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="E88" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F88" t="str">
-        <v>9003000076</v>
+        <v>9003000099</v>
       </c>
       <c r="G88" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H88" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="I88" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="J88" t="str">
-        <v>30000601844</v>
+        <v>30000783981</v>
       </c>
       <c r="K88" t="str">
         <v>State Bank of India</v>
@@ -5049,39 +5097,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M88" t="str">
-        <v>SBIN0004899</v>
+        <v>SBIN0009459</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>0300117</v>
+        <v>0300069</v>
       </c>
       <c r="B89" t="str">
-        <v>NITISH VERMA</v>
+        <v>RAVI ANSARI</v>
       </c>
       <c r="C89" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D89" t="str">
-        <v>State Bank of India, Piprahi</v>
+        <v>Panchayat Bhawan Sheohar</v>
       </c>
       <c r="E89" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F89" t="str">
-        <v>9003000117</v>
+        <v>9003000069</v>
       </c>
       <c r="G89" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H89" t="str">
         <v>Piprahi</v>
       </c>
       <c r="I89" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J89" t="str">
-        <v>30000926523</v>
+        <v>30000546411</v>
       </c>
       <c r="K89" t="str">
         <v>State Bank of India</v>
@@ -5090,39 +5138,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M89" t="str">
-        <v>SBIN0003420</v>
+        <v>SBIN0006768</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>0300069</v>
+        <v>0300111</v>
       </c>
       <c r="B90" t="str">
-        <v>REKHA KHATUN</v>
+        <v>SURESH PRASAD Q</v>
       </c>
       <c r="C90" t="str">
-        <v>Clerk</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D90" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>Bank of India, Purnahiya</v>
       </c>
       <c r="E90" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F90" t="str">
-        <v>9003000069</v>
+        <v>9003000111</v>
       </c>
       <c r="G90" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H90" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="I90" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="I90" t="str">
-        <v>Dumri Katsari</v>
-      </c>
       <c r="J90" t="str">
-        <v>30000546411</v>
+        <v>30000879009</v>
       </c>
       <c r="K90" t="str">
         <v>State Bank of India</v>
@@ -5131,39 +5179,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M90" t="str">
-        <v>SBIN0004285</v>
+        <v>SBIN0004784</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>0300059</v>
+        <v>0300047</v>
       </c>
       <c r="B91" t="str">
-        <v>RAVI OJHA</v>
+        <v>SANJAY TIWARI</v>
       </c>
       <c r="C91" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Clerk</v>
       </c>
       <c r="D91" t="str">
-        <v>Middle School Purnahiya No.2</v>
+        <v>Middle School Purnahiya No.3</v>
       </c>
       <c r="E91" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F91" t="str">
-        <v>9003000059</v>
+        <v>9003000047</v>
       </c>
       <c r="G91" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="H91" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I91" t="str">
         <v>Purnahiya</v>
       </c>
       <c r="J91" t="str">
-        <v>30000467221</v>
+        <v>30000372193</v>
       </c>
       <c r="K91" t="str">
         <v>State Bank of India</v>
@@ -5172,39 +5220,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M91" t="str">
-        <v>SBIN0001491</v>
+        <v>SBIN0003576</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>0300101</v>
+        <v>0300118</v>
       </c>
       <c r="B92" t="str">
-        <v>ANIL RAI</v>
+        <v>SHAILESH PANDEY</v>
       </c>
       <c r="C92" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D92" t="str">
-        <v>RWD Sub-Division Tariyani</v>
+        <v>UCO Bank, Dumri Katsari</v>
       </c>
       <c r="E92" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F92" t="str">
-        <v>9003000101</v>
+        <v>9003000118</v>
       </c>
       <c r="G92" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H92" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="I92" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I92" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="J92" t="str">
-        <v>30000799819</v>
+        <v>30000934442</v>
       </c>
       <c r="K92" t="str">
         <v>State Bank of India</v>
@@ -5213,39 +5261,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M92" t="str">
-        <v>SBIN0007172</v>
+        <v>SBIN0001771</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>0300041</v>
+        <v>0300098</v>
       </c>
       <c r="B93" t="str">
-        <v>SHAILESH JHA</v>
+        <v>SURESH SAH</v>
       </c>
       <c r="C93" t="str">
-        <v>Head Clerk</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D93" t="str">
-        <v>PHC Purnahiya</v>
+        <v>RWD Sub-Division Piprahi</v>
       </c>
       <c r="E93" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F93" t="str">
-        <v>9003000041</v>
+        <v>9003000098</v>
       </c>
       <c r="G93" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H93" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="I93" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="J93" t="str">
-        <v>30000324679</v>
+        <v>30000776062</v>
       </c>
       <c r="K93" t="str">
         <v>State Bank of India</v>
@@ -5254,39 +5302,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M93" t="str">
-        <v>SBIN0008013</v>
+        <v>SBIN0007719</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>0300118</v>
+        <v>0300117</v>
       </c>
       <c r="B94" t="str">
-        <v>ASHA KHATUN</v>
+        <v>RANJIT GUPTA</v>
       </c>
       <c r="C94" t="str">
-        <v>Branch Manager</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D94" t="str">
-        <v>LIC Branch Office, Piprahi</v>
+        <v>Bank of India, Purnahiya</v>
       </c>
       <c r="E94" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F94" t="str">
-        <v>9003000118</v>
+        <v>9003000117</v>
       </c>
       <c r="G94" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="H94" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I94" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J94" t="str">
-        <v>30000934442</v>
+        <v>30000926523</v>
       </c>
       <c r="K94" t="str">
         <v>State Bank of India</v>
@@ -5295,39 +5343,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M94" t="str">
-        <v>SBIN0002716</v>
+        <v>SBIN0005816</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>0300110</v>
+        <v>0300025</v>
       </c>
       <c r="B95" t="str">
-        <v>SAVITA PANDEY</v>
+        <v>ALOK TIWARI</v>
       </c>
       <c r="C95" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D95" t="str">
-        <v>Punjab National Bank, Piprahi</v>
+        <v>Block Education Office Sheohar</v>
       </c>
       <c r="E95" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F95" t="str">
-        <v>9003000110</v>
+        <v>9003000025</v>
       </c>
       <c r="G95" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H95" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="I95" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J95" t="str">
-        <v>30000871090</v>
+        <v>30000197975</v>
       </c>
       <c r="K95" t="str">
         <v>State Bank of India</v>
@@ -5336,30 +5384,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M95" t="str">
-        <v>SBIN0009637</v>
+        <v>SBIN0008915</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>0300090</v>
+        <v>0300125</v>
       </c>
       <c r="B96" t="str">
-        <v>RINKU PRASAD</v>
+        <v>NIRMALA THAKUR</v>
       </c>
       <c r="C96" t="str">
-        <v>Revenue Officer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D96" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>State Bank of India, Purnahiya</v>
       </c>
       <c r="E96" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F96" t="str">
-        <v>9003000090</v>
+        <v>9003000125</v>
       </c>
       <c r="G96" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H96" t="str">
         <v>Purnahiya</v>
@@ -5368,7 +5416,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="J96" t="str">
-        <v>30000712710</v>
+        <v>30000989875</v>
       </c>
       <c r="K96" t="str">
         <v>State Bank of India</v>
@@ -5377,39 +5425,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M96" t="str">
-        <v>SBIN0003047</v>
+        <v>SBIN0005619</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0300007</v>
+        <v>0300035</v>
       </c>
       <c r="B97" t="str">
-        <v>ARVIND SINHA</v>
+        <v>DEEPAK PASWAN</v>
       </c>
       <c r="C97" t="str">
-        <v>Senior Teacher</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D97" t="str">
-        <v>Block Education Office Tariyani No.2</v>
+        <v>Block Education Office Piprahi</v>
       </c>
       <c r="E97" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F97" t="str">
-        <v>9003000007</v>
+        <v>9003000035</v>
       </c>
       <c r="G97" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H97" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I97" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="J97" t="str">
-        <v>30000055433</v>
+        <v>30000277165</v>
       </c>
       <c r="K97" t="str">
         <v>State Bank of India</v>
@@ -5418,39 +5466,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M97" t="str">
-        <v>SBIN0006534</v>
+        <v>SBIN0005522</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>0300001</v>
+        <v>0300040</v>
       </c>
       <c r="B98" t="str">
-        <v>REKHA PANDEY</v>
+        <v>RAVI JHA</v>
       </c>
       <c r="C98" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D98" t="str">
-        <v>Circle Office Purnahiya No.2</v>
+        <v>PHC Tariyani</v>
       </c>
       <c r="E98" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F98" t="str">
-        <v>9003000001</v>
+        <v>9003000040</v>
       </c>
       <c r="G98" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H98" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I98" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="J98" t="str">
-        <v>30000007919</v>
+        <v>30000316760</v>
       </c>
       <c r="K98" t="str">
         <v>State Bank of India</v>
@@ -5459,39 +5507,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M98" t="str">
-        <v>SBIN0007948</v>
+        <v>SBIN0007869</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>0300115</v>
+        <v>0300078</v>
       </c>
       <c r="B99" t="str">
-        <v>KUMARI ANJALI VERMA M</v>
+        <v>MUKESH JHA</v>
       </c>
       <c r="C99" t="str">
-        <v>Administrative Officer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D99" t="str">
-        <v>BSNL Exchange, Sheohar</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="E99" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F99" t="str">
-        <v>9003000115</v>
+        <v>9003000078</v>
       </c>
       <c r="G99" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H99" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I99" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J99" t="str">
-        <v>30000910685</v>
+        <v>30000617682</v>
       </c>
       <c r="K99" t="str">
         <v>State Bank of India</v>
@@ -5500,39 +5548,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M99" t="str">
-        <v>SBIN0009440</v>
+        <v>SBIN0004311</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>0300012</v>
+        <v>0300072</v>
       </c>
       <c r="B100" t="str">
-        <v>PRAMOD VERMA</v>
+        <v>UMESH TIWARI</v>
       </c>
       <c r="C100" t="str">
-        <v>Section Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D100" t="str">
-        <v>Panchayat Bhawan Tariyani</v>
+        <v>Primary School Dumri Katsari</v>
       </c>
       <c r="E100" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F100" t="str">
-        <v>9003000012</v>
+        <v>9003000072</v>
       </c>
       <c r="G100" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H100" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="I100" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I100" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="J100" t="str">
-        <v>30000095028</v>
+        <v>30000570168</v>
       </c>
       <c r="K100" t="str">
         <v>State Bank of India</v>
@@ -5541,39 +5589,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M100" t="str">
-        <v>SBIN0007899</v>
+        <v>SBIN0009826</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>0300126</v>
+        <v>0300044</v>
       </c>
       <c r="B101" t="str">
-        <v>PANKAJ SINGH</v>
+        <v>PRAMOD CHAUDHARY</v>
       </c>
       <c r="C101" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Accountant</v>
       </c>
       <c r="D101" t="str">
-        <v>BSNL Exchange, Sheohar</v>
+        <v>High School Sheohar No.1</v>
       </c>
       <c r="E101" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F101" t="str">
-        <v>9003000126</v>
+        <v>9003000044</v>
       </c>
       <c r="G101" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H101" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I101" t="str">
         <v>Sheohar</v>
       </c>
       <c r="J101" t="str">
-        <v>30000997794</v>
+        <v>30000348436</v>
       </c>
       <c r="K101" t="str">
         <v>State Bank of India</v>
@@ -5582,18 +5630,18 @@
         <v>Sheohar</v>
       </c>
       <c r="M101" t="str">
-        <v>SBIN0002889</v>
+        <v>SBIN0009782</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>0300066</v>
+        <v>0300071</v>
       </c>
       <c r="B102" t="str">
-        <v>SAVITA SHARMA</v>
+        <v>MD. IRFAN PANDEY</v>
       </c>
       <c r="C102" t="str">
-        <v>Teacher</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D102" t="str">
         <v>RWD Division Sheohar</v>
@@ -5602,19 +5650,19 @@
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F102" t="str">
-        <v>9003000066</v>
+        <v>9003000071</v>
       </c>
       <c r="G102" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="H102" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="I102" t="str">
         <v>Sheohar</v>
       </c>
       <c r="J102" t="str">
-        <v>30000522654</v>
+        <v>30000562249</v>
       </c>
       <c r="K102" t="str">
         <v>State Bank of India</v>
@@ -5623,39 +5671,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M102" t="str">
-        <v>SBIN0008176</v>
+        <v>SBIN0007042</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>0300124</v>
+        <v>0300102</v>
       </c>
       <c r="B103" t="str">
-        <v>RAMESH JHA</v>
+        <v>MANOJ PRASAD</v>
       </c>
       <c r="C103" t="str">
-        <v>Administrative Officer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D103" t="str">
-        <v>Central Bank of India, Dumri Katsari</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="E103" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F103" t="str">
-        <v>9003000124</v>
+        <v>9003000102</v>
       </c>
       <c r="G103" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H103" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="I103" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="J103" t="str">
-        <v>30000981956</v>
+        <v>30000807738</v>
       </c>
       <c r="K103" t="str">
         <v>State Bank of India</v>
@@ -5664,39 +5712,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M103" t="str">
-        <v>SBIN0009965</v>
+        <v>SBIN0005193</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>0300125</v>
+        <v>0300022</v>
       </c>
       <c r="B104" t="str">
-        <v>ALOK DEVI</v>
+        <v>MAMTA DEVI</v>
       </c>
       <c r="C104" t="str">
-        <v>Postmaster</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D104" t="str">
-        <v>Punjab National Bank, Purnahiya</v>
+        <v>PHC Piprahi No.1</v>
       </c>
       <c r="E104" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F104" t="str">
-        <v>9003000125</v>
+        <v>9003000022</v>
       </c>
       <c r="G104" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H104" t="str">
         <v>Piprahi</v>
       </c>
       <c r="I104" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="J104" t="str">
-        <v>30000989875</v>
+        <v>30000174218</v>
       </c>
       <c r="K104" t="str">
         <v>State Bank of India</v>
@@ -5705,39 +5753,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M104" t="str">
-        <v>SBIN0002315</v>
+        <v>SBIN0006475</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>0300051</v>
+        <v>0300086</v>
       </c>
       <c r="B105" t="str">
-        <v>UMESH YADAV</v>
+        <v>AMIT KHATUN</v>
       </c>
       <c r="C105" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D105" t="str">
-        <v>Primary School Sheohar</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="E105" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F105" t="str">
-        <v>9003000051</v>
+        <v>9003000086</v>
       </c>
       <c r="G105" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H105" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I105" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J105" t="str">
-        <v>30000403869</v>
+        <v>30000681034</v>
       </c>
       <c r="K105" t="str">
         <v>State Bank of India</v>
@@ -5746,39 +5794,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M105" t="str">
-        <v>SBIN0008453</v>
+        <v>SBIN0001640</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>0300031</v>
+        <v>0300018</v>
       </c>
       <c r="B106" t="str">
-        <v>FARHAT DEVI</v>
+        <v>SAVITA SINHA</v>
       </c>
       <c r="C106" t="str">
-        <v>Senior Clerk</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D106" t="str">
-        <v>PHC Purnahiya No.4</v>
+        <v>Circle Office Sheohar</v>
       </c>
       <c r="E106" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F106" t="str">
-        <v>9003000031</v>
+        <v>9003000018</v>
       </c>
       <c r="G106" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H106" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I106" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J106" t="str">
-        <v>30000245489</v>
+        <v>30000142542</v>
       </c>
       <c r="K106" t="str">
         <v>State Bank of India</v>
@@ -5787,39 +5835,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M106" t="str">
-        <v>SBIN0002216</v>
+        <v>SBIN0006453</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>0300122</v>
+        <v>0300063</v>
       </c>
       <c r="B107" t="str">
-        <v>MANOJ SINHA</v>
+        <v>SHAILESH SHARMA</v>
       </c>
       <c r="C107" t="str">
-        <v>Administrative Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D107" t="str">
-        <v>Central Bank of India, Sheohar</v>
+        <v>Block Agriculture Office Purnahiya No.1</v>
       </c>
       <c r="E107" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F107" t="str">
-        <v>9003000122</v>
+        <v>9003000063</v>
       </c>
       <c r="G107" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H107" t="str">
         <v>Tariyani</v>
       </c>
       <c r="I107" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J107" t="str">
-        <v>30000966118</v>
+        <v>30000498897</v>
       </c>
       <c r="K107" t="str">
         <v>State Bank of India</v>
@@ -5828,39 +5876,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M107" t="str">
-        <v>SBIN0005090</v>
+        <v>SBIN0008111</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>0300024</v>
+        <v>0300029</v>
       </c>
       <c r="B108" t="str">
-        <v>MANOJ RAI</v>
+        <v>ARVIND MISHRA</v>
       </c>
       <c r="C108" t="str">
         <v>Panchayat Secretary</v>
       </c>
       <c r="D108" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Middle School Piprahi No.3</v>
       </c>
       <c r="E108" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F108" t="str">
-        <v>9003000024</v>
+        <v>9003000029</v>
       </c>
       <c r="G108" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="H108" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I108" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J108" t="str">
-        <v>30000190056</v>
+        <v>30000229651</v>
       </c>
       <c r="K108" t="str">
         <v>State Bank of India</v>
@@ -5869,39 +5917,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M108" t="str">
-        <v>SBIN0005225</v>
+        <v>SBIN0008875</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>0300109</v>
+        <v>0300055</v>
       </c>
       <c r="B109" t="str">
-        <v>ASHA DEVI</v>
+        <v>DINESH SINHA</v>
       </c>
       <c r="C109" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D109" t="str">
-        <v>BSNL Exchange, Sheohar</v>
+        <v>High School Dumri Katsari No.4</v>
       </c>
       <c r="E109" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F109" t="str">
-        <v>9003000109</v>
+        <v>9003000055</v>
       </c>
       <c r="G109" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H109" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I109" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J109" t="str">
-        <v>30000863171</v>
+        <v>30000435545</v>
       </c>
       <c r="K109" t="str">
         <v>State Bank of India</v>
@@ -5910,39 +5958,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M109" t="str">
-        <v>SBIN0008773</v>
+        <v>SBIN0005117</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>0300035</v>
+        <v>0300052</v>
       </c>
       <c r="B110" t="str">
-        <v>SUNIL PASWAN</v>
+        <v>ASHA TIWARI</v>
       </c>
       <c r="C110" t="str">
-        <v>Senior Clerk</v>
+        <v>Clerk</v>
       </c>
       <c r="D110" t="str">
-        <v>Circle Office Piprahi No.4</v>
+        <v>High School Dumri Katsari No.1</v>
       </c>
       <c r="E110" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F110" t="str">
-        <v>9003000035</v>
+        <v>9003000052</v>
       </c>
       <c r="G110" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H110" t="str">
         <v>Piprahi</v>
       </c>
       <c r="I110" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J110" t="str">
-        <v>30000277165</v>
+        <v>30000411788</v>
       </c>
       <c r="K110" t="str">
         <v>State Bank of India</v>
@@ -5951,39 +5999,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M110" t="str">
-        <v>SBIN0005039</v>
+        <v>SBIN0007210</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>0300120</v>
+        <v>0300067</v>
       </c>
       <c r="B111" t="str">
-        <v>MAMTA SAH</v>
+        <v>SUNIL THAKUR</v>
       </c>
       <c r="C111" t="str">
-        <v>Administrative Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D111" t="str">
-        <v>Punjab National Bank, Tariyani</v>
+        <v>Middle School Purnahiya</v>
       </c>
       <c r="E111" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F111" t="str">
-        <v>9003000120</v>
+        <v>9003000067</v>
       </c>
       <c r="G111" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H111" t="str">
         <v>Dumri Katsari</v>
       </c>
       <c r="I111" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J111" t="str">
-        <v>30000950280</v>
+        <v>30000530573</v>
       </c>
       <c r="K111" t="str">
         <v>State Bank of India</v>
@@ -5992,39 +6040,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M111" t="str">
-        <v>SBIN0004598</v>
+        <v>SBIN0004495</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>0300071</v>
+        <v>0300015</v>
       </c>
       <c r="B112" t="str">
-        <v>RAVI THAKUR</v>
+        <v>NIRMALA MAHTO</v>
       </c>
       <c r="C112" t="str">
-        <v>Data Entry Operator</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D112" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>Block Education Office Purnahiya</v>
       </c>
       <c r="E112" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F112" t="str">
-        <v>9003000071</v>
+        <v>9003000015</v>
       </c>
       <c r="G112" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H112" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I112" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J112" t="str">
-        <v>30000562249</v>
+        <v>30000118785</v>
       </c>
       <c r="K112" t="str">
         <v>State Bank of India</v>
@@ -6033,27 +6081,27 @@
         <v>Sheohar</v>
       </c>
       <c r="M112" t="str">
-        <v>SBIN0003639</v>
+        <v>SBIN0001511</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>0300068</v>
+        <v>0300064</v>
       </c>
       <c r="B113" t="str">
-        <v>MD. IRFAN RAM D</v>
+        <v>MAMTA MISHRA</v>
       </c>
       <c r="C113" t="str">
-        <v>Data Entry Operator</v>
+        <v>Teacher</v>
       </c>
       <c r="D113" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>Panchayat Bhawan Dumri Katsari</v>
       </c>
       <c r="E113" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F113" t="str">
-        <v>9003000068</v>
+        <v>9003000064</v>
       </c>
       <c r="G113" t="str">
         <v>POLLING OFFICER-3</v>
@@ -6062,10 +6110,10 @@
         <v>Purnahiya</v>
       </c>
       <c r="I113" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J113" t="str">
-        <v>30000538492</v>
+        <v>30000506816</v>
       </c>
       <c r="K113" t="str">
         <v>State Bank of India</v>
@@ -6074,39 +6122,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M113" t="str">
-        <v>SBIN0008807</v>
+        <v>SBIN0002446</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>0300098</v>
+        <v>0300032</v>
       </c>
       <c r="B114" t="str">
-        <v>KIRAN SHARMA</v>
+        <v>SAVITA TIWARI</v>
       </c>
       <c r="C114" t="str">
-        <v>Junior Engineer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D114" t="str">
-        <v>Block Office Piprahi</v>
+        <v>CDPO Office Tariyani No.3</v>
       </c>
       <c r="E114" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F114" t="str">
-        <v>9003000098</v>
+        <v>9003000032</v>
       </c>
       <c r="G114" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H114" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="I114" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="J114" t="str">
-        <v>30000776062</v>
+        <v>30000253408</v>
       </c>
       <c r="K114" t="str">
         <v>State Bank of India</v>
@@ -6115,39 +6163,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M114" t="str">
-        <v>SBIN0007691</v>
+        <v>SBIN0003419</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>0300046</v>
+        <v>0300068</v>
       </c>
       <c r="B115" t="str">
-        <v>MUKESH CHAUDHARY</v>
+        <v>DEEPAK PASWAN A</v>
       </c>
       <c r="C115" t="str">
-        <v>Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D115" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>Primary School Tariyani No.3</v>
       </c>
       <c r="E115" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F115" t="str">
-        <v>9003000046</v>
+        <v>9003000068</v>
       </c>
       <c r="G115" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H115" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I115" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="J115" t="str">
-        <v>30000364274</v>
+        <v>30000538492</v>
       </c>
       <c r="K115" t="str">
         <v>State Bank of India</v>
@@ -6156,39 +6204,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M115" t="str">
-        <v>SBIN0001608</v>
+        <v>SBIN0001258</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>0300019</v>
+        <v>0300043</v>
       </c>
       <c r="B116" t="str">
-        <v>RAJESH RAI</v>
+        <v>AMIT VERMA</v>
       </c>
       <c r="C116" t="str">
-        <v>Assistant Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D116" t="str">
-        <v>CDPO Office Sheohar No.4</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="E116" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F116" t="str">
-        <v>9003000019</v>
+        <v>9003000043</v>
       </c>
       <c r="G116" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H116" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I116" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J116" t="str">
-        <v>30000150461</v>
+        <v>30000340517</v>
       </c>
       <c r="K116" t="str">
         <v>State Bank of India</v>
@@ -6197,39 +6245,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M116" t="str">
-        <v>SBIN0003172</v>
+        <v>SBIN0006639</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>0300082</v>
+        <v>0300108</v>
       </c>
       <c r="B117" t="str">
-        <v>ABDUL KALAM SHARMA</v>
+        <v>VINOD SINHA</v>
       </c>
       <c r="C117" t="str">
-        <v>Office Assistant</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D117" t="str">
-        <v>High School Dumri Katsari No.1</v>
+        <v>Central Bank of India, Piprahi</v>
       </c>
       <c r="E117" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F117" t="str">
-        <v>9003000082</v>
+        <v>9003000108</v>
       </c>
       <c r="G117" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H117" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="I117" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="J117" t="str">
-        <v>30000649358</v>
+        <v>30000855252</v>
       </c>
       <c r="K117" t="str">
         <v>State Bank of India</v>
@@ -6238,39 +6286,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M117" t="str">
-        <v>SBIN0005799</v>
+        <v>SBIN0007997</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>0300048</v>
+        <v>0300030</v>
       </c>
       <c r="B118" t="str">
-        <v>SURESH SINHA</v>
+        <v>AJAY JHA</v>
       </c>
       <c r="C118" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D118" t="str">
-        <v>High School Dumri Katsari</v>
+        <v>CDPO Office Purnahiya No.4</v>
       </c>
       <c r="E118" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F118" t="str">
-        <v>9003000048</v>
+        <v>9003000030</v>
       </c>
       <c r="G118" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H118" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="I118" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J118" t="str">
-        <v>30000380112</v>
+        <v>30000237570</v>
       </c>
       <c r="K118" t="str">
         <v>State Bank of India</v>
@@ -6279,39 +6327,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M118" t="str">
-        <v>SBIN0009852</v>
+        <v>SBIN0001061</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>0300013</v>
+        <v>0300097</v>
       </c>
       <c r="B119" t="str">
-        <v>ARVIND KHATUN</v>
+        <v>SAVITA DEVI</v>
       </c>
       <c r="C119" t="str">
-        <v>Headmaster</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D119" t="str">
-        <v>PHC Sheohar</v>
+        <v>RWD Sub-Division Tariyani</v>
       </c>
       <c r="E119" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F119" t="str">
-        <v>9003000013</v>
+        <v>9003000097</v>
       </c>
       <c r="G119" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H119" t="str">
         <v>Tariyani</v>
       </c>
       <c r="I119" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="J119" t="str">
-        <v>30000102947</v>
+        <v>30000768143</v>
       </c>
       <c r="K119" t="str">
         <v>State Bank of India</v>
@@ -6320,39 +6368,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M119" t="str">
-        <v>SBIN0003490</v>
+        <v>SBIN0001087</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>0300075</v>
+        <v>0300049</v>
       </c>
       <c r="B120" t="str">
-        <v>ALOK KHATUN</v>
+        <v>USHA RAM</v>
       </c>
       <c r="C120" t="str">
-        <v>Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D120" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>High School Piprahi No.2</v>
       </c>
       <c r="E120" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F120" t="str">
-        <v>9003000075</v>
+        <v>9003000049</v>
       </c>
       <c r="G120" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H120" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I120" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="J120" t="str">
-        <v>30000593925</v>
+        <v>30000388031</v>
       </c>
       <c r="K120" t="str">
         <v>State Bank of India</v>
@@ -6361,39 +6409,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M120" t="str">
-        <v>SBIN0006369</v>
+        <v>SBIN0003712</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>0300073</v>
+        <v>0300089</v>
       </c>
       <c r="B121" t="str">
-        <v>NASREEN GUPTA</v>
+        <v>SAVITA VERMA</v>
       </c>
       <c r="C121" t="str">
-        <v>Teacher</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D121" t="str">
-        <v>CDPO Office Tariyani No.2</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="E121" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F121" t="str">
-        <v>9003000073</v>
+        <v>9003000089</v>
       </c>
       <c r="G121" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H121" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I121" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="J121" t="str">
-        <v>30000578087</v>
+        <v>30000704791</v>
       </c>
       <c r="K121" t="str">
         <v>State Bank of India</v>
@@ -6402,39 +6450,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M121" t="str">
-        <v>SBIN0002291</v>
+        <v>SBIN0005122</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>0300009</v>
+        <v>0300026</v>
       </c>
       <c r="B122" t="str">
-        <v>NITISH SHARMA</v>
+        <v>KUMARI ANJALI KHATUN</v>
       </c>
       <c r="C122" t="str">
-        <v>Senior Teacher</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D122" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>Primary School Piprahi No.2</v>
       </c>
       <c r="E122" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F122" t="str">
-        <v>9003000009</v>
+        <v>9003000026</v>
       </c>
       <c r="G122" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H122" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="I122" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J122" t="str">
-        <v>30000071271</v>
+        <v>30000205894</v>
       </c>
       <c r="K122" t="str">
         <v>State Bank of India</v>
@@ -6443,39 +6491,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M122" t="str">
-        <v>SBIN0009436</v>
+        <v>SBIN0007495</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>0300062</v>
+        <v>0300061</v>
       </c>
       <c r="B123" t="str">
-        <v>ALOK THAKUR</v>
+        <v>ARVIND PASWAN</v>
       </c>
       <c r="C123" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Teacher</v>
       </c>
       <c r="D123" t="str">
-        <v>Kanya Middle School Tariyani No.1</v>
+        <v>Project Girls High School Sheohar</v>
       </c>
       <c r="E123" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F123" t="str">
-        <v>9003000062</v>
+        <v>9003000061</v>
       </c>
       <c r="G123" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="H123" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="I123" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="J123" t="str">
-        <v>30000490978</v>
+        <v>30000483059</v>
       </c>
       <c r="K123" t="str">
         <v>State Bank of India</v>
@@ -6484,39 +6532,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M123" t="str">
-        <v>SBIN0006900</v>
+        <v>SBIN0001437</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>0300113</v>
+        <v>0300106</v>
       </c>
       <c r="B124" t="str">
-        <v>ABDUL KALAM KUMAR</v>
+        <v>SUNIL YADAV</v>
       </c>
       <c r="C124" t="str">
         <v>Branch Manager</v>
       </c>
       <c r="D124" t="str">
-        <v>UCO Bank, Purnahiya</v>
+        <v>Head Post Office, Tariyani</v>
       </c>
       <c r="E124" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F124" t="str">
-        <v>9003000113</v>
+        <v>9003000106</v>
       </c>
       <c r="G124" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="H124" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I124" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="J124" t="str">
-        <v>30000894847</v>
+        <v>30000839414</v>
       </c>
       <c r="K124" t="str">
         <v>State Bank of India</v>
@@ -6525,39 +6573,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M124" t="str">
-        <v>SBIN0004516</v>
+        <v>SBIN0001696</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>0300114</v>
+        <v>0300028</v>
       </c>
       <c r="B125" t="str">
-        <v>DINESH ALAM</v>
+        <v>FARHAT GUPTA</v>
       </c>
       <c r="C125" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D125" t="str">
-        <v>Punjab National Bank, Dumri Katsari</v>
+        <v>Block Agriculture Office Dumri Katsari No.4</v>
       </c>
       <c r="E125" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F125" t="str">
-        <v>9003000114</v>
+        <v>9003000028</v>
       </c>
       <c r="G125" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H125" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I125" t="str">
         <v>Dumri Katsari</v>
       </c>
       <c r="J125" t="str">
-        <v>30000902766</v>
+        <v>30000221732</v>
       </c>
       <c r="K125" t="str">
         <v>State Bank of India</v>
@@ -6566,39 +6614,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M125" t="str">
-        <v>SBIN0007574</v>
+        <v>SBIN0004142</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>0300034</v>
+        <v>0300014</v>
       </c>
       <c r="B126" t="str">
-        <v>NASREEN CHAUDHARY</v>
+        <v>RAJESH KHATUN</v>
       </c>
       <c r="C126" t="str">
-        <v>Assistant Teacher</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D126" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Block Office Purnahiya No.2</v>
       </c>
       <c r="E126" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F126" t="str">
-        <v>9003000034</v>
+        <v>9003000014</v>
       </c>
       <c r="G126" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H126" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I126" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J126" t="str">
-        <v>30000269246</v>
+        <v>30000110866</v>
       </c>
       <c r="K126" t="str">
         <v>State Bank of India</v>
@@ -6607,39 +6655,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M126" t="str">
-        <v>SBIN0008840</v>
+        <v>SBIN0005477</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>0300060</v>
+        <v>0300095</v>
       </c>
       <c r="B127" t="str">
-        <v>SUNIL MISHRA</v>
+        <v>MAHESH TIWARI</v>
       </c>
       <c r="C127" t="str">
-        <v>Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D127" t="str">
-        <v>Middle School Piprahi No.1</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="E127" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F127" t="str">
-        <v>9003000060</v>
+        <v>9003000095</v>
       </c>
       <c r="G127" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H127" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I127" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J127" t="str">
-        <v>30000475140</v>
+        <v>30000752305</v>
       </c>
       <c r="K127" t="str">
         <v>State Bank of India</v>
@@ -6648,7 +6696,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M127" t="str">
-        <v>SBIN0009576</v>
+        <v>SBIN0005540</v>
       </c>
     </row>
   </sheetData>
@@ -6697,7 +6745,7 @@
         <v>Main</v>
       </c>
       <c r="D2" t="str">
-        <v>High School Sheohar, Room 2</v>
+        <v>Middle School Sheohar, Room 2</v>
       </c>
       <c r="E2" t="str">
         <v>Sheohar</v>
@@ -6714,7 +6762,7 @@
         <v>Main</v>
       </c>
       <c r="D3" t="str">
-        <v>Panchayat Bhawan Piprahi, Room 3</v>
+        <v>Kanya Middle School Piprahi, Room 3</v>
       </c>
       <c r="E3" t="str">
         <v>Piprahi</v>
@@ -6731,7 +6779,7 @@
         <v>Main</v>
       </c>
       <c r="D4" t="str">
-        <v>Block Office Hall Purnahiya, Room 1</v>
+        <v>High School Purnahiya, Room 1</v>
       </c>
       <c r="E4" t="str">
         <v>Purnahiya</v>
@@ -6782,7 +6830,7 @@
         <v>Main</v>
       </c>
       <c r="D7" t="str">
-        <v>High School Sheohar, Room 1</v>
+        <v>Middle School Sheohar, Room 1</v>
       </c>
       <c r="E7" t="str">
         <v>Sheohar</v>
@@ -6799,7 +6847,7 @@
         <v>Main</v>
       </c>
       <c r="D8" t="str">
-        <v>Panchayat Bhawan Purnahiya, Room 2</v>
+        <v>Middle School Purnahiya, Room 2</v>
       </c>
       <c r="E8" t="str">
         <v>Purnahiya</v>
@@ -6833,7 +6881,7 @@
         <v>Main</v>
       </c>
       <c r="D10" t="str">
-        <v>Panchayat Bhawan Tariyani, Room 1</v>
+        <v>High School Tariyani, Room 1</v>
       </c>
       <c r="E10" t="str">
         <v>Tariyani</v>
@@ -6850,7 +6898,7 @@
         <v>Main</v>
       </c>
       <c r="D11" t="str">
-        <v>Block Office Hall Sheohar, Room 2</v>
+        <v>Middle School Sheohar, Room 2</v>
       </c>
       <c r="E11" t="str">
         <v>Sheohar</v>
@@ -6867,7 +6915,7 @@
         <v>Main</v>
       </c>
       <c r="D12" t="str">
-        <v>Panchayat Bhawan Piprahi, Room 3</v>
+        <v>Middle School Piprahi, Room 3</v>
       </c>
       <c r="E12" t="str">
         <v>Piprahi</v>
@@ -6884,7 +6932,7 @@
         <v>Main</v>
       </c>
       <c r="D13" t="str">
-        <v>Panchayat Bhawan Purnahiya, Room 1</v>
+        <v>Block Office Hall Purnahiya, Room 1</v>
       </c>
       <c r="E13" t="str">
         <v>Purnahiya</v>

--- a/test-data/TEST_Sheohar_Project.xlsx
+++ b/test-data/TEST_Sheohar_Project.xlsx
@@ -612,7 +612,7 @@
         <v>Saved at</v>
       </c>
       <c r="B4" t="str">
-        <v>12-10-2026 18:19:44</v>
+        <v>12-10-2026 18:31:45</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12-10-2026 18:19:44</v>
+        <v>12-10-2026 18:31:45</v>
       </c>
       <c r="B2" t="str">
         <v>Test data generated (Small — Sheohar style (5 blocks, 6 TC + 6 GC booths))</v>
@@ -1535,34 +1535,34 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0300012</v>
+        <v>0300008</v>
       </c>
       <c r="B2" t="str">
-        <v>USHA SINGH</v>
+        <v>MAHESH VERMA</v>
       </c>
       <c r="C2" t="str">
-        <v>Senior Teacher</v>
+        <v>Lecturer</v>
       </c>
       <c r="D2" t="str">
-        <v>Block Education Office Piprahi No.2</v>
+        <v>Block Agriculture Office Purnahiya No.2</v>
       </c>
       <c r="E2" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F2" t="str">
-        <v>9003000012</v>
+        <v>9003000008</v>
       </c>
       <c r="G2" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="H2" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="I2" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J2" t="str">
-        <v>30000095028</v>
+        <v>30000063352</v>
       </c>
       <c r="K2" t="str">
         <v>State Bank of India</v>
@@ -1571,39 +1571,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M2" t="str">
-        <v>SBIN0004474</v>
+        <v>SBIN0007711</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0300004</v>
+        <v>0300122</v>
       </c>
       <c r="B3" t="str">
-        <v>MAMTA THAKUR</v>
+        <v>KIRAN OJHA</v>
       </c>
       <c r="C3" t="str">
-        <v>Headmaster</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D3" t="str">
-        <v>High School Dumri Katsari No.4</v>
+        <v>UCO Bank, Purnahiya</v>
       </c>
       <c r="E3" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F3" t="str">
-        <v>9003000004</v>
+        <v>9003000122</v>
       </c>
       <c r="G3" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H3" t="str">
         <v>Piprahi</v>
       </c>
       <c r="I3" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J3" t="str">
-        <v>30000031676</v>
+        <v>30000966118</v>
       </c>
       <c r="K3" t="str">
         <v>State Bank of India</v>
@@ -1612,39 +1612,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M3" t="str">
-        <v>SBIN0003675</v>
+        <v>SBIN0001590</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0300114</v>
+        <v>0300081</v>
       </c>
       <c r="B4" t="str">
-        <v>SAVITA PANDEY</v>
+        <v>MD. IRFAN PANDEY</v>
       </c>
       <c r="C4" t="str">
-        <v>Assistant Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D4" t="str">
-        <v>Head Post Office, Purnahiya</v>
+        <v>Project Girls High School Piprahi</v>
       </c>
       <c r="E4" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F4" t="str">
-        <v>9003000114</v>
+        <v>9003000081</v>
       </c>
       <c r="G4" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H4" t="str">
         <v>Piprahi</v>
       </c>
       <c r="I4" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="J4" t="str">
-        <v>30000902766</v>
+        <v>30000641439</v>
       </c>
       <c r="K4" t="str">
         <v>State Bank of India</v>
@@ -1653,39 +1653,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M4" t="str">
-        <v>SBIN0003704</v>
+        <v>SBIN0004716</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0300060</v>
+        <v>0300024</v>
       </c>
       <c r="B5" t="str">
-        <v>MUKESH KUMAR</v>
+        <v>SUNIL MAHTO</v>
       </c>
       <c r="C5" t="str">
-        <v>Clerk</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D5" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>Project Girls High School Tariyani No.3</v>
       </c>
       <c r="E5" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F5" t="str">
-        <v>9003000060</v>
+        <v>9003000024</v>
       </c>
       <c r="G5" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H5" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="I5" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I5" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="J5" t="str">
-        <v>30000475140</v>
+        <v>30000190056</v>
       </c>
       <c r="K5" t="str">
         <v>State Bank of India</v>
@@ -1694,39 +1694,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M5" t="str">
-        <v>SBIN0009610</v>
+        <v>SBIN0004986</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0300100</v>
+        <v>0300017</v>
       </c>
       <c r="B6" t="str">
-        <v>ASHA JHA</v>
+        <v>ANITA RAM</v>
       </c>
       <c r="C6" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D6" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>Block Office Sheohar</v>
       </c>
       <c r="E6" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F6" t="str">
-        <v>9003000100</v>
+        <v>9003000017</v>
       </c>
       <c r="G6" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H6" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I6" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J6" t="str">
-        <v>30000791900</v>
+        <v>30000134623</v>
       </c>
       <c r="K6" t="str">
         <v>State Bank of India</v>
@@ -1735,39 +1735,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M6" t="str">
-        <v>SBIN0002940</v>
+        <v>SBIN0009889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>0300031</v>
+        <v>0300123</v>
       </c>
       <c r="B7" t="str">
-        <v>AMIT SHARMA</v>
+        <v>PANKAJ DEVI</v>
       </c>
       <c r="C7" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D7" t="str">
-        <v>Primary School Dumri Katsari No.1</v>
+        <v>LIC Branch Office, Sheohar</v>
       </c>
       <c r="E7" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F7" t="str">
-        <v>9003000031</v>
+        <v>9003000123</v>
       </c>
       <c r="G7" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H7" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="I7" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="J7" t="str">
-        <v>30000245489</v>
+        <v>30000974037</v>
       </c>
       <c r="K7" t="str">
         <v>State Bank of India</v>
@@ -1776,39 +1776,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M7" t="str">
-        <v>SBIN0008556</v>
+        <v>SBIN0002977</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0300110</v>
+        <v>0300093</v>
       </c>
       <c r="B8" t="str">
-        <v>SAVITA DEVI C</v>
+        <v>POONAM KUMAR</v>
       </c>
       <c r="C8" t="str">
-        <v>Assistant Manager</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D8" t="str">
-        <v>Bank of India, Sheohar</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="E8" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F8" t="str">
-        <v>9003000110</v>
+        <v>9003000093</v>
       </c>
       <c r="G8" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H8" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I8" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J8" t="str">
-        <v>30000871090</v>
+        <v>30000736467</v>
       </c>
       <c r="K8" t="str">
         <v>State Bank of India</v>
@@ -1817,39 +1817,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M8" t="str">
-        <v>SBIN0003602</v>
+        <v>SBIN0003584</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0300101</v>
+        <v>0300041</v>
       </c>
       <c r="B9" t="str">
-        <v>ANITA MISHRA</v>
+        <v>SUNIL KHATUN</v>
       </c>
       <c r="C9" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D9" t="str">
-        <v>Minor Irrigation Office Tariyani</v>
+        <v>CDPO Office Piprahi No.2</v>
       </c>
       <c r="E9" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F9" t="str">
-        <v>9003000101</v>
+        <v>9003000041</v>
       </c>
       <c r="G9" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H9" t="str">
         <v>Tariyani</v>
       </c>
       <c r="I9" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="J9" t="str">
-        <v>30000799819</v>
+        <v>30000324679</v>
       </c>
       <c r="K9" t="str">
         <v>State Bank of India</v>
@@ -1858,39 +1858,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M9" t="str">
-        <v>SBIN0006645</v>
+        <v>SBIN0007960</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0300121</v>
+        <v>0300114</v>
       </c>
       <c r="B10" t="str">
-        <v>KIRAN KUMAR</v>
+        <v>SURESH SAH</v>
       </c>
       <c r="C10" t="str">
-        <v>Administrative Officer</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D10" t="str">
-        <v>Head Post Office, Sheohar</v>
+        <v>BSNL Exchange, Sheohar</v>
       </c>
       <c r="E10" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F10" t="str">
-        <v>9003000121</v>
+        <v>9003000114</v>
       </c>
       <c r="G10" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="H10" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="I10" t="str">
         <v>Sheohar</v>
       </c>
       <c r="J10" t="str">
-        <v>30000958199</v>
+        <v>30000902766</v>
       </c>
       <c r="K10" t="str">
         <v>State Bank of India</v>
@@ -1899,39 +1899,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M10" t="str">
-        <v>SBIN0005457</v>
+        <v>SBIN0003389</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>0300079</v>
+        <v>0300052</v>
       </c>
       <c r="B11" t="str">
-        <v>FARHAT PRASAD</v>
+        <v>MD. IRFAN SHARMA</v>
       </c>
       <c r="C11" t="str">
-        <v>Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D11" t="str">
-        <v>Kanya Middle School Purnahiya</v>
+        <v>District Treasury Sheohar</v>
       </c>
       <c r="E11" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F11" t="str">
-        <v>9003000079</v>
+        <v>9003000052</v>
       </c>
       <c r="G11" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H11" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I11" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J11" t="str">
-        <v>30000625601</v>
+        <v>30000411788</v>
       </c>
       <c r="K11" t="str">
         <v>State Bank of India</v>
@@ -1940,39 +1940,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M11" t="str">
-        <v>SBIN0007441</v>
+        <v>SBIN0002020</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>0300123</v>
+        <v>0300112</v>
       </c>
       <c r="B12" t="str">
-        <v>RAVI JHA M</v>
+        <v>KIRAN MISHRA</v>
       </c>
       <c r="C12" t="str">
-        <v>Postmaster</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D12" t="str">
-        <v>UCO Bank, Piprahi</v>
+        <v>Punjab National Bank, Purnahiya</v>
       </c>
       <c r="E12" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F12" t="str">
-        <v>9003000123</v>
+        <v>9003000112</v>
       </c>
       <c r="G12" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="H12" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I12" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J12" t="str">
-        <v>30000974037</v>
+        <v>30000886928</v>
       </c>
       <c r="K12" t="str">
         <v>State Bank of India</v>
@@ -1981,39 +1981,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M12" t="str">
-        <v>SBIN0003472</v>
+        <v>SBIN0004606</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0300113</v>
+        <v>0300003</v>
       </c>
       <c r="B13" t="str">
-        <v>SURESH PRASAD J</v>
+        <v>REKHA MAHTO</v>
       </c>
       <c r="C13" t="str">
-        <v>Postmaster</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D13" t="str">
-        <v>Punjab National Bank, Dumri Katsari</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="E13" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F13" t="str">
-        <v>9003000113</v>
+        <v>9003000003</v>
       </c>
       <c r="G13" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H13" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I13" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="J13" t="str">
-        <v>30000894847</v>
+        <v>30000023757</v>
       </c>
       <c r="K13" t="str">
         <v>State Bank of India</v>
@@ -2022,39 +2022,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M13" t="str">
-        <v>SBIN0002154</v>
+        <v>SBIN0001398</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0300050</v>
+        <v>0300104</v>
       </c>
       <c r="B14" t="str">
-        <v>RAVI PRASAD</v>
+        <v>NIRMALA GUPTA</v>
       </c>
       <c r="C14" t="str">
-        <v>Accountant</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D14" t="str">
-        <v>High School Tariyani</v>
+        <v>Block Office Sheohar</v>
       </c>
       <c r="E14" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F14" t="str">
-        <v>9003000050</v>
+        <v>9003000104</v>
       </c>
       <c r="G14" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H14" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="I14" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="J14" t="str">
-        <v>30000395950</v>
+        <v>30000823576</v>
       </c>
       <c r="K14" t="str">
         <v>State Bank of India</v>
@@ -2063,39 +2063,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M14" t="str">
-        <v>SBIN0002852</v>
+        <v>SBIN0008080</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>0300062</v>
+        <v>0300009</v>
       </c>
       <c r="B15" t="str">
-        <v>ARVIND SHARMA</v>
+        <v>NITISH THAKUR</v>
       </c>
       <c r="C15" t="str">
-        <v>Teacher</v>
+        <v>Section Officer</v>
       </c>
       <c r="D15" t="str">
-        <v>Panchayat Bhawan Purnahiya No.1</v>
+        <v>Block Office Sheohar No.1</v>
       </c>
       <c r="E15" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F15" t="str">
-        <v>9003000062</v>
+        <v>9003000009</v>
       </c>
       <c r="G15" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H15" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="I15" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J15" t="str">
-        <v>30000490978</v>
+        <v>30000071271</v>
       </c>
       <c r="K15" t="str">
         <v>State Bank of India</v>
@@ -2104,39 +2104,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M15" t="str">
-        <v>SBIN0002294</v>
+        <v>SBIN0002299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>0300059</v>
+        <v>0300028</v>
       </c>
       <c r="B16" t="str">
-        <v>RAVI GUPTA</v>
+        <v>MUKESH YADAV</v>
       </c>
       <c r="C16" t="str">
-        <v>Clerk</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D16" t="str">
-        <v>Project Girls High School Dumri Katsari</v>
+        <v>Circle Office Tariyani No.3</v>
       </c>
       <c r="E16" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F16" t="str">
-        <v>9003000059</v>
+        <v>9003000028</v>
       </c>
       <c r="G16" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H16" t="str">
         <v>Tariyani</v>
       </c>
       <c r="I16" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="J16" t="str">
-        <v>30000467221</v>
+        <v>30000221732</v>
       </c>
       <c r="K16" t="str">
         <v>State Bank of India</v>
@@ -2145,39 +2145,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M16" t="str">
-        <v>SBIN0003004</v>
+        <v>SBIN0005239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>0300075</v>
+        <v>0300088</v>
       </c>
       <c r="B17" t="str">
-        <v>REKHA JHA</v>
+        <v>VINOD CHAUDHARY</v>
       </c>
       <c r="C17" t="str">
-        <v>Data Entry Operator</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D17" t="str">
-        <v>High School Tariyani No.3</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="E17" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F17" t="str">
-        <v>9003000075</v>
+        <v>9003000088</v>
       </c>
       <c r="G17" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H17" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I17" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="J17" t="str">
-        <v>30000593925</v>
+        <v>30000696872</v>
       </c>
       <c r="K17" t="str">
         <v>State Bank of India</v>
@@ -2186,39 +2186,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M17" t="str">
-        <v>SBIN0006523</v>
+        <v>SBIN0003829</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>0300021</v>
+        <v>0300034</v>
       </c>
       <c r="B18" t="str">
-        <v>NASREEN OJHA</v>
+        <v>KUMARI ANJALI RAM</v>
       </c>
       <c r="C18" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D18" t="str">
-        <v>Middle School Sheohar No.1</v>
+        <v>PHC Piprahi No.4</v>
       </c>
       <c r="E18" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F18" t="str">
-        <v>9003000021</v>
+        <v>9003000034</v>
       </c>
       <c r="G18" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H18" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="I18" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J18" t="str">
-        <v>30000166299</v>
+        <v>30000269246</v>
       </c>
       <c r="K18" t="str">
         <v>State Bank of India</v>
@@ -2227,39 +2227,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M18" t="str">
-        <v>SBIN0001449</v>
+        <v>SBIN0005249</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>0300045</v>
+        <v>0300011</v>
       </c>
       <c r="B19" t="str">
-        <v>SANJAY JHA</v>
+        <v>DEEPAK SINGH</v>
       </c>
       <c r="C19" t="str">
-        <v>Teacher</v>
+        <v>Headmaster</v>
       </c>
       <c r="D19" t="str">
-        <v>Primary School Tariyani No.4</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="E19" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F19" t="str">
-        <v>9003000045</v>
+        <v>9003000011</v>
       </c>
       <c r="G19" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H19" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="I19" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J19" t="str">
-        <v>30000356355</v>
+        <v>30000087109</v>
       </c>
       <c r="K19" t="str">
         <v>State Bank of India</v>
@@ -2268,39 +2268,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M19" t="str">
-        <v>SBIN0001347</v>
+        <v>SBIN0003404</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>0300023</v>
+        <v>0300043</v>
       </c>
       <c r="B20" t="str">
-        <v>SANTOSH RAI</v>
+        <v>NASREEN SHARMA</v>
       </c>
       <c r="C20" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D20" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Middle School Dumri Katsari No.4</v>
       </c>
       <c r="E20" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F20" t="str">
-        <v>9003000023</v>
+        <v>9003000043</v>
       </c>
       <c r="G20" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H20" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I20" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J20" t="str">
-        <v>30000182137</v>
+        <v>30000340517</v>
       </c>
       <c r="K20" t="str">
         <v>State Bank of India</v>
@@ -2309,39 +2309,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M20" t="str">
-        <v>SBIN0004786</v>
+        <v>SBIN0006377</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>0300066</v>
+        <v>0300054</v>
       </c>
       <c r="B21" t="str">
-        <v>RINKU DEVI</v>
+        <v>SAVITA SAH</v>
       </c>
       <c r="C21" t="str">
         <v>Clerk</v>
       </c>
       <c r="D21" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Primary School Dumri Katsari No.2</v>
       </c>
       <c r="E21" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F21" t="str">
-        <v>9003000066</v>
+        <v>9003000054</v>
       </c>
       <c r="G21" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H21" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I21" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J21" t="str">
-        <v>30000522654</v>
+        <v>30000427626</v>
       </c>
       <c r="K21" t="str">
         <v>State Bank of India</v>
@@ -2350,39 +2350,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M21" t="str">
-        <v>SBIN0003668</v>
+        <v>SBIN0005877</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>0300037</v>
+        <v>0300007</v>
       </c>
       <c r="B22" t="str">
-        <v>RAMESH OJHA</v>
+        <v>SURESH MAHTO</v>
       </c>
       <c r="C22" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Section Officer</v>
       </c>
       <c r="D22" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>Panchayat Bhawan Tariyani No.1</v>
       </c>
       <c r="E22" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F22" t="str">
-        <v>9003000037</v>
+        <v>9003000007</v>
       </c>
       <c r="G22" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H22" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="I22" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="J22" t="str">
-        <v>30000293003</v>
+        <v>30000055433</v>
       </c>
       <c r="K22" t="str">
         <v>State Bank of India</v>
@@ -2391,30 +2391,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M22" t="str">
-        <v>SBIN0006367</v>
+        <v>SBIN0006290</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>0300020</v>
+        <v>0300032</v>
       </c>
       <c r="B23" t="str">
-        <v>NITISH SINGH</v>
+        <v>UMESH SINHA</v>
       </c>
       <c r="C23" t="str">
-        <v>Lecturer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D23" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="E23" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F23" t="str">
-        <v>9003000020</v>
+        <v>9003000032</v>
       </c>
       <c r="G23" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H23" t="str">
         <v>Sheohar</v>
@@ -2423,7 +2423,7 @@
         <v>Sheohar</v>
       </c>
       <c r="J23" t="str">
-        <v>30000158380</v>
+        <v>30000253408</v>
       </c>
       <c r="K23" t="str">
         <v>State Bank of India</v>
@@ -2432,39 +2432,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M23" t="str">
-        <v>SBIN0003881</v>
+        <v>SBIN0001361</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>0300070</v>
+        <v>0300044</v>
       </c>
       <c r="B24" t="str">
-        <v>SANJAY OJHA</v>
+        <v>SUNIL SHARMA</v>
       </c>
       <c r="C24" t="str">
-        <v>Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D24" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>Project Girls High School Purnahiya No.2</v>
       </c>
       <c r="E24" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F24" t="str">
-        <v>9003000070</v>
+        <v>9003000044</v>
       </c>
       <c r="G24" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H24" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I24" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J24" t="str">
-        <v>30000554330</v>
+        <v>30000348436</v>
       </c>
       <c r="K24" t="str">
         <v>State Bank of India</v>
@@ -2473,39 +2473,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M24" t="str">
-        <v>SBIN0004984</v>
+        <v>SBIN0003918</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0300002</v>
+        <v>0300030</v>
       </c>
       <c r="B25" t="str">
-        <v>NIRMALA OJHA</v>
+        <v>DINESH THAKUR</v>
       </c>
       <c r="C25" t="str">
-        <v>Lecturer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D25" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="E25" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F25" t="str">
-        <v>9003000002</v>
+        <v>9003000030</v>
       </c>
       <c r="G25" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H25" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="I25" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J25" t="str">
-        <v>30000015838</v>
+        <v>30000237570</v>
       </c>
       <c r="K25" t="str">
         <v>State Bank of India</v>
@@ -2514,39 +2514,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M25" t="str">
-        <v>SBIN0003827</v>
+        <v>SBIN0007052</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>0300076</v>
+        <v>0300115</v>
       </c>
       <c r="B26" t="str">
-        <v>POONAM SINHA</v>
+        <v>AMIT SINGH</v>
       </c>
       <c r="C26" t="str">
-        <v>Office Assistant</v>
+        <v>Postmaster</v>
       </c>
       <c r="D26" t="str">
-        <v>Kanya Middle School Dumri Katsari No.2</v>
+        <v>Central Bank of India, Purnahiya</v>
       </c>
       <c r="E26" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F26" t="str">
-        <v>9003000076</v>
+        <v>9003000115</v>
       </c>
       <c r="G26" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H26" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I26" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J26" t="str">
-        <v>30000601844</v>
+        <v>30000910685</v>
       </c>
       <c r="K26" t="str">
         <v>State Bank of India</v>
@@ -2555,39 +2555,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M26" t="str">
-        <v>SBIN0005783</v>
+        <v>SBIN0004707</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>0300008</v>
+        <v>0300102</v>
       </c>
       <c r="B27" t="str">
-        <v>ANITA PRASAD</v>
+        <v>POONAM GUPTA</v>
       </c>
       <c r="C27" t="str">
-        <v>Lecturer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D27" t="str">
-        <v>Block Education Office Sheohar No.4</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="E27" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F27" t="str">
-        <v>9003000008</v>
+        <v>9003000102</v>
       </c>
       <c r="G27" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H27" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="I27" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J27" t="str">
-        <v>30000063352</v>
+        <v>30000807738</v>
       </c>
       <c r="K27" t="str">
         <v>State Bank of India</v>
@@ -2596,39 +2596,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M27" t="str">
-        <v>SBIN0007356</v>
+        <v>SBIN0008741</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>0300024</v>
+        <v>0300038</v>
       </c>
       <c r="B28" t="str">
-        <v>USHA KUMAR</v>
+        <v>MANOJ GUPTA</v>
       </c>
       <c r="C28" t="str">
-        <v>Head Clerk</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D28" t="str">
-        <v>Middle School Dumri Katsari No.2</v>
+        <v>Panchayat Bhawan Purnahiya No.3</v>
       </c>
       <c r="E28" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F28" t="str">
-        <v>9003000024</v>
+        <v>9003000038</v>
       </c>
       <c r="G28" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="H28" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="I28" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="I28" t="str">
-        <v>Dumri Katsari</v>
-      </c>
       <c r="J28" t="str">
-        <v>30000190056</v>
+        <v>30000300922</v>
       </c>
       <c r="K28" t="str">
         <v>State Bank of India</v>
@@ -2637,39 +2637,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M28" t="str">
-        <v>SBIN0007097</v>
+        <v>SBIN0006866</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>0300092</v>
+        <v>0300124</v>
       </c>
       <c r="B29" t="str">
-        <v>RANJIT KUMAR</v>
+        <v>MD. SHAHID MISHRA</v>
       </c>
       <c r="C29" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D29" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>UCO Bank, Tariyani</v>
       </c>
       <c r="E29" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="F29" t="str">
-        <v>9003000092</v>
+        <v>9003000124</v>
       </c>
       <c r="G29" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H29" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="I29" t="str">
         <v>Tariyani</v>
       </c>
       <c r="J29" t="str">
-        <v>30000728548</v>
+        <v>30000981956</v>
       </c>
       <c r="K29" t="str">
         <v>State Bank of India</v>
@@ -2678,39 +2678,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M29" t="str">
-        <v>SBIN0004854</v>
+        <v>SBIN0007161</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>0300093</v>
+        <v>0300073</v>
       </c>
       <c r="B30" t="str">
-        <v>ANIL MAHTO</v>
+        <v>RAKESH PRASAD</v>
       </c>
       <c r="C30" t="str">
-        <v>Assistant Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D30" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="E30" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F30" t="str">
-        <v>9003000093</v>
+        <v>9003000073</v>
       </c>
       <c r="G30" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H30" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I30" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J30" t="str">
-        <v>30000736467</v>
+        <v>30000578087</v>
       </c>
       <c r="K30" t="str">
         <v>State Bank of India</v>
@@ -2719,39 +2719,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M30" t="str">
-        <v>SBIN0002484</v>
+        <v>SBIN0004668</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>0300058</v>
+        <v>0300096</v>
       </c>
       <c r="B31" t="str">
-        <v>USHA GUPTA</v>
+        <v>SUNITA SINHA</v>
       </c>
       <c r="C31" t="str">
-        <v>Clerk</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D31" t="str">
-        <v>High School Piprahi No.2</v>
+        <v>RWD Sub-Division Sheohar</v>
       </c>
       <c r="E31" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F31" t="str">
-        <v>9003000058</v>
+        <v>9003000096</v>
       </c>
       <c r="G31" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H31" t="str">
         <v>Sheohar</v>
       </c>
       <c r="I31" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J31" t="str">
-        <v>30000459302</v>
+        <v>30000760224</v>
       </c>
       <c r="K31" t="str">
         <v>State Bank of India</v>
@@ -2760,39 +2760,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M31" t="str">
-        <v>SBIN0001717</v>
+        <v>SBIN0004767</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>0300116</v>
+        <v>0300107</v>
       </c>
       <c r="B32" t="str">
-        <v>AJAY DEVI</v>
+        <v>VINOD THAKUR</v>
       </c>
       <c r="C32" t="str">
-        <v>Assistant Manager</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D32" t="str">
-        <v>Bank of India, Purnahiya</v>
+        <v>Head Post Office, Dumri Katsari</v>
       </c>
       <c r="E32" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F32" t="str">
-        <v>9003000116</v>
+        <v>9003000107</v>
       </c>
       <c r="G32" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="H32" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I32" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J32" t="str">
-        <v>30000918604</v>
+        <v>30000847333</v>
       </c>
       <c r="K32" t="str">
         <v>State Bank of India</v>
@@ -2801,27 +2801,27 @@
         <v>Sheohar</v>
       </c>
       <c r="M32" t="str">
-        <v>SBIN0009492</v>
+        <v>SBIN0004453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>0300081</v>
+        <v>0300067</v>
       </c>
       <c r="B33" t="str">
-        <v>DINESH MAHTO</v>
+        <v>ASHA MISHRA</v>
       </c>
       <c r="C33" t="str">
-        <v>Office Assistant</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D33" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="E33" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F33" t="str">
-        <v>9003000081</v>
+        <v>9003000067</v>
       </c>
       <c r="G33" t="str">
         <v>POLLING OFFICER-3</v>
@@ -2833,7 +2833,7 @@
         <v>Sheohar</v>
       </c>
       <c r="J33" t="str">
-        <v>30000641439</v>
+        <v>30000530573</v>
       </c>
       <c r="K33" t="str">
         <v>State Bank of India</v>
@@ -2842,39 +2842,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M33" t="str">
-        <v>SBIN0004911</v>
+        <v>SBIN0007768</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>0300080</v>
+        <v>0300069</v>
       </c>
       <c r="B34" t="str">
-        <v>PANKAJ TIWARI</v>
+        <v>FARHAT YADAV</v>
       </c>
       <c r="C34" t="str">
         <v>Teacher</v>
       </c>
       <c r="D34" t="str">
-        <v>PHC Dumri Katsari No.3</v>
+        <v>PHC Piprahi</v>
       </c>
       <c r="E34" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F34" t="str">
-        <v>9003000080</v>
+        <v>9003000069</v>
       </c>
       <c r="G34" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="H34" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="I34" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="J34" t="str">
-        <v>30000633520</v>
+        <v>30000546411</v>
       </c>
       <c r="K34" t="str">
         <v>State Bank of India</v>
@@ -2883,30 +2883,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M34" t="str">
-        <v>SBIN0002681</v>
+        <v>SBIN0004900</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>0300056</v>
+        <v>0300125</v>
       </c>
       <c r="B35" t="str">
-        <v>RAVI OJHA</v>
+        <v>POONAM KHATUN</v>
       </c>
       <c r="C35" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Postmaster</v>
       </c>
       <c r="D35" t="str">
-        <v>CDPO Office Sheohar</v>
+        <v>Punjab National Bank, Sheohar</v>
       </c>
       <c r="E35" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F35" t="str">
-        <v>9003000056</v>
+        <v>9003000125</v>
       </c>
       <c r="G35" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H35" t="str">
         <v>Sheohar</v>
@@ -2915,7 +2915,7 @@
         <v>Sheohar</v>
       </c>
       <c r="J35" t="str">
-        <v>30000443464</v>
+        <v>30000989875</v>
       </c>
       <c r="K35" t="str">
         <v>State Bank of India</v>
@@ -2924,39 +2924,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M35" t="str">
-        <v>SBIN0006139</v>
+        <v>SBIN0003854</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>0300010</v>
+        <v>0300020</v>
       </c>
       <c r="B36" t="str">
-        <v>SURESH KHATUN</v>
+        <v>KUMARI ANJALI MAHTO</v>
       </c>
       <c r="C36" t="str">
-        <v>Headmaster</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D36" t="str">
-        <v>Middle School Tariyani No.1</v>
+        <v>Middle School Dumri Katsari No.3</v>
       </c>
       <c r="E36" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F36" t="str">
-        <v>9003000010</v>
+        <v>9003000020</v>
       </c>
       <c r="G36" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="H36" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I36" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J36" t="str">
-        <v>30000079190</v>
+        <v>30000158380</v>
       </c>
       <c r="K36" t="str">
         <v>State Bank of India</v>
@@ -2965,39 +2965,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M36" t="str">
-        <v>SBIN0005392</v>
+        <v>SBIN0009850</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>0300039</v>
+        <v>0300049</v>
       </c>
       <c r="B37" t="str">
-        <v>RAKESH MISHRA</v>
+        <v>ASHA CHAUDHARY</v>
       </c>
       <c r="C37" t="str">
-        <v>Senior Clerk</v>
+        <v>Clerk</v>
       </c>
       <c r="D37" t="str">
-        <v>Middle School Dumri Katsari No.4</v>
+        <v>High School Tariyani</v>
       </c>
       <c r="E37" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F37" t="str">
-        <v>9003000039</v>
+        <v>9003000049</v>
       </c>
       <c r="G37" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H37" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I37" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="J37" t="str">
-        <v>30000308841</v>
+        <v>30000388031</v>
       </c>
       <c r="K37" t="str">
         <v>State Bank of India</v>
@@ -3006,18 +3006,18 @@
         <v>Sheohar</v>
       </c>
       <c r="M37" t="str">
-        <v>SBIN0002214</v>
+        <v>SBIN0002138</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>0300011</v>
+        <v>0300091</v>
       </c>
       <c r="B38" t="str">
-        <v>SHAILESH SINHA</v>
+        <v>VIJAY KUMAR</v>
       </c>
       <c r="C38" t="str">
-        <v>Section Officer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D38" t="str">
         <v>Block Office Sheohar</v>
@@ -3026,10 +3026,10 @@
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F38" t="str">
-        <v>9003000011</v>
+        <v>9003000091</v>
       </c>
       <c r="G38" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H38" t="str">
         <v>Sheohar</v>
@@ -3038,7 +3038,7 @@
         <v>Sheohar</v>
       </c>
       <c r="J38" t="str">
-        <v>30000087109</v>
+        <v>30000720629</v>
       </c>
       <c r="K38" t="str">
         <v>State Bank of India</v>
@@ -3047,39 +3047,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M38" t="str">
-        <v>SBIN0008478</v>
+        <v>SBIN0001984</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>0300094</v>
+        <v>0300083</v>
       </c>
       <c r="B39" t="str">
         <v>SUNITA OJHA</v>
       </c>
       <c r="C39" t="str">
-        <v>Assistant Engineer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D39" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Block Office Sheohar No.1</v>
       </c>
       <c r="E39" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F39" t="str">
-        <v>9003000094</v>
+        <v>9003000083</v>
       </c>
       <c r="G39" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H39" t="str">
         <v>Piprahi</v>
       </c>
       <c r="I39" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J39" t="str">
-        <v>30000744386</v>
+        <v>30000657277</v>
       </c>
       <c r="K39" t="str">
         <v>State Bank of India</v>
@@ -3088,39 +3088,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M39" t="str">
-        <v>SBIN0007434</v>
+        <v>SBIN0003700</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>0300104</v>
+        <v>0300082</v>
       </c>
       <c r="B40" t="str">
-        <v>SUNITA PANDEY</v>
+        <v>RAKESH THAKUR</v>
       </c>
       <c r="C40" t="str">
-        <v>Junior Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D40" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Circle Office Dumri Katsari No.1</v>
       </c>
       <c r="E40" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F40" t="str">
-        <v>9003000104</v>
+        <v>9003000082</v>
       </c>
       <c r="G40" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H40" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I40" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J40" t="str">
-        <v>30000823576</v>
+        <v>30000649358</v>
       </c>
       <c r="K40" t="str">
         <v>State Bank of India</v>
@@ -3129,39 +3129,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M40" t="str">
-        <v>SBIN0005687</v>
+        <v>SBIN0004422</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>0300112</v>
+        <v>0300071</v>
       </c>
       <c r="B41" t="str">
-        <v>PANKAJ GUPTA</v>
+        <v>USHA SAH</v>
       </c>
       <c r="C41" t="str">
-        <v>Postmaster</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D41" t="str">
-        <v>State Bank of India, Dumri Katsari</v>
+        <v>Circle Office Dumri Katsari No.2</v>
       </c>
       <c r="E41" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F41" t="str">
-        <v>9003000112</v>
+        <v>9003000071</v>
       </c>
       <c r="G41" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H41" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="I41" t="str">
         <v>Dumri Katsari</v>
       </c>
       <c r="J41" t="str">
-        <v>30000886928</v>
+        <v>30000562249</v>
       </c>
       <c r="K41" t="str">
         <v>State Bank of India</v>
@@ -3170,39 +3170,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M41" t="str">
-        <v>SBIN0001601</v>
+        <v>SBIN0005373</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>0300074</v>
+        <v>0300026</v>
       </c>
       <c r="B42" t="str">
-        <v>NEHA SAH</v>
+        <v>USHA SINHA</v>
       </c>
       <c r="C42" t="str">
-        <v>Teacher</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D42" t="str">
-        <v>Circle Office Dumri Katsari No.4</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="E42" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F42" t="str">
-        <v>9003000074</v>
+        <v>9003000026</v>
       </c>
       <c r="G42" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H42" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I42" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="J42" t="str">
-        <v>30000586006</v>
+        <v>30000205894</v>
       </c>
       <c r="K42" t="str">
         <v>State Bank of India</v>
@@ -3211,39 +3211,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M42" t="str">
-        <v>SBIN0009102</v>
+        <v>SBIN0008204</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>0300088</v>
+        <v>0300029</v>
       </c>
       <c r="B43" t="str">
-        <v>KIRAN VERMA</v>
+        <v>MD. IRFAN SAH</v>
       </c>
       <c r="C43" t="str">
-        <v>Assistant Engineer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D43" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>Block Agriculture Office Dumri Katsari No.4</v>
       </c>
       <c r="E43" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F43" t="str">
-        <v>9003000088</v>
+        <v>9003000029</v>
       </c>
       <c r="G43" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H43" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I43" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J43" t="str">
-        <v>30000696872</v>
+        <v>30000229651</v>
       </c>
       <c r="K43" t="str">
         <v>State Bank of India</v>
@@ -3252,39 +3252,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M43" t="str">
-        <v>SBIN0007139</v>
+        <v>SBIN0006550</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>0300107</v>
+        <v>0300021</v>
       </c>
       <c r="B44" t="str">
-        <v>UMESH ANSARI</v>
+        <v>ASHA RAM</v>
       </c>
       <c r="C44" t="str">
-        <v>Branch Manager</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D44" t="str">
-        <v>Punjab National Bank, Dumri Katsari</v>
+        <v>PHC Sheohar No.1</v>
       </c>
       <c r="E44" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F44" t="str">
-        <v>9003000107</v>
+        <v>9003000021</v>
       </c>
       <c r="G44" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H44" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="I44" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="J44" t="str">
-        <v>30000847333</v>
+        <v>30000166299</v>
       </c>
       <c r="K44" t="str">
         <v>State Bank of India</v>
@@ -3293,39 +3293,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M44" t="str">
-        <v>SBIN0001860</v>
+        <v>SBIN0002682</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>0300084</v>
+        <v>0300012</v>
       </c>
       <c r="B45" t="str">
-        <v>KUMARI ANJALI ANSARI</v>
+        <v>MAMTA JHA</v>
       </c>
       <c r="C45" t="str">
-        <v>Clerk</v>
+        <v>Section Officer</v>
       </c>
       <c r="D45" t="str">
-        <v>Middle School Purnahiya No.4</v>
+        <v>Panchayat Bhawan Tariyani No.3</v>
       </c>
       <c r="E45" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F45" t="str">
-        <v>9003000084</v>
+        <v>9003000012</v>
       </c>
       <c r="G45" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H45" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="I45" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I45" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="J45" t="str">
-        <v>30000665196</v>
+        <v>30000095028</v>
       </c>
       <c r="K45" t="str">
         <v>State Bank of India</v>
@@ -3334,39 +3334,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M45" t="str">
-        <v>SBIN0004505</v>
+        <v>SBIN0009997</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>0300082</v>
+        <v>0300106</v>
       </c>
       <c r="B46" t="str">
-        <v>ANITA MAHTO</v>
+        <v>MANOJ PASWAN</v>
       </c>
       <c r="C46" t="str">
-        <v>Office Assistant</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D46" t="str">
-        <v>PHC Dumri Katsari No.4</v>
+        <v>State Bank of India, Dumri Katsari</v>
       </c>
       <c r="E46" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F46" t="str">
-        <v>9003000082</v>
+        <v>9003000106</v>
       </c>
       <c r="G46" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H46" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I46" t="str">
         <v>Dumri Katsari</v>
       </c>
       <c r="J46" t="str">
-        <v>30000649358</v>
+        <v>30000839414</v>
       </c>
       <c r="K46" t="str">
         <v>State Bank of India</v>
@@ -3375,39 +3375,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M46" t="str">
-        <v>SBIN0003052</v>
+        <v>SBIN0006740</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0300085</v>
+        <v>0300110</v>
       </c>
       <c r="B47" t="str">
-        <v>MD. IRFAN GUPTA</v>
+        <v>RAVI SINGH</v>
       </c>
       <c r="C47" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D47" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>Head Post Office, Dumri Katsari</v>
       </c>
       <c r="E47" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F47" t="str">
-        <v>9003000085</v>
+        <v>9003000110</v>
       </c>
       <c r="G47" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H47" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I47" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J47" t="str">
-        <v>30000673115</v>
+        <v>30000871090</v>
       </c>
       <c r="K47" t="str">
         <v>State Bank of India</v>
@@ -3416,39 +3416,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M47" t="str">
-        <v>SBIN0001827</v>
+        <v>SBIN0003304</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0300017</v>
+        <v>0300078</v>
       </c>
       <c r="B48" t="str">
-        <v>PANKAJ MISHRA</v>
+        <v>SURESH TIWARI</v>
       </c>
       <c r="C48" t="str">
-        <v>Senior Teacher</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D48" t="str">
-        <v>Panchayat Bhawan Piprahi No.4</v>
+        <v>CDPO Office Purnahiya No.3</v>
       </c>
       <c r="E48" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F48" t="str">
-        <v>9003000017</v>
+        <v>9003000078</v>
       </c>
       <c r="G48" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H48" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I48" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J48" t="str">
-        <v>30000134623</v>
+        <v>30000617682</v>
       </c>
       <c r="K48" t="str">
         <v>State Bank of India</v>
@@ -3457,30 +3457,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M48" t="str">
-        <v>SBIN0005930</v>
+        <v>SBIN0009785</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0300091</v>
+        <v>0300109</v>
       </c>
       <c r="B49" t="str">
-        <v>NEHA RAI</v>
+        <v>NASREEN CHAUDHARY</v>
       </c>
       <c r="C49" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D49" t="str">
-        <v>RWD Sub-Division Sheohar</v>
+        <v>State Bank of India, Sheohar</v>
       </c>
       <c r="E49" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F49" t="str">
-        <v>9003000091</v>
+        <v>9003000109</v>
       </c>
       <c r="G49" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H49" t="str">
         <v>Sheohar</v>
@@ -3489,7 +3489,7 @@
         <v>Sheohar</v>
       </c>
       <c r="J49" t="str">
-        <v>30000720629</v>
+        <v>30000863171</v>
       </c>
       <c r="K49" t="str">
         <v>State Bank of India</v>
@@ -3498,39 +3498,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M49" t="str">
-        <v>SBIN0007316</v>
+        <v>SBIN0005546</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0300048</v>
+        <v>0300087</v>
       </c>
       <c r="B50" t="str">
-        <v>NITISH GUPTA</v>
+        <v>DEEPAK PASWAN</v>
       </c>
       <c r="C50" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D50" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="E50" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F50" t="str">
-        <v>9003000048</v>
+        <v>9003000087</v>
       </c>
       <c r="G50" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H50" t="str">
         <v>Piprahi</v>
       </c>
       <c r="I50" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J50" t="str">
-        <v>30000380112</v>
+        <v>30000688953</v>
       </c>
       <c r="K50" t="str">
         <v>State Bank of India</v>
@@ -3539,39 +3539,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M50" t="str">
-        <v>SBIN0006386</v>
+        <v>SBIN0002677</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>0300034</v>
+        <v>0300101</v>
       </c>
       <c r="B51" t="str">
-        <v>NIRMALA SAH</v>
+        <v>MD. SHAHID GUPTA</v>
       </c>
       <c r="C51" t="str">
-        <v>Senior Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D51" t="str">
-        <v>Panchayat Bhawan Piprahi</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="E51" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F51" t="str">
-        <v>9003000034</v>
+        <v>9003000101</v>
       </c>
       <c r="G51" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H51" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I51" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J51" t="str">
-        <v>30000269246</v>
+        <v>30000799819</v>
       </c>
       <c r="K51" t="str">
         <v>State Bank of India</v>
@@ -3580,39 +3580,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M51" t="str">
-        <v>SBIN0003356</v>
+        <v>SBIN0001031</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>0300053</v>
+        <v>0300077</v>
       </c>
       <c r="B52" t="str">
-        <v>VINOD SAH</v>
+        <v>RINKU PANDEY</v>
       </c>
       <c r="C52" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D52" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>Project Girls High School Piprahi</v>
       </c>
       <c r="E52" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F52" t="str">
-        <v>9003000053</v>
+        <v>9003000077</v>
       </c>
       <c r="G52" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H52" t="str">
         <v>Purnahiya</v>
       </c>
       <c r="I52" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="J52" t="str">
-        <v>30000419707</v>
+        <v>30000609763</v>
       </c>
       <c r="K52" t="str">
         <v>State Bank of India</v>
@@ -3621,39 +3621,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M52" t="str">
-        <v>SBIN0003196</v>
+        <v>SBIN0002003</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>0300003</v>
+        <v>0300019</v>
       </c>
       <c r="B53" t="str">
-        <v>PRAMOD JHA</v>
+        <v>PANKAJ PANDEY</v>
       </c>
       <c r="C53" t="str">
-        <v>Assistant Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D53" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>High School Tariyani No.1</v>
       </c>
       <c r="E53" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F53" t="str">
-        <v>9003000003</v>
+        <v>9003000019</v>
       </c>
       <c r="G53" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="H53" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I53" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="J53" t="str">
-        <v>30000023757</v>
+        <v>30000150461</v>
       </c>
       <c r="K53" t="str">
         <v>State Bank of India</v>
@@ -3662,39 +3662,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M53" t="str">
-        <v>SBIN0003273</v>
+        <v>SBIN0009974</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>0300036</v>
+        <v>0300042</v>
       </c>
       <c r="B54" t="str">
-        <v>MAHESH MAHTO</v>
+        <v>MD. IRFAN GUPTA</v>
       </c>
       <c r="C54" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D54" t="str">
-        <v>Project Girls High School Purnahiya No.2</v>
+        <v>Primary School Dumri Katsari No.4</v>
       </c>
       <c r="E54" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F54" t="str">
-        <v>9003000036</v>
+        <v>9003000042</v>
       </c>
       <c r="G54" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="H54" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I54" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J54" t="str">
-        <v>30000285084</v>
+        <v>30000332598</v>
       </c>
       <c r="K54" t="str">
         <v>State Bank of India</v>
@@ -3703,39 +3703,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M54" t="str">
-        <v>SBIN0006757</v>
+        <v>SBIN0006386</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>0300122</v>
+        <v>0300047</v>
       </c>
       <c r="B55" t="str">
-        <v>NIRMALA RAI</v>
+        <v>MAMTA OJHA</v>
       </c>
       <c r="C55" t="str">
-        <v>Branch Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D55" t="str">
-        <v>UCO Bank, Purnahiya</v>
+        <v>Middle School Sheohar No.1</v>
       </c>
       <c r="E55" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F55" t="str">
-        <v>9003000122</v>
+        <v>9003000047</v>
       </c>
       <c r="G55" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H55" t="str">
         <v>Purnahiya</v>
       </c>
       <c r="I55" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J55" t="str">
-        <v>30000966118</v>
+        <v>30000372193</v>
       </c>
       <c r="K55" t="str">
         <v>State Bank of India</v>
@@ -3744,39 +3744,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M55" t="str">
-        <v>SBIN0003736</v>
+        <v>SBIN0009792</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>0300009</v>
+        <v>0300031</v>
       </c>
       <c r="B56" t="str">
-        <v>NASREEN VERMA</v>
+        <v>ASHA DEVI</v>
       </c>
       <c r="C56" t="str">
-        <v>Section Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D56" t="str">
-        <v>CDPO Office Piprahi</v>
+        <v>Primary School Dumri Katsari</v>
       </c>
       <c r="E56" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F56" t="str">
-        <v>9003000009</v>
+        <v>9003000031</v>
       </c>
       <c r="G56" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H56" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I56" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J56" t="str">
-        <v>30000071271</v>
+        <v>30000245489</v>
       </c>
       <c r="K56" t="str">
         <v>State Bank of India</v>
@@ -3785,39 +3785,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M56" t="str">
-        <v>SBIN0009883</v>
+        <v>SBIN0009360</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>0300033</v>
+        <v>0300103</v>
       </c>
       <c r="B57" t="str">
-        <v>MD. IRFAN PRASAD</v>
+        <v>FARHAT KHATUN</v>
       </c>
       <c r="C57" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D57" t="str">
-        <v>Panchayat Bhawan Dumri Katsari</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="E57" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F57" t="str">
-        <v>9003000033</v>
+        <v>9003000103</v>
       </c>
       <c r="G57" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H57" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I57" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="J57" t="str">
-        <v>30000261327</v>
+        <v>30000815657</v>
       </c>
       <c r="K57" t="str">
         <v>State Bank of India</v>
@@ -3826,39 +3826,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M57" t="str">
-        <v>SBIN0008331</v>
+        <v>SBIN0006099</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>0300007</v>
+        <v>0300058</v>
       </c>
       <c r="B58" t="str">
-        <v>NITISH VERMA</v>
+        <v>USHA SINGH</v>
       </c>
       <c r="C58" t="str">
-        <v>Assistant Engineer</v>
+        <v>Accountant</v>
       </c>
       <c r="D58" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>Block Education Office Piprahi No.1</v>
       </c>
       <c r="E58" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F58" t="str">
-        <v>9003000007</v>
+        <v>9003000058</v>
       </c>
       <c r="G58" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H58" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I58" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J58" t="str">
-        <v>30000055433</v>
+        <v>30000459302</v>
       </c>
       <c r="K58" t="str">
         <v>State Bank of India</v>
@@ -3867,39 +3867,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M58" t="str">
-        <v>SBIN0001123</v>
+        <v>SBIN0009753</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>0300065</v>
+        <v>0300005</v>
       </c>
       <c r="B59" t="str">
-        <v>ANIL TIWARI</v>
+        <v>NEHA SINHA</v>
       </c>
       <c r="C59" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D59" t="str">
-        <v>Panchayat Bhawan Piprahi No.3</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="E59" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F59" t="str">
-        <v>9003000065</v>
+        <v>9003000005</v>
       </c>
       <c r="G59" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H59" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I59" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J59" t="str">
-        <v>30000514735</v>
+        <v>30000039595</v>
       </c>
       <c r="K59" t="str">
         <v>State Bank of India</v>
@@ -3908,39 +3908,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M59" t="str">
-        <v>SBIN0009027</v>
+        <v>SBIN0004345</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>0300087</v>
+        <v>0300079</v>
       </c>
       <c r="B60" t="str">
-        <v>RAVI PRASAD P</v>
+        <v>NASREEN YADAV</v>
       </c>
       <c r="C60" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D60" t="str">
-        <v>Block Office Tariyani</v>
+        <v>Middle School Piprahi</v>
       </c>
       <c r="E60" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F60" t="str">
-        <v>9003000087</v>
+        <v>9003000079</v>
       </c>
       <c r="G60" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H60" t="str">
         <v>Tariyani</v>
       </c>
       <c r="I60" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="J60" t="str">
-        <v>30000688953</v>
+        <v>30000625601</v>
       </c>
       <c r="K60" t="str">
         <v>State Bank of India</v>
@@ -3949,39 +3949,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M60" t="str">
-        <v>SBIN0002985</v>
+        <v>SBIN0008927</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>0300057</v>
+        <v>0300070</v>
       </c>
       <c r="B61" t="str">
-        <v>KIRAN MISHRA</v>
+        <v>KUMARI ANJALI SHARMA</v>
       </c>
       <c r="C61" t="str">
         <v>Teacher</v>
       </c>
       <c r="D61" t="str">
-        <v>PHC Dumri Katsari</v>
+        <v>Circle Office Purnahiya No.2</v>
       </c>
       <c r="E61" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F61" t="str">
-        <v>9003000057</v>
+        <v>9003000070</v>
       </c>
       <c r="G61" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H61" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="I61" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J61" t="str">
-        <v>30000451383</v>
+        <v>30000554330</v>
       </c>
       <c r="K61" t="str">
         <v>State Bank of India</v>
@@ -3990,39 +3990,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M61" t="str">
-        <v>SBIN0004889</v>
+        <v>SBIN0004132</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>0300016</v>
+        <v>0300027</v>
       </c>
       <c r="B62" t="str">
-        <v>MAHESH SHARMA</v>
+        <v>SANJAY KHATUN</v>
       </c>
       <c r="C62" t="str">
-        <v>Senior Teacher</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D62" t="str">
-        <v>Kanya Middle School Piprahi No.3</v>
+        <v>PHC Dumri Katsari No.1</v>
       </c>
       <c r="E62" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F62" t="str">
-        <v>9003000016</v>
+        <v>9003000027</v>
       </c>
       <c r="G62" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H62" t="str">
         <v>Tariyani</v>
       </c>
       <c r="I62" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J62" t="str">
-        <v>30000126704</v>
+        <v>30000213813</v>
       </c>
       <c r="K62" t="str">
         <v>State Bank of India</v>
@@ -4031,39 +4031,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M62" t="str">
-        <v>SBIN0008116</v>
+        <v>SBIN0006060</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>0300041</v>
+        <v>0300068</v>
       </c>
       <c r="B63" t="str">
-        <v>AMIT ALAM</v>
+        <v>SANTOSH SAH</v>
       </c>
       <c r="C63" t="str">
-        <v>Senior Clerk</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D63" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>CDPO Office Tariyani</v>
       </c>
       <c r="E63" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="F63" t="str">
-        <v>9003000041</v>
+        <v>9003000068</v>
       </c>
       <c r="G63" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H63" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I63" t="str">
         <v>Tariyani</v>
       </c>
       <c r="J63" t="str">
-        <v>30000324679</v>
+        <v>30000538492</v>
       </c>
       <c r="K63" t="str">
         <v>State Bank of India</v>
@@ -4072,39 +4072,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M63" t="str">
-        <v>SBIN0004282</v>
+        <v>SBIN0003789</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>0300046</v>
+        <v>0300002</v>
       </c>
       <c r="B64" t="str">
-        <v>RAKESH MISHRA T</v>
+        <v>MAMTA SINGH</v>
       </c>
       <c r="C64" t="str">
-        <v>Teacher</v>
+        <v>Section Officer</v>
       </c>
       <c r="D64" t="str">
-        <v>CDPO Office Sheohar No.1</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="E64" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F64" t="str">
-        <v>9003000046</v>
+        <v>9003000002</v>
       </c>
       <c r="G64" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H64" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="I64" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="J64" t="str">
-        <v>30000364274</v>
+        <v>30000015838</v>
       </c>
       <c r="K64" t="str">
         <v>State Bank of India</v>
@@ -4113,30 +4113,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M64" t="str">
-        <v>SBIN0002320</v>
+        <v>SBIN0007559</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>0300090</v>
+        <v>0300111</v>
       </c>
       <c r="B65" t="str">
-        <v>RAMESH ALAM</v>
+        <v>AJAY CHAUDHARY</v>
       </c>
       <c r="C65" t="str">
-        <v>Junior Engineer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D65" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>Central Bank of India, Dumri Katsari</v>
       </c>
       <c r="E65" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F65" t="str">
-        <v>9003000090</v>
+        <v>9003000111</v>
       </c>
       <c r="G65" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H65" t="str">
         <v>Dumri Katsari</v>
@@ -4145,7 +4145,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="J65" t="str">
-        <v>30000712710</v>
+        <v>30000879009</v>
       </c>
       <c r="K65" t="str">
         <v>State Bank of India</v>
@@ -4154,39 +4154,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M65" t="str">
-        <v>SBIN0007828</v>
+        <v>SBIN0002430</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>0300054</v>
+        <v>0300018</v>
       </c>
       <c r="B66" t="str">
-        <v>RAMESH MISHRA</v>
+        <v>RAJESH SAH</v>
       </c>
       <c r="C66" t="str">
-        <v>Accountant</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D66" t="str">
-        <v>Block Office Sheohar No.1</v>
+        <v>Block Education Office Piprahi No.4</v>
       </c>
       <c r="E66" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F66" t="str">
-        <v>9003000054</v>
+        <v>9003000018</v>
       </c>
       <c r="G66" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H66" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I66" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J66" t="str">
-        <v>30000427626</v>
+        <v>30000142542</v>
       </c>
       <c r="K66" t="str">
         <v>State Bank of India</v>
@@ -4195,39 +4195,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M66" t="str">
-        <v>SBIN0004560</v>
+        <v>SBIN0009286</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>0300115</v>
+        <v>0300098</v>
       </c>
       <c r="B67" t="str">
-        <v>MD. IRFAN PRASAD M</v>
+        <v>MAMTA KUMAR</v>
       </c>
       <c r="C67" t="str">
-        <v>Administrative Officer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D67" t="str">
-        <v>Punjab National Bank, Dumri Katsari</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="E67" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F67" t="str">
-        <v>9003000115</v>
+        <v>9003000098</v>
       </c>
       <c r="G67" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H67" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I67" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J67" t="str">
-        <v>30000910685</v>
+        <v>30000776062</v>
       </c>
       <c r="K67" t="str">
         <v>State Bank of India</v>
@@ -4236,39 +4236,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M67" t="str">
-        <v>SBIN0009397</v>
+        <v>SBIN0006839</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>0300005</v>
+        <v>0300050</v>
       </c>
       <c r="B68" t="str">
-        <v>ASHA OJHA</v>
+        <v>ALOK SINHA</v>
       </c>
       <c r="C68" t="str">
-        <v>Lecturer</v>
+        <v>Teacher</v>
       </c>
       <c r="D68" t="str">
-        <v>Kanya Middle School Piprahi No.3</v>
+        <v>PHC Purnahiya No.3</v>
       </c>
       <c r="E68" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F68" t="str">
-        <v>9003000005</v>
+        <v>9003000050</v>
       </c>
       <c r="G68" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H68" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I68" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J68" t="str">
-        <v>30000039595</v>
+        <v>30000395950</v>
       </c>
       <c r="K68" t="str">
         <v>State Bank of India</v>
@@ -4277,30 +4277,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M68" t="str">
-        <v>SBIN0004909</v>
+        <v>SBIN0009474</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>0300006</v>
+        <v>0300116</v>
       </c>
       <c r="B69" t="str">
-        <v>SURESH PRASAD</v>
+        <v>ANITA PANDEY</v>
       </c>
       <c r="C69" t="str">
-        <v>Headmaster</v>
+        <v>Postmaster</v>
       </c>
       <c r="D69" t="str">
-        <v>CDPO Office Piprahi No.3</v>
+        <v>Punjab National Bank, Piprahi</v>
       </c>
       <c r="E69" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="F69" t="str">
-        <v>9003000006</v>
+        <v>9003000116</v>
       </c>
       <c r="G69" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H69" t="str">
         <v>Piprahi</v>
@@ -4309,7 +4309,7 @@
         <v>Piprahi</v>
       </c>
       <c r="J69" t="str">
-        <v>30000047514</v>
+        <v>30000918604</v>
       </c>
       <c r="K69" t="str">
         <v>State Bank of India</v>
@@ -4318,39 +4318,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M69" t="str">
-        <v>SBIN0008480</v>
+        <v>SBIN0004415</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>0300042</v>
+        <v>0300113</v>
       </c>
       <c r="B70" t="str">
-        <v>SUNITA SINGH</v>
+        <v>SURESH ANSARI</v>
       </c>
       <c r="C70" t="str">
-        <v>Assistant Teacher</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D70" t="str">
-        <v>Block Education Office Sheohar</v>
+        <v>Bank of India, Piprahi</v>
       </c>
       <c r="E70" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F70" t="str">
-        <v>9003000042</v>
+        <v>9003000113</v>
       </c>
       <c r="G70" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H70" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I70" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J70" t="str">
-        <v>30000332598</v>
+        <v>30000894847</v>
       </c>
       <c r="K70" t="str">
         <v>State Bank of India</v>
@@ -4359,39 +4359,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M70" t="str">
-        <v>SBIN0001203</v>
+        <v>SBIN0007124</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>0300073</v>
+        <v>0300016</v>
       </c>
       <c r="B71" t="str">
-        <v>NEHA PRASAD</v>
+        <v>ABDUL KALAM DEVI</v>
       </c>
       <c r="C71" t="str">
-        <v>Data Entry Operator</v>
+        <v>Lecturer</v>
       </c>
       <c r="D71" t="str">
-        <v>Middle School Dumri Katsari No.3</v>
+        <v>PHC Piprahi No.3</v>
       </c>
       <c r="E71" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F71" t="str">
-        <v>9003000073</v>
+        <v>9003000016</v>
       </c>
       <c r="G71" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H71" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I71" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="J71" t="str">
-        <v>30000578087</v>
+        <v>30000126704</v>
       </c>
       <c r="K71" t="str">
         <v>State Bank of India</v>
@@ -4400,15 +4400,15 @@
         <v>Sheohar</v>
       </c>
       <c r="M71" t="str">
-        <v>SBIN0007924</v>
+        <v>SBIN0007804</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>0300051</v>
+        <v>0300059</v>
       </c>
       <c r="B72" t="str">
-        <v>KIRAN OJHA</v>
+        <v>PRAMOD PASWAN</v>
       </c>
       <c r="C72" t="str">
         <v>Revenue Karmachari</v>
@@ -4420,7 +4420,7 @@
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F72" t="str">
-        <v>9003000051</v>
+        <v>9003000059</v>
       </c>
       <c r="G72" t="str">
         <v>POLLING OFFICER-2</v>
@@ -4432,7 +4432,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="J72" t="str">
-        <v>30000403869</v>
+        <v>30000467221</v>
       </c>
       <c r="K72" t="str">
         <v>State Bank of India</v>
@@ -4441,39 +4441,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M72" t="str">
-        <v>SBIN0009725</v>
+        <v>SBIN0009715</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>0300103</v>
+        <v>0300095</v>
       </c>
       <c r="B73" t="str">
-        <v>RAKESH SINGH</v>
+        <v>NASREEN MISHRA</v>
       </c>
       <c r="C73" t="str">
-        <v>Assistant Engineer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D73" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="E73" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F73" t="str">
-        <v>9003000103</v>
+        <v>9003000095</v>
       </c>
       <c r="G73" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H73" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I73" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="J73" t="str">
-        <v>30000815657</v>
+        <v>30000752305</v>
       </c>
       <c r="K73" t="str">
         <v>State Bank of India</v>
@@ -4482,39 +4482,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M73" t="str">
-        <v>SBIN0002976</v>
+        <v>SBIN0003824</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>0300038</v>
+        <v>0300015</v>
       </c>
       <c r="B74" t="str">
-        <v>DEEPAK JHA</v>
+        <v>MD. SHAHID KUMAR</v>
       </c>
       <c r="C74" t="str">
-        <v>Senior Clerk</v>
+        <v>Lecturer</v>
       </c>
       <c r="D74" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Circle Office Tariyani No.2</v>
       </c>
       <c r="E74" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F74" t="str">
-        <v>9003000038</v>
+        <v>9003000015</v>
       </c>
       <c r="G74" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H74" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="I74" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="J74" t="str">
-        <v>30000300922</v>
+        <v>30000118785</v>
       </c>
       <c r="K74" t="str">
         <v>State Bank of India</v>
@@ -4523,30 +4523,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M74" t="str">
-        <v>SBIN0005616</v>
+        <v>SBIN0002763</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>0300120</v>
+        <v>0300100</v>
       </c>
       <c r="B75" t="str">
-        <v>MAHESH SAH</v>
+        <v>ALOK PRASAD</v>
       </c>
       <c r="C75" t="str">
-        <v>Postmaster</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D75" t="str">
-        <v>UCO Bank, Piprahi</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="E75" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="F75" t="str">
-        <v>9003000120</v>
+        <v>9003000100</v>
       </c>
       <c r="G75" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H75" t="str">
         <v>Sheohar</v>
@@ -4555,7 +4555,7 @@
         <v>Piprahi</v>
       </c>
       <c r="J75" t="str">
-        <v>30000950280</v>
+        <v>30000791900</v>
       </c>
       <c r="K75" t="str">
         <v>State Bank of India</v>
@@ -4564,7 +4564,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M75" t="str">
-        <v>SBIN0003150</v>
+        <v>SBIN0009517</v>
       </c>
     </row>
     <row r="76">
@@ -4572,16 +4572,16 @@
         <v>0300013</v>
       </c>
       <c r="B76" t="str">
-        <v>SHAILESH ALAM</v>
+        <v>NEHA YADAV</v>
       </c>
       <c r="C76" t="str">
-        <v>Lecturer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D76" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>Block Education Office Purnahiya</v>
       </c>
       <c r="E76" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F76" t="str">
         <v>9003000013</v>
@@ -4590,10 +4590,10 @@
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="H76" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I76" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J76" t="str">
         <v>30000102947</v>
@@ -4605,39 +4605,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M76" t="str">
-        <v>SBIN0008023</v>
+        <v>SBIN0001900</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>0300077</v>
+        <v>0300045</v>
       </c>
       <c r="B77" t="str">
-        <v>REKHA GUPTA</v>
+        <v>FARHAT RAI</v>
       </c>
       <c r="C77" t="str">
         <v>Teacher</v>
       </c>
       <c r="D77" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Kanya Middle School Tariyani</v>
       </c>
       <c r="E77" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F77" t="str">
-        <v>9003000077</v>
+        <v>9003000045</v>
       </c>
       <c r="G77" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H77" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I77" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="J77" t="str">
-        <v>30000609763</v>
+        <v>30000356355</v>
       </c>
       <c r="K77" t="str">
         <v>State Bank of India</v>
@@ -4646,39 +4646,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M77" t="str">
-        <v>SBIN0005667</v>
+        <v>SBIN0002223</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>0300109</v>
+        <v>0300063</v>
       </c>
       <c r="B78" t="str">
-        <v>POONAM PANDEY</v>
+        <v>DINESH RAI</v>
       </c>
       <c r="C78" t="str">
-        <v>Administrative Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D78" t="str">
-        <v>State Bank of India, Purnahiya</v>
+        <v>Kanya Middle School Tariyani</v>
       </c>
       <c r="E78" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F78" t="str">
-        <v>9003000109</v>
+        <v>9003000063</v>
       </c>
       <c r="G78" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H78" t="str">
         <v>Tariyani</v>
       </c>
       <c r="I78" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="J78" t="str">
-        <v>30000863171</v>
+        <v>30000498897</v>
       </c>
       <c r="K78" t="str">
         <v>State Bank of India</v>
@@ -4687,39 +4687,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M78" t="str">
-        <v>SBIN0002365</v>
+        <v>SBIN0003132</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0300119</v>
+        <v>0300061</v>
       </c>
       <c r="B79" t="str">
-        <v>PRIYANKA SHARMA</v>
+        <v>ALOK MISHRA</v>
       </c>
       <c r="C79" t="str">
-        <v>Assistant Manager</v>
+        <v>Clerk</v>
       </c>
       <c r="D79" t="str">
-        <v>BSNL Exchange, Purnahiya</v>
+        <v>Kanya Middle School Tariyani No.2</v>
       </c>
       <c r="E79" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F79" t="str">
-        <v>9003000119</v>
+        <v>9003000061</v>
       </c>
       <c r="G79" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H79" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I79" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="J79" t="str">
-        <v>30000942361</v>
+        <v>30000483059</v>
       </c>
       <c r="K79" t="str">
         <v>State Bank of India</v>
@@ -4728,39 +4728,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M79" t="str">
-        <v>SBIN0008612</v>
+        <v>SBIN0008025</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>0300105</v>
+        <v>0300037</v>
       </c>
       <c r="B80" t="str">
-        <v>SANJAY PANDEY</v>
+        <v>SHAILESH PASWAN</v>
       </c>
       <c r="C80" t="str">
-        <v>Revenue Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D80" t="str">
-        <v>RWD Sub-Division Tariyani</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="E80" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F80" t="str">
-        <v>9003000105</v>
+        <v>9003000037</v>
       </c>
       <c r="G80" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H80" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="I80" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="J80" t="str">
-        <v>30000831495</v>
+        <v>30000293003</v>
       </c>
       <c r="K80" t="str">
         <v>State Bank of India</v>
@@ -4769,39 +4769,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M80" t="str">
-        <v>SBIN0001798</v>
+        <v>SBIN0008263</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>0300001</v>
+        <v>0300076</v>
       </c>
       <c r="B81" t="str">
-        <v>SANJAY MISHRA</v>
+        <v>MUKESH PASWAN</v>
       </c>
       <c r="C81" t="str">
-        <v>Headmaster</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D81" t="str">
-        <v>CDPO Office Purnahiya No.2</v>
+        <v>Kanya Middle School Sheohar No.4</v>
       </c>
       <c r="E81" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F81" t="str">
-        <v>9003000001</v>
+        <v>9003000076</v>
       </c>
       <c r="G81" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H81" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I81" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J81" t="str">
-        <v>30000007919</v>
+        <v>30000601844</v>
       </c>
       <c r="K81" t="str">
         <v>State Bank of India</v>
@@ -4810,39 +4810,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M81" t="str">
-        <v>SBIN0001721</v>
+        <v>SBIN0006444</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>0300124</v>
+        <v>0300118</v>
       </c>
       <c r="B82" t="str">
-        <v>USHA YADAV</v>
+        <v>NASREEN RAI</v>
       </c>
       <c r="C82" t="str">
-        <v>Postmaster</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D82" t="str">
-        <v>Central Bank of India, Piprahi</v>
+        <v>Central Bank of India, Dumri Katsari</v>
       </c>
       <c r="E82" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F82" t="str">
-        <v>9003000124</v>
+        <v>9003000118</v>
       </c>
       <c r="G82" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="H82" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I82" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J82" t="str">
-        <v>30000981956</v>
+        <v>30000934442</v>
       </c>
       <c r="K82" t="str">
         <v>State Bank of India</v>
@@ -4851,39 +4851,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M82" t="str">
-        <v>SBIN0001802</v>
+        <v>SBIN0008812</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>0300096</v>
+        <v>0300085</v>
       </c>
       <c r="B83" t="str">
-        <v>DEEPAK MISHRA</v>
+        <v>PRAMOD JHA D</v>
       </c>
       <c r="C83" t="str">
         <v>Junior Engineer</v>
       </c>
       <c r="D83" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="E83" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="F83" t="str">
-        <v>9003000096</v>
+        <v>9003000085</v>
       </c>
       <c r="G83" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H83" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I83" t="str">
         <v>Piprahi</v>
       </c>
       <c r="J83" t="str">
-        <v>30000760224</v>
+        <v>30000673115</v>
       </c>
       <c r="K83" t="str">
         <v>State Bank of India</v>
@@ -4892,39 +4892,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M83" t="str">
-        <v>SBIN0002481</v>
+        <v>SBIN0007520</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>0300083</v>
+        <v>0300035</v>
       </c>
       <c r="B84" t="str">
-        <v>ANITA RAM</v>
+        <v>MUKESH PRASAD</v>
       </c>
       <c r="C84" t="str">
-        <v>Office Assistant</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D84" t="str">
-        <v>Primary School Piprahi No.2</v>
+        <v>District Treasury Sheohar</v>
       </c>
       <c r="E84" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F84" t="str">
-        <v>9003000083</v>
+        <v>9003000035</v>
       </c>
       <c r="G84" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H84" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I84" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J84" t="str">
-        <v>30000657277</v>
+        <v>30000277165</v>
       </c>
       <c r="K84" t="str">
         <v>State Bank of India</v>
@@ -4933,39 +4933,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M84" t="str">
-        <v>SBIN0002527</v>
+        <v>SBIN0009090</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>0300019</v>
+        <v>0300099</v>
       </c>
       <c r="B85" t="str">
-        <v>MD. SHAHID GUPTA</v>
+        <v>SHAILESH MAHTO</v>
       </c>
       <c r="C85" t="str">
-        <v>Section Officer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D85" t="str">
-        <v>PHC Purnahiya</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="E85" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F85" t="str">
-        <v>9003000019</v>
+        <v>9003000099</v>
       </c>
       <c r="G85" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H85" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I85" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J85" t="str">
-        <v>30000150461</v>
+        <v>30000783981</v>
       </c>
       <c r="K85" t="str">
         <v>State Bank of India</v>
@@ -4974,39 +4974,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M85" t="str">
-        <v>SBIN0004236</v>
+        <v>SBIN0003314</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>0300027</v>
+        <v>0300048</v>
       </c>
       <c r="B86" t="str">
-        <v>SURESH ANSARI</v>
+        <v>KUMARI ANJALI MAHTO F</v>
       </c>
       <c r="C86" t="str">
-        <v>Head Clerk</v>
+        <v>Clerk</v>
       </c>
       <c r="D86" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Project Girls High School Dumri Katsari</v>
       </c>
       <c r="E86" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F86" t="str">
-        <v>9003000027</v>
+        <v>9003000048</v>
       </c>
       <c r="G86" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H86" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I86" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J86" t="str">
-        <v>30000213813</v>
+        <v>30000380112</v>
       </c>
       <c r="K86" t="str">
         <v>State Bank of India</v>
@@ -5015,39 +5015,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M86" t="str">
-        <v>SBIN0003252</v>
+        <v>SBIN0003742</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>0300126</v>
+        <v>0300072</v>
       </c>
       <c r="B87" t="str">
-        <v>MD. IRFAN DEVI</v>
+        <v>MD. SHAHID KUMAR G</v>
       </c>
       <c r="C87" t="str">
-        <v>Postmaster</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D87" t="str">
-        <v>Central Bank of India, Piprahi</v>
+        <v>Block Agriculture Office Purnahiya No.2</v>
       </c>
       <c r="E87" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F87" t="str">
-        <v>9003000126</v>
+        <v>9003000072</v>
       </c>
       <c r="G87" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H87" t="str">
         <v>Dumri Katsari</v>
       </c>
       <c r="I87" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J87" t="str">
-        <v>30000997794</v>
+        <v>30000570168</v>
       </c>
       <c r="K87" t="str">
         <v>State Bank of India</v>
@@ -5056,39 +5056,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M87" t="str">
-        <v>SBIN0001441</v>
+        <v>SBIN0009606</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>0300099</v>
+        <v>0300075</v>
       </c>
       <c r="B88" t="str">
-        <v>RAMESH MAHTO</v>
+        <v>RANJIT YADAV</v>
       </c>
       <c r="C88" t="str">
-        <v>Junior Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D88" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Block Education Office Sheohar</v>
       </c>
       <c r="E88" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F88" t="str">
-        <v>9003000099</v>
+        <v>9003000075</v>
       </c>
       <c r="G88" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H88" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I88" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J88" t="str">
-        <v>30000783981</v>
+        <v>30000593925</v>
       </c>
       <c r="K88" t="str">
         <v>State Bank of India</v>
@@ -5097,30 +5097,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M88" t="str">
-        <v>SBIN0009459</v>
+        <v>SBIN0009504</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>0300069</v>
+        <v>0300039</v>
       </c>
       <c r="B89" t="str">
-        <v>RAVI ANSARI</v>
+        <v>MD. SHAHID KHATUN</v>
       </c>
       <c r="C89" t="str">
-        <v>Clerk</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D89" t="str">
-        <v>Panchayat Bhawan Sheohar</v>
+        <v>High School Sheohar</v>
       </c>
       <c r="E89" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F89" t="str">
-        <v>9003000069</v>
+        <v>9003000039</v>
       </c>
       <c r="G89" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H89" t="str">
         <v>Piprahi</v>
@@ -5129,7 +5129,7 @@
         <v>Sheohar</v>
       </c>
       <c r="J89" t="str">
-        <v>30000546411</v>
+        <v>30000308841</v>
       </c>
       <c r="K89" t="str">
         <v>State Bank of India</v>
@@ -5138,39 +5138,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M89" t="str">
-        <v>SBIN0006768</v>
+        <v>SBIN0001133</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>0300111</v>
+        <v>0300064</v>
       </c>
       <c r="B90" t="str">
-        <v>SURESH PRASAD Q</v>
+        <v>PRIYANKA YADAV</v>
       </c>
       <c r="C90" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Teacher</v>
       </c>
       <c r="D90" t="str">
-        <v>Bank of India, Purnahiya</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="E90" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F90" t="str">
-        <v>9003000111</v>
+        <v>9003000064</v>
       </c>
       <c r="G90" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H90" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="I90" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I90" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="J90" t="str">
-        <v>30000879009</v>
+        <v>30000506816</v>
       </c>
       <c r="K90" t="str">
         <v>State Bank of India</v>
@@ -5179,39 +5179,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M90" t="str">
-        <v>SBIN0004784</v>
+        <v>SBIN0003247</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>0300047</v>
+        <v>0300060</v>
       </c>
       <c r="B91" t="str">
-        <v>SANJAY TIWARI</v>
+        <v>PRAMOD MAHTO</v>
       </c>
       <c r="C91" t="str">
-        <v>Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D91" t="str">
-        <v>Middle School Purnahiya No.3</v>
+        <v>Block Agriculture Office Piprahi No.1</v>
       </c>
       <c r="E91" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F91" t="str">
-        <v>9003000047</v>
+        <v>9003000060</v>
       </c>
       <c r="G91" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="H91" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="I91" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="J91" t="str">
-        <v>30000372193</v>
+        <v>30000475140</v>
       </c>
       <c r="K91" t="str">
         <v>State Bank of India</v>
@@ -5220,39 +5220,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M91" t="str">
-        <v>SBIN0003576</v>
+        <v>SBIN0001887</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>0300118</v>
+        <v>0300036</v>
       </c>
       <c r="B92" t="str">
-        <v>SHAILESH PANDEY</v>
+        <v>PANKAJ MAHTO</v>
       </c>
       <c r="C92" t="str">
-        <v>Assistant Manager</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D92" t="str">
-        <v>UCO Bank, Dumri Katsari</v>
+        <v>High School Sheohar</v>
       </c>
       <c r="E92" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F92" t="str">
-        <v>9003000118</v>
+        <v>9003000036</v>
       </c>
       <c r="G92" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H92" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="I92" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="J92" t="str">
-        <v>30000934442</v>
+        <v>30000285084</v>
       </c>
       <c r="K92" t="str">
         <v>State Bank of India</v>
@@ -5261,39 +5261,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M92" t="str">
-        <v>SBIN0001771</v>
+        <v>SBIN0001873</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>0300098</v>
+        <v>0300010</v>
       </c>
       <c r="B93" t="str">
-        <v>SURESH SAH</v>
+        <v>KIRAN SINGH</v>
       </c>
       <c r="C93" t="str">
-        <v>Revenue Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D93" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>Project Girls High School Tariyani No.1</v>
       </c>
       <c r="E93" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F93" t="str">
-        <v>9003000098</v>
+        <v>9003000010</v>
       </c>
       <c r="G93" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H93" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I93" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="J93" t="str">
-        <v>30000776062</v>
+        <v>30000079190</v>
       </c>
       <c r="K93" t="str">
         <v>State Bank of India</v>
@@ -5302,39 +5302,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M93" t="str">
-        <v>SBIN0007719</v>
+        <v>SBIN0004368</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>0300117</v>
+        <v>0300097</v>
       </c>
       <c r="B94" t="str">
-        <v>RANJIT GUPTA</v>
+        <v>KIRAN PASWAN</v>
       </c>
       <c r="C94" t="str">
-        <v>Assistant Manager</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D94" t="str">
-        <v>Bank of India, Purnahiya</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="E94" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F94" t="str">
-        <v>9003000117</v>
+        <v>9003000097</v>
       </c>
       <c r="G94" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H94" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I94" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="J94" t="str">
-        <v>30000926523</v>
+        <v>30000768143</v>
       </c>
       <c r="K94" t="str">
         <v>State Bank of India</v>
@@ -5343,30 +5343,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M94" t="str">
-        <v>SBIN0005816</v>
+        <v>SBIN0006265</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>0300025</v>
+        <v>0300089</v>
       </c>
       <c r="B95" t="str">
-        <v>ALOK TIWARI</v>
+        <v>ARVIND GUPTA</v>
       </c>
       <c r="C95" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D95" t="str">
-        <v>Block Education Office Sheohar</v>
+        <v>Minor Irrigation Office Sheohar</v>
       </c>
       <c r="E95" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F95" t="str">
-        <v>9003000025</v>
+        <v>9003000089</v>
       </c>
       <c r="G95" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H95" t="str">
         <v>Sheohar</v>
@@ -5375,7 +5375,7 @@
         <v>Sheohar</v>
       </c>
       <c r="J95" t="str">
-        <v>30000197975</v>
+        <v>30000704791</v>
       </c>
       <c r="K95" t="str">
         <v>State Bank of India</v>
@@ -5384,39 +5384,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M95" t="str">
-        <v>SBIN0008915</v>
+        <v>SBIN0008877</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>0300125</v>
+        <v>0300090</v>
       </c>
       <c r="B96" t="str">
-        <v>NIRMALA THAKUR</v>
+        <v>KIRAN ALAM</v>
       </c>
       <c r="C96" t="str">
-        <v>Administrative Officer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D96" t="str">
-        <v>State Bank of India, Purnahiya</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="E96" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F96" t="str">
-        <v>9003000125</v>
+        <v>9003000090</v>
       </c>
       <c r="G96" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H96" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="I96" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="J96" t="str">
-        <v>30000989875</v>
+        <v>30000712710</v>
       </c>
       <c r="K96" t="str">
         <v>State Bank of India</v>
@@ -5425,39 +5425,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M96" t="str">
-        <v>SBIN0005619</v>
+        <v>SBIN0009978</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0300035</v>
+        <v>0300119</v>
       </c>
       <c r="B97" t="str">
-        <v>DEEPAK PASWAN</v>
+        <v>PANKAJ KUMAR</v>
       </c>
       <c r="C97" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Postmaster</v>
       </c>
       <c r="D97" t="str">
-        <v>Block Education Office Piprahi</v>
+        <v>Head Post Office, Sheohar</v>
       </c>
       <c r="E97" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F97" t="str">
-        <v>9003000035</v>
+        <v>9003000119</v>
       </c>
       <c r="G97" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H97" t="str">
         <v>Purnahiya</v>
       </c>
       <c r="I97" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J97" t="str">
-        <v>30000277165</v>
+        <v>30000942361</v>
       </c>
       <c r="K97" t="str">
         <v>State Bank of India</v>
@@ -5466,39 +5466,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M97" t="str">
-        <v>SBIN0005522</v>
+        <v>SBIN0003122</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>0300040</v>
+        <v>0300004</v>
       </c>
       <c r="B98" t="str">
-        <v>RAVI JHA</v>
+        <v>POONAM MISHRA</v>
       </c>
       <c r="C98" t="str">
-        <v>Head Clerk</v>
+        <v>Lecturer</v>
       </c>
       <c r="D98" t="str">
-        <v>PHC Tariyani</v>
+        <v>High School Tariyani No.3</v>
       </c>
       <c r="E98" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="F98" t="str">
-        <v>9003000040</v>
+        <v>9003000004</v>
       </c>
       <c r="G98" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H98" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I98" t="str">
         <v>Tariyani</v>
       </c>
       <c r="J98" t="str">
-        <v>30000316760</v>
+        <v>30000031676</v>
       </c>
       <c r="K98" t="str">
         <v>State Bank of India</v>
@@ -5507,39 +5507,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M98" t="str">
-        <v>SBIN0007869</v>
+        <v>SBIN0003247</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>0300078</v>
+        <v>0300053</v>
       </c>
       <c r="B99" t="str">
-        <v>MUKESH JHA</v>
+        <v>MAHESH TIWARI</v>
       </c>
       <c r="C99" t="str">
-        <v>Data Entry Operator</v>
+        <v>Teacher</v>
       </c>
       <c r="D99" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Block Office Purnahiya No.4</v>
       </c>
       <c r="E99" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F99" t="str">
-        <v>9003000078</v>
+        <v>9003000053</v>
       </c>
       <c r="G99" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H99" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I99" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J99" t="str">
-        <v>30000617682</v>
+        <v>30000419707</v>
       </c>
       <c r="K99" t="str">
         <v>State Bank of India</v>
@@ -5548,39 +5548,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M99" t="str">
-        <v>SBIN0004311</v>
+        <v>SBIN0005985</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>0300072</v>
+        <v>0300084</v>
       </c>
       <c r="B100" t="str">
-        <v>UMESH TIWARI</v>
+        <v>RANJIT VERMA</v>
       </c>
       <c r="C100" t="str">
-        <v>Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D100" t="str">
-        <v>Primary School Dumri Katsari</v>
+        <v>District Treasury Sheohar</v>
       </c>
       <c r="E100" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F100" t="str">
-        <v>9003000072</v>
+        <v>9003000084</v>
       </c>
       <c r="G100" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="H100" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I100" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="J100" t="str">
-        <v>30000570168</v>
+        <v>30000665196</v>
       </c>
       <c r="K100" t="str">
         <v>State Bank of India</v>
@@ -5589,39 +5589,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M100" t="str">
-        <v>SBIN0009826</v>
+        <v>SBIN0002889</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>0300044</v>
+        <v>0300074</v>
       </c>
       <c r="B101" t="str">
-        <v>PRAMOD CHAUDHARY</v>
+        <v>RINKU RAM</v>
       </c>
       <c r="C101" t="str">
-        <v>Accountant</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D101" t="str">
-        <v>High School Sheohar No.1</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="E101" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F101" t="str">
-        <v>9003000044</v>
+        <v>9003000074</v>
       </c>
       <c r="G101" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H101" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="I101" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J101" t="str">
-        <v>30000348436</v>
+        <v>30000586006</v>
       </c>
       <c r="K101" t="str">
         <v>State Bank of India</v>
@@ -5630,39 +5630,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M101" t="str">
-        <v>SBIN0009782</v>
+        <v>SBIN0009298</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>0300071</v>
+        <v>0300126</v>
       </c>
       <c r="B102" t="str">
-        <v>MD. IRFAN PANDEY</v>
+        <v>FARHAT SHARMA</v>
       </c>
       <c r="C102" t="str">
-        <v>Office Assistant</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D102" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>BSNL Exchange, Piprahi</v>
       </c>
       <c r="E102" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F102" t="str">
-        <v>9003000071</v>
+        <v>9003000126</v>
       </c>
       <c r="G102" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H102" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I102" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="J102" t="str">
-        <v>30000562249</v>
+        <v>30000997794</v>
       </c>
       <c r="K102" t="str">
         <v>State Bank of India</v>
@@ -5671,39 +5671,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M102" t="str">
-        <v>SBIN0007042</v>
+        <v>SBIN0003206</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>0300102</v>
+        <v>0300105</v>
       </c>
       <c r="B103" t="str">
-        <v>MANOJ PRASAD</v>
+        <v>AMIT RAM</v>
       </c>
       <c r="C103" t="str">
         <v>Labour Enforcement Officer</v>
       </c>
       <c r="D103" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="E103" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="F103" t="str">
-        <v>9003000102</v>
+        <v>9003000105</v>
       </c>
       <c r="G103" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H103" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I103" t="str">
         <v>Tariyani</v>
       </c>
       <c r="J103" t="str">
-        <v>30000807738</v>
+        <v>30000831495</v>
       </c>
       <c r="K103" t="str">
         <v>State Bank of India</v>
@@ -5712,30 +5712,30 @@
         <v>Sheohar</v>
       </c>
       <c r="M103" t="str">
-        <v>SBIN0005193</v>
+        <v>SBIN0004922</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>0300022</v>
+        <v>0300117</v>
       </c>
       <c r="B104" t="str">
-        <v>MAMTA DEVI</v>
+        <v>ANITA MAHTO</v>
       </c>
       <c r="C104" t="str">
-        <v>Assistant Teacher</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D104" t="str">
-        <v>PHC Piprahi No.1</v>
+        <v>LIC Branch Office, Piprahi</v>
       </c>
       <c r="E104" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="F104" t="str">
-        <v>9003000022</v>
+        <v>9003000117</v>
       </c>
       <c r="G104" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H104" t="str">
         <v>Piprahi</v>
@@ -5744,7 +5744,7 @@
         <v>Piprahi</v>
       </c>
       <c r="J104" t="str">
-        <v>30000174218</v>
+        <v>30000926523</v>
       </c>
       <c r="K104" t="str">
         <v>State Bank of India</v>
@@ -5753,39 +5753,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M104" t="str">
-        <v>SBIN0006475</v>
+        <v>SBIN0006405</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>0300086</v>
+        <v>0300055</v>
       </c>
       <c r="B105" t="str">
-        <v>AMIT KHATUN</v>
+        <v>AJAY DEVI</v>
       </c>
       <c r="C105" t="str">
-        <v>Junior Engineer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D105" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Block Education Office Tariyani</v>
       </c>
       <c r="E105" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F105" t="str">
-        <v>9003000086</v>
+        <v>9003000055</v>
       </c>
       <c r="G105" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H105" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="I105" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="J105" t="str">
-        <v>30000681034</v>
+        <v>30000435545</v>
       </c>
       <c r="K105" t="str">
         <v>State Bank of India</v>
@@ -5794,27 +5794,27 @@
         <v>Sheohar</v>
       </c>
       <c r="M105" t="str">
-        <v>SBIN0001640</v>
+        <v>SBIN0002311</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>0300018</v>
+        <v>0300014</v>
       </c>
       <c r="B106" t="str">
-        <v>SAVITA SINHA</v>
+        <v>FARHAT SAH</v>
       </c>
       <c r="C106" t="str">
-        <v>Senior Teacher</v>
+        <v>Section Officer</v>
       </c>
       <c r="D106" t="str">
-        <v>Circle Office Sheohar</v>
+        <v>Panchayat Bhawan Sheohar</v>
       </c>
       <c r="E106" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="F106" t="str">
-        <v>9003000018</v>
+        <v>9003000014</v>
       </c>
       <c r="G106" t="str">
         <v>PRESIDING OFFICER</v>
@@ -5826,7 +5826,7 @@
         <v>Sheohar</v>
       </c>
       <c r="J106" t="str">
-        <v>30000142542</v>
+        <v>30000110866</v>
       </c>
       <c r="K106" t="str">
         <v>State Bank of India</v>
@@ -5835,39 +5835,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M106" t="str">
-        <v>SBIN0006453</v>
+        <v>SBIN0006071</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>0300063</v>
+        <v>0300022</v>
       </c>
       <c r="B107" t="str">
-        <v>SHAILESH SHARMA</v>
+        <v>RANJIT SAH</v>
       </c>
       <c r="C107" t="str">
-        <v>Teacher</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D107" t="str">
-        <v>Block Agriculture Office Purnahiya No.1</v>
+        <v>PHC Dumri Katsari</v>
       </c>
       <c r="E107" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F107" t="str">
-        <v>9003000063</v>
+        <v>9003000022</v>
       </c>
       <c r="G107" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H107" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="I107" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J107" t="str">
-        <v>30000498897</v>
+        <v>30000174218</v>
       </c>
       <c r="K107" t="str">
         <v>State Bank of India</v>
@@ -5876,39 +5876,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M107" t="str">
-        <v>SBIN0008111</v>
+        <v>SBIN0006085</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>0300029</v>
+        <v>0300092</v>
       </c>
       <c r="B108" t="str">
-        <v>ARVIND MISHRA</v>
+        <v>ABDUL KALAM ALAM</v>
       </c>
       <c r="C108" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D108" t="str">
-        <v>Middle School Piprahi No.3</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="E108" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="F108" t="str">
-        <v>9003000029</v>
+        <v>9003000092</v>
       </c>
       <c r="G108" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H108" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I108" t="str">
         <v>Piprahi</v>
       </c>
       <c r="J108" t="str">
-        <v>30000229651</v>
+        <v>30000728548</v>
       </c>
       <c r="K108" t="str">
         <v>State Bank of India</v>
@@ -5917,39 +5917,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M108" t="str">
-        <v>SBIN0008875</v>
+        <v>SBIN0001790</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>0300055</v>
+        <v>0300001</v>
       </c>
       <c r="B109" t="str">
-        <v>DINESH SINHA</v>
+        <v>ARVIND VERMA</v>
       </c>
       <c r="C109" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Lecturer</v>
       </c>
       <c r="D109" t="str">
-        <v>High School Dumri Katsari No.4</v>
+        <v>Primary School Dumri Katsari No.2</v>
       </c>
       <c r="E109" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F109" t="str">
-        <v>9003000055</v>
+        <v>9003000001</v>
       </c>
       <c r="G109" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H109" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I109" t="str">
         <v>Dumri Katsari</v>
       </c>
       <c r="J109" t="str">
-        <v>30000435545</v>
+        <v>30000007919</v>
       </c>
       <c r="K109" t="str">
         <v>State Bank of India</v>
@@ -5958,39 +5958,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M109" t="str">
-        <v>SBIN0005117</v>
+        <v>SBIN0001102</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>0300052</v>
+        <v>0300121</v>
       </c>
       <c r="B110" t="str">
-        <v>ASHA TIWARI</v>
+        <v>AMIT KUMAR</v>
       </c>
       <c r="C110" t="str">
-        <v>Clerk</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D110" t="str">
-        <v>High School Dumri Katsari No.1</v>
+        <v>Head Post Office, Purnahiya</v>
       </c>
       <c r="E110" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="F110" t="str">
-        <v>9003000052</v>
+        <v>9003000121</v>
       </c>
       <c r="G110" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H110" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I110" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="J110" t="str">
-        <v>30000411788</v>
+        <v>30000958199</v>
       </c>
       <c r="K110" t="str">
         <v>State Bank of India</v>
@@ -5999,39 +5999,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M110" t="str">
-        <v>SBIN0007210</v>
+        <v>SBIN0004966</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>0300067</v>
+        <v>0300057</v>
       </c>
       <c r="B111" t="str">
-        <v>SUNIL THAKUR</v>
+        <v>ALOK PANDEY</v>
       </c>
       <c r="C111" t="str">
         <v>Teacher</v>
       </c>
       <c r="D111" t="str">
-        <v>Middle School Purnahiya</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="E111" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F111" t="str">
-        <v>9003000067</v>
+        <v>9003000057</v>
       </c>
       <c r="G111" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H111" t="str">
         <v>Dumri Katsari</v>
       </c>
       <c r="I111" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J111" t="str">
-        <v>30000530573</v>
+        <v>30000451383</v>
       </c>
       <c r="K111" t="str">
         <v>State Bank of India</v>
@@ -6040,39 +6040,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M111" t="str">
-        <v>SBIN0004495</v>
+        <v>SBIN0009298</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>0300015</v>
+        <v>0300066</v>
       </c>
       <c r="B112" t="str">
-        <v>NIRMALA MAHTO</v>
+        <v>DINESH JHA</v>
       </c>
       <c r="C112" t="str">
-        <v>Senior Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D112" t="str">
-        <v>Block Education Office Purnahiya</v>
+        <v>Circle Office Tariyani No.3</v>
       </c>
       <c r="E112" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F112" t="str">
-        <v>9003000015</v>
+        <v>9003000066</v>
       </c>
       <c r="G112" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H112" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="I112" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="J112" t="str">
-        <v>30000118785</v>
+        <v>30000522654</v>
       </c>
       <c r="K112" t="str">
         <v>State Bank of India</v>
@@ -6081,39 +6081,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M112" t="str">
-        <v>SBIN0001511</v>
+        <v>SBIN0001789</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>0300064</v>
+        <v>0300120</v>
       </c>
       <c r="B113" t="str">
-        <v>MAMTA MISHRA</v>
+        <v>SANTOSH SAH A</v>
       </c>
       <c r="C113" t="str">
-        <v>Teacher</v>
+        <v>Postmaster</v>
       </c>
       <c r="D113" t="str">
-        <v>Panchayat Bhawan Dumri Katsari</v>
+        <v>BSNL Exchange, Piprahi</v>
       </c>
       <c r="E113" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="F113" t="str">
-        <v>9003000064</v>
+        <v>9003000120</v>
       </c>
       <c r="G113" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H113" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I113" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="J113" t="str">
-        <v>30000506816</v>
+        <v>30000950280</v>
       </c>
       <c r="K113" t="str">
         <v>State Bank of India</v>
@@ -6122,39 +6122,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M113" t="str">
-        <v>SBIN0002446</v>
+        <v>SBIN0005018</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>0300032</v>
+        <v>0300065</v>
       </c>
       <c r="B114" t="str">
-        <v>SAVITA TIWARI</v>
+        <v>PRAMOD JHA</v>
       </c>
       <c r="C114" t="str">
-        <v>Assistant Teacher</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D114" t="str">
-        <v>CDPO Office Tariyani No.3</v>
+        <v>Circle Office Dumri Katsari No.3</v>
       </c>
       <c r="E114" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F114" t="str">
-        <v>9003000032</v>
+        <v>9003000065</v>
       </c>
       <c r="G114" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H114" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I114" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J114" t="str">
-        <v>30000253408</v>
+        <v>30000514735</v>
       </c>
       <c r="K114" t="str">
         <v>State Bank of India</v>
@@ -6163,18 +6163,18 @@
         <v>Sheohar</v>
       </c>
       <c r="M114" t="str">
-        <v>SBIN0003419</v>
+        <v>SBIN0003689</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>0300068</v>
+        <v>0300025</v>
       </c>
       <c r="B115" t="str">
-        <v>DEEPAK PASWAN A</v>
+        <v>MUKESH ALAM</v>
       </c>
       <c r="C115" t="str">
-        <v>Teacher</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D115" t="str">
         <v>Primary School Tariyani No.3</v>
@@ -6183,10 +6183,10 @@
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="F115" t="str">
-        <v>9003000068</v>
+        <v>9003000025</v>
       </c>
       <c r="G115" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H115" t="str">
         <v>Tariyani</v>
@@ -6195,7 +6195,7 @@
         <v>Tariyani</v>
       </c>
       <c r="J115" t="str">
-        <v>30000538492</v>
+        <v>30000197975</v>
       </c>
       <c r="K115" t="str">
         <v>State Bank of India</v>
@@ -6204,39 +6204,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M115" t="str">
-        <v>SBIN0001258</v>
+        <v>SBIN0008563</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>0300043</v>
+        <v>0300051</v>
       </c>
       <c r="B116" t="str">
-        <v>AMIT VERMA</v>
+        <v>ABDUL KALAM MAHTO</v>
       </c>
       <c r="C116" t="str">
-        <v>Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D116" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>CDPO Office Dumri Katsari</v>
       </c>
       <c r="E116" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F116" t="str">
-        <v>9003000043</v>
+        <v>9003000051</v>
       </c>
       <c r="G116" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="H116" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I116" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J116" t="str">
-        <v>30000340517</v>
+        <v>30000403869</v>
       </c>
       <c r="K116" t="str">
         <v>State Bank of India</v>
@@ -6245,39 +6245,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M116" t="str">
-        <v>SBIN0006639</v>
+        <v>SBIN0008125</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>0300108</v>
+        <v>0300094</v>
       </c>
       <c r="B117" t="str">
-        <v>VINOD SINHA</v>
+        <v>ALOK ANSARI</v>
       </c>
       <c r="C117" t="str">
-        <v>Assistant Manager</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D117" t="str">
-        <v>Central Bank of India, Piprahi</v>
+        <v>Minor Irrigation Office Dumri Katsari</v>
       </c>
       <c r="E117" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F117" t="str">
-        <v>9003000108</v>
+        <v>9003000094</v>
       </c>
       <c r="G117" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H117" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I117" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J117" t="str">
-        <v>30000855252</v>
+        <v>30000744386</v>
       </c>
       <c r="K117" t="str">
         <v>State Bank of India</v>
@@ -6286,27 +6286,27 @@
         <v>Sheohar</v>
       </c>
       <c r="M117" t="str">
-        <v>SBIN0007997</v>
+        <v>SBIN0008102</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>0300030</v>
+        <v>0300033</v>
       </c>
       <c r="B118" t="str">
-        <v>AJAY JHA</v>
+        <v>MAMTA PASWAN</v>
       </c>
       <c r="C118" t="str">
         <v>Senior Clerk</v>
       </c>
       <c r="D118" t="str">
-        <v>CDPO Office Purnahiya No.4</v>
+        <v>Project Girls High School Sheohar No.1</v>
       </c>
       <c r="E118" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F118" t="str">
-        <v>9003000030</v>
+        <v>9003000033</v>
       </c>
       <c r="G118" t="str">
         <v>POLLING OFFICER-1</v>
@@ -6315,10 +6315,10 @@
         <v>Piprahi</v>
       </c>
       <c r="I118" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J118" t="str">
-        <v>30000237570</v>
+        <v>30000261327</v>
       </c>
       <c r="K118" t="str">
         <v>State Bank of India</v>
@@ -6327,39 +6327,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M118" t="str">
-        <v>SBIN0001061</v>
+        <v>SBIN0009329</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>0300097</v>
+        <v>0300108</v>
       </c>
       <c r="B119" t="str">
-        <v>SAVITA DEVI</v>
+        <v>PANKAJ TIWARI</v>
       </c>
       <c r="C119" t="str">
-        <v>Assistant Engineer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D119" t="str">
-        <v>RWD Sub-Division Tariyani</v>
+        <v>LIC Branch Office, Dumri Katsari</v>
       </c>
       <c r="E119" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F119" t="str">
-        <v>9003000097</v>
+        <v>9003000108</v>
       </c>
       <c r="G119" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="H119" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="I119" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="J119" t="str">
-        <v>30000768143</v>
+        <v>30000855252</v>
       </c>
       <c r="K119" t="str">
         <v>State Bank of India</v>
@@ -6368,39 +6368,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M119" t="str">
-        <v>SBIN0001087</v>
+        <v>SBIN0005277</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>0300049</v>
+        <v>0300006</v>
       </c>
       <c r="B120" t="str">
-        <v>USHA RAM</v>
+        <v>SANJAY JHA</v>
       </c>
       <c r="C120" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Lecturer</v>
       </c>
       <c r="D120" t="str">
-        <v>High School Piprahi No.2</v>
+        <v>Block Agriculture Office Tariyani No.2</v>
       </c>
       <c r="E120" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F120" t="str">
-        <v>9003000049</v>
+        <v>9003000006</v>
       </c>
       <c r="G120" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="H120" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="I120" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="J120" t="str">
-        <v>30000388031</v>
+        <v>30000047514</v>
       </c>
       <c r="K120" t="str">
         <v>State Bank of India</v>
@@ -6409,39 +6409,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M120" t="str">
-        <v>SBIN0003712</v>
+        <v>SBIN0002829</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>0300089</v>
+        <v>0300040</v>
       </c>
       <c r="B121" t="str">
-        <v>SAVITA VERMA</v>
+        <v>RANJIT SINGH</v>
       </c>
       <c r="C121" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D121" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="E121" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F121" t="str">
-        <v>9003000089</v>
+        <v>9003000040</v>
       </c>
       <c r="G121" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="H121" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="I121" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="J121" t="str">
-        <v>30000704791</v>
+        <v>30000316760</v>
       </c>
       <c r="K121" t="str">
         <v>State Bank of India</v>
@@ -6450,39 +6450,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M121" t="str">
-        <v>SBIN0005122</v>
+        <v>SBIN0007965</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>0300026</v>
+        <v>0300023</v>
       </c>
       <c r="B122" t="str">
-        <v>KUMARI ANJALI KHATUN</v>
+        <v>FARHAT MISHRA</v>
       </c>
       <c r="C122" t="str">
         <v>Assistant Teacher</v>
       </c>
       <c r="D122" t="str">
-        <v>Primary School Piprahi No.2</v>
+        <v>Block Office Tariyani No.4</v>
       </c>
       <c r="E122" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F122" t="str">
-        <v>9003000026</v>
+        <v>9003000023</v>
       </c>
       <c r="G122" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="H122" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="I122" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="J122" t="str">
-        <v>30000205894</v>
+        <v>30000182137</v>
       </c>
       <c r="K122" t="str">
         <v>State Bank of India</v>
@@ -6491,27 +6491,27 @@
         <v>Sheohar</v>
       </c>
       <c r="M122" t="str">
-        <v>SBIN0007495</v>
+        <v>SBIN0009788</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>0300061</v>
+        <v>0300046</v>
       </c>
       <c r="B123" t="str">
-        <v>ARVIND PASWAN</v>
+        <v>SANJAY GUPTA</v>
       </c>
       <c r="C123" t="str">
-        <v>Teacher</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D123" t="str">
-        <v>Project Girls High School Sheohar</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="E123" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F123" t="str">
-        <v>9003000061</v>
+        <v>9003000046</v>
       </c>
       <c r="G123" t="str">
         <v>POLLING OFFICER-2</v>
@@ -6520,10 +6520,10 @@
         <v>Sheohar</v>
       </c>
       <c r="I123" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="J123" t="str">
-        <v>30000483059</v>
+        <v>30000364274</v>
       </c>
       <c r="K123" t="str">
         <v>State Bank of India</v>
@@ -6532,39 +6532,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M123" t="str">
-        <v>SBIN0001437</v>
+        <v>SBIN0007894</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>0300106</v>
+        <v>0300056</v>
       </c>
       <c r="B124" t="str">
-        <v>SUNIL YADAV</v>
+        <v>RAKESH OJHA</v>
       </c>
       <c r="C124" t="str">
-        <v>Branch Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D124" t="str">
-        <v>Head Post Office, Tariyani</v>
+        <v>Middle School Tariyani</v>
       </c>
       <c r="E124" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="F124" t="str">
-        <v>9003000106</v>
+        <v>9003000056</v>
       </c>
       <c r="G124" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H124" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="I124" t="str">
         <v>Tariyani</v>
       </c>
       <c r="J124" t="str">
-        <v>30000839414</v>
+        <v>30000443464</v>
       </c>
       <c r="K124" t="str">
         <v>State Bank of India</v>
@@ -6573,39 +6573,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M124" t="str">
-        <v>SBIN0001696</v>
+        <v>SBIN0004651</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>0300028</v>
+        <v>0300080</v>
       </c>
       <c r="B125" t="str">
-        <v>FARHAT GUPTA</v>
+        <v>USHA KHATUN</v>
       </c>
       <c r="C125" t="str">
-        <v>Senior Clerk</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D125" t="str">
-        <v>Block Agriculture Office Dumri Katsari No.4</v>
+        <v>PHC Dumri Katsari No.2</v>
       </c>
       <c r="E125" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="F125" t="str">
-        <v>9003000028</v>
+        <v>9003000080</v>
       </c>
       <c r="G125" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="H125" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="I125" t="str">
         <v>Dumri Katsari</v>
       </c>
       <c r="J125" t="str">
-        <v>30000221732</v>
+        <v>30000633520</v>
       </c>
       <c r="K125" t="str">
         <v>State Bank of India</v>
@@ -6614,39 +6614,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M125" t="str">
-        <v>SBIN0004142</v>
+        <v>SBIN0008257</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>0300014</v>
+        <v>0300062</v>
       </c>
       <c r="B126" t="str">
-        <v>RAJESH KHATUN</v>
+        <v>UMESH KHATUN</v>
       </c>
       <c r="C126" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D126" t="str">
-        <v>Block Office Purnahiya No.2</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="E126" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="F126" t="str">
-        <v>9003000014</v>
+        <v>9003000062</v>
       </c>
       <c r="G126" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="H126" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I126" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="J126" t="str">
-        <v>30000110866</v>
+        <v>30000490978</v>
       </c>
       <c r="K126" t="str">
         <v>State Bank of India</v>
@@ -6655,39 +6655,39 @@
         <v>Sheohar</v>
       </c>
       <c r="M126" t="str">
-        <v>SBIN0005477</v>
+        <v>SBIN0003088</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>0300095</v>
+        <v>0300086</v>
       </c>
       <c r="B127" t="str">
-        <v>MAHESH TIWARI</v>
+        <v>DINESH SINHA</v>
       </c>
       <c r="C127" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D127" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="E127" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="F127" t="str">
-        <v>9003000095</v>
+        <v>9003000086</v>
       </c>
       <c r="G127" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="H127" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="I127" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="J127" t="str">
-        <v>30000752305</v>
+        <v>30000681034</v>
       </c>
       <c r="K127" t="str">
         <v>State Bank of India</v>
@@ -6696,7 +6696,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M127" t="str">
-        <v>SBIN0005540</v>
+        <v>SBIN0006393</v>
       </c>
     </row>
   </sheetData>
@@ -6762,7 +6762,7 @@
         <v>Main</v>
       </c>
       <c r="D3" t="str">
-        <v>Kanya Middle School Piprahi, Room 3</v>
+        <v>High School Piprahi, Room 3</v>
       </c>
       <c r="E3" t="str">
         <v>Piprahi</v>
@@ -6864,7 +6864,7 @@
         <v>Main</v>
       </c>
       <c r="D9" t="str">
-        <v>Kanya Middle School Dumri Katsari, Room 3</v>
+        <v>Panchayat Bhawan Dumri Katsari, Room 3</v>
       </c>
       <c r="E9" t="str">
         <v>Dumri Katsari</v>
@@ -6898,7 +6898,7 @@
         <v>Main</v>
       </c>
       <c r="D11" t="str">
-        <v>Middle School Sheohar, Room 2</v>
+        <v>High School Sheohar, Room 2</v>
       </c>
       <c r="E11" t="str">
         <v>Sheohar</v>
@@ -6915,7 +6915,7 @@
         <v>Main</v>
       </c>
       <c r="D12" t="str">
-        <v>Middle School Piprahi, Room 3</v>
+        <v>High School Piprahi, Room 3</v>
       </c>
       <c r="E12" t="str">
         <v>Piprahi</v>
@@ -6932,7 +6932,7 @@
         <v>Main</v>
       </c>
       <c r="D13" t="str">
-        <v>Block Office Hall Purnahiya, Room 1</v>
+        <v>Panchayat Bhawan Purnahiya, Room 1</v>
       </c>
       <c r="E13" t="str">
         <v>Purnahiya</v>

--- a/test-data/TEST_Sheohar_Project.xlsx
+++ b/test-data/TEST_Sheohar_Project.xlsx
@@ -457,17 +457,17 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Officers — Home Block and Posting Block are used for exclusion: nobody is tagged to a booth in his/her home or posting block.</v>
+        <v>Officers — Home Block (Code) and Posting Block (Code) are used for exclusion: nobody is tagged to a booth in his/her home or posting block. When both officer and booth have a block code (e.g. census code), the code decides.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Officers — Office Name is used for the rule that the 4 members of a party must be from different offices.</v>
+        <v>Officers — Office Code (or Office Name if no code) is used for the rule that the 4 members of a party must be from different offices. Codes protect against spelling mistakes in names.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Booths   — Constituency must be one of the codes in the Constituencies sheet (e.g. TC, GC). Block is mandatory.</v>
+        <v>Booths   — Constituency must be one of the codes in the Constituencies sheet (e.g. TC, GC). Block name or Block Code is mandatory (Block Code recommended).</v>
       </c>
     </row>
     <row r="12">
@@ -612,7 +612,7 @@
         <v>Saved at</v>
       </c>
       <c r="B4" t="str">
-        <v>12-10-2026 18:31:45</v>
+        <v>13-10-2026 03:46:43</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12-10-2026 18:31:45</v>
+        <v>13-10-2026 03:46:43</v>
       </c>
       <c r="B2" t="str">
         <v>Test data generated (Small — Sheohar style (5 blocks, 6 TC + 6 GC booths))</v>
@@ -1475,21 +1475,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:P127"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
     <col min="10" max="10" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1503,2576 +1506,3143 @@
         <v>Designation</v>
       </c>
       <c r="D1" t="str">
+        <v>Office Code</v>
+      </c>
+      <c r="E1" t="str">
         <v>Office Name</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Office Address</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Mobile</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Duty</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
+        <v>Home Block Code</v>
+      </c>
+      <c r="J1" t="str">
         <v>Home Block</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
+        <v>Posting Block Code</v>
+      </c>
+      <c r="L1" t="str">
         <v>Posting Block</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>Account No</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>Bank</v>
       </c>
-      <c r="L1" t="str">
+      <c r="O1" t="str">
         <v>Branch</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>IFSC</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0300008</v>
+        <v>0300015</v>
       </c>
       <c r="B2" t="str">
-        <v>MAHESH VERMA</v>
+        <v>KUMARI ANJALI ANSARI</v>
       </c>
       <c r="C2" t="str">
         <v>Lecturer</v>
       </c>
       <c r="D2" t="str">
-        <v>Block Agriculture Office Purnahiya No.2</v>
+        <v>03015</v>
       </c>
       <c r="E2" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F2" t="str">
-        <v>9003000008</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G2" t="str">
+        <v>9003000015</v>
+      </c>
+      <c r="H2" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
-      <c r="H2" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="I2" t="str">
-        <v>Purnahiya</v>
+        <v>0301</v>
       </c>
       <c r="J2" t="str">
-        <v>30000063352</v>
+        <v>Sheohar</v>
       </c>
       <c r="K2" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L2" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M2" t="str">
-        <v>SBIN0007711</v>
+        <v>30000118785</v>
+      </c>
+      <c r="N2" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P2" t="str">
+        <v>SBIN0008705</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0300122</v>
+        <v>0300059</v>
       </c>
       <c r="B3" t="str">
-        <v>KIRAN OJHA</v>
+        <v>RAVI TIWARI</v>
       </c>
       <c r="C3" t="str">
-        <v>Administrative Officer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D3" t="str">
-        <v>UCO Bank, Purnahiya</v>
+        <v>03030</v>
       </c>
       <c r="E3" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F3" t="str">
-        <v>9003000122</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G3" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000059</v>
       </c>
       <c r="H3" t="str">
-        <v>Piprahi</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I3" t="str">
-        <v>Purnahiya</v>
+        <v>0301</v>
       </c>
       <c r="J3" t="str">
-        <v>30000966118</v>
+        <v>Sheohar</v>
       </c>
       <c r="K3" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L3" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M3" t="str">
-        <v>SBIN0001590</v>
+        <v>30000467221</v>
+      </c>
+      <c r="N3" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P3" t="str">
+        <v>SBIN0002974</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0300081</v>
+        <v>0300098</v>
       </c>
       <c r="B4" t="str">
-        <v>MD. IRFAN PANDEY</v>
+        <v>RANJIT OJHA</v>
       </c>
       <c r="C4" t="str">
-        <v>Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D4" t="str">
-        <v>Project Girls High School Piprahi</v>
+        <v>03075</v>
       </c>
       <c r="E4" t="str">
+        <v>Circle Office Piprahi</v>
+      </c>
+      <c r="F4" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
-      <c r="F4" t="str">
-        <v>9003000081</v>
-      </c>
       <c r="G4" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000098</v>
       </c>
       <c r="H4" t="str">
+        <v>PATROLLING MAGISTRATE</v>
+      </c>
+      <c r="I4" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K4" t="str">
+        <v>0302</v>
+      </c>
+      <c r="L4" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="I4" t="str">
-        <v>Piprahi</v>
-      </c>
-      <c r="J4" t="str">
-        <v>30000641439</v>
-      </c>
-      <c r="K4" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M4" t="str">
-        <v>SBIN0004716</v>
+        <v>30000776062</v>
+      </c>
+      <c r="N4" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P4" t="str">
+        <v>SBIN0006530</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0300024</v>
+        <v>0300023</v>
       </c>
       <c r="B5" t="str">
-        <v>SUNIL MAHTO</v>
+        <v>POONAM MAHTO</v>
       </c>
       <c r="C5" t="str">
         <v>Panchayat Secretary</v>
       </c>
       <c r="D5" t="str">
-        <v>Project Girls High School Tariyani No.3</v>
+        <v>03021</v>
       </c>
       <c r="E5" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Middle School Dumri Katsari No.2</v>
       </c>
       <c r="F5" t="str">
-        <v>9003000024</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G5" t="str">
+        <v>9003000023</v>
+      </c>
+      <c r="H5" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
-      <c r="H5" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="I5" t="str">
-        <v>Tariyani</v>
+        <v>0301</v>
       </c>
       <c r="J5" t="str">
-        <v>30000190056</v>
+        <v>Sheohar</v>
       </c>
       <c r="K5" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L5" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M5" t="str">
-        <v>SBIN0004986</v>
+        <v>30000182137</v>
+      </c>
+      <c r="N5" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O5" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P5" t="str">
+        <v>SBIN0001260</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0300017</v>
+        <v>0300037</v>
       </c>
       <c r="B6" t="str">
-        <v>ANITA RAM</v>
+        <v>SHAILESH OJHA</v>
       </c>
       <c r="C6" t="str">
-        <v>Senior Teacher</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D6" t="str">
-        <v>Block Office Sheohar</v>
+        <v>03034</v>
       </c>
       <c r="E6" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Circle Office Purnahiya No.1</v>
       </c>
       <c r="F6" t="str">
-        <v>9003000017</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G6" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000037</v>
       </c>
       <c r="H6" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I6" t="str">
-        <v>Sheohar</v>
+        <v>0305</v>
       </c>
       <c r="J6" t="str">
-        <v>30000134623</v>
+        <v>Tariyani</v>
       </c>
       <c r="K6" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L6" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M6" t="str">
-        <v>SBIN0009889</v>
+        <v>30000293003</v>
+      </c>
+      <c r="N6" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O6" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P6" t="str">
+        <v>SBIN0009950</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>0300123</v>
+        <v>0300090</v>
       </c>
       <c r="B7" t="str">
-        <v>PANKAJ DEVI</v>
+        <v>SANTOSH SINGH</v>
       </c>
       <c r="C7" t="str">
-        <v>Assistant Manager</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D7" t="str">
-        <v>LIC Branch Office, Sheohar</v>
+        <v>03073</v>
       </c>
       <c r="E7" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>RWD Sub-Division Purnahiya</v>
       </c>
       <c r="F7" t="str">
-        <v>9003000123</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G7" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000090</v>
       </c>
       <c r="H7" t="str">
+        <v>PATROLLING MAGISTRATE</v>
+      </c>
+      <c r="I7" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J7" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I7" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="J7" t="str">
-        <v>30000974037</v>
-      </c>
       <c r="K7" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L7" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M7" t="str">
-        <v>SBIN0002977</v>
+        <v>30000712710</v>
+      </c>
+      <c r="N7" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P7" t="str">
+        <v>SBIN0007281</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0300093</v>
+        <v>0300028</v>
       </c>
       <c r="B8" t="str">
-        <v>POONAM KUMAR</v>
+        <v>UMESH ANSARI</v>
       </c>
       <c r="C8" t="str">
-        <v>Revenue Officer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D8" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>03026</v>
       </c>
       <c r="E8" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Kanya Middle School Purnahiya No.1</v>
       </c>
       <c r="F8" t="str">
-        <v>9003000093</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G8" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000028</v>
       </c>
       <c r="H8" t="str">
-        <v>Tariyani</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I8" t="str">
-        <v>Piprahi</v>
+        <v>0303</v>
       </c>
       <c r="J8" t="str">
-        <v>30000736467</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K8" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L8" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M8" t="str">
-        <v>SBIN0003584</v>
+        <v>30000221732</v>
+      </c>
+      <c r="N8" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P8" t="str">
+        <v>SBIN0004029</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0300041</v>
+        <v>0300043</v>
       </c>
       <c r="B9" t="str">
-        <v>SUNIL KHATUN</v>
+        <v>KIRAN JHA</v>
       </c>
       <c r="C9" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Clerk</v>
       </c>
       <c r="D9" t="str">
-        <v>CDPO Office Piprahi No.2</v>
+        <v>03008</v>
       </c>
       <c r="E9" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="F9" t="str">
-        <v>9003000041</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G9" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000043</v>
       </c>
       <c r="H9" t="str">
+        <v>POLLING OFFICER-2</v>
+      </c>
+      <c r="I9" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K9" t="str">
+        <v>0305</v>
+      </c>
+      <c r="L9" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I9" t="str">
-        <v>Piprahi</v>
-      </c>
-      <c r="J9" t="str">
-        <v>30000324679</v>
-      </c>
-      <c r="K9" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L9" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M9" t="str">
-        <v>SBIN0007960</v>
+        <v>30000340517</v>
+      </c>
+      <c r="N9" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O9" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P9" t="str">
+        <v>SBIN0005994</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0300114</v>
+        <v>0300030</v>
       </c>
       <c r="B10" t="str">
-        <v>SURESH SAH</v>
+        <v>ASHA CHAUDHARY</v>
       </c>
       <c r="C10" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D10" t="str">
-        <v>BSNL Exchange, Sheohar</v>
+        <v>03028</v>
       </c>
       <c r="E10" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Primary School Purnahiya No.2</v>
       </c>
       <c r="F10" t="str">
-        <v>9003000114</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G10" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000030</v>
       </c>
       <c r="H10" t="str">
-        <v>Piprahi</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I10" t="str">
-        <v>Sheohar</v>
+        <v>0303</v>
       </c>
       <c r="J10" t="str">
-        <v>30000902766</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K10" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L10" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M10" t="str">
-        <v>SBIN0003389</v>
+        <v>30000237570</v>
+      </c>
+      <c r="N10" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O10" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P10" t="str">
+        <v>SBIN0007418</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>0300052</v>
+        <v>0300041</v>
       </c>
       <c r="B11" t="str">
-        <v>MD. IRFAN SHARMA</v>
+        <v>PANKAJ SAH</v>
       </c>
       <c r="C11" t="str">
-        <v>Teacher</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D11" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>03037</v>
       </c>
       <c r="E11" t="str">
+        <v>Block Agriculture Office Sheohar No.4</v>
+      </c>
+      <c r="F11" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
-      <c r="F11" t="str">
-        <v>9003000052</v>
-      </c>
       <c r="G11" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000041</v>
       </c>
       <c r="H11" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I11" t="str">
-        <v>Sheohar</v>
+        <v>0302</v>
       </c>
       <c r="J11" t="str">
-        <v>30000411788</v>
+        <v>Piprahi</v>
       </c>
       <c r="K11" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L11" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M11" t="str">
-        <v>SBIN0002020</v>
+        <v>30000324679</v>
+      </c>
+      <c r="N11" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P11" t="str">
+        <v>SBIN0003169</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>0300112</v>
+        <v>0300009</v>
       </c>
       <c r="B12" t="str">
-        <v>KIRAN MISHRA</v>
+        <v>FARHAT TIWARI</v>
       </c>
       <c r="C12" t="str">
-        <v>Assistant Manager</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D12" t="str">
-        <v>Punjab National Bank, Purnahiya</v>
+        <v>03009</v>
       </c>
       <c r="E12" t="str">
+        <v>Panchayat Bhawan Purnahiya</v>
+      </c>
+      <c r="F12" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
-      <c r="F12" t="str">
-        <v>9003000112</v>
-      </c>
       <c r="G12" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000009</v>
       </c>
       <c r="H12" t="str">
-        <v>Tariyani</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I12" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K12" t="str">
+        <v>0303</v>
+      </c>
+      <c r="L12" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="J12" t="str">
-        <v>30000886928</v>
-      </c>
-      <c r="K12" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L12" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M12" t="str">
-        <v>SBIN0004606</v>
+        <v>30000071271</v>
+      </c>
+      <c r="N12" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P12" t="str">
+        <v>SBIN0008642</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0300003</v>
+        <v>0300096</v>
       </c>
       <c r="B13" t="str">
-        <v>REKHA MAHTO</v>
+        <v>UMESH MAHTO</v>
       </c>
       <c r="C13" t="str">
-        <v>Senior Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D13" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>03073</v>
       </c>
       <c r="E13" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>RWD Sub-Division Purnahiya</v>
       </c>
       <c r="F13" t="str">
-        <v>9003000003</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G13" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000096</v>
       </c>
       <c r="H13" t="str">
-        <v>Sheohar</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I13" t="str">
-        <v>Sheohar</v>
+        <v>0303</v>
       </c>
       <c r="J13" t="str">
-        <v>30000023757</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K13" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L13" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M13" t="str">
-        <v>SBIN0001398</v>
+        <v>30000760224</v>
+      </c>
+      <c r="N13" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O13" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P13" t="str">
+        <v>SBIN0003751</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0300104</v>
+        <v>0300013</v>
       </c>
       <c r="B14" t="str">
-        <v>NIRMALA GUPTA</v>
+        <v>RINKU PASWAN</v>
       </c>
       <c r="C14" t="str">
-        <v>Assistant Engineer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D14" t="str">
-        <v>Block Office Sheohar</v>
+        <v>03013</v>
       </c>
       <c r="E14" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>High School Dumri Katsari No.4</v>
       </c>
       <c r="F14" t="str">
-        <v>9003000104</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G14" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000013</v>
       </c>
       <c r="H14" t="str">
-        <v>Piprahi</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I14" t="str">
-        <v>Sheohar</v>
+        <v>0304</v>
       </c>
       <c r="J14" t="str">
-        <v>30000823576</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K14" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L14" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M14" t="str">
-        <v>SBIN0008080</v>
+        <v>30000102947</v>
+      </c>
+      <c r="N14" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O14" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P14" t="str">
+        <v>SBIN0002299</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>0300009</v>
+        <v>0300063</v>
       </c>
       <c r="B15" t="str">
-        <v>NITISH THAKUR</v>
+        <v>MAHESH SAH</v>
       </c>
       <c r="C15" t="str">
-        <v>Section Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D15" t="str">
-        <v>Block Office Sheohar No.1</v>
+        <v>03055</v>
       </c>
       <c r="E15" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>CDPO Office Purnahiya No.1</v>
       </c>
       <c r="F15" t="str">
-        <v>9003000009</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G15" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000063</v>
       </c>
       <c r="H15" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I15" t="str">
-        <v>Sheohar</v>
+        <v>0303</v>
       </c>
       <c r="J15" t="str">
-        <v>30000071271</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K15" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L15" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M15" t="str">
-        <v>SBIN0002299</v>
+        <v>30000498897</v>
+      </c>
+      <c r="N15" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P15" t="str">
+        <v>SBIN0001480</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>0300028</v>
+        <v>0300054</v>
       </c>
       <c r="B16" t="str">
-        <v>MUKESH YADAV</v>
+        <v>RAKESH OJHA</v>
       </c>
       <c r="C16" t="str">
-        <v>Senior Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D16" t="str">
-        <v>Circle Office Tariyani No.3</v>
+        <v>03047</v>
       </c>
       <c r="E16" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>CDPO Office Purnahiya No.2</v>
       </c>
       <c r="F16" t="str">
-        <v>9003000028</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G16" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000054</v>
       </c>
       <c r="H16" t="str">
-        <v>Tariyani</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I16" t="str">
-        <v>Tariyani</v>
+        <v>0303</v>
       </c>
       <c r="J16" t="str">
-        <v>30000221732</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K16" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L16" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M16" t="str">
-        <v>SBIN0005239</v>
+        <v>30000427626</v>
+      </c>
+      <c r="N16" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O16" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P16" t="str">
+        <v>SBIN0001078</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>0300088</v>
+        <v>0300046</v>
       </c>
       <c r="B17" t="str">
-        <v>VINOD CHAUDHARY</v>
+        <v>ANITA RAM</v>
       </c>
       <c r="C17" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D17" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>03041</v>
       </c>
       <c r="E17" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Project Girls High School Tariyani No.3</v>
       </c>
       <c r="F17" t="str">
-        <v>9003000088</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G17" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000046</v>
       </c>
       <c r="H17" t="str">
+        <v>POLLING OFFICER-2</v>
+      </c>
+      <c r="I17" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K17" t="str">
+        <v>0305</v>
+      </c>
+      <c r="L17" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I17" t="str">
-        <v>Piprahi</v>
-      </c>
-      <c r="J17" t="str">
-        <v>30000696872</v>
-      </c>
-      <c r="K17" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L17" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M17" t="str">
-        <v>SBIN0003829</v>
+        <v>30000364274</v>
+      </c>
+      <c r="N17" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O17" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P17" t="str">
+        <v>SBIN0007655</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>0300034</v>
+        <v>0300075</v>
       </c>
       <c r="B18" t="str">
-        <v>KUMARI ANJALI RAM</v>
+        <v>MUKESH OJHA</v>
       </c>
       <c r="C18" t="str">
-        <v>Assistant Teacher</v>
+        <v>Teacher</v>
       </c>
       <c r="D18" t="str">
-        <v>PHC Piprahi No.4</v>
+        <v>03063</v>
       </c>
       <c r="E18" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Block Office Tariyani No.1</v>
       </c>
       <c r="F18" t="str">
-        <v>9003000034</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G18" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000075</v>
       </c>
       <c r="H18" t="str">
-        <v>Piprahi</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I18" t="str">
-        <v>Piprahi</v>
+        <v>0305</v>
       </c>
       <c r="J18" t="str">
-        <v>30000269246</v>
+        <v>Tariyani</v>
       </c>
       <c r="K18" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L18" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M18" t="str">
-        <v>SBIN0005249</v>
+        <v>30000593925</v>
+      </c>
+      <c r="N18" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O18" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P18" t="str">
+        <v>SBIN0002841</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>0300011</v>
+        <v>0300019</v>
       </c>
       <c r="B19" t="str">
-        <v>DEEPAK SINGH</v>
+        <v>VINOD MISHRA</v>
       </c>
       <c r="C19" t="str">
         <v>Headmaster</v>
       </c>
       <c r="D19" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>03017</v>
       </c>
       <c r="E19" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="F19" t="str">
-        <v>9003000011</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G19" t="str">
+        <v>9003000019</v>
+      </c>
+      <c r="H19" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J19" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="I19" t="str">
-        <v>Dumri Katsari</v>
-      </c>
-      <c r="J19" t="str">
-        <v>30000087109</v>
-      </c>
       <c r="K19" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L19" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M19" t="str">
-        <v>SBIN0003404</v>
+        <v>30000150461</v>
+      </c>
+      <c r="N19" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O19" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P19" t="str">
+        <v>SBIN0009856</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>0300043</v>
+        <v>0300027</v>
       </c>
       <c r="B20" t="str">
-        <v>NASREEN SHARMA</v>
+        <v>PANKAJ ALAM</v>
       </c>
       <c r="C20" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D20" t="str">
-        <v>Middle School Dumri Katsari No.4</v>
+        <v>03025</v>
       </c>
       <c r="E20" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Kanya Middle School Piprahi No.4</v>
       </c>
       <c r="F20" t="str">
-        <v>9003000043</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G20" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000027</v>
       </c>
       <c r="H20" t="str">
+        <v>POLLING OFFICER-1</v>
+      </c>
+      <c r="I20" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J20" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I20" t="str">
-        <v>Dumri Katsari</v>
-      </c>
-      <c r="J20" t="str">
-        <v>30000340517</v>
-      </c>
       <c r="K20" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L20" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M20" t="str">
-        <v>SBIN0006377</v>
+        <v>30000213813</v>
+      </c>
+      <c r="N20" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O20" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P20" t="str">
+        <v>SBIN0009455</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>0300054</v>
+        <v>0300086</v>
       </c>
       <c r="B21" t="str">
-        <v>SAVITA SAH</v>
+        <v>AMIT MAHTO</v>
       </c>
       <c r="C21" t="str">
-        <v>Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D21" t="str">
-        <v>Primary School Dumri Katsari No.2</v>
+        <v>03071</v>
       </c>
       <c r="E21" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>RWD Sub-Division Sheohar</v>
       </c>
       <c r="F21" t="str">
-        <v>9003000054</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G21" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000086</v>
       </c>
       <c r="H21" t="str">
-        <v>Piprahi</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I21" t="str">
-        <v>Dumri Katsari</v>
+        <v>0301</v>
       </c>
       <c r="J21" t="str">
-        <v>30000427626</v>
+        <v>Sheohar</v>
       </c>
       <c r="K21" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L21" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M21" t="str">
-        <v>SBIN0005877</v>
+        <v>30000681034</v>
+      </c>
+      <c r="N21" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P21" t="str">
+        <v>SBIN0008061</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>0300007</v>
+        <v>0300084</v>
       </c>
       <c r="B22" t="str">
-        <v>SURESH MAHTO</v>
+        <v>SUNITA TIWARI</v>
       </c>
       <c r="C22" t="str">
-        <v>Section Officer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D22" t="str">
-        <v>Panchayat Bhawan Tariyani No.1</v>
+        <v>03070</v>
       </c>
       <c r="E22" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F22" t="str">
-        <v>9003000007</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G22" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000084</v>
       </c>
       <c r="H22" t="str">
-        <v>Tariyani</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I22" t="str">
-        <v>Tariyani</v>
+        <v>0304</v>
       </c>
       <c r="J22" t="str">
-        <v>30000055433</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K22" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L22" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M22" t="str">
-        <v>SBIN0006290</v>
+        <v>30000665196</v>
+      </c>
+      <c r="N22" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O22" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P22" t="str">
+        <v>SBIN0006735</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>0300032</v>
+        <v>0300021</v>
       </c>
       <c r="B23" t="str">
-        <v>UMESH SINHA</v>
+        <v>MAMTA THAKUR</v>
       </c>
       <c r="C23" t="str">
-        <v>Head Clerk</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D23" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>03019</v>
       </c>
       <c r="E23" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Primary School Piprahi No.1</v>
       </c>
       <c r="F23" t="str">
-        <v>9003000032</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G23" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000021</v>
       </c>
       <c r="H23" t="str">
-        <v>Sheohar</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I23" t="str">
-        <v>Sheohar</v>
+        <v>0302</v>
       </c>
       <c r="J23" t="str">
-        <v>30000253408</v>
+        <v>Piprahi</v>
       </c>
       <c r="K23" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L23" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M23" t="str">
-        <v>SBIN0001361</v>
+        <v>30000166299</v>
+      </c>
+      <c r="N23" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O23" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P23" t="str">
+        <v>SBIN0008175</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>0300044</v>
+        <v>0300056</v>
       </c>
       <c r="B24" t="str">
-        <v>SUNIL SHARMA</v>
+        <v>PRIYANKA OJHA</v>
       </c>
       <c r="C24" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Teacher</v>
       </c>
       <c r="D24" t="str">
-        <v>Project Girls High School Purnahiya No.2</v>
+        <v>03049</v>
       </c>
       <c r="E24" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Circle Office Dumri Katsari No.4</v>
       </c>
       <c r="F24" t="str">
-        <v>9003000044</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G24" t="str">
+        <v>9003000056</v>
+      </c>
+      <c r="H24" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
-      <c r="H24" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="I24" t="str">
-        <v>Purnahiya</v>
+        <v>0304</v>
       </c>
       <c r="J24" t="str">
-        <v>30000348436</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K24" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L24" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M24" t="str">
-        <v>SBIN0003918</v>
+        <v>30000443464</v>
+      </c>
+      <c r="N24" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O24" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P24" t="str">
+        <v>SBIN0002222</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0300030</v>
+        <v>0300058</v>
       </c>
       <c r="B25" t="str">
-        <v>DINESH THAKUR</v>
+        <v>SURESH VERMA</v>
       </c>
       <c r="C25" t="str">
-        <v>Assistant Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D25" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>03051</v>
       </c>
       <c r="E25" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Kanya Middle School Tariyani No.1</v>
       </c>
       <c r="F25" t="str">
-        <v>9003000030</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G25" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000058</v>
       </c>
       <c r="H25" t="str">
-        <v>Piprahi</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I25" t="str">
-        <v>Dumri Katsari</v>
+        <v>0303</v>
       </c>
       <c r="J25" t="str">
-        <v>30000237570</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K25" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L25" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M25" t="str">
-        <v>SBIN0007052</v>
+        <v>30000459302</v>
+      </c>
+      <c r="N25" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O25" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P25" t="str">
+        <v>SBIN0002339</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>0300115</v>
+        <v>0300111</v>
       </c>
       <c r="B26" t="str">
-        <v>AMIT SINGH</v>
+        <v>MUKESH KUMAR</v>
       </c>
       <c r="C26" t="str">
         <v>Postmaster</v>
       </c>
       <c r="D26" t="str">
-        <v>Central Bank of India, Purnahiya</v>
+        <v>03083</v>
       </c>
       <c r="E26" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>LIC Branch Office, Dumri Katsari</v>
       </c>
       <c r="F26" t="str">
-        <v>9003000115</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G26" t="str">
+        <v>9003000111</v>
+      </c>
+      <c r="H26" t="str">
         <v>MICRO OBSERVER</v>
       </c>
-      <c r="H26" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="I26" t="str">
-        <v>Purnahiya</v>
+        <v>0305</v>
       </c>
       <c r="J26" t="str">
-        <v>30000910685</v>
+        <v>Tariyani</v>
       </c>
       <c r="K26" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L26" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M26" t="str">
-        <v>SBIN0004707</v>
+        <v>30000879009</v>
+      </c>
+      <c r="N26" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O26" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P26" t="str">
+        <v>SBIN0009657</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>0300102</v>
+        <v>0300089</v>
       </c>
       <c r="B27" t="str">
-        <v>POONAM GUPTA</v>
+        <v>SANJAY VERMA B</v>
       </c>
       <c r="C27" t="str">
-        <v>Revenue Officer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D27" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>03072</v>
       </c>
       <c r="E27" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>RWD Sub-Division Piprahi</v>
       </c>
       <c r="F27" t="str">
-        <v>9003000102</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G27" t="str">
+        <v>9003000089</v>
+      </c>
+      <c r="H27" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
-      <c r="H27" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="I27" t="str">
-        <v>Purnahiya</v>
+        <v>0302</v>
       </c>
       <c r="J27" t="str">
-        <v>30000807738</v>
+        <v>Piprahi</v>
       </c>
       <c r="K27" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L27" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M27" t="str">
-        <v>SBIN0008741</v>
+        <v>30000704791</v>
+      </c>
+      <c r="N27" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O27" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P27" t="str">
+        <v>SBIN0006075</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>0300038</v>
+        <v>0300109</v>
       </c>
       <c r="B28" t="str">
-        <v>MANOJ GUPTA</v>
+        <v>PRAMOD TIWARI</v>
       </c>
       <c r="C28" t="str">
-        <v>Senior Clerk</v>
+        <v>Postmaster</v>
       </c>
       <c r="D28" t="str">
-        <v>Panchayat Bhawan Purnahiya No.3</v>
+        <v>03080</v>
       </c>
       <c r="E28" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Bank of India, Dumri Katsari</v>
       </c>
       <c r="F28" t="str">
-        <v>9003000038</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G28" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000109</v>
       </c>
       <c r="H28" t="str">
-        <v>Sheohar</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I28" t="str">
-        <v>Purnahiya</v>
+        <v>0304</v>
       </c>
       <c r="J28" t="str">
-        <v>30000300922</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K28" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L28" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M28" t="str">
-        <v>SBIN0006866</v>
+        <v>30000863171</v>
+      </c>
+      <c r="N28" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O28" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P28" t="str">
+        <v>SBIN0003444</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>0300124</v>
+        <v>0300007</v>
       </c>
       <c r="B29" t="str">
-        <v>MD. SHAHID MISHRA</v>
+        <v>MAHESH CHAUDHARY</v>
       </c>
       <c r="C29" t="str">
-        <v>Assistant Manager</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D29" t="str">
-        <v>UCO Bank, Tariyani</v>
+        <v>03007</v>
       </c>
       <c r="E29" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F29" t="str">
-        <v>9003000124</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G29" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000007</v>
       </c>
       <c r="H29" t="str">
-        <v>Sheohar</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I29" t="str">
-        <v>Tariyani</v>
+        <v>0302</v>
       </c>
       <c r="J29" t="str">
-        <v>30000981956</v>
+        <v>Piprahi</v>
       </c>
       <c r="K29" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L29" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M29" t="str">
-        <v>SBIN0007161</v>
+        <v>30000055433</v>
+      </c>
+      <c r="N29" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O29" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P29" t="str">
+        <v>SBIN0003056</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>0300073</v>
+        <v>0300025</v>
       </c>
       <c r="B30" t="str">
-        <v>RAKESH PRASAD</v>
+        <v>USHA SAH</v>
       </c>
       <c r="C30" t="str">
-        <v>Clerk</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D30" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>03023</v>
       </c>
       <c r="E30" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>High School Tariyani</v>
       </c>
       <c r="F30" t="str">
-        <v>9003000073</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G30" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000025</v>
       </c>
       <c r="H30" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I30" t="str">
-        <v>Sheohar</v>
+        <v>0301</v>
       </c>
       <c r="J30" t="str">
-        <v>30000578087</v>
+        <v>Sheohar</v>
       </c>
       <c r="K30" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L30" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M30" t="str">
-        <v>SBIN0004668</v>
+        <v>30000197975</v>
+      </c>
+      <c r="N30" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O30" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P30" t="str">
+        <v>SBIN0009569</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>0300096</v>
+        <v>0300083</v>
       </c>
       <c r="B31" t="str">
-        <v>SUNITA SINHA</v>
+        <v>NEHA THAKUR</v>
       </c>
       <c r="C31" t="str">
-        <v>Junior Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D31" t="str">
-        <v>RWD Sub-Division Sheohar</v>
+        <v>03017</v>
       </c>
       <c r="E31" t="str">
+        <v>District Agriculture Office Sheohar</v>
+      </c>
+      <c r="F31" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
-      <c r="F31" t="str">
-        <v>9003000096</v>
-      </c>
       <c r="G31" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000083</v>
       </c>
       <c r="H31" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I31" t="str">
-        <v>Sheohar</v>
+        <v>0303</v>
       </c>
       <c r="J31" t="str">
-        <v>30000760224</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K31" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L31" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M31" t="str">
-        <v>SBIN0004767</v>
+        <v>30000657277</v>
+      </c>
+      <c r="N31" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O31" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P31" t="str">
+        <v>SBIN0007297</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>0300107</v>
+        <v>0300081</v>
       </c>
       <c r="B32" t="str">
-        <v>VINOD THAKUR</v>
+        <v>SANTOSH RAM</v>
       </c>
       <c r="C32" t="str">
-        <v>Branch Manager</v>
+        <v>Clerk</v>
       </c>
       <c r="D32" t="str">
-        <v>Head Post Office, Dumri Katsari</v>
+        <v>03068</v>
       </c>
       <c r="E32" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Panchayat Bhawan Piprahi</v>
       </c>
       <c r="F32" t="str">
-        <v>9003000107</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G32" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000081</v>
       </c>
       <c r="H32" t="str">
-        <v>Dumri Katsari</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I32" t="str">
-        <v>Dumri Katsari</v>
+        <v>0302</v>
       </c>
       <c r="J32" t="str">
-        <v>30000847333</v>
+        <v>Piprahi</v>
       </c>
       <c r="K32" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L32" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M32" t="str">
-        <v>SBIN0004453</v>
+        <v>30000641439</v>
+      </c>
+      <c r="N32" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O32" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P32" t="str">
+        <v>SBIN0003095</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>0300067</v>
+        <v>0300050</v>
       </c>
       <c r="B33" t="str">
-        <v>ASHA MISHRA</v>
+        <v>SUNIL ANSARI</v>
       </c>
       <c r="C33" t="str">
-        <v>Data Entry Operator</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D33" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>03045</v>
       </c>
       <c r="E33" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Middle School Tariyani</v>
       </c>
       <c r="F33" t="str">
-        <v>9003000067</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G33" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000050</v>
       </c>
       <c r="H33" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I33" t="str">
-        <v>Sheohar</v>
+        <v>0305</v>
       </c>
       <c r="J33" t="str">
-        <v>30000530573</v>
+        <v>Tariyani</v>
       </c>
       <c r="K33" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L33" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M33" t="str">
-        <v>SBIN0007768</v>
+        <v>30000395950</v>
+      </c>
+      <c r="N33" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O33" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P33" t="str">
+        <v>SBIN0004589</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>0300069</v>
+        <v>0300035</v>
       </c>
       <c r="B34" t="str">
-        <v>FARHAT YADAV</v>
+        <v>AJAY PRASAD</v>
       </c>
       <c r="C34" t="str">
-        <v>Teacher</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D34" t="str">
-        <v>PHC Piprahi</v>
+        <v>03032</v>
       </c>
       <c r="E34" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Kanya Middle School Tariyani</v>
       </c>
       <c r="F34" t="str">
-        <v>9003000069</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G34" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000035</v>
       </c>
       <c r="H34" t="str">
-        <v>Piprahi</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I34" t="str">
-        <v>Piprahi</v>
+        <v>0305</v>
       </c>
       <c r="J34" t="str">
-        <v>30000546411</v>
+        <v>Tariyani</v>
       </c>
       <c r="K34" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L34" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M34" t="str">
-        <v>SBIN0004900</v>
+        <v>30000277165</v>
+      </c>
+      <c r="N34" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O34" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P34" t="str">
+        <v>SBIN0005274</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>0300125</v>
+        <v>0300116</v>
       </c>
       <c r="B35" t="str">
-        <v>POONAM KHATUN</v>
+        <v>UMESH MAHTO O</v>
       </c>
       <c r="C35" t="str">
-        <v>Postmaster</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D35" t="str">
-        <v>Punjab National Bank, Sheohar</v>
+        <v>03087</v>
       </c>
       <c r="E35" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Bank of India, Tariyani</v>
       </c>
       <c r="F35" t="str">
-        <v>9003000125</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G35" t="str">
+        <v>9003000116</v>
+      </c>
+      <c r="H35" t="str">
         <v>MICRO OBSERVER</v>
       </c>
-      <c r="H35" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="I35" t="str">
-        <v>Sheohar</v>
+        <v>0305</v>
       </c>
       <c r="J35" t="str">
-        <v>30000989875</v>
+        <v>Tariyani</v>
       </c>
       <c r="K35" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L35" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M35" t="str">
-        <v>SBIN0003854</v>
+        <v>30000918604</v>
+      </c>
+      <c r="N35" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O35" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P35" t="str">
+        <v>SBIN0003278</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>0300020</v>
+        <v>0300017</v>
       </c>
       <c r="B36" t="str">
-        <v>KUMARI ANJALI MAHTO</v>
+        <v>POONAM PRASAD</v>
       </c>
       <c r="C36" t="str">
-        <v>Senior Teacher</v>
+        <v>Headmaster</v>
       </c>
       <c r="D36" t="str">
-        <v>Middle School Dumri Katsari No.3</v>
+        <v>03015</v>
       </c>
       <c r="E36" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F36" t="str">
-        <v>9003000020</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G36" t="str">
+        <v>9003000017</v>
+      </c>
+      <c r="H36" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
-      <c r="H36" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="I36" t="str">
-        <v>Dumri Katsari</v>
+        <v>0301</v>
       </c>
       <c r="J36" t="str">
-        <v>30000158380</v>
+        <v>Sheohar</v>
       </c>
       <c r="K36" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L36" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M36" t="str">
-        <v>SBIN0009850</v>
+        <v>30000134623</v>
+      </c>
+      <c r="N36" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O36" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P36" t="str">
+        <v>SBIN0006798</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>0300049</v>
+        <v>0300100</v>
       </c>
       <c r="B37" t="str">
-        <v>ASHA CHAUDHARY</v>
+        <v>DEEPAK SINGH</v>
       </c>
       <c r="C37" t="str">
-        <v>Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D37" t="str">
-        <v>High School Tariyani</v>
+        <v>03076</v>
       </c>
       <c r="E37" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>RWD Sub-Division Dumri Katsari</v>
       </c>
       <c r="F37" t="str">
-        <v>9003000049</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G37" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000100</v>
       </c>
       <c r="H37" t="str">
-        <v>Purnahiya</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I37" t="str">
-        <v>Tariyani</v>
+        <v>0304</v>
       </c>
       <c r="J37" t="str">
-        <v>30000388031</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K37" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L37" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M37" t="str">
-        <v>SBIN0002138</v>
+        <v>30000791900</v>
+      </c>
+      <c r="N37" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O37" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P37" t="str">
+        <v>SBIN0005875</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>0300091</v>
+        <v>0300112</v>
       </c>
       <c r="B38" t="str">
-        <v>VIJAY KUMAR</v>
+        <v>USHA VERMA</v>
       </c>
       <c r="C38" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D38" t="str">
-        <v>Block Office Sheohar</v>
+        <v>03084</v>
       </c>
       <c r="E38" t="str">
+        <v>Punjab National Bank, Sheohar</v>
+      </c>
+      <c r="F38" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
-      <c r="F38" t="str">
-        <v>9003000091</v>
-      </c>
       <c r="G38" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000112</v>
       </c>
       <c r="H38" t="str">
-        <v>Sheohar</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I38" t="str">
-        <v>Sheohar</v>
+        <v>0304</v>
       </c>
       <c r="J38" t="str">
-        <v>30000720629</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K38" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L38" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M38" t="str">
-        <v>SBIN0001984</v>
+        <v>30000886928</v>
+      </c>
+      <c r="N38" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O38" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P38" t="str">
+        <v>SBIN0008866</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>0300083</v>
+        <v>0300113</v>
       </c>
       <c r="B39" t="str">
-        <v>SUNITA OJHA</v>
+        <v>AMIT SHARMA</v>
       </c>
       <c r="C39" t="str">
-        <v>Office Assistant</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D39" t="str">
-        <v>Block Office Sheohar No.1</v>
+        <v>03085</v>
       </c>
       <c r="E39" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>State Bank of India, Purnahiya</v>
       </c>
       <c r="F39" t="str">
-        <v>9003000083</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G39" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000113</v>
       </c>
       <c r="H39" t="str">
+        <v>MICRO OBSERVER</v>
+      </c>
+      <c r="I39" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J39" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="I39" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="J39" t="str">
-        <v>30000657277</v>
-      </c>
       <c r="K39" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L39" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M39" t="str">
-        <v>SBIN0003700</v>
+        <v>30000894847</v>
+      </c>
+      <c r="N39" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O39" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P39" t="str">
+        <v>SBIN0001918</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>0300082</v>
+        <v>0300033</v>
       </c>
       <c r="B40" t="str">
-        <v>RAKESH THAKUR</v>
+        <v>RAVI THAKUR</v>
       </c>
       <c r="C40" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D40" t="str">
-        <v>Circle Office Dumri Katsari No.1</v>
+        <v>03031</v>
       </c>
       <c r="E40" t="str">
+        <v>Primary School Dumri Katsari No.4</v>
+      </c>
+      <c r="F40" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
-      <c r="F40" t="str">
-        <v>9003000082</v>
-      </c>
       <c r="G40" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000033</v>
       </c>
       <c r="H40" t="str">
+        <v>POLLING OFFICER-1</v>
+      </c>
+      <c r="I40" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K40" t="str">
+        <v>0304</v>
+      </c>
+      <c r="L40" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I40" t="str">
-        <v>Dumri Katsari</v>
-      </c>
-      <c r="J40" t="str">
-        <v>30000649358</v>
-      </c>
-      <c r="K40" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L40" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M40" t="str">
-        <v>SBIN0004422</v>
+        <v>30000261327</v>
+      </c>
+      <c r="N40" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O40" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P40" t="str">
+        <v>SBIN0008149</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>0300071</v>
+        <v>0300124</v>
       </c>
       <c r="B41" t="str">
-        <v>USHA SAH</v>
+        <v>ALOK ANSARI</v>
       </c>
       <c r="C41" t="str">
-        <v>Data Entry Operator</v>
+        <v>Postmaster</v>
       </c>
       <c r="D41" t="str">
-        <v>Circle Office Dumri Katsari No.2</v>
+        <v>03094</v>
       </c>
       <c r="E41" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Central Bank of India, Tariyani</v>
       </c>
       <c r="F41" t="str">
-        <v>9003000071</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G41" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000124</v>
       </c>
       <c r="H41" t="str">
-        <v>Piprahi</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I41" t="str">
-        <v>Dumri Katsari</v>
+        <v>0305</v>
       </c>
       <c r="J41" t="str">
-        <v>30000562249</v>
+        <v>Tariyani</v>
       </c>
       <c r="K41" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L41" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M41" t="str">
-        <v>SBIN0005373</v>
+        <v>30000981956</v>
+      </c>
+      <c r="N41" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O41" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P41" t="str">
+        <v>SBIN0009563</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>0300026</v>
+        <v>0300078</v>
       </c>
       <c r="B42" t="str">
-        <v>USHA SINHA</v>
+        <v>SAVITA SINHA</v>
       </c>
       <c r="C42" t="str">
-        <v>Head Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D42" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>03065</v>
       </c>
       <c r="E42" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Block Office Dumri Katsari</v>
       </c>
       <c r="F42" t="str">
-        <v>9003000026</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G42" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000078</v>
       </c>
       <c r="H42" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I42" t="str">
-        <v>Sheohar</v>
+        <v>0304</v>
       </c>
       <c r="J42" t="str">
-        <v>30000205894</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K42" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L42" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M42" t="str">
-        <v>SBIN0008204</v>
+        <v>30000617682</v>
+      </c>
+      <c r="N42" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O42" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P42" t="str">
+        <v>SBIN0003906</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>0300029</v>
+        <v>0300042</v>
       </c>
       <c r="B43" t="str">
-        <v>MD. IRFAN SAH</v>
+        <v>POONAM SINGH</v>
       </c>
       <c r="C43" t="str">
-        <v>Assistant Teacher</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D43" t="str">
-        <v>Block Agriculture Office Dumri Katsari No.4</v>
+        <v>03038</v>
       </c>
       <c r="E43" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="F43" t="str">
-        <v>9003000029</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G43" t="str">
+        <v>9003000042</v>
+      </c>
+      <c r="H43" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
-      <c r="H43" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="I43" t="str">
-        <v>Dumri Katsari</v>
+        <v>0302</v>
       </c>
       <c r="J43" t="str">
-        <v>30000229651</v>
+        <v>Piprahi</v>
       </c>
       <c r="K43" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L43" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M43" t="str">
-        <v>SBIN0006550</v>
+        <v>30000332598</v>
+      </c>
+      <c r="N43" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O43" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P43" t="str">
+        <v>SBIN0003077</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>0300021</v>
+        <v>0300026</v>
       </c>
       <c r="B44" t="str">
-        <v>ASHA RAM</v>
+        <v>SUNITA PASWAN</v>
       </c>
       <c r="C44" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D44" t="str">
-        <v>PHC Sheohar No.1</v>
+        <v>03024</v>
       </c>
       <c r="E44" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Block Education Office Purnahiya</v>
       </c>
       <c r="F44" t="str">
-        <v>9003000021</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G44" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000026</v>
       </c>
       <c r="H44" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I44" t="str">
-        <v>Sheohar</v>
+        <v>0302</v>
       </c>
       <c r="J44" t="str">
-        <v>30000166299</v>
+        <v>Piprahi</v>
       </c>
       <c r="K44" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L44" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M44" t="str">
-        <v>SBIN0002682</v>
+        <v>30000205894</v>
+      </c>
+      <c r="N44" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O44" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P44" t="str">
+        <v>SBIN0007162</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>0300012</v>
+        <v>0300115</v>
       </c>
       <c r="B45" t="str">
-        <v>MAMTA JHA</v>
+        <v>ANITA TIWARI</v>
       </c>
       <c r="C45" t="str">
-        <v>Section Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D45" t="str">
-        <v>Panchayat Bhawan Tariyani No.3</v>
+        <v>03081</v>
       </c>
       <c r="E45" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Punjab National Bank, Dumri Katsari</v>
       </c>
       <c r="F45" t="str">
-        <v>9003000012</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G45" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000115</v>
       </c>
       <c r="H45" t="str">
-        <v>Sheohar</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I45" t="str">
-        <v>Tariyani</v>
+        <v>0304</v>
       </c>
       <c r="J45" t="str">
-        <v>30000095028</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K45" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L45" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M45" t="str">
-        <v>SBIN0009997</v>
+        <v>30000910685</v>
+      </c>
+      <c r="N45" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O45" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P45" t="str">
+        <v>SBIN0007367</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>0300106</v>
+        <v>0300061</v>
       </c>
       <c r="B46" t="str">
-        <v>MANOJ PASWAN</v>
+        <v>MD. SHAHID DEVI</v>
       </c>
       <c r="C46" t="str">
-        <v>Assistant Manager</v>
+        <v>Accountant</v>
       </c>
       <c r="D46" t="str">
-        <v>State Bank of India, Dumri Katsari</v>
+        <v>03053</v>
       </c>
       <c r="E46" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Block Agriculture Office Sheohar No.1</v>
       </c>
       <c r="F46" t="str">
-        <v>9003000106</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G46" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000061</v>
       </c>
       <c r="H46" t="str">
-        <v>Dumri Katsari</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I46" t="str">
-        <v>Dumri Katsari</v>
+        <v>0301</v>
       </c>
       <c r="J46" t="str">
-        <v>30000839414</v>
+        <v>Sheohar</v>
       </c>
       <c r="K46" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L46" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M46" t="str">
-        <v>SBIN0006740</v>
+        <v>30000483059</v>
+      </c>
+      <c r="N46" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O46" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P46" t="str">
+        <v>SBIN0007749</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0300110</v>
+        <v>0300001</v>
       </c>
       <c r="B47" t="str">
-        <v>RAVI SINGH</v>
+        <v>ASHA RAM</v>
       </c>
       <c r="C47" t="str">
-        <v>Administrative Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D47" t="str">
-        <v>Head Post Office, Dumri Katsari</v>
+        <v>03001</v>
       </c>
       <c r="E47" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Circle Office Sheohar</v>
       </c>
       <c r="F47" t="str">
-        <v>9003000110</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G47" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000001</v>
       </c>
       <c r="H47" t="str">
-        <v>Sheohar</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I47" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J47" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="J47" t="str">
-        <v>30000871090</v>
-      </c>
       <c r="K47" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L47" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M47" t="str">
-        <v>SBIN0003304</v>
+        <v>30000007919</v>
+      </c>
+      <c r="N47" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O47" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P47" t="str">
+        <v>SBIN0004896</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0300078</v>
+        <v>0300094</v>
       </c>
       <c r="B48" t="str">
-        <v>SURESH TIWARI</v>
+        <v>MD. SHAHID MISHRA</v>
       </c>
       <c r="C48" t="str">
-        <v>Office Assistant</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D48" t="str">
-        <v>CDPO Office Purnahiya No.3</v>
+        <v>03065</v>
       </c>
       <c r="E48" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Block Office Dumri Katsari</v>
       </c>
       <c r="F48" t="str">
-        <v>9003000078</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G48" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000094</v>
       </c>
       <c r="H48" t="str">
-        <v>Purnahiya</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I48" t="str">
-        <v>Purnahiya</v>
+        <v>0304</v>
       </c>
       <c r="J48" t="str">
-        <v>30000617682</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K48" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L48" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M48" t="str">
-        <v>SBIN0009785</v>
+        <v>30000744386</v>
+      </c>
+      <c r="N48" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O48" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P48" t="str">
+        <v>SBIN0004380</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0300109</v>
+        <v>0300048</v>
       </c>
       <c r="B49" t="str">
-        <v>NASREEN CHAUDHARY</v>
+        <v>FARHAT YADAV</v>
       </c>
       <c r="C49" t="str">
-        <v>Administrative Officer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D49" t="str">
-        <v>State Bank of India, Sheohar</v>
+        <v>03043</v>
       </c>
       <c r="E49" t="str">
+        <v>Block Agriculture Office Sheohar</v>
+      </c>
+      <c r="F49" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
-      <c r="F49" t="str">
-        <v>9003000109</v>
-      </c>
       <c r="G49" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000048</v>
       </c>
       <c r="H49" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I49" t="str">
-        <v>Sheohar</v>
+        <v>0301</v>
       </c>
       <c r="J49" t="str">
-        <v>30000863171</v>
+        <v>Sheohar</v>
       </c>
       <c r="K49" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L49" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M49" t="str">
-        <v>SBIN0005546</v>
+        <v>30000380112</v>
+      </c>
+      <c r="N49" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O49" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P49" t="str">
+        <v>SBIN0001521</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0300087</v>
+        <v>0300095</v>
       </c>
       <c r="B50" t="str">
-        <v>DEEPAK PASWAN</v>
+        <v>USHA THAKUR</v>
       </c>
       <c r="C50" t="str">
-        <v>Revenue Officer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D50" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>03043</v>
       </c>
       <c r="E50" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="F50" t="str">
-        <v>9003000087</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G50" t="str">
+        <v>9003000095</v>
+      </c>
+      <c r="H50" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
-      <c r="H50" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="I50" t="str">
-        <v>Purnahiya</v>
+        <v>0301</v>
       </c>
       <c r="J50" t="str">
-        <v>30000688953</v>
+        <v>Sheohar</v>
       </c>
       <c r="K50" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L50" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M50" t="str">
-        <v>SBIN0002677</v>
+        <v>30000752305</v>
+      </c>
+      <c r="N50" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O50" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P50" t="str">
+        <v>SBIN0005196</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>0300101</v>
+        <v>0300120</v>
       </c>
       <c r="B51" t="str">
-        <v>MD. SHAHID GUPTA</v>
+        <v>AJAY SAH</v>
       </c>
       <c r="C51" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D51" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>03090</v>
       </c>
       <c r="E51" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>LIC Branch Office, Tariyani</v>
       </c>
       <c r="F51" t="str">
-        <v>9003000101</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G51" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000120</v>
       </c>
       <c r="H51" t="str">
-        <v>Dumri Katsari</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I51" t="str">
-        <v>Dumri Katsari</v>
+        <v>0301</v>
       </c>
       <c r="J51" t="str">
-        <v>30000799819</v>
+        <v>Sheohar</v>
       </c>
       <c r="K51" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L51" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M51" t="str">
-        <v>SBIN0001031</v>
+        <v>30000950280</v>
+      </c>
+      <c r="N51" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O51" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P51" t="str">
+        <v>SBIN0009146</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>0300077</v>
+        <v>0300040</v>
       </c>
       <c r="B52" t="str">
-        <v>RINKU PANDEY</v>
+        <v>RAKESH GUPTA</v>
       </c>
       <c r="C52" t="str">
-        <v>Data Entry Operator</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D52" t="str">
-        <v>Project Girls High School Piprahi</v>
+        <v>03036</v>
       </c>
       <c r="E52" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Kanya Middle School Purnahiya</v>
       </c>
       <c r="F52" t="str">
-        <v>9003000077</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G52" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000040</v>
       </c>
       <c r="H52" t="str">
+        <v>POLLING OFFICER-1</v>
+      </c>
+      <c r="I52" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J52" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="I52" t="str">
-        <v>Piprahi</v>
-      </c>
-      <c r="J52" t="str">
-        <v>30000609763</v>
-      </c>
       <c r="K52" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L52" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M52" t="str">
-        <v>SBIN0002003</v>
+        <v>30000316760</v>
+      </c>
+      <c r="N52" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O52" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P52" t="str">
+        <v>SBIN0009889</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>0300019</v>
+        <v>0300020</v>
       </c>
       <c r="B53" t="str">
-        <v>PANKAJ PANDEY</v>
+        <v>PANKAJ RAI</v>
       </c>
       <c r="C53" t="str">
-        <v>Headmaster</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D53" t="str">
-        <v>High School Tariyani No.1</v>
+        <v>03018</v>
       </c>
       <c r="E53" t="str">
+        <v>High School Tariyani No.2</v>
+      </c>
+      <c r="F53" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
-      <c r="F53" t="str">
-        <v>9003000019</v>
-      </c>
       <c r="G53" t="str">
+        <v>9003000020</v>
+      </c>
+      <c r="H53" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
-      <c r="H53" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="I53" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K53" t="str">
+        <v>0305</v>
+      </c>
+      <c r="L53" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="J53" t="str">
-        <v>30000150461</v>
-      </c>
-      <c r="K53" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L53" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M53" t="str">
-        <v>SBIN0009974</v>
+        <v>30000158380</v>
+      </c>
+      <c r="N53" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O53" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P53" t="str">
+        <v>SBIN0008367</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>0300042</v>
+        <v>0300088</v>
       </c>
       <c r="B54" t="str">
-        <v>MD. IRFAN GUPTA</v>
+        <v>KIRAN OJHA</v>
       </c>
       <c r="C54" t="str">
-        <v>Senior Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D54" t="str">
-        <v>Primary School Dumri Katsari No.4</v>
+        <v>03008</v>
       </c>
       <c r="E54" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="F54" t="str">
-        <v>9003000042</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G54" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000088</v>
       </c>
       <c r="H54" t="str">
-        <v>Dumri Katsari</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I54" t="str">
-        <v>Dumri Katsari</v>
+        <v>0303</v>
       </c>
       <c r="J54" t="str">
-        <v>30000332598</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K54" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L54" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M54" t="str">
-        <v>SBIN0006386</v>
+        <v>30000696872</v>
+      </c>
+      <c r="N54" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O54" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P54" t="str">
+        <v>SBIN0002313</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>0300047</v>
+        <v>0300101</v>
       </c>
       <c r="B55" t="str">
-        <v>MAMTA OJHA</v>
+        <v>ASHA VERMA</v>
       </c>
       <c r="C55" t="str">
-        <v>Teacher</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D55" t="str">
-        <v>Middle School Sheohar No.1</v>
+        <v>03077</v>
       </c>
       <c r="E55" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Minor Irrigation Office Tariyani</v>
       </c>
       <c r="F55" t="str">
-        <v>9003000047</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G55" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000101</v>
       </c>
       <c r="H55" t="str">
-        <v>Purnahiya</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I55" t="str">
-        <v>Sheohar</v>
+        <v>0301</v>
       </c>
       <c r="J55" t="str">
-        <v>30000372193</v>
+        <v>Sheohar</v>
       </c>
       <c r="K55" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L55" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M55" t="str">
-        <v>SBIN0009792</v>
+        <v>30000799819</v>
+      </c>
+      <c r="N55" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O55" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P55" t="str">
+        <v>SBIN0005004</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>0300031</v>
+        <v>0300092</v>
       </c>
       <c r="B56" t="str">
-        <v>ASHA DEVI</v>
+        <v>RINKU TIWARI</v>
       </c>
       <c r="C56" t="str">
-        <v>Assistant Teacher</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D56" t="str">
-        <v>Primary School Dumri Katsari</v>
+        <v>03073</v>
       </c>
       <c r="E56" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>RWD Sub-Division Purnahiya</v>
       </c>
       <c r="F56" t="str">
-        <v>9003000031</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G56" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000092</v>
       </c>
       <c r="H56" t="str">
+        <v>PATROLLING MAGISTRATE</v>
+      </c>
+      <c r="I56" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J56" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I56" t="str">
-        <v>Dumri Katsari</v>
-      </c>
-      <c r="J56" t="str">
-        <v>30000245489</v>
-      </c>
       <c r="K56" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L56" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M56" t="str">
-        <v>SBIN0009360</v>
+        <v>30000728548</v>
+      </c>
+      <c r="N56" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O56" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P56" t="str">
+        <v>SBIN0009268</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>0300103</v>
+        <v>0300047</v>
       </c>
       <c r="B57" t="str">
-        <v>FARHAT KHATUN</v>
+        <v>RINKU PANDEY</v>
       </c>
       <c r="C57" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D57" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>03042</v>
       </c>
       <c r="E57" t="str">
+        <v>Block Office Sheohar No.2</v>
+      </c>
+      <c r="F57" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
-      <c r="F57" t="str">
-        <v>9003000103</v>
-      </c>
       <c r="G57" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000047</v>
       </c>
       <c r="H57" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I57" t="str">
-        <v>Sheohar</v>
+        <v>0304</v>
       </c>
       <c r="J57" t="str">
-        <v>30000815657</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K57" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L57" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M57" t="str">
-        <v>SBIN0006099</v>
+        <v>30000372193</v>
+      </c>
+      <c r="N57" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O57" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P57" t="str">
+        <v>SBIN0002847</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>0300058</v>
+        <v>0300114</v>
       </c>
       <c r="B58" t="str">
-        <v>USHA SINGH</v>
+        <v>POONAM SINHA</v>
       </c>
       <c r="C58" t="str">
-        <v>Accountant</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D58" t="str">
-        <v>Block Education Office Piprahi No.1</v>
+        <v>03086</v>
       </c>
       <c r="E58" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>BSNL Exchange, Tariyani</v>
       </c>
       <c r="F58" t="str">
-        <v>9003000058</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G58" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000114</v>
       </c>
       <c r="H58" t="str">
-        <v>Piprahi</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I58" t="str">
-        <v>Piprahi</v>
+        <v>0305</v>
       </c>
       <c r="J58" t="str">
-        <v>30000459302</v>
+        <v>Tariyani</v>
       </c>
       <c r="K58" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L58" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M58" t="str">
-        <v>SBIN0009753</v>
+        <v>30000902766</v>
+      </c>
+      <c r="N58" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O58" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P58" t="str">
+        <v>SBIN0008030</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>0300005</v>
+        <v>0300110</v>
       </c>
       <c r="B59" t="str">
-        <v>NEHA SINHA</v>
+        <v>SANJAY DEVI</v>
       </c>
       <c r="C59" t="str">
-        <v>Assistant Engineer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D59" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>03082</v>
       </c>
       <c r="E59" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>LIC Branch Office, Piprahi</v>
       </c>
       <c r="F59" t="str">
-        <v>9003000005</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G59" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000110</v>
       </c>
       <c r="H59" t="str">
-        <v>Dumri Katsari</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I59" t="str">
-        <v>Sheohar</v>
+        <v>0302</v>
       </c>
       <c r="J59" t="str">
-        <v>30000039595</v>
+        <v>Piprahi</v>
       </c>
       <c r="K59" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L59" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M59" t="str">
-        <v>SBIN0004345</v>
+        <v>30000871090</v>
+      </c>
+      <c r="N59" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O59" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P59" t="str">
+        <v>SBIN0007594</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>0300079</v>
+        <v>0300024</v>
       </c>
       <c r="B60" t="str">
-        <v>NASREEN YADAV</v>
+        <v>DEEPAK SINHA</v>
       </c>
       <c r="C60" t="str">
-        <v>Office Assistant</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D60" t="str">
-        <v>Middle School Piprahi</v>
+        <v>03022</v>
       </c>
       <c r="E60" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Project Girls High School Tariyani</v>
       </c>
       <c r="F60" t="str">
-        <v>9003000079</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G60" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000024</v>
       </c>
       <c r="H60" t="str">
+        <v>POLLING OFFICER-1</v>
+      </c>
+      <c r="I60" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J60" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K60" t="str">
+        <v>0305</v>
+      </c>
+      <c r="L60" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I60" t="str">
-        <v>Piprahi</v>
-      </c>
-      <c r="J60" t="str">
-        <v>30000625601</v>
-      </c>
-      <c r="K60" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L60" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M60" t="str">
-        <v>SBIN0008927</v>
+        <v>30000190056</v>
+      </c>
+      <c r="N60" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O60" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P60" t="str">
+        <v>SBIN0003458</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>0300070</v>
+        <v>0300076</v>
       </c>
       <c r="B61" t="str">
-        <v>KUMARI ANJALI SHARMA</v>
+        <v>UMESH MISHRA</v>
       </c>
       <c r="C61" t="str">
-        <v>Teacher</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D61" t="str">
-        <v>Circle Office Purnahiya No.2</v>
+        <v>03064</v>
       </c>
       <c r="E61" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>High School Dumri Katsari No.3</v>
       </c>
       <c r="F61" t="str">
-        <v>9003000070</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G61" t="str">
+        <v>9003000076</v>
+      </c>
+      <c r="H61" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
-      <c r="H61" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="I61" t="str">
-        <v>Purnahiya</v>
+        <v>0304</v>
       </c>
       <c r="J61" t="str">
-        <v>30000554330</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K61" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L61" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M61" t="str">
-        <v>SBIN0004132</v>
+        <v>30000601844</v>
+      </c>
+      <c r="N61" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O61" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P61" t="str">
+        <v>SBIN0006310</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>0300027</v>
+        <v>0300108</v>
       </c>
       <c r="B62" t="str">
-        <v>SANJAY KHATUN</v>
+        <v>ARVIND MISHRA</v>
       </c>
       <c r="C62" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D62" t="str">
-        <v>PHC Dumri Katsari No.1</v>
+        <v>03081</v>
       </c>
       <c r="E62" t="str">
+        <v>Punjab National Bank, Dumri Katsari</v>
+      </c>
+      <c r="F62" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
-      <c r="F62" t="str">
-        <v>9003000027</v>
-      </c>
       <c r="G62" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000108</v>
       </c>
       <c r="H62" t="str">
-        <v>Tariyani</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I62" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J62" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="J62" t="str">
-        <v>30000213813</v>
-      </c>
       <c r="K62" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L62" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M62" t="str">
-        <v>SBIN0006060</v>
+        <v>30000855252</v>
+      </c>
+      <c r="N62" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O62" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P62" t="str">
+        <v>SBIN0007979</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>0300068</v>
+        <v>0300031</v>
       </c>
       <c r="B63" t="str">
-        <v>SANTOSH SAH</v>
+        <v>NITISH KHATUN</v>
       </c>
       <c r="C63" t="str">
-        <v>Office Assistant</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D63" t="str">
-        <v>CDPO Office Tariyani</v>
+        <v>03029</v>
       </c>
       <c r="E63" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Primary School Dumri Katsari No.3</v>
       </c>
       <c r="F63" t="str">
-        <v>9003000068</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G63" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000031</v>
       </c>
       <c r="H63" t="str">
-        <v>Purnahiya</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I63" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J63" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="J63" t="str">
-        <v>30000538492</v>
-      </c>
       <c r="K63" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L63" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M63" t="str">
-        <v>SBIN0003789</v>
+        <v>30000245489</v>
+      </c>
+      <c r="N63" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O63" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P63" t="str">
+        <v>SBIN0009745</v>
       </c>
     </row>
     <row r="64">
@@ -4080,81 +4650,99 @@
         <v>0300002</v>
       </c>
       <c r="B64" t="str">
-        <v>MAMTA SINGH</v>
+        <v>PRAMOD MISHRA</v>
       </c>
       <c r="C64" t="str">
         <v>Section Officer</v>
       </c>
       <c r="D64" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>03002</v>
       </c>
       <c r="E64" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Kanya Middle School Dumri Katsari No.2</v>
       </c>
       <c r="F64" t="str">
+        <v>Dumri Katsari, Sheohar</v>
+      </c>
+      <c r="G64" t="str">
         <v>9003000002</v>
       </c>
-      <c r="G64" t="str">
+      <c r="H64" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
-      <c r="H64" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="I64" t="str">
-        <v>Tariyani</v>
+        <v>0301</v>
       </c>
       <c r="J64" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K64" t="str">
+        <v>0304</v>
+      </c>
+      <c r="L64" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="M64" t="str">
         <v>30000015838</v>
       </c>
-      <c r="K64" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L64" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="M64" t="str">
-        <v>SBIN0007559</v>
+      <c r="N64" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O64" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P64" t="str">
+        <v>SBIN0007114</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>0300111</v>
+        <v>0300079</v>
       </c>
       <c r="B65" t="str">
-        <v>AJAY CHAUDHARY</v>
+        <v>VIJAY MAHTO S</v>
       </c>
       <c r="C65" t="str">
-        <v>Branch Manager</v>
+        <v>Clerk</v>
       </c>
       <c r="D65" t="str">
-        <v>Central Bank of India, Dumri Katsari</v>
+        <v>03066</v>
       </c>
       <c r="E65" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Kanya Middle School Purnahiya No.2</v>
       </c>
       <c r="F65" t="str">
-        <v>9003000111</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G65" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000079</v>
       </c>
       <c r="H65" t="str">
-        <v>Dumri Katsari</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I65" t="str">
-        <v>Dumri Katsari</v>
+        <v>0303</v>
       </c>
       <c r="J65" t="str">
-        <v>30000879009</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K65" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L65" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M65" t="str">
-        <v>SBIN0002430</v>
+        <v>30000625601</v>
+      </c>
+      <c r="N65" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O65" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P65" t="str">
+        <v>SBIN0006759</v>
       </c>
     </row>
     <row r="66">
@@ -4162,2559 +4750,3118 @@
         <v>0300018</v>
       </c>
       <c r="B66" t="str">
-        <v>RAJESH SAH</v>
+        <v>NEHA JHA</v>
       </c>
       <c r="C66" t="str">
-        <v>Assistant Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D66" t="str">
-        <v>Block Education Office Piprahi No.4</v>
+        <v>03006</v>
       </c>
       <c r="E66" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Block Education Office Sheohar No.2</v>
       </c>
       <c r="F66" t="str">
+        <v>Sheohar, Sheohar</v>
+      </c>
+      <c r="G66" t="str">
         <v>9003000018</v>
       </c>
-      <c r="G66" t="str">
+      <c r="H66" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
-      <c r="H66" t="str">
-        <v>Dumri Katsari</v>
-      </c>
       <c r="I66" t="str">
-        <v>Piprahi</v>
+        <v>0301</v>
       </c>
       <c r="J66" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K66" t="str">
+        <v>0301</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="M66" t="str">
         <v>30000142542</v>
       </c>
-      <c r="K66" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L66" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="M66" t="str">
-        <v>SBIN0009286</v>
+      <c r="N66" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O66" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P66" t="str">
+        <v>SBIN0007766</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>0300098</v>
+        <v>0300011</v>
       </c>
       <c r="B67" t="str">
-        <v>MAMTA KUMAR</v>
+        <v>RAVI ALAM</v>
       </c>
       <c r="C67" t="str">
-        <v>Junior Engineer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D67" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>03011</v>
       </c>
       <c r="E67" t="str">
+        <v>Block Office Purnahiya No.2</v>
+      </c>
+      <c r="F67" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
-      <c r="F67" t="str">
-        <v>9003000098</v>
-      </c>
       <c r="G67" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000011</v>
       </c>
       <c r="H67" t="str">
+        <v>PRESIDING OFFICER</v>
+      </c>
+      <c r="I67" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J67" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="I67" t="str">
+      <c r="K67" t="str">
+        <v>0303</v>
+      </c>
+      <c r="L67" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="J67" t="str">
-        <v>30000776062</v>
-      </c>
-      <c r="K67" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L67" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M67" t="str">
-        <v>SBIN0006839</v>
+        <v>30000087109</v>
+      </c>
+      <c r="N67" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O67" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P67" t="str">
+        <v>SBIN0004156</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>0300050</v>
+        <v>0300049</v>
       </c>
       <c r="B68" t="str">
-        <v>ALOK SINHA</v>
+        <v>DINESH MISHRA</v>
       </c>
       <c r="C68" t="str">
         <v>Teacher</v>
       </c>
       <c r="D68" t="str">
-        <v>PHC Purnahiya No.3</v>
+        <v>03044</v>
       </c>
       <c r="E68" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Block Office Dumri Katsari No.2</v>
       </c>
       <c r="F68" t="str">
-        <v>9003000050</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G68" t="str">
+        <v>9003000049</v>
+      </c>
+      <c r="H68" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
-      <c r="H68" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="I68" t="str">
-        <v>Purnahiya</v>
+        <v>0301</v>
       </c>
       <c r="J68" t="str">
-        <v>30000395950</v>
+        <v>Sheohar</v>
       </c>
       <c r="K68" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L68" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M68" t="str">
-        <v>SBIN0009474</v>
+        <v>30000388031</v>
+      </c>
+      <c r="N68" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O68" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P68" t="str">
+        <v>SBIN0007011</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>0300116</v>
+        <v>0300097</v>
       </c>
       <c r="B69" t="str">
-        <v>ANITA PANDEY</v>
+        <v>SANTOSH VERMA</v>
       </c>
       <c r="C69" t="str">
-        <v>Postmaster</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D69" t="str">
-        <v>Punjab National Bank, Piprahi</v>
+        <v>03046</v>
       </c>
       <c r="E69" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Block Office Sheohar</v>
       </c>
       <c r="F69" t="str">
-        <v>9003000116</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G69" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000097</v>
       </c>
       <c r="H69" t="str">
-        <v>Piprahi</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I69" t="str">
-        <v>Piprahi</v>
+        <v>0304</v>
       </c>
       <c r="J69" t="str">
-        <v>30000918604</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K69" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L69" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M69" t="str">
-        <v>SBIN0004415</v>
+        <v>30000768143</v>
+      </c>
+      <c r="N69" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O69" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P69" t="str">
+        <v>SBIN0009118</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>0300113</v>
+        <v>0300022</v>
       </c>
       <c r="B70" t="str">
-        <v>SURESH ANSARI</v>
+        <v>MAHESH KUMAR</v>
       </c>
       <c r="C70" t="str">
-        <v>Branch Manager</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D70" t="str">
-        <v>Bank of India, Piprahi</v>
+        <v>03020</v>
       </c>
       <c r="E70" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Block Education Office Tariyani No.3</v>
       </c>
       <c r="F70" t="str">
-        <v>9003000113</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G70" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000022</v>
       </c>
       <c r="H70" t="str">
-        <v>Dumri Katsari</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I70" t="str">
-        <v>Piprahi</v>
+        <v>0305</v>
       </c>
       <c r="J70" t="str">
-        <v>30000894847</v>
+        <v>Tariyani</v>
       </c>
       <c r="K70" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L70" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M70" t="str">
-        <v>SBIN0007124</v>
+        <v>30000174218</v>
+      </c>
+      <c r="N70" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O70" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P70" t="str">
+        <v>SBIN0003756</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>0300016</v>
+        <v>0300044</v>
       </c>
       <c r="B71" t="str">
-        <v>ABDUL KALAM DEVI</v>
+        <v>AMIT TIWARI</v>
       </c>
       <c r="C71" t="str">
-        <v>Lecturer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D71" t="str">
-        <v>PHC Piprahi No.3</v>
+        <v>03039</v>
       </c>
       <c r="E71" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F71" t="str">
-        <v>9003000016</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G71" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000044</v>
       </c>
       <c r="H71" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I71" t="str">
-        <v>Piprahi</v>
+        <v>0301</v>
       </c>
       <c r="J71" t="str">
-        <v>30000126704</v>
+        <v>Sheohar</v>
       </c>
       <c r="K71" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L71" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M71" t="str">
-        <v>SBIN0007804</v>
+        <v>30000348436</v>
+      </c>
+      <c r="N71" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O71" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P71" t="str">
+        <v>SBIN0003476</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>0300059</v>
+        <v>0300065</v>
       </c>
       <c r="B72" t="str">
-        <v>PRAMOD PASWAN</v>
+        <v>DINESH ANSARI</v>
       </c>
       <c r="C72" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D72" t="str">
-        <v>CDPO Office Purnahiya</v>
+        <v>03057</v>
       </c>
       <c r="E72" t="str">
+        <v>Project Girls High School Purnahiya</v>
+      </c>
+      <c r="F72" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
-      <c r="F72" t="str">
-        <v>9003000059</v>
-      </c>
       <c r="G72" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000065</v>
       </c>
       <c r="H72" t="str">
+        <v>POLLING OFFICER-3</v>
+      </c>
+      <c r="I72" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J72" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="I72" t="str">
+      <c r="K72" t="str">
+        <v>0303</v>
+      </c>
+      <c r="L72" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="J72" t="str">
-        <v>30000467221</v>
-      </c>
-      <c r="K72" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L72" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M72" t="str">
-        <v>SBIN0009715</v>
+        <v>30000514735</v>
+      </c>
+      <c r="N72" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O72" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P72" t="str">
+        <v>SBIN0006470</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>0300095</v>
+        <v>0300010</v>
       </c>
       <c r="B73" t="str">
-        <v>NASREEN MISHRA</v>
+        <v>MAMTA DEVI</v>
       </c>
       <c r="C73" t="str">
-        <v>Junior Engineer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D73" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>03010</v>
       </c>
       <c r="E73" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Panchayat Bhawan Purnahiya No.4</v>
       </c>
       <c r="F73" t="str">
-        <v>9003000095</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G73" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000010</v>
       </c>
       <c r="H73" t="str">
-        <v>Sheohar</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I73" t="str">
-        <v>Piprahi</v>
+        <v>0305</v>
       </c>
       <c r="J73" t="str">
-        <v>30000752305</v>
+        <v>Tariyani</v>
       </c>
       <c r="K73" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L73" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M73" t="str">
-        <v>SBIN0003824</v>
+        <v>30000079190</v>
+      </c>
+      <c r="N73" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O73" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P73" t="str">
+        <v>SBIN0009303</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>0300015</v>
+        <v>0300070</v>
       </c>
       <c r="B74" t="str">
-        <v>MD. SHAHID KUMAR</v>
+        <v>POONAM PANDEY</v>
       </c>
       <c r="C74" t="str">
-        <v>Lecturer</v>
+        <v>Teacher</v>
       </c>
       <c r="D74" t="str">
-        <v>Circle Office Tariyani No.2</v>
+        <v>03021</v>
       </c>
       <c r="E74" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Middle School Dumri Katsari No.2</v>
       </c>
       <c r="F74" t="str">
-        <v>9003000015</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G74" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000070</v>
       </c>
       <c r="H74" t="str">
+        <v>POLLING OFFICER-3</v>
+      </c>
+      <c r="I74" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J74" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I74" t="str">
-        <v>Tariyani</v>
-      </c>
-      <c r="J74" t="str">
-        <v>30000118785</v>
-      </c>
       <c r="K74" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L74" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M74" t="str">
-        <v>SBIN0002763</v>
+        <v>30000554330</v>
+      </c>
+      <c r="N74" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O74" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P74" t="str">
+        <v>SBIN0002229</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>0300100</v>
+        <v>0300122</v>
       </c>
       <c r="B75" t="str">
-        <v>ALOK PRASAD</v>
+        <v>RAJESH RAI</v>
       </c>
       <c r="C75" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D75" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>03092</v>
       </c>
       <c r="E75" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Central Bank of India, Sheohar</v>
       </c>
       <c r="F75" t="str">
-        <v>9003000100</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G75" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000122</v>
       </c>
       <c r="H75" t="str">
-        <v>Sheohar</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I75" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J75" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="J75" t="str">
-        <v>30000791900</v>
-      </c>
       <c r="K75" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L75" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M75" t="str">
-        <v>SBIN0009517</v>
+        <v>30000966118</v>
+      </c>
+      <c r="N75" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O75" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P75" t="str">
+        <v>SBIN0005272</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>0300013</v>
+        <v>0300051</v>
       </c>
       <c r="B76" t="str">
-        <v>NEHA YADAV</v>
+        <v>DEEPAK PANDEY</v>
       </c>
       <c r="C76" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D76" t="str">
-        <v>Block Education Office Purnahiya</v>
+        <v>03046</v>
       </c>
       <c r="E76" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Block Office Sheohar</v>
       </c>
       <c r="F76" t="str">
-        <v>9003000013</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G76" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000051</v>
       </c>
       <c r="H76" t="str">
-        <v>Piprahi</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I76" t="str">
-        <v>Purnahiya</v>
+        <v>0305</v>
       </c>
       <c r="J76" t="str">
-        <v>30000102947</v>
+        <v>Tariyani</v>
       </c>
       <c r="K76" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L76" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M76" t="str">
-        <v>SBIN0001900</v>
+        <v>30000403869</v>
+      </c>
+      <c r="N76" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O76" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P76" t="str">
+        <v>SBIN0005318</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>0300045</v>
+        <v>0300003</v>
       </c>
       <c r="B77" t="str">
-        <v>FARHAT RAI</v>
+        <v>MAMTA VERMA</v>
       </c>
       <c r="C77" t="str">
-        <v>Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D77" t="str">
-        <v>Kanya Middle School Tariyani</v>
+        <v>03003</v>
       </c>
       <c r="E77" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Project Girls High School Sheohar No.3</v>
       </c>
       <c r="F77" t="str">
-        <v>9003000045</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G77" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000003</v>
       </c>
       <c r="H77" t="str">
-        <v>Tariyani</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I77" t="str">
-        <v>Tariyani</v>
+        <v>0301</v>
       </c>
       <c r="J77" t="str">
-        <v>30000356355</v>
+        <v>Sheohar</v>
       </c>
       <c r="K77" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L77" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M77" t="str">
-        <v>SBIN0002223</v>
+        <v>30000023757</v>
+      </c>
+      <c r="N77" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O77" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P77" t="str">
+        <v>SBIN0002632</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>0300063</v>
+        <v>0300107</v>
       </c>
       <c r="B78" t="str">
-        <v>DINESH RAI</v>
+        <v>ARVIND GUPTA</v>
       </c>
       <c r="C78" t="str">
-        <v>Accountant</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D78" t="str">
-        <v>Kanya Middle School Tariyani</v>
+        <v>03080</v>
       </c>
       <c r="E78" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Bank of India, Dumri Katsari</v>
       </c>
       <c r="F78" t="str">
-        <v>9003000063</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G78" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000107</v>
       </c>
       <c r="H78" t="str">
-        <v>Tariyani</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I78" t="str">
-        <v>Tariyani</v>
+        <v>0304</v>
       </c>
       <c r="J78" t="str">
-        <v>30000498897</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K78" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L78" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M78" t="str">
-        <v>SBIN0003132</v>
+        <v>30000847333</v>
+      </c>
+      <c r="N78" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O78" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P78" t="str">
+        <v>SBIN0009936</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0300061</v>
+        <v>0300077</v>
       </c>
       <c r="B79" t="str">
-        <v>ALOK MISHRA</v>
+        <v>SAVITA PRASAD</v>
       </c>
       <c r="C79" t="str">
-        <v>Clerk</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D79" t="str">
-        <v>Kanya Middle School Tariyani No.2</v>
+        <v>03032</v>
       </c>
       <c r="E79" t="str">
+        <v>Kanya Middle School Tariyani</v>
+      </c>
+      <c r="F79" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
-      <c r="F79" t="str">
-        <v>9003000061</v>
-      </c>
       <c r="G79" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000077</v>
       </c>
       <c r="H79" t="str">
+        <v>POLLING OFFICER-3</v>
+      </c>
+      <c r="I79" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J79" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I79" t="str">
+      <c r="K79" t="str">
+        <v>0305</v>
+      </c>
+      <c r="L79" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="J79" t="str">
-        <v>30000483059</v>
-      </c>
-      <c r="K79" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L79" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M79" t="str">
-        <v>SBIN0008025</v>
+        <v>30000609763</v>
+      </c>
+      <c r="N79" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O79" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P79" t="str">
+        <v>SBIN0004211</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>0300037</v>
+        <v>0300004</v>
       </c>
       <c r="B80" t="str">
-        <v>SHAILESH PASWAN</v>
+        <v>SANJAY VERMA</v>
       </c>
       <c r="C80" t="str">
-        <v>Assistant Teacher</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D80" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>03004</v>
       </c>
       <c r="E80" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Project Girls High School Dumri Katsari No.4</v>
       </c>
       <c r="F80" t="str">
-        <v>9003000037</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G80" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000004</v>
       </c>
       <c r="H80" t="str">
-        <v>Piprahi</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I80" t="str">
-        <v>Sheohar</v>
+        <v>0301</v>
       </c>
       <c r="J80" t="str">
-        <v>30000293003</v>
+        <v>Sheohar</v>
       </c>
       <c r="K80" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L80" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M80" t="str">
-        <v>SBIN0008263</v>
+        <v>30000031676</v>
+      </c>
+      <c r="N80" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O80" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P80" t="str">
+        <v>SBIN0007104</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>0300076</v>
+        <v>0300118</v>
       </c>
       <c r="B81" t="str">
-        <v>MUKESH PASWAN</v>
+        <v>AJAY KUMAR G</v>
       </c>
       <c r="C81" t="str">
-        <v>Data Entry Operator</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D81" t="str">
-        <v>Kanya Middle School Sheohar No.4</v>
+        <v>03089</v>
       </c>
       <c r="E81" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Punjab National Bank, Tariyani</v>
       </c>
       <c r="F81" t="str">
-        <v>9003000076</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G81" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000118</v>
       </c>
       <c r="H81" t="str">
-        <v>Sheohar</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I81" t="str">
-        <v>Sheohar</v>
+        <v>0305</v>
       </c>
       <c r="J81" t="str">
-        <v>30000601844</v>
+        <v>Tariyani</v>
       </c>
       <c r="K81" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L81" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M81" t="str">
-        <v>SBIN0006444</v>
+        <v>30000934442</v>
+      </c>
+      <c r="N81" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O81" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P81" t="str">
+        <v>SBIN0002402</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>0300118</v>
+        <v>0300034</v>
       </c>
       <c r="B82" t="str">
-        <v>NASREEN RAI</v>
+        <v>NASREEN YADAV</v>
       </c>
       <c r="C82" t="str">
-        <v>Branch Manager</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D82" t="str">
-        <v>Central Bank of India, Dumri Katsari</v>
+        <v>03024</v>
       </c>
       <c r="E82" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Block Education Office Purnahiya</v>
       </c>
       <c r="F82" t="str">
-        <v>9003000118</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G82" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000034</v>
       </c>
       <c r="H82" t="str">
-        <v>Tariyani</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I82" t="str">
-        <v>Dumri Katsari</v>
+        <v>0303</v>
       </c>
       <c r="J82" t="str">
-        <v>30000934442</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K82" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L82" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M82" t="str">
-        <v>SBIN0008812</v>
+        <v>30000269246</v>
+      </c>
+      <c r="N82" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O82" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P82" t="str">
+        <v>SBIN0008806</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>0300085</v>
+        <v>0300106</v>
       </c>
       <c r="B83" t="str">
-        <v>PRAMOD JHA D</v>
+        <v>DEEPAK SINHA U</v>
       </c>
       <c r="C83" t="str">
-        <v>Junior Engineer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D83" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>03079</v>
       </c>
       <c r="E83" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Punjab National Bank, Purnahiya</v>
       </c>
       <c r="F83" t="str">
-        <v>9003000085</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G83" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000106</v>
       </c>
       <c r="H83" t="str">
-        <v>Dumri Katsari</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I83" t="str">
-        <v>Piprahi</v>
+        <v>0303</v>
       </c>
       <c r="J83" t="str">
-        <v>30000673115</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K83" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L83" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M83" t="str">
-        <v>SBIN0007520</v>
+        <v>30000839414</v>
+      </c>
+      <c r="N83" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O83" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P83" t="str">
+        <v>SBIN0007304</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>0300035</v>
+        <v>0300072</v>
       </c>
       <c r="B84" t="str">
-        <v>MUKESH PRASAD</v>
+        <v>VIJAY MAHTO</v>
       </c>
       <c r="C84" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D84" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>03062</v>
       </c>
       <c r="E84" t="str">
+        <v>Primary School Sheohar No.2</v>
+      </c>
+      <c r="F84" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
-      <c r="F84" t="str">
-        <v>9003000035</v>
-      </c>
       <c r="G84" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000072</v>
       </c>
       <c r="H84" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I84" t="str">
-        <v>Sheohar</v>
+        <v>0304</v>
       </c>
       <c r="J84" t="str">
-        <v>30000277165</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K84" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L84" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M84" t="str">
-        <v>SBIN0009090</v>
+        <v>30000570168</v>
+      </c>
+      <c r="N84" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O84" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P84" t="str">
+        <v>SBIN0002494</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>0300099</v>
+        <v>0300123</v>
       </c>
       <c r="B85" t="str">
-        <v>SHAILESH MAHTO</v>
+        <v>MANOJ RAM</v>
       </c>
       <c r="C85" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D85" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>03093</v>
       </c>
       <c r="E85" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Punjab National Bank, Piprahi</v>
       </c>
       <c r="F85" t="str">
-        <v>9003000099</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G85" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000123</v>
       </c>
       <c r="H85" t="str">
-        <v>Sheohar</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I85" t="str">
-        <v>Sheohar</v>
+        <v>0302</v>
       </c>
       <c r="J85" t="str">
-        <v>30000783981</v>
+        <v>Piprahi</v>
       </c>
       <c r="K85" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L85" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M85" t="str">
-        <v>SBIN0003314</v>
+        <v>30000974037</v>
+      </c>
+      <c r="N85" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O85" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P85" t="str">
+        <v>SBIN0001093</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>0300048</v>
+        <v>0300045</v>
       </c>
       <c r="B86" t="str">
-        <v>KUMARI ANJALI MAHTO F</v>
+        <v>MD. IRFAN PANDEY</v>
       </c>
       <c r="C86" t="str">
-        <v>Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D86" t="str">
-        <v>Project Girls High School Dumri Katsari</v>
+        <v>03040</v>
       </c>
       <c r="E86" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F86" t="str">
-        <v>9003000048</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G86" t="str">
+        <v>9003000045</v>
+      </c>
+      <c r="H86" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
-      <c r="H86" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="I86" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J86" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="J86" t="str">
-        <v>30000380112</v>
-      </c>
       <c r="K86" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L86" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M86" t="str">
-        <v>SBIN0003742</v>
+        <v>30000356355</v>
+      </c>
+      <c r="N86" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O86" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P86" t="str">
+        <v>SBIN0008508</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>0300072</v>
+        <v>0300087</v>
       </c>
       <c r="B87" t="str">
-        <v>MD. SHAHID KUMAR G</v>
+        <v>SAVITA KHATUN</v>
       </c>
       <c r="C87" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D87" t="str">
-        <v>Block Agriculture Office Purnahiya No.2</v>
+        <v>03070</v>
       </c>
       <c r="E87" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F87" t="str">
-        <v>9003000072</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G87" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000087</v>
       </c>
       <c r="H87" t="str">
+        <v>PATROLLING MAGISTRATE</v>
+      </c>
+      <c r="I87" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J87" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K87" t="str">
+        <v>0304</v>
+      </c>
+      <c r="L87" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I87" t="str">
-        <v>Purnahiya</v>
-      </c>
-      <c r="J87" t="str">
-        <v>30000570168</v>
-      </c>
-      <c r="K87" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L87" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M87" t="str">
-        <v>SBIN0009606</v>
+        <v>30000688953</v>
+      </c>
+      <c r="N87" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O87" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P87" t="str">
+        <v>SBIN0005730</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>0300075</v>
+        <v>0300036</v>
       </c>
       <c r="B88" t="str">
-        <v>RANJIT YADAV</v>
+        <v>RAJESH SINGH</v>
       </c>
       <c r="C88" t="str">
-        <v>Data Entry Operator</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D88" t="str">
-        <v>Block Education Office Sheohar</v>
+        <v>03033</v>
       </c>
       <c r="E88" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Block Office Piprahi No.4</v>
       </c>
       <c r="F88" t="str">
-        <v>9003000075</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G88" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000036</v>
       </c>
       <c r="H88" t="str">
+        <v>POLLING OFFICER-1</v>
+      </c>
+      <c r="I88" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J88" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I88" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="J88" t="str">
-        <v>30000593925</v>
-      </c>
       <c r="K88" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L88" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M88" t="str">
-        <v>SBIN0009504</v>
+        <v>30000285084</v>
+      </c>
+      <c r="N88" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O88" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P88" t="str">
+        <v>SBIN0002350</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>0300039</v>
+        <v>0300085</v>
       </c>
       <c r="B89" t="str">
-        <v>MD. SHAHID KHATUN</v>
+        <v>SURESH MAHTO</v>
       </c>
       <c r="C89" t="str">
-        <v>Assistant Teacher</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D89" t="str">
-        <v>High School Sheohar</v>
+        <v>03038</v>
       </c>
       <c r="E89" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="F89" t="str">
-        <v>9003000039</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G89" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000085</v>
       </c>
       <c r="H89" t="str">
+        <v>PATROLLING MAGISTRATE</v>
+      </c>
+      <c r="I89" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J89" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="I89" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="J89" t="str">
-        <v>30000308841</v>
-      </c>
       <c r="K89" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L89" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M89" t="str">
-        <v>SBIN0001133</v>
+        <v>30000673115</v>
+      </c>
+      <c r="N89" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O89" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P89" t="str">
+        <v>SBIN0008022</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>0300064</v>
+        <v>0300093</v>
       </c>
       <c r="B90" t="str">
-        <v>PRIYANKA YADAV</v>
+        <v>SANTOSH PRASAD</v>
       </c>
       <c r="C90" t="str">
-        <v>Teacher</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D90" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>03046</v>
       </c>
       <c r="E90" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Block Office Sheohar</v>
       </c>
       <c r="F90" t="str">
-        <v>9003000064</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G90" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000093</v>
       </c>
       <c r="H90" t="str">
-        <v>Dumri Katsari</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I90" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J90" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="J90" t="str">
-        <v>30000506816</v>
-      </c>
       <c r="K90" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L90" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M90" t="str">
-        <v>SBIN0003247</v>
+        <v>30000736467</v>
+      </c>
+      <c r="N90" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O90" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P90" t="str">
+        <v>SBIN0009257</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>0300060</v>
+        <v>0300074</v>
       </c>
       <c r="B91" t="str">
-        <v>PRAMOD MAHTO</v>
+        <v>FARHAT PASWAN</v>
       </c>
       <c r="C91" t="str">
-        <v>Accountant</v>
+        <v>Clerk</v>
       </c>
       <c r="D91" t="str">
-        <v>Block Agriculture Office Piprahi No.1</v>
+        <v>03046</v>
       </c>
       <c r="E91" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Block Office Sheohar</v>
       </c>
       <c r="F91" t="str">
-        <v>9003000060</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G91" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000074</v>
       </c>
       <c r="H91" t="str">
-        <v>Piprahi</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I91" t="str">
-        <v>Piprahi</v>
+        <v>0303</v>
       </c>
       <c r="J91" t="str">
-        <v>30000475140</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K91" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L91" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M91" t="str">
-        <v>SBIN0001887</v>
+        <v>30000586006</v>
+      </c>
+      <c r="N91" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O91" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P91" t="str">
+        <v>SBIN0009908</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>0300036</v>
+        <v>0300057</v>
       </c>
       <c r="B92" t="str">
-        <v>PANKAJ MAHTO</v>
+        <v>VIJAY PASWAN</v>
       </c>
       <c r="C92" t="str">
-        <v>Head Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D92" t="str">
-        <v>High School Sheohar</v>
+        <v>03050</v>
       </c>
       <c r="E92" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Panchayat Bhawan Purnahiya No.2</v>
       </c>
       <c r="F92" t="str">
-        <v>9003000036</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G92" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000057</v>
       </c>
       <c r="H92" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I92" t="str">
-        <v>Sheohar</v>
+        <v>0303</v>
       </c>
       <c r="J92" t="str">
-        <v>30000285084</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K92" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L92" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M92" t="str">
-        <v>SBIN0001873</v>
+        <v>30000451383</v>
+      </c>
+      <c r="N92" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O92" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P92" t="str">
+        <v>SBIN0009799</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>0300010</v>
+        <v>0300071</v>
       </c>
       <c r="B93" t="str">
-        <v>KIRAN SINGH</v>
+        <v>ABDUL KALAM SINHA</v>
       </c>
       <c r="C93" t="str">
-        <v>Assistant Engineer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D93" t="str">
-        <v>Project Girls High School Tariyani No.1</v>
+        <v>03039</v>
       </c>
       <c r="E93" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F93" t="str">
-        <v>9003000010</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G93" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000071</v>
       </c>
       <c r="H93" t="str">
-        <v>Tariyani</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I93" t="str">
-        <v>Tariyani</v>
+        <v>0301</v>
       </c>
       <c r="J93" t="str">
-        <v>30000079190</v>
+        <v>Sheohar</v>
       </c>
       <c r="K93" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L93" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M93" t="str">
-        <v>SBIN0004368</v>
+        <v>30000562249</v>
+      </c>
+      <c r="N93" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O93" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P93" t="str">
+        <v>SBIN0001722</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>0300097</v>
+        <v>0300126</v>
       </c>
       <c r="B94" t="str">
-        <v>KIRAN PASWAN</v>
+        <v>ANITA KUMAR</v>
       </c>
       <c r="C94" t="str">
-        <v>Assistant Engineer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D94" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>03096</v>
       </c>
       <c r="E94" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Head Post Office, Dumri Katsari</v>
       </c>
       <c r="F94" t="str">
-        <v>9003000097</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G94" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000126</v>
       </c>
       <c r="H94" t="str">
+        <v>MICRO OBSERVER</v>
+      </c>
+      <c r="I94" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J94" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I94" t="str">
-        <v>Tariyani</v>
-      </c>
-      <c r="J94" t="str">
-        <v>30000768143</v>
-      </c>
       <c r="K94" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L94" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M94" t="str">
-        <v>SBIN0006265</v>
+        <v>30000997794</v>
+      </c>
+      <c r="N94" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O94" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P94" t="str">
+        <v>SBIN0009575</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>0300089</v>
+        <v>0300016</v>
       </c>
       <c r="B95" t="str">
-        <v>ARVIND GUPTA</v>
+        <v>AJAY YADAV</v>
       </c>
       <c r="C95" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D95" t="str">
-        <v>Minor Irrigation Office Sheohar</v>
+        <v>03016</v>
       </c>
       <c r="E95" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Block Agriculture Office Piprahi No.2</v>
       </c>
       <c r="F95" t="str">
-        <v>9003000089</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G95" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000016</v>
       </c>
       <c r="H95" t="str">
-        <v>Sheohar</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I95" t="str">
-        <v>Sheohar</v>
+        <v>0302</v>
       </c>
       <c r="J95" t="str">
-        <v>30000704791</v>
+        <v>Piprahi</v>
       </c>
       <c r="K95" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L95" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M95" t="str">
-        <v>SBIN0008877</v>
+        <v>30000126704</v>
+      </c>
+      <c r="N95" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O95" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P95" t="str">
+        <v>SBIN0005767</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>0300090</v>
+        <v>0300029</v>
       </c>
       <c r="B96" t="str">
-        <v>KIRAN ALAM</v>
+        <v>NEHA ALAM</v>
       </c>
       <c r="C96" t="str">
-        <v>Revenue Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D96" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>03027</v>
       </c>
       <c r="E96" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Middle School Sheohar No.4</v>
       </c>
       <c r="F96" t="str">
-        <v>9003000090</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G96" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000029</v>
       </c>
       <c r="H96" t="str">
-        <v>Piprahi</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I96" t="str">
-        <v>Piprahi</v>
+        <v>0301</v>
       </c>
       <c r="J96" t="str">
-        <v>30000712710</v>
+        <v>Sheohar</v>
       </c>
       <c r="K96" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L96" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M96" t="str">
-        <v>SBIN0009978</v>
+        <v>30000229651</v>
+      </c>
+      <c r="N96" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O96" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P96" t="str">
+        <v>SBIN0008276</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0300119</v>
+        <v>0300066</v>
       </c>
       <c r="B97" t="str">
-        <v>PANKAJ KUMAR</v>
+        <v>NASREEN RAM</v>
       </c>
       <c r="C97" t="str">
-        <v>Postmaster</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D97" t="str">
-        <v>Head Post Office, Sheohar</v>
+        <v>03058</v>
       </c>
       <c r="E97" t="str">
+        <v>Kanya Middle School Sheohar</v>
+      </c>
+      <c r="F97" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
-      <c r="F97" t="str">
-        <v>9003000119</v>
-      </c>
       <c r="G97" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000066</v>
       </c>
       <c r="H97" t="str">
-        <v>Purnahiya</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I97" t="str">
-        <v>Sheohar</v>
+        <v>0301</v>
       </c>
       <c r="J97" t="str">
-        <v>30000942361</v>
+        <v>Sheohar</v>
       </c>
       <c r="K97" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L97" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M97" t="str">
-        <v>SBIN0003122</v>
+        <v>30000522654</v>
+      </c>
+      <c r="N97" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O97" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P97" t="str">
+        <v>SBIN0001211</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>0300004</v>
+        <v>0300104</v>
       </c>
       <c r="B98" t="str">
-        <v>POONAM MISHRA</v>
+        <v>RINKU VERMA</v>
       </c>
       <c r="C98" t="str">
-        <v>Lecturer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D98" t="str">
-        <v>High School Tariyani No.3</v>
+        <v>03078</v>
       </c>
       <c r="E98" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="F98" t="str">
-        <v>9003000004</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G98" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000104</v>
       </c>
       <c r="H98" t="str">
+        <v>PATROLLING MAGISTRATE</v>
+      </c>
+      <c r="I98" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J98" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I98" t="str">
-        <v>Tariyani</v>
-      </c>
-      <c r="J98" t="str">
-        <v>30000031676</v>
-      </c>
       <c r="K98" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L98" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M98" t="str">
-        <v>SBIN0003247</v>
+        <v>30000823576</v>
+      </c>
+      <c r="N98" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O98" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P98" t="str">
+        <v>SBIN0007514</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>0300053</v>
+        <v>0300068</v>
       </c>
       <c r="B99" t="str">
-        <v>MAHESH TIWARI</v>
+        <v>SAVITA CHAUDHARY</v>
       </c>
       <c r="C99" t="str">
-        <v>Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D99" t="str">
-        <v>Block Office Purnahiya No.4</v>
+        <v>03060</v>
       </c>
       <c r="E99" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Kanya Middle School Piprahi No.1</v>
       </c>
       <c r="F99" t="str">
-        <v>9003000053</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G99" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000068</v>
       </c>
       <c r="H99" t="str">
+        <v>POLLING OFFICER-3</v>
+      </c>
+      <c r="I99" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J99" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="I99" t="str">
-        <v>Purnahiya</v>
-      </c>
-      <c r="J99" t="str">
-        <v>30000419707</v>
-      </c>
       <c r="K99" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L99" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M99" t="str">
-        <v>SBIN0005985</v>
+        <v>30000538492</v>
+      </c>
+      <c r="N99" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O99" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P99" t="str">
+        <v>SBIN0003011</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>0300084</v>
+        <v>0300005</v>
       </c>
       <c r="B100" t="str">
-        <v>RANJIT VERMA</v>
+        <v>PRAMOD PRASAD</v>
       </c>
       <c r="C100" t="str">
-        <v>Teacher</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D100" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>03005</v>
       </c>
       <c r="E100" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Kanya Middle School Dumri Katsari No.3</v>
       </c>
       <c r="F100" t="str">
-        <v>9003000084</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G100" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000005</v>
       </c>
       <c r="H100" t="str">
-        <v>Purnahiya</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I100" t="str">
-        <v>Sheohar</v>
+        <v>0305</v>
       </c>
       <c r="J100" t="str">
-        <v>30000665196</v>
+        <v>Tariyani</v>
       </c>
       <c r="K100" t="str">
-        <v>State Bank of India</v>
+        <v>0304</v>
       </c>
       <c r="L100" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M100" t="str">
-        <v>SBIN0002889</v>
+        <v>30000039595</v>
+      </c>
+      <c r="N100" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O100" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P100" t="str">
+        <v>SBIN0009557</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>0300074</v>
+        <v>0300060</v>
       </c>
       <c r="B101" t="str">
-        <v>RINKU RAM</v>
+        <v>NASREEN CHAUDHARY</v>
       </c>
       <c r="C101" t="str">
-        <v>Office Assistant</v>
+        <v>Teacher</v>
       </c>
       <c r="D101" t="str">
-        <v>Block Office Piprahi</v>
+        <v>03052</v>
       </c>
       <c r="E101" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Circle Office Purnahiya No.3</v>
       </c>
       <c r="F101" t="str">
-        <v>9003000074</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G101" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000060</v>
       </c>
       <c r="H101" t="str">
-        <v>Piprahi</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I101" t="str">
-        <v>Piprahi</v>
+        <v>0303</v>
       </c>
       <c r="J101" t="str">
-        <v>30000586006</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K101" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L101" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M101" t="str">
-        <v>SBIN0009298</v>
+        <v>30000475140</v>
+      </c>
+      <c r="N101" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O101" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P101" t="str">
+        <v>SBIN0007830</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>0300126</v>
+        <v>0300032</v>
       </c>
       <c r="B102" t="str">
-        <v>FARHAT SHARMA</v>
+        <v>ANIL SHARMA</v>
       </c>
       <c r="C102" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D102" t="str">
-        <v>BSNL Exchange, Piprahi</v>
+        <v>03030</v>
       </c>
       <c r="E102" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F102" t="str">
-        <v>9003000126</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G102" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000032</v>
       </c>
       <c r="H102" t="str">
-        <v>Dumri Katsari</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I102" t="str">
-        <v>Piprahi</v>
+        <v>0305</v>
       </c>
       <c r="J102" t="str">
-        <v>30000997794</v>
+        <v>Tariyani</v>
       </c>
       <c r="K102" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L102" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M102" t="str">
-        <v>SBIN0003206</v>
+        <v>30000253408</v>
+      </c>
+      <c r="N102" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O102" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P102" t="str">
+        <v>SBIN0004761</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>0300105</v>
+        <v>0300102</v>
       </c>
       <c r="B103" t="str">
-        <v>AMIT RAM</v>
+        <v>FARHAT DEVI</v>
       </c>
       <c r="C103" t="str">
         <v>Labour Enforcement Officer</v>
       </c>
       <c r="D103" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>03074</v>
       </c>
       <c r="E103" t="str">
+        <v>Block Office Tariyani</v>
+      </c>
+      <c r="F103" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
-      <c r="F103" t="str">
-        <v>9003000105</v>
-      </c>
       <c r="G103" t="str">
+        <v>9003000102</v>
+      </c>
+      <c r="H103" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
-      <c r="H103" t="str">
+      <c r="I103" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J103" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K103" t="str">
+        <v>0305</v>
+      </c>
+      <c r="L103" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I103" t="str">
-        <v>Tariyani</v>
-      </c>
-      <c r="J103" t="str">
-        <v>30000831495</v>
-      </c>
-      <c r="K103" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L103" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M103" t="str">
-        <v>SBIN0004922</v>
+        <v>30000807738</v>
+      </c>
+      <c r="N103" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O103" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P103" t="str">
+        <v>SBIN0003674</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>0300117</v>
+        <v>0300121</v>
       </c>
       <c r="B104" t="str">
-        <v>ANITA MAHTO</v>
+        <v>MAMTA GUPTA</v>
       </c>
       <c r="C104" t="str">
-        <v>Branch Manager</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D104" t="str">
-        <v>LIC Branch Office, Piprahi</v>
+        <v>03091</v>
       </c>
       <c r="E104" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>BSNL Exchange, Sheohar</v>
       </c>
       <c r="F104" t="str">
-        <v>9003000117</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G104" t="str">
+        <v>9003000121</v>
+      </c>
+      <c r="H104" t="str">
         <v>MICRO OBSERVER</v>
       </c>
-      <c r="H104" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="I104" t="str">
-        <v>Piprahi</v>
+        <v>0303</v>
       </c>
       <c r="J104" t="str">
-        <v>30000926523</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K104" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L104" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M104" t="str">
-        <v>SBIN0006405</v>
+        <v>30000958199</v>
+      </c>
+      <c r="N104" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O104" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P104" t="str">
+        <v>SBIN0006103</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>0300055</v>
+        <v>0300039</v>
       </c>
       <c r="B105" t="str">
-        <v>AJAY DEVI</v>
+        <v>ANIL ANSARI</v>
       </c>
       <c r="C105" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D105" t="str">
-        <v>Block Education Office Tariyani</v>
+        <v>03035</v>
       </c>
       <c r="E105" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>High School Purnahiya No.2</v>
       </c>
       <c r="F105" t="str">
-        <v>9003000055</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G105" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000039</v>
       </c>
       <c r="H105" t="str">
-        <v>Tariyani</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I105" t="str">
-        <v>Tariyani</v>
+        <v>0303</v>
       </c>
       <c r="J105" t="str">
-        <v>30000435545</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K105" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L105" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M105" t="str">
-        <v>SBIN0002311</v>
+        <v>30000308841</v>
+      </c>
+      <c r="N105" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O105" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P105" t="str">
+        <v>SBIN0005728</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>0300014</v>
+        <v>0300117</v>
       </c>
       <c r="B106" t="str">
-        <v>FARHAT SAH</v>
+        <v>MD. SHAHID KHATUN</v>
       </c>
       <c r="C106" t="str">
-        <v>Section Officer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D106" t="str">
-        <v>Panchayat Bhawan Sheohar</v>
+        <v>03088</v>
       </c>
       <c r="E106" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Central Bank of India, Purnahiya</v>
       </c>
       <c r="F106" t="str">
-        <v>9003000014</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G106" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000117</v>
       </c>
       <c r="H106" t="str">
-        <v>Sheohar</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I106" t="str">
-        <v>Sheohar</v>
+        <v>0303</v>
       </c>
       <c r="J106" t="str">
-        <v>30000110866</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K106" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L106" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M106" t="str">
-        <v>SBIN0006071</v>
+        <v>30000926523</v>
+      </c>
+      <c r="N106" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O106" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P106" t="str">
+        <v>SBIN0003112</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>0300022</v>
+        <v>0300103</v>
       </c>
       <c r="B107" t="str">
-        <v>RANJIT SAH</v>
+        <v>AJAY KUMAR</v>
       </c>
       <c r="C107" t="str">
-        <v>Assistant Teacher</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D107" t="str">
-        <v>PHC Dumri Katsari</v>
+        <v>03040</v>
       </c>
       <c r="E107" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F107" t="str">
-        <v>9003000022</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G107" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000103</v>
       </c>
       <c r="H107" t="str">
-        <v>Sheohar</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I107" t="str">
-        <v>Dumri Katsari</v>
+        <v>0303</v>
       </c>
       <c r="J107" t="str">
-        <v>30000174218</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K107" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L107" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M107" t="str">
-        <v>SBIN0006085</v>
+        <v>30000815657</v>
+      </c>
+      <c r="N107" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O107" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P107" t="str">
+        <v>SBIN0005901</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>0300092</v>
+        <v>0300006</v>
       </c>
       <c r="B108" t="str">
-        <v>ABDUL KALAM ALAM</v>
+        <v>REKHA MISHRA</v>
       </c>
       <c r="C108" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D108" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>03006</v>
       </c>
       <c r="E108" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Block Education Office Sheohar No.2</v>
       </c>
       <c r="F108" t="str">
-        <v>9003000092</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G108" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000006</v>
       </c>
       <c r="H108" t="str">
-        <v>Tariyani</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I108" t="str">
-        <v>Piprahi</v>
+        <v>0303</v>
       </c>
       <c r="J108" t="str">
-        <v>30000728548</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K108" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L108" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M108" t="str">
-        <v>SBIN0001790</v>
+        <v>30000047514</v>
+      </c>
+      <c r="N108" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O108" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P108" t="str">
+        <v>SBIN0009822</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>0300001</v>
+        <v>0300012</v>
       </c>
       <c r="B109" t="str">
-        <v>ARVIND VERMA</v>
+        <v>ARVIND SAH</v>
       </c>
       <c r="C109" t="str">
-        <v>Lecturer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D109" t="str">
-        <v>Primary School Dumri Katsari No.2</v>
+        <v>03012</v>
       </c>
       <c r="E109" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>PHED Division Sheohar</v>
       </c>
       <c r="F109" t="str">
-        <v>9003000001</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G109" t="str">
+        <v>9003000012</v>
+      </c>
+      <c r="H109" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
-      <c r="H109" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="I109" t="str">
-        <v>Dumri Katsari</v>
+        <v>0301</v>
       </c>
       <c r="J109" t="str">
-        <v>30000007919</v>
+        <v>Sheohar</v>
       </c>
       <c r="K109" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L109" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M109" t="str">
-        <v>SBIN0001102</v>
+        <v>30000095028</v>
+      </c>
+      <c r="N109" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O109" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P109" t="str">
+        <v>SBIN0005292</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>0300121</v>
+        <v>0300067</v>
       </c>
       <c r="B110" t="str">
-        <v>AMIT KUMAR</v>
+        <v>MD. SHAHID SINGH</v>
       </c>
       <c r="C110" t="str">
-        <v>Branch Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D110" t="str">
-        <v>Head Post Office, Purnahiya</v>
+        <v>03059</v>
       </c>
       <c r="E110" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>CDPO Office Piprahi No.1</v>
       </c>
       <c r="F110" t="str">
-        <v>9003000121</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G110" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000067</v>
       </c>
       <c r="H110" t="str">
-        <v>Purnahiya</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I110" t="str">
-        <v>Purnahiya</v>
+        <v>0302</v>
       </c>
       <c r="J110" t="str">
-        <v>30000958199</v>
+        <v>Piprahi</v>
       </c>
       <c r="K110" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L110" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M110" t="str">
-        <v>SBIN0004966</v>
+        <v>30000530573</v>
+      </c>
+      <c r="N110" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O110" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P110" t="str">
+        <v>SBIN0006480</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>0300057</v>
+        <v>0300053</v>
       </c>
       <c r="B111" t="str">
-        <v>ALOK PANDEY</v>
+        <v>MD. IRFAN OJHA</v>
       </c>
       <c r="C111" t="str">
-        <v>Teacher</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D111" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>03043</v>
       </c>
       <c r="E111" t="str">
+        <v>Block Agriculture Office Sheohar</v>
+      </c>
+      <c r="F111" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
-      <c r="F111" t="str">
-        <v>9003000057</v>
-      </c>
       <c r="G111" t="str">
+        <v>9003000053</v>
+      </c>
+      <c r="H111" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
-      <c r="H111" t="str">
-        <v>Dumri Katsari</v>
-      </c>
       <c r="I111" t="str">
-        <v>Sheohar</v>
+        <v>0301</v>
       </c>
       <c r="J111" t="str">
-        <v>30000451383</v>
+        <v>Sheohar</v>
       </c>
       <c r="K111" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L111" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M111" t="str">
-        <v>SBIN0009298</v>
+        <v>30000419707</v>
+      </c>
+      <c r="N111" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O111" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P111" t="str">
+        <v>SBIN0001742</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>0300066</v>
+        <v>0300125</v>
       </c>
       <c r="B112" t="str">
-        <v>DINESH JHA</v>
+        <v>ARVIND SAH K</v>
       </c>
       <c r="C112" t="str">
-        <v>Clerk</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D112" t="str">
-        <v>Circle Office Tariyani No.3</v>
+        <v>03095</v>
       </c>
       <c r="E112" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>UCO Bank, Purnahiya</v>
       </c>
       <c r="F112" t="str">
-        <v>9003000066</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G112" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000125</v>
       </c>
       <c r="H112" t="str">
-        <v>Tariyani</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I112" t="str">
-        <v>Tariyani</v>
+        <v>0303</v>
       </c>
       <c r="J112" t="str">
-        <v>30000522654</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K112" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L112" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M112" t="str">
-        <v>SBIN0001789</v>
+        <v>30000989875</v>
+      </c>
+      <c r="N112" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O112" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P112" t="str">
+        <v>SBIN0002687</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>0300120</v>
+        <v>0300080</v>
       </c>
       <c r="B113" t="str">
-        <v>SANTOSH SAH A</v>
+        <v>SANJAY PANDEY</v>
       </c>
       <c r="C113" t="str">
-        <v>Postmaster</v>
+        <v>Teacher</v>
       </c>
       <c r="D113" t="str">
-        <v>BSNL Exchange, Piprahi</v>
+        <v>03067</v>
       </c>
       <c r="E113" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Block Office Sheohar No.1</v>
       </c>
       <c r="F113" t="str">
-        <v>9003000120</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G113" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000080</v>
       </c>
       <c r="H113" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I113" t="str">
-        <v>Piprahi</v>
+        <v>0304</v>
       </c>
       <c r="J113" t="str">
-        <v>30000950280</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K113" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L113" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M113" t="str">
-        <v>SBIN0005018</v>
+        <v>30000633520</v>
+      </c>
+      <c r="N113" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O113" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P113" t="str">
+        <v>SBIN0006100</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>0300065</v>
+        <v>0300062</v>
       </c>
       <c r="B114" t="str">
-        <v>PRAMOD JHA</v>
+        <v>NASREEN PRASAD</v>
       </c>
       <c r="C114" t="str">
-        <v>Office Assistant</v>
+        <v>Accountant</v>
       </c>
       <c r="D114" t="str">
-        <v>Circle Office Dumri Katsari No.3</v>
+        <v>03054</v>
       </c>
       <c r="E114" t="str">
+        <v>Kanya Middle School Dumri Katsari No.4</v>
+      </c>
+      <c r="F114" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
-      <c r="F114" t="str">
-        <v>9003000065</v>
-      </c>
       <c r="G114" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000062</v>
       </c>
       <c r="H114" t="str">
+        <v>POLLING OFFICER-2</v>
+      </c>
+      <c r="I114" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J114" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I114" t="str">
+      <c r="K114" t="str">
+        <v>0304</v>
+      </c>
+      <c r="L114" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="J114" t="str">
-        <v>30000514735</v>
-      </c>
-      <c r="K114" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L114" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M114" t="str">
-        <v>SBIN0003689</v>
+        <v>30000490978</v>
+      </c>
+      <c r="N114" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O114" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P114" t="str">
+        <v>SBIN0007867</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>0300025</v>
+        <v>0300064</v>
       </c>
       <c r="B115" t="str">
-        <v>MUKESH ALAM</v>
+        <v>NIRMALA ALAM</v>
       </c>
       <c r="C115" t="str">
-        <v>Head Clerk</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D115" t="str">
-        <v>Primary School Tariyani No.3</v>
+        <v>03056</v>
       </c>
       <c r="E115" t="str">
+        <v>Block Agriculture Office Tariyani No.1</v>
+      </c>
+      <c r="F115" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
-      <c r="F115" t="str">
-        <v>9003000025</v>
-      </c>
       <c r="G115" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000064</v>
       </c>
       <c r="H115" t="str">
+        <v>POLLING OFFICER-3</v>
+      </c>
+      <c r="I115" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J115" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="I115" t="str">
+      <c r="K115" t="str">
+        <v>0305</v>
+      </c>
+      <c r="L115" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="J115" t="str">
-        <v>30000197975</v>
-      </c>
-      <c r="K115" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L115" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M115" t="str">
-        <v>SBIN0008563</v>
+        <v>30000506816</v>
+      </c>
+      <c r="N115" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O115" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P115" t="str">
+        <v>SBIN0007820</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>0300051</v>
+        <v>0300091</v>
       </c>
       <c r="B116" t="str">
-        <v>ABDUL KALAM MAHTO</v>
+        <v>RAKESH KHATUN</v>
       </c>
       <c r="C116" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D116" t="str">
-        <v>CDPO Office Dumri Katsari</v>
+        <v>03074</v>
       </c>
       <c r="E116" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="F116" t="str">
-        <v>9003000051</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G116" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000091</v>
       </c>
       <c r="H116" t="str">
-        <v>Dumri Katsari</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I116" t="str">
-        <v>Dumri Katsari</v>
+        <v>0302</v>
       </c>
       <c r="J116" t="str">
-        <v>30000403869</v>
+        <v>Piprahi</v>
       </c>
       <c r="K116" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L116" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M116" t="str">
-        <v>SBIN0008125</v>
+        <v>30000720629</v>
+      </c>
+      <c r="N116" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O116" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P116" t="str">
+        <v>SBIN0004144</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>0300094</v>
+        <v>0300014</v>
       </c>
       <c r="B117" t="str">
-        <v>ALOK ANSARI</v>
+        <v>NEHA PRASAD</v>
       </c>
       <c r="C117" t="str">
-        <v>Junior Engineer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D117" t="str">
-        <v>Minor Irrigation Office Dumri Katsari</v>
+        <v>03014</v>
       </c>
       <c r="E117" t="str">
+        <v>Block Office Dumri Katsari No.4</v>
+      </c>
+      <c r="F117" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
-      <c r="F117" t="str">
-        <v>9003000094</v>
-      </c>
       <c r="G117" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>9003000014</v>
       </c>
       <c r="H117" t="str">
+        <v>PRESIDING OFFICER</v>
+      </c>
+      <c r="I117" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J117" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I117" t="str">
+      <c r="K117" t="str">
+        <v>0304</v>
+      </c>
+      <c r="L117" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="J117" t="str">
-        <v>30000744386</v>
-      </c>
-      <c r="K117" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L117" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M117" t="str">
-        <v>SBIN0008102</v>
+        <v>30000110866</v>
+      </c>
+      <c r="N117" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O117" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P117" t="str">
+        <v>SBIN0004424</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>0300033</v>
+        <v>0300038</v>
       </c>
       <c r="B118" t="str">
-        <v>MAMTA PASWAN</v>
+        <v>MD. SHAHID VERMA</v>
       </c>
       <c r="C118" t="str">
-        <v>Senior Clerk</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D118" t="str">
-        <v>Project Girls High School Sheohar No.1</v>
+        <v>03030</v>
       </c>
       <c r="E118" t="str">
+        <v>Civil Surgeon Office Sheohar</v>
+      </c>
+      <c r="F118" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
-      <c r="F118" t="str">
-        <v>9003000033</v>
-      </c>
       <c r="G118" t="str">
+        <v>9003000038</v>
+      </c>
+      <c r="H118" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
-      <c r="H118" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="I118" t="str">
-        <v>Sheohar</v>
+        <v>0303</v>
       </c>
       <c r="J118" t="str">
-        <v>30000261327</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K118" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L118" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M118" t="str">
-        <v>SBIN0009329</v>
+        <v>30000300922</v>
+      </c>
+      <c r="N118" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O118" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P118" t="str">
+        <v>SBIN0004403</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>0300108</v>
+        <v>0300073</v>
       </c>
       <c r="B119" t="str">
-        <v>PANKAJ TIWARI</v>
+        <v>VINOD YADAV</v>
       </c>
       <c r="C119" t="str">
-        <v>Assistant Manager</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D119" t="str">
-        <v>LIC Branch Office, Dumri Katsari</v>
+        <v>03018</v>
       </c>
       <c r="E119" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>High School Tariyani No.2</v>
       </c>
       <c r="F119" t="str">
-        <v>9003000108</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G119" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>9003000073</v>
       </c>
       <c r="H119" t="str">
-        <v>Piprahi</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I119" t="str">
-        <v>Dumri Katsari</v>
+        <v>0305</v>
       </c>
       <c r="J119" t="str">
-        <v>30000855252</v>
+        <v>Tariyani</v>
       </c>
       <c r="K119" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L119" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M119" t="str">
-        <v>SBIN0005277</v>
+        <v>30000578087</v>
+      </c>
+      <c r="N119" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O119" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P119" t="str">
+        <v>SBIN0001831</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>0300006</v>
+        <v>0300119</v>
       </c>
       <c r="B120" t="str">
-        <v>SANJAY JHA</v>
+        <v>SANTOSH DEVI</v>
       </c>
       <c r="C120" t="str">
-        <v>Lecturer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D120" t="str">
-        <v>Block Agriculture Office Tariyani No.2</v>
+        <v>03083</v>
       </c>
       <c r="E120" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>LIC Branch Office, Dumri Katsari</v>
       </c>
       <c r="F120" t="str">
-        <v>9003000006</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G120" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>9003000119</v>
       </c>
       <c r="H120" t="str">
+        <v>MICRO OBSERVER</v>
+      </c>
+      <c r="I120" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J120" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K120" t="str">
+        <v>0304</v>
+      </c>
+      <c r="L120" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="I120" t="str">
-        <v>Tariyani</v>
-      </c>
-      <c r="J120" t="str">
-        <v>30000047514</v>
-      </c>
-      <c r="K120" t="str">
-        <v>State Bank of India</v>
-      </c>
-      <c r="L120" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M120" t="str">
-        <v>SBIN0002829</v>
+        <v>30000942361</v>
+      </c>
+      <c r="N120" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O120" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P120" t="str">
+        <v>SBIN0006114</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>0300040</v>
+        <v>0300099</v>
       </c>
       <c r="B121" t="str">
-        <v>RANJIT SINGH</v>
+        <v>DINESH MAHTO</v>
       </c>
       <c r="C121" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D121" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>03007</v>
       </c>
       <c r="E121" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F121" t="str">
-        <v>9003000040</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G121" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000099</v>
       </c>
       <c r="H121" t="str">
-        <v>Purnahiya</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I121" t="str">
-        <v>Sheohar</v>
+        <v>0302</v>
       </c>
       <c r="J121" t="str">
-        <v>30000316760</v>
+        <v>Piprahi</v>
       </c>
       <c r="K121" t="str">
-        <v>State Bank of India</v>
+        <v>0302</v>
       </c>
       <c r="L121" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M121" t="str">
-        <v>SBIN0007965</v>
+        <v>30000783981</v>
+      </c>
+      <c r="N121" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O121" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P121" t="str">
+        <v>SBIN0001517</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>0300023</v>
+        <v>0300082</v>
       </c>
       <c r="B122" t="str">
-        <v>FARHAT MISHRA</v>
+        <v>REKHA CHAUDHARY</v>
       </c>
       <c r="C122" t="str">
-        <v>Assistant Teacher</v>
+        <v>Teacher</v>
       </c>
       <c r="D122" t="str">
-        <v>Block Office Tariyani No.4</v>
+        <v>03069</v>
       </c>
       <c r="E122" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>High School Purnahiya No.4</v>
       </c>
       <c r="F122" t="str">
-        <v>9003000023</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G122" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>9003000082</v>
       </c>
       <c r="H122" t="str">
-        <v>Tariyani</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I122" t="str">
-        <v>Tariyani</v>
+        <v>0303</v>
       </c>
       <c r="J122" t="str">
-        <v>30000182137</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K122" t="str">
-        <v>State Bank of India</v>
+        <v>0303</v>
       </c>
       <c r="L122" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M122" t="str">
-        <v>SBIN0009788</v>
+        <v>30000649358</v>
+      </c>
+      <c r="N122" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O122" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P122" t="str">
+        <v>SBIN0005400</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>0300046</v>
+        <v>0300069</v>
       </c>
       <c r="B123" t="str">
-        <v>SANJAY GUPTA</v>
+        <v>SUNIL PASWAN</v>
       </c>
       <c r="C123" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D123" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>03061</v>
       </c>
       <c r="E123" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Block Education Office Sheohar No.1</v>
       </c>
       <c r="F123" t="str">
-        <v>9003000046</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G123" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000069</v>
       </c>
       <c r="H123" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I123" t="str">
-        <v>Tariyani</v>
+        <v>0301</v>
       </c>
       <c r="J123" t="str">
-        <v>30000364274</v>
+        <v>Sheohar</v>
       </c>
       <c r="K123" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L123" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M123" t="str">
-        <v>SBIN0007894</v>
+        <v>30000546411</v>
+      </c>
+      <c r="N123" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O123" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P123" t="str">
+        <v>SBIN0007734</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>0300056</v>
+        <v>0300052</v>
       </c>
       <c r="B124" t="str">
-        <v>RAKESH OJHA</v>
+        <v>NITISH JHA</v>
       </c>
       <c r="C124" t="str">
-        <v>Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D124" t="str">
-        <v>Middle School Tariyani</v>
+        <v>03039</v>
       </c>
       <c r="E124" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F124" t="str">
-        <v>9003000056</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G124" t="str">
+        <v>9003000052</v>
+      </c>
+      <c r="H124" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
-      <c r="H124" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="I124" t="str">
-        <v>Tariyani</v>
+        <v>0301</v>
       </c>
       <c r="J124" t="str">
-        <v>30000443464</v>
+        <v>Sheohar</v>
       </c>
       <c r="K124" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L124" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M124" t="str">
-        <v>SBIN0004651</v>
+        <v>30000411788</v>
+      </c>
+      <c r="N124" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O124" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P124" t="str">
+        <v>SBIN0006306</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>0300080</v>
+        <v>0300055</v>
       </c>
       <c r="B125" t="str">
-        <v>USHA KHATUN</v>
+        <v>REKHA KHATUN</v>
       </c>
       <c r="C125" t="str">
-        <v>Office Assistant</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D125" t="str">
-        <v>PHC Dumri Katsari No.2</v>
+        <v>03048</v>
       </c>
       <c r="E125" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>District Treasury Sheohar</v>
       </c>
       <c r="F125" t="str">
-        <v>9003000080</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G125" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>9003000055</v>
       </c>
       <c r="H125" t="str">
-        <v>Sheohar</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I125" t="str">
-        <v>Dumri Katsari</v>
+        <v>0301</v>
       </c>
       <c r="J125" t="str">
-        <v>30000633520</v>
+        <v>Sheohar</v>
       </c>
       <c r="K125" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L125" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M125" t="str">
-        <v>SBIN0008257</v>
+        <v>30000435545</v>
+      </c>
+      <c r="N125" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O125" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P125" t="str">
+        <v>SBIN0002875</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>0300062</v>
+        <v>0300008</v>
       </c>
       <c r="B126" t="str">
-        <v>UMESH KHATUN</v>
+        <v>RAMESH TIWARI</v>
       </c>
       <c r="C126" t="str">
-        <v>Clerk</v>
+        <v>Headmaster</v>
       </c>
       <c r="D126" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>03008</v>
       </c>
       <c r="E126" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="F126" t="str">
-        <v>9003000062</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G126" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>9003000008</v>
       </c>
       <c r="H126" t="str">
-        <v>Sheohar</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I126" t="str">
-        <v>Sheohar</v>
+        <v>0305</v>
       </c>
       <c r="J126" t="str">
-        <v>30000490978</v>
+        <v>Tariyani</v>
       </c>
       <c r="K126" t="str">
-        <v>State Bank of India</v>
+        <v>0305</v>
       </c>
       <c r="L126" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M126" t="str">
-        <v>SBIN0003088</v>
+        <v>30000063352</v>
+      </c>
+      <c r="N126" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O126" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P126" t="str">
+        <v>SBIN0009950</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>0300086</v>
+        <v>0300105</v>
       </c>
       <c r="B127" t="str">
-        <v>DINESH SINHA</v>
+        <v>SURESH RAI</v>
       </c>
       <c r="C127" t="str">
-        <v>Revenue Officer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D127" t="str">
-        <v>Block Office Tariyani</v>
+        <v>03071</v>
       </c>
       <c r="E127" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>RWD Sub-Division Sheohar</v>
       </c>
       <c r="F127" t="str">
-        <v>9003000086</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G127" t="str">
+        <v>9003000105</v>
+      </c>
+      <c r="H127" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
-      <c r="H127" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="I127" t="str">
-        <v>Tariyani</v>
+        <v>0301</v>
       </c>
       <c r="J127" t="str">
-        <v>30000681034</v>
+        <v>Sheohar</v>
       </c>
       <c r="K127" t="str">
-        <v>State Bank of India</v>
+        <v>0301</v>
       </c>
       <c r="L127" t="str">
         <v>Sheohar</v>
       </c>
       <c r="M127" t="str">
-        <v>SBIN0006393</v>
+        <v>30000831495</v>
+      </c>
+      <c r="N127" t="str">
+        <v>State Bank of India</v>
+      </c>
+      <c r="O127" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="P127" t="str">
+        <v>SBIN0001809</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M127"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P127"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="44.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6731,6 +7878,9 @@
         <v>Location / Building</v>
       </c>
       <c r="E1" t="str">
+        <v>Block Code</v>
+      </c>
+      <c r="F1" t="str">
         <v>Block</v>
       </c>
     </row>
@@ -6748,6 +7898,9 @@
         <v>Middle School Sheohar, Room 2</v>
       </c>
       <c r="E2" t="str">
+        <v>0301</v>
+      </c>
+      <c r="F2" t="str">
         <v>Sheohar</v>
       </c>
     </row>
@@ -6765,6 +7918,9 @@
         <v>High School Piprahi, Room 3</v>
       </c>
       <c r="E3" t="str">
+        <v>0302</v>
+      </c>
+      <c r="F3" t="str">
         <v>Piprahi</v>
       </c>
     </row>
@@ -6779,9 +7935,12 @@
         <v>Main</v>
       </c>
       <c r="D4" t="str">
-        <v>High School Purnahiya, Room 1</v>
+        <v>Kanya Middle School Purnahiya, Room 1</v>
       </c>
       <c r="E4" t="str">
+        <v>0303</v>
+      </c>
+      <c r="F4" t="str">
         <v>Purnahiya</v>
       </c>
     </row>
@@ -6796,9 +7955,12 @@
         <v>Main</v>
       </c>
       <c r="D5" t="str">
-        <v>Middle School Dumri Katsari, Room 2</v>
+        <v>Kanya Middle School Dumri Katsari, Room 2</v>
       </c>
       <c r="E5" t="str">
+        <v>0304</v>
+      </c>
+      <c r="F5" t="str">
         <v>Dumri Katsari</v>
       </c>
     </row>
@@ -6813,9 +7975,12 @@
         <v>Main</v>
       </c>
       <c r="D6" t="str">
-        <v>Panchayat Bhawan Tariyani, Room 3</v>
+        <v>High School Tariyani, Room 3</v>
       </c>
       <c r="E6" t="str">
+        <v>0305</v>
+      </c>
+      <c r="F6" t="str">
         <v>Tariyani</v>
       </c>
     </row>
@@ -6830,9 +7995,12 @@
         <v>Main</v>
       </c>
       <c r="D7" t="str">
-        <v>Middle School Sheohar, Room 1</v>
+        <v>Block Office Hall Sheohar, Room 1</v>
       </c>
       <c r="E7" t="str">
+        <v>0301</v>
+      </c>
+      <c r="F7" t="str">
         <v>Sheohar</v>
       </c>
     </row>
@@ -6847,9 +8015,12 @@
         <v>Main</v>
       </c>
       <c r="D8" t="str">
-        <v>Middle School Purnahiya, Room 2</v>
+        <v>Block Office Hall Purnahiya, Room 2</v>
       </c>
       <c r="E8" t="str">
+        <v>0303</v>
+      </c>
+      <c r="F8" t="str">
         <v>Purnahiya</v>
       </c>
     </row>
@@ -6867,6 +8038,9 @@
         <v>Panchayat Bhawan Dumri Katsari, Room 3</v>
       </c>
       <c r="E9" t="str">
+        <v>0304</v>
+      </c>
+      <c r="F9" t="str">
         <v>Dumri Katsari</v>
       </c>
     </row>
@@ -6881,9 +8055,12 @@
         <v>Main</v>
       </c>
       <c r="D10" t="str">
-        <v>High School Tariyani, Room 1</v>
+        <v>Kanya Middle School Tariyani, Room 1</v>
       </c>
       <c r="E10" t="str">
+        <v>0305</v>
+      </c>
+      <c r="F10" t="str">
         <v>Tariyani</v>
       </c>
     </row>
@@ -6901,6 +8078,9 @@
         <v>High School Sheohar, Room 2</v>
       </c>
       <c r="E11" t="str">
+        <v>0301</v>
+      </c>
+      <c r="F11" t="str">
         <v>Sheohar</v>
       </c>
     </row>
@@ -6915,9 +8095,12 @@
         <v>Main</v>
       </c>
       <c r="D12" t="str">
-        <v>High School Piprahi, Room 3</v>
+        <v>Middle School Piprahi, Room 3</v>
       </c>
       <c r="E12" t="str">
+        <v>0302</v>
+      </c>
+      <c r="F12" t="str">
         <v>Piprahi</v>
       </c>
     </row>
@@ -6932,15 +8115,18 @@
         <v>Main</v>
       </c>
       <c r="D13" t="str">
-        <v>Panchayat Bhawan Purnahiya, Room 1</v>
+        <v>Block Office Hall Purnahiya, Room 1</v>
       </c>
       <c r="E13" t="str">
+        <v>0303</v>
+      </c>
+      <c r="F13" t="str">
         <v>Purnahiya</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/test-data/TEST_Sheohar_Project.xlsx
+++ b/test-data/TEST_Sheohar_Project.xlsx
@@ -612,7 +612,7 @@
         <v>Saved at</v>
       </c>
       <c r="B4" t="str">
-        <v>13-10-2026 03:46:43</v>
+        <v>13-10-2026 06:03:26</v>
       </c>
     </row>
     <row r="5">
@@ -744,7 +744,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>13-10-2026 03:46:43</v>
+        <v>13-10-2026 06:03:26</v>
       </c>
       <c r="B2" t="str">
         <v>Test data generated (Small — Sheohar style (5 blocks, 6 TC + 6 GC booths))</v>
@@ -759,7 +759,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -1008,9 +1008,20 @@
         <v>No</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>outsideMarkers</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Out-of-district block markers (codes / names, comma separated)</v>
+      </c>
+      <c r="C23" t="str">
+        <v>999, 9999, 99999, 999999, OTHERS, OTHER, OUT OF DISTRICT, OUTSIDE DISTRICT, OTHER DISTRICT</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1547,34 +1558,34 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0300015</v>
+        <v>0300086</v>
       </c>
       <c r="B2" t="str">
-        <v>KUMARI ANJALI ANSARI</v>
+        <v>ANIL ANSARI</v>
       </c>
       <c r="C2" t="str">
-        <v>Lecturer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D2" t="str">
-        <v>03015</v>
+        <v>03069</v>
       </c>
       <c r="E2" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>Minor Irrigation Office Sheohar</v>
       </c>
       <c r="F2" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G2" t="str">
-        <v>9003000015</v>
+        <v>9003000086</v>
       </c>
       <c r="H2" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I2" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J2" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K2" t="str">
         <v>0301</v>
@@ -1583,7 +1594,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M2" t="str">
-        <v>30000118785</v>
+        <v>30000681034</v>
       </c>
       <c r="N2" t="str">
         <v>State Bank of India</v>
@@ -1592,33 +1603,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P2" t="str">
-        <v>SBIN0008705</v>
+        <v>SBIN0007358</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0300059</v>
+        <v>0300119</v>
       </c>
       <c r="B3" t="str">
-        <v>RAVI TIWARI</v>
+        <v>UMESH THAKUR</v>
       </c>
       <c r="C3" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Postmaster</v>
       </c>
       <c r="D3" t="str">
-        <v>03030</v>
+        <v>03090</v>
       </c>
       <c r="E3" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Punjab National Bank, Piprahi</v>
       </c>
       <c r="F3" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G3" t="str">
-        <v>9003000059</v>
+        <v>9003000119</v>
       </c>
       <c r="H3" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I3" t="str">
         <v>0301</v>
@@ -1627,13 +1638,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K3" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L3" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M3" t="str">
-        <v>30000467221</v>
+        <v>30000942361</v>
       </c>
       <c r="N3" t="str">
         <v>State Bank of India</v>
@@ -1642,48 +1653,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P3" t="str">
-        <v>SBIN0002974</v>
+        <v>SBIN0003269</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0300098</v>
+        <v>0300023</v>
       </c>
       <c r="B4" t="str">
-        <v>RANJIT OJHA</v>
+        <v>FARHAT MAHTO</v>
       </c>
       <c r="C4" t="str">
-        <v>Assistant Engineer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D4" t="str">
-        <v>03075</v>
+        <v>03022</v>
       </c>
       <c r="E4" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F4" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G4" t="str">
-        <v>9003000098</v>
+        <v>9003000023</v>
       </c>
       <c r="H4" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I4" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J4" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K4" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L4" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M4" t="str">
-        <v>30000776062</v>
+        <v>30000182137</v>
       </c>
       <c r="N4" t="str">
         <v>State Bank of India</v>
@@ -1692,39 +1703,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P4" t="str">
-        <v>SBIN0006530</v>
+        <v>SBIN0008583</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0300023</v>
+        <v>0300043</v>
       </c>
       <c r="B5" t="str">
-        <v>POONAM MAHTO</v>
+        <v>VIJAY SINHA</v>
       </c>
       <c r="C5" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Clerk</v>
       </c>
       <c r="D5" t="str">
-        <v>03021</v>
+        <v>03036</v>
       </c>
       <c r="E5" t="str">
-        <v>Middle School Dumri Katsari No.2</v>
+        <v>Block Office Dumri Katsari No.2</v>
       </c>
       <c r="F5" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G5" t="str">
-        <v>9003000023</v>
+        <v>9003000043</v>
       </c>
       <c r="H5" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I5" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J5" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K5" t="str">
         <v>0304</v>
@@ -1733,7 +1744,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M5" t="str">
-        <v>30000182137</v>
+        <v>30000340517</v>
       </c>
       <c r="N5" t="str">
         <v>State Bank of India</v>
@@ -1742,33 +1753,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P5" t="str">
-        <v>SBIN0001260</v>
+        <v>SBIN0008107</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0300037</v>
+        <v>0300104</v>
       </c>
       <c r="B6" t="str">
-        <v>SHAILESH OJHA</v>
+        <v>SHAILESH THAKUR</v>
       </c>
       <c r="C6" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D6" t="str">
-        <v>03034</v>
+        <v>03079</v>
       </c>
       <c r="E6" t="str">
-        <v>Circle Office Purnahiya No.1</v>
+        <v>Minor Irrigation Office Tariyani</v>
       </c>
       <c r="F6" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G6" t="str">
-        <v>9003000037</v>
+        <v>9003000104</v>
       </c>
       <c r="H6" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I6" t="str">
         <v>0305</v>
@@ -1777,13 +1788,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K6" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L6" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M6" t="str">
-        <v>30000293003</v>
+        <v>30000823576</v>
       </c>
       <c r="N6" t="str">
         <v>State Bank of India</v>
@@ -1792,39 +1803,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P6" t="str">
-        <v>SBIN0009950</v>
+        <v>SBIN0004649</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>0300090</v>
+        <v>0300096</v>
       </c>
       <c r="B7" t="str">
-        <v>SANTOSH SINGH</v>
+        <v>MAMTA RAI</v>
       </c>
       <c r="C7" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D7" t="str">
-        <v>03073</v>
+        <v>03054</v>
       </c>
       <c r="E7" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F7" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G7" t="str">
-        <v>9003000090</v>
+        <v>9003000096</v>
       </c>
       <c r="H7" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I7" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J7" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K7" t="str">
         <v>0303</v>
@@ -1833,7 +1844,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M7" t="str">
-        <v>30000712710</v>
+        <v>30000760224</v>
       </c>
       <c r="N7" t="str">
         <v>State Bank of India</v>
@@ -1842,39 +1853,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P7" t="str">
-        <v>SBIN0007281</v>
+        <v>SBIN0004089</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0300028</v>
+        <v>0300049</v>
       </c>
       <c r="B8" t="str">
-        <v>UMESH ANSARI</v>
+        <v>MUKESH SINHA</v>
       </c>
       <c r="C8" t="str">
-        <v>Senior Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D8" t="str">
-        <v>03026</v>
+        <v>03041</v>
       </c>
       <c r="E8" t="str">
-        <v>Kanya Middle School Purnahiya No.1</v>
+        <v>High School Purnahiya</v>
       </c>
       <c r="F8" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G8" t="str">
-        <v>9003000028</v>
+        <v>9003000049</v>
       </c>
       <c r="H8" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I8" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J8" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K8" t="str">
         <v>0303</v>
@@ -1883,7 +1894,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M8" t="str">
-        <v>30000221732</v>
+        <v>30000388031</v>
       </c>
       <c r="N8" t="str">
         <v>State Bank of India</v>
@@ -1892,33 +1903,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P8" t="str">
-        <v>SBIN0004029</v>
+        <v>SBIN0002615</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0300043</v>
+        <v>0300100</v>
       </c>
       <c r="B9" t="str">
-        <v>KIRAN JHA</v>
+        <v>DEEPAK RAI</v>
       </c>
       <c r="C9" t="str">
-        <v>Clerk</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D9" t="str">
-        <v>03008</v>
+        <v>03069</v>
       </c>
       <c r="E9" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>Minor Irrigation Office Sheohar</v>
       </c>
       <c r="F9" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G9" t="str">
-        <v>9003000043</v>
+        <v>9003000100</v>
       </c>
       <c r="H9" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I9" t="str">
         <v>0301</v>
@@ -1927,13 +1938,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K9" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L9" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M9" t="str">
-        <v>30000340517</v>
+        <v>30000791900</v>
       </c>
       <c r="N9" t="str">
         <v>State Bank of India</v>
@@ -1942,30 +1953,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P9" t="str">
-        <v>SBIN0005994</v>
+        <v>SBIN0003306</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0300030</v>
+        <v>0300024</v>
       </c>
       <c r="B10" t="str">
-        <v>ASHA CHAUDHARY</v>
+        <v>MD. SHAHID SINGH</v>
       </c>
       <c r="C10" t="str">
         <v>Panchayat Secretary</v>
       </c>
       <c r="D10" t="str">
-        <v>03028</v>
+        <v>03023</v>
       </c>
       <c r="E10" t="str">
-        <v>Primary School Purnahiya No.2</v>
+        <v>PHC Purnahiya No.4</v>
       </c>
       <c r="F10" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G10" t="str">
-        <v>9003000030</v>
+        <v>9003000024</v>
       </c>
       <c r="H10" t="str">
         <v>POLLING OFFICER-1</v>
@@ -1983,7 +1994,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M10" t="str">
-        <v>30000237570</v>
+        <v>30000190056</v>
       </c>
       <c r="N10" t="str">
         <v>State Bank of India</v>
@@ -1992,48 +2003,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P10" t="str">
-        <v>SBIN0007418</v>
+        <v>SBIN0002071</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>0300041</v>
+        <v>0300021</v>
       </c>
       <c r="B11" t="str">
-        <v>PANKAJ SAH</v>
+        <v>NITISH CHAUDHARY</v>
       </c>
       <c r="C11" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Section Officer</v>
       </c>
       <c r="D11" t="str">
-        <v>03037</v>
+        <v>03021</v>
       </c>
       <c r="E11" t="str">
-        <v>Block Agriculture Office Sheohar No.4</v>
+        <v>High School Tariyani No.4</v>
       </c>
       <c r="F11" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G11" t="str">
-        <v>9003000041</v>
+        <v>9003000021</v>
       </c>
       <c r="H11" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I11" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J11" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K11" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L11" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M11" t="str">
-        <v>30000324679</v>
+        <v>30000166299</v>
       </c>
       <c r="N11" t="str">
         <v>State Bank of India</v>
@@ -2042,48 +2053,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P11" t="str">
-        <v>SBIN0003169</v>
+        <v>SBIN0007720</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>0300009</v>
+        <v>0300069</v>
       </c>
       <c r="B12" t="str">
-        <v>FARHAT TIWARI</v>
+        <v>MD. IRFAN YADAV</v>
       </c>
       <c r="C12" t="str">
-        <v>Senior Teacher</v>
+        <v>Teacher</v>
       </c>
       <c r="D12" t="str">
-        <v>03009</v>
+        <v>03056</v>
       </c>
       <c r="E12" t="str">
-        <v>Panchayat Bhawan Purnahiya</v>
+        <v>PHC Dumri Katsari No.3</v>
       </c>
       <c r="F12" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G12" t="str">
-        <v>9003000009</v>
+        <v>9003000069</v>
       </c>
       <c r="H12" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I12" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J12" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K12" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L12" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M12" t="str">
-        <v>30000071271</v>
+        <v>30000546411</v>
       </c>
       <c r="N12" t="str">
         <v>State Bank of India</v>
@@ -2092,48 +2103,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P12" t="str">
-        <v>SBIN0008642</v>
+        <v>SBIN0002247</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0300096</v>
+        <v>0300025</v>
       </c>
       <c r="B13" t="str">
-        <v>UMESH MAHTO</v>
+        <v>NEHA YADAV</v>
       </c>
       <c r="C13" t="str">
-        <v>Assistant Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D13" t="str">
-        <v>03073</v>
+        <v>03024</v>
       </c>
       <c r="E13" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>RWD Division (deputed from other district)</v>
       </c>
       <c r="F13" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G13" t="str">
-        <v>9003000096</v>
+        <v>9003000025</v>
       </c>
       <c r="H13" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I13" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J13" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K13" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="L13" t="str">
-        <v>Purnahiya</v>
+        <v>Other District</v>
       </c>
       <c r="M13" t="str">
-        <v>30000760224</v>
+        <v>30000197975</v>
       </c>
       <c r="N13" t="str">
         <v>State Bank of India</v>
@@ -2142,48 +2153,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P13" t="str">
-        <v>SBIN0003751</v>
+        <v>SBIN0009253</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0300013</v>
+        <v>0300063</v>
       </c>
       <c r="B14" t="str">
-        <v>RINKU PASWAN</v>
+        <v>RAMESH MAHTO</v>
       </c>
       <c r="C14" t="str">
-        <v>Section Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D14" t="str">
-        <v>03013</v>
+        <v>03051</v>
       </c>
       <c r="E14" t="str">
-        <v>High School Dumri Katsari No.4</v>
+        <v>Block Education Office Piprahi</v>
       </c>
       <c r="F14" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G14" t="str">
-        <v>9003000013</v>
+        <v>9003000063</v>
       </c>
       <c r="H14" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I14" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J14" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K14" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L14" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M14" t="str">
-        <v>30000102947</v>
+        <v>30000498897</v>
       </c>
       <c r="N14" t="str">
         <v>State Bank of India</v>
@@ -2192,48 +2203,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P14" t="str">
-        <v>SBIN0002299</v>
+        <v>SBIN0003779</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>0300063</v>
+        <v>0300044</v>
       </c>
       <c r="B15" t="str">
-        <v>MAHESH SAH</v>
+        <v>DINESH PASWAN</v>
       </c>
       <c r="C15" t="str">
-        <v>Teacher</v>
+        <v>Accountant</v>
       </c>
       <c r="D15" t="str">
-        <v>03055</v>
+        <v>03037</v>
       </c>
       <c r="E15" t="str">
-        <v>CDPO Office Purnahiya No.1</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="F15" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G15" t="str">
-        <v>9003000063</v>
+        <v>9003000044</v>
       </c>
       <c r="H15" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I15" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J15" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K15" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L15" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M15" t="str">
-        <v>30000498897</v>
+        <v>30000348436</v>
       </c>
       <c r="N15" t="str">
         <v>State Bank of India</v>
@@ -2242,39 +2253,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P15" t="str">
-        <v>SBIN0001480</v>
+        <v>SBIN0004116</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>0300054</v>
+        <v>0300051</v>
       </c>
       <c r="B16" t="str">
-        <v>RAKESH OJHA</v>
+        <v>RANJIT PASWAN</v>
       </c>
       <c r="C16" t="str">
-        <v>Teacher</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D16" t="str">
-        <v>03047</v>
+        <v>03015</v>
       </c>
       <c r="E16" t="str">
-        <v>CDPO Office Purnahiya No.2</v>
+        <v>Block Agriculture Office Purnahiya No.2</v>
       </c>
       <c r="F16" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G16" t="str">
-        <v>9003000054</v>
+        <v>9003000051</v>
       </c>
       <c r="H16" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I16" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J16" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K16" t="str">
         <v>0303</v>
@@ -2283,7 +2294,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M16" t="str">
-        <v>30000427626</v>
+        <v>30000403869</v>
       </c>
       <c r="N16" t="str">
         <v>State Bank of India</v>
@@ -2292,48 +2303,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P16" t="str">
-        <v>SBIN0001078</v>
+        <v>SBIN0008534</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>0300046</v>
+        <v>0300065</v>
       </c>
       <c r="B17" t="str">
-        <v>ANITA RAM</v>
+        <v>SANTOSH MAHTO</v>
       </c>
       <c r="C17" t="str">
-        <v>Accountant</v>
+        <v>Teacher</v>
       </c>
       <c r="D17" t="str">
-        <v>03041</v>
+        <v>03052</v>
       </c>
       <c r="E17" t="str">
-        <v>Project Girls High School Tariyani No.3</v>
+        <v>Block Office Sheohar</v>
       </c>
       <c r="F17" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G17" t="str">
-        <v>9003000046</v>
+        <v>9003000065</v>
       </c>
       <c r="H17" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I17" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="K17" t="str">
         <v>0301</v>
       </c>
-      <c r="J17" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K17" t="str">
-        <v>0305</v>
-      </c>
       <c r="L17" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M17" t="str">
-        <v>30000364274</v>
+        <v>30000514735</v>
       </c>
       <c r="N17" t="str">
         <v>State Bank of India</v>
@@ -2342,48 +2353,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P17" t="str">
-        <v>SBIN0007655</v>
+        <v>SBIN0009592</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>0300075</v>
+        <v>0300062</v>
       </c>
       <c r="B18" t="str">
-        <v>MUKESH OJHA</v>
+        <v>ABDUL KALAM KUMAR</v>
       </c>
       <c r="C18" t="str">
-        <v>Teacher</v>
+        <v>Accountant</v>
       </c>
       <c r="D18" t="str">
-        <v>03063</v>
+        <v>03007</v>
       </c>
       <c r="E18" t="str">
-        <v>Block Office Tariyani No.1</v>
+        <v>Middle School Piprahi No.3</v>
       </c>
       <c r="F18" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G18" t="str">
-        <v>9003000075</v>
+        <v>9003000062</v>
       </c>
       <c r="H18" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I18" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J18" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K18" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L18" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M18" t="str">
-        <v>30000593925</v>
+        <v>30000490978</v>
       </c>
       <c r="N18" t="str">
         <v>State Bank of India</v>
@@ -2392,48 +2403,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P18" t="str">
-        <v>SBIN0002841</v>
+        <v>SBIN0002219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>0300019</v>
+        <v>0300076</v>
       </c>
       <c r="B19" t="str">
-        <v>VINOD MISHRA</v>
+        <v>KUMARI ANJALI ALAM</v>
       </c>
       <c r="C19" t="str">
-        <v>Headmaster</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D19" t="str">
-        <v>03017</v>
+        <v>03061</v>
       </c>
       <c r="E19" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F19" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G19" t="str">
-        <v>9003000019</v>
+        <v>9003000076</v>
       </c>
       <c r="H19" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I19" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J19" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K19" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L19" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M19" t="str">
-        <v>30000150461</v>
+        <v>30000601844</v>
       </c>
       <c r="N19" t="str">
         <v>State Bank of India</v>
@@ -2442,48 +2453,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P19" t="str">
-        <v>SBIN0009856</v>
+        <v>SBIN0008323</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>0300027</v>
+        <v>0300081</v>
       </c>
       <c r="B20" t="str">
-        <v>PANKAJ ALAM</v>
+        <v>KIRAN DEVI</v>
       </c>
       <c r="C20" t="str">
-        <v>Assistant Teacher</v>
+        <v>Teacher</v>
       </c>
       <c r="D20" t="str">
-        <v>03025</v>
+        <v>03049</v>
       </c>
       <c r="E20" t="str">
-        <v>Kanya Middle School Piprahi No.4</v>
+        <v>CDPO Office Sheohar No.2</v>
       </c>
       <c r="F20" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G20" t="str">
-        <v>9003000027</v>
+        <v>9003000081</v>
       </c>
       <c r="H20" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I20" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J20" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K20" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L20" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M20" t="str">
-        <v>30000213813</v>
+        <v>30000641439</v>
       </c>
       <c r="N20" t="str">
         <v>State Bank of India</v>
@@ -2492,48 +2503,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P20" t="str">
-        <v>SBIN0009455</v>
+        <v>SBIN0005602</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>0300086</v>
+        <v>0300010</v>
       </c>
       <c r="B21" t="str">
-        <v>AMIT MAHTO</v>
+        <v>SANJAY ALAM</v>
       </c>
       <c r="C21" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D21" t="str">
-        <v>03071</v>
+        <v>03010</v>
       </c>
       <c r="E21" t="str">
-        <v>RWD Sub-Division Sheohar</v>
+        <v>Block Office Tariyani No.2</v>
       </c>
       <c r="F21" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G21" t="str">
-        <v>9003000086</v>
+        <v>9003000010</v>
       </c>
       <c r="H21" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I21" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J21" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K21" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L21" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M21" t="str">
-        <v>30000681034</v>
+        <v>30000079190</v>
       </c>
       <c r="N21" t="str">
         <v>State Bank of India</v>
@@ -2542,48 +2553,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P21" t="str">
-        <v>SBIN0008061</v>
+        <v>SBIN0003802</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>0300084</v>
+        <v>0300099</v>
       </c>
       <c r="B22" t="str">
-        <v>SUNITA TIWARI</v>
+        <v>ASHA CHAUDHARY</v>
       </c>
       <c r="C22" t="str">
-        <v>Data Entry Operator</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D22" t="str">
-        <v>03070</v>
+        <v>03076</v>
       </c>
       <c r="E22" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="F22" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G22" t="str">
-        <v>9003000084</v>
+        <v>9003000099</v>
       </c>
       <c r="H22" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I22" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J22" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K22" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L22" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M22" t="str">
-        <v>30000665196</v>
+        <v>30000783981</v>
       </c>
       <c r="N22" t="str">
         <v>State Bank of India</v>
@@ -2592,33 +2603,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P22" t="str">
-        <v>SBIN0006735</v>
+        <v>SBIN0008599</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>0300021</v>
+        <v>0300027</v>
       </c>
       <c r="B23" t="str">
-        <v>MAMTA THAKUR</v>
+        <v>ASHA JHA</v>
       </c>
       <c r="C23" t="str">
-        <v>Senior Teacher</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D23" t="str">
-        <v>03019</v>
+        <v>03025</v>
       </c>
       <c r="E23" t="str">
-        <v>Primary School Piprahi No.1</v>
+        <v>Block Agriculture Office Sheohar No.3</v>
       </c>
       <c r="F23" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G23" t="str">
-        <v>9003000021</v>
+        <v>9003000027</v>
       </c>
       <c r="H23" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I23" t="str">
         <v>0302</v>
@@ -2627,13 +2638,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K23" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L23" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M23" t="str">
-        <v>30000166299</v>
+        <v>30000213813</v>
       </c>
       <c r="N23" t="str">
         <v>State Bank of India</v>
@@ -2642,33 +2653,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P23" t="str">
-        <v>SBIN0008175</v>
+        <v>SBIN0004551</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>0300056</v>
+        <v>0300083</v>
       </c>
       <c r="B24" t="str">
-        <v>PRIYANKA OJHA</v>
+        <v>MANOJ PANDEY</v>
       </c>
       <c r="C24" t="str">
         <v>Teacher</v>
       </c>
       <c r="D24" t="str">
-        <v>03049</v>
+        <v>03066</v>
       </c>
       <c r="E24" t="str">
-        <v>Circle Office Dumri Katsari No.4</v>
+        <v>PHC Dumri Katsari No.2</v>
       </c>
       <c r="F24" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G24" t="str">
-        <v>9003000056</v>
+        <v>9003000083</v>
       </c>
       <c r="H24" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I24" t="str">
         <v>0304</v>
@@ -2683,7 +2694,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M24" t="str">
-        <v>30000443464</v>
+        <v>30000657277</v>
       </c>
       <c r="N24" t="str">
         <v>State Bank of India</v>
@@ -2692,33 +2703,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P24" t="str">
-        <v>SBIN0002222</v>
+        <v>SBIN0008495</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0300058</v>
+        <v>0300111</v>
       </c>
       <c r="B25" t="str">
-        <v>SURESH VERMA</v>
+        <v>SAVITA RAM</v>
       </c>
       <c r="C25" t="str">
-        <v>Clerk</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D25" t="str">
-        <v>03051</v>
+        <v>03083</v>
       </c>
       <c r="E25" t="str">
-        <v>Kanya Middle School Tariyani No.1</v>
+        <v>Central Bank of India, Piprahi</v>
       </c>
       <c r="F25" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G25" t="str">
-        <v>9003000058</v>
+        <v>9003000111</v>
       </c>
       <c r="H25" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I25" t="str">
         <v>0303</v>
@@ -2727,13 +2738,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K25" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L25" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M25" t="str">
-        <v>30000459302</v>
+        <v>30000879009</v>
       </c>
       <c r="N25" t="str">
         <v>State Bank of India</v>
@@ -2742,33 +2753,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P25" t="str">
-        <v>SBIN0002339</v>
+        <v>SBIN0005781</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>0300111</v>
+        <v>0300011</v>
       </c>
       <c r="B26" t="str">
-        <v>MUKESH KUMAR</v>
+        <v>VINOD RAI</v>
       </c>
       <c r="C26" t="str">
-        <v>Postmaster</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D26" t="str">
-        <v>03083</v>
+        <v>03011</v>
       </c>
       <c r="E26" t="str">
-        <v>LIC Branch Office, Dumri Katsari</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="F26" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G26" t="str">
-        <v>9003000111</v>
+        <v>9003000011</v>
       </c>
       <c r="H26" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I26" t="str">
         <v>0305</v>
@@ -2777,13 +2788,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K26" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L26" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M26" t="str">
-        <v>30000879009</v>
+        <v>30000087109</v>
       </c>
       <c r="N26" t="str">
         <v>State Bank of India</v>
@@ -2792,48 +2803,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P26" t="str">
-        <v>SBIN0009657</v>
+        <v>SBIN0007107</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>0300089</v>
+        <v>0300035</v>
       </c>
       <c r="B27" t="str">
-        <v>SANJAY VERMA B</v>
+        <v>FARHAT PANDEY</v>
       </c>
       <c r="C27" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D27" t="str">
-        <v>03072</v>
+        <v>03033</v>
       </c>
       <c r="E27" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>Block Education Office Purnahiya No.2</v>
       </c>
       <c r="F27" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G27" t="str">
-        <v>9003000089</v>
+        <v>9003000035</v>
       </c>
       <c r="H27" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I27" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J27" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K27" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L27" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M27" t="str">
-        <v>30000704791</v>
+        <v>30000277165</v>
       </c>
       <c r="N27" t="str">
         <v>State Bank of India</v>
@@ -2842,39 +2853,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P27" t="str">
-        <v>SBIN0006075</v>
+        <v>SBIN0002270</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>0300109</v>
+        <v>0300125</v>
       </c>
       <c r="B28" t="str">
-        <v>PRAMOD TIWARI</v>
+        <v>RANJIT PASWAN J</v>
       </c>
       <c r="C28" t="str">
         <v>Postmaster</v>
       </c>
       <c r="D28" t="str">
-        <v>03080</v>
+        <v>03094</v>
       </c>
       <c r="E28" t="str">
-        <v>Bank of India, Dumri Katsari</v>
+        <v>LIC Branch Office, Dumri Katsari</v>
       </c>
       <c r="F28" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G28" t="str">
-        <v>9003000109</v>
+        <v>9003000125</v>
       </c>
       <c r="H28" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I28" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J28" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K28" t="str">
         <v>0304</v>
@@ -2883,7 +2894,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M28" t="str">
-        <v>30000863171</v>
+        <v>30000989875</v>
       </c>
       <c r="N28" t="str">
         <v>State Bank of India</v>
@@ -2892,48 +2903,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P28" t="str">
-        <v>SBIN0003444</v>
+        <v>SBIN0003229</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>0300007</v>
+        <v>0300071</v>
       </c>
       <c r="B29" t="str">
-        <v>MAHESH CHAUDHARY</v>
+        <v>DEEPAK OJHA</v>
       </c>
       <c r="C29" t="str">
-        <v>Assistant Engineer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D29" t="str">
-        <v>03007</v>
+        <v>03057</v>
       </c>
       <c r="E29" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Kanya Middle School Purnahiya No.4</v>
       </c>
       <c r="F29" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G29" t="str">
-        <v>9003000007</v>
+        <v>9003000071</v>
       </c>
       <c r="H29" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I29" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J29" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K29" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L29" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M29" t="str">
-        <v>30000055433</v>
+        <v>30000562249</v>
       </c>
       <c r="N29" t="str">
         <v>State Bank of India</v>
@@ -2942,39 +2953,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P29" t="str">
-        <v>SBIN0003056</v>
+        <v>SBIN0006297</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>0300025</v>
+        <v>0300004</v>
       </c>
       <c r="B30" t="str">
-        <v>USHA SAH</v>
+        <v>NITISH YADAV</v>
       </c>
       <c r="C30" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D30" t="str">
-        <v>03023</v>
+        <v>03004</v>
       </c>
       <c r="E30" t="str">
-        <v>High School Tariyani</v>
+        <v>Primary School Tariyani No.4</v>
       </c>
       <c r="F30" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G30" t="str">
-        <v>9003000025</v>
+        <v>9003000004</v>
       </c>
       <c r="H30" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I30" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J30" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K30" t="str">
         <v>0305</v>
@@ -2983,7 +2994,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M30" t="str">
-        <v>30000197975</v>
+        <v>30000031676</v>
       </c>
       <c r="N30" t="str">
         <v>State Bank of India</v>
@@ -2992,48 +3003,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P30" t="str">
-        <v>SBIN0009569</v>
+        <v>SBIN0002593</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>0300083</v>
+        <v>0300046</v>
       </c>
       <c r="B31" t="str">
-        <v>NEHA THAKUR</v>
+        <v>DEEPAK PASWAN X</v>
       </c>
       <c r="C31" t="str">
-        <v>Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D31" t="str">
-        <v>03017</v>
+        <v>03039</v>
       </c>
       <c r="E31" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Kanya Middle School Dumri Katsari</v>
       </c>
       <c r="F31" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G31" t="str">
-        <v>9003000083</v>
+        <v>9003000046</v>
       </c>
       <c r="H31" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I31" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J31" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K31" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L31" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M31" t="str">
-        <v>30000657277</v>
+        <v>30000364274</v>
       </c>
       <c r="N31" t="str">
         <v>State Bank of India</v>
@@ -3042,30 +3053,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P31" t="str">
-        <v>SBIN0007297</v>
+        <v>SBIN0003724</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>0300081</v>
+        <v>0300064</v>
       </c>
       <c r="B32" t="str">
-        <v>SANTOSH RAM</v>
+        <v>RAVI SINGH</v>
       </c>
       <c r="C32" t="str">
-        <v>Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D32" t="str">
-        <v>03068</v>
+        <v>03051</v>
       </c>
       <c r="E32" t="str">
-        <v>Panchayat Bhawan Piprahi</v>
+        <v>Block Education Office Piprahi</v>
       </c>
       <c r="F32" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G32" t="str">
-        <v>9003000081</v>
+        <v>9003000064</v>
       </c>
       <c r="H32" t="str">
         <v>POLLING OFFICER-3</v>
@@ -3083,7 +3094,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M32" t="str">
-        <v>30000641439</v>
+        <v>30000506816</v>
       </c>
       <c r="N32" t="str">
         <v>State Bank of India</v>
@@ -3092,48 +3103,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P32" t="str">
-        <v>SBIN0003095</v>
+        <v>SBIN0005150</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>0300050</v>
+        <v>0300066</v>
       </c>
       <c r="B33" t="str">
-        <v>SUNIL ANSARI</v>
+        <v>KIRAN GUPTA</v>
       </c>
       <c r="C33" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D33" t="str">
-        <v>03045</v>
+        <v>03053</v>
       </c>
       <c r="E33" t="str">
-        <v>Middle School Tariyani</v>
+        <v>CDPO Office Purnahiya</v>
       </c>
       <c r="F33" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G33" t="str">
-        <v>9003000050</v>
+        <v>9003000066</v>
       </c>
       <c r="H33" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I33" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J33" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K33" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L33" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M33" t="str">
-        <v>30000395950</v>
+        <v>30000522654</v>
       </c>
       <c r="N33" t="str">
         <v>State Bank of India</v>
@@ -3142,48 +3153,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P33" t="str">
-        <v>SBIN0004589</v>
+        <v>SBIN0004804</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>0300035</v>
+        <v>0300101</v>
       </c>
       <c r="B34" t="str">
-        <v>AJAY PRASAD</v>
+        <v>ALOK SAH Q</v>
       </c>
       <c r="C34" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D34" t="str">
-        <v>03032</v>
+        <v>03077</v>
       </c>
       <c r="E34" t="str">
-        <v>Kanya Middle School Tariyani</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F34" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G34" t="str">
-        <v>9003000035</v>
+        <v>9003000101</v>
       </c>
       <c r="H34" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I34" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J34" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K34" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L34" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M34" t="str">
-        <v>30000277165</v>
+        <v>30000799819</v>
       </c>
       <c r="N34" t="str">
         <v>State Bank of India</v>
@@ -3192,48 +3203,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P34" t="str">
-        <v>SBIN0005274</v>
+        <v>SBIN0007588</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>0300116</v>
+        <v>0300077</v>
       </c>
       <c r="B35" t="str">
-        <v>UMESH MAHTO O</v>
+        <v>PRAMOD GUPTA</v>
       </c>
       <c r="C35" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D35" t="str">
-        <v>03087</v>
+        <v>03062</v>
       </c>
       <c r="E35" t="str">
-        <v>Bank of India, Tariyani</v>
+        <v>Primary School Piprahi No.1</v>
       </c>
       <c r="F35" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G35" t="str">
-        <v>9003000116</v>
+        <v>9003000077</v>
       </c>
       <c r="H35" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I35" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J35" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K35" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L35" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M35" t="str">
-        <v>30000918604</v>
+        <v>30000609763</v>
       </c>
       <c r="N35" t="str">
         <v>State Bank of India</v>
@@ -3242,33 +3253,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P35" t="str">
-        <v>SBIN0003278</v>
+        <v>SBIN0004982</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>0300017</v>
+        <v>0300080</v>
       </c>
       <c r="B36" t="str">
-        <v>POONAM PRASAD</v>
+        <v>NIRMALA PRASAD</v>
       </c>
       <c r="C36" t="str">
-        <v>Headmaster</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D36" t="str">
-        <v>03015</v>
+        <v>03028</v>
       </c>
       <c r="E36" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>CDPO Office Tariyani No.1</v>
       </c>
       <c r="F36" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G36" t="str">
-        <v>9003000017</v>
+        <v>9003000080</v>
       </c>
       <c r="H36" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I36" t="str">
         <v>0301</v>
@@ -3277,13 +3288,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K36" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L36" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M36" t="str">
-        <v>30000134623</v>
+        <v>30000633520</v>
       </c>
       <c r="N36" t="str">
         <v>State Bank of India</v>
@@ -3292,48 +3303,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P36" t="str">
-        <v>SBIN0006798</v>
+        <v>SBIN0007142</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>0300100</v>
+        <v>0300126</v>
       </c>
       <c r="B37" t="str">
-        <v>DEEPAK SINGH</v>
+        <v>NIRMALA SHARMA</v>
       </c>
       <c r="C37" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D37" t="str">
-        <v>03076</v>
+        <v>03085</v>
       </c>
       <c r="E37" t="str">
-        <v>RWD Sub-Division Dumri Katsari</v>
+        <v>Head Post Office, Piprahi</v>
       </c>
       <c r="F37" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G37" t="str">
-        <v>9003000100</v>
+        <v>9003000126</v>
       </c>
       <c r="H37" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I37" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J37" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K37" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L37" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M37" t="str">
-        <v>30000791900</v>
+        <v>30000997794</v>
       </c>
       <c r="N37" t="str">
         <v>State Bank of India</v>
@@ -3342,33 +3353,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P37" t="str">
-        <v>SBIN0005875</v>
+        <v>SBIN0002334</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>0300112</v>
+        <v>0300058</v>
       </c>
       <c r="B38" t="str">
-        <v>USHA VERMA</v>
+        <v>ARVIND SINHA</v>
       </c>
       <c r="C38" t="str">
-        <v>Assistant Manager</v>
+        <v>Clerk</v>
       </c>
       <c r="D38" t="str">
-        <v>03084</v>
+        <v>03047</v>
       </c>
       <c r="E38" t="str">
-        <v>Punjab National Bank, Sheohar</v>
+        <v>CDPO Office Dumri Katsari</v>
       </c>
       <c r="F38" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G38" t="str">
-        <v>9003000112</v>
+        <v>9003000058</v>
       </c>
       <c r="H38" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I38" t="str">
         <v>0304</v>
@@ -3377,13 +3388,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K38" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L38" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M38" t="str">
-        <v>30000886928</v>
+        <v>30000459302</v>
       </c>
       <c r="N38" t="str">
         <v>State Bank of India</v>
@@ -3392,48 +3403,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P38" t="str">
-        <v>SBIN0008866</v>
+        <v>SBIN0005642</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>0300113</v>
+        <v>0300042</v>
       </c>
       <c r="B39" t="str">
-        <v>AMIT SHARMA</v>
+        <v>NEHA YADAV S</v>
       </c>
       <c r="C39" t="str">
-        <v>Administrative Officer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D39" t="str">
-        <v>03085</v>
+        <v>03035</v>
       </c>
       <c r="E39" t="str">
-        <v>State Bank of India, Purnahiya</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="F39" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G39" t="str">
-        <v>9003000113</v>
+        <v>9003000042</v>
       </c>
       <c r="H39" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I39" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J39" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K39" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L39" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M39" t="str">
-        <v>30000894847</v>
+        <v>30000332598</v>
       </c>
       <c r="N39" t="str">
         <v>State Bank of India</v>
@@ -3442,39 +3453,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P39" t="str">
-        <v>SBIN0001918</v>
+        <v>SBIN0007083</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>0300033</v>
+        <v>0300028</v>
       </c>
       <c r="B40" t="str">
-        <v>RAVI THAKUR</v>
+        <v>RAJESH CHAUDHARY</v>
       </c>
       <c r="C40" t="str">
-        <v>Assistant Teacher</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D40" t="str">
-        <v>03031</v>
+        <v>03026</v>
       </c>
       <c r="E40" t="str">
-        <v>Primary School Dumri Katsari No.4</v>
+        <v>Project Girls High School Dumri Katsari</v>
       </c>
       <c r="F40" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G40" t="str">
-        <v>9003000033</v>
+        <v>9003000028</v>
       </c>
       <c r="H40" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I40" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J40" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K40" t="str">
         <v>0304</v>
@@ -3483,7 +3494,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M40" t="str">
-        <v>30000261327</v>
+        <v>30000221732</v>
       </c>
       <c r="N40" t="str">
         <v>State Bank of India</v>
@@ -3492,48 +3503,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P40" t="str">
-        <v>SBIN0008149</v>
+        <v>SBIN0005517</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>0300124</v>
+        <v>0300019</v>
       </c>
       <c r="B41" t="str">
-        <v>ALOK ANSARI</v>
+        <v>SANTOSH CHAUDHARY</v>
       </c>
       <c r="C41" t="str">
-        <v>Postmaster</v>
+        <v>Section Officer</v>
       </c>
       <c r="D41" t="str">
-        <v>03094</v>
+        <v>03019</v>
       </c>
       <c r="E41" t="str">
-        <v>Central Bank of India, Tariyani</v>
+        <v>PHED Division (deputed from other district)</v>
       </c>
       <c r="F41" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G41" t="str">
-        <v>9003000124</v>
+        <v>9003000019</v>
       </c>
       <c r="H41" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I41" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J41" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K41" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="L41" t="str">
-        <v>Tariyani</v>
+        <v>Other District</v>
       </c>
       <c r="M41" t="str">
-        <v>30000981956</v>
+        <v>30000150461</v>
       </c>
       <c r="N41" t="str">
         <v>State Bank of India</v>
@@ -3542,48 +3553,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P41" t="str">
-        <v>SBIN0009563</v>
+        <v>SBIN0008494</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>0300078</v>
+        <v>0300112</v>
       </c>
       <c r="B42" t="str">
-        <v>SAVITA SINHA</v>
+        <v>AJAY KUMAR</v>
       </c>
       <c r="C42" t="str">
-        <v>Teacher</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D42" t="str">
-        <v>03065</v>
+        <v>03084</v>
       </c>
       <c r="E42" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>LIC Branch Office, Sheohar</v>
       </c>
       <c r="F42" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G42" t="str">
-        <v>9003000078</v>
+        <v>9003000112</v>
       </c>
       <c r="H42" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I42" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J42" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K42" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L42" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M42" t="str">
-        <v>30000617682</v>
+        <v>30000886928</v>
       </c>
       <c r="N42" t="str">
         <v>State Bank of India</v>
@@ -3592,48 +3603,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P42" t="str">
-        <v>SBIN0003906</v>
+        <v>SBIN0007236</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>0300042</v>
+        <v>0300018</v>
       </c>
       <c r="B43" t="str">
-        <v>POONAM SINGH</v>
+        <v>AMIT VERMA M</v>
       </c>
       <c r="C43" t="str">
-        <v>Head Clerk</v>
+        <v>Headmaster</v>
       </c>
       <c r="D43" t="str">
-        <v>03038</v>
+        <v>03018</v>
       </c>
       <c r="E43" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Circle Office Sheohar No.3</v>
       </c>
       <c r="F43" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G43" t="str">
-        <v>9003000042</v>
+        <v>9003000018</v>
       </c>
       <c r="H43" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I43" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J43" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K43" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L43" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M43" t="str">
-        <v>30000332598</v>
+        <v>30000142542</v>
       </c>
       <c r="N43" t="str">
         <v>State Bank of India</v>
@@ -3642,33 +3653,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P43" t="str">
-        <v>SBIN0003077</v>
+        <v>SBIN0003892</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>0300026</v>
+        <v>0300095</v>
       </c>
       <c r="B44" t="str">
-        <v>SUNITA PASWAN</v>
+        <v>SAVITA DEVI</v>
       </c>
       <c r="C44" t="str">
-        <v>Senior Clerk</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D44" t="str">
-        <v>03024</v>
+        <v>03074</v>
       </c>
       <c r="E44" t="str">
-        <v>Block Education Office Purnahiya</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="F44" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G44" t="str">
-        <v>9003000026</v>
+        <v>9003000095</v>
       </c>
       <c r="H44" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I44" t="str">
         <v>0302</v>
@@ -3677,13 +3688,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K44" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L44" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M44" t="str">
-        <v>30000205894</v>
+        <v>30000752305</v>
       </c>
       <c r="N44" t="str">
         <v>State Bank of India</v>
@@ -3692,33 +3703,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P44" t="str">
-        <v>SBIN0007162</v>
+        <v>SBIN0002955</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>0300115</v>
+        <v>0300026</v>
       </c>
       <c r="B45" t="str">
-        <v>ANITA TIWARI</v>
+        <v>USHA MISHRA</v>
       </c>
       <c r="C45" t="str">
-        <v>Assistant Manager</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D45" t="str">
-        <v>03081</v>
+        <v>03021</v>
       </c>
       <c r="E45" t="str">
-        <v>Punjab National Bank, Dumri Katsari</v>
+        <v>High School Tariyani No.4</v>
       </c>
       <c r="F45" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G45" t="str">
-        <v>9003000115</v>
+        <v>9003000026</v>
       </c>
       <c r="H45" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I45" t="str">
         <v>0304</v>
@@ -3727,13 +3738,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K45" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L45" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M45" t="str">
-        <v>30000910685</v>
+        <v>30000205894</v>
       </c>
       <c r="N45" t="str">
         <v>State Bank of India</v>
@@ -3742,39 +3753,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P45" t="str">
-        <v>SBIN0007367</v>
+        <v>SBIN0001690</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>0300061</v>
+        <v>0300068</v>
       </c>
       <c r="B46" t="str">
-        <v>MD. SHAHID DEVI</v>
+        <v>SUNIL VERMA</v>
       </c>
       <c r="C46" t="str">
-        <v>Accountant</v>
+        <v>Clerk</v>
       </c>
       <c r="D46" t="str">
-        <v>03053</v>
+        <v>03055</v>
       </c>
       <c r="E46" t="str">
-        <v>Block Agriculture Office Sheohar No.1</v>
+        <v>Block Agriculture Office Sheohar No.2</v>
       </c>
       <c r="F46" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G46" t="str">
-        <v>9003000061</v>
+        <v>9003000068</v>
       </c>
       <c r="H46" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I46" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J46" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K46" t="str">
         <v>0301</v>
@@ -3783,7 +3794,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M46" t="str">
-        <v>30000483059</v>
+        <v>30000538492</v>
       </c>
       <c r="N46" t="str">
         <v>State Bank of India</v>
@@ -3792,39 +3803,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P46" t="str">
-        <v>SBIN0007749</v>
+        <v>SBIN0003402</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0300001</v>
+        <v>0300013</v>
       </c>
       <c r="B47" t="str">
-        <v>ASHA RAM</v>
+        <v>RANJIT MISHRA</v>
       </c>
       <c r="C47" t="str">
-        <v>Assistant Engineer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D47" t="str">
-        <v>03001</v>
+        <v>03013</v>
       </c>
       <c r="E47" t="str">
-        <v>Circle Office Sheohar</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="F47" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G47" t="str">
-        <v>9003000001</v>
+        <v>9003000013</v>
       </c>
       <c r="H47" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I47" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J47" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K47" t="str">
         <v>0301</v>
@@ -3833,7 +3844,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M47" t="str">
-        <v>30000007919</v>
+        <v>30000102947</v>
       </c>
       <c r="N47" t="str">
         <v>State Bank of India</v>
@@ -3842,48 +3853,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P47" t="str">
-        <v>SBIN0004896</v>
+        <v>SBIN0001680</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0300094</v>
+        <v>0300037</v>
       </c>
       <c r="B48" t="str">
-        <v>MD. SHAHID MISHRA</v>
+        <v>VIJAY CHAUDHARY</v>
       </c>
       <c r="C48" t="str">
-        <v>Revenue Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D48" t="str">
-        <v>03065</v>
+        <v>03003</v>
       </c>
       <c r="E48" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F48" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G48" t="str">
-        <v>9003000094</v>
+        <v>9003000037</v>
       </c>
       <c r="H48" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I48" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J48" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K48" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L48" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M48" t="str">
-        <v>30000744386</v>
+        <v>30000293003</v>
       </c>
       <c r="N48" t="str">
         <v>State Bank of India</v>
@@ -3892,48 +3903,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P48" t="str">
-        <v>SBIN0004380</v>
+        <v>SBIN0004142</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0300048</v>
+        <v>0300108</v>
       </c>
       <c r="B49" t="str">
-        <v>FARHAT YADAV</v>
+        <v>MD. SHAHID CHAUDHARY</v>
       </c>
       <c r="C49" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Postmaster</v>
       </c>
       <c r="D49" t="str">
-        <v>03043</v>
+        <v>03082</v>
       </c>
       <c r="E49" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>BSNL Exchange, Tariyani</v>
       </c>
       <c r="F49" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G49" t="str">
-        <v>9003000048</v>
+        <v>9003000108</v>
       </c>
       <c r="H49" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I49" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J49" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K49" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L49" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M49" t="str">
-        <v>30000380112</v>
+        <v>30000855252</v>
       </c>
       <c r="N49" t="str">
         <v>State Bank of India</v>
@@ -3942,48 +3953,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P49" t="str">
-        <v>SBIN0001521</v>
+        <v>SBIN0001877</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0300095</v>
+        <v>0300088</v>
       </c>
       <c r="B50" t="str">
-        <v>USHA THAKUR</v>
+        <v>PRIYANKA KHATUN</v>
       </c>
       <c r="C50" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D50" t="str">
-        <v>03043</v>
+        <v>03068</v>
       </c>
       <c r="E50" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F50" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G50" t="str">
-        <v>9003000095</v>
+        <v>9003000088</v>
       </c>
       <c r="H50" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I50" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J50" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K50" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L50" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M50" t="str">
-        <v>30000752305</v>
+        <v>30000696872</v>
       </c>
       <c r="N50" t="str">
         <v>State Bank of India</v>
@@ -3992,7 +4003,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P50" t="str">
-        <v>SBIN0005196</v>
+        <v>SBIN0001908</v>
       </c>
     </row>
     <row r="51">
@@ -4000,16 +4011,16 @@
         <v>0300120</v>
       </c>
       <c r="B51" t="str">
-        <v>AJAY SAH</v>
+        <v>VINOD SAH</v>
       </c>
       <c r="C51" t="str">
-        <v>Assistant Manager</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D51" t="str">
-        <v>03090</v>
+        <v>03091</v>
       </c>
       <c r="E51" t="str">
-        <v>LIC Branch Office, Tariyani</v>
+        <v>Central Bank of India, Tariyani</v>
       </c>
       <c r="F51" t="str">
         <v>Tariyani, Sheohar</v>
@@ -4021,10 +4032,10 @@
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I51" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J51" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K51" t="str">
         <v>0305</v>
@@ -4042,48 +4053,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P51" t="str">
-        <v>SBIN0009146</v>
+        <v>SBIN0007479</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>0300040</v>
+        <v>0300082</v>
       </c>
       <c r="B52" t="str">
-        <v>RAKESH GUPTA</v>
+        <v>ARVIND KUMAR</v>
       </c>
       <c r="C52" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Teacher</v>
       </c>
       <c r="D52" t="str">
-        <v>03036</v>
+        <v>03065</v>
       </c>
       <c r="E52" t="str">
-        <v>Kanya Middle School Purnahiya</v>
+        <v>Middle School Tariyani No.2</v>
       </c>
       <c r="F52" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G52" t="str">
-        <v>9003000040</v>
+        <v>9003000082</v>
       </c>
       <c r="H52" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I52" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J52" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K52" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L52" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M52" t="str">
-        <v>30000316760</v>
+        <v>30000649358</v>
       </c>
       <c r="N52" t="str">
         <v>State Bank of India</v>
@@ -4092,39 +4103,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P52" t="str">
-        <v>SBIN0009889</v>
+        <v>SBIN0007867</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>0300020</v>
+        <v>0300053</v>
       </c>
       <c r="B53" t="str">
-        <v>PANKAJ RAI</v>
+        <v>AJAY THAKUR</v>
       </c>
       <c r="C53" t="str">
-        <v>Assistant Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D53" t="str">
-        <v>03018</v>
+        <v>03043</v>
       </c>
       <c r="E53" t="str">
-        <v>High School Tariyani No.2</v>
+        <v>Block Education Office Tariyani No.2</v>
       </c>
       <c r="F53" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G53" t="str">
-        <v>9003000020</v>
+        <v>9003000053</v>
       </c>
       <c r="H53" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I53" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J53" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K53" t="str">
         <v>0305</v>
@@ -4133,7 +4144,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M53" t="str">
-        <v>30000158380</v>
+        <v>30000419707</v>
       </c>
       <c r="N53" t="str">
         <v>State Bank of India</v>
@@ -4142,48 +4153,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P53" t="str">
-        <v>SBIN0008367</v>
+        <v>SBIN0006521</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>0300088</v>
+        <v>0300091</v>
       </c>
       <c r="B54" t="str">
-        <v>KIRAN OJHA</v>
+        <v>ALOK SAH</v>
       </c>
       <c r="C54" t="str">
-        <v>Assistant Engineer</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D54" t="str">
-        <v>03008</v>
+        <v>03071</v>
       </c>
       <c r="E54" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>Block Office Dumri Katsari</v>
       </c>
       <c r="F54" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G54" t="str">
-        <v>9003000088</v>
+        <v>9003000091</v>
       </c>
       <c r="H54" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I54" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J54" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K54" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L54" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M54" t="str">
-        <v>30000696872</v>
+        <v>30000720629</v>
       </c>
       <c r="N54" t="str">
         <v>State Bank of India</v>
@@ -4192,30 +4203,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P54" t="str">
-        <v>SBIN0002313</v>
+        <v>SBIN0008419</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>0300101</v>
+        <v>0300097</v>
       </c>
       <c r="B55" t="str">
-        <v>ASHA VERMA</v>
+        <v>SANTOSH OJHA</v>
       </c>
       <c r="C55" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D55" t="str">
-        <v>03077</v>
+        <v>03075</v>
       </c>
       <c r="E55" t="str">
-        <v>Minor Irrigation Office Tariyani</v>
+        <v>Circle Office Sheohar</v>
       </c>
       <c r="F55" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G55" t="str">
-        <v>9003000101</v>
+        <v>9003000097</v>
       </c>
       <c r="H55" t="str">
         <v>PATROLLING MAGISTRATE</v>
@@ -4227,13 +4238,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K55" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L55" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M55" t="str">
-        <v>30000799819</v>
+        <v>30000768143</v>
       </c>
       <c r="N55" t="str">
         <v>State Bank of India</v>
@@ -4242,48 +4253,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P55" t="str">
-        <v>SBIN0005004</v>
+        <v>SBIN0006895</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>0300092</v>
+        <v>0300039</v>
       </c>
       <c r="B56" t="str">
-        <v>RINKU TIWARI</v>
+        <v>RANJIT SINHA</v>
       </c>
       <c r="C56" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D56" t="str">
-        <v>03073</v>
+        <v>03022</v>
       </c>
       <c r="E56" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F56" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G56" t="str">
-        <v>9003000092</v>
+        <v>9003000039</v>
       </c>
       <c r="H56" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I56" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J56" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K56" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L56" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M56" t="str">
-        <v>30000728548</v>
+        <v>30000308841</v>
       </c>
       <c r="N56" t="str">
         <v>State Bank of India</v>
@@ -4292,48 +4303,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P56" t="str">
-        <v>SBIN0009268</v>
+        <v>SBIN0009972</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>0300047</v>
+        <v>0300094</v>
       </c>
       <c r="B57" t="str">
-        <v>RINKU PANDEY</v>
+        <v>MAHESH SHARMA</v>
       </c>
       <c r="C57" t="str">
-        <v>Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D57" t="str">
-        <v>03042</v>
+        <v>03073</v>
       </c>
       <c r="E57" t="str">
-        <v>Block Office Sheohar No.2</v>
+        <v>RWD Sub-Division Purnahiya</v>
       </c>
       <c r="F57" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G57" t="str">
-        <v>9003000047</v>
+        <v>9003000094</v>
       </c>
       <c r="H57" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I57" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J57" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K57" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L57" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M57" t="str">
-        <v>30000372193</v>
+        <v>30000744386</v>
       </c>
       <c r="N57" t="str">
         <v>State Bank of India</v>
@@ -4342,48 +4353,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P57" t="str">
-        <v>SBIN0002847</v>
+        <v>SBIN0005115</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>0300114</v>
+        <v>0300007</v>
       </c>
       <c r="B58" t="str">
-        <v>POONAM SINHA</v>
+        <v>NIRMALA MAHTO</v>
       </c>
       <c r="C58" t="str">
-        <v>Branch Manager</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D58" t="str">
-        <v>03086</v>
+        <v>03007</v>
       </c>
       <c r="E58" t="str">
-        <v>BSNL Exchange, Tariyani</v>
+        <v>Middle School Piprahi No.3</v>
       </c>
       <c r="F58" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G58" t="str">
-        <v>9003000114</v>
+        <v>9003000007</v>
       </c>
       <c r="H58" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I58" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J58" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K58" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L58" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M58" t="str">
-        <v>30000902766</v>
+        <v>30000055433</v>
       </c>
       <c r="N58" t="str">
         <v>State Bank of India</v>
@@ -4392,48 +4403,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P58" t="str">
-        <v>SBIN0008030</v>
+        <v>SBIN0007829</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>0300110</v>
+        <v>0300085</v>
       </c>
       <c r="B59" t="str">
-        <v>SANJAY DEVI</v>
+        <v>SANJAY SINGH</v>
       </c>
       <c r="C59" t="str">
-        <v>Assistant Manager</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D59" t="str">
-        <v>03082</v>
+        <v>03068</v>
       </c>
       <c r="E59" t="str">
-        <v>LIC Branch Office, Piprahi</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F59" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G59" t="str">
-        <v>9003000110</v>
+        <v>9003000085</v>
       </c>
       <c r="H59" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I59" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J59" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K59" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L59" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M59" t="str">
-        <v>30000871090</v>
+        <v>30000673115</v>
       </c>
       <c r="N59" t="str">
         <v>State Bank of India</v>
@@ -4442,39 +4453,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P59" t="str">
-        <v>SBIN0007594</v>
+        <v>SBIN0004543</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>0300024</v>
+        <v>0300124</v>
       </c>
       <c r="B60" t="str">
-        <v>DEEPAK SINHA</v>
+        <v>PRIYANKA MISHRA</v>
       </c>
       <c r="C60" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Postmaster</v>
       </c>
       <c r="D60" t="str">
-        <v>03022</v>
+        <v>03091</v>
       </c>
       <c r="E60" t="str">
-        <v>Project Girls High School Tariyani</v>
+        <v>Central Bank of India, Tariyani</v>
       </c>
       <c r="F60" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G60" t="str">
-        <v>9003000024</v>
+        <v>9003000124</v>
       </c>
       <c r="H60" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I60" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J60" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K60" t="str">
         <v>0305</v>
@@ -4483,7 +4494,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M60" t="str">
-        <v>30000190056</v>
+        <v>30000981956</v>
       </c>
       <c r="N60" t="str">
         <v>State Bank of India</v>
@@ -4492,48 +4503,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P60" t="str">
-        <v>SBIN0003458</v>
+        <v>SBIN0001272</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>0300076</v>
+        <v>0300114</v>
       </c>
       <c r="B61" t="str">
-        <v>UMESH MISHRA</v>
+        <v>RINKU ALAM</v>
       </c>
       <c r="C61" t="str">
-        <v>Data Entry Operator</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D61" t="str">
-        <v>03064</v>
+        <v>03080</v>
       </c>
       <c r="E61" t="str">
-        <v>High School Dumri Katsari No.3</v>
+        <v>UCO Bank, Tariyani</v>
       </c>
       <c r="F61" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G61" t="str">
-        <v>9003000076</v>
+        <v>9003000114</v>
       </c>
       <c r="H61" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I61" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J61" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K61" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L61" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M61" t="str">
-        <v>30000601844</v>
+        <v>30000902766</v>
       </c>
       <c r="N61" t="str">
         <v>State Bank of India</v>
@@ -4542,48 +4553,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P61" t="str">
-        <v>SBIN0006310</v>
+        <v>SBIN0003081</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>0300108</v>
+        <v>0300048</v>
       </c>
       <c r="B62" t="str">
-        <v>ARVIND MISHRA</v>
+        <v>SUNIL SINHA</v>
       </c>
       <c r="C62" t="str">
-        <v>Assistant Manager</v>
+        <v>Accountant</v>
       </c>
       <c r="D62" t="str">
-        <v>03081</v>
+        <v>03020</v>
       </c>
       <c r="E62" t="str">
-        <v>Punjab National Bank, Dumri Katsari</v>
+        <v>Block Education Office Tariyani</v>
       </c>
       <c r="F62" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G62" t="str">
-        <v>9003000108</v>
+        <v>9003000048</v>
       </c>
       <c r="H62" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I62" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J62" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K62" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L62" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M62" t="str">
-        <v>30000855252</v>
+        <v>30000380112</v>
       </c>
       <c r="N62" t="str">
         <v>State Bank of India</v>
@@ -4592,48 +4603,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P62" t="str">
-        <v>SBIN0007979</v>
+        <v>SBIN0001093</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>0300031</v>
+        <v>0300067</v>
       </c>
       <c r="B63" t="str">
-        <v>NITISH KHATUN</v>
+        <v>ARVIND SINHA K</v>
       </c>
       <c r="C63" t="str">
-        <v>Assistant Teacher</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D63" t="str">
-        <v>03029</v>
+        <v>03054</v>
       </c>
       <c r="E63" t="str">
-        <v>Primary School Dumri Katsari No.3</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F63" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G63" t="str">
-        <v>9003000031</v>
+        <v>9003000067</v>
       </c>
       <c r="H63" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I63" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J63" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K63" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L63" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M63" t="str">
-        <v>30000245489</v>
+        <v>30000530573</v>
       </c>
       <c r="N63" t="str">
         <v>State Bank of India</v>
@@ -4642,48 +4653,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P63" t="str">
-        <v>SBIN0009745</v>
+        <v>SBIN0009319</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>0300002</v>
+        <v>0300006</v>
       </c>
       <c r="B64" t="str">
-        <v>PRAMOD MISHRA</v>
+        <v>VIJAY TIWARI</v>
       </c>
       <c r="C64" t="str">
-        <v>Section Officer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D64" t="str">
-        <v>03002</v>
+        <v>03006</v>
       </c>
       <c r="E64" t="str">
-        <v>Kanya Middle School Dumri Katsari No.2</v>
+        <v>PHC Sheohar</v>
       </c>
       <c r="F64" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G64" t="str">
-        <v>9003000002</v>
+        <v>9003000006</v>
       </c>
       <c r="H64" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I64" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J64" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K64" t="str">
         <v>0301</v>
       </c>
-      <c r="J64" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K64" t="str">
-        <v>0304</v>
-      </c>
       <c r="L64" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M64" t="str">
-        <v>30000015838</v>
+        <v>30000047514</v>
       </c>
       <c r="N64" t="str">
         <v>State Bank of India</v>
@@ -4692,48 +4703,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P64" t="str">
-        <v>SBIN0007114</v>
+        <v>SBIN0009024</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>0300079</v>
+        <v>0300052</v>
       </c>
       <c r="B65" t="str">
-        <v>VIJAY MAHTO S</v>
+        <v>DEEPAK JHA</v>
       </c>
       <c r="C65" t="str">
         <v>Clerk</v>
       </c>
       <c r="D65" t="str">
-        <v>03066</v>
+        <v>03042</v>
       </c>
       <c r="E65" t="str">
-        <v>Kanya Middle School Purnahiya No.2</v>
+        <v>Block Office Sheohar No.4</v>
       </c>
       <c r="F65" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G65" t="str">
-        <v>9003000079</v>
+        <v>9003000052</v>
       </c>
       <c r="H65" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I65" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J65" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K65" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L65" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M65" t="str">
-        <v>30000625601</v>
+        <v>30000411788</v>
       </c>
       <c r="N65" t="str">
         <v>State Bank of India</v>
@@ -4742,48 +4753,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P65" t="str">
-        <v>SBIN0006759</v>
+        <v>SBIN0002904</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>0300018</v>
+        <v>0300074</v>
       </c>
       <c r="B66" t="str">
-        <v>NEHA JHA</v>
+        <v>ANITA VERMA</v>
       </c>
       <c r="C66" t="str">
-        <v>Headmaster</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D66" t="str">
-        <v>03006</v>
+        <v>03060</v>
       </c>
       <c r="E66" t="str">
-        <v>Block Education Office Sheohar No.2</v>
+        <v>Block Office Piprahi No.3</v>
       </c>
       <c r="F66" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G66" t="str">
-        <v>9003000018</v>
+        <v>9003000074</v>
       </c>
       <c r="H66" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I66" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J66" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K66" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L66" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M66" t="str">
-        <v>30000142542</v>
+        <v>30000586006</v>
       </c>
       <c r="N66" t="str">
         <v>State Bank of India</v>
@@ -4792,48 +4803,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P66" t="str">
-        <v>SBIN0007766</v>
+        <v>SBIN0005260</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>0300011</v>
+        <v>0300089</v>
       </c>
       <c r="B67" t="str">
-        <v>RAVI ALAM</v>
+        <v>NEHA SINHA</v>
       </c>
       <c r="C67" t="str">
-        <v>Section Officer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D67" t="str">
-        <v>03011</v>
+        <v>03068</v>
       </c>
       <c r="E67" t="str">
-        <v>Block Office Purnahiya No.2</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F67" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G67" t="str">
-        <v>9003000011</v>
+        <v>9003000089</v>
       </c>
       <c r="H67" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I67" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J67" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K67" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L67" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M67" t="str">
-        <v>30000087109</v>
+        <v>30000704791</v>
       </c>
       <c r="N67" t="str">
         <v>State Bank of India</v>
@@ -4842,48 +4853,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P67" t="str">
-        <v>SBIN0004156</v>
+        <v>SBIN0003152</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>0300049</v>
+        <v>0300033</v>
       </c>
       <c r="B68" t="str">
-        <v>DINESH MISHRA</v>
+        <v>MD. IRFAN MAHTO</v>
       </c>
       <c r="C68" t="str">
-        <v>Teacher</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D68" t="str">
-        <v>03044</v>
+        <v>03031</v>
       </c>
       <c r="E68" t="str">
-        <v>Block Office Dumri Katsari No.2</v>
+        <v>Panchayat Bhawan Piprahi</v>
       </c>
       <c r="F68" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G68" t="str">
-        <v>9003000049</v>
+        <v>9003000033</v>
       </c>
       <c r="H68" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I68" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J68" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K68" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L68" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M68" t="str">
-        <v>30000388031</v>
+        <v>30000261327</v>
       </c>
       <c r="N68" t="str">
         <v>State Bank of India</v>
@@ -4892,39 +4903,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P68" t="str">
-        <v>SBIN0007011</v>
+        <v>SBIN0002629</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>0300097</v>
+        <v>0300038</v>
       </c>
       <c r="B69" t="str">
-        <v>SANTOSH VERMA</v>
+        <v>NIRMALA MAHTO N</v>
       </c>
       <c r="C69" t="str">
-        <v>Revenue Officer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D69" t="str">
-        <v>03046</v>
+        <v>03014</v>
       </c>
       <c r="E69" t="str">
-        <v>Block Office Sheohar</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F69" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G69" t="str">
-        <v>9003000097</v>
+        <v>9003000038</v>
       </c>
       <c r="H69" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I69" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="J69" t="str">
-        <v>Dumri Katsari</v>
+        <v>Others</v>
       </c>
       <c r="K69" t="str">
         <v>0301</v>
@@ -4933,7 +4944,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M69" t="str">
-        <v>30000768143</v>
+        <v>30000300922</v>
       </c>
       <c r="N69" t="str">
         <v>State Bank of India</v>
@@ -4942,48 +4953,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P69" t="str">
-        <v>SBIN0009118</v>
+        <v>SBIN0006198</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>0300022</v>
+        <v>0300015</v>
       </c>
       <c r="B70" t="str">
-        <v>MAHESH KUMAR</v>
+        <v>NITISH PRASAD</v>
       </c>
       <c r="C70" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Lecturer</v>
       </c>
       <c r="D70" t="str">
-        <v>03020</v>
+        <v>03015</v>
       </c>
       <c r="E70" t="str">
-        <v>Block Education Office Tariyani No.3</v>
+        <v>Block Agriculture Office Purnahiya No.2</v>
       </c>
       <c r="F70" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G70" t="str">
-        <v>9003000022</v>
+        <v>9003000015</v>
       </c>
       <c r="H70" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I70" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J70" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K70" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L70" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M70" t="str">
-        <v>30000174218</v>
+        <v>30000118785</v>
       </c>
       <c r="N70" t="str">
         <v>State Bank of India</v>
@@ -4992,48 +5003,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P70" t="str">
-        <v>SBIN0003756</v>
+        <v>SBIN0005045</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>0300044</v>
+        <v>0300105</v>
       </c>
       <c r="B71" t="str">
-        <v>AMIT TIWARI</v>
+        <v>ALOK VERMA</v>
       </c>
       <c r="C71" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D71" t="str">
-        <v>03039</v>
+        <v>03068</v>
       </c>
       <c r="E71" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F71" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G71" t="str">
-        <v>9003000044</v>
+        <v>9003000105</v>
       </c>
       <c r="H71" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I71" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J71" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K71" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L71" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M71" t="str">
-        <v>30000348436</v>
+        <v>30000831495</v>
       </c>
       <c r="N71" t="str">
         <v>State Bank of India</v>
@@ -5042,48 +5053,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P71" t="str">
-        <v>SBIN0003476</v>
+        <v>SBIN0006669</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>0300065</v>
+        <v>0300090</v>
       </c>
       <c r="B72" t="str">
-        <v>DINESH ANSARI</v>
+        <v>VIJAY CHAUDHARY P</v>
       </c>
       <c r="C72" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D72" t="str">
-        <v>03057</v>
+        <v>03070</v>
       </c>
       <c r="E72" t="str">
-        <v>Project Girls High School Purnahiya</v>
+        <v>RWD Sub-Division Piprahi</v>
       </c>
       <c r="F72" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G72" t="str">
-        <v>9003000065</v>
+        <v>9003000090</v>
       </c>
       <c r="H72" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I72" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J72" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K72" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L72" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M72" t="str">
-        <v>30000514735</v>
+        <v>30000712710</v>
       </c>
       <c r="N72" t="str">
         <v>State Bank of India</v>
@@ -5092,48 +5103,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P72" t="str">
-        <v>SBIN0006470</v>
+        <v>SBIN0004290</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>0300010</v>
+        <v>0300017</v>
       </c>
       <c r="B73" t="str">
-        <v>MAMTA DEVI</v>
+        <v>SUNITA ANSARI</v>
       </c>
       <c r="C73" t="str">
-        <v>Assistant Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D73" t="str">
-        <v>03010</v>
+        <v>03017</v>
       </c>
       <c r="E73" t="str">
-        <v>Panchayat Bhawan Purnahiya No.4</v>
+        <v>Block Office Tariyani No.3</v>
       </c>
       <c r="F73" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G73" t="str">
-        <v>9003000010</v>
+        <v>9003000017</v>
       </c>
       <c r="H73" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I73" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J73" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="K73" t="str">
         <v>0305</v>
       </c>
-      <c r="J73" t="str">
+      <c r="L73" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="K73" t="str">
-        <v>0303</v>
-      </c>
-      <c r="L73" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="M73" t="str">
-        <v>30000079190</v>
+        <v>30000134623</v>
       </c>
       <c r="N73" t="str">
         <v>State Bank of India</v>
@@ -5142,48 +5153,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P73" t="str">
-        <v>SBIN0009303</v>
+        <v>SBIN0002120</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>0300070</v>
+        <v>0300002</v>
       </c>
       <c r="B74" t="str">
-        <v>POONAM PANDEY</v>
+        <v>ANIL CHAUDHARY</v>
       </c>
       <c r="C74" t="str">
-        <v>Teacher</v>
+        <v>Lecturer</v>
       </c>
       <c r="D74" t="str">
-        <v>03021</v>
+        <v>03002</v>
       </c>
       <c r="E74" t="str">
-        <v>Middle School Dumri Katsari No.2</v>
+        <v>Middle School Sheohar</v>
       </c>
       <c r="F74" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G74" t="str">
-        <v>9003000070</v>
+        <v>9003000002</v>
       </c>
       <c r="H74" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I74" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J74" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K74" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L74" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M74" t="str">
-        <v>30000554330</v>
+        <v>30000015838</v>
       </c>
       <c r="N74" t="str">
         <v>State Bank of India</v>
@@ -5192,48 +5203,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P74" t="str">
-        <v>SBIN0002229</v>
+        <v>SBIN0003477</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>0300122</v>
+        <v>0300110</v>
       </c>
       <c r="B75" t="str">
-        <v>RAJESH RAI</v>
+        <v>AJAY OJHA</v>
       </c>
       <c r="C75" t="str">
-        <v>Postmaster</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D75" t="str">
-        <v>03092</v>
+        <v>03080</v>
       </c>
       <c r="E75" t="str">
-        <v>Central Bank of India, Sheohar</v>
+        <v>UCO Bank, Tariyani</v>
       </c>
       <c r="F75" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G75" t="str">
-        <v>9003000122</v>
+        <v>9003000110</v>
       </c>
       <c r="H75" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I75" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J75" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K75" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L75" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M75" t="str">
-        <v>30000966118</v>
+        <v>30000871090</v>
       </c>
       <c r="N75" t="str">
         <v>State Bank of India</v>
@@ -5242,48 +5253,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P75" t="str">
-        <v>SBIN0005272</v>
+        <v>SBIN0003717</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>0300051</v>
+        <v>0300098</v>
       </c>
       <c r="B76" t="str">
-        <v>DEEPAK PANDEY</v>
+        <v>PRIYANKA PRASAD</v>
       </c>
       <c r="C76" t="str">
-        <v>Teacher</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D76" t="str">
-        <v>03046</v>
+        <v>03074</v>
       </c>
       <c r="E76" t="str">
-        <v>Block Office Sheohar</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="F76" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G76" t="str">
-        <v>9003000051</v>
+        <v>9003000098</v>
       </c>
       <c r="H76" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I76" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J76" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K76" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L76" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M76" t="str">
-        <v>30000403869</v>
+        <v>30000776062</v>
       </c>
       <c r="N76" t="str">
         <v>State Bank of India</v>
@@ -5292,48 +5303,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P76" t="str">
-        <v>SBIN0005318</v>
+        <v>SBIN0002632</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>0300003</v>
+        <v>0300116</v>
       </c>
       <c r="B77" t="str">
-        <v>MAMTA VERMA</v>
+        <v>RANJIT ANSARI</v>
       </c>
       <c r="C77" t="str">
-        <v>Assistant Engineer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D77" t="str">
-        <v>03003</v>
+        <v>03087</v>
       </c>
       <c r="E77" t="str">
-        <v>Project Girls High School Sheohar No.3</v>
+        <v>BSNL Exchange, Purnahiya</v>
       </c>
       <c r="F77" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G77" t="str">
-        <v>9003000003</v>
+        <v>9003000116</v>
       </c>
       <c r="H77" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I77" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J77" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K77" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L77" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M77" t="str">
-        <v>30000023757</v>
+        <v>30000918604</v>
       </c>
       <c r="N77" t="str">
         <v>State Bank of India</v>
@@ -5342,48 +5353,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P77" t="str">
-        <v>SBIN0002632</v>
+        <v>SBIN0008676</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>0300107</v>
+        <v>0300036</v>
       </c>
       <c r="B78" t="str">
-        <v>ARVIND GUPTA</v>
+        <v>MAMTA KUMAR</v>
       </c>
       <c r="C78" t="str">
-        <v>Assistant Manager</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D78" t="str">
-        <v>03080</v>
+        <v>03034</v>
       </c>
       <c r="E78" t="str">
-        <v>Bank of India, Dumri Katsari</v>
+        <v>Project Girls High School Purnahiya No.4</v>
       </c>
       <c r="F78" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G78" t="str">
-        <v>9003000107</v>
+        <v>9003000036</v>
       </c>
       <c r="H78" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I78" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J78" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K78" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L78" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M78" t="str">
-        <v>30000847333</v>
+        <v>30000285084</v>
       </c>
       <c r="N78" t="str">
         <v>State Bank of India</v>
@@ -5392,33 +5403,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P78" t="str">
-        <v>SBIN0009936</v>
+        <v>SBIN0002033</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0300077</v>
+        <v>0300106</v>
       </c>
       <c r="B79" t="str">
-        <v>SAVITA PRASAD</v>
+        <v>NITISH ALAM</v>
       </c>
       <c r="C79" t="str">
-        <v>Data Entry Operator</v>
+        <v>Postmaster</v>
       </c>
       <c r="D79" t="str">
-        <v>03032</v>
+        <v>03080</v>
       </c>
       <c r="E79" t="str">
-        <v>Kanya Middle School Tariyani</v>
+        <v>UCO Bank, Tariyani</v>
       </c>
       <c r="F79" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G79" t="str">
-        <v>9003000077</v>
+        <v>9003000106</v>
       </c>
       <c r="H79" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I79" t="str">
         <v>0305</v>
@@ -5433,7 +5444,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M79" t="str">
-        <v>30000609763</v>
+        <v>30000839414</v>
       </c>
       <c r="N79" t="str">
         <v>State Bank of India</v>
@@ -5442,48 +5453,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P79" t="str">
-        <v>SBIN0004211</v>
+        <v>SBIN0004822</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>0300004</v>
+        <v>0300030</v>
       </c>
       <c r="B80" t="str">
-        <v>SANJAY VERMA</v>
+        <v>DEEPAK PASWAN</v>
       </c>
       <c r="C80" t="str">
-        <v>Senior Teacher</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D80" t="str">
-        <v>03004</v>
+        <v>03028</v>
       </c>
       <c r="E80" t="str">
-        <v>Project Girls High School Dumri Katsari No.4</v>
+        <v>CDPO Office Tariyani No.1</v>
       </c>
       <c r="F80" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G80" t="str">
-        <v>9003000004</v>
+        <v>9003000030</v>
       </c>
       <c r="H80" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I80" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J80" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K80" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L80" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M80" t="str">
-        <v>30000031676</v>
+        <v>30000237570</v>
       </c>
       <c r="N80" t="str">
         <v>State Bank of India</v>
@@ -5492,48 +5503,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P80" t="str">
-        <v>SBIN0007104</v>
+        <v>SBIN0002891</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>0300118</v>
+        <v>0300009</v>
       </c>
       <c r="B81" t="str">
-        <v>AJAY KUMAR G</v>
+        <v>FARHAT SINHA</v>
       </c>
       <c r="C81" t="str">
-        <v>Administrative Officer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D81" t="str">
-        <v>03089</v>
+        <v>03009</v>
       </c>
       <c r="E81" t="str">
-        <v>Punjab National Bank, Tariyani</v>
+        <v>PHC Piprahi No.4</v>
       </c>
       <c r="F81" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G81" t="str">
-        <v>9003000118</v>
+        <v>9003000009</v>
       </c>
       <c r="H81" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I81" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J81" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K81" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L81" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M81" t="str">
-        <v>30000934442</v>
+        <v>30000071271</v>
       </c>
       <c r="N81" t="str">
         <v>State Bank of India</v>
@@ -5542,48 +5553,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P81" t="str">
-        <v>SBIN0002402</v>
+        <v>SBIN0004292</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>0300034</v>
+        <v>0300109</v>
       </c>
       <c r="B82" t="str">
-        <v>NASREEN YADAV</v>
+        <v>NITISH PANDEY</v>
       </c>
       <c r="C82" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D82" t="str">
-        <v>03024</v>
+        <v>03082</v>
       </c>
       <c r="E82" t="str">
-        <v>Block Education Office Purnahiya</v>
+        <v>BSNL Exchange, Tariyani</v>
       </c>
       <c r="F82" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G82" t="str">
-        <v>9003000034</v>
+        <v>9003000109</v>
       </c>
       <c r="H82" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I82" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J82" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K82" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L82" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M82" t="str">
-        <v>30000269246</v>
+        <v>30000863171</v>
       </c>
       <c r="N82" t="str">
         <v>State Bank of India</v>
@@ -5592,48 +5603,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P82" t="str">
-        <v>SBIN0008806</v>
+        <v>SBIN0002305</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>0300106</v>
+        <v>0300022</v>
       </c>
       <c r="B83" t="str">
-        <v>DEEPAK SINHA U</v>
+        <v>ANITA JHA</v>
       </c>
       <c r="C83" t="str">
-        <v>Assistant Manager</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D83" t="str">
-        <v>03079</v>
+        <v>03011</v>
       </c>
       <c r="E83" t="str">
-        <v>Punjab National Bank, Purnahiya</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="F83" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G83" t="str">
-        <v>9003000106</v>
+        <v>9003000022</v>
       </c>
       <c r="H83" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I83" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J83" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K83" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L83" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M83" t="str">
-        <v>30000839414</v>
+        <v>30000174218</v>
       </c>
       <c r="N83" t="str">
         <v>State Bank of India</v>
@@ -5642,7 +5653,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P83" t="str">
-        <v>SBIN0007304</v>
+        <v>SBIN0009776</v>
       </c>
     </row>
     <row r="84">
@@ -5650,16 +5661,16 @@
         <v>0300072</v>
       </c>
       <c r="B84" t="str">
-        <v>VIJAY MAHTO</v>
+        <v>VIJAY GUPTA</v>
       </c>
       <c r="C84" t="str">
-        <v>Office Assistant</v>
+        <v>Teacher</v>
       </c>
       <c r="D84" t="str">
-        <v>03062</v>
+        <v>03058</v>
       </c>
       <c r="E84" t="str">
-        <v>Primary School Sheohar No.2</v>
+        <v>Panchayat Bhawan Sheohar No.2</v>
       </c>
       <c r="F84" t="str">
         <v>Sheohar, Sheohar</v>
@@ -5671,10 +5682,10 @@
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I84" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J84" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K84" t="str">
         <v>0301</v>
@@ -5692,48 +5703,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P84" t="str">
-        <v>SBIN0002494</v>
+        <v>SBIN0003962</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>0300123</v>
+        <v>0300059</v>
       </c>
       <c r="B85" t="str">
-        <v>MANOJ RAM</v>
+        <v>RAMESH ALAM</v>
       </c>
       <c r="C85" t="str">
-        <v>Assistant Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D85" t="str">
-        <v>03093</v>
+        <v>03048</v>
       </c>
       <c r="E85" t="str">
-        <v>Punjab National Bank, Piprahi</v>
+        <v>Circle Office Dumri Katsari No.3</v>
       </c>
       <c r="F85" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G85" t="str">
-        <v>9003000123</v>
+        <v>9003000059</v>
       </c>
       <c r="H85" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I85" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J85" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K85" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L85" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M85" t="str">
-        <v>30000974037</v>
+        <v>30000467221</v>
       </c>
       <c r="N85" t="str">
         <v>State Bank of India</v>
@@ -5742,48 +5753,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P85" t="str">
-        <v>SBIN0001093</v>
+        <v>SBIN0007485</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>0300045</v>
+        <v>0300122</v>
       </c>
       <c r="B86" t="str">
-        <v>MD. IRFAN PANDEY</v>
+        <v>ANITA YADAV</v>
       </c>
       <c r="C86" t="str">
-        <v>Accountant</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D86" t="str">
-        <v>03040</v>
+        <v>03083</v>
       </c>
       <c r="E86" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Central Bank of India, Piprahi</v>
       </c>
       <c r="F86" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G86" t="str">
-        <v>9003000045</v>
+        <v>9003000122</v>
       </c>
       <c r="H86" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I86" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J86" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K86" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L86" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M86" t="str">
-        <v>30000356355</v>
+        <v>30000966118</v>
       </c>
       <c r="N86" t="str">
         <v>State Bank of India</v>
@@ -5792,33 +5803,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P86" t="str">
-        <v>SBIN0008508</v>
+        <v>SBIN0004038</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>0300087</v>
+        <v>0300016</v>
       </c>
       <c r="B87" t="str">
-        <v>SAVITA KHATUN</v>
+        <v>NASREEN DEVI</v>
       </c>
       <c r="C87" t="str">
-        <v>Assistant Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D87" t="str">
-        <v>03070</v>
+        <v>03016</v>
       </c>
       <c r="E87" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>Kanya Middle School Tariyani No.4</v>
       </c>
       <c r="F87" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G87" t="str">
-        <v>9003000087</v>
+        <v>9003000016</v>
       </c>
       <c r="H87" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I87" t="str">
         <v>0303</v>
@@ -5827,13 +5838,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K87" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L87" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M87" t="str">
-        <v>30000688953</v>
+        <v>30000126704</v>
       </c>
       <c r="N87" t="str">
         <v>State Bank of India</v>
@@ -5842,39 +5853,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P87" t="str">
-        <v>SBIN0005730</v>
+        <v>SBIN0009616</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>0300036</v>
+        <v>0300078</v>
       </c>
       <c r="B88" t="str">
-        <v>RAJESH SINGH</v>
+        <v>VINOD ANSARI</v>
       </c>
       <c r="C88" t="str">
-        <v>Senior Clerk</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D88" t="str">
-        <v>03033</v>
+        <v>03063</v>
       </c>
       <c r="E88" t="str">
-        <v>Block Office Piprahi No.4</v>
+        <v>Project Girls High School Piprahi No.1</v>
       </c>
       <c r="F88" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G88" t="str">
-        <v>9003000036</v>
+        <v>9003000078</v>
       </c>
       <c r="H88" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I88" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="J88" t="str">
-        <v>Dumri Katsari</v>
+        <v>Others</v>
       </c>
       <c r="K88" t="str">
         <v>0302</v>
@@ -5883,7 +5894,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M88" t="str">
-        <v>30000285084</v>
+        <v>30000617682</v>
       </c>
       <c r="N88" t="str">
         <v>State Bank of India</v>
@@ -5892,33 +5903,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P88" t="str">
-        <v>SBIN0002350</v>
+        <v>SBIN0001270</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>0300085</v>
+        <v>0300123</v>
       </c>
       <c r="B89" t="str">
-        <v>SURESH MAHTO</v>
+        <v>RINKU YADAV N</v>
       </c>
       <c r="C89" t="str">
-        <v>Revenue Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D89" t="str">
-        <v>03038</v>
+        <v>03093</v>
       </c>
       <c r="E89" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Punjab National Bank, Tariyani</v>
       </c>
       <c r="F89" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G89" t="str">
-        <v>9003000085</v>
+        <v>9003000123</v>
       </c>
       <c r="H89" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I89" t="str">
         <v>0302</v>
@@ -5927,13 +5938,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K89" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L89" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M89" t="str">
-        <v>30000673115</v>
+        <v>30000974037</v>
       </c>
       <c r="N89" t="str">
         <v>State Bank of India</v>
@@ -5942,48 +5953,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P89" t="str">
-        <v>SBIN0008022</v>
+        <v>SBIN0002702</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>0300093</v>
+        <v>0300107</v>
       </c>
       <c r="B90" t="str">
-        <v>SANTOSH PRASAD</v>
+        <v>RAJESH ALAM</v>
       </c>
       <c r="C90" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D90" t="str">
-        <v>03046</v>
+        <v>03081</v>
       </c>
       <c r="E90" t="str">
-        <v>Block Office Sheohar</v>
+        <v>Central Bank of India, Dumri Katsari</v>
       </c>
       <c r="F90" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G90" t="str">
-        <v>9003000093</v>
+        <v>9003000107</v>
       </c>
       <c r="H90" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I90" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J90" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K90" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L90" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M90" t="str">
-        <v>30000736467</v>
+        <v>30000847333</v>
       </c>
       <c r="N90" t="str">
         <v>State Bank of India</v>
@@ -5992,48 +6003,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P90" t="str">
-        <v>SBIN0009257</v>
+        <v>SBIN0007957</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>0300074</v>
+        <v>0300087</v>
       </c>
       <c r="B91" t="str">
-        <v>FARHAT PASWAN</v>
+        <v>AJAY THAKUR S</v>
       </c>
       <c r="C91" t="str">
-        <v>Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D91" t="str">
-        <v>03046</v>
+        <v>03024</v>
       </c>
       <c r="E91" t="str">
-        <v>Block Office Sheohar</v>
+        <v>RWD Division (deputed from other district)</v>
       </c>
       <c r="F91" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G91" t="str">
-        <v>9003000074</v>
+        <v>9003000087</v>
       </c>
       <c r="H91" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I91" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J91" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K91" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="L91" t="str">
-        <v>Sheohar</v>
+        <v>Other District</v>
       </c>
       <c r="M91" t="str">
-        <v>30000586006</v>
+        <v>30000688953</v>
       </c>
       <c r="N91" t="str">
         <v>State Bank of India</v>
@@ -6042,48 +6053,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P91" t="str">
-        <v>SBIN0009908</v>
+        <v>SBIN0002070</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>0300057</v>
+        <v>0300001</v>
       </c>
       <c r="B92" t="str">
-        <v>VIJAY PASWAN</v>
+        <v>RAVI SHARMA</v>
       </c>
       <c r="C92" t="str">
-        <v>Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D92" t="str">
-        <v>03050</v>
+        <v>03001</v>
       </c>
       <c r="E92" t="str">
-        <v>Panchayat Bhawan Purnahiya No.2</v>
+        <v>Circle Office Piprahi No.1</v>
       </c>
       <c r="F92" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G92" t="str">
-        <v>9003000057</v>
+        <v>9003000001</v>
       </c>
       <c r="H92" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I92" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J92" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K92" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L92" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M92" t="str">
-        <v>30000451383</v>
+        <v>30000007919</v>
       </c>
       <c r="N92" t="str">
         <v>State Bank of India</v>
@@ -6092,30 +6103,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P92" t="str">
-        <v>SBIN0009799</v>
+        <v>SBIN0007384</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>0300071</v>
+        <v>0300084</v>
       </c>
       <c r="B93" t="str">
-        <v>ABDUL KALAM SINHA</v>
+        <v>POONAM GUPTA</v>
       </c>
       <c r="C93" t="str">
-        <v>Office Assistant</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D93" t="str">
-        <v>03039</v>
+        <v>03067</v>
       </c>
       <c r="E93" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>Block Education Office Dumri Katsari</v>
       </c>
       <c r="F93" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G93" t="str">
-        <v>9003000071</v>
+        <v>9003000084</v>
       </c>
       <c r="H93" t="str">
         <v>POLLING OFFICER-3</v>
@@ -6127,13 +6138,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K93" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L93" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M93" t="str">
-        <v>30000562249</v>
+        <v>30000665196</v>
       </c>
       <c r="N93" t="str">
         <v>State Bank of India</v>
@@ -6142,48 +6153,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P93" t="str">
-        <v>SBIN0001722</v>
+        <v>SBIN0002041</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>0300126</v>
+        <v>0300047</v>
       </c>
       <c r="B94" t="str">
-        <v>ANITA KUMAR</v>
+        <v>RANJIT JHA</v>
       </c>
       <c r="C94" t="str">
-        <v>Administrative Officer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D94" t="str">
-        <v>03096</v>
+        <v>03040</v>
       </c>
       <c r="E94" t="str">
-        <v>Head Post Office, Dumri Katsari</v>
+        <v>Kanya Middle School Sheohar No.2</v>
       </c>
       <c r="F94" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G94" t="str">
-        <v>9003000126</v>
+        <v>9003000047</v>
       </c>
       <c r="H94" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I94" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J94" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K94" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L94" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M94" t="str">
-        <v>30000997794</v>
+        <v>30000372193</v>
       </c>
       <c r="N94" t="str">
         <v>State Bank of India</v>
@@ -6192,48 +6203,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P94" t="str">
-        <v>SBIN0009575</v>
+        <v>SBIN0007154</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>0300016</v>
+        <v>0300060</v>
       </c>
       <c r="B95" t="str">
-        <v>AJAY YADAV</v>
+        <v>AMIT SAH</v>
       </c>
       <c r="C95" t="str">
-        <v>Section Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D95" t="str">
-        <v>03016</v>
+        <v>03049</v>
       </c>
       <c r="E95" t="str">
-        <v>Block Agriculture Office Piprahi No.2</v>
+        <v>CDPO Office Sheohar No.2</v>
       </c>
       <c r="F95" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G95" t="str">
-        <v>9003000016</v>
+        <v>9003000060</v>
       </c>
       <c r="H95" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I95" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J95" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K95" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L95" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M95" t="str">
-        <v>30000126704</v>
+        <v>30000475140</v>
       </c>
       <c r="N95" t="str">
         <v>State Bank of India</v>
@@ -6242,48 +6253,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P95" t="str">
-        <v>SBIN0005767</v>
+        <v>SBIN0002661</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>0300029</v>
+        <v>0300093</v>
       </c>
       <c r="B96" t="str">
-        <v>NEHA ALAM</v>
+        <v>DINESH PASWAN G</v>
       </c>
       <c r="C96" t="str">
-        <v>Assistant Teacher</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D96" t="str">
-        <v>03027</v>
+        <v>03011</v>
       </c>
       <c r="E96" t="str">
-        <v>Middle School Sheohar No.4</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="F96" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G96" t="str">
-        <v>9003000029</v>
+        <v>9003000093</v>
       </c>
       <c r="H96" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I96" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J96" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K96" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L96" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M96" t="str">
-        <v>30000229651</v>
+        <v>30000736467</v>
       </c>
       <c r="N96" t="str">
         <v>State Bank of India</v>
@@ -6292,33 +6303,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P96" t="str">
-        <v>SBIN0008276</v>
+        <v>SBIN0005349</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0300066</v>
+        <v>0300055</v>
       </c>
       <c r="B97" t="str">
-        <v>NASREEN RAM</v>
+        <v>AMIT RAI</v>
       </c>
       <c r="C97" t="str">
-        <v>Data Entry Operator</v>
+        <v>Teacher</v>
       </c>
       <c r="D97" t="str">
-        <v>03058</v>
+        <v>03044</v>
       </c>
       <c r="E97" t="str">
-        <v>Kanya Middle School Sheohar</v>
+        <v>Primary School Sheohar No.3</v>
       </c>
       <c r="F97" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G97" t="str">
-        <v>9003000066</v>
+        <v>9003000055</v>
       </c>
       <c r="H97" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I97" t="str">
         <v>0301</v>
@@ -6333,7 +6344,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M97" t="str">
-        <v>30000522654</v>
+        <v>30000435545</v>
       </c>
       <c r="N97" t="str">
         <v>State Bank of India</v>
@@ -6342,48 +6353,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P97" t="str">
-        <v>SBIN0001211</v>
+        <v>SBIN0002164</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>0300104</v>
+        <v>0300061</v>
       </c>
       <c r="B98" t="str">
-        <v>RINKU VERMA</v>
+        <v>RAKESH JHA</v>
       </c>
       <c r="C98" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D98" t="str">
-        <v>03078</v>
+        <v>03050</v>
       </c>
       <c r="E98" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>Block Office Tariyani No.4</v>
       </c>
       <c r="F98" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G98" t="str">
-        <v>9003000104</v>
+        <v>9003000061</v>
       </c>
       <c r="H98" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I98" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J98" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K98" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L98" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M98" t="str">
-        <v>30000823576</v>
+        <v>30000483059</v>
       </c>
       <c r="N98" t="str">
         <v>State Bank of India</v>
@@ -6392,48 +6403,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P98" t="str">
-        <v>SBIN0007514</v>
+        <v>SBIN0002248</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>0300068</v>
+        <v>0300012</v>
       </c>
       <c r="B99" t="str">
-        <v>SAVITA CHAUDHARY</v>
+        <v>PRIYANKA RAI</v>
       </c>
       <c r="C99" t="str">
-        <v>Clerk</v>
+        <v>Lecturer</v>
       </c>
       <c r="D99" t="str">
-        <v>03060</v>
+        <v>03012</v>
       </c>
       <c r="E99" t="str">
-        <v>Kanya Middle School Piprahi No.1</v>
+        <v>Block Office Sheohar No.3</v>
       </c>
       <c r="F99" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G99" t="str">
-        <v>9003000068</v>
+        <v>9003000012</v>
       </c>
       <c r="H99" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I99" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J99" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K99" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L99" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M99" t="str">
-        <v>30000538492</v>
+        <v>30000095028</v>
       </c>
       <c r="N99" t="str">
         <v>State Bank of India</v>
@@ -6442,48 +6453,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P99" t="str">
-        <v>SBIN0003011</v>
+        <v>SBIN0005887</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>0300005</v>
+        <v>0300073</v>
       </c>
       <c r="B100" t="str">
-        <v>PRAMOD PRASAD</v>
+        <v>FARHAT DEVI</v>
       </c>
       <c r="C100" t="str">
-        <v>Senior Teacher</v>
+        <v>Teacher</v>
       </c>
       <c r="D100" t="str">
-        <v>03005</v>
+        <v>03059</v>
       </c>
       <c r="E100" t="str">
-        <v>Kanya Middle School Dumri Katsari No.3</v>
+        <v>Kanya Middle School Sheohar No.1</v>
       </c>
       <c r="F100" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G100" t="str">
-        <v>9003000005</v>
+        <v>9003000073</v>
       </c>
       <c r="H100" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I100" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J100" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K100" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L100" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M100" t="str">
-        <v>30000039595</v>
+        <v>30000578087</v>
       </c>
       <c r="N100" t="str">
         <v>State Bank of India</v>
@@ -6492,33 +6503,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P100" t="str">
-        <v>SBIN0009557</v>
+        <v>SBIN0006398</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>0300060</v>
+        <v>0300031</v>
       </c>
       <c r="B101" t="str">
-        <v>NASREEN CHAUDHARY</v>
+        <v>KUMARI ANJALI KHATUN</v>
       </c>
       <c r="C101" t="str">
-        <v>Teacher</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D101" t="str">
-        <v>03052</v>
+        <v>03029</v>
       </c>
       <c r="E101" t="str">
-        <v>Circle Office Purnahiya No.3</v>
+        <v>PHC Purnahiya No.1</v>
       </c>
       <c r="F101" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G101" t="str">
-        <v>9003000060</v>
+        <v>9003000031</v>
       </c>
       <c r="H101" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I101" t="str">
         <v>0303</v>
@@ -6533,7 +6544,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M101" t="str">
-        <v>30000475140</v>
+        <v>30000245489</v>
       </c>
       <c r="N101" t="str">
         <v>State Bank of India</v>
@@ -6542,48 +6553,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P101" t="str">
-        <v>SBIN0007830</v>
+        <v>SBIN0007100</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>0300032</v>
+        <v>0300041</v>
       </c>
       <c r="B102" t="str">
-        <v>ANIL SHARMA</v>
+        <v>DINESH KUMAR</v>
       </c>
       <c r="C102" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D102" t="str">
-        <v>03030</v>
+        <v>03019</v>
       </c>
       <c r="E102" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>PHED Division (deputed from other district)</v>
       </c>
       <c r="F102" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G102" t="str">
-        <v>9003000032</v>
+        <v>9003000041</v>
       </c>
       <c r="H102" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I102" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J102" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K102" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="L102" t="str">
-        <v>Sheohar</v>
+        <v>Other District</v>
       </c>
       <c r="M102" t="str">
-        <v>30000253408</v>
+        <v>30000324679</v>
       </c>
       <c r="N102" t="str">
         <v>State Bank of India</v>
@@ -6592,48 +6603,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P102" t="str">
-        <v>SBIN0004761</v>
+        <v>SBIN0007855</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>0300102</v>
+        <v>0300079</v>
       </c>
       <c r="B103" t="str">
-        <v>FARHAT DEVI</v>
+        <v>MAHESH RAM</v>
       </c>
       <c r="C103" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D103" t="str">
-        <v>03074</v>
+        <v>03064</v>
       </c>
       <c r="E103" t="str">
-        <v>Block Office Tariyani</v>
+        <v>Block Office Piprahi No.4</v>
       </c>
       <c r="F103" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G103" t="str">
-        <v>9003000102</v>
+        <v>9003000079</v>
       </c>
       <c r="H103" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I103" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J103" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K103" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L103" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M103" t="str">
-        <v>30000807738</v>
+        <v>30000625601</v>
       </c>
       <c r="N103" t="str">
         <v>State Bank of India</v>
@@ -6642,39 +6653,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P103" t="str">
-        <v>SBIN0003674</v>
+        <v>SBIN0009296</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>0300121</v>
+        <v>0300014</v>
       </c>
       <c r="B104" t="str">
-        <v>MAMTA GUPTA</v>
+        <v>SHAILESH MISHRA</v>
       </c>
       <c r="C104" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D104" t="str">
-        <v>03091</v>
+        <v>03014</v>
       </c>
       <c r="E104" t="str">
-        <v>BSNL Exchange, Sheohar</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F104" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G104" t="str">
-        <v>9003000121</v>
+        <v>9003000014</v>
       </c>
       <c r="H104" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I104" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J104" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K104" t="str">
         <v>0301</v>
@@ -6683,7 +6694,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M104" t="str">
-        <v>30000958199</v>
+        <v>30000110866</v>
       </c>
       <c r="N104" t="str">
         <v>State Bank of India</v>
@@ -6692,33 +6703,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P104" t="str">
-        <v>SBIN0006103</v>
+        <v>SBIN0009030</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>0300039</v>
+        <v>0300008</v>
       </c>
       <c r="B105" t="str">
-        <v>ANIL ANSARI</v>
+        <v>AMIT VERMA</v>
       </c>
       <c r="C105" t="str">
-        <v>Senior Clerk</v>
+        <v>Headmaster</v>
       </c>
       <c r="D105" t="str">
-        <v>03035</v>
+        <v>03008</v>
       </c>
       <c r="E105" t="str">
-        <v>High School Purnahiya No.2</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F105" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G105" t="str">
-        <v>9003000039</v>
+        <v>9003000008</v>
       </c>
       <c r="H105" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I105" t="str">
         <v>0303</v>
@@ -6727,13 +6738,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K105" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L105" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M105" t="str">
-        <v>30000308841</v>
+        <v>30000063352</v>
       </c>
       <c r="N105" t="str">
         <v>State Bank of India</v>
@@ -6742,48 +6753,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P105" t="str">
-        <v>SBIN0005728</v>
+        <v>SBIN0005803</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>0300117</v>
+        <v>0300056</v>
       </c>
       <c r="B106" t="str">
-        <v>MD. SHAHID KHATUN</v>
+        <v>PRAMOD SAH</v>
       </c>
       <c r="C106" t="str">
-        <v>Postmaster</v>
+        <v>Clerk</v>
       </c>
       <c r="D106" t="str">
-        <v>03088</v>
+        <v>03045</v>
       </c>
       <c r="E106" t="str">
-        <v>Central Bank of India, Purnahiya</v>
+        <v>Panchayat Bhawan Sheohar</v>
       </c>
       <c r="F106" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G106" t="str">
-        <v>9003000117</v>
+        <v>9003000056</v>
       </c>
       <c r="H106" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I106" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J106" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K106" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L106" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M106" t="str">
-        <v>30000926523</v>
+        <v>30000443464</v>
       </c>
       <c r="N106" t="str">
         <v>State Bank of India</v>
@@ -6792,48 +6803,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P106" t="str">
-        <v>SBIN0003112</v>
+        <v>SBIN0004128</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>0300103</v>
+        <v>0300029</v>
       </c>
       <c r="B107" t="str">
-        <v>AJAY KUMAR</v>
+        <v>SURESH RAI</v>
       </c>
       <c r="C107" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D107" t="str">
-        <v>03040</v>
+        <v>03027</v>
       </c>
       <c r="E107" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>High School Piprahi</v>
       </c>
       <c r="F107" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G107" t="str">
-        <v>9003000103</v>
+        <v>9003000029</v>
       </c>
       <c r="H107" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I107" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J107" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K107" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L107" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M107" t="str">
-        <v>30000815657</v>
+        <v>30000229651</v>
       </c>
       <c r="N107" t="str">
         <v>State Bank of India</v>
@@ -6842,39 +6853,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P107" t="str">
-        <v>SBIN0005901</v>
+        <v>SBIN0005618</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>0300006</v>
+        <v>0300102</v>
       </c>
       <c r="B108" t="str">
-        <v>REKHA MISHRA</v>
+        <v>USHA PANDEY</v>
       </c>
       <c r="C108" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D108" t="str">
-        <v>03006</v>
+        <v>03075</v>
       </c>
       <c r="E108" t="str">
-        <v>Block Education Office Sheohar No.2</v>
+        <v>Circle Office Sheohar</v>
       </c>
       <c r="F108" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G108" t="str">
-        <v>9003000006</v>
+        <v>9003000102</v>
       </c>
       <c r="H108" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I108" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J108" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K108" t="str">
         <v>0301</v>
@@ -6883,7 +6894,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M108" t="str">
-        <v>30000047514</v>
+        <v>30000807738</v>
       </c>
       <c r="N108" t="str">
         <v>State Bank of India</v>
@@ -6892,48 +6903,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P108" t="str">
-        <v>SBIN0009822</v>
+        <v>SBIN0006329</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>0300012</v>
+        <v>0300040</v>
       </c>
       <c r="B109" t="str">
-        <v>ARVIND SAH</v>
+        <v>SAVITA JHA</v>
       </c>
       <c r="C109" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D109" t="str">
-        <v>03012</v>
+        <v>03027</v>
       </c>
       <c r="E109" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>High School Piprahi</v>
       </c>
       <c r="F109" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G109" t="str">
-        <v>9003000012</v>
+        <v>9003000040</v>
       </c>
       <c r="H109" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I109" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J109" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K109" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L109" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M109" t="str">
-        <v>30000095028</v>
+        <v>30000316760</v>
       </c>
       <c r="N109" t="str">
         <v>State Bank of India</v>
@@ -6942,39 +6953,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P109" t="str">
-        <v>SBIN0005292</v>
+        <v>SBIN0002466</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>0300067</v>
+        <v>0300113</v>
       </c>
       <c r="B110" t="str">
-        <v>MD. SHAHID SINGH</v>
+        <v>PRAMOD PANDEY</v>
       </c>
       <c r="C110" t="str">
-        <v>Teacher</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D110" t="str">
-        <v>03059</v>
+        <v>03085</v>
       </c>
       <c r="E110" t="str">
-        <v>CDPO Office Piprahi No.1</v>
+        <v>Head Post Office, Piprahi</v>
       </c>
       <c r="F110" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G110" t="str">
-        <v>9003000067</v>
+        <v>9003000113</v>
       </c>
       <c r="H110" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I110" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J110" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K110" t="str">
         <v>0302</v>
@@ -6983,7 +6994,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M110" t="str">
-        <v>30000530573</v>
+        <v>30000894847</v>
       </c>
       <c r="N110" t="str">
         <v>State Bank of India</v>
@@ -6992,48 +7003,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P110" t="str">
-        <v>SBIN0006480</v>
+        <v>SBIN0007349</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>0300053</v>
+        <v>0300070</v>
       </c>
       <c r="B111" t="str">
-        <v>MD. IRFAN OJHA</v>
+        <v>ARVIND KHATUN</v>
       </c>
       <c r="C111" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Clerk</v>
       </c>
       <c r="D111" t="str">
-        <v>03043</v>
+        <v>03010</v>
       </c>
       <c r="E111" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>Block Office Tariyani No.2</v>
       </c>
       <c r="F111" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G111" t="str">
-        <v>9003000053</v>
+        <v>9003000070</v>
       </c>
       <c r="H111" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I111" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J111" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K111" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L111" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M111" t="str">
-        <v>30000419707</v>
+        <v>30000554330</v>
       </c>
       <c r="N111" t="str">
         <v>State Bank of India</v>
@@ -7042,33 +7053,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P111" t="str">
-        <v>SBIN0001742</v>
+        <v>SBIN0002886</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>0300125</v>
+        <v>0300075</v>
       </c>
       <c r="B112" t="str">
-        <v>ARVIND SAH K</v>
+        <v>SHAILESH MAHTO</v>
       </c>
       <c r="C112" t="str">
-        <v>Branch Manager</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D112" t="str">
-        <v>03095</v>
+        <v>03007</v>
       </c>
       <c r="E112" t="str">
-        <v>UCO Bank, Purnahiya</v>
+        <v>Middle School Piprahi No.3</v>
       </c>
       <c r="F112" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G112" t="str">
-        <v>9003000125</v>
+        <v>9003000075</v>
       </c>
       <c r="H112" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I112" t="str">
         <v>0303</v>
@@ -7077,13 +7088,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K112" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L112" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M112" t="str">
-        <v>30000989875</v>
+        <v>30000593925</v>
       </c>
       <c r="N112" t="str">
         <v>State Bank of India</v>
@@ -7092,48 +7103,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P112" t="str">
-        <v>SBIN0002687</v>
+        <v>SBIN0005476</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>0300080</v>
+        <v>0300121</v>
       </c>
       <c r="B113" t="str">
-        <v>SANJAY PANDEY</v>
+        <v>PRIYANKA DEVI</v>
       </c>
       <c r="C113" t="str">
-        <v>Teacher</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D113" t="str">
-        <v>03067</v>
+        <v>03092</v>
       </c>
       <c r="E113" t="str">
-        <v>Block Office Sheohar No.1</v>
+        <v>LIC Branch Office, Purnahiya</v>
       </c>
       <c r="F113" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G113" t="str">
-        <v>9003000080</v>
+        <v>9003000121</v>
       </c>
       <c r="H113" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I113" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J113" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K113" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L113" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M113" t="str">
-        <v>30000633520</v>
+        <v>30000958199</v>
       </c>
       <c r="N113" t="str">
         <v>State Bank of India</v>
@@ -7142,48 +7153,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P113" t="str">
-        <v>SBIN0006100</v>
+        <v>SBIN0006764</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>0300062</v>
+        <v>0300003</v>
       </c>
       <c r="B114" t="str">
-        <v>NASREEN PRASAD</v>
+        <v>RANJIT SINGH</v>
       </c>
       <c r="C114" t="str">
-        <v>Accountant</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D114" t="str">
-        <v>03054</v>
+        <v>03003</v>
       </c>
       <c r="E114" t="str">
-        <v>Kanya Middle School Dumri Katsari No.4</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F114" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G114" t="str">
-        <v>9003000062</v>
+        <v>9003000003</v>
       </c>
       <c r="H114" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I114" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J114" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K114" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L114" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M114" t="str">
-        <v>30000490978</v>
+        <v>30000023757</v>
       </c>
       <c r="N114" t="str">
         <v>State Bank of India</v>
@@ -7192,48 +7203,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P114" t="str">
-        <v>SBIN0007867</v>
+        <v>SBIN0001939</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>0300064</v>
+        <v>0300005</v>
       </c>
       <c r="B115" t="str">
-        <v>NIRMALA ALAM</v>
+        <v>DINESH YADAV</v>
       </c>
       <c r="C115" t="str">
-        <v>Office Assistant</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D115" t="str">
-        <v>03056</v>
+        <v>03005</v>
       </c>
       <c r="E115" t="str">
-        <v>Block Agriculture Office Tariyani No.1</v>
+        <v>Circle Office Piprahi No.3</v>
       </c>
       <c r="F115" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G115" t="str">
-        <v>9003000064</v>
+        <v>9003000005</v>
       </c>
       <c r="H115" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I115" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J115" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K115" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L115" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M115" t="str">
-        <v>30000506816</v>
+        <v>30000039595</v>
       </c>
       <c r="N115" t="str">
         <v>State Bank of India</v>
@@ -7242,48 +7253,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P115" t="str">
-        <v>SBIN0007820</v>
+        <v>SBIN0009541</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>0300091</v>
+        <v>0300092</v>
       </c>
       <c r="B116" t="str">
-        <v>RAKESH KHATUN</v>
+        <v>SANTOSH MISHRA</v>
       </c>
       <c r="C116" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D116" t="str">
-        <v>03074</v>
+        <v>03072</v>
       </c>
       <c r="E116" t="str">
-        <v>Block Office Tariyani</v>
+        <v>RWD Sub-Division Dumri Katsari</v>
       </c>
       <c r="F116" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G116" t="str">
-        <v>9003000091</v>
+        <v>9003000092</v>
       </c>
       <c r="H116" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I116" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J116" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K116" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L116" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M116" t="str">
-        <v>30000720629</v>
+        <v>30000728548</v>
       </c>
       <c r="N116" t="str">
         <v>State Bank of India</v>
@@ -7292,48 +7303,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P116" t="str">
-        <v>SBIN0004144</v>
+        <v>SBIN0003279</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>0300014</v>
+        <v>0300034</v>
       </c>
       <c r="B117" t="str">
-        <v>NEHA PRASAD</v>
+        <v>NIRMALA ALAM</v>
       </c>
       <c r="C117" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D117" t="str">
-        <v>03014</v>
+        <v>03032</v>
       </c>
       <c r="E117" t="str">
-        <v>Block Office Dumri Katsari No.4</v>
+        <v>Project Girls High School Tariyani No.1</v>
       </c>
       <c r="F117" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G117" t="str">
-        <v>9003000014</v>
+        <v>9003000034</v>
       </c>
       <c r="H117" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I117" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J117" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K117" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L117" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M117" t="str">
-        <v>30000110866</v>
+        <v>30000269246</v>
       </c>
       <c r="N117" t="str">
         <v>State Bank of India</v>
@@ -7342,48 +7353,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P117" t="str">
-        <v>SBIN0004424</v>
+        <v>SBIN0008615</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>0300038</v>
+        <v>0300103</v>
       </c>
       <c r="B118" t="str">
-        <v>MD. SHAHID VERMA</v>
+        <v>AJAY MISHRA</v>
       </c>
       <c r="C118" t="str">
-        <v>Assistant Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D118" t="str">
-        <v>03030</v>
+        <v>03078</v>
       </c>
       <c r="E118" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F118" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G118" t="str">
-        <v>9003000038</v>
+        <v>9003000103</v>
       </c>
       <c r="H118" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I118" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J118" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K118" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L118" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M118" t="str">
-        <v>30000300922</v>
+        <v>30000815657</v>
       </c>
       <c r="N118" t="str">
         <v>State Bank of India</v>
@@ -7392,48 +7403,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P118" t="str">
-        <v>SBIN0004403</v>
+        <v>SBIN0008678</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>0300073</v>
+        <v>0300050</v>
       </c>
       <c r="B119" t="str">
-        <v>VINOD YADAV</v>
+        <v>DINESH PASWAN V</v>
       </c>
       <c r="C119" t="str">
-        <v>Office Assistant</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D119" t="str">
-        <v>03018</v>
+        <v>03026</v>
       </c>
       <c r="E119" t="str">
-        <v>High School Tariyani No.2</v>
+        <v>Project Girls High School Dumri Katsari</v>
       </c>
       <c r="F119" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G119" t="str">
-        <v>9003000073</v>
+        <v>9003000050</v>
       </c>
       <c r="H119" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I119" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J119" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K119" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L119" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M119" t="str">
-        <v>30000578087</v>
+        <v>30000395950</v>
       </c>
       <c r="N119" t="str">
         <v>State Bank of India</v>
@@ -7442,39 +7453,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P119" t="str">
-        <v>SBIN0001831</v>
+        <v>SBIN0009287</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>0300119</v>
+        <v>0300054</v>
       </c>
       <c r="B120" t="str">
-        <v>SANTOSH DEVI</v>
+        <v>UMESH DEVI</v>
       </c>
       <c r="C120" t="str">
-        <v>Assistant Manager</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D120" t="str">
-        <v>03083</v>
+        <v>03037</v>
       </c>
       <c r="E120" t="str">
-        <v>LIC Branch Office, Dumri Katsari</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="F120" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G120" t="str">
-        <v>9003000119</v>
+        <v>9003000054</v>
       </c>
       <c r="H120" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I120" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J120" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K120" t="str">
         <v>0304</v>
@@ -7483,7 +7494,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M120" t="str">
-        <v>30000942361</v>
+        <v>30000427626</v>
       </c>
       <c r="N120" t="str">
         <v>State Bank of India</v>
@@ -7492,48 +7503,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P120" t="str">
-        <v>SBIN0006114</v>
+        <v>SBIN0001571</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>0300099</v>
+        <v>0300020</v>
       </c>
       <c r="B121" t="str">
-        <v>DINESH MAHTO</v>
+        <v>ASHA PRASAD</v>
       </c>
       <c r="C121" t="str">
-        <v>Assistant Engineer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D121" t="str">
-        <v>03007</v>
+        <v>03020</v>
       </c>
       <c r="E121" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Block Education Office Tariyani</v>
       </c>
       <c r="F121" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G121" t="str">
-        <v>9003000099</v>
+        <v>9003000020</v>
       </c>
       <c r="H121" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I121" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J121" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K121" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L121" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M121" t="str">
-        <v>30000783981</v>
+        <v>30000158380</v>
       </c>
       <c r="N121" t="str">
         <v>State Bank of India</v>
@@ -7542,48 +7553,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P121" t="str">
-        <v>SBIN0001517</v>
+        <v>SBIN0005227</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>0300082</v>
+        <v>0300115</v>
       </c>
       <c r="B122" t="str">
-        <v>REKHA CHAUDHARY</v>
+        <v>RINKU YADAV</v>
       </c>
       <c r="C122" t="str">
-        <v>Teacher</v>
+        <v>Postmaster</v>
       </c>
       <c r="D122" t="str">
-        <v>03069</v>
+        <v>03086</v>
       </c>
       <c r="E122" t="str">
-        <v>High School Purnahiya No.4</v>
+        <v>Bank of India, Piprahi</v>
       </c>
       <c r="F122" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G122" t="str">
-        <v>9003000082</v>
+        <v>9003000115</v>
       </c>
       <c r="H122" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I122" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J122" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K122" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L122" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M122" t="str">
-        <v>30000649358</v>
+        <v>30000910685</v>
       </c>
       <c r="N122" t="str">
         <v>State Bank of India</v>
@@ -7592,39 +7603,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P122" t="str">
-        <v>SBIN0005400</v>
+        <v>SBIN0004243</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>0300069</v>
+        <v>0300117</v>
       </c>
       <c r="B123" t="str">
-        <v>SUNIL PASWAN</v>
+        <v>MD. SHAHID ALAM</v>
       </c>
       <c r="C123" t="str">
-        <v>Data Entry Operator</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D123" t="str">
-        <v>03061</v>
+        <v>03088</v>
       </c>
       <c r="E123" t="str">
-        <v>Block Education Office Sheohar No.1</v>
+        <v>Central Bank of India, Sheohar</v>
       </c>
       <c r="F123" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G123" t="str">
-        <v>9003000069</v>
+        <v>9003000117</v>
       </c>
       <c r="H123" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I123" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J123" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K123" t="str">
         <v>0301</v>
@@ -7633,7 +7644,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M123" t="str">
-        <v>30000546411</v>
+        <v>30000926523</v>
       </c>
       <c r="N123" t="str">
         <v>State Bank of India</v>
@@ -7642,30 +7653,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P123" t="str">
-        <v>SBIN0007734</v>
+        <v>SBIN0007368</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>0300052</v>
+        <v>0300057</v>
       </c>
       <c r="B124" t="str">
-        <v>NITISH JHA</v>
+        <v>NIRMALA MISHRA</v>
       </c>
       <c r="C124" t="str">
-        <v>Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D124" t="str">
-        <v>03039</v>
+        <v>03046</v>
       </c>
       <c r="E124" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>Middle School Sheohar No.3</v>
       </c>
       <c r="F124" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G124" t="str">
-        <v>9003000052</v>
+        <v>9003000057</v>
       </c>
       <c r="H124" t="str">
         <v>POLLING OFFICER-2</v>
@@ -7683,7 +7694,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M124" t="str">
-        <v>30000411788</v>
+        <v>30000451383</v>
       </c>
       <c r="N124" t="str">
         <v>State Bank of India</v>
@@ -7692,39 +7703,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P124" t="str">
-        <v>SBIN0006306</v>
+        <v>SBIN0006094</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>0300055</v>
+        <v>0300045</v>
       </c>
       <c r="B125" t="str">
-        <v>REKHA KHATUN</v>
+        <v>REKHA VERMA</v>
       </c>
       <c r="C125" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Teacher</v>
       </c>
       <c r="D125" t="str">
-        <v>03048</v>
+        <v>03038</v>
       </c>
       <c r="E125" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>CDPO Office Sheohar No.1</v>
       </c>
       <c r="F125" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G125" t="str">
-        <v>9003000055</v>
+        <v>9003000045</v>
       </c>
       <c r="H125" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I125" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J125" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K125" t="str">
         <v>0301</v>
@@ -7733,7 +7744,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M125" t="str">
-        <v>30000435545</v>
+        <v>30000356355</v>
       </c>
       <c r="N125" t="str">
         <v>State Bank of India</v>
@@ -7742,48 +7753,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P125" t="str">
-        <v>SBIN0002875</v>
+        <v>SBIN0004190</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>0300008</v>
+        <v>0300118</v>
       </c>
       <c r="B126" t="str">
-        <v>RAMESH TIWARI</v>
+        <v>NIRMALA PANDEY</v>
       </c>
       <c r="C126" t="str">
-        <v>Headmaster</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D126" t="str">
-        <v>03008</v>
+        <v>03089</v>
       </c>
       <c r="E126" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>LIC Branch Office, Piprahi</v>
       </c>
       <c r="F126" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G126" t="str">
-        <v>9003000008</v>
+        <v>9003000118</v>
       </c>
       <c r="H126" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I126" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J126" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K126" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L126" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M126" t="str">
-        <v>30000063352</v>
+        <v>30000934442</v>
       </c>
       <c r="N126" t="str">
         <v>State Bank of India</v>
@@ -7792,48 +7803,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P126" t="str">
-        <v>SBIN0009950</v>
+        <v>SBIN0007981</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>0300105</v>
+        <v>0300032</v>
       </c>
       <c r="B127" t="str">
-        <v>SURESH RAI</v>
+        <v>UMESH YADAV</v>
       </c>
       <c r="C127" t="str">
-        <v>Junior Engineer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D127" t="str">
-        <v>03071</v>
+        <v>03030</v>
       </c>
       <c r="E127" t="str">
-        <v>RWD Sub-Division Sheohar</v>
+        <v>Panchayat Bhawan Dumri Katsari No.2</v>
       </c>
       <c r="F127" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G127" t="str">
-        <v>9003000105</v>
+        <v>9003000032</v>
       </c>
       <c r="H127" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I127" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J127" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K127" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L127" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M127" t="str">
-        <v>30000831495</v>
+        <v>30000253408</v>
       </c>
       <c r="N127" t="str">
         <v>State Bank of India</v>
@@ -7842,7 +7853,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P127" t="str">
-        <v>SBIN0001809</v>
+        <v>SBIN0006648</v>
       </c>
     </row>
   </sheetData>
@@ -7895,7 +7906,7 @@
         <v>Main</v>
       </c>
       <c r="D2" t="str">
-        <v>Middle School Sheohar, Room 2</v>
+        <v>Kanya Middle School Sheohar, Room 2</v>
       </c>
       <c r="E2" t="str">
         <v>0301</v>
@@ -7915,7 +7926,7 @@
         <v>Main</v>
       </c>
       <c r="D3" t="str">
-        <v>High School Piprahi, Room 3</v>
+        <v>Kanya Middle School Piprahi, Room 3</v>
       </c>
       <c r="E3" t="str">
         <v>0302</v>
@@ -7955,7 +7966,7 @@
         <v>Main</v>
       </c>
       <c r="D5" t="str">
-        <v>Kanya Middle School Dumri Katsari, Room 2</v>
+        <v>Block Office Hall Dumri Katsari, Room 2</v>
       </c>
       <c r="E5" t="str">
         <v>0304</v>
@@ -7975,7 +7986,7 @@
         <v>Main</v>
       </c>
       <c r="D6" t="str">
-        <v>High School Tariyani, Room 3</v>
+        <v>Kanya Middle School Tariyani, Room 3</v>
       </c>
       <c r="E6" t="str">
         <v>0305</v>
@@ -7995,7 +8006,7 @@
         <v>Main</v>
       </c>
       <c r="D7" t="str">
-        <v>Block Office Hall Sheohar, Room 1</v>
+        <v>Kanya Middle School Sheohar, Room 1</v>
       </c>
       <c r="E7" t="str">
         <v>0301</v>
@@ -8015,7 +8026,7 @@
         <v>Main</v>
       </c>
       <c r="D8" t="str">
-        <v>Block Office Hall Purnahiya, Room 2</v>
+        <v>Panchayat Bhawan Purnahiya, Room 2</v>
       </c>
       <c r="E8" t="str">
         <v>0303</v>
@@ -8055,7 +8066,7 @@
         <v>Main</v>
       </c>
       <c r="D10" t="str">
-        <v>Kanya Middle School Tariyani, Room 1</v>
+        <v>Panchayat Bhawan Tariyani, Room 1</v>
       </c>
       <c r="E10" t="str">
         <v>0305</v>
@@ -8075,7 +8086,7 @@
         <v>Main</v>
       </c>
       <c r="D11" t="str">
-        <v>High School Sheohar, Room 2</v>
+        <v>Block Office Hall Sheohar, Room 2</v>
       </c>
       <c r="E11" t="str">
         <v>0301</v>
@@ -8095,7 +8106,7 @@
         <v>Main</v>
       </c>
       <c r="D12" t="str">
-        <v>Middle School Piprahi, Room 3</v>
+        <v>Panchayat Bhawan Piprahi, Room 3</v>
       </c>
       <c r="E12" t="str">
         <v>0302</v>
@@ -8115,7 +8126,7 @@
         <v>Main</v>
       </c>
       <c r="D13" t="str">
-        <v>Block Office Hall Purnahiya, Room 1</v>
+        <v>Panchayat Bhawan Purnahiya, Room 1</v>
       </c>
       <c r="E13" t="str">
         <v>0303</v>

--- a/test-data/TEST_Sheohar_Project.xlsx
+++ b/test-data/TEST_Sheohar_Project.xlsx
@@ -16,7 +16,8 @@
     <sheet name="Final_PCCP" sheetId="11" r:id="rId11"/>
     <sheet name="Final_Micro" sheetId="12" r:id="rId12"/>
     <sheet name="Status" sheetId="13" r:id="rId13"/>
-    <sheet name="Audit_Log" sheetId="14" r:id="rId14"/>
+    <sheet name="Exemptions" sheetId="14" r:id="rId14"/>
+    <sheet name="Audit_Log" sheetId="15" r:id="rId15"/>
   </sheets>
 </workbook>
 </file>
@@ -612,7 +613,7 @@
         <v>Saved at</v>
       </c>
       <c r="B4" t="str">
-        <v>13-10-2026 06:03:26</v>
+        <v>13-10-2026 06:16:05</v>
       </c>
     </row>
     <row r="5">
@@ -727,6 +728,53 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H1"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="50.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PIN</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Duty</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Reason</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Order Ref</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Recorded At</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
   <cols>
@@ -744,7 +792,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>13-10-2026 06:03:26</v>
+        <v>13-10-2026 06:16:05</v>
       </c>
       <c r="B2" t="str">
         <v>Test data generated (Small — Sheohar style (5 blocks, 6 TC + 6 GC booths))</v>
@@ -1558,34 +1606,34 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0300086</v>
+        <v>0300057</v>
       </c>
       <c r="B2" t="str">
-        <v>ANIL ANSARI</v>
+        <v>NIRMALA PRASAD</v>
       </c>
       <c r="C2" t="str">
-        <v>Junior Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D2" t="str">
-        <v>03069</v>
+        <v>03048</v>
       </c>
       <c r="E2" t="str">
-        <v>Minor Irrigation Office Sheohar</v>
+        <v>Project Girls High School Sheohar</v>
       </c>
       <c r="F2" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G2" t="str">
-        <v>9003000086</v>
+        <v>9003000057</v>
       </c>
       <c r="H2" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I2" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J2" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K2" t="str">
         <v>0301</v>
@@ -1594,7 +1642,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M2" t="str">
-        <v>30000681034</v>
+        <v>30000451383</v>
       </c>
       <c r="N2" t="str">
         <v>State Bank of India</v>
@@ -1603,33 +1651,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P2" t="str">
-        <v>SBIN0007358</v>
+        <v>SBIN0003106</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0300119</v>
+        <v>0300054</v>
       </c>
       <c r="B3" t="str">
-        <v>UMESH THAKUR</v>
+        <v>RAJESH KHATUN J</v>
       </c>
       <c r="C3" t="str">
-        <v>Postmaster</v>
+        <v>Clerk</v>
       </c>
       <c r="D3" t="str">
-        <v>03090</v>
+        <v>03045</v>
       </c>
       <c r="E3" t="str">
-        <v>Punjab National Bank, Piprahi</v>
+        <v>Project Girls High School Sheohar No.1</v>
       </c>
       <c r="F3" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G3" t="str">
-        <v>9003000119</v>
+        <v>9003000054</v>
       </c>
       <c r="H3" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I3" t="str">
         <v>0301</v>
@@ -1638,13 +1686,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K3" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L3" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M3" t="str">
-        <v>30000942361</v>
+        <v>30000427626</v>
       </c>
       <c r="N3" t="str">
         <v>State Bank of India</v>
@@ -1653,33 +1701,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P3" t="str">
-        <v>SBIN0003269</v>
+        <v>SBIN0004951</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0300023</v>
+        <v>0300047</v>
       </c>
       <c r="B4" t="str">
-        <v>FARHAT MAHTO</v>
+        <v>MANOJ VERMA</v>
       </c>
       <c r="C4" t="str">
-        <v>Head Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D4" t="str">
-        <v>03022</v>
+        <v>03039</v>
       </c>
       <c r="E4" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Kanya Middle School Piprahi No.1</v>
       </c>
       <c r="F4" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G4" t="str">
-        <v>9003000023</v>
+        <v>9003000047</v>
       </c>
       <c r="H4" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I4" t="str">
         <v>0301</v>
@@ -1688,13 +1736,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K4" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L4" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M4" t="str">
-        <v>30000182137</v>
+        <v>30000372193</v>
       </c>
       <c r="N4" t="str">
         <v>State Bank of India</v>
@@ -1703,48 +1751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P4" t="str">
-        <v>SBIN0008583</v>
+        <v>SBIN0004755</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0300043</v>
+        <v>0300007</v>
       </c>
       <c r="B5" t="str">
-        <v>VIJAY SINHA</v>
+        <v>SUNITA OJHA</v>
       </c>
       <c r="C5" t="str">
-        <v>Clerk</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D5" t="str">
-        <v>03036</v>
+        <v>03007</v>
       </c>
       <c r="E5" t="str">
-        <v>Block Office Dumri Katsari No.2</v>
+        <v>PHED Division (deputed from other district)</v>
       </c>
       <c r="F5" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G5" t="str">
-        <v>9003000043</v>
+        <v>9003000007</v>
       </c>
       <c r="H5" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I5" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J5" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K5" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="L5" t="str">
-        <v>Dumri Katsari</v>
+        <v>Other District</v>
       </c>
       <c r="M5" t="str">
-        <v>30000340517</v>
+        <v>30000055433</v>
       </c>
       <c r="N5" t="str">
         <v>State Bank of India</v>
@@ -1753,48 +1801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P5" t="str">
-        <v>SBIN0008107</v>
+        <v>SBIN0002916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0300104</v>
+        <v>0300001</v>
       </c>
       <c r="B6" t="str">
-        <v>SHAILESH THAKUR</v>
+        <v>PANKAJ VERMA</v>
       </c>
       <c r="C6" t="str">
-        <v>Assistant Engineer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D6" t="str">
-        <v>03079</v>
+        <v>03001</v>
       </c>
       <c r="E6" t="str">
-        <v>Minor Irrigation Office Tariyani</v>
+        <v>Panchayat Bhawan Sheohar No.1</v>
       </c>
       <c r="F6" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G6" t="str">
-        <v>9003000104</v>
+        <v>9003000001</v>
       </c>
       <c r="H6" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I6" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J6" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K6" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L6" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M6" t="str">
-        <v>30000823576</v>
+        <v>30000007919</v>
       </c>
       <c r="N6" t="str">
         <v>State Bank of India</v>
@@ -1803,48 +1851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P6" t="str">
-        <v>SBIN0004649</v>
+        <v>SBIN0001153</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>0300096</v>
+        <v>0300011</v>
       </c>
       <c r="B7" t="str">
-        <v>MAMTA RAI</v>
+        <v>NITISH VERMA</v>
       </c>
       <c r="C7" t="str">
-        <v>Assistant Engineer</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D7" t="str">
-        <v>03054</v>
+        <v>03011</v>
       </c>
       <c r="E7" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>PHC Dumri Katsari No.1</v>
       </c>
       <c r="F7" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G7" t="str">
-        <v>9003000096</v>
+        <v>9003000011</v>
       </c>
       <c r="H7" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I7" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J7" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K7" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L7" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M7" t="str">
-        <v>30000760224</v>
+        <v>30000087109</v>
       </c>
       <c r="N7" t="str">
         <v>State Bank of India</v>
@@ -1853,33 +1901,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P7" t="str">
-        <v>SBIN0004089</v>
+        <v>SBIN0006988</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0300049</v>
+        <v>0300041</v>
       </c>
       <c r="B8" t="str">
-        <v>MUKESH SINHA</v>
+        <v>ALOK KUMAR</v>
       </c>
       <c r="C8" t="str">
-        <v>Accountant</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D8" t="str">
-        <v>03041</v>
+        <v>03020</v>
       </c>
       <c r="E8" t="str">
-        <v>High School Purnahiya</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F8" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G8" t="str">
-        <v>9003000049</v>
+        <v>9003000041</v>
       </c>
       <c r="H8" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I8" t="str">
         <v>0301</v>
@@ -1888,13 +1936,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K8" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L8" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M8" t="str">
-        <v>30000388031</v>
+        <v>30000324679</v>
       </c>
       <c r="N8" t="str">
         <v>State Bank of India</v>
@@ -1903,39 +1951,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P8" t="str">
-        <v>SBIN0002615</v>
+        <v>SBIN0008520</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0300100</v>
+        <v>0300037</v>
       </c>
       <c r="B9" t="str">
-        <v>DEEPAK RAI</v>
+        <v>VIJAY THAKUR</v>
       </c>
       <c r="C9" t="str">
-        <v>Junior Engineer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D9" t="str">
-        <v>03069</v>
+        <v>03032</v>
       </c>
       <c r="E9" t="str">
-        <v>Minor Irrigation Office Sheohar</v>
+        <v>PHED Division Sheohar</v>
       </c>
       <c r="F9" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G9" t="str">
-        <v>9003000100</v>
+        <v>9003000037</v>
       </c>
       <c r="H9" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I9" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J9" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K9" t="str">
         <v>0301</v>
@@ -1944,7 +1992,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M9" t="str">
-        <v>30000791900</v>
+        <v>30000293003</v>
       </c>
       <c r="N9" t="str">
         <v>State Bank of India</v>
@@ -1953,39 +2001,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P9" t="str">
-        <v>SBIN0003306</v>
+        <v>SBIN0006108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0300024</v>
+        <v>0300065</v>
       </c>
       <c r="B10" t="str">
-        <v>MD. SHAHID SINGH</v>
+        <v>REKHA THAKUR</v>
       </c>
       <c r="C10" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Teacher</v>
       </c>
       <c r="D10" t="str">
-        <v>03023</v>
+        <v>03053</v>
       </c>
       <c r="E10" t="str">
-        <v>PHC Purnahiya No.4</v>
+        <v>Block Agriculture Office Purnahiya No.1</v>
       </c>
       <c r="F10" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G10" t="str">
-        <v>9003000024</v>
+        <v>9003000065</v>
       </c>
       <c r="H10" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I10" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J10" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K10" t="str">
         <v>0303</v>
@@ -1994,7 +2042,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M10" t="str">
-        <v>30000190056</v>
+        <v>30000514735</v>
       </c>
       <c r="N10" t="str">
         <v>State Bank of India</v>
@@ -2003,48 +2051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P10" t="str">
-        <v>SBIN0002071</v>
+        <v>SBIN0004771</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>0300021</v>
+        <v>0300078</v>
       </c>
       <c r="B11" t="str">
-        <v>NITISH CHAUDHARY</v>
+        <v>FARHAT RAI</v>
       </c>
       <c r="C11" t="str">
-        <v>Section Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D11" t="str">
-        <v>03021</v>
+        <v>03064</v>
       </c>
       <c r="E11" t="str">
-        <v>High School Tariyani No.4</v>
+        <v>Circle Office Piprahi No.4</v>
       </c>
       <c r="F11" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G11" t="str">
-        <v>9003000021</v>
+        <v>9003000078</v>
       </c>
       <c r="H11" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I11" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J11" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K11" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L11" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M11" t="str">
-        <v>30000166299</v>
+        <v>30000617682</v>
       </c>
       <c r="N11" t="str">
         <v>State Bank of India</v>
@@ -2053,33 +2101,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P11" t="str">
-        <v>SBIN0007720</v>
+        <v>SBIN0008320</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>0300069</v>
+        <v>0300117</v>
       </c>
       <c r="B12" t="str">
-        <v>MD. IRFAN YADAV</v>
+        <v>MD. SHAHID KUMAR</v>
       </c>
       <c r="C12" t="str">
-        <v>Teacher</v>
+        <v>Postmaster</v>
       </c>
       <c r="D12" t="str">
-        <v>03056</v>
+        <v>03088</v>
       </c>
       <c r="E12" t="str">
-        <v>PHC Dumri Katsari No.3</v>
+        <v>LIC Branch Office, Dumri Katsari</v>
       </c>
       <c r="F12" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G12" t="str">
-        <v>9003000069</v>
+        <v>9003000117</v>
       </c>
       <c r="H12" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I12" t="str">
         <v>0304</v>
@@ -2094,7 +2142,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M12" t="str">
-        <v>30000546411</v>
+        <v>30000926523</v>
       </c>
       <c r="N12" t="str">
         <v>State Bank of India</v>
@@ -2103,48 +2151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P12" t="str">
-        <v>SBIN0002247</v>
+        <v>SBIN0008998</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0300025</v>
+        <v>0300009</v>
       </c>
       <c r="B13" t="str">
-        <v>NEHA YADAV</v>
+        <v>SUNITA SHARMA</v>
       </c>
       <c r="C13" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Headmaster</v>
       </c>
       <c r="D13" t="str">
-        <v>03024</v>
+        <v>03009</v>
       </c>
       <c r="E13" t="str">
-        <v>RWD Division (deputed from other district)</v>
+        <v>High School Tariyani No.1</v>
       </c>
       <c r="F13" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G13" t="str">
-        <v>9003000025</v>
+        <v>9003000009</v>
       </c>
       <c r="H13" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I13" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J13" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K13" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="L13" t="str">
-        <v>Other District</v>
+        <v>Tariyani</v>
       </c>
       <c r="M13" t="str">
-        <v>30000197975</v>
+        <v>30000071271</v>
       </c>
       <c r="N13" t="str">
         <v>State Bank of India</v>
@@ -2153,48 +2201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P13" t="str">
-        <v>SBIN0009253</v>
+        <v>SBIN0009414</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0300063</v>
+        <v>0300040</v>
       </c>
       <c r="B14" t="str">
-        <v>RAMESH MAHTO</v>
+        <v>SUNIL PASWAN</v>
       </c>
       <c r="C14" t="str">
-        <v>Teacher</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D14" t="str">
-        <v>03051</v>
+        <v>03034</v>
       </c>
       <c r="E14" t="str">
-        <v>Block Education Office Piprahi</v>
+        <v>High School Tariyani No.3</v>
       </c>
       <c r="F14" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G14" t="str">
-        <v>9003000063</v>
+        <v>9003000040</v>
       </c>
       <c r="H14" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I14" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J14" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K14" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L14" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M14" t="str">
-        <v>30000498897</v>
+        <v>30000316760</v>
       </c>
       <c r="N14" t="str">
         <v>State Bank of India</v>
@@ -2203,33 +2251,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P14" t="str">
-        <v>SBIN0003779</v>
+        <v>SBIN0007694</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>0300044</v>
+        <v>0300089</v>
       </c>
       <c r="B15" t="str">
-        <v>DINESH PASWAN</v>
+        <v>NEHA GUPTA</v>
       </c>
       <c r="C15" t="str">
-        <v>Accountant</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D15" t="str">
-        <v>03037</v>
+        <v>03041</v>
       </c>
       <c r="E15" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F15" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G15" t="str">
-        <v>9003000044</v>
+        <v>9003000089</v>
       </c>
       <c r="H15" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I15" t="str">
         <v>0302</v>
@@ -2238,13 +2286,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K15" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L15" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M15" t="str">
-        <v>30000348436</v>
+        <v>30000704791</v>
       </c>
       <c r="N15" t="str">
         <v>State Bank of India</v>
@@ -2253,48 +2301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P15" t="str">
-        <v>SBIN0004116</v>
+        <v>SBIN0002524</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>0300051</v>
+        <v>0300114</v>
       </c>
       <c r="B16" t="str">
-        <v>RANJIT PASWAN</v>
+        <v>MD. IRFAN SHARMA</v>
       </c>
       <c r="C16" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Postmaster</v>
       </c>
       <c r="D16" t="str">
-        <v>03015</v>
+        <v>03085</v>
       </c>
       <c r="E16" t="str">
-        <v>Block Agriculture Office Purnahiya No.2</v>
+        <v>UCO Bank, Sheohar</v>
       </c>
       <c r="F16" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G16" t="str">
-        <v>9003000051</v>
+        <v>9003000114</v>
       </c>
       <c r="H16" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I16" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J16" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K16" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L16" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M16" t="str">
-        <v>30000403869</v>
+        <v>30000902766</v>
       </c>
       <c r="N16" t="str">
         <v>State Bank of India</v>
@@ -2303,33 +2351,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P16" t="str">
-        <v>SBIN0008534</v>
+        <v>SBIN0005634</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>0300065</v>
+        <v>0300111</v>
       </c>
       <c r="B17" t="str">
-        <v>SANTOSH MAHTO</v>
+        <v>POONAM SHARMA</v>
       </c>
       <c r="C17" t="str">
-        <v>Teacher</v>
+        <v>Postmaster</v>
       </c>
       <c r="D17" t="str">
-        <v>03052</v>
+        <v>03085</v>
       </c>
       <c r="E17" t="str">
-        <v>Block Office Sheohar</v>
+        <v>UCO Bank, Sheohar</v>
       </c>
       <c r="F17" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G17" t="str">
-        <v>9003000065</v>
+        <v>9003000111</v>
       </c>
       <c r="H17" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I17" t="str">
         <v>0304</v>
@@ -2344,7 +2392,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M17" t="str">
-        <v>30000514735</v>
+        <v>30000879009</v>
       </c>
       <c r="N17" t="str">
         <v>State Bank of India</v>
@@ -2353,48 +2401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P17" t="str">
-        <v>SBIN0009592</v>
+        <v>SBIN0005085</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>0300062</v>
+        <v>0300077</v>
       </c>
       <c r="B18" t="str">
-        <v>ABDUL KALAM KUMAR</v>
+        <v>RAVI MISHRA</v>
       </c>
       <c r="C18" t="str">
-        <v>Accountant</v>
+        <v>Clerk</v>
       </c>
       <c r="D18" t="str">
-        <v>03007</v>
+        <v>03063</v>
       </c>
       <c r="E18" t="str">
-        <v>Middle School Piprahi No.3</v>
+        <v>CDPO Office Tariyani No.3</v>
       </c>
       <c r="F18" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G18" t="str">
-        <v>9003000062</v>
+        <v>9003000077</v>
       </c>
       <c r="H18" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I18" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J18" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K18" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L18" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M18" t="str">
-        <v>30000490978</v>
+        <v>30000609763</v>
       </c>
       <c r="N18" t="str">
         <v>State Bank of India</v>
@@ -2403,48 +2451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P18" t="str">
-        <v>SBIN0002219</v>
+        <v>SBIN0005954</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>0300076</v>
+        <v>0300125</v>
       </c>
       <c r="B19" t="str">
-        <v>KUMARI ANJALI ALAM</v>
+        <v>KIRAN GUPTA</v>
       </c>
       <c r="C19" t="str">
-        <v>Office Assistant</v>
+        <v>Postmaster</v>
       </c>
       <c r="D19" t="str">
-        <v>03061</v>
+        <v>03093</v>
       </c>
       <c r="E19" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>Head Post Office, Sheohar</v>
       </c>
       <c r="F19" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G19" t="str">
-        <v>9003000076</v>
+        <v>9003000125</v>
       </c>
       <c r="H19" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I19" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K19" t="str">
         <v>0301</v>
       </c>
-      <c r="J19" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K19" t="str">
-        <v>0303</v>
-      </c>
       <c r="L19" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M19" t="str">
-        <v>30000601844</v>
+        <v>30000989875</v>
       </c>
       <c r="N19" t="str">
         <v>State Bank of India</v>
@@ -2453,48 +2501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P19" t="str">
-        <v>SBIN0008323</v>
+        <v>SBIN0002960</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>0300081</v>
+        <v>0300075</v>
       </c>
       <c r="B20" t="str">
-        <v>KIRAN DEVI</v>
+        <v>NIRMALA KUMAR</v>
       </c>
       <c r="C20" t="str">
-        <v>Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D20" t="str">
-        <v>03049</v>
+        <v>03007</v>
       </c>
       <c r="E20" t="str">
-        <v>CDPO Office Sheohar No.2</v>
+        <v>PHED Division (deputed from other district)</v>
       </c>
       <c r="F20" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G20" t="str">
-        <v>9003000081</v>
+        <v>9003000075</v>
       </c>
       <c r="H20" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I20" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J20" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K20" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="L20" t="str">
-        <v>Sheohar</v>
+        <v>Other District</v>
       </c>
       <c r="M20" t="str">
-        <v>30000641439</v>
+        <v>30000593925</v>
       </c>
       <c r="N20" t="str">
         <v>State Bank of India</v>
@@ -2503,39 +2551,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P20" t="str">
-        <v>SBIN0005602</v>
+        <v>SBIN0009995</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>0300010</v>
+        <v>0300123</v>
       </c>
       <c r="B21" t="str">
-        <v>SANJAY ALAM</v>
+        <v>ANIL THAKUR</v>
       </c>
       <c r="C21" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D21" t="str">
-        <v>03010</v>
+        <v>03091</v>
       </c>
       <c r="E21" t="str">
-        <v>Block Office Tariyani No.2</v>
+        <v>BSNL Exchange, Tariyani</v>
       </c>
       <c r="F21" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G21" t="str">
-        <v>9003000010</v>
+        <v>9003000123</v>
       </c>
       <c r="H21" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I21" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J21" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K21" t="str">
         <v>0305</v>
@@ -2544,7 +2592,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M21" t="str">
-        <v>30000079190</v>
+        <v>30000974037</v>
       </c>
       <c r="N21" t="str">
         <v>State Bank of India</v>
@@ -2553,48 +2601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P21" t="str">
-        <v>SBIN0003802</v>
+        <v>SBIN0009742</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>0300099</v>
+        <v>0300058</v>
       </c>
       <c r="B22" t="str">
-        <v>ASHA CHAUDHARY</v>
+        <v>MD. IRFAN MAHTO</v>
       </c>
       <c r="C22" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D22" t="str">
-        <v>03076</v>
+        <v>03049</v>
       </c>
       <c r="E22" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>High School Purnahiya</v>
       </c>
       <c r="F22" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G22" t="str">
-        <v>9003000099</v>
+        <v>9003000058</v>
       </c>
       <c r="H22" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I22" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J22" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K22" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L22" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M22" t="str">
-        <v>30000783981</v>
+        <v>30000459302</v>
       </c>
       <c r="N22" t="str">
         <v>State Bank of India</v>
@@ -2603,39 +2651,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P22" t="str">
-        <v>SBIN0008599</v>
+        <v>SBIN0003351</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>0300027</v>
+        <v>0300018</v>
       </c>
       <c r="B23" t="str">
-        <v>ASHA JHA</v>
+        <v>SUNITA PANDEY</v>
       </c>
       <c r="C23" t="str">
-        <v>Assistant Teacher</v>
+        <v>Lecturer</v>
       </c>
       <c r="D23" t="str">
-        <v>03025</v>
+        <v>03017</v>
       </c>
       <c r="E23" t="str">
-        <v>Block Agriculture Office Sheohar No.3</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F23" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G23" t="str">
-        <v>9003000027</v>
+        <v>9003000018</v>
       </c>
       <c r="H23" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I23" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J23" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K23" t="str">
         <v>0301</v>
@@ -2644,7 +2692,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M23" t="str">
-        <v>30000213813</v>
+        <v>30000142542</v>
       </c>
       <c r="N23" t="str">
         <v>State Bank of India</v>
@@ -2653,33 +2701,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P23" t="str">
-        <v>SBIN0004551</v>
+        <v>SBIN0008245</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>0300083</v>
+        <v>0300006</v>
       </c>
       <c r="B24" t="str">
-        <v>MANOJ PANDEY</v>
+        <v>SUNIL OJHA</v>
       </c>
       <c r="C24" t="str">
-        <v>Teacher</v>
+        <v>Section Officer</v>
       </c>
       <c r="D24" t="str">
-        <v>03066</v>
+        <v>03006</v>
       </c>
       <c r="E24" t="str">
-        <v>PHC Dumri Katsari No.2</v>
+        <v>CDPO Office Purnahiya No.2</v>
       </c>
       <c r="F24" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G24" t="str">
-        <v>9003000083</v>
+        <v>9003000006</v>
       </c>
       <c r="H24" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I24" t="str">
         <v>0304</v>
@@ -2688,13 +2736,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K24" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L24" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M24" t="str">
-        <v>30000657277</v>
+        <v>30000047514</v>
       </c>
       <c r="N24" t="str">
         <v>State Bank of India</v>
@@ -2703,39 +2751,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P24" t="str">
-        <v>SBIN0008495</v>
+        <v>SBIN0008758</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0300111</v>
+        <v>0300126</v>
       </c>
       <c r="B25" t="str">
-        <v>SAVITA RAM</v>
+        <v>PANKAJ CHAUDHARY</v>
       </c>
       <c r="C25" t="str">
-        <v>Administrative Officer</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D25" t="str">
-        <v>03083</v>
+        <v>03094</v>
       </c>
       <c r="E25" t="str">
-        <v>Central Bank of India, Piprahi</v>
+        <v>Head Post Office, Piprahi</v>
       </c>
       <c r="F25" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G25" t="str">
-        <v>9003000111</v>
+        <v>9003000126</v>
       </c>
       <c r="H25" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I25" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J25" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K25" t="str">
         <v>0302</v>
@@ -2744,7 +2792,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M25" t="str">
-        <v>30000879009</v>
+        <v>30000997794</v>
       </c>
       <c r="N25" t="str">
         <v>State Bank of India</v>
@@ -2753,33 +2801,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P25" t="str">
-        <v>SBIN0005781</v>
+        <v>SBIN0007429</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>0300011</v>
+        <v>0300101</v>
       </c>
       <c r="B26" t="str">
-        <v>VINOD RAI</v>
+        <v>MAMTA ANSARI K</v>
       </c>
       <c r="C26" t="str">
-        <v>Senior Teacher</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D26" t="str">
-        <v>03011</v>
+        <v>03078</v>
       </c>
       <c r="E26" t="str">
-        <v>Block Office Tariyani</v>
+        <v>Block Office Dumri Katsari</v>
       </c>
       <c r="F26" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G26" t="str">
-        <v>9003000011</v>
+        <v>9003000101</v>
       </c>
       <c r="H26" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I26" t="str">
         <v>0305</v>
@@ -2788,13 +2836,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K26" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L26" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M26" t="str">
-        <v>30000087109</v>
+        <v>30000799819</v>
       </c>
       <c r="N26" t="str">
         <v>State Bank of India</v>
@@ -2803,30 +2851,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P26" t="str">
-        <v>SBIN0007107</v>
+        <v>SBIN0007516</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>0300035</v>
+        <v>0300039</v>
       </c>
       <c r="B27" t="str">
-        <v>FARHAT PANDEY</v>
+        <v>PRIYANKA SAH</v>
       </c>
       <c r="C27" t="str">
         <v>Senior Clerk</v>
       </c>
       <c r="D27" t="str">
-        <v>03033</v>
+        <v>03026</v>
       </c>
       <c r="E27" t="str">
-        <v>Block Education Office Purnahiya No.2</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F27" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G27" t="str">
-        <v>9003000035</v>
+        <v>9003000039</v>
       </c>
       <c r="H27" t="str">
         <v>POLLING OFFICER-1</v>
@@ -2838,13 +2886,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K27" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L27" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M27" t="str">
-        <v>30000277165</v>
+        <v>30000308841</v>
       </c>
       <c r="N27" t="str">
         <v>State Bank of India</v>
@@ -2853,48 +2901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P27" t="str">
-        <v>SBIN0002270</v>
+        <v>SBIN0005304</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>0300125</v>
+        <v>0300022</v>
       </c>
       <c r="B28" t="str">
-        <v>RANJIT PASWAN J</v>
+        <v>DEEPAK PRASAD</v>
       </c>
       <c r="C28" t="str">
-        <v>Postmaster</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D28" t="str">
-        <v>03094</v>
+        <v>03020</v>
       </c>
       <c r="E28" t="str">
-        <v>LIC Branch Office, Dumri Katsari</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F28" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G28" t="str">
-        <v>9003000125</v>
+        <v>9003000022</v>
       </c>
       <c r="H28" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I28" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J28" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K28" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L28" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M28" t="str">
-        <v>30000989875</v>
+        <v>30000174218</v>
       </c>
       <c r="N28" t="str">
         <v>State Bank of India</v>
@@ -2903,48 +2951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P28" t="str">
-        <v>SBIN0003229</v>
+        <v>SBIN0002922</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>0300071</v>
+        <v>0300098</v>
       </c>
       <c r="B29" t="str">
-        <v>DEEPAK OJHA</v>
+        <v>NASREEN ANSARI</v>
       </c>
       <c r="C29" t="str">
-        <v>Office Assistant</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D29" t="str">
-        <v>03057</v>
+        <v>03077</v>
       </c>
       <c r="E29" t="str">
-        <v>Kanya Middle School Purnahiya No.4</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F29" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G29" t="str">
-        <v>9003000071</v>
+        <v>9003000098</v>
       </c>
       <c r="H29" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I29" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J29" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K29" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L29" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M29" t="str">
-        <v>30000562249</v>
+        <v>30000776062</v>
       </c>
       <c r="N29" t="str">
         <v>State Bank of India</v>
@@ -2953,48 +3001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P29" t="str">
-        <v>SBIN0006297</v>
+        <v>SBIN0006166</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>0300004</v>
+        <v>0300027</v>
       </c>
       <c r="B30" t="str">
-        <v>NITISH YADAV</v>
+        <v>MUKESH CHAUDHARY</v>
       </c>
       <c r="C30" t="str">
-        <v>Assistant Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D30" t="str">
-        <v>03004</v>
+        <v>03025</v>
       </c>
       <c r="E30" t="str">
-        <v>Primary School Tariyani No.4</v>
+        <v>Block Agriculture Office Dumri Katsari No.4</v>
       </c>
       <c r="F30" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G30" t="str">
-        <v>9003000004</v>
+        <v>9003000027</v>
       </c>
       <c r="H30" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I30" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J30" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K30" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L30" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M30" t="str">
-        <v>30000031676</v>
+        <v>30000213813</v>
       </c>
       <c r="N30" t="str">
         <v>State Bank of India</v>
@@ -3003,33 +3051,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P30" t="str">
-        <v>SBIN0002593</v>
+        <v>SBIN0007952</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>0300046</v>
+        <v>0300096</v>
       </c>
       <c r="B31" t="str">
-        <v>DEEPAK PASWAN X</v>
+        <v>PRAMOD RAI</v>
       </c>
       <c r="C31" t="str">
-        <v>Teacher</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D31" t="str">
-        <v>03039</v>
+        <v>03075</v>
       </c>
       <c r="E31" t="str">
-        <v>Kanya Middle School Dumri Katsari</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="F31" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G31" t="str">
-        <v>9003000046</v>
+        <v>9003000096</v>
       </c>
       <c r="H31" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I31" t="str">
         <v>0301</v>
@@ -3038,13 +3086,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K31" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L31" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M31" t="str">
-        <v>30000364274</v>
+        <v>30000760224</v>
       </c>
       <c r="N31" t="str">
         <v>State Bank of India</v>
@@ -3053,48 +3101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P31" t="str">
-        <v>SBIN0003724</v>
+        <v>SBIN0004938</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>0300064</v>
+        <v>0300051</v>
       </c>
       <c r="B32" t="str">
-        <v>RAVI SINGH</v>
+        <v>RAMESH KUMAR</v>
       </c>
       <c r="C32" t="str">
         <v>Teacher</v>
       </c>
       <c r="D32" t="str">
-        <v>03051</v>
+        <v>03028</v>
       </c>
       <c r="E32" t="str">
-        <v>Block Education Office Piprahi</v>
+        <v>PHC Purnahiya</v>
       </c>
       <c r="F32" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G32" t="str">
-        <v>9003000064</v>
+        <v>9003000051</v>
       </c>
       <c r="H32" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I32" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J32" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K32" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L32" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M32" t="str">
-        <v>30000506816</v>
+        <v>30000403869</v>
       </c>
       <c r="N32" t="str">
         <v>State Bank of India</v>
@@ -3103,48 +3151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P32" t="str">
-        <v>SBIN0005150</v>
+        <v>SBIN0003922</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>0300066</v>
+        <v>0300113</v>
       </c>
       <c r="B33" t="str">
-        <v>KIRAN GUPTA</v>
+        <v>SHAILESH KHATUN</v>
       </c>
       <c r="C33" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D33" t="str">
-        <v>03053</v>
+        <v>03085</v>
       </c>
       <c r="E33" t="str">
-        <v>CDPO Office Purnahiya</v>
+        <v>UCO Bank, Sheohar</v>
       </c>
       <c r="F33" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G33" t="str">
-        <v>9003000066</v>
+        <v>9003000113</v>
       </c>
       <c r="H33" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I33" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J33" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K33" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L33" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M33" t="str">
-        <v>30000522654</v>
+        <v>30000894847</v>
       </c>
       <c r="N33" t="str">
         <v>State Bank of India</v>
@@ -3153,48 +3201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P33" t="str">
-        <v>SBIN0004804</v>
+        <v>SBIN0007492</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>0300101</v>
+        <v>0300060</v>
       </c>
       <c r="B34" t="str">
-        <v>ALOK SAH Q</v>
+        <v>UMESH JHA</v>
       </c>
       <c r="C34" t="str">
-        <v>Junior Engineer</v>
+        <v>Teacher</v>
       </c>
       <c r="D34" t="str">
-        <v>03077</v>
+        <v>03050</v>
       </c>
       <c r="E34" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Panchayat Bhawan Piprahi</v>
       </c>
       <c r="F34" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G34" t="str">
-        <v>9003000101</v>
+        <v>9003000060</v>
       </c>
       <c r="H34" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I34" t="str">
+        <v>999999</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Others</v>
+      </c>
+      <c r="K34" t="str">
         <v>0302</v>
       </c>
-      <c r="J34" t="str">
+      <c r="L34" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K34" t="str">
-        <v>0303</v>
-      </c>
-      <c r="L34" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="M34" t="str">
-        <v>30000799819</v>
+        <v>30000475140</v>
       </c>
       <c r="N34" t="str">
         <v>State Bank of India</v>
@@ -3203,48 +3251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P34" t="str">
-        <v>SBIN0007588</v>
+        <v>SBIN0004033</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>0300077</v>
+        <v>0300044</v>
       </c>
       <c r="B35" t="str">
-        <v>PRAMOD GUPTA</v>
+        <v>SUNITA CHAUDHARY</v>
       </c>
       <c r="C35" t="str">
-        <v>Office Assistant</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D35" t="str">
-        <v>03062</v>
+        <v>03006</v>
       </c>
       <c r="E35" t="str">
-        <v>Primary School Piprahi No.1</v>
+        <v>CDPO Office Purnahiya No.2</v>
       </c>
       <c r="F35" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G35" t="str">
-        <v>9003000077</v>
+        <v>9003000044</v>
       </c>
       <c r="H35" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I35" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J35" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K35" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L35" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M35" t="str">
-        <v>30000609763</v>
+        <v>30000348436</v>
       </c>
       <c r="N35" t="str">
         <v>State Bank of India</v>
@@ -3253,33 +3301,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P35" t="str">
-        <v>SBIN0004982</v>
+        <v>SBIN0007514</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>0300080</v>
+        <v>0300025</v>
       </c>
       <c r="B36" t="str">
-        <v>NIRMALA PRASAD</v>
+        <v>MAHESH SINHA</v>
       </c>
       <c r="C36" t="str">
-        <v>Data Entry Operator</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D36" t="str">
-        <v>03028</v>
+        <v>03023</v>
       </c>
       <c r="E36" t="str">
-        <v>CDPO Office Tariyani No.1</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F36" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G36" t="str">
-        <v>9003000080</v>
+        <v>9003000025</v>
       </c>
       <c r="H36" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I36" t="str">
         <v>0301</v>
@@ -3288,13 +3336,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K36" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L36" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M36" t="str">
-        <v>30000633520</v>
+        <v>30000197975</v>
       </c>
       <c r="N36" t="str">
         <v>State Bank of India</v>
@@ -3303,48 +3351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P36" t="str">
-        <v>SBIN0007142</v>
+        <v>SBIN0002599</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>0300126</v>
+        <v>0300102</v>
       </c>
       <c r="B37" t="str">
-        <v>NIRMALA SHARMA</v>
+        <v>ABDUL KALAM MISHRA</v>
       </c>
       <c r="C37" t="str">
-        <v>Branch Manager</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D37" t="str">
-        <v>03085</v>
+        <v>03079</v>
       </c>
       <c r="E37" t="str">
-        <v>Head Post Office, Piprahi</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="F37" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G37" t="str">
-        <v>9003000126</v>
+        <v>9003000102</v>
       </c>
       <c r="H37" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I37" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J37" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K37" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L37" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M37" t="str">
-        <v>30000997794</v>
+        <v>30000807738</v>
       </c>
       <c r="N37" t="str">
         <v>State Bank of India</v>
@@ -3353,48 +3401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P37" t="str">
-        <v>SBIN0002334</v>
+        <v>SBIN0001820</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>0300058</v>
+        <v>0300055</v>
       </c>
       <c r="B38" t="str">
-        <v>ARVIND SINHA</v>
+        <v>MUKESH CHAUDHARY A</v>
       </c>
       <c r="C38" t="str">
-        <v>Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D38" t="str">
-        <v>03047</v>
+        <v>03046</v>
       </c>
       <c r="E38" t="str">
-        <v>CDPO Office Dumri Katsari</v>
+        <v>CDPO Office Tariyani No.2</v>
       </c>
       <c r="F38" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G38" t="str">
-        <v>9003000058</v>
+        <v>9003000055</v>
       </c>
       <c r="H38" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I38" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J38" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K38" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L38" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M38" t="str">
-        <v>30000459302</v>
+        <v>30000435545</v>
       </c>
       <c r="N38" t="str">
         <v>State Bank of India</v>
@@ -3403,39 +3451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P38" t="str">
-        <v>SBIN0005642</v>
+        <v>SBIN0007561</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>0300042</v>
+        <v>0300097</v>
       </c>
       <c r="B39" t="str">
-        <v>NEHA YADAV S</v>
+        <v>USHA SINHA</v>
       </c>
       <c r="C39" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D39" t="str">
-        <v>03035</v>
+        <v>03076</v>
       </c>
       <c r="E39" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>RWD Sub-Division Sheohar</v>
       </c>
       <c r="F39" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G39" t="str">
-        <v>9003000042</v>
+        <v>9003000097</v>
       </c>
       <c r="H39" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I39" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J39" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K39" t="str">
         <v>0301</v>
@@ -3444,7 +3492,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M39" t="str">
-        <v>30000332598</v>
+        <v>30000768143</v>
       </c>
       <c r="N39" t="str">
         <v>State Bank of India</v>
@@ -3453,30 +3501,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P39" t="str">
-        <v>SBIN0007083</v>
+        <v>SBIN0002048</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>0300028</v>
+        <v>0300034</v>
       </c>
       <c r="B40" t="str">
-        <v>RAJESH CHAUDHARY</v>
+        <v>PANKAJ SAH</v>
       </c>
       <c r="C40" t="str">
         <v>Panchayat Secretary</v>
       </c>
       <c r="D40" t="str">
-        <v>03026</v>
+        <v>03029</v>
       </c>
       <c r="E40" t="str">
-        <v>Project Girls High School Dumri Katsari</v>
+        <v>Middle School Dumri Katsari No.3</v>
       </c>
       <c r="F40" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G40" t="str">
-        <v>9003000028</v>
+        <v>9003000034</v>
       </c>
       <c r="H40" t="str">
         <v>POLLING OFFICER-1</v>
@@ -3494,7 +3542,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M40" t="str">
-        <v>30000221732</v>
+        <v>30000269246</v>
       </c>
       <c r="N40" t="str">
         <v>State Bank of India</v>
@@ -3503,48 +3551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P40" t="str">
-        <v>SBIN0005517</v>
+        <v>SBIN0008050</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>0300019</v>
+        <v>0300013</v>
       </c>
       <c r="B41" t="str">
-        <v>SANTOSH CHAUDHARY</v>
+        <v>SANTOSH RAM</v>
       </c>
       <c r="C41" t="str">
-        <v>Section Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D41" t="str">
-        <v>03019</v>
+        <v>03013</v>
       </c>
       <c r="E41" t="str">
-        <v>PHED Division (deputed from other district)</v>
+        <v>Kanya Middle School Purnahiya No.2</v>
       </c>
       <c r="F41" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G41" t="str">
-        <v>9003000019</v>
+        <v>9003000013</v>
       </c>
       <c r="H41" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I41" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K41" t="str">
         <v>0303</v>
       </c>
-      <c r="J41" t="str">
+      <c r="L41" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="K41" t="str">
-        <v>999999</v>
-      </c>
-      <c r="L41" t="str">
-        <v>Other District</v>
-      </c>
       <c r="M41" t="str">
-        <v>30000150461</v>
+        <v>30000102947</v>
       </c>
       <c r="N41" t="str">
         <v>State Bank of India</v>
@@ -3553,39 +3601,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P41" t="str">
-        <v>SBIN0008494</v>
+        <v>SBIN0003097</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>0300112</v>
+        <v>0300019</v>
       </c>
       <c r="B42" t="str">
-        <v>AJAY KUMAR</v>
+        <v>MD. IRFAN JHA</v>
       </c>
       <c r="C42" t="str">
-        <v>Assistant Manager</v>
+        <v>Lecturer</v>
       </c>
       <c r="D42" t="str">
-        <v>03084</v>
+        <v>03018</v>
       </c>
       <c r="E42" t="str">
-        <v>LIC Branch Office, Sheohar</v>
+        <v>District Treasury Sheohar</v>
       </c>
       <c r="F42" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G42" t="str">
-        <v>9003000112</v>
+        <v>9003000019</v>
       </c>
       <c r="H42" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I42" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J42" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K42" t="str">
         <v>0301</v>
@@ -3594,7 +3642,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M42" t="str">
-        <v>30000886928</v>
+        <v>30000150461</v>
       </c>
       <c r="N42" t="str">
         <v>State Bank of India</v>
@@ -3603,39 +3651,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P42" t="str">
-        <v>SBIN0007236</v>
+        <v>SBIN0001780</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>0300018</v>
+        <v>0300086</v>
       </c>
       <c r="B43" t="str">
-        <v>AMIT VERMA M</v>
+        <v>SAVITA VERMA</v>
       </c>
       <c r="C43" t="str">
-        <v>Headmaster</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D43" t="str">
-        <v>03018</v>
+        <v>03069</v>
       </c>
       <c r="E43" t="str">
-        <v>Circle Office Sheohar No.3</v>
+        <v>Circle Office Sheohar</v>
       </c>
       <c r="F43" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G43" t="str">
-        <v>9003000018</v>
+        <v>9003000086</v>
       </c>
       <c r="H43" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I43" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="J43" t="str">
-        <v>Dumri Katsari</v>
+        <v>Others</v>
       </c>
       <c r="K43" t="str">
         <v>0301</v>
@@ -3644,7 +3692,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M43" t="str">
-        <v>30000142542</v>
+        <v>30000681034</v>
       </c>
       <c r="N43" t="str">
         <v>State Bank of India</v>
@@ -3653,48 +3701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P43" t="str">
-        <v>SBIN0003892</v>
+        <v>SBIN0007321</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>0300095</v>
+        <v>0300029</v>
       </c>
       <c r="B44" t="str">
-        <v>SAVITA DEVI</v>
+        <v>SANTOSH THAKUR</v>
       </c>
       <c r="C44" t="str">
-        <v>Junior Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D44" t="str">
-        <v>03074</v>
+        <v>03026</v>
       </c>
       <c r="E44" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F44" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G44" t="str">
-        <v>9003000095</v>
+        <v>9003000029</v>
       </c>
       <c r="H44" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I44" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J44" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K44" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L44" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M44" t="str">
-        <v>30000752305</v>
+        <v>30000229651</v>
       </c>
       <c r="N44" t="str">
         <v>State Bank of India</v>
@@ -3703,48 +3751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P44" t="str">
-        <v>SBIN0002955</v>
+        <v>SBIN0009857</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>0300026</v>
+        <v>0300085</v>
       </c>
       <c r="B45" t="str">
-        <v>USHA MISHRA</v>
+        <v>POONAM YADAV</v>
       </c>
       <c r="C45" t="str">
-        <v>Assistant Teacher</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D45" t="str">
-        <v>03021</v>
+        <v>03002</v>
       </c>
       <c r="E45" t="str">
-        <v>High School Tariyani No.4</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F45" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G45" t="str">
-        <v>9003000026</v>
+        <v>9003000085</v>
       </c>
       <c r="H45" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I45" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J45" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K45" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L45" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M45" t="str">
-        <v>30000205894</v>
+        <v>30000673115</v>
       </c>
       <c r="N45" t="str">
         <v>State Bank of India</v>
@@ -3753,48 +3801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P45" t="str">
-        <v>SBIN0001690</v>
+        <v>SBIN0006697</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>0300068</v>
+        <v>0300056</v>
       </c>
       <c r="B46" t="str">
-        <v>SUNIL VERMA</v>
+        <v>ANIL PANDEY</v>
       </c>
       <c r="C46" t="str">
-        <v>Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D46" t="str">
-        <v>03055</v>
+        <v>03047</v>
       </c>
       <c r="E46" t="str">
-        <v>Block Agriculture Office Sheohar No.2</v>
+        <v>Block Education Office Piprahi No.2</v>
       </c>
       <c r="F46" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G46" t="str">
-        <v>9003000068</v>
+        <v>9003000056</v>
       </c>
       <c r="H46" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I46" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K46" t="str">
         <v>0302</v>
       </c>
-      <c r="J46" t="str">
+      <c r="L46" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K46" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L46" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M46" t="str">
-        <v>30000538492</v>
+        <v>30000443464</v>
       </c>
       <c r="N46" t="str">
         <v>State Bank of India</v>
@@ -3803,39 +3851,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P46" t="str">
-        <v>SBIN0003402</v>
+        <v>SBIN0008327</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0300013</v>
+        <v>0300016</v>
       </c>
       <c r="B47" t="str">
-        <v>RANJIT MISHRA</v>
+        <v>PANKAJ ALAM</v>
       </c>
       <c r="C47" t="str">
-        <v>Section Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D47" t="str">
-        <v>03013</v>
+        <v>03015</v>
       </c>
       <c r="E47" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Block Education Office Sheohar No.2</v>
       </c>
       <c r="F47" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G47" t="str">
-        <v>9003000013</v>
+        <v>9003000016</v>
       </c>
       <c r="H47" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I47" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J47" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K47" t="str">
         <v>0301</v>
@@ -3844,7 +3892,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M47" t="str">
-        <v>30000102947</v>
+        <v>30000126704</v>
       </c>
       <c r="N47" t="str">
         <v>State Bank of India</v>
@@ -3853,39 +3901,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P47" t="str">
-        <v>SBIN0001680</v>
+        <v>SBIN0006809</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0300037</v>
+        <v>0300064</v>
       </c>
       <c r="B48" t="str">
-        <v>VIJAY CHAUDHARY</v>
+        <v>RAJESH ANSARI</v>
       </c>
       <c r="C48" t="str">
-        <v>Assistant Teacher</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D48" t="str">
-        <v>03003</v>
+        <v>03018</v>
       </c>
       <c r="E48" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>District Treasury Sheohar</v>
       </c>
       <c r="F48" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G48" t="str">
-        <v>9003000037</v>
+        <v>9003000064</v>
       </c>
       <c r="H48" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I48" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J48" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K48" t="str">
         <v>0301</v>
@@ -3894,7 +3942,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M48" t="str">
-        <v>30000293003</v>
+        <v>30000506816</v>
       </c>
       <c r="N48" t="str">
         <v>State Bank of India</v>
@@ -3903,48 +3951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P48" t="str">
-        <v>SBIN0004142</v>
+        <v>SBIN0008786</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0300108</v>
+        <v>0300024</v>
       </c>
       <c r="B49" t="str">
-        <v>MD. SHAHID CHAUDHARY</v>
+        <v>MUKESH ALAM</v>
       </c>
       <c r="C49" t="str">
-        <v>Postmaster</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D49" t="str">
-        <v>03082</v>
+        <v>03022</v>
       </c>
       <c r="E49" t="str">
-        <v>BSNL Exchange, Tariyani</v>
+        <v>Kanya Middle School Dumri Katsari No.1</v>
       </c>
       <c r="F49" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G49" t="str">
-        <v>9003000108</v>
+        <v>9003000024</v>
       </c>
       <c r="H49" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I49" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J49" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K49" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L49" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M49" t="str">
-        <v>30000855252</v>
+        <v>30000190056</v>
       </c>
       <c r="N49" t="str">
         <v>State Bank of India</v>
@@ -3953,48 +4001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P49" t="str">
-        <v>SBIN0001877</v>
+        <v>SBIN0004604</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0300088</v>
+        <v>0300100</v>
       </c>
       <c r="B50" t="str">
-        <v>PRIYANKA KHATUN</v>
+        <v>MAMTA SHARMA</v>
       </c>
       <c r="C50" t="str">
-        <v>Revenue Officer</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D50" t="str">
-        <v>03068</v>
+        <v>03077</v>
       </c>
       <c r="E50" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F50" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G50" t="str">
-        <v>9003000088</v>
+        <v>9003000100</v>
       </c>
       <c r="H50" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I50" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J50" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K50" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L50" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M50" t="str">
-        <v>30000696872</v>
+        <v>30000791900</v>
       </c>
       <c r="N50" t="str">
         <v>State Bank of India</v>
@@ -4003,48 +4051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P50" t="str">
-        <v>SBIN0001908</v>
+        <v>SBIN0002508</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>0300120</v>
+        <v>0300099</v>
       </c>
       <c r="B51" t="str">
-        <v>VINOD SAH</v>
+        <v>PRIYANKA DEVI</v>
       </c>
       <c r="C51" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D51" t="str">
-        <v>03091</v>
+        <v>03072</v>
       </c>
       <c r="E51" t="str">
-        <v>Central Bank of India, Tariyani</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F51" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G51" t="str">
-        <v>9003000120</v>
+        <v>9003000099</v>
       </c>
       <c r="H51" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I51" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J51" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K51" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L51" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M51" t="str">
-        <v>30000950280</v>
+        <v>30000783981</v>
       </c>
       <c r="N51" t="str">
         <v>State Bank of India</v>
@@ -4053,48 +4101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P51" t="str">
-        <v>SBIN0007479</v>
+        <v>SBIN0005594</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>0300082</v>
+        <v>0300104</v>
       </c>
       <c r="B52" t="str">
-        <v>ARVIND KUMAR</v>
+        <v>PRAMOD JHA</v>
       </c>
       <c r="C52" t="str">
-        <v>Teacher</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D52" t="str">
-        <v>03065</v>
+        <v>03075</v>
       </c>
       <c r="E52" t="str">
-        <v>Middle School Tariyani No.2</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="F52" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G52" t="str">
-        <v>9003000082</v>
+        <v>9003000104</v>
       </c>
       <c r="H52" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I52" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K52" t="str">
         <v>0301</v>
       </c>
-      <c r="J52" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K52" t="str">
-        <v>0305</v>
-      </c>
       <c r="L52" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M52" t="str">
-        <v>30000649358</v>
+        <v>30000823576</v>
       </c>
       <c r="N52" t="str">
         <v>State Bank of India</v>
@@ -4103,48 +4151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P52" t="str">
-        <v>SBIN0007867</v>
+        <v>SBIN0002061</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>0300053</v>
+        <v>0300026</v>
       </c>
       <c r="B53" t="str">
-        <v>AJAY THAKUR</v>
+        <v>AJAY SHARMA</v>
       </c>
       <c r="C53" t="str">
-        <v>Clerk</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D53" t="str">
-        <v>03043</v>
+        <v>03024</v>
       </c>
       <c r="E53" t="str">
-        <v>Block Education Office Tariyani No.2</v>
+        <v>Primary School Dumri Katsari No.4</v>
       </c>
       <c r="F53" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G53" t="str">
-        <v>9003000053</v>
+        <v>9003000026</v>
       </c>
       <c r="H53" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I53" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K53" t="str">
         <v>0304</v>
       </c>
-      <c r="J53" t="str">
+      <c r="L53" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="K53" t="str">
-        <v>0305</v>
-      </c>
-      <c r="L53" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="M53" t="str">
-        <v>30000419707</v>
+        <v>30000205894</v>
       </c>
       <c r="N53" t="str">
         <v>State Bank of India</v>
@@ -4153,48 +4201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P53" t="str">
-        <v>SBIN0006521</v>
+        <v>SBIN0007326</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>0300091</v>
+        <v>0300014</v>
       </c>
       <c r="B54" t="str">
-        <v>ALOK SAH</v>
+        <v>USHA DEVI</v>
       </c>
       <c r="C54" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D54" t="str">
-        <v>03071</v>
+        <v>03014</v>
       </c>
       <c r="E54" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>PHC Purnahiya No.1</v>
       </c>
       <c r="F54" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G54" t="str">
-        <v>9003000091</v>
+        <v>9003000014</v>
       </c>
       <c r="H54" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I54" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J54" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K54" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L54" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M54" t="str">
-        <v>30000720629</v>
+        <v>30000110866</v>
       </c>
       <c r="N54" t="str">
         <v>State Bank of India</v>
@@ -4203,48 +4251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P54" t="str">
-        <v>SBIN0008419</v>
+        <v>SBIN0006920</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>0300097</v>
+        <v>0300032</v>
       </c>
       <c r="B55" t="str">
-        <v>SANTOSH OJHA</v>
+        <v>DINESH MISHRA</v>
       </c>
       <c r="C55" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D55" t="str">
-        <v>03075</v>
+        <v>03028</v>
       </c>
       <c r="E55" t="str">
-        <v>Circle Office Sheohar</v>
+        <v>PHC Purnahiya</v>
       </c>
       <c r="F55" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G55" t="str">
-        <v>9003000097</v>
+        <v>9003000032</v>
       </c>
       <c r="H55" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I55" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J55" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K55" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L55" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M55" t="str">
-        <v>30000768143</v>
+        <v>30000253408</v>
       </c>
       <c r="N55" t="str">
         <v>State Bank of India</v>
@@ -4253,48 +4301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P55" t="str">
-        <v>SBIN0006895</v>
+        <v>SBIN0008758</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>0300039</v>
+        <v>0300010</v>
       </c>
       <c r="B56" t="str">
-        <v>RANJIT SINHA</v>
+        <v>NITISH SAH</v>
       </c>
       <c r="C56" t="str">
-        <v>Senior Clerk</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D56" t="str">
-        <v>03022</v>
+        <v>03010</v>
       </c>
       <c r="E56" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Kanya Middle School Dumri Katsari No.2</v>
       </c>
       <c r="F56" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G56" t="str">
-        <v>9003000039</v>
+        <v>9003000010</v>
       </c>
       <c r="H56" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I56" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J56" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K56" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L56" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M56" t="str">
-        <v>30000308841</v>
+        <v>30000079190</v>
       </c>
       <c r="N56" t="str">
         <v>State Bank of India</v>
@@ -4303,48 +4351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P56" t="str">
-        <v>SBIN0009972</v>
+        <v>SBIN0004846</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>0300094</v>
+        <v>0300083</v>
       </c>
       <c r="B57" t="str">
-        <v>MAHESH SHARMA</v>
+        <v>RINKU MAHTO</v>
       </c>
       <c r="C57" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D57" t="str">
-        <v>03073</v>
+        <v>03066</v>
       </c>
       <c r="E57" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>Middle School Tariyani No.4</v>
       </c>
       <c r="F57" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G57" t="str">
-        <v>9003000094</v>
+        <v>9003000083</v>
       </c>
       <c r="H57" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I57" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J57" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K57" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L57" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M57" t="str">
-        <v>30000744386</v>
+        <v>30000657277</v>
       </c>
       <c r="N57" t="str">
         <v>State Bank of India</v>
@@ -4353,48 +4401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P57" t="str">
-        <v>SBIN0005115</v>
+        <v>SBIN0007720</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>0300007</v>
+        <v>0300046</v>
       </c>
       <c r="B58" t="str">
-        <v>NIRMALA MAHTO</v>
+        <v>NIRMALA OJHA</v>
       </c>
       <c r="C58" t="str">
-        <v>Assistant Engineer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D58" t="str">
-        <v>03007</v>
+        <v>03038</v>
       </c>
       <c r="E58" t="str">
-        <v>Middle School Piprahi No.3</v>
+        <v>High School Dumri Katsari No.1</v>
       </c>
       <c r="F58" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G58" t="str">
-        <v>9003000007</v>
+        <v>9003000046</v>
       </c>
       <c r="H58" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I58" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J58" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K58" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L58" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M58" t="str">
-        <v>30000055433</v>
+        <v>30000364274</v>
       </c>
       <c r="N58" t="str">
         <v>State Bank of India</v>
@@ -4403,48 +4451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P58" t="str">
-        <v>SBIN0007829</v>
+        <v>SBIN0003116</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>0300085</v>
+        <v>0300121</v>
       </c>
       <c r="B59" t="str">
-        <v>SANJAY SINGH</v>
+        <v>RAVI MAHTO</v>
       </c>
       <c r="C59" t="str">
-        <v>Junior Engineer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D59" t="str">
-        <v>03068</v>
+        <v>03080</v>
       </c>
       <c r="E59" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>LIC Branch Office, Piprahi</v>
       </c>
       <c r="F59" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G59" t="str">
-        <v>9003000085</v>
+        <v>9003000121</v>
       </c>
       <c r="H59" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I59" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J59" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K59" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L59" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M59" t="str">
-        <v>30000673115</v>
+        <v>30000958199</v>
       </c>
       <c r="N59" t="str">
         <v>State Bank of India</v>
@@ -4453,33 +4501,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P59" t="str">
-        <v>SBIN0004543</v>
+        <v>SBIN0004265</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>0300124</v>
+        <v>0300073</v>
       </c>
       <c r="B60" t="str">
-        <v>PRIYANKA MISHRA</v>
+        <v>SURESH OJHA</v>
       </c>
       <c r="C60" t="str">
-        <v>Postmaster</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D60" t="str">
-        <v>03091</v>
+        <v>03060</v>
       </c>
       <c r="E60" t="str">
-        <v>Central Bank of India, Tariyani</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F60" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G60" t="str">
-        <v>9003000124</v>
+        <v>9003000073</v>
       </c>
       <c r="H60" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I60" t="str">
         <v>0305</v>
@@ -4488,13 +4536,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K60" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L60" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M60" t="str">
-        <v>30000981956</v>
+        <v>30000578087</v>
       </c>
       <c r="N60" t="str">
         <v>State Bank of India</v>
@@ -4503,48 +4551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P60" t="str">
-        <v>SBIN0001272</v>
+        <v>SBIN0005422</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>0300114</v>
+        <v>0300091</v>
       </c>
       <c r="B61" t="str">
-        <v>RINKU ALAM</v>
+        <v>SANTOSH YADAV</v>
       </c>
       <c r="C61" t="str">
-        <v>Administrative Officer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D61" t="str">
-        <v>03080</v>
+        <v>03072</v>
       </c>
       <c r="E61" t="str">
-        <v>UCO Bank, Tariyani</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F61" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G61" t="str">
-        <v>9003000114</v>
+        <v>9003000091</v>
       </c>
       <c r="H61" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I61" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J61" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K61" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L61" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M61" t="str">
-        <v>30000902766</v>
+        <v>30000720629</v>
       </c>
       <c r="N61" t="str">
         <v>State Bank of India</v>
@@ -4553,33 +4601,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P61" t="str">
-        <v>SBIN0003081</v>
+        <v>SBIN0001238</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>0300048</v>
+        <v>0300015</v>
       </c>
       <c r="B62" t="str">
-        <v>SUNIL SINHA</v>
+        <v>DINESH TIWARI</v>
       </c>
       <c r="C62" t="str">
-        <v>Accountant</v>
+        <v>Section Officer</v>
       </c>
       <c r="D62" t="str">
-        <v>03020</v>
+        <v>03010</v>
       </c>
       <c r="E62" t="str">
-        <v>Block Education Office Tariyani</v>
+        <v>Kanya Middle School Dumri Katsari No.2</v>
       </c>
       <c r="F62" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G62" t="str">
-        <v>9003000048</v>
+        <v>9003000015</v>
       </c>
       <c r="H62" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I62" t="str">
         <v>0305</v>
@@ -4588,13 +4636,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K62" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L62" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M62" t="str">
-        <v>30000380112</v>
+        <v>30000118785</v>
       </c>
       <c r="N62" t="str">
         <v>State Bank of India</v>
@@ -4603,48 +4651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P62" t="str">
-        <v>SBIN0001093</v>
+        <v>SBIN0005574</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>0300067</v>
+        <v>0300042</v>
       </c>
       <c r="B63" t="str">
-        <v>ARVIND SINHA K</v>
+        <v>ANIL PRASAD</v>
       </c>
       <c r="C63" t="str">
-        <v>Office Assistant</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D63" t="str">
-        <v>03054</v>
+        <v>03035</v>
       </c>
       <c r="E63" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>Block Agriculture Office Dumri Katsari No.2</v>
       </c>
       <c r="F63" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G63" t="str">
-        <v>9003000067</v>
+        <v>9003000042</v>
       </c>
       <c r="H63" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I63" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J63" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K63" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L63" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M63" t="str">
-        <v>30000530573</v>
+        <v>30000332598</v>
       </c>
       <c r="N63" t="str">
         <v>State Bank of India</v>
@@ -4653,39 +4701,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P63" t="str">
-        <v>SBIN0009319</v>
+        <v>SBIN0003110</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>0300006</v>
+        <v>0300017</v>
       </c>
       <c r="B64" t="str">
-        <v>VIJAY TIWARI</v>
+        <v>AMIT CHAUDHARY</v>
       </c>
       <c r="C64" t="str">
-        <v>Lecturer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D64" t="str">
-        <v>03006</v>
+        <v>03016</v>
       </c>
       <c r="E64" t="str">
-        <v>PHC Sheohar</v>
+        <v>Kanya Middle School Sheohar</v>
       </c>
       <c r="F64" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G64" t="str">
-        <v>9003000006</v>
+        <v>9003000017</v>
       </c>
       <c r="H64" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I64" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J64" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K64" t="str">
         <v>0301</v>
@@ -4694,7 +4742,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M64" t="str">
-        <v>30000047514</v>
+        <v>30000134623</v>
       </c>
       <c r="N64" t="str">
         <v>State Bank of India</v>
@@ -4703,33 +4751,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P64" t="str">
-        <v>SBIN0009024</v>
+        <v>SBIN0001199</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>0300052</v>
+        <v>0300004</v>
       </c>
       <c r="B65" t="str">
-        <v>DEEPAK JHA</v>
+        <v>NEHA SINHA</v>
       </c>
       <c r="C65" t="str">
-        <v>Clerk</v>
+        <v>Section Officer</v>
       </c>
       <c r="D65" t="str">
-        <v>03042</v>
+        <v>03004</v>
       </c>
       <c r="E65" t="str">
-        <v>Block Office Sheohar No.4</v>
+        <v>High School Sheohar</v>
       </c>
       <c r="F65" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G65" t="str">
-        <v>9003000052</v>
+        <v>9003000004</v>
       </c>
       <c r="H65" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I65" t="str">
         <v>0301</v>
@@ -4744,7 +4792,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M65" t="str">
-        <v>30000411788</v>
+        <v>30000031676</v>
       </c>
       <c r="N65" t="str">
         <v>State Bank of India</v>
@@ -4753,33 +4801,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P65" t="str">
-        <v>SBIN0002904</v>
+        <v>SBIN0002061</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>0300074</v>
+        <v>0300045</v>
       </c>
       <c r="B66" t="str">
-        <v>ANITA VERMA</v>
+        <v>ABDUL KALAM ALAM</v>
       </c>
       <c r="C66" t="str">
-        <v>Data Entry Operator</v>
+        <v>Teacher</v>
       </c>
       <c r="D66" t="str">
-        <v>03060</v>
+        <v>03037</v>
       </c>
       <c r="E66" t="str">
-        <v>Block Office Piprahi No.3</v>
+        <v>CDPO Office Piprahi No.2</v>
       </c>
       <c r="F66" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G66" t="str">
-        <v>9003000074</v>
+        <v>9003000045</v>
       </c>
       <c r="H66" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I66" t="str">
         <v>0302</v>
@@ -4794,7 +4842,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M66" t="str">
-        <v>30000586006</v>
+        <v>30000356355</v>
       </c>
       <c r="N66" t="str">
         <v>State Bank of India</v>
@@ -4803,48 +4851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P66" t="str">
-        <v>SBIN0005260</v>
+        <v>SBIN0003621</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>0300089</v>
+        <v>0300061</v>
       </c>
       <c r="B67" t="str">
-        <v>NEHA SINHA</v>
+        <v>MD. SHAHID SHARMA</v>
       </c>
       <c r="C67" t="str">
-        <v>Revenue Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D67" t="str">
-        <v>03068</v>
+        <v>03051</v>
       </c>
       <c r="E67" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>Middle School Sheohar</v>
       </c>
       <c r="F67" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G67" t="str">
-        <v>9003000089</v>
+        <v>9003000061</v>
       </c>
       <c r="H67" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I67" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="J67" t="str">
-        <v>Dumri Katsari</v>
+        <v>Others</v>
       </c>
       <c r="K67" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L67" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M67" t="str">
-        <v>30000704791</v>
+        <v>30000483059</v>
       </c>
       <c r="N67" t="str">
         <v>State Bank of India</v>
@@ -4853,48 +4901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P67" t="str">
-        <v>SBIN0003152</v>
+        <v>SBIN0008616</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>0300033</v>
+        <v>0300012</v>
       </c>
       <c r="B68" t="str">
-        <v>MD. IRFAN MAHTO</v>
+        <v>RAMESH GUPTA G</v>
       </c>
       <c r="C68" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Headmaster</v>
       </c>
       <c r="D68" t="str">
-        <v>03031</v>
+        <v>03012</v>
       </c>
       <c r="E68" t="str">
-        <v>Panchayat Bhawan Piprahi</v>
+        <v>Block Education Office Dumri Katsari No.1</v>
       </c>
       <c r="F68" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G68" t="str">
-        <v>9003000033</v>
+        <v>9003000012</v>
       </c>
       <c r="H68" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I68" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J68" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K68" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L68" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M68" t="str">
-        <v>30000261327</v>
+        <v>30000095028</v>
       </c>
       <c r="N68" t="str">
         <v>State Bank of India</v>
@@ -4903,48 +4951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P68" t="str">
-        <v>SBIN0002629</v>
+        <v>SBIN0008413</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>0300038</v>
+        <v>0300119</v>
       </c>
       <c r="B69" t="str">
-        <v>NIRMALA MAHTO N</v>
+        <v>PRAMOD SHARMA</v>
       </c>
       <c r="C69" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D69" t="str">
-        <v>03014</v>
+        <v>03089</v>
       </c>
       <c r="E69" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>UCO Bank, Tariyani</v>
       </c>
       <c r="F69" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G69" t="str">
-        <v>9003000038</v>
+        <v>9003000119</v>
       </c>
       <c r="H69" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I69" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J69" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K69" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L69" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M69" t="str">
-        <v>30000300922</v>
+        <v>30000942361</v>
       </c>
       <c r="N69" t="str">
         <v>State Bank of India</v>
@@ -4953,48 +5001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P69" t="str">
-        <v>SBIN0006198</v>
+        <v>SBIN0009553</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>0300015</v>
+        <v>0300072</v>
       </c>
       <c r="B70" t="str">
-        <v>NITISH PRASAD</v>
+        <v>AMIT THAKUR</v>
       </c>
       <c r="C70" t="str">
-        <v>Lecturer</v>
+        <v>Teacher</v>
       </c>
       <c r="D70" t="str">
-        <v>03015</v>
+        <v>03059</v>
       </c>
       <c r="E70" t="str">
-        <v>Block Agriculture Office Purnahiya No.2</v>
+        <v>PHC Tariyani No.1</v>
       </c>
       <c r="F70" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G70" t="str">
-        <v>9003000015</v>
+        <v>9003000072</v>
       </c>
       <c r="H70" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I70" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J70" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K70" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L70" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M70" t="str">
-        <v>30000118785</v>
+        <v>30000570168</v>
       </c>
       <c r="N70" t="str">
         <v>State Bank of India</v>
@@ -5003,48 +5051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P70" t="str">
-        <v>SBIN0005045</v>
+        <v>SBIN0001336</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>0300105</v>
+        <v>0300048</v>
       </c>
       <c r="B71" t="str">
-        <v>ALOK VERMA</v>
+        <v>NITISH MISHRA</v>
       </c>
       <c r="C71" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D71" t="str">
-        <v>03068</v>
+        <v>03040</v>
       </c>
       <c r="E71" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>Project Girls High School Sheohar No.4</v>
       </c>
       <c r="F71" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G71" t="str">
-        <v>9003000105</v>
+        <v>9003000048</v>
       </c>
       <c r="H71" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I71" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J71" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K71" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L71" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M71" t="str">
-        <v>30000831495</v>
+        <v>30000380112</v>
       </c>
       <c r="N71" t="str">
         <v>State Bank of India</v>
@@ -5053,48 +5101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P71" t="str">
-        <v>SBIN0006669</v>
+        <v>SBIN0008684</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>0300090</v>
+        <v>0300088</v>
       </c>
       <c r="B72" t="str">
-        <v>VIJAY CHAUDHARY P</v>
+        <v>SURESH CHAUDHARY</v>
       </c>
       <c r="C72" t="str">
-        <v>Assistant Engineer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D72" t="str">
-        <v>03070</v>
+        <v>03071</v>
       </c>
       <c r="E72" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>RWD Division (deputed from other district)</v>
       </c>
       <c r="F72" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G72" t="str">
-        <v>9003000090</v>
+        <v>9003000088</v>
       </c>
       <c r="H72" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I72" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J72" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K72" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="L72" t="str">
-        <v>Piprahi</v>
+        <v>Other District</v>
       </c>
       <c r="M72" t="str">
-        <v>30000712710</v>
+        <v>30000696872</v>
       </c>
       <c r="N72" t="str">
         <v>State Bank of India</v>
@@ -5103,30 +5151,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P72" t="str">
-        <v>SBIN0004290</v>
+        <v>SBIN0004501</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>0300017</v>
+        <v>0300008</v>
       </c>
       <c r="B73" t="str">
-        <v>SUNITA ANSARI</v>
+        <v>SURESH TIWARI</v>
       </c>
       <c r="C73" t="str">
-        <v>Headmaster</v>
+        <v>Lecturer</v>
       </c>
       <c r="D73" t="str">
-        <v>03017</v>
+        <v>03008</v>
       </c>
       <c r="E73" t="str">
-        <v>Block Office Tariyani No.3</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F73" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G73" t="str">
-        <v>9003000017</v>
+        <v>9003000008</v>
       </c>
       <c r="H73" t="str">
         <v>PRESIDING OFFICER</v>
@@ -5138,13 +5186,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K73" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L73" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M73" t="str">
-        <v>30000134623</v>
+        <v>30000063352</v>
       </c>
       <c r="N73" t="str">
         <v>State Bank of India</v>
@@ -5153,48 +5201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P73" t="str">
-        <v>SBIN0002120</v>
+        <v>SBIN0005760</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>0300002</v>
+        <v>0300093</v>
       </c>
       <c r="B74" t="str">
-        <v>ANIL CHAUDHARY</v>
+        <v>MAHESH SAH</v>
       </c>
       <c r="C74" t="str">
-        <v>Lecturer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D74" t="str">
-        <v>03002</v>
+        <v>03073</v>
       </c>
       <c r="E74" t="str">
-        <v>Middle School Sheohar</v>
+        <v>RWD Sub-Division Dumri Katsari</v>
       </c>
       <c r="F74" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G74" t="str">
-        <v>9003000002</v>
+        <v>9003000093</v>
       </c>
       <c r="H74" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I74" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J74" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K74" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L74" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M74" t="str">
-        <v>30000015838</v>
+        <v>30000736467</v>
       </c>
       <c r="N74" t="str">
         <v>State Bank of India</v>
@@ -5203,48 +5251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P74" t="str">
-        <v>SBIN0003477</v>
+        <v>SBIN0003159</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>0300110</v>
+        <v>0300092</v>
       </c>
       <c r="B75" t="str">
-        <v>AJAY OJHA</v>
+        <v>MD. IRFAN YADAV</v>
       </c>
       <c r="C75" t="str">
-        <v>Administrative Officer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D75" t="str">
-        <v>03080</v>
+        <v>03041</v>
       </c>
       <c r="E75" t="str">
-        <v>UCO Bank, Tariyani</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F75" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G75" t="str">
-        <v>9003000110</v>
+        <v>9003000092</v>
       </c>
       <c r="H75" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I75" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J75" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K75" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L75" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M75" t="str">
-        <v>30000871090</v>
+        <v>30000728548</v>
       </c>
       <c r="N75" t="str">
         <v>State Bank of India</v>
@@ -5253,48 +5301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P75" t="str">
-        <v>SBIN0003717</v>
+        <v>SBIN0003522</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>0300098</v>
+        <v>0300076</v>
       </c>
       <c r="B76" t="str">
-        <v>PRIYANKA PRASAD</v>
+        <v>MAMTA ANSARI</v>
       </c>
       <c r="C76" t="str">
-        <v>Junior Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D76" t="str">
-        <v>03074</v>
+        <v>03062</v>
       </c>
       <c r="E76" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Middle School Sheohar No.3</v>
       </c>
       <c r="F76" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G76" t="str">
-        <v>9003000098</v>
+        <v>9003000076</v>
       </c>
       <c r="H76" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I76" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J76" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K76" t="str">
         <v>0301</v>
       </c>
-      <c r="J76" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K76" t="str">
-        <v>0302</v>
-      </c>
       <c r="L76" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M76" t="str">
-        <v>30000776062</v>
+        <v>30000601844</v>
       </c>
       <c r="N76" t="str">
         <v>State Bank of India</v>
@@ -5303,33 +5351,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P76" t="str">
-        <v>SBIN0002632</v>
+        <v>SBIN0005596</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>0300116</v>
+        <v>0300021</v>
       </c>
       <c r="B77" t="str">
-        <v>RANJIT ANSARI</v>
+        <v>ARVIND PRASAD</v>
       </c>
       <c r="C77" t="str">
-        <v>Postmaster</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D77" t="str">
-        <v>03087</v>
+        <v>03019</v>
       </c>
       <c r="E77" t="str">
-        <v>BSNL Exchange, Purnahiya</v>
+        <v>Primary School Dumri Katsari</v>
       </c>
       <c r="F77" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G77" t="str">
-        <v>9003000116</v>
+        <v>9003000021</v>
       </c>
       <c r="H77" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I77" t="str">
         <v>0303</v>
@@ -5338,13 +5386,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K77" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L77" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M77" t="str">
-        <v>30000918604</v>
+        <v>30000166299</v>
       </c>
       <c r="N77" t="str">
         <v>State Bank of India</v>
@@ -5353,48 +5401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P77" t="str">
-        <v>SBIN0008676</v>
+        <v>SBIN0009427</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>0300036</v>
+        <v>0300079</v>
       </c>
       <c r="B78" t="str">
-        <v>MAMTA KUMAR</v>
+        <v>RAJESH ANSARI K</v>
       </c>
       <c r="C78" t="str">
-        <v>Head Clerk</v>
+        <v>Clerk</v>
       </c>
       <c r="D78" t="str">
-        <v>03034</v>
+        <v>03065</v>
       </c>
       <c r="E78" t="str">
-        <v>Project Girls High School Purnahiya No.4</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="F78" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G78" t="str">
-        <v>9003000036</v>
+        <v>9003000079</v>
       </c>
       <c r="H78" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I78" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J78" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K78" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L78" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M78" t="str">
-        <v>30000285084</v>
+        <v>30000625601</v>
       </c>
       <c r="N78" t="str">
         <v>State Bank of India</v>
@@ -5403,48 +5451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P78" t="str">
-        <v>SBIN0002033</v>
+        <v>SBIN0007906</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0300106</v>
+        <v>0300052</v>
       </c>
       <c r="B79" t="str">
-        <v>NITISH ALAM</v>
+        <v>NITISH JHA</v>
       </c>
       <c r="C79" t="str">
-        <v>Postmaster</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D79" t="str">
-        <v>03080</v>
+        <v>03043</v>
       </c>
       <c r="E79" t="str">
-        <v>UCO Bank, Tariyani</v>
+        <v>CDPO Office Piprahi No.3</v>
       </c>
       <c r="F79" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G79" t="str">
-        <v>9003000106</v>
+        <v>9003000052</v>
       </c>
       <c r="H79" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I79" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J79" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K79" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L79" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M79" t="str">
-        <v>30000839414</v>
+        <v>30000411788</v>
       </c>
       <c r="N79" t="str">
         <v>State Bank of India</v>
@@ -5453,48 +5501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P79" t="str">
-        <v>SBIN0004822</v>
+        <v>SBIN0006158</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>0300030</v>
+        <v>0300109</v>
       </c>
       <c r="B80" t="str">
-        <v>DEEPAK PASWAN</v>
+        <v>ABDUL KALAM GUPTA Z</v>
       </c>
       <c r="C80" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Postmaster</v>
       </c>
       <c r="D80" t="str">
-        <v>03028</v>
+        <v>03083</v>
       </c>
       <c r="E80" t="str">
-        <v>CDPO Office Tariyani No.1</v>
+        <v>BSNL Exchange, Purnahiya</v>
       </c>
       <c r="F80" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G80" t="str">
-        <v>9003000030</v>
+        <v>9003000109</v>
       </c>
       <c r="H80" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I80" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J80" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K80" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L80" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M80" t="str">
-        <v>30000237570</v>
+        <v>30000863171</v>
       </c>
       <c r="N80" t="str">
         <v>State Bank of India</v>
@@ -5503,48 +5551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P80" t="str">
-        <v>SBIN0002891</v>
+        <v>SBIN0001645</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>0300009</v>
+        <v>0300059</v>
       </c>
       <c r="B81" t="str">
-        <v>FARHAT SINHA</v>
+        <v>VIJAY PANDEY</v>
       </c>
       <c r="C81" t="str">
-        <v>Section Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D81" t="str">
-        <v>03009</v>
+        <v>03003</v>
       </c>
       <c r="E81" t="str">
-        <v>PHC Piprahi No.4</v>
+        <v>Block Education Office Dumri Katsari</v>
       </c>
       <c r="F81" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G81" t="str">
-        <v>9003000009</v>
+        <v>9003000059</v>
       </c>
       <c r="H81" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I81" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J81" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K81" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L81" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M81" t="str">
-        <v>30000071271</v>
+        <v>30000467221</v>
       </c>
       <c r="N81" t="str">
         <v>State Bank of India</v>
@@ -5553,48 +5601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P81" t="str">
-        <v>SBIN0004292</v>
+        <v>SBIN0002077</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>0300109</v>
+        <v>0300081</v>
       </c>
       <c r="B82" t="str">
-        <v>NITISH PANDEY</v>
+        <v>SAVITA RAM</v>
       </c>
       <c r="C82" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D82" t="str">
-        <v>03082</v>
+        <v>03067</v>
       </c>
       <c r="E82" t="str">
-        <v>BSNL Exchange, Tariyani</v>
+        <v>Block Office Piprahi No.4</v>
       </c>
       <c r="F82" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G82" t="str">
-        <v>9003000109</v>
+        <v>9003000081</v>
       </c>
       <c r="H82" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I82" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J82" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K82" t="str">
         <v>0302</v>
       </c>
-      <c r="J82" t="str">
+      <c r="L82" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K82" t="str">
-        <v>0305</v>
-      </c>
-      <c r="L82" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="M82" t="str">
-        <v>30000863171</v>
+        <v>30000641439</v>
       </c>
       <c r="N82" t="str">
         <v>State Bank of India</v>
@@ -5603,48 +5651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P82" t="str">
-        <v>SBIN0002305</v>
+        <v>SBIN0003067</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>0300022</v>
+        <v>0300003</v>
       </c>
       <c r="B83" t="str">
-        <v>ANITA JHA</v>
+        <v>RAMESH GUPTA</v>
       </c>
       <c r="C83" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D83" t="str">
-        <v>03011</v>
+        <v>03003</v>
       </c>
       <c r="E83" t="str">
-        <v>Block Office Tariyani</v>
+        <v>Block Education Office Dumri Katsari</v>
       </c>
       <c r="F83" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G83" t="str">
-        <v>9003000022</v>
+        <v>9003000003</v>
       </c>
       <c r="H83" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I83" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="J83" t="str">
-        <v>Others</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K83" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L83" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M83" t="str">
-        <v>30000174218</v>
+        <v>30000023757</v>
       </c>
       <c r="N83" t="str">
         <v>State Bank of India</v>
@@ -5653,30 +5701,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P83" t="str">
-        <v>SBIN0009776</v>
+        <v>SBIN0007073</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>0300072</v>
+        <v>0300067</v>
       </c>
       <c r="B84" t="str">
-        <v>VIJAY GUPTA</v>
+        <v>SANTOSH SAH</v>
       </c>
       <c r="C84" t="str">
-        <v>Teacher</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D84" t="str">
-        <v>03058</v>
+        <v>03048</v>
       </c>
       <c r="E84" t="str">
-        <v>Panchayat Bhawan Sheohar No.2</v>
+        <v>Project Girls High School Sheohar</v>
       </c>
       <c r="F84" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G84" t="str">
-        <v>9003000072</v>
+        <v>9003000067</v>
       </c>
       <c r="H84" t="str">
         <v>POLLING OFFICER-3</v>
@@ -5694,7 +5742,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M84" t="str">
-        <v>30000570168</v>
+        <v>30000530573</v>
       </c>
       <c r="N84" t="str">
         <v>State Bank of India</v>
@@ -5703,48 +5751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P84" t="str">
-        <v>SBIN0003962</v>
+        <v>SBIN0007528</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>0300059</v>
+        <v>0300070</v>
       </c>
       <c r="B85" t="str">
-        <v>RAMESH ALAM</v>
+        <v>ABDUL KALAM THAKUR</v>
       </c>
       <c r="C85" t="str">
-        <v>Teacher</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D85" t="str">
-        <v>03048</v>
+        <v>03057</v>
       </c>
       <c r="E85" t="str">
-        <v>Circle Office Dumri Katsari No.3</v>
+        <v>Middle School Purnahiya</v>
       </c>
       <c r="F85" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G85" t="str">
-        <v>9003000059</v>
+        <v>9003000070</v>
       </c>
       <c r="H85" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I85" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J85" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K85" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L85" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M85" t="str">
-        <v>30000467221</v>
+        <v>30000554330</v>
       </c>
       <c r="N85" t="str">
         <v>State Bank of India</v>
@@ -5753,48 +5801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P85" t="str">
-        <v>SBIN0007485</v>
+        <v>SBIN0002281</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>0300122</v>
+        <v>0300074</v>
       </c>
       <c r="B86" t="str">
-        <v>ANITA YADAV</v>
+        <v>MAHESH OJHA</v>
       </c>
       <c r="C86" t="str">
-        <v>Branch Manager</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D86" t="str">
-        <v>03083</v>
+        <v>03061</v>
       </c>
       <c r="E86" t="str">
-        <v>Central Bank of India, Piprahi</v>
+        <v>High School Tariyani No.2</v>
       </c>
       <c r="F86" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G86" t="str">
-        <v>9003000122</v>
+        <v>9003000074</v>
       </c>
       <c r="H86" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I86" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J86" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K86" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L86" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M86" t="str">
-        <v>30000966118</v>
+        <v>30000586006</v>
       </c>
       <c r="N86" t="str">
         <v>State Bank of India</v>
@@ -5803,48 +5851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P86" t="str">
-        <v>SBIN0004038</v>
+        <v>SBIN0003465</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>0300016</v>
+        <v>0300005</v>
       </c>
       <c r="B87" t="str">
-        <v>NASREEN DEVI</v>
+        <v>UMESH SINHA</v>
       </c>
       <c r="C87" t="str">
-        <v>Headmaster</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D87" t="str">
-        <v>03016</v>
+        <v>03005</v>
       </c>
       <c r="E87" t="str">
-        <v>Kanya Middle School Tariyani No.4</v>
+        <v>District Education Office (deputed from other district)</v>
       </c>
       <c r="F87" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G87" t="str">
-        <v>9003000016</v>
+        <v>9003000005</v>
       </c>
       <c r="H87" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I87" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J87" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K87" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="L87" t="str">
-        <v>Tariyani</v>
+        <v>Other District</v>
       </c>
       <c r="M87" t="str">
-        <v>30000126704</v>
+        <v>30000039595</v>
       </c>
       <c r="N87" t="str">
         <v>State Bank of India</v>
@@ -5853,39 +5901,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P87" t="str">
-        <v>SBIN0009616</v>
+        <v>SBIN0003733</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>0300078</v>
+        <v>0300103</v>
       </c>
       <c r="B88" t="str">
-        <v>VINOD ANSARI</v>
+        <v>ABDUL KALAM GUPTA P</v>
       </c>
       <c r="C88" t="str">
-        <v>Office Assistant</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D88" t="str">
-        <v>03063</v>
+        <v>03041</v>
       </c>
       <c r="E88" t="str">
-        <v>Project Girls High School Piprahi No.1</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F88" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G88" t="str">
-        <v>9003000078</v>
+        <v>9003000103</v>
       </c>
       <c r="H88" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I88" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="J88" t="str">
-        <v>Others</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K88" t="str">
         <v>0302</v>
@@ -5894,7 +5942,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M88" t="str">
-        <v>30000617682</v>
+        <v>30000815657</v>
       </c>
       <c r="N88" t="str">
         <v>State Bank of India</v>
@@ -5903,48 +5951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P88" t="str">
-        <v>SBIN0001270</v>
+        <v>SBIN0008334</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>0300123</v>
+        <v>0300082</v>
       </c>
       <c r="B89" t="str">
-        <v>RINKU YADAV N</v>
+        <v>VIJAY SHARMA</v>
       </c>
       <c r="C89" t="str">
-        <v>Assistant Manager</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D89" t="str">
-        <v>03093</v>
+        <v>03068</v>
       </c>
       <c r="E89" t="str">
-        <v>Punjab National Bank, Tariyani</v>
+        <v>Circle Office Dumri Katsari No.4</v>
       </c>
       <c r="F89" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G89" t="str">
-        <v>9003000123</v>
+        <v>9003000082</v>
       </c>
       <c r="H89" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I89" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J89" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K89" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L89" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M89" t="str">
-        <v>30000974037</v>
+        <v>30000649358</v>
       </c>
       <c r="N89" t="str">
         <v>State Bank of India</v>
@@ -5953,33 +6001,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P89" t="str">
-        <v>SBIN0002702</v>
+        <v>SBIN0002839</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>0300107</v>
+        <v>0300053</v>
       </c>
       <c r="B90" t="str">
-        <v>RAJESH ALAM</v>
+        <v>RANJIT MAHTO</v>
       </c>
       <c r="C90" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D90" t="str">
-        <v>03081</v>
+        <v>03044</v>
       </c>
       <c r="E90" t="str">
-        <v>Central Bank of India, Dumri Katsari</v>
+        <v>Block Agriculture Office Dumri Katsari No.1</v>
       </c>
       <c r="F90" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G90" t="str">
-        <v>9003000107</v>
+        <v>9003000053</v>
       </c>
       <c r="H90" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I90" t="str">
         <v>0304</v>
@@ -5994,7 +6042,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M90" t="str">
-        <v>30000847333</v>
+        <v>30000419707</v>
       </c>
       <c r="N90" t="str">
         <v>State Bank of India</v>
@@ -6003,48 +6051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P90" t="str">
-        <v>SBIN0007957</v>
+        <v>SBIN0007952</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>0300087</v>
+        <v>0300043</v>
       </c>
       <c r="B91" t="str">
-        <v>AJAY THAKUR S</v>
+        <v>USHA KHATUN</v>
       </c>
       <c r="C91" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D91" t="str">
-        <v>03024</v>
+        <v>03036</v>
       </c>
       <c r="E91" t="str">
-        <v>RWD Division (deputed from other district)</v>
+        <v>Middle School Tariyani No.3</v>
       </c>
       <c r="F91" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G91" t="str">
-        <v>9003000087</v>
+        <v>9003000043</v>
       </c>
       <c r="H91" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I91" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J91" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K91" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="L91" t="str">
-        <v>Other District</v>
+        <v>Tariyani</v>
       </c>
       <c r="M91" t="str">
-        <v>30000688953</v>
+        <v>30000340517</v>
       </c>
       <c r="N91" t="str">
         <v>State Bank of India</v>
@@ -6053,48 +6101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P91" t="str">
-        <v>SBIN0002070</v>
+        <v>SBIN0002886</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>0300001</v>
+        <v>0300062</v>
       </c>
       <c r="B92" t="str">
-        <v>RAVI SHARMA</v>
+        <v>SUNIL RAM</v>
       </c>
       <c r="C92" t="str">
-        <v>Assistant Engineer</v>
+        <v>Accountant</v>
       </c>
       <c r="D92" t="str">
-        <v>03001</v>
+        <v>03052</v>
       </c>
       <c r="E92" t="str">
-        <v>Circle Office Piprahi No.1</v>
+        <v>Block Office Purnahiya No.1</v>
       </c>
       <c r="F92" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G92" t="str">
-        <v>9003000001</v>
+        <v>9003000062</v>
       </c>
       <c r="H92" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I92" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J92" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K92" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L92" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M92" t="str">
-        <v>30000007919</v>
+        <v>30000490978</v>
       </c>
       <c r="N92" t="str">
         <v>State Bank of India</v>
@@ -6103,39 +6151,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P92" t="str">
-        <v>SBIN0007384</v>
+        <v>SBIN0007817</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>0300084</v>
+        <v>0300095</v>
       </c>
       <c r="B93" t="str">
-        <v>POONAM GUPTA</v>
+        <v>ABDUL KALAM ALAM L</v>
       </c>
       <c r="C93" t="str">
-        <v>Data Entry Operator</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D93" t="str">
-        <v>03067</v>
+        <v>03074</v>
       </c>
       <c r="E93" t="str">
-        <v>Block Education Office Dumri Katsari</v>
+        <v>Minor Irrigation Office Dumri Katsari</v>
       </c>
       <c r="F93" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G93" t="str">
-        <v>9003000084</v>
+        <v>9003000095</v>
       </c>
       <c r="H93" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I93" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J93" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K93" t="str">
         <v>0304</v>
@@ -6144,7 +6192,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M93" t="str">
-        <v>30000665196</v>
+        <v>30000752305</v>
       </c>
       <c r="N93" t="str">
         <v>State Bank of India</v>
@@ -6153,48 +6201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P93" t="str">
-        <v>SBIN0002041</v>
+        <v>SBIN0009533</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>0300047</v>
+        <v>0300068</v>
       </c>
       <c r="B94" t="str">
-        <v>RANJIT JHA</v>
+        <v>SUNITA SINGH</v>
       </c>
       <c r="C94" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D94" t="str">
-        <v>03040</v>
+        <v>03055</v>
       </c>
       <c r="E94" t="str">
-        <v>Kanya Middle School Sheohar No.2</v>
+        <v>Middle School Purnahiya No.1</v>
       </c>
       <c r="F94" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G94" t="str">
-        <v>9003000047</v>
+        <v>9003000068</v>
       </c>
       <c r="H94" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I94" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J94" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K94" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L94" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M94" t="str">
-        <v>30000372193</v>
+        <v>30000538492</v>
       </c>
       <c r="N94" t="str">
         <v>State Bank of India</v>
@@ -6203,48 +6251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P94" t="str">
-        <v>SBIN0007154</v>
+        <v>SBIN0003394</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>0300060</v>
+        <v>0300036</v>
       </c>
       <c r="B95" t="str">
-        <v>AMIT SAH</v>
+        <v>ARVIND CHAUDHARY</v>
       </c>
       <c r="C95" t="str">
-        <v>Accountant</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D95" t="str">
-        <v>03049</v>
+        <v>03031</v>
       </c>
       <c r="E95" t="str">
-        <v>CDPO Office Sheohar No.2</v>
+        <v>Middle School Purnahiya No.3</v>
       </c>
       <c r="F95" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G95" t="str">
-        <v>9003000060</v>
+        <v>9003000036</v>
       </c>
       <c r="H95" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I95" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J95" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K95" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L95" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M95" t="str">
-        <v>30000475140</v>
+        <v>30000285084</v>
       </c>
       <c r="N95" t="str">
         <v>State Bank of India</v>
@@ -6253,48 +6301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P95" t="str">
-        <v>SBIN0002661</v>
+        <v>SBIN0009063</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>0300093</v>
+        <v>0300049</v>
       </c>
       <c r="B96" t="str">
-        <v>DINESH PASWAN G</v>
+        <v>NEHA SINGH</v>
       </c>
       <c r="C96" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D96" t="str">
-        <v>03011</v>
+        <v>03041</v>
       </c>
       <c r="E96" t="str">
-        <v>Block Office Tariyani</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F96" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G96" t="str">
-        <v>9003000093</v>
+        <v>9003000049</v>
       </c>
       <c r="H96" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I96" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J96" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K96" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L96" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M96" t="str">
-        <v>30000736467</v>
+        <v>30000388031</v>
       </c>
       <c r="N96" t="str">
         <v>State Bank of India</v>
@@ -6303,33 +6351,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P96" t="str">
-        <v>SBIN0005349</v>
+        <v>SBIN0008748</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0300055</v>
+        <v>0300110</v>
       </c>
       <c r="B97" t="str">
-        <v>AMIT RAI</v>
+        <v>KUMARI ANJALI PRASAD</v>
       </c>
       <c r="C97" t="str">
-        <v>Teacher</v>
+        <v>Postmaster</v>
       </c>
       <c r="D97" t="str">
-        <v>03044</v>
+        <v>03084</v>
       </c>
       <c r="E97" t="str">
-        <v>Primary School Sheohar No.3</v>
+        <v>State Bank of India, Sheohar</v>
       </c>
       <c r="F97" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G97" t="str">
-        <v>9003000055</v>
+        <v>9003000110</v>
       </c>
       <c r="H97" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I97" t="str">
         <v>0301</v>
@@ -6344,7 +6392,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M97" t="str">
-        <v>30000435545</v>
+        <v>30000871090</v>
       </c>
       <c r="N97" t="str">
         <v>State Bank of India</v>
@@ -6353,48 +6401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P97" t="str">
-        <v>SBIN0002164</v>
+        <v>SBIN0007757</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>0300061</v>
+        <v>0300035</v>
       </c>
       <c r="B98" t="str">
-        <v>RAKESH JHA</v>
+        <v>AMIT SAH</v>
       </c>
       <c r="C98" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D98" t="str">
-        <v>03050</v>
+        <v>03030</v>
       </c>
       <c r="E98" t="str">
-        <v>Block Office Tariyani No.4</v>
+        <v>Circle Office Sheohar No.2</v>
       </c>
       <c r="F98" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G98" t="str">
-        <v>9003000061</v>
+        <v>9003000035</v>
       </c>
       <c r="H98" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I98" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J98" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K98" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L98" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M98" t="str">
-        <v>30000483059</v>
+        <v>30000277165</v>
       </c>
       <c r="N98" t="str">
         <v>State Bank of India</v>
@@ -6403,39 +6451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P98" t="str">
-        <v>SBIN0002248</v>
+        <v>SBIN0007616</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>0300012</v>
+        <v>0300028</v>
       </c>
       <c r="B99" t="str">
-        <v>PRIYANKA RAI</v>
+        <v>NIRMALA PASWAN</v>
       </c>
       <c r="C99" t="str">
-        <v>Lecturer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D99" t="str">
-        <v>03012</v>
+        <v>03020</v>
       </c>
       <c r="E99" t="str">
-        <v>Block Office Sheohar No.3</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F99" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G99" t="str">
-        <v>9003000012</v>
+        <v>9003000028</v>
       </c>
       <c r="H99" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I99" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="J99" t="str">
-        <v>Others</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K99" t="str">
         <v>0301</v>
@@ -6444,7 +6492,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M99" t="str">
-        <v>30000095028</v>
+        <v>30000221732</v>
       </c>
       <c r="N99" t="str">
         <v>State Bank of India</v>
@@ -6453,39 +6501,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P99" t="str">
-        <v>SBIN0005887</v>
+        <v>SBIN0006334</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>0300073</v>
+        <v>0300084</v>
       </c>
       <c r="B100" t="str">
-        <v>FARHAT DEVI</v>
+        <v>VINOD MAHTO</v>
       </c>
       <c r="C100" t="str">
         <v>Teacher</v>
       </c>
       <c r="D100" t="str">
-        <v>03059</v>
+        <v>03017</v>
       </c>
       <c r="E100" t="str">
-        <v>Kanya Middle School Sheohar No.1</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F100" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G100" t="str">
-        <v>9003000073</v>
+        <v>9003000084</v>
       </c>
       <c r="H100" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I100" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J100" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K100" t="str">
         <v>0301</v>
@@ -6494,7 +6542,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M100" t="str">
-        <v>30000578087</v>
+        <v>30000665196</v>
       </c>
       <c r="N100" t="str">
         <v>State Bank of India</v>
@@ -6503,7 +6551,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P100" t="str">
-        <v>SBIN0006398</v>
+        <v>SBIN0009854</v>
       </c>
     </row>
     <row r="101">
@@ -6511,19 +6559,19 @@
         <v>0300031</v>
       </c>
       <c r="B101" t="str">
-        <v>KUMARI ANJALI KHATUN</v>
+        <v>MUKESH MISHRA</v>
       </c>
       <c r="C101" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D101" t="str">
-        <v>03029</v>
+        <v>03017</v>
       </c>
       <c r="E101" t="str">
-        <v>PHC Purnahiya No.1</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F101" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G101" t="str">
         <v>9003000031</v>
@@ -6532,16 +6580,16 @@
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I101" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J101" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K101" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L101" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M101" t="str">
         <v>30000245489</v>
@@ -6553,33 +6601,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P101" t="str">
-        <v>SBIN0007100</v>
+        <v>SBIN0009394</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>0300041</v>
+        <v>0300080</v>
       </c>
       <c r="B102" t="str">
-        <v>DINESH KUMAR</v>
+        <v>SURESH PASWAN</v>
       </c>
       <c r="C102" t="str">
-        <v>Head Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D102" t="str">
-        <v>03019</v>
+        <v>03066</v>
       </c>
       <c r="E102" t="str">
-        <v>PHED Division (deputed from other district)</v>
+        <v>Middle School Tariyani No.4</v>
       </c>
       <c r="F102" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G102" t="str">
-        <v>9003000041</v>
+        <v>9003000080</v>
       </c>
       <c r="H102" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I102" t="str">
         <v>0301</v>
@@ -6588,13 +6636,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K102" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="L102" t="str">
-        <v>Other District</v>
+        <v>Tariyani</v>
       </c>
       <c r="M102" t="str">
-        <v>30000324679</v>
+        <v>30000633520</v>
       </c>
       <c r="N102" t="str">
         <v>State Bank of India</v>
@@ -6603,33 +6651,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P102" t="str">
-        <v>SBIN0007855</v>
+        <v>SBIN0006021</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>0300079</v>
+        <v>0300116</v>
       </c>
       <c r="B103" t="str">
-        <v>MAHESH RAM</v>
+        <v>RINKU YADAV</v>
       </c>
       <c r="C103" t="str">
-        <v>Clerk</v>
+        <v>Postmaster</v>
       </c>
       <c r="D103" t="str">
-        <v>03064</v>
+        <v>03087</v>
       </c>
       <c r="E103" t="str">
-        <v>Block Office Piprahi No.4</v>
+        <v>BSNL Exchange, Piprahi</v>
       </c>
       <c r="F103" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G103" t="str">
-        <v>9003000079</v>
+        <v>9003000116</v>
       </c>
       <c r="H103" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I103" t="str">
         <v>0302</v>
@@ -6644,7 +6692,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M103" t="str">
-        <v>30000625601</v>
+        <v>30000918604</v>
       </c>
       <c r="N103" t="str">
         <v>State Bank of India</v>
@@ -6653,48 +6701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P103" t="str">
-        <v>SBIN0009296</v>
+        <v>SBIN0003147</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>0300014</v>
+        <v>0300069</v>
       </c>
       <c r="B104" t="str">
-        <v>SHAILESH MISHRA</v>
+        <v>KIRAN ANSARI</v>
       </c>
       <c r="C104" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D104" t="str">
-        <v>03014</v>
+        <v>03056</v>
       </c>
       <c r="E104" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>Block Agriculture Office Purnahiya No.2</v>
       </c>
       <c r="F104" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G104" t="str">
-        <v>9003000014</v>
+        <v>9003000069</v>
       </c>
       <c r="H104" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I104" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J104" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K104" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L104" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M104" t="str">
-        <v>30000110866</v>
+        <v>30000546411</v>
       </c>
       <c r="N104" t="str">
         <v>State Bank of India</v>
@@ -6703,48 +6751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P104" t="str">
-        <v>SBIN0009030</v>
+        <v>SBIN0005046</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>0300008</v>
+        <v>0300108</v>
       </c>
       <c r="B105" t="str">
-        <v>AMIT VERMA</v>
+        <v>RAJESH RAI</v>
       </c>
       <c r="C105" t="str">
-        <v>Headmaster</v>
+        <v>Postmaster</v>
       </c>
       <c r="D105" t="str">
-        <v>03008</v>
+        <v>03082</v>
       </c>
       <c r="E105" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Head Post Office, Tariyani</v>
       </c>
       <c r="F105" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G105" t="str">
-        <v>9003000008</v>
+        <v>9003000108</v>
       </c>
       <c r="H105" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I105" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J105" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K105" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L105" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M105" t="str">
-        <v>30000063352</v>
+        <v>30000855252</v>
       </c>
       <c r="N105" t="str">
         <v>State Bank of India</v>
@@ -6753,48 +6801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P105" t="str">
-        <v>SBIN0005803</v>
+        <v>SBIN0001882</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>0300056</v>
+        <v>0300105</v>
       </c>
       <c r="B106" t="str">
-        <v>PRAMOD SAH</v>
+        <v>PANKAJ ALAM T</v>
       </c>
       <c r="C106" t="str">
-        <v>Clerk</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D106" t="str">
-        <v>03045</v>
+        <v>03008</v>
       </c>
       <c r="E106" t="str">
-        <v>Panchayat Bhawan Sheohar</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F106" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G106" t="str">
-        <v>9003000056</v>
+        <v>9003000105</v>
       </c>
       <c r="H106" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I106" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J106" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K106" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L106" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M106" t="str">
-        <v>30000443464</v>
+        <v>30000831495</v>
       </c>
       <c r="N106" t="str">
         <v>State Bank of India</v>
@@ -6803,48 +6851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P106" t="str">
-        <v>SBIN0004128</v>
+        <v>SBIN0007569</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>0300029</v>
+        <v>0300090</v>
       </c>
       <c r="B107" t="str">
-        <v>SURESH RAI</v>
+        <v>PRAMOD MAHTO</v>
       </c>
       <c r="C107" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D107" t="str">
-        <v>03027</v>
+        <v>03002</v>
       </c>
       <c r="E107" t="str">
-        <v>High School Piprahi</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F107" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G107" t="str">
-        <v>9003000029</v>
+        <v>9003000090</v>
       </c>
       <c r="H107" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I107" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J107" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K107" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L107" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M107" t="str">
-        <v>30000229651</v>
+        <v>30000712710</v>
       </c>
       <c r="N107" t="str">
         <v>State Bank of India</v>
@@ -6853,48 +6901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P107" t="str">
-        <v>SBIN0005618</v>
+        <v>SBIN0008671</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>0300102</v>
+        <v>0300038</v>
       </c>
       <c r="B108" t="str">
-        <v>USHA PANDEY</v>
+        <v>RAJESH KHATUN</v>
       </c>
       <c r="C108" t="str">
-        <v>Revenue Officer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D108" t="str">
-        <v>03075</v>
+        <v>03033</v>
       </c>
       <c r="E108" t="str">
-        <v>Circle Office Sheohar</v>
+        <v>Kanya Middle School Piprahi No.4</v>
       </c>
       <c r="F108" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G108" t="str">
-        <v>9003000102</v>
+        <v>9003000038</v>
       </c>
       <c r="H108" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I108" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J108" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K108" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L108" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M108" t="str">
-        <v>30000807738</v>
+        <v>30000300922</v>
       </c>
       <c r="N108" t="str">
         <v>State Bank of India</v>
@@ -6903,48 +6951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P108" t="str">
-        <v>SBIN0006329</v>
+        <v>SBIN0003432</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>0300040</v>
+        <v>0300033</v>
       </c>
       <c r="B109" t="str">
-        <v>SAVITA JHA</v>
+        <v>ASHA MISHRA</v>
       </c>
       <c r="C109" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D109" t="str">
-        <v>03027</v>
+        <v>03021</v>
       </c>
       <c r="E109" t="str">
-        <v>High School Piprahi</v>
+        <v>Primary School Purnahiya</v>
       </c>
       <c r="F109" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G109" t="str">
-        <v>9003000040</v>
+        <v>9003000033</v>
       </c>
       <c r="H109" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I109" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J109" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K109" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L109" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M109" t="str">
-        <v>30000316760</v>
+        <v>30000261327</v>
       </c>
       <c r="N109" t="str">
         <v>State Bank of India</v>
@@ -6953,48 +7001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P109" t="str">
-        <v>SBIN0002466</v>
+        <v>SBIN0004678</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>0300113</v>
+        <v>0300112</v>
       </c>
       <c r="B110" t="str">
-        <v>PRAMOD PANDEY</v>
+        <v>NITISH KHATUN</v>
       </c>
       <c r="C110" t="str">
         <v>Administrative Officer</v>
       </c>
       <c r="D110" t="str">
-        <v>03085</v>
+        <v>03086</v>
       </c>
       <c r="E110" t="str">
-        <v>Head Post Office, Piprahi</v>
+        <v>LIC Branch Office, Purnahiya</v>
       </c>
       <c r="F110" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G110" t="str">
-        <v>9003000113</v>
+        <v>9003000112</v>
       </c>
       <c r="H110" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I110" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J110" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K110" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L110" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M110" t="str">
-        <v>30000894847</v>
+        <v>30000886928</v>
       </c>
       <c r="N110" t="str">
         <v>State Bank of India</v>
@@ -7003,48 +7051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P110" t="str">
-        <v>SBIN0007349</v>
+        <v>SBIN0003921</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>0300070</v>
+        <v>0300124</v>
       </c>
       <c r="B111" t="str">
-        <v>ARVIND KHATUN</v>
+        <v>MUKESH MAHTO</v>
       </c>
       <c r="C111" t="str">
-        <v>Clerk</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D111" t="str">
-        <v>03010</v>
+        <v>03092</v>
       </c>
       <c r="E111" t="str">
-        <v>Block Office Tariyani No.2</v>
+        <v>Head Post Office, Dumri Katsari</v>
       </c>
       <c r="F111" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G111" t="str">
-        <v>9003000070</v>
+        <v>9003000124</v>
       </c>
       <c r="H111" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I111" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J111" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K111" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L111" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M111" t="str">
-        <v>30000554330</v>
+        <v>30000981956</v>
       </c>
       <c r="N111" t="str">
         <v>State Bank of India</v>
@@ -7053,39 +7101,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P111" t="str">
-        <v>SBIN0002886</v>
+        <v>SBIN0005736</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>0300075</v>
+        <v>0300094</v>
       </c>
       <c r="B112" t="str">
-        <v>SHAILESH MAHTO</v>
+        <v>ARVIND SAH</v>
       </c>
       <c r="C112" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D112" t="str">
-        <v>03007</v>
+        <v>03072</v>
       </c>
       <c r="E112" t="str">
-        <v>Middle School Piprahi No.3</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F112" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G112" t="str">
-        <v>9003000075</v>
+        <v>9003000094</v>
       </c>
       <c r="H112" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I112" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J112" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K112" t="str">
         <v>0302</v>
@@ -7094,7 +7142,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M112" t="str">
-        <v>30000593925</v>
+        <v>30000744386</v>
       </c>
       <c r="N112" t="str">
         <v>State Bank of India</v>
@@ -7103,48 +7151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P112" t="str">
-        <v>SBIN0005476</v>
+        <v>SBIN0008841</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>0300121</v>
+        <v>0300120</v>
       </c>
       <c r="B113" t="str">
-        <v>PRIYANKA DEVI</v>
+        <v>SUNIL DEVI</v>
       </c>
       <c r="C113" t="str">
-        <v>Administrative Officer</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D113" t="str">
-        <v>03092</v>
+        <v>03090</v>
       </c>
       <c r="E113" t="str">
-        <v>LIC Branch Office, Purnahiya</v>
+        <v>UCO Bank, Dumri Katsari</v>
       </c>
       <c r="F113" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G113" t="str">
-        <v>9003000121</v>
+        <v>9003000120</v>
       </c>
       <c r="H113" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I113" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J113" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K113" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L113" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M113" t="str">
-        <v>30000958199</v>
+        <v>30000950280</v>
       </c>
       <c r="N113" t="str">
         <v>State Bank of India</v>
@@ -7153,48 +7201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P113" t="str">
-        <v>SBIN0006764</v>
+        <v>SBIN0008351</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>0300003</v>
+        <v>0300002</v>
       </c>
       <c r="B114" t="str">
-        <v>RANJIT SINGH</v>
+        <v>USHA THAKUR</v>
       </c>
       <c r="C114" t="str">
-        <v>Assistant Engineer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D114" t="str">
-        <v>03003</v>
+        <v>03002</v>
       </c>
       <c r="E114" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F114" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G114" t="str">
-        <v>9003000003</v>
+        <v>9003000002</v>
       </c>
       <c r="H114" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I114" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J114" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K114" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L114" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M114" t="str">
-        <v>30000023757</v>
+        <v>30000015838</v>
       </c>
       <c r="N114" t="str">
         <v>State Bank of India</v>
@@ -7203,48 +7251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P114" t="str">
-        <v>SBIN0001939</v>
+        <v>SBIN0006537</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>0300005</v>
+        <v>0300122</v>
       </c>
       <c r="B115" t="str">
-        <v>DINESH YADAV</v>
+        <v>RINKU ALAM</v>
       </c>
       <c r="C115" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D115" t="str">
-        <v>03005</v>
+        <v>03085</v>
       </c>
       <c r="E115" t="str">
-        <v>Circle Office Piprahi No.3</v>
+        <v>UCO Bank, Sheohar</v>
       </c>
       <c r="F115" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G115" t="str">
-        <v>9003000005</v>
+        <v>9003000122</v>
       </c>
       <c r="H115" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I115" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J115" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K115" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L115" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M115" t="str">
-        <v>30000039595</v>
+        <v>30000966118</v>
       </c>
       <c r="N115" t="str">
         <v>State Bank of India</v>
@@ -7253,33 +7301,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P115" t="str">
-        <v>SBIN0009541</v>
+        <v>SBIN0002851</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>0300092</v>
+        <v>0300020</v>
       </c>
       <c r="B116" t="str">
-        <v>SANTOSH MISHRA</v>
+        <v>VINOD RAM</v>
       </c>
       <c r="C116" t="str">
-        <v>Assistant Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D116" t="str">
-        <v>03072</v>
+        <v>03004</v>
       </c>
       <c r="E116" t="str">
-        <v>RWD Sub-Division Dumri Katsari</v>
+        <v>High School Sheohar</v>
       </c>
       <c r="F116" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G116" t="str">
-        <v>9003000092</v>
+        <v>9003000020</v>
       </c>
       <c r="H116" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I116" t="str">
         <v>0305</v>
@@ -7288,13 +7336,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K116" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L116" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M116" t="str">
-        <v>30000728548</v>
+        <v>30000158380</v>
       </c>
       <c r="N116" t="str">
         <v>State Bank of India</v>
@@ -7303,48 +7351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P116" t="str">
-        <v>SBIN0003279</v>
+        <v>SBIN0006794</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>0300034</v>
+        <v>0300118</v>
       </c>
       <c r="B117" t="str">
-        <v>NIRMALA ALAM</v>
+        <v>DINESH VERMA</v>
       </c>
       <c r="C117" t="str">
-        <v>Assistant Teacher</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D117" t="str">
-        <v>03032</v>
+        <v>03080</v>
       </c>
       <c r="E117" t="str">
-        <v>Project Girls High School Tariyani No.1</v>
+        <v>LIC Branch Office, Piprahi</v>
       </c>
       <c r="F117" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G117" t="str">
-        <v>9003000034</v>
+        <v>9003000118</v>
       </c>
       <c r="H117" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I117" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J117" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K117" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L117" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M117" t="str">
-        <v>30000269246</v>
+        <v>30000934442</v>
       </c>
       <c r="N117" t="str">
         <v>State Bank of India</v>
@@ -7353,39 +7401,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P117" t="str">
-        <v>SBIN0008615</v>
+        <v>SBIN0009592</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>0300103</v>
+        <v>0300050</v>
       </c>
       <c r="B118" t="str">
-        <v>AJAY MISHRA</v>
+        <v>SANJAY CHAUDHARY</v>
       </c>
       <c r="C118" t="str">
-        <v>Assistant Engineer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D118" t="str">
-        <v>03078</v>
+        <v>03042</v>
       </c>
       <c r="E118" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>High School Piprahi No.3</v>
       </c>
       <c r="F118" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G118" t="str">
-        <v>9003000103</v>
+        <v>9003000050</v>
       </c>
       <c r="H118" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I118" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J118" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K118" t="str">
         <v>0302</v>
@@ -7394,7 +7442,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M118" t="str">
-        <v>30000815657</v>
+        <v>30000395950</v>
       </c>
       <c r="N118" t="str">
         <v>State Bank of India</v>
@@ -7403,48 +7451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P118" t="str">
-        <v>SBIN0008678</v>
+        <v>SBIN0004082</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>0300050</v>
+        <v>0300087</v>
       </c>
       <c r="B119" t="str">
-        <v>DINESH PASWAN V</v>
+        <v>SUNITA MISHRA</v>
       </c>
       <c r="C119" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D119" t="str">
-        <v>03026</v>
+        <v>03070</v>
       </c>
       <c r="E119" t="str">
-        <v>Project Girls High School Dumri Katsari</v>
+        <v>RWD Sub-Division Piprahi</v>
       </c>
       <c r="F119" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G119" t="str">
-        <v>9003000050</v>
+        <v>9003000087</v>
       </c>
       <c r="H119" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I119" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J119" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K119" t="str">
         <v>0302</v>
       </c>
-      <c r="J119" t="str">
+      <c r="L119" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K119" t="str">
-        <v>0304</v>
-      </c>
-      <c r="L119" t="str">
-        <v>Dumri Katsari</v>
-      </c>
       <c r="M119" t="str">
-        <v>30000395950</v>
+        <v>30000688953</v>
       </c>
       <c r="N119" t="str">
         <v>State Bank of India</v>
@@ -7453,48 +7501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P119" t="str">
-        <v>SBIN0009287</v>
+        <v>SBIN0009870</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>0300054</v>
+        <v>0300063</v>
       </c>
       <c r="B120" t="str">
-        <v>UMESH DEVI</v>
+        <v>ABDUL KALAM GUPTA</v>
       </c>
       <c r="C120" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Clerk</v>
       </c>
       <c r="D120" t="str">
-        <v>03037</v>
+        <v>03026</v>
       </c>
       <c r="E120" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F120" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G120" t="str">
-        <v>9003000054</v>
+        <v>9003000063</v>
       </c>
       <c r="H120" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I120" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J120" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K120" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L120" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M120" t="str">
-        <v>30000427626</v>
+        <v>30000498897</v>
       </c>
       <c r="N120" t="str">
         <v>State Bank of India</v>
@@ -7503,39 +7551,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P120" t="str">
-        <v>SBIN0001571</v>
+        <v>SBIN0006011</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>0300020</v>
+        <v>0300107</v>
       </c>
       <c r="B121" t="str">
-        <v>ASHA PRASAD</v>
+        <v>VIJAY PANDEY E</v>
       </c>
       <c r="C121" t="str">
-        <v>Section Officer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D121" t="str">
-        <v>03020</v>
+        <v>03081</v>
       </c>
       <c r="E121" t="str">
-        <v>Block Education Office Tariyani</v>
+        <v>LIC Branch Office, Tariyani</v>
       </c>
       <c r="F121" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G121" t="str">
-        <v>9003000020</v>
+        <v>9003000107</v>
       </c>
       <c r="H121" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I121" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J121" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K121" t="str">
         <v>0305</v>
@@ -7544,7 +7592,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M121" t="str">
-        <v>30000158380</v>
+        <v>30000847333</v>
       </c>
       <c r="N121" t="str">
         <v>State Bank of India</v>
@@ -7553,33 +7601,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P121" t="str">
-        <v>SBIN0005227</v>
+        <v>SBIN0001070</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>0300115</v>
+        <v>0300066</v>
       </c>
       <c r="B122" t="str">
-        <v>RINKU YADAV</v>
+        <v>RANJIT TIWARI</v>
       </c>
       <c r="C122" t="str">
-        <v>Postmaster</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D122" t="str">
-        <v>03086</v>
+        <v>03054</v>
       </c>
       <c r="E122" t="str">
-        <v>Bank of India, Piprahi</v>
+        <v>Block Education Office Piprahi</v>
       </c>
       <c r="F122" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G122" t="str">
-        <v>9003000115</v>
+        <v>9003000066</v>
       </c>
       <c r="H122" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I122" t="str">
         <v>0302</v>
@@ -7594,7 +7642,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M122" t="str">
-        <v>30000910685</v>
+        <v>30000522654</v>
       </c>
       <c r="N122" t="str">
         <v>State Bank of India</v>
@@ -7603,48 +7651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P122" t="str">
-        <v>SBIN0004243</v>
+        <v>SBIN0009437</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>0300117</v>
+        <v>0300115</v>
       </c>
       <c r="B123" t="str">
-        <v>MD. SHAHID ALAM</v>
+        <v>PANKAJ SINHA</v>
       </c>
       <c r="C123" t="str">
-        <v>Administrative Officer</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D123" t="str">
-        <v>03088</v>
+        <v>03082</v>
       </c>
       <c r="E123" t="str">
-        <v>Central Bank of India, Sheohar</v>
+        <v>Head Post Office, Tariyani</v>
       </c>
       <c r="F123" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G123" t="str">
-        <v>9003000117</v>
+        <v>9003000115</v>
       </c>
       <c r="H123" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I123" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J123" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K123" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L123" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M123" t="str">
-        <v>30000926523</v>
+        <v>30000910685</v>
       </c>
       <c r="N123" t="str">
         <v>State Bank of India</v>
@@ -7653,48 +7701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P123" t="str">
-        <v>SBIN0007368</v>
+        <v>SBIN0007683</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>0300057</v>
+        <v>0300030</v>
       </c>
       <c r="B124" t="str">
-        <v>NIRMALA MISHRA</v>
+        <v>RAVI DEVI</v>
       </c>
       <c r="C124" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D124" t="str">
-        <v>03046</v>
+        <v>03027</v>
       </c>
       <c r="E124" t="str">
-        <v>Middle School Sheohar No.3</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="F124" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G124" t="str">
-        <v>9003000057</v>
+        <v>9003000030</v>
       </c>
       <c r="H124" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I124" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J124" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K124" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L124" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M124" t="str">
-        <v>30000451383</v>
+        <v>30000237570</v>
       </c>
       <c r="N124" t="str">
         <v>State Bank of India</v>
@@ -7703,48 +7751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P124" t="str">
-        <v>SBIN0006094</v>
+        <v>SBIN0002578</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>0300045</v>
+        <v>0300071</v>
       </c>
       <c r="B125" t="str">
-        <v>REKHA VERMA</v>
+        <v>VINOD CHAUDHARY</v>
       </c>
       <c r="C125" t="str">
-        <v>Teacher</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D125" t="str">
-        <v>03038</v>
+        <v>03058</v>
       </c>
       <c r="E125" t="str">
-        <v>CDPO Office Sheohar No.1</v>
+        <v>PHC Purnahiya No.4</v>
       </c>
       <c r="F125" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G125" t="str">
-        <v>9003000045</v>
+        <v>9003000071</v>
       </c>
       <c r="H125" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I125" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J125" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K125" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L125" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M125" t="str">
-        <v>30000356355</v>
+        <v>30000562249</v>
       </c>
       <c r="N125" t="str">
         <v>State Bank of India</v>
@@ -7753,21 +7801,21 @@
         <v>Sheohar</v>
       </c>
       <c r="P125" t="str">
-        <v>SBIN0004190</v>
+        <v>SBIN0007996</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>0300118</v>
+        <v>0300106</v>
       </c>
       <c r="B126" t="str">
-        <v>NIRMALA PANDEY</v>
+        <v>SUNIL JHA</v>
       </c>
       <c r="C126" t="str">
         <v>Assistant Manager</v>
       </c>
       <c r="D126" t="str">
-        <v>03089</v>
+        <v>03080</v>
       </c>
       <c r="E126" t="str">
         <v>LIC Branch Office, Piprahi</v>
@@ -7776,16 +7824,16 @@
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G126" t="str">
-        <v>9003000118</v>
+        <v>9003000106</v>
       </c>
       <c r="H126" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I126" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J126" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K126" t="str">
         <v>0302</v>
@@ -7794,7 +7842,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M126" t="str">
-        <v>30000934442</v>
+        <v>30000839414</v>
       </c>
       <c r="N126" t="str">
         <v>State Bank of India</v>
@@ -7803,48 +7851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P126" t="str">
-        <v>SBIN0007981</v>
+        <v>SBIN0004723</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>0300032</v>
+        <v>0300023</v>
       </c>
       <c r="B127" t="str">
-        <v>UMESH YADAV</v>
+        <v>MAHESH MAHTO</v>
       </c>
       <c r="C127" t="str">
-        <v>Assistant Teacher</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D127" t="str">
-        <v>03030</v>
+        <v>03021</v>
       </c>
       <c r="E127" t="str">
-        <v>Panchayat Bhawan Dumri Katsari No.2</v>
+        <v>Primary School Purnahiya</v>
       </c>
       <c r="F127" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G127" t="str">
-        <v>9003000032</v>
+        <v>9003000023</v>
       </c>
       <c r="H127" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I127" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J127" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K127" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L127" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M127" t="str">
-        <v>30000253408</v>
+        <v>30000182137</v>
       </c>
       <c r="N127" t="str">
         <v>State Bank of India</v>
@@ -7853,7 +7901,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P127" t="str">
-        <v>SBIN0006648</v>
+        <v>SBIN0003647</v>
       </c>
     </row>
   </sheetData>
@@ -7906,7 +7954,7 @@
         <v>Main</v>
       </c>
       <c r="D2" t="str">
-        <v>Kanya Middle School Sheohar, Room 2</v>
+        <v>Middle School Sheohar, Room 2</v>
       </c>
       <c r="E2" t="str">
         <v>0301</v>
@@ -7926,7 +7974,7 @@
         <v>Main</v>
       </c>
       <c r="D3" t="str">
-        <v>Kanya Middle School Piprahi, Room 3</v>
+        <v>Panchayat Bhawan Piprahi, Room 3</v>
       </c>
       <c r="E3" t="str">
         <v>0302</v>
@@ -7946,7 +7994,7 @@
         <v>Main</v>
       </c>
       <c r="D4" t="str">
-        <v>Kanya Middle School Purnahiya, Room 1</v>
+        <v>High School Purnahiya, Room 1</v>
       </c>
       <c r="E4" t="str">
         <v>0303</v>
@@ -7966,7 +8014,7 @@
         <v>Main</v>
       </c>
       <c r="D5" t="str">
-        <v>Block Office Hall Dumri Katsari, Room 2</v>
+        <v>Panchayat Bhawan Dumri Katsari, Room 2</v>
       </c>
       <c r="E5" t="str">
         <v>0304</v>
@@ -7986,7 +8034,7 @@
         <v>Main</v>
       </c>
       <c r="D6" t="str">
-        <v>Kanya Middle School Tariyani, Room 3</v>
+        <v>High School Tariyani, Room 3</v>
       </c>
       <c r="E6" t="str">
         <v>0305</v>
@@ -8006,7 +8054,7 @@
         <v>Main</v>
       </c>
       <c r="D7" t="str">
-        <v>Kanya Middle School Sheohar, Room 1</v>
+        <v>Block Office Hall Sheohar, Room 1</v>
       </c>
       <c r="E7" t="str">
         <v>0301</v>
@@ -8026,7 +8074,7 @@
         <v>Main</v>
       </c>
       <c r="D8" t="str">
-        <v>Panchayat Bhawan Purnahiya, Room 2</v>
+        <v>Kanya Middle School Purnahiya, Room 2</v>
       </c>
       <c r="E8" t="str">
         <v>0303</v>
@@ -8046,7 +8094,7 @@
         <v>Main</v>
       </c>
       <c r="D9" t="str">
-        <v>Panchayat Bhawan Dumri Katsari, Room 3</v>
+        <v>Middle School Dumri Katsari, Room 3</v>
       </c>
       <c r="E9" t="str">
         <v>0304</v>
@@ -8086,7 +8134,7 @@
         <v>Main</v>
       </c>
       <c r="D11" t="str">
-        <v>Block Office Hall Sheohar, Room 2</v>
+        <v>High School Sheohar, Room 2</v>
       </c>
       <c r="E11" t="str">
         <v>0301</v>
@@ -8106,7 +8154,7 @@
         <v>Main</v>
       </c>
       <c r="D12" t="str">
-        <v>Panchayat Bhawan Piprahi, Room 3</v>
+        <v>Middle School Piprahi, Room 3</v>
       </c>
       <c r="E12" t="str">
         <v>0302</v>

--- a/test-data/TEST_Sheohar_Project.xlsx
+++ b/test-data/TEST_Sheohar_Project.xlsx
@@ -613,7 +613,7 @@
         <v>Saved at</v>
       </c>
       <c r="B4" t="str">
-        <v>13-10-2026 06:16:05</v>
+        <v>13-10-2026 06:23:20</v>
       </c>
     </row>
     <row r="5">
@@ -792,7 +792,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>13-10-2026 06:16:05</v>
+        <v>13-10-2026 06:23:20</v>
       </c>
       <c r="B2" t="str">
         <v>Test data generated (Small — Sheohar style (5 blocks, 6 TC + 6 GC booths))</v>
@@ -1606,28 +1606,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0300057</v>
+        <v>0300040</v>
       </c>
       <c r="B2" t="str">
-        <v>NIRMALA PRASAD</v>
+        <v>ALOK JHA</v>
       </c>
       <c r="C2" t="str">
-        <v>Clerk</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D2" t="str">
-        <v>03048</v>
+        <v>03036</v>
       </c>
       <c r="E2" t="str">
-        <v>Project Girls High School Sheohar</v>
+        <v>High School Purnahiya</v>
       </c>
       <c r="F2" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G2" t="str">
-        <v>9003000057</v>
+        <v>9003000040</v>
       </c>
       <c r="H2" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I2" t="str">
         <v>0305</v>
@@ -1636,13 +1636,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K2" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L2" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M2" t="str">
-        <v>30000451383</v>
+        <v>30000316760</v>
       </c>
       <c r="N2" t="str">
         <v>State Bank of India</v>
@@ -1651,48 +1651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P2" t="str">
-        <v>SBIN0003106</v>
+        <v>SBIN0002676</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0300054</v>
+        <v>0300095</v>
       </c>
       <c r="B3" t="str">
-        <v>RAJESH KHATUN J</v>
+        <v>MANOJ KUMAR</v>
       </c>
       <c r="C3" t="str">
-        <v>Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D3" t="str">
-        <v>03045</v>
+        <v>03076</v>
       </c>
       <c r="E3" t="str">
-        <v>Project Girls High School Sheohar No.1</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="F3" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G3" t="str">
-        <v>9003000054</v>
+        <v>9003000095</v>
       </c>
       <c r="H3" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I3" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J3" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K3" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L3" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M3" t="str">
-        <v>30000427626</v>
+        <v>30000752305</v>
       </c>
       <c r="N3" t="str">
         <v>State Bank of India</v>
@@ -1701,48 +1701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P3" t="str">
-        <v>SBIN0004951</v>
+        <v>SBIN0008847</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0300047</v>
+        <v>0300009</v>
       </c>
       <c r="B4" t="str">
-        <v>MANOJ VERMA</v>
+        <v>VINOD JHA</v>
       </c>
       <c r="C4" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Lecturer</v>
       </c>
       <c r="D4" t="str">
-        <v>03039</v>
+        <v>03009</v>
       </c>
       <c r="E4" t="str">
-        <v>Kanya Middle School Piprahi No.1</v>
+        <v>PHED Division Sheohar</v>
       </c>
       <c r="F4" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G4" t="str">
-        <v>9003000047</v>
+        <v>9003000009</v>
       </c>
       <c r="H4" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I4" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="K4" t="str">
         <v>0301</v>
       </c>
-      <c r="J4" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K4" t="str">
-        <v>0302</v>
-      </c>
       <c r="L4" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M4" t="str">
-        <v>30000372193</v>
+        <v>30000071271</v>
       </c>
       <c r="N4" t="str">
         <v>State Bank of India</v>
@@ -1751,48 +1751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P4" t="str">
-        <v>SBIN0004755</v>
+        <v>SBIN0006341</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0300007</v>
+        <v>0300073</v>
       </c>
       <c r="B5" t="str">
-        <v>SUNITA OJHA</v>
+        <v>FARHAT SHARMA</v>
       </c>
       <c r="C5" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D5" t="str">
-        <v>03007</v>
+        <v>03060</v>
       </c>
       <c r="E5" t="str">
-        <v>PHED Division (deputed from other district)</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="F5" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G5" t="str">
-        <v>9003000007</v>
+        <v>9003000073</v>
       </c>
       <c r="H5" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I5" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J5" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K5" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="L5" t="str">
-        <v>Other District</v>
+        <v>Tariyani</v>
       </c>
       <c r="M5" t="str">
-        <v>30000055433</v>
+        <v>30000578087</v>
       </c>
       <c r="N5" t="str">
         <v>State Bank of India</v>
@@ -1801,33 +1801,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P5" t="str">
-        <v>SBIN0002916</v>
+        <v>SBIN0006835</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0300001</v>
+        <v>0300046</v>
       </c>
       <c r="B6" t="str">
-        <v>PANKAJ VERMA</v>
+        <v>RAJESH KUMAR</v>
       </c>
       <c r="C6" t="str">
-        <v>Lecturer</v>
+        <v>Clerk</v>
       </c>
       <c r="D6" t="str">
-        <v>03001</v>
+        <v>03040</v>
       </c>
       <c r="E6" t="str">
-        <v>Panchayat Bhawan Sheohar No.1</v>
+        <v>Block Education Office Tariyani No.3</v>
       </c>
       <c r="F6" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G6" t="str">
-        <v>9003000001</v>
+        <v>9003000046</v>
       </c>
       <c r="H6" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I6" t="str">
         <v>0301</v>
@@ -1836,13 +1836,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K6" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L6" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M6" t="str">
-        <v>30000007919</v>
+        <v>30000364274</v>
       </c>
       <c r="N6" t="str">
         <v>State Bank of India</v>
@@ -1851,33 +1851,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P6" t="str">
-        <v>SBIN0001153</v>
+        <v>SBIN0001680</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>0300011</v>
+        <v>0300125</v>
       </c>
       <c r="B7" t="str">
-        <v>NITISH VERMA</v>
+        <v>KIRAN SINGH</v>
       </c>
       <c r="C7" t="str">
-        <v>Senior Teacher</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D7" t="str">
-        <v>03011</v>
+        <v>03098</v>
       </c>
       <c r="E7" t="str">
-        <v>PHC Dumri Katsari No.1</v>
+        <v>State Bank of India, Dumri Katsari</v>
       </c>
       <c r="F7" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G7" t="str">
-        <v>9003000011</v>
+        <v>9003000125</v>
       </c>
       <c r="H7" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I7" t="str">
         <v>0304</v>
@@ -1892,7 +1892,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M7" t="str">
-        <v>30000087109</v>
+        <v>30000989875</v>
       </c>
       <c r="N7" t="str">
         <v>State Bank of India</v>
@@ -1901,39 +1901,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P7" t="str">
-        <v>SBIN0006988</v>
+        <v>SBIN0006947</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0300041</v>
+        <v>0300054</v>
       </c>
       <c r="B8" t="str">
-        <v>ALOK KUMAR</v>
+        <v>SHAILESH MAHTO</v>
       </c>
       <c r="C8" t="str">
-        <v>Head Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D8" t="str">
-        <v>03020</v>
+        <v>03047</v>
       </c>
       <c r="E8" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>Block Office Sheohar No.2</v>
       </c>
       <c r="F8" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G8" t="str">
-        <v>9003000041</v>
+        <v>9003000054</v>
       </c>
       <c r="H8" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I8" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J8" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K8" t="str">
         <v>0301</v>
@@ -1942,7 +1942,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M8" t="str">
-        <v>30000324679</v>
+        <v>30000427626</v>
       </c>
       <c r="N8" t="str">
         <v>State Bank of India</v>
@@ -1951,33 +1951,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P8" t="str">
-        <v>SBIN0008520</v>
+        <v>SBIN0006264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0300037</v>
+        <v>0300126</v>
       </c>
       <c r="B9" t="str">
-        <v>VIJAY THAKUR</v>
+        <v>MUKESH RAM</v>
       </c>
       <c r="C9" t="str">
-        <v>Senior Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D9" t="str">
-        <v>03032</v>
+        <v>03085</v>
       </c>
       <c r="E9" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>BSNL Exchange, Purnahiya</v>
       </c>
       <c r="F9" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G9" t="str">
-        <v>9003000037</v>
+        <v>9003000126</v>
       </c>
       <c r="H9" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I9" t="str">
         <v>0302</v>
@@ -1986,13 +1986,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K9" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L9" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M9" t="str">
-        <v>30000293003</v>
+        <v>30000997794</v>
       </c>
       <c r="N9" t="str">
         <v>State Bank of India</v>
@@ -2001,48 +2001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P9" t="str">
-        <v>SBIN0006108</v>
+        <v>SBIN0001846</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0300065</v>
+        <v>0300007</v>
       </c>
       <c r="B10" t="str">
-        <v>REKHA THAKUR</v>
+        <v>MANOJ JHA</v>
       </c>
       <c r="C10" t="str">
-        <v>Teacher</v>
+        <v>Headmaster</v>
       </c>
       <c r="D10" t="str">
-        <v>03053</v>
+        <v>03007</v>
       </c>
       <c r="E10" t="str">
-        <v>Block Agriculture Office Purnahiya No.1</v>
+        <v>High School Tariyani No.1</v>
       </c>
       <c r="F10" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G10" t="str">
-        <v>9003000065</v>
+        <v>9003000007</v>
       </c>
       <c r="H10" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I10" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J10" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K10" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L10" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M10" t="str">
-        <v>30000514735</v>
+        <v>30000055433</v>
       </c>
       <c r="N10" t="str">
         <v>State Bank of India</v>
@@ -2051,48 +2051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P10" t="str">
-        <v>SBIN0004771</v>
+        <v>SBIN0002582</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>0300078</v>
+        <v>0300010</v>
       </c>
       <c r="B11" t="str">
-        <v>FARHAT RAI</v>
+        <v>DINESH PANDEY</v>
       </c>
       <c r="C11" t="str">
-        <v>Office Assistant</v>
+        <v>Lecturer</v>
       </c>
       <c r="D11" t="str">
-        <v>03064</v>
+        <v>03010</v>
       </c>
       <c r="E11" t="str">
-        <v>Circle Office Piprahi No.4</v>
+        <v>Block Agriculture Office Purnahiya No.4</v>
       </c>
       <c r="F11" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G11" t="str">
-        <v>9003000078</v>
+        <v>9003000010</v>
       </c>
       <c r="H11" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I11" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J11" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K11" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L11" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M11" t="str">
-        <v>30000617682</v>
+        <v>30000079190</v>
       </c>
       <c r="N11" t="str">
         <v>State Bank of India</v>
@@ -2101,48 +2101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P11" t="str">
-        <v>SBIN0008320</v>
+        <v>SBIN0006148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>0300117</v>
+        <v>0300079</v>
       </c>
       <c r="B12" t="str">
-        <v>MD. SHAHID KUMAR</v>
+        <v>VINOD RAI</v>
       </c>
       <c r="C12" t="str">
-        <v>Postmaster</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D12" t="str">
-        <v>03088</v>
+        <v>03064</v>
       </c>
       <c r="E12" t="str">
-        <v>LIC Branch Office, Dumri Katsari</v>
+        <v>Project Girls High School Piprahi No.4</v>
       </c>
       <c r="F12" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G12" t="str">
-        <v>9003000117</v>
+        <v>9003000079</v>
       </c>
       <c r="H12" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I12" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J12" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K12" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L12" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M12" t="str">
-        <v>30000926523</v>
+        <v>30000625601</v>
       </c>
       <c r="N12" t="str">
         <v>State Bank of India</v>
@@ -2151,48 +2151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P12" t="str">
-        <v>SBIN0008998</v>
+        <v>SBIN0006217</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0300009</v>
+        <v>0300105</v>
       </c>
       <c r="B13" t="str">
-        <v>SUNITA SHARMA</v>
+        <v>REKHA VERMA</v>
       </c>
       <c r="C13" t="str">
-        <v>Headmaster</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D13" t="str">
-        <v>03009</v>
+        <v>03077</v>
       </c>
       <c r="E13" t="str">
-        <v>High School Tariyani No.1</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F13" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G13" t="str">
-        <v>9003000009</v>
+        <v>9003000105</v>
       </c>
       <c r="H13" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I13" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J13" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K13" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L13" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M13" t="str">
-        <v>30000071271</v>
+        <v>30000831495</v>
       </c>
       <c r="N13" t="str">
         <v>State Bank of India</v>
@@ -2201,39 +2201,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P13" t="str">
-        <v>SBIN0009414</v>
+        <v>SBIN0006816</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0300040</v>
+        <v>0300057</v>
       </c>
       <c r="B14" t="str">
-        <v>SUNIL PASWAN</v>
+        <v>PRAMOD KUMAR</v>
       </c>
       <c r="C14" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D14" t="str">
-        <v>03034</v>
+        <v>03050</v>
       </c>
       <c r="E14" t="str">
-        <v>High School Tariyani No.3</v>
+        <v>High School Tariyani</v>
       </c>
       <c r="F14" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G14" t="str">
-        <v>9003000040</v>
+        <v>9003000057</v>
       </c>
       <c r="H14" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I14" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J14" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K14" t="str">
         <v>0305</v>
@@ -2242,7 +2242,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M14" t="str">
-        <v>30000316760</v>
+        <v>30000451383</v>
       </c>
       <c r="N14" t="str">
         <v>State Bank of India</v>
@@ -2251,48 +2251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P14" t="str">
-        <v>SBIN0007694</v>
+        <v>SBIN0001242</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>0300089</v>
+        <v>0300069</v>
       </c>
       <c r="B15" t="str">
-        <v>NEHA GUPTA</v>
+        <v>POONAM ALAM</v>
       </c>
       <c r="C15" t="str">
-        <v>Junior Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D15" t="str">
-        <v>03041</v>
+        <v>03057</v>
       </c>
       <c r="E15" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>CDPO Office Dumri Katsari</v>
       </c>
       <c r="F15" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G15" t="str">
-        <v>9003000089</v>
+        <v>9003000069</v>
       </c>
       <c r="H15" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I15" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J15" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K15" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L15" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M15" t="str">
-        <v>30000704791</v>
+        <v>30000546411</v>
       </c>
       <c r="N15" t="str">
         <v>State Bank of India</v>
@@ -2301,48 +2301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P15" t="str">
-        <v>SBIN0002524</v>
+        <v>SBIN0007965</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>0300114</v>
+        <v>0300110</v>
       </c>
       <c r="B16" t="str">
-        <v>MD. IRFAN SHARMA</v>
+        <v>PRIYANKA OJHA</v>
       </c>
       <c r="C16" t="str">
-        <v>Postmaster</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D16" t="str">
-        <v>03085</v>
+        <v>03087</v>
       </c>
       <c r="E16" t="str">
-        <v>UCO Bank, Sheohar</v>
+        <v>Head Post Office, Purnahiya</v>
       </c>
       <c r="F16" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G16" t="str">
-        <v>9003000114</v>
+        <v>9003000110</v>
       </c>
       <c r="H16" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I16" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J16" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K16" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L16" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M16" t="str">
-        <v>30000902766</v>
+        <v>30000871090</v>
       </c>
       <c r="N16" t="str">
         <v>State Bank of India</v>
@@ -2351,39 +2351,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P16" t="str">
-        <v>SBIN0005634</v>
+        <v>SBIN0001067</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>0300111</v>
+        <v>0300120</v>
       </c>
       <c r="B17" t="str">
-        <v>POONAM SHARMA</v>
+        <v>MUKESH PRASAD</v>
       </c>
       <c r="C17" t="str">
-        <v>Postmaster</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D17" t="str">
-        <v>03085</v>
+        <v>03094</v>
       </c>
       <c r="E17" t="str">
-        <v>UCO Bank, Sheohar</v>
+        <v>BSNL Exchange, Sheohar</v>
       </c>
       <c r="F17" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G17" t="str">
-        <v>9003000111</v>
+        <v>9003000120</v>
       </c>
       <c r="H17" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I17" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J17" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K17" t="str">
         <v>0301</v>
@@ -2392,7 +2392,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M17" t="str">
-        <v>30000879009</v>
+        <v>30000950280</v>
       </c>
       <c r="N17" t="str">
         <v>State Bank of India</v>
@@ -2401,39 +2401,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P17" t="str">
-        <v>SBIN0005085</v>
+        <v>SBIN0001348</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>0300077</v>
+        <v>0300002</v>
       </c>
       <c r="B18" t="str">
-        <v>RAVI MISHRA</v>
+        <v>MAHESH RAI</v>
       </c>
       <c r="C18" t="str">
-        <v>Clerk</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D18" t="str">
-        <v>03063</v>
+        <v>03002</v>
       </c>
       <c r="E18" t="str">
-        <v>CDPO Office Tariyani No.3</v>
+        <v>Primary School Tariyani No.2</v>
       </c>
       <c r="F18" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G18" t="str">
-        <v>9003000077</v>
+        <v>9003000002</v>
       </c>
       <c r="H18" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I18" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J18" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K18" t="str">
         <v>0305</v>
@@ -2442,7 +2442,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M18" t="str">
-        <v>30000609763</v>
+        <v>30000015838</v>
       </c>
       <c r="N18" t="str">
         <v>State Bank of India</v>
@@ -2451,33 +2451,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P18" t="str">
-        <v>SBIN0005954</v>
+        <v>SBIN0005230</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>0300125</v>
+        <v>0300005</v>
       </c>
       <c r="B19" t="str">
-        <v>KIRAN GUPTA</v>
+        <v>POONAM OJHA</v>
       </c>
       <c r="C19" t="str">
-        <v>Postmaster</v>
+        <v>Lecturer</v>
       </c>
       <c r="D19" t="str">
-        <v>03093</v>
+        <v>03005</v>
       </c>
       <c r="E19" t="str">
-        <v>Head Post Office, Sheohar</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F19" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G19" t="str">
-        <v>9003000125</v>
+        <v>9003000005</v>
       </c>
       <c r="H19" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I19" t="str">
         <v>0302</v>
@@ -2486,13 +2486,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K19" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L19" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M19" t="str">
-        <v>30000989875</v>
+        <v>30000039595</v>
       </c>
       <c r="N19" t="str">
         <v>State Bank of India</v>
@@ -2501,48 +2501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P19" t="str">
-        <v>SBIN0002960</v>
+        <v>SBIN0004196</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>0300075</v>
+        <v>0300028</v>
       </c>
       <c r="B20" t="str">
-        <v>NIRMALA KUMAR</v>
+        <v>RAKESH CHAUDHARY</v>
       </c>
       <c r="C20" t="str">
-        <v>Clerk</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D20" t="str">
-        <v>03007</v>
+        <v>03026</v>
       </c>
       <c r="E20" t="str">
-        <v>PHED Division (deputed from other district)</v>
+        <v>Project Girls High School Dumri Katsari No.1</v>
       </c>
       <c r="F20" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G20" t="str">
-        <v>9003000075</v>
+        <v>9003000028</v>
       </c>
       <c r="H20" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I20" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K20" t="str">
         <v>0304</v>
       </c>
-      <c r="J20" t="str">
+      <c r="L20" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="K20" t="str">
-        <v>999999</v>
-      </c>
-      <c r="L20" t="str">
-        <v>Other District</v>
-      </c>
       <c r="M20" t="str">
-        <v>30000593925</v>
+        <v>30000221732</v>
       </c>
       <c r="N20" t="str">
         <v>State Bank of India</v>
@@ -2551,39 +2551,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P20" t="str">
-        <v>SBIN0009995</v>
+        <v>SBIN0004117</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>0300123</v>
+        <v>0300024</v>
       </c>
       <c r="B21" t="str">
-        <v>ANIL THAKUR</v>
+        <v>PRAMOD RAM</v>
       </c>
       <c r="C21" t="str">
-        <v>Branch Manager</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D21" t="str">
-        <v>03091</v>
+        <v>03022</v>
       </c>
       <c r="E21" t="str">
-        <v>BSNL Exchange, Tariyani</v>
+        <v>Middle School Tariyani No.2</v>
       </c>
       <c r="F21" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G21" t="str">
-        <v>9003000123</v>
+        <v>9003000024</v>
       </c>
       <c r="H21" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I21" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J21" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K21" t="str">
         <v>0305</v>
@@ -2592,7 +2592,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M21" t="str">
-        <v>30000974037</v>
+        <v>30000190056</v>
       </c>
       <c r="N21" t="str">
         <v>State Bank of India</v>
@@ -2601,48 +2601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P21" t="str">
-        <v>SBIN0009742</v>
+        <v>SBIN0009111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>0300058</v>
+        <v>0300104</v>
       </c>
       <c r="B22" t="str">
-        <v>MD. IRFAN MAHTO</v>
+        <v>PRAMOD PASWAN</v>
       </c>
       <c r="C22" t="str">
-        <v>Clerk</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D22" t="str">
-        <v>03049</v>
+        <v>03077</v>
       </c>
       <c r="E22" t="str">
-        <v>High School Purnahiya</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F22" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G22" t="str">
-        <v>9003000058</v>
+        <v>9003000104</v>
       </c>
       <c r="H22" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I22" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J22" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K22" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L22" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M22" t="str">
-        <v>30000459302</v>
+        <v>30000823576</v>
       </c>
       <c r="N22" t="str">
         <v>State Bank of India</v>
@@ -2651,48 +2651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P22" t="str">
-        <v>SBIN0003351</v>
+        <v>SBIN0006055</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>0300018</v>
+        <v>0300050</v>
       </c>
       <c r="B23" t="str">
-        <v>SUNITA PANDEY</v>
+        <v>SUNIL DEVI</v>
       </c>
       <c r="C23" t="str">
-        <v>Lecturer</v>
+        <v>Accountant</v>
       </c>
       <c r="D23" t="str">
-        <v>03017</v>
+        <v>03043</v>
       </c>
       <c r="E23" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>High School Piprahi No.1</v>
       </c>
       <c r="F23" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G23" t="str">
-        <v>9003000018</v>
+        <v>9003000050</v>
       </c>
       <c r="H23" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I23" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J23" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K23" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L23" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M23" t="str">
-        <v>30000142542</v>
+        <v>30000395950</v>
       </c>
       <c r="N23" t="str">
         <v>State Bank of India</v>
@@ -2701,48 +2701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P23" t="str">
-        <v>SBIN0008245</v>
+        <v>SBIN0006799</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>0300006</v>
+        <v>0300053</v>
       </c>
       <c r="B24" t="str">
-        <v>SUNIL OJHA</v>
+        <v>RAVI PRASAD</v>
       </c>
       <c r="C24" t="str">
-        <v>Section Officer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D24" t="str">
-        <v>03006</v>
+        <v>03046</v>
       </c>
       <c r="E24" t="str">
-        <v>CDPO Office Purnahiya No.2</v>
+        <v>Panchayat Bhawan Piprahi No.3</v>
       </c>
       <c r="F24" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G24" t="str">
-        <v>9003000006</v>
+        <v>9003000053</v>
       </c>
       <c r="H24" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I24" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J24" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K24" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L24" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M24" t="str">
-        <v>30000047514</v>
+        <v>30000419707</v>
       </c>
       <c r="N24" t="str">
         <v>State Bank of India</v>
@@ -2751,39 +2751,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P24" t="str">
-        <v>SBIN0008758</v>
+        <v>SBIN0007055</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0300126</v>
+        <v>0300070</v>
       </c>
       <c r="B25" t="str">
-        <v>PANKAJ CHAUDHARY</v>
+        <v>RAMESH RAM</v>
       </c>
       <c r="C25" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D25" t="str">
-        <v>03094</v>
+        <v>03058</v>
       </c>
       <c r="E25" t="str">
-        <v>Head Post Office, Piprahi</v>
+        <v>Kanya Middle School Piprahi No.4</v>
       </c>
       <c r="F25" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G25" t="str">
-        <v>9003000126</v>
+        <v>9003000070</v>
       </c>
       <c r="H25" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I25" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J25" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K25" t="str">
         <v>0302</v>
@@ -2792,7 +2792,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M25" t="str">
-        <v>30000997794</v>
+        <v>30000554330</v>
       </c>
       <c r="N25" t="str">
         <v>State Bank of India</v>
@@ -2801,48 +2801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P25" t="str">
-        <v>SBIN0007429</v>
+        <v>SBIN0008096</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>0300101</v>
+        <v>0300035</v>
       </c>
       <c r="B26" t="str">
-        <v>MAMTA ANSARI K</v>
+        <v>MAMTA MAHTO</v>
       </c>
       <c r="C26" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D26" t="str">
-        <v>03078</v>
+        <v>03027</v>
       </c>
       <c r="E26" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F26" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G26" t="str">
-        <v>9003000101</v>
+        <v>9003000035</v>
       </c>
       <c r="H26" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I26" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J26" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K26" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L26" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M26" t="str">
-        <v>30000799819</v>
+        <v>30000277165</v>
       </c>
       <c r="N26" t="str">
         <v>State Bank of India</v>
@@ -2851,48 +2851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P26" t="str">
-        <v>SBIN0007516</v>
+        <v>SBIN0007546</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>0300039</v>
+        <v>0300027</v>
       </c>
       <c r="B27" t="str">
-        <v>PRIYANKA SAH</v>
+        <v>RINKU SINGH</v>
       </c>
       <c r="C27" t="str">
-        <v>Senior Clerk</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D27" t="str">
-        <v>03026</v>
+        <v>03025</v>
       </c>
       <c r="E27" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>High School Dumri Katsari No.4</v>
       </c>
       <c r="F27" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G27" t="str">
-        <v>9003000039</v>
+        <v>9003000027</v>
       </c>
       <c r="H27" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I27" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J27" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K27" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L27" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M27" t="str">
-        <v>30000308841</v>
+        <v>30000213813</v>
       </c>
       <c r="N27" t="str">
         <v>State Bank of India</v>
@@ -2901,33 +2901,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P27" t="str">
-        <v>SBIN0005304</v>
+        <v>SBIN0001764</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>0300022</v>
+        <v>0300093</v>
       </c>
       <c r="B28" t="str">
-        <v>DEEPAK PRASAD</v>
+        <v>ANITA SAH</v>
       </c>
       <c r="C28" t="str">
-        <v>Senior Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D28" t="str">
-        <v>03020</v>
+        <v>03074</v>
       </c>
       <c r="E28" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>RWD Sub-Division Dumri Katsari</v>
       </c>
       <c r="F28" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G28" t="str">
-        <v>9003000022</v>
+        <v>9003000093</v>
       </c>
       <c r="H28" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I28" t="str">
         <v>0304</v>
@@ -2936,13 +2936,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K28" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L28" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M28" t="str">
-        <v>30000174218</v>
+        <v>30000736467</v>
       </c>
       <c r="N28" t="str">
         <v>State Bank of India</v>
@@ -2951,48 +2951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P28" t="str">
-        <v>SBIN0002922</v>
+        <v>SBIN0006302</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>0300098</v>
+        <v>0300048</v>
       </c>
       <c r="B29" t="str">
-        <v>NASREEN ANSARI</v>
+        <v>MD. IRFAN DEVI</v>
       </c>
       <c r="C29" t="str">
-        <v>Junior Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D29" t="str">
-        <v>03077</v>
+        <v>03041</v>
       </c>
       <c r="E29" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>PHC Sheohar</v>
       </c>
       <c r="F29" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G29" t="str">
-        <v>9003000098</v>
+        <v>9003000048</v>
       </c>
       <c r="H29" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I29" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J29" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K29" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L29" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M29" t="str">
-        <v>30000776062</v>
+        <v>30000380112</v>
       </c>
       <c r="N29" t="str">
         <v>State Bank of India</v>
@@ -3001,33 +3001,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P29" t="str">
-        <v>SBIN0006166</v>
+        <v>SBIN0006186</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>0300027</v>
+        <v>0300124</v>
       </c>
       <c r="B30" t="str">
-        <v>MUKESH CHAUDHARY</v>
+        <v>ANITA RAM</v>
       </c>
       <c r="C30" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D30" t="str">
-        <v>03025</v>
+        <v>03097</v>
       </c>
       <c r="E30" t="str">
-        <v>Block Agriculture Office Dumri Katsari No.4</v>
+        <v>Central Bank of India, Purnahiya</v>
       </c>
       <c r="F30" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G30" t="str">
-        <v>9003000027</v>
+        <v>9003000124</v>
       </c>
       <c r="H30" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I30" t="str">
         <v>0304</v>
@@ -3036,13 +3036,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K30" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L30" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M30" t="str">
-        <v>30000213813</v>
+        <v>30000981956</v>
       </c>
       <c r="N30" t="str">
         <v>State Bank of India</v>
@@ -3051,33 +3051,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P30" t="str">
-        <v>SBIN0007952</v>
+        <v>SBIN0007366</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>0300096</v>
+        <v>0300029</v>
       </c>
       <c r="B31" t="str">
-        <v>PRAMOD RAI</v>
+        <v>USHA PRASAD</v>
       </c>
       <c r="C31" t="str">
-        <v>Revenue Officer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D31" t="str">
-        <v>03075</v>
+        <v>03027</v>
       </c>
       <c r="E31" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F31" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G31" t="str">
-        <v>9003000096</v>
+        <v>9003000029</v>
       </c>
       <c r="H31" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I31" t="str">
         <v>0301</v>
@@ -3092,7 +3092,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M31" t="str">
-        <v>30000760224</v>
+        <v>30000229651</v>
       </c>
       <c r="N31" t="str">
         <v>State Bank of India</v>
@@ -3101,48 +3101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P31" t="str">
-        <v>SBIN0004938</v>
+        <v>SBIN0008202</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>0300051</v>
+        <v>0300106</v>
       </c>
       <c r="B32" t="str">
-        <v>RAMESH KUMAR</v>
+        <v>NASREEN KUMAR</v>
       </c>
       <c r="C32" t="str">
-        <v>Teacher</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D32" t="str">
-        <v>03028</v>
+        <v>03083</v>
       </c>
       <c r="E32" t="str">
-        <v>PHC Purnahiya</v>
+        <v>UCO Bank, Tariyani</v>
       </c>
       <c r="F32" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G32" t="str">
-        <v>9003000051</v>
+        <v>9003000106</v>
       </c>
       <c r="H32" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I32" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J32" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K32" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L32" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M32" t="str">
-        <v>30000403869</v>
+        <v>30000839414</v>
       </c>
       <c r="N32" t="str">
         <v>State Bank of India</v>
@@ -3151,39 +3151,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P32" t="str">
-        <v>SBIN0003922</v>
+        <v>SBIN0003197</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>0300113</v>
+        <v>0300015</v>
       </c>
       <c r="B33" t="str">
-        <v>SHAILESH KHATUN</v>
+        <v>ARVIND TIWARI</v>
       </c>
       <c r="C33" t="str">
-        <v>Assistant Manager</v>
+        <v>Section Officer</v>
       </c>
       <c r="D33" t="str">
-        <v>03085</v>
+        <v>03015</v>
       </c>
       <c r="E33" t="str">
-        <v>UCO Bank, Sheohar</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="F33" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G33" t="str">
-        <v>9003000113</v>
+        <v>9003000015</v>
       </c>
       <c r="H33" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I33" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J33" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K33" t="str">
         <v>0301</v>
@@ -3192,7 +3192,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M33" t="str">
-        <v>30000894847</v>
+        <v>30000118785</v>
       </c>
       <c r="N33" t="str">
         <v>State Bank of India</v>
@@ -3201,39 +3201,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P33" t="str">
-        <v>SBIN0007492</v>
+        <v>SBIN0003975</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>0300060</v>
+        <v>0300122</v>
       </c>
       <c r="B34" t="str">
-        <v>UMESH JHA</v>
+        <v>PRIYANKA YADAV</v>
       </c>
       <c r="C34" t="str">
-        <v>Teacher</v>
+        <v>Postmaster</v>
       </c>
       <c r="D34" t="str">
-        <v>03050</v>
+        <v>03095</v>
       </c>
       <c r="E34" t="str">
-        <v>Panchayat Bhawan Piprahi</v>
+        <v>Central Bank of India, Piprahi</v>
       </c>
       <c r="F34" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G34" t="str">
-        <v>9003000060</v>
+        <v>9003000122</v>
       </c>
       <c r="H34" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I34" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J34" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K34" t="str">
         <v>0302</v>
@@ -3242,7 +3242,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M34" t="str">
-        <v>30000475140</v>
+        <v>30000966118</v>
       </c>
       <c r="N34" t="str">
         <v>State Bank of India</v>
@@ -3251,39 +3251,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P34" t="str">
-        <v>SBIN0004033</v>
+        <v>SBIN0006826</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>0300044</v>
+        <v>0300115</v>
       </c>
       <c r="B35" t="str">
-        <v>SUNITA CHAUDHARY</v>
+        <v>MANOJ RAM</v>
       </c>
       <c r="C35" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D35" t="str">
-        <v>03006</v>
+        <v>03091</v>
       </c>
       <c r="E35" t="str">
-        <v>CDPO Office Purnahiya No.2</v>
+        <v>LIC Branch Office, Purnahiya</v>
       </c>
       <c r="F35" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G35" t="str">
-        <v>9003000044</v>
+        <v>9003000115</v>
       </c>
       <c r="H35" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I35" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J35" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K35" t="str">
         <v>0303</v>
@@ -3292,7 +3292,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M35" t="str">
-        <v>30000348436</v>
+        <v>30000910685</v>
       </c>
       <c r="N35" t="str">
         <v>State Bank of India</v>
@@ -3301,48 +3301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P35" t="str">
-        <v>SBIN0007514</v>
+        <v>SBIN0009617</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>0300025</v>
+        <v>0300108</v>
       </c>
       <c r="B36" t="str">
-        <v>MAHESH SINHA</v>
+        <v>DEEPAK VERMA</v>
       </c>
       <c r="C36" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Postmaster</v>
       </c>
       <c r="D36" t="str">
-        <v>03023</v>
+        <v>03085</v>
       </c>
       <c r="E36" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>BSNL Exchange, Purnahiya</v>
       </c>
       <c r="F36" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G36" t="str">
-        <v>9003000025</v>
+        <v>9003000108</v>
       </c>
       <c r="H36" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I36" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J36" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K36" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L36" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M36" t="str">
-        <v>30000197975</v>
+        <v>30000855252</v>
       </c>
       <c r="N36" t="str">
         <v>State Bank of India</v>
@@ -3351,48 +3351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P36" t="str">
-        <v>SBIN0002599</v>
+        <v>SBIN0002418</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>0300102</v>
+        <v>0300056</v>
       </c>
       <c r="B37" t="str">
-        <v>ABDUL KALAM MISHRA</v>
+        <v>RAMESH PANDEY</v>
       </c>
       <c r="C37" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D37" t="str">
-        <v>03079</v>
+        <v>03049</v>
       </c>
       <c r="E37" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F37" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G37" t="str">
-        <v>9003000102</v>
+        <v>9003000056</v>
       </c>
       <c r="H37" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I37" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J37" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K37" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L37" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M37" t="str">
-        <v>30000807738</v>
+        <v>30000443464</v>
       </c>
       <c r="N37" t="str">
         <v>State Bank of India</v>
@@ -3401,48 +3401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P37" t="str">
-        <v>SBIN0001820</v>
+        <v>SBIN0006959</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>0300055</v>
+        <v>0300099</v>
       </c>
       <c r="B38" t="str">
-        <v>MUKESH CHAUDHARY A</v>
+        <v>ANIL GUPTA</v>
       </c>
       <c r="C38" t="str">
-        <v>Accountant</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D38" t="str">
-        <v>03046</v>
+        <v>03072</v>
       </c>
       <c r="E38" t="str">
-        <v>CDPO Office Tariyani No.2</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F38" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G38" t="str">
-        <v>9003000055</v>
+        <v>9003000099</v>
       </c>
       <c r="H38" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I38" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K38" t="str">
         <v>0303</v>
       </c>
-      <c r="J38" t="str">
+      <c r="L38" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="K38" t="str">
-        <v>0305</v>
-      </c>
-      <c r="L38" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="M38" t="str">
-        <v>30000435545</v>
+        <v>30000783981</v>
       </c>
       <c r="N38" t="str">
         <v>State Bank of India</v>
@@ -3451,48 +3451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P38" t="str">
-        <v>SBIN0007561</v>
+        <v>SBIN0004895</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>0300097</v>
+        <v>0300121</v>
       </c>
       <c r="B39" t="str">
-        <v>USHA SINHA</v>
+        <v>MAHESH KHATUN</v>
       </c>
       <c r="C39" t="str">
-        <v>Assistant Engineer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D39" t="str">
-        <v>03076</v>
+        <v>03089</v>
       </c>
       <c r="E39" t="str">
-        <v>RWD Sub-Division Sheohar</v>
+        <v>LIC Branch Office, Tariyani</v>
       </c>
       <c r="F39" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G39" t="str">
-        <v>9003000097</v>
+        <v>9003000121</v>
       </c>
       <c r="H39" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I39" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J39" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K39" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L39" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M39" t="str">
-        <v>30000768143</v>
+        <v>30000958199</v>
       </c>
       <c r="N39" t="str">
         <v>State Bank of India</v>
@@ -3501,48 +3501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P39" t="str">
-        <v>SBIN0002048</v>
+        <v>SBIN0005548</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>0300034</v>
+        <v>0300111</v>
       </c>
       <c r="B40" t="str">
-        <v>PANKAJ SAH</v>
+        <v>DEEPAK KHATUN</v>
       </c>
       <c r="C40" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D40" t="str">
-        <v>03029</v>
+        <v>03088</v>
       </c>
       <c r="E40" t="str">
-        <v>Middle School Dumri Katsari No.3</v>
+        <v>UCO Bank, Sheohar</v>
       </c>
       <c r="F40" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G40" t="str">
-        <v>9003000034</v>
+        <v>9003000111</v>
       </c>
       <c r="H40" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I40" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J40" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K40" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L40" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M40" t="str">
-        <v>30000269246</v>
+        <v>30000879009</v>
       </c>
       <c r="N40" t="str">
         <v>State Bank of India</v>
@@ -3551,39 +3551,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P40" t="str">
-        <v>SBIN0008050</v>
+        <v>SBIN0008626</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>0300013</v>
+        <v>0300114</v>
       </c>
       <c r="B41" t="str">
-        <v>SANTOSH RAM</v>
+        <v>ABDUL KALAM KHATUN</v>
       </c>
       <c r="C41" t="str">
-        <v>Assistant Engineer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D41" t="str">
-        <v>03013</v>
+        <v>03090</v>
       </c>
       <c r="E41" t="str">
-        <v>Kanya Middle School Purnahiya No.2</v>
+        <v>State Bank of India, Purnahiya</v>
       </c>
       <c r="F41" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G41" t="str">
-        <v>9003000013</v>
+        <v>9003000114</v>
       </c>
       <c r="H41" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I41" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J41" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K41" t="str">
         <v>0303</v>
@@ -3592,7 +3592,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M41" t="str">
-        <v>30000102947</v>
+        <v>30000902766</v>
       </c>
       <c r="N41" t="str">
         <v>State Bank of India</v>
@@ -3601,33 +3601,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P41" t="str">
-        <v>SBIN0003097</v>
+        <v>SBIN0003588</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>0300019</v>
+        <v>0300072</v>
       </c>
       <c r="B42" t="str">
-        <v>MD. IRFAN JHA</v>
+        <v>SANTOSH RAI</v>
       </c>
       <c r="C42" t="str">
-        <v>Lecturer</v>
+        <v>Clerk</v>
       </c>
       <c r="D42" t="str">
-        <v>03018</v>
+        <v>03053</v>
       </c>
       <c r="E42" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>Panchayat Bhawan Dumri Katsari No.4</v>
       </c>
       <c r="F42" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G42" t="str">
-        <v>9003000019</v>
+        <v>9003000072</v>
       </c>
       <c r="H42" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I42" t="str">
         <v>0304</v>
@@ -3636,13 +3636,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K42" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L42" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M42" t="str">
-        <v>30000150461</v>
+        <v>30000570168</v>
       </c>
       <c r="N42" t="str">
         <v>State Bank of India</v>
@@ -3651,39 +3651,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P42" t="str">
-        <v>SBIN0001780</v>
+        <v>SBIN0001520</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>0300086</v>
+        <v>0300020</v>
       </c>
       <c r="B43" t="str">
-        <v>SAVITA VERMA</v>
+        <v>ANITA PRASAD</v>
       </c>
       <c r="C43" t="str">
-        <v>Assistant Engineer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D43" t="str">
-        <v>03069</v>
+        <v>03019</v>
       </c>
       <c r="E43" t="str">
-        <v>Circle Office Sheohar</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F43" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G43" t="str">
-        <v>9003000086</v>
+        <v>9003000020</v>
       </c>
       <c r="H43" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I43" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J43" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K43" t="str">
         <v>0301</v>
@@ -3692,7 +3692,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M43" t="str">
-        <v>30000681034</v>
+        <v>30000158380</v>
       </c>
       <c r="N43" t="str">
         <v>State Bank of India</v>
@@ -3701,39 +3701,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P43" t="str">
-        <v>SBIN0007321</v>
+        <v>SBIN0006494</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>0300029</v>
+        <v>0300019</v>
       </c>
       <c r="B44" t="str">
-        <v>SANTOSH THAKUR</v>
+        <v>ANIL VERMA</v>
       </c>
       <c r="C44" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Section Officer</v>
       </c>
       <c r="D44" t="str">
-        <v>03026</v>
+        <v>03019</v>
       </c>
       <c r="E44" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F44" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G44" t="str">
-        <v>9003000029</v>
+        <v>9003000019</v>
       </c>
       <c r="H44" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I44" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J44" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K44" t="str">
         <v>0301</v>
@@ -3742,7 +3742,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M44" t="str">
-        <v>30000229651</v>
+        <v>30000150461</v>
       </c>
       <c r="N44" t="str">
         <v>State Bank of India</v>
@@ -3751,39 +3751,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P44" t="str">
-        <v>SBIN0009857</v>
+        <v>SBIN0008162</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>0300085</v>
+        <v>0300083</v>
       </c>
       <c r="B45" t="str">
-        <v>POONAM YADAV</v>
+        <v>MAHESH PANDEY</v>
       </c>
       <c r="C45" t="str">
-        <v>Junior Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D45" t="str">
-        <v>03002</v>
+        <v>03068</v>
       </c>
       <c r="E45" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>Block Education Office Purnahiya No.4</v>
       </c>
       <c r="F45" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G45" t="str">
-        <v>9003000085</v>
+        <v>9003000083</v>
       </c>
       <c r="H45" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I45" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J45" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K45" t="str">
         <v>0303</v>
@@ -3792,7 +3792,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M45" t="str">
-        <v>30000673115</v>
+        <v>30000657277</v>
       </c>
       <c r="N45" t="str">
         <v>State Bank of India</v>
@@ -3801,48 +3801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P45" t="str">
-        <v>SBIN0006697</v>
+        <v>SBIN0001295</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>0300056</v>
+        <v>0300011</v>
       </c>
       <c r="B46" t="str">
-        <v>ANIL PANDEY</v>
+        <v>MD. SHAHID SINHA</v>
       </c>
       <c r="C46" t="str">
-        <v>Teacher</v>
+        <v>Section Officer</v>
       </c>
       <c r="D46" t="str">
-        <v>03047</v>
+        <v>03011</v>
       </c>
       <c r="E46" t="str">
-        <v>Block Education Office Piprahi No.2</v>
+        <v>Project Girls High School Sheohar No.2</v>
       </c>
       <c r="F46" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G46" t="str">
-        <v>9003000056</v>
+        <v>9003000011</v>
       </c>
       <c r="H46" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I46" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J46" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K46" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L46" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M46" t="str">
-        <v>30000443464</v>
+        <v>30000087109</v>
       </c>
       <c r="N46" t="str">
         <v>State Bank of India</v>
@@ -3851,48 +3851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P46" t="str">
-        <v>SBIN0008327</v>
+        <v>SBIN0006751</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0300016</v>
+        <v>0300051</v>
       </c>
       <c r="B47" t="str">
-        <v>PANKAJ ALAM</v>
+        <v>PRAMOD THAKUR</v>
       </c>
       <c r="C47" t="str">
-        <v>Assistant Engineer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D47" t="str">
-        <v>03015</v>
+        <v>03044</v>
       </c>
       <c r="E47" t="str">
-        <v>Block Education Office Sheohar No.2</v>
+        <v>Middle School Purnahiya No.1</v>
       </c>
       <c r="F47" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G47" t="str">
-        <v>9003000016</v>
+        <v>9003000051</v>
       </c>
       <c r="H47" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I47" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J47" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K47" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L47" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M47" t="str">
-        <v>30000126704</v>
+        <v>30000403869</v>
       </c>
       <c r="N47" t="str">
         <v>State Bank of India</v>
@@ -3901,33 +3901,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P47" t="str">
-        <v>SBIN0006809</v>
+        <v>SBIN0003499</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0300064</v>
+        <v>0300109</v>
       </c>
       <c r="B48" t="str">
-        <v>RAJESH ANSARI</v>
+        <v>PANKAJ TIWARI</v>
       </c>
       <c r="C48" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D48" t="str">
-        <v>03018</v>
+        <v>03086</v>
       </c>
       <c r="E48" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>Bank of India, Sheohar</v>
       </c>
       <c r="F48" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G48" t="str">
-        <v>9003000064</v>
+        <v>9003000109</v>
       </c>
       <c r="H48" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I48" t="str">
         <v>0302</v>
@@ -3942,7 +3942,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M48" t="str">
-        <v>30000506816</v>
+        <v>30000863171</v>
       </c>
       <c r="N48" t="str">
         <v>State Bank of India</v>
@@ -3951,48 +3951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P48" t="str">
-        <v>SBIN0008786</v>
+        <v>SBIN0006944</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0300024</v>
+        <v>0300068</v>
       </c>
       <c r="B49" t="str">
-        <v>MUKESH ALAM</v>
+        <v>SAVITA MAHTO</v>
       </c>
       <c r="C49" t="str">
-        <v>Head Clerk</v>
+        <v>Clerk</v>
       </c>
       <c r="D49" t="str">
-        <v>03022</v>
+        <v>03009</v>
       </c>
       <c r="E49" t="str">
-        <v>Kanya Middle School Dumri Katsari No.1</v>
+        <v>PHED Division Sheohar</v>
       </c>
       <c r="F49" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G49" t="str">
-        <v>9003000024</v>
+        <v>9003000068</v>
       </c>
       <c r="H49" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I49" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J49" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K49" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L49" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M49" t="str">
-        <v>30000190056</v>
+        <v>30000538492</v>
       </c>
       <c r="N49" t="str">
         <v>State Bank of India</v>
@@ -4001,48 +4001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P49" t="str">
-        <v>SBIN0004604</v>
+        <v>SBIN0005700</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0300100</v>
+        <v>0300021</v>
       </c>
       <c r="B50" t="str">
-        <v>MAMTA SHARMA</v>
+        <v>VIJAY KUMAR</v>
       </c>
       <c r="C50" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D50" t="str">
-        <v>03077</v>
+        <v>03020</v>
       </c>
       <c r="E50" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>Circle Office Sheohar No.3</v>
       </c>
       <c r="F50" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G50" t="str">
-        <v>9003000100</v>
+        <v>9003000021</v>
       </c>
       <c r="H50" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I50" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J50" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K50" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L50" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M50" t="str">
-        <v>30000791900</v>
+        <v>30000166299</v>
       </c>
       <c r="N50" t="str">
         <v>State Bank of India</v>
@@ -4051,48 +4051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P50" t="str">
-        <v>SBIN0002508</v>
+        <v>SBIN0007266</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>0300099</v>
+        <v>0300092</v>
       </c>
       <c r="B51" t="str">
-        <v>PRIYANKA DEVI</v>
+        <v>MD. IRFAN ANSARI</v>
       </c>
       <c r="C51" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D51" t="str">
-        <v>03072</v>
+        <v>03073</v>
       </c>
       <c r="E51" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>Minor Irrigation Office Dumri Katsari</v>
       </c>
       <c r="F51" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G51" t="str">
-        <v>9003000099</v>
+        <v>9003000092</v>
       </c>
       <c r="H51" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I51" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J51" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K51" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L51" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M51" t="str">
-        <v>30000783981</v>
+        <v>30000728548</v>
       </c>
       <c r="N51" t="str">
         <v>State Bank of India</v>
@@ -4101,39 +4101,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P51" t="str">
-        <v>SBIN0005594</v>
+        <v>SBIN0004203</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>0300104</v>
+        <v>0300031</v>
       </c>
       <c r="B52" t="str">
-        <v>PRAMOD JHA</v>
+        <v>RAKESH PASWAN</v>
       </c>
       <c r="C52" t="str">
-        <v>Revenue Officer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D52" t="str">
-        <v>03075</v>
+        <v>03027</v>
       </c>
       <c r="E52" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F52" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G52" t="str">
-        <v>9003000104</v>
+        <v>9003000031</v>
       </c>
       <c r="H52" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I52" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J52" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K52" t="str">
         <v>0301</v>
@@ -4142,7 +4142,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M52" t="str">
-        <v>30000823576</v>
+        <v>30000245489</v>
       </c>
       <c r="N52" t="str">
         <v>State Bank of India</v>
@@ -4151,48 +4151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P52" t="str">
-        <v>SBIN0002061</v>
+        <v>SBIN0004511</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>0300026</v>
+        <v>0300066</v>
       </c>
       <c r="B53" t="str">
-        <v>AJAY SHARMA</v>
+        <v>SHAILESH RAI J</v>
       </c>
       <c r="C53" t="str">
-        <v>Head Clerk</v>
+        <v>Clerk</v>
       </c>
       <c r="D53" t="str">
-        <v>03024</v>
+        <v>03055</v>
       </c>
       <c r="E53" t="str">
-        <v>Primary School Dumri Katsari No.4</v>
+        <v>CDPO Office Piprahi</v>
       </c>
       <c r="F53" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G53" t="str">
-        <v>9003000026</v>
+        <v>9003000066</v>
       </c>
       <c r="H53" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I53" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J53" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K53" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L53" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M53" t="str">
-        <v>30000205894</v>
+        <v>30000522654</v>
       </c>
       <c r="N53" t="str">
         <v>State Bank of India</v>
@@ -4201,33 +4201,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P53" t="str">
-        <v>SBIN0007326</v>
+        <v>SBIN0009025</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>0300014</v>
+        <v>0300042</v>
       </c>
       <c r="B54" t="str">
-        <v>USHA DEVI</v>
+        <v>ABDUL KALAM YADAV</v>
       </c>
       <c r="C54" t="str">
-        <v>Headmaster</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D54" t="str">
-        <v>03014</v>
+        <v>03037</v>
       </c>
       <c r="E54" t="str">
-        <v>PHC Purnahiya No.1</v>
+        <v>Primary School Piprahi No.2</v>
       </c>
       <c r="F54" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G54" t="str">
-        <v>9003000014</v>
+        <v>9003000042</v>
       </c>
       <c r="H54" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I54" t="str">
         <v>0303</v>
@@ -4236,13 +4236,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K54" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L54" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M54" t="str">
-        <v>30000110866</v>
+        <v>30000332598</v>
       </c>
       <c r="N54" t="str">
         <v>State Bank of India</v>
@@ -4251,39 +4251,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P54" t="str">
-        <v>SBIN0006920</v>
+        <v>SBIN0001297</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>0300032</v>
+        <v>0300097</v>
       </c>
       <c r="B55" t="str">
-        <v>DINESH MISHRA</v>
+        <v>ANIL SINGH C</v>
       </c>
       <c r="C55" t="str">
-        <v>Senior Clerk</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D55" t="str">
-        <v>03028</v>
+        <v>03078</v>
       </c>
       <c r="E55" t="str">
-        <v>PHC Purnahiya</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F55" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G55" t="str">
-        <v>9003000032</v>
+        <v>9003000097</v>
       </c>
       <c r="H55" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I55" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J55" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K55" t="str">
         <v>0303</v>
@@ -4292,7 +4292,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M55" t="str">
-        <v>30000253408</v>
+        <v>30000768143</v>
       </c>
       <c r="N55" t="str">
         <v>State Bank of India</v>
@@ -4301,48 +4301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P55" t="str">
-        <v>SBIN0008758</v>
+        <v>SBIN0001056</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>0300010</v>
+        <v>0300063</v>
       </c>
       <c r="B56" t="str">
-        <v>NITISH SAH</v>
+        <v>UMESH OJHA</v>
       </c>
       <c r="C56" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D56" t="str">
-        <v>03010</v>
+        <v>03027</v>
       </c>
       <c r="E56" t="str">
-        <v>Kanya Middle School Dumri Katsari No.2</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F56" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G56" t="str">
-        <v>9003000010</v>
+        <v>9003000063</v>
       </c>
       <c r="H56" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I56" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J56" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K56" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L56" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M56" t="str">
-        <v>30000079190</v>
+        <v>30000498897</v>
       </c>
       <c r="N56" t="str">
         <v>State Bank of India</v>
@@ -4351,48 +4351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P56" t="str">
-        <v>SBIN0004846</v>
+        <v>SBIN0006132</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>0300083</v>
+        <v>0300055</v>
       </c>
       <c r="B57" t="str">
-        <v>RINKU MAHTO</v>
+        <v>ABDUL KALAM RAI V</v>
       </c>
       <c r="C57" t="str">
-        <v>Data Entry Operator</v>
+        <v>Teacher</v>
       </c>
       <c r="D57" t="str">
-        <v>03066</v>
+        <v>03048</v>
       </c>
       <c r="E57" t="str">
-        <v>Middle School Tariyani No.4</v>
+        <v>High School Sheohar No.1</v>
       </c>
       <c r="F57" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G57" t="str">
-        <v>9003000083</v>
+        <v>9003000055</v>
       </c>
       <c r="H57" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I57" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J57" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K57" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L57" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M57" t="str">
-        <v>30000657277</v>
+        <v>30000435545</v>
       </c>
       <c r="N57" t="str">
         <v>State Bank of India</v>
@@ -4401,39 +4401,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P57" t="str">
-        <v>SBIN0007720</v>
+        <v>SBIN0009410</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>0300046</v>
+        <v>0300039</v>
       </c>
       <c r="B58" t="str">
-        <v>NIRMALA OJHA</v>
+        <v>SUNIL JHA T</v>
       </c>
       <c r="C58" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D58" t="str">
-        <v>03038</v>
+        <v>03035</v>
       </c>
       <c r="E58" t="str">
-        <v>High School Dumri Katsari No.1</v>
+        <v>Panchayat Bhawan Dumri Katsari No.2</v>
       </c>
       <c r="F58" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G58" t="str">
-        <v>9003000046</v>
+        <v>9003000039</v>
       </c>
       <c r="H58" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I58" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J58" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K58" t="str">
         <v>0304</v>
@@ -4442,7 +4442,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M58" t="str">
-        <v>30000364274</v>
+        <v>30000308841</v>
       </c>
       <c r="N58" t="str">
         <v>State Bank of India</v>
@@ -4451,33 +4451,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P58" t="str">
-        <v>SBIN0003116</v>
+        <v>SBIN0007041</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>0300121</v>
+        <v>0300018</v>
       </c>
       <c r="B59" t="str">
-        <v>RAVI MAHTO</v>
+        <v>PRIYANKA TIWARI</v>
       </c>
       <c r="C59" t="str">
-        <v>Administrative Officer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D59" t="str">
-        <v>03080</v>
+        <v>03018</v>
       </c>
       <c r="E59" t="str">
-        <v>LIC Branch Office, Piprahi</v>
+        <v>CDPO Office Dumri Katsari No.4</v>
       </c>
       <c r="F59" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G59" t="str">
-        <v>9003000121</v>
+        <v>9003000018</v>
       </c>
       <c r="H59" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I59" t="str">
         <v>0304</v>
@@ -4486,13 +4486,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K59" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L59" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M59" t="str">
-        <v>30000958199</v>
+        <v>30000142542</v>
       </c>
       <c r="N59" t="str">
         <v>State Bank of India</v>
@@ -4501,39 +4501,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P59" t="str">
-        <v>SBIN0004265</v>
+        <v>SBIN0006103</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>0300073</v>
+        <v>0300071</v>
       </c>
       <c r="B60" t="str">
-        <v>SURESH OJHA</v>
+        <v>NIRMALA SHARMA</v>
       </c>
       <c r="C60" t="str">
-        <v>Data Entry Operator</v>
+        <v>Clerk</v>
       </c>
       <c r="D60" t="str">
-        <v>03060</v>
+        <v>03059</v>
       </c>
       <c r="E60" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Project Girls High School Purnahiya No.2</v>
       </c>
       <c r="F60" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G60" t="str">
-        <v>9003000073</v>
+        <v>9003000071</v>
       </c>
       <c r="H60" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I60" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J60" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K60" t="str">
         <v>0303</v>
@@ -4542,7 +4542,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M60" t="str">
-        <v>30000578087</v>
+        <v>30000562249</v>
       </c>
       <c r="N60" t="str">
         <v>State Bank of India</v>
@@ -4551,48 +4551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P60" t="str">
-        <v>SBIN0005422</v>
+        <v>SBIN0004237</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>0300091</v>
+        <v>0300088</v>
       </c>
       <c r="B61" t="str">
-        <v>SANTOSH YADAV</v>
+        <v>FARHAT ANSARI</v>
       </c>
       <c r="C61" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D61" t="str">
-        <v>03072</v>
+        <v>03070</v>
       </c>
       <c r="E61" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>RWD Sub-Division Tariyani</v>
       </c>
       <c r="F61" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G61" t="str">
-        <v>9003000091</v>
+        <v>9003000088</v>
       </c>
       <c r="H61" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I61" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J61" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K61" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L61" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M61" t="str">
-        <v>30000720629</v>
+        <v>30000696872</v>
       </c>
       <c r="N61" t="str">
         <v>State Bank of India</v>
@@ -4601,48 +4601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P61" t="str">
-        <v>SBIN0001238</v>
+        <v>SBIN0009209</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>0300015</v>
+        <v>0300116</v>
       </c>
       <c r="B62" t="str">
-        <v>DINESH TIWARI</v>
+        <v>MUKESH KUMAR</v>
       </c>
       <c r="C62" t="str">
-        <v>Section Officer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D62" t="str">
-        <v>03010</v>
+        <v>03092</v>
       </c>
       <c r="E62" t="str">
-        <v>Kanya Middle School Dumri Katsari No.2</v>
+        <v>State Bank of India, Sheohar</v>
       </c>
       <c r="F62" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G62" t="str">
-        <v>9003000015</v>
+        <v>9003000116</v>
       </c>
       <c r="H62" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I62" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J62" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K62" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L62" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M62" t="str">
-        <v>30000118785</v>
+        <v>30000918604</v>
       </c>
       <c r="N62" t="str">
         <v>State Bank of India</v>
@@ -4651,48 +4651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P62" t="str">
-        <v>SBIN0005574</v>
+        <v>SBIN0004804</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>0300042</v>
+        <v>0300058</v>
       </c>
       <c r="B63" t="str">
-        <v>ANIL PRASAD</v>
+        <v>SUNITA SHARMA</v>
       </c>
       <c r="C63" t="str">
-        <v>Senior Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D63" t="str">
-        <v>03035</v>
+        <v>03038</v>
       </c>
       <c r="E63" t="str">
-        <v>Block Agriculture Office Dumri Katsari No.2</v>
+        <v>High School Sheohar</v>
       </c>
       <c r="F63" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G63" t="str">
-        <v>9003000042</v>
+        <v>9003000058</v>
       </c>
       <c r="H63" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I63" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J63" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K63" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L63" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M63" t="str">
-        <v>30000332598</v>
+        <v>30000459302</v>
       </c>
       <c r="N63" t="str">
         <v>State Bank of India</v>
@@ -4701,39 +4701,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P63" t="str">
-        <v>SBIN0003110</v>
+        <v>SBIN0003831</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>0300017</v>
+        <v>0300065</v>
       </c>
       <c r="B64" t="str">
-        <v>AMIT CHAUDHARY</v>
+        <v>SURESH PANDEY</v>
       </c>
       <c r="C64" t="str">
-        <v>Section Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D64" t="str">
-        <v>03016</v>
+        <v>03051</v>
       </c>
       <c r="E64" t="str">
-        <v>Kanya Middle School Sheohar</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F64" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G64" t="str">
-        <v>9003000017</v>
+        <v>9003000065</v>
       </c>
       <c r="H64" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I64" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J64" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K64" t="str">
         <v>0301</v>
@@ -4742,7 +4742,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M64" t="str">
-        <v>30000134623</v>
+        <v>30000514735</v>
       </c>
       <c r="N64" t="str">
         <v>State Bank of India</v>
@@ -4751,39 +4751,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P64" t="str">
-        <v>SBIN0001199</v>
+        <v>SBIN0005959</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>0300004</v>
+        <v>0300052</v>
       </c>
       <c r="B65" t="str">
-        <v>NEHA SINHA</v>
+        <v>RANJIT ALAM</v>
       </c>
       <c r="C65" t="str">
-        <v>Section Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D65" t="str">
-        <v>03004</v>
+        <v>03045</v>
       </c>
       <c r="E65" t="str">
-        <v>High School Sheohar</v>
+        <v>CDPO Office Sheohar No.1</v>
       </c>
       <c r="F65" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G65" t="str">
-        <v>9003000004</v>
+        <v>9003000052</v>
       </c>
       <c r="H65" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I65" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J65" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K65" t="str">
         <v>0301</v>
@@ -4792,7 +4792,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M65" t="str">
-        <v>30000031676</v>
+        <v>30000411788</v>
       </c>
       <c r="N65" t="str">
         <v>State Bank of India</v>
@@ -4801,39 +4801,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P65" t="str">
-        <v>SBIN0002061</v>
+        <v>SBIN0004095</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>0300045</v>
+        <v>0300096</v>
       </c>
       <c r="B66" t="str">
-        <v>ABDUL KALAM ALAM</v>
+        <v>UMESH MISHRA</v>
       </c>
       <c r="C66" t="str">
-        <v>Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D66" t="str">
-        <v>03037</v>
+        <v>03077</v>
       </c>
       <c r="E66" t="str">
-        <v>CDPO Office Piprahi No.2</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F66" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G66" t="str">
-        <v>9003000045</v>
+        <v>9003000096</v>
       </c>
       <c r="H66" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I66" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J66" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K66" t="str">
         <v>0302</v>
@@ -4842,7 +4842,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M66" t="str">
-        <v>30000356355</v>
+        <v>30000760224</v>
       </c>
       <c r="N66" t="str">
         <v>State Bank of India</v>
@@ -4851,48 +4851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P66" t="str">
-        <v>SBIN0003621</v>
+        <v>SBIN0004158</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>0300061</v>
+        <v>0300003</v>
       </c>
       <c r="B67" t="str">
-        <v>MD. SHAHID SHARMA</v>
+        <v>NASREEN RAI</v>
       </c>
       <c r="C67" t="str">
-        <v>Accountant</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D67" t="str">
-        <v>03051</v>
+        <v>03003</v>
       </c>
       <c r="E67" t="str">
-        <v>Middle School Sheohar</v>
+        <v>Primary School Dumri Katsari No.1</v>
       </c>
       <c r="F67" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G67" t="str">
-        <v>9003000061</v>
+        <v>9003000003</v>
       </c>
       <c r="H67" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I67" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J67" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K67" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L67" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M67" t="str">
-        <v>30000483059</v>
+        <v>30000023757</v>
       </c>
       <c r="N67" t="str">
         <v>State Bank of India</v>
@@ -4901,48 +4901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P67" t="str">
-        <v>SBIN0008616</v>
+        <v>SBIN0008941</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>0300012</v>
+        <v>0300041</v>
       </c>
       <c r="B68" t="str">
-        <v>RAMESH GUPTA G</v>
+        <v>ABDUL KALAM RAI</v>
       </c>
       <c r="C68" t="str">
-        <v>Headmaster</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D68" t="str">
-        <v>03012</v>
+        <v>03005</v>
       </c>
       <c r="E68" t="str">
-        <v>Block Education Office Dumri Katsari No.1</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F68" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G68" t="str">
-        <v>9003000012</v>
+        <v>9003000041</v>
       </c>
       <c r="H68" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I68" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J68" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K68" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L68" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M68" t="str">
-        <v>30000095028</v>
+        <v>30000324679</v>
       </c>
       <c r="N68" t="str">
         <v>State Bank of India</v>
@@ -4951,48 +4951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P68" t="str">
-        <v>SBIN0008413</v>
+        <v>SBIN0009719</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>0300119</v>
+        <v>0300102</v>
       </c>
       <c r="B69" t="str">
-        <v>PRAMOD SHARMA</v>
+        <v>SAVITA PANDEY</v>
       </c>
       <c r="C69" t="str">
-        <v>Assistant Manager</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D69" t="str">
-        <v>03089</v>
+        <v>03077</v>
       </c>
       <c r="E69" t="str">
-        <v>UCO Bank, Tariyani</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F69" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G69" t="str">
-        <v>9003000119</v>
+        <v>9003000102</v>
       </c>
       <c r="H69" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I69" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J69" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K69" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L69" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M69" t="str">
-        <v>30000942361</v>
+        <v>30000807738</v>
       </c>
       <c r="N69" t="str">
         <v>State Bank of India</v>
@@ -5001,48 +5001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P69" t="str">
-        <v>SBIN0009553</v>
+        <v>SBIN0007610</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>0300072</v>
+        <v>0300103</v>
       </c>
       <c r="B70" t="str">
-        <v>AMIT THAKUR</v>
+        <v>REKHA DEVI</v>
       </c>
       <c r="C70" t="str">
-        <v>Teacher</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D70" t="str">
-        <v>03059</v>
+        <v>03082</v>
       </c>
       <c r="E70" t="str">
-        <v>PHC Tariyani No.1</v>
+        <v>RWD Sub-Division Purnahiya</v>
       </c>
       <c r="F70" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G70" t="str">
-        <v>9003000072</v>
+        <v>9003000103</v>
       </c>
       <c r="H70" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I70" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J70" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K70" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L70" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M70" t="str">
-        <v>30000570168</v>
+        <v>30000815657</v>
       </c>
       <c r="N70" t="str">
         <v>State Bank of India</v>
@@ -5051,48 +5051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P70" t="str">
-        <v>SBIN0001336</v>
+        <v>SBIN0007608</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>0300048</v>
+        <v>0300086</v>
       </c>
       <c r="B71" t="str">
-        <v>NITISH MISHRA</v>
+        <v>RANJIT PASWAN</v>
       </c>
       <c r="C71" t="str">
-        <v>Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D71" t="str">
-        <v>03040</v>
+        <v>03049</v>
       </c>
       <c r="E71" t="str">
-        <v>Project Girls High School Sheohar No.4</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F71" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G71" t="str">
-        <v>9003000048</v>
+        <v>9003000086</v>
       </c>
       <c r="H71" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I71" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="J71" t="str">
-        <v>Dumri Katsari</v>
+        <v>Others</v>
       </c>
       <c r="K71" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L71" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M71" t="str">
-        <v>30000380112</v>
+        <v>30000681034</v>
       </c>
       <c r="N71" t="str">
         <v>State Bank of India</v>
@@ -5101,48 +5101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P71" t="str">
-        <v>SBIN0008684</v>
+        <v>SBIN0006823</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>0300088</v>
+        <v>0300012</v>
       </c>
       <c r="B72" t="str">
-        <v>SURESH CHAUDHARY</v>
+        <v>SURESH RAM</v>
       </c>
       <c r="C72" t="str">
-        <v>Junior Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D72" t="str">
-        <v>03071</v>
+        <v>03012</v>
       </c>
       <c r="E72" t="str">
-        <v>RWD Division (deputed from other district)</v>
+        <v>CDPO Office Piprahi No.1</v>
       </c>
       <c r="F72" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G72" t="str">
-        <v>9003000088</v>
+        <v>9003000012</v>
       </c>
       <c r="H72" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I72" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J72" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K72" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="L72" t="str">
-        <v>Other District</v>
+        <v>Piprahi</v>
       </c>
       <c r="M72" t="str">
-        <v>30000696872</v>
+        <v>30000095028</v>
       </c>
       <c r="N72" t="str">
         <v>State Bank of India</v>
@@ -5151,48 +5151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P72" t="str">
-        <v>SBIN0004501</v>
+        <v>SBIN0003109</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>0300008</v>
+        <v>0300022</v>
       </c>
       <c r="B73" t="str">
-        <v>SURESH TIWARI</v>
+        <v>SURESH KUMAR</v>
       </c>
       <c r="C73" t="str">
-        <v>Lecturer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D73" t="str">
-        <v>03008</v>
+        <v>03006</v>
       </c>
       <c r="E73" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F73" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G73" t="str">
-        <v>9003000008</v>
+        <v>9003000022</v>
       </c>
       <c r="H73" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I73" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J73" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K73" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L73" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M73" t="str">
-        <v>30000063352</v>
+        <v>30000174218</v>
       </c>
       <c r="N73" t="str">
         <v>State Bank of India</v>
@@ -5201,48 +5201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P73" t="str">
-        <v>SBIN0005760</v>
+        <v>SBIN0006941</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>0300093</v>
+        <v>0300123</v>
       </c>
       <c r="B74" t="str">
-        <v>MAHESH SAH</v>
+        <v>ANITA YADAV</v>
       </c>
       <c r="C74" t="str">
-        <v>Junior Engineer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D74" t="str">
-        <v>03073</v>
+        <v>03096</v>
       </c>
       <c r="E74" t="str">
-        <v>RWD Sub-Division Dumri Katsari</v>
+        <v>Central Bank of India, Sheohar</v>
       </c>
       <c r="F74" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G74" t="str">
-        <v>9003000093</v>
+        <v>9003000123</v>
       </c>
       <c r="H74" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I74" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J74" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K74" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L74" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M74" t="str">
-        <v>30000736467</v>
+        <v>30000974037</v>
       </c>
       <c r="N74" t="str">
         <v>State Bank of India</v>
@@ -5251,48 +5251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P74" t="str">
-        <v>SBIN0003159</v>
+        <v>SBIN0005507</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>0300092</v>
+        <v>0300090</v>
       </c>
       <c r="B75" t="str">
-        <v>MD. IRFAN YADAV</v>
+        <v>AJAY RAM</v>
       </c>
       <c r="C75" t="str">
-        <v>Revenue Officer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D75" t="str">
-        <v>03041</v>
+        <v>03072</v>
       </c>
       <c r="E75" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F75" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G75" t="str">
-        <v>9003000092</v>
+        <v>9003000090</v>
       </c>
       <c r="H75" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I75" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J75" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K75" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L75" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M75" t="str">
-        <v>30000728548</v>
+        <v>30000712710</v>
       </c>
       <c r="N75" t="str">
         <v>State Bank of India</v>
@@ -5301,48 +5301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P75" t="str">
-        <v>SBIN0003522</v>
+        <v>SBIN0005348</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>0300076</v>
+        <v>0300033</v>
       </c>
       <c r="B76" t="str">
-        <v>MAMTA ANSARI</v>
+        <v>UMESH SHARMA</v>
       </c>
       <c r="C76" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D76" t="str">
-        <v>03062</v>
+        <v>03030</v>
       </c>
       <c r="E76" t="str">
-        <v>Middle School Sheohar No.3</v>
+        <v>Primary School Dumri Katsari</v>
       </c>
       <c r="F76" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G76" t="str">
-        <v>9003000076</v>
+        <v>9003000033</v>
       </c>
       <c r="H76" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I76" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J76" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K76" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L76" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M76" t="str">
-        <v>30000601844</v>
+        <v>30000261327</v>
       </c>
       <c r="N76" t="str">
         <v>State Bank of India</v>
@@ -5351,48 +5351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P76" t="str">
-        <v>SBIN0005596</v>
+        <v>SBIN0008849</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>0300021</v>
+        <v>0300043</v>
       </c>
       <c r="B77" t="str">
-        <v>ARVIND PRASAD</v>
+        <v>RINKU TIWARI</v>
       </c>
       <c r="C77" t="str">
-        <v>Assistant Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D77" t="str">
-        <v>03019</v>
+        <v>03038</v>
       </c>
       <c r="E77" t="str">
-        <v>Primary School Dumri Katsari</v>
+        <v>High School Sheohar</v>
       </c>
       <c r="F77" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G77" t="str">
-        <v>9003000021</v>
+        <v>9003000043</v>
       </c>
       <c r="H77" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I77" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J77" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K77" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L77" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M77" t="str">
-        <v>30000166299</v>
+        <v>30000340517</v>
       </c>
       <c r="N77" t="str">
         <v>State Bank of India</v>
@@ -5401,48 +5401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P77" t="str">
-        <v>SBIN0009427</v>
+        <v>SBIN0007367</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>0300079</v>
+        <v>0300008</v>
       </c>
       <c r="B78" t="str">
-        <v>RAJESH ANSARI K</v>
+        <v>VINOD ALAM</v>
       </c>
       <c r="C78" t="str">
-        <v>Clerk</v>
+        <v>Lecturer</v>
       </c>
       <c r="D78" t="str">
-        <v>03065</v>
+        <v>03008</v>
       </c>
       <c r="E78" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Kanya Middle School Tariyani No.1</v>
       </c>
       <c r="F78" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G78" t="str">
-        <v>9003000079</v>
+        <v>9003000008</v>
       </c>
       <c r="H78" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I78" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J78" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K78" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L78" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M78" t="str">
-        <v>30000625601</v>
+        <v>30000063352</v>
       </c>
       <c r="N78" t="str">
         <v>State Bank of India</v>
@@ -5451,48 +5451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P78" t="str">
-        <v>SBIN0007906</v>
+        <v>SBIN0003276</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0300052</v>
+        <v>0300117</v>
       </c>
       <c r="B79" t="str">
-        <v>NITISH JHA</v>
+        <v>SURESH SINHA</v>
       </c>
       <c r="C79" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Postmaster</v>
       </c>
       <c r="D79" t="str">
-        <v>03043</v>
+        <v>03088</v>
       </c>
       <c r="E79" t="str">
-        <v>CDPO Office Piprahi No.3</v>
+        <v>UCO Bank, Sheohar</v>
       </c>
       <c r="F79" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G79" t="str">
-        <v>9003000052</v>
+        <v>9003000117</v>
       </c>
       <c r="H79" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I79" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J79" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K79" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L79" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M79" t="str">
-        <v>30000411788</v>
+        <v>30000926523</v>
       </c>
       <c r="N79" t="str">
         <v>State Bank of India</v>
@@ -5501,48 +5501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P79" t="str">
-        <v>SBIN0006158</v>
+        <v>SBIN0005736</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>0300109</v>
+        <v>0300094</v>
       </c>
       <c r="B80" t="str">
-        <v>ABDUL KALAM GUPTA Z</v>
+        <v>ANIL RAI</v>
       </c>
       <c r="C80" t="str">
-        <v>Postmaster</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D80" t="str">
-        <v>03083</v>
+        <v>03075</v>
       </c>
       <c r="E80" t="str">
-        <v>BSNL Exchange, Purnahiya</v>
+        <v>Minor Irrigation Office Sheohar</v>
       </c>
       <c r="F80" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G80" t="str">
-        <v>9003000109</v>
+        <v>9003000094</v>
       </c>
       <c r="H80" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I80" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J80" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K80" t="str">
         <v>0301</v>
       </c>
-      <c r="J80" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K80" t="str">
-        <v>0303</v>
-      </c>
       <c r="L80" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M80" t="str">
-        <v>30000863171</v>
+        <v>30000744386</v>
       </c>
       <c r="N80" t="str">
         <v>State Bank of India</v>
@@ -5551,48 +5551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P80" t="str">
-        <v>SBIN0001645</v>
+        <v>SBIN0005339</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>0300059</v>
+        <v>0300016</v>
       </c>
       <c r="B81" t="str">
-        <v>VIJAY PANDEY</v>
+        <v>ANIL PANDEY</v>
       </c>
       <c r="C81" t="str">
-        <v>Accountant</v>
+        <v>Section Officer</v>
       </c>
       <c r="D81" t="str">
-        <v>03003</v>
+        <v>03016</v>
       </c>
       <c r="E81" t="str">
-        <v>Block Education Office Dumri Katsari</v>
+        <v>Block Office Purnahiya No.3</v>
       </c>
       <c r="F81" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G81" t="str">
-        <v>9003000059</v>
+        <v>9003000016</v>
       </c>
       <c r="H81" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I81" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J81" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K81" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L81" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M81" t="str">
-        <v>30000467221</v>
+        <v>30000126704</v>
       </c>
       <c r="N81" t="str">
         <v>State Bank of India</v>
@@ -5601,48 +5601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P81" t="str">
-        <v>SBIN0002077</v>
+        <v>SBIN0009715</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>0300081</v>
+        <v>0300060</v>
       </c>
       <c r="B82" t="str">
-        <v>SAVITA RAM</v>
+        <v>MAMTA CHAUDHARY</v>
       </c>
       <c r="C82" t="str">
-        <v>Data Entry Operator</v>
+        <v>Teacher</v>
       </c>
       <c r="D82" t="str">
-        <v>03067</v>
+        <v>03019</v>
       </c>
       <c r="E82" t="str">
-        <v>Block Office Piprahi No.4</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F82" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G82" t="str">
-        <v>9003000081</v>
+        <v>9003000060</v>
       </c>
       <c r="H82" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I82" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J82" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K82" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L82" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M82" t="str">
-        <v>30000641439</v>
+        <v>30000475140</v>
       </c>
       <c r="N82" t="str">
         <v>State Bank of India</v>
@@ -5651,33 +5651,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P82" t="str">
-        <v>SBIN0003067</v>
+        <v>SBIN0005919</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>0300003</v>
+        <v>0300098</v>
       </c>
       <c r="B83" t="str">
-        <v>RAMESH GUPTA</v>
+        <v>RAKESH RAM</v>
       </c>
       <c r="C83" t="str">
-        <v>Assistant Engineer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D83" t="str">
-        <v>03003</v>
+        <v>03079</v>
       </c>
       <c r="E83" t="str">
-        <v>Block Education Office Dumri Katsari</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F83" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G83" t="str">
-        <v>9003000003</v>
+        <v>9003000098</v>
       </c>
       <c r="H83" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I83" t="str">
         <v>0304</v>
@@ -5686,13 +5686,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K83" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L83" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M83" t="str">
-        <v>30000023757</v>
+        <v>30000776062</v>
       </c>
       <c r="N83" t="str">
         <v>State Bank of India</v>
@@ -5701,48 +5701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P83" t="str">
-        <v>SBIN0007073</v>
+        <v>SBIN0003941</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>0300067</v>
+        <v>0300032</v>
       </c>
       <c r="B84" t="str">
-        <v>SANTOSH SAH</v>
+        <v>RINKU SINGH B</v>
       </c>
       <c r="C84" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D84" t="str">
-        <v>03048</v>
+        <v>03029</v>
       </c>
       <c r="E84" t="str">
-        <v>Project Girls High School Sheohar</v>
+        <v>Block Office Piprahi No.4</v>
       </c>
       <c r="F84" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G84" t="str">
-        <v>9003000067</v>
+        <v>9003000032</v>
       </c>
       <c r="H84" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I84" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J84" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K84" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L84" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M84" t="str">
-        <v>30000530573</v>
+        <v>30000253408</v>
       </c>
       <c r="N84" t="str">
         <v>State Bank of India</v>
@@ -5751,48 +5751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P84" t="str">
-        <v>SBIN0007528</v>
+        <v>SBIN0006216</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>0300070</v>
+        <v>0300013</v>
       </c>
       <c r="B85" t="str">
-        <v>ABDUL KALAM THAKUR</v>
+        <v>PRAMOD VERMA</v>
       </c>
       <c r="C85" t="str">
-        <v>Data Entry Operator</v>
+        <v>Lecturer</v>
       </c>
       <c r="D85" t="str">
-        <v>03057</v>
+        <v>03013</v>
       </c>
       <c r="E85" t="str">
-        <v>Middle School Purnahiya</v>
+        <v>High School Dumri Katsari No.2</v>
       </c>
       <c r="F85" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G85" t="str">
-        <v>9003000070</v>
+        <v>9003000013</v>
       </c>
       <c r="H85" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I85" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J85" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K85" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L85" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M85" t="str">
-        <v>30000554330</v>
+        <v>30000102947</v>
       </c>
       <c r="N85" t="str">
         <v>State Bank of India</v>
@@ -5801,48 +5801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P85" t="str">
-        <v>SBIN0002281</v>
+        <v>SBIN0003055</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>0300074</v>
+        <v>0300014</v>
       </c>
       <c r="B86" t="str">
-        <v>MAHESH OJHA</v>
+        <v>ALOK YADAV</v>
       </c>
       <c r="C86" t="str">
-        <v>Office Assistant</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D86" t="str">
-        <v>03061</v>
+        <v>03014</v>
       </c>
       <c r="E86" t="str">
-        <v>High School Tariyani No.2</v>
+        <v>Block Agriculture Office Purnahiya No.3</v>
       </c>
       <c r="F86" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G86" t="str">
-        <v>9003000074</v>
+        <v>9003000014</v>
       </c>
       <c r="H86" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I86" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J86" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K86" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L86" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M86" t="str">
-        <v>30000586006</v>
+        <v>30000110866</v>
       </c>
       <c r="N86" t="str">
         <v>State Bank of India</v>
@@ -5851,48 +5851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P86" t="str">
-        <v>SBIN0003465</v>
+        <v>SBIN0001319</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>0300005</v>
+        <v>0300030</v>
       </c>
       <c r="B87" t="str">
-        <v>UMESH SINHA</v>
+        <v>SHAILESH OJHA</v>
       </c>
       <c r="C87" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D87" t="str">
-        <v>03005</v>
+        <v>03028</v>
       </c>
       <c r="E87" t="str">
-        <v>District Education Office (deputed from other district)</v>
+        <v>Middle School Sheohar</v>
       </c>
       <c r="F87" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G87" t="str">
-        <v>9003000005</v>
+        <v>9003000030</v>
       </c>
       <c r="H87" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I87" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="J87" t="str">
-        <v>Dumri Katsari</v>
+        <v>Others</v>
       </c>
       <c r="K87" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="L87" t="str">
-        <v>Other District</v>
+        <v>Sheohar</v>
       </c>
       <c r="M87" t="str">
-        <v>30000039595</v>
+        <v>30000237570</v>
       </c>
       <c r="N87" t="str">
         <v>State Bank of India</v>
@@ -5901,39 +5901,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P87" t="str">
-        <v>SBIN0003733</v>
+        <v>SBIN0005689</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>0300103</v>
+        <v>0300036</v>
       </c>
       <c r="B88" t="str">
-        <v>ABDUL KALAM GUPTA P</v>
+        <v>NEHA MAHTO</v>
       </c>
       <c r="C88" t="str">
-        <v>Revenue Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D88" t="str">
-        <v>03041</v>
+        <v>03032</v>
       </c>
       <c r="E88" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Block Education Office Piprahi No.4</v>
       </c>
       <c r="F88" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G88" t="str">
-        <v>9003000103</v>
+        <v>9003000036</v>
       </c>
       <c r="H88" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I88" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J88" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K88" t="str">
         <v>0302</v>
@@ -5942,7 +5942,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M88" t="str">
-        <v>30000815657</v>
+        <v>30000285084</v>
       </c>
       <c r="N88" t="str">
         <v>State Bank of India</v>
@@ -5951,7 +5951,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P88" t="str">
-        <v>SBIN0008334</v>
+        <v>SBIN0007040</v>
       </c>
     </row>
     <row r="89">
@@ -5959,19 +5959,19 @@
         <v>0300082</v>
       </c>
       <c r="B89" t="str">
-        <v>VIJAY SHARMA</v>
+        <v>VIJAY OJHA</v>
       </c>
       <c r="C89" t="str">
         <v>Office Assistant</v>
       </c>
       <c r="D89" t="str">
-        <v>03068</v>
+        <v>03067</v>
       </c>
       <c r="E89" t="str">
-        <v>Circle Office Dumri Katsari No.4</v>
+        <v>Middle School Piprahi No.4</v>
       </c>
       <c r="F89" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G89" t="str">
         <v>9003000082</v>
@@ -5980,16 +5980,16 @@
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I89" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J89" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K89" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L89" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M89" t="str">
         <v>30000649358</v>
@@ -6001,48 +6001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P89" t="str">
-        <v>SBIN0002839</v>
+        <v>SBIN0005974</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>0300053</v>
+        <v>0300091</v>
       </c>
       <c r="B90" t="str">
-        <v>RANJIT MAHTO</v>
+        <v>SHAILESH MISHRA P</v>
       </c>
       <c r="C90" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D90" t="str">
-        <v>03044</v>
+        <v>03049</v>
       </c>
       <c r="E90" t="str">
-        <v>Block Agriculture Office Dumri Katsari No.1</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F90" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G90" t="str">
-        <v>9003000053</v>
+        <v>9003000091</v>
       </c>
       <c r="H90" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I90" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J90" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K90" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L90" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M90" t="str">
-        <v>30000419707</v>
+        <v>30000720629</v>
       </c>
       <c r="N90" t="str">
         <v>State Bank of India</v>
@@ -6051,39 +6051,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P90" t="str">
-        <v>SBIN0007952</v>
+        <v>SBIN0007378</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>0300043</v>
+        <v>0300080</v>
       </c>
       <c r="B91" t="str">
-        <v>USHA KHATUN</v>
+        <v>VIJAY RAI</v>
       </c>
       <c r="C91" t="str">
         <v>Clerk</v>
       </c>
       <c r="D91" t="str">
-        <v>03036</v>
+        <v>03065</v>
       </c>
       <c r="E91" t="str">
-        <v>Middle School Tariyani No.3</v>
+        <v>High School Tariyani No.4</v>
       </c>
       <c r="F91" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G91" t="str">
-        <v>9003000043</v>
+        <v>9003000080</v>
       </c>
       <c r="H91" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I91" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J91" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K91" t="str">
         <v>0305</v>
@@ -6092,7 +6092,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M91" t="str">
-        <v>30000340517</v>
+        <v>30000633520</v>
       </c>
       <c r="N91" t="str">
         <v>State Bank of India</v>
@@ -6101,48 +6101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P91" t="str">
-        <v>SBIN0002886</v>
+        <v>SBIN0002487</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>0300062</v>
+        <v>0300047</v>
       </c>
       <c r="B92" t="str">
-        <v>SUNIL RAM</v>
+        <v>MANOJ MISHRA</v>
       </c>
       <c r="C92" t="str">
-        <v>Accountant</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D92" t="str">
-        <v>03052</v>
+        <v>03005</v>
       </c>
       <c r="E92" t="str">
-        <v>Block Office Purnahiya No.1</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F92" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G92" t="str">
-        <v>9003000062</v>
+        <v>9003000047</v>
       </c>
       <c r="H92" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I92" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J92" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K92" t="str">
         <v>0302</v>
       </c>
-      <c r="J92" t="str">
+      <c r="L92" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K92" t="str">
-        <v>0303</v>
-      </c>
-      <c r="L92" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="M92" t="str">
-        <v>30000490978</v>
+        <v>30000372193</v>
       </c>
       <c r="N92" t="str">
         <v>State Bank of India</v>
@@ -6151,48 +6151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P92" t="str">
-        <v>SBIN0007817</v>
+        <v>SBIN0006548</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>0300095</v>
+        <v>0300006</v>
       </c>
       <c r="B93" t="str">
-        <v>ABDUL KALAM ALAM L</v>
+        <v>REKHA OJHA</v>
       </c>
       <c r="C93" t="str">
-        <v>Junior Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D93" t="str">
-        <v>03074</v>
+        <v>03006</v>
       </c>
       <c r="E93" t="str">
-        <v>Minor Irrigation Office Dumri Katsari</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F93" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G93" t="str">
-        <v>9003000095</v>
+        <v>9003000006</v>
       </c>
       <c r="H93" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I93" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J93" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K93" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L93" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M93" t="str">
-        <v>30000752305</v>
+        <v>30000047514</v>
       </c>
       <c r="N93" t="str">
         <v>State Bank of India</v>
@@ -6201,48 +6201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P93" t="str">
-        <v>SBIN0009533</v>
+        <v>SBIN0001521</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>0300068</v>
+        <v>0300078</v>
       </c>
       <c r="B94" t="str">
-        <v>SUNITA SINGH</v>
+        <v>RANJIT JHA</v>
       </c>
       <c r="C94" t="str">
-        <v>Office Assistant</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D94" t="str">
-        <v>03055</v>
+        <v>03006</v>
       </c>
       <c r="E94" t="str">
-        <v>Middle School Purnahiya No.1</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F94" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G94" t="str">
-        <v>9003000068</v>
+        <v>9003000078</v>
       </c>
       <c r="H94" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I94" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J94" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K94" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L94" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M94" t="str">
-        <v>30000538492</v>
+        <v>30000617682</v>
       </c>
       <c r="N94" t="str">
         <v>State Bank of India</v>
@@ -6251,48 +6251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P94" t="str">
-        <v>SBIN0003394</v>
+        <v>SBIN0009926</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>0300036</v>
+        <v>0300037</v>
       </c>
       <c r="B95" t="str">
-        <v>ARVIND CHAUDHARY</v>
+        <v>USHA DEVI</v>
       </c>
       <c r="C95" t="str">
-        <v>Senior Clerk</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D95" t="str">
-        <v>03031</v>
+        <v>03033</v>
       </c>
       <c r="E95" t="str">
-        <v>Middle School Purnahiya No.3</v>
+        <v>Panchayat Bhawan Sheohar No.3</v>
       </c>
       <c r="F95" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G95" t="str">
-        <v>9003000036</v>
+        <v>9003000037</v>
       </c>
       <c r="H95" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I95" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J95" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K95" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L95" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M95" t="str">
-        <v>30000285084</v>
+        <v>30000293003</v>
       </c>
       <c r="N95" t="str">
         <v>State Bank of India</v>
@@ -6301,33 +6301,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P95" t="str">
-        <v>SBIN0009063</v>
+        <v>SBIN0006396</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>0300049</v>
+        <v>0300085</v>
       </c>
       <c r="B96" t="str">
-        <v>NEHA SINGH</v>
+        <v>MAHESH SINGH</v>
       </c>
       <c r="C96" t="str">
-        <v>Accountant</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D96" t="str">
-        <v>03041</v>
+        <v>03005</v>
       </c>
       <c r="E96" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F96" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G96" t="str">
-        <v>9003000049</v>
+        <v>9003000085</v>
       </c>
       <c r="H96" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I96" t="str">
         <v>0303</v>
@@ -6342,7 +6342,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M96" t="str">
-        <v>30000388031</v>
+        <v>30000673115</v>
       </c>
       <c r="N96" t="str">
         <v>State Bank of India</v>
@@ -6351,48 +6351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P96" t="str">
-        <v>SBIN0008748</v>
+        <v>SBIN0005101</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0300110</v>
+        <v>0300025</v>
       </c>
       <c r="B97" t="str">
-        <v>KUMARI ANJALI PRASAD</v>
+        <v>ABDUL KALAM SINGH</v>
       </c>
       <c r="C97" t="str">
-        <v>Postmaster</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D97" t="str">
-        <v>03084</v>
+        <v>03023</v>
       </c>
       <c r="E97" t="str">
-        <v>State Bank of India, Sheohar</v>
+        <v>Middle School Piprahi No.3</v>
       </c>
       <c r="F97" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G97" t="str">
-        <v>9003000110</v>
+        <v>9003000025</v>
       </c>
       <c r="H97" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I97" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J97" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K97" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L97" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M97" t="str">
-        <v>30000871090</v>
+        <v>30000197975</v>
       </c>
       <c r="N97" t="str">
         <v>State Bank of India</v>
@@ -6401,48 +6401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P97" t="str">
-        <v>SBIN0007757</v>
+        <v>SBIN0006498</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>0300035</v>
+        <v>0300107</v>
       </c>
       <c r="B98" t="str">
-        <v>AMIT SAH</v>
+        <v>DEEPAK SINGH</v>
       </c>
       <c r="C98" t="str">
-        <v>Head Clerk</v>
+        <v>Postmaster</v>
       </c>
       <c r="D98" t="str">
-        <v>03030</v>
+        <v>03084</v>
       </c>
       <c r="E98" t="str">
-        <v>Circle Office Sheohar No.2</v>
+        <v>Punjab National Bank, Tariyani</v>
       </c>
       <c r="F98" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G98" t="str">
-        <v>9003000035</v>
+        <v>9003000107</v>
       </c>
       <c r="H98" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I98" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J98" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K98" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L98" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M98" t="str">
-        <v>30000277165</v>
+        <v>30000847333</v>
       </c>
       <c r="N98" t="str">
         <v>State Bank of India</v>
@@ -6451,39 +6451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P98" t="str">
-        <v>SBIN0007616</v>
+        <v>SBIN0004325</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>0300028</v>
+        <v>0300074</v>
       </c>
       <c r="B99" t="str">
-        <v>NIRMALA PASWAN</v>
+        <v>MUKESH PANDEY</v>
       </c>
       <c r="C99" t="str">
-        <v>Senior Clerk</v>
+        <v>Clerk</v>
       </c>
       <c r="D99" t="str">
-        <v>03020</v>
+        <v>03019</v>
       </c>
       <c r="E99" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F99" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G99" t="str">
-        <v>9003000028</v>
+        <v>9003000074</v>
       </c>
       <c r="H99" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I99" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J99" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K99" t="str">
         <v>0301</v>
@@ -6492,7 +6492,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M99" t="str">
-        <v>30000221732</v>
+        <v>30000586006</v>
       </c>
       <c r="N99" t="str">
         <v>State Bank of India</v>
@@ -6501,33 +6501,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P99" t="str">
-        <v>SBIN0006334</v>
+        <v>SBIN0004743</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>0300084</v>
+        <v>0300023</v>
       </c>
       <c r="B100" t="str">
-        <v>VINOD MAHTO</v>
+        <v>RAJESH MAHTO</v>
       </c>
       <c r="C100" t="str">
-        <v>Teacher</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D100" t="str">
-        <v>03017</v>
+        <v>03021</v>
       </c>
       <c r="E100" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>Project Girls High School Dumri Katsari</v>
       </c>
       <c r="F100" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G100" t="str">
-        <v>9003000084</v>
+        <v>9003000023</v>
       </c>
       <c r="H100" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I100" t="str">
         <v>0303</v>
@@ -6536,13 +6536,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K100" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L100" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M100" t="str">
-        <v>30000665196</v>
+        <v>30000182137</v>
       </c>
       <c r="N100" t="str">
         <v>State Bank of India</v>
@@ -6551,48 +6551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P100" t="str">
-        <v>SBIN0009854</v>
+        <v>SBIN0007425</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>0300031</v>
+        <v>0300089</v>
       </c>
       <c r="B101" t="str">
-        <v>MUKESH MISHRA</v>
+        <v>SHAILESH MISHRA</v>
       </c>
       <c r="C101" t="str">
-        <v>Assistant Teacher</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D101" t="str">
-        <v>03017</v>
+        <v>03071</v>
       </c>
       <c r="E101" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>Minor Irrigation Office Purnahiya</v>
       </c>
       <c r="F101" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G101" t="str">
-        <v>9003000031</v>
+        <v>9003000089</v>
       </c>
       <c r="H101" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I101" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J101" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K101" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L101" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M101" t="str">
-        <v>30000245489</v>
+        <v>30000704791</v>
       </c>
       <c r="N101" t="str">
         <v>State Bank of India</v>
@@ -6601,48 +6601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P101" t="str">
-        <v>SBIN0009394</v>
+        <v>SBIN0008271</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>0300080</v>
+        <v>0300101</v>
       </c>
       <c r="B102" t="str">
-        <v>SURESH PASWAN</v>
+        <v>DINESH ALAM</v>
       </c>
       <c r="C102" t="str">
-        <v>Teacher</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D102" t="str">
-        <v>03066</v>
+        <v>03081</v>
       </c>
       <c r="E102" t="str">
-        <v>Middle School Tariyani No.4</v>
+        <v>RWD Sub-Division Piprahi</v>
       </c>
       <c r="F102" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G102" t="str">
-        <v>9003000080</v>
+        <v>9003000101</v>
       </c>
       <c r="H102" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I102" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J102" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K102" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L102" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M102" t="str">
-        <v>30000633520</v>
+        <v>30000799819</v>
       </c>
       <c r="N102" t="str">
         <v>State Bank of India</v>
@@ -6651,33 +6651,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P102" t="str">
-        <v>SBIN0006021</v>
+        <v>SBIN0005381</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>0300116</v>
+        <v>0300049</v>
       </c>
       <c r="B103" t="str">
-        <v>RINKU YADAV</v>
+        <v>ANIL SINGH</v>
       </c>
       <c r="C103" t="str">
-        <v>Postmaster</v>
+        <v>Accountant</v>
       </c>
       <c r="D103" t="str">
-        <v>03087</v>
+        <v>03042</v>
       </c>
       <c r="E103" t="str">
-        <v>BSNL Exchange, Piprahi</v>
+        <v>Block Office Dumri Katsari No.1</v>
       </c>
       <c r="F103" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G103" t="str">
-        <v>9003000116</v>
+        <v>9003000049</v>
       </c>
       <c r="H103" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I103" t="str">
         <v>0302</v>
@@ -6686,13 +6686,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K103" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L103" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M103" t="str">
-        <v>30000918604</v>
+        <v>30000388031</v>
       </c>
       <c r="N103" t="str">
         <v>State Bank of India</v>
@@ -6701,48 +6701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P103" t="str">
-        <v>SBIN0003147</v>
+        <v>SBIN0007320</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>0300069</v>
+        <v>0300026</v>
       </c>
       <c r="B104" t="str">
-        <v>KIRAN ANSARI</v>
+        <v>SAVITA SINHA</v>
       </c>
       <c r="C104" t="str">
-        <v>Data Entry Operator</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D104" t="str">
-        <v>03056</v>
+        <v>03024</v>
       </c>
       <c r="E104" t="str">
-        <v>Block Agriculture Office Purnahiya No.2</v>
+        <v>Kanya Middle School Dumri Katsari No.4</v>
       </c>
       <c r="F104" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G104" t="str">
-        <v>9003000069</v>
+        <v>9003000026</v>
       </c>
       <c r="H104" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I104" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J104" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K104" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L104" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M104" t="str">
-        <v>30000546411</v>
+        <v>30000205894</v>
       </c>
       <c r="N104" t="str">
         <v>State Bank of India</v>
@@ -6751,39 +6751,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P104" t="str">
-        <v>SBIN0005046</v>
+        <v>SBIN0008622</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>0300108</v>
+        <v>0300113</v>
       </c>
       <c r="B105" t="str">
-        <v>RAJESH RAI</v>
+        <v>SUNITA PASWAN</v>
       </c>
       <c r="C105" t="str">
-        <v>Postmaster</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D105" t="str">
-        <v>03082</v>
+        <v>03089</v>
       </c>
       <c r="E105" t="str">
-        <v>Head Post Office, Tariyani</v>
+        <v>LIC Branch Office, Tariyani</v>
       </c>
       <c r="F105" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G105" t="str">
-        <v>9003000108</v>
+        <v>9003000113</v>
       </c>
       <c r="H105" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I105" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J105" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K105" t="str">
         <v>0305</v>
@@ -6792,7 +6792,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M105" t="str">
-        <v>30000855252</v>
+        <v>30000894847</v>
       </c>
       <c r="N105" t="str">
         <v>State Bank of India</v>
@@ -6801,48 +6801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P105" t="str">
-        <v>SBIN0001882</v>
+        <v>SBIN0003641</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>0300105</v>
+        <v>0300004</v>
       </c>
       <c r="B106" t="str">
-        <v>PANKAJ ALAM T</v>
+        <v>SHAILESH RAI</v>
       </c>
       <c r="C106" t="str">
-        <v>Junior Engineer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D106" t="str">
-        <v>03008</v>
+        <v>03004</v>
       </c>
       <c r="E106" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F106" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G106" t="str">
-        <v>9003000105</v>
+        <v>9003000004</v>
       </c>
       <c r="H106" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I106" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J106" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K106" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L106" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M106" t="str">
-        <v>30000831495</v>
+        <v>30000031676</v>
       </c>
       <c r="N106" t="str">
         <v>State Bank of India</v>
@@ -6851,48 +6851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P106" t="str">
-        <v>SBIN0007569</v>
+        <v>SBIN0006357</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>0300090</v>
+        <v>0300077</v>
       </c>
       <c r="B107" t="str">
-        <v>PRAMOD MAHTO</v>
+        <v>RAKESH MAHTO</v>
       </c>
       <c r="C107" t="str">
-        <v>Assistant Engineer</v>
+        <v>Teacher</v>
       </c>
       <c r="D107" t="str">
-        <v>03002</v>
+        <v>03063</v>
       </c>
       <c r="E107" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="F107" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G107" t="str">
-        <v>9003000090</v>
+        <v>9003000077</v>
       </c>
       <c r="H107" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I107" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J107" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K107" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L107" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M107" t="str">
-        <v>30000712710</v>
+        <v>30000609763</v>
       </c>
       <c r="N107" t="str">
         <v>State Bank of India</v>
@@ -6901,33 +6901,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P107" t="str">
-        <v>SBIN0008671</v>
+        <v>SBIN0006008</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>0300038</v>
+        <v>0300076</v>
       </c>
       <c r="B108" t="str">
-        <v>RAJESH KHATUN</v>
+        <v>KUMARI ANJALI OJHA</v>
       </c>
       <c r="C108" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D108" t="str">
-        <v>03033</v>
+        <v>03062</v>
       </c>
       <c r="E108" t="str">
-        <v>Kanya Middle School Piprahi No.4</v>
+        <v>Primary School Piprahi No.3</v>
       </c>
       <c r="F108" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G108" t="str">
-        <v>9003000038</v>
+        <v>9003000076</v>
       </c>
       <c r="H108" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I108" t="str">
         <v>0302</v>
@@ -6942,7 +6942,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M108" t="str">
-        <v>30000300922</v>
+        <v>30000601844</v>
       </c>
       <c r="N108" t="str">
         <v>State Bank of India</v>
@@ -6951,33 +6951,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P108" t="str">
-        <v>SBIN0003432</v>
+        <v>SBIN0006145</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>0300033</v>
+        <v>0300017</v>
       </c>
       <c r="B109" t="str">
-        <v>ASHA MISHRA</v>
+        <v>SUNIL JHA</v>
       </c>
       <c r="C109" t="str">
-        <v>Senior Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D109" t="str">
-        <v>03021</v>
+        <v>03017</v>
       </c>
       <c r="E109" t="str">
-        <v>Primary School Purnahiya</v>
+        <v>Kanya Middle School Tariyani No.2</v>
       </c>
       <c r="F109" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G109" t="str">
-        <v>9003000033</v>
+        <v>9003000017</v>
       </c>
       <c r="H109" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I109" t="str">
         <v>0303</v>
@@ -6986,13 +6986,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K109" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L109" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M109" t="str">
-        <v>30000261327</v>
+        <v>30000134623</v>
       </c>
       <c r="N109" t="str">
         <v>State Bank of India</v>
@@ -7001,48 +7001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P109" t="str">
-        <v>SBIN0004678</v>
+        <v>SBIN0008419</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>0300112</v>
+        <v>0300001</v>
       </c>
       <c r="B110" t="str">
-        <v>NITISH KHATUN</v>
+        <v>ALOK TIWARI</v>
       </c>
       <c r="C110" t="str">
-        <v>Administrative Officer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D110" t="str">
-        <v>03086</v>
+        <v>03001</v>
       </c>
       <c r="E110" t="str">
-        <v>LIC Branch Office, Purnahiya</v>
+        <v>Panchayat Bhawan Piprahi No.4</v>
       </c>
       <c r="F110" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G110" t="str">
-        <v>9003000112</v>
+        <v>9003000001</v>
       </c>
       <c r="H110" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I110" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J110" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K110" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L110" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M110" t="str">
-        <v>30000886928</v>
+        <v>30000007919</v>
       </c>
       <c r="N110" t="str">
         <v>State Bank of India</v>
@@ -7051,48 +7051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P110" t="str">
-        <v>SBIN0003921</v>
+        <v>SBIN0003170</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>0300124</v>
+        <v>0300045</v>
       </c>
       <c r="B111" t="str">
-        <v>MUKESH MAHTO</v>
+        <v>MAHESH RAM</v>
       </c>
       <c r="C111" t="str">
-        <v>Administrative Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D111" t="str">
-        <v>03092</v>
+        <v>03039</v>
       </c>
       <c r="E111" t="str">
-        <v>Head Post Office, Dumri Katsari</v>
+        <v>Block Education Office Tariyani No.4</v>
       </c>
       <c r="F111" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G111" t="str">
-        <v>9003000124</v>
+        <v>9003000045</v>
       </c>
       <c r="H111" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I111" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J111" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K111" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L111" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M111" t="str">
-        <v>30000981956</v>
+        <v>30000356355</v>
       </c>
       <c r="N111" t="str">
         <v>State Bank of India</v>
@@ -7101,48 +7101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P111" t="str">
-        <v>SBIN0005736</v>
+        <v>SBIN0003791</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>0300094</v>
+        <v>0300081</v>
       </c>
       <c r="B112" t="str">
-        <v>ARVIND SAH</v>
+        <v>FARHAT RAI</v>
       </c>
       <c r="C112" t="str">
-        <v>Assistant Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D112" t="str">
-        <v>03072</v>
+        <v>03066</v>
       </c>
       <c r="E112" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>PHC Purnahiya</v>
       </c>
       <c r="F112" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G112" t="str">
-        <v>9003000094</v>
+        <v>9003000081</v>
       </c>
       <c r="H112" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I112" t="str">
-        <v>999999</v>
+        <v>0303</v>
       </c>
       <c r="J112" t="str">
-        <v>Others</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K112" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L112" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M112" t="str">
-        <v>30000744386</v>
+        <v>30000641439</v>
       </c>
       <c r="N112" t="str">
         <v>State Bank of India</v>
@@ -7151,48 +7151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P112" t="str">
-        <v>SBIN0008841</v>
+        <v>SBIN0007534</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>0300120</v>
+        <v>0300119</v>
       </c>
       <c r="B113" t="str">
-        <v>SUNIL DEVI</v>
+        <v>ANIL RAI V</v>
       </c>
       <c r="C113" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D113" t="str">
-        <v>03090</v>
+        <v>03083</v>
       </c>
       <c r="E113" t="str">
-        <v>UCO Bank, Dumri Katsari</v>
+        <v>UCO Bank, Tariyani</v>
       </c>
       <c r="F113" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G113" t="str">
-        <v>9003000120</v>
+        <v>9003000119</v>
       </c>
       <c r="H113" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I113" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J113" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K113" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L113" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M113" t="str">
-        <v>30000950280</v>
+        <v>30000942361</v>
       </c>
       <c r="N113" t="str">
         <v>State Bank of India</v>
@@ -7201,48 +7201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P113" t="str">
-        <v>SBIN0008351</v>
+        <v>SBIN0003366</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>0300002</v>
+        <v>0300118</v>
       </c>
       <c r="B114" t="str">
-        <v>USHA THAKUR</v>
+        <v>SANTOSH SINGH</v>
       </c>
       <c r="C114" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D114" t="str">
-        <v>03002</v>
+        <v>03093</v>
       </c>
       <c r="E114" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>Bank of India, Tariyani</v>
       </c>
       <c r="F114" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G114" t="str">
-        <v>9003000002</v>
+        <v>9003000118</v>
       </c>
       <c r="H114" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I114" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J114" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K114" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L114" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M114" t="str">
-        <v>30000015838</v>
+        <v>30000934442</v>
       </c>
       <c r="N114" t="str">
         <v>State Bank of India</v>
@@ -7251,39 +7251,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P114" t="str">
-        <v>SBIN0006537</v>
+        <v>SBIN0007771</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>0300122</v>
+        <v>0300059</v>
       </c>
       <c r="B115" t="str">
-        <v>RINKU ALAM</v>
+        <v>RINKU RAM</v>
       </c>
       <c r="C115" t="str">
-        <v>Assistant Manager</v>
+        <v>Clerk</v>
       </c>
       <c r="D115" t="str">
-        <v>03085</v>
+        <v>03051</v>
       </c>
       <c r="E115" t="str">
-        <v>UCO Bank, Sheohar</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F115" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G115" t="str">
-        <v>9003000122</v>
+        <v>9003000059</v>
       </c>
       <c r="H115" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I115" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J115" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K115" t="str">
         <v>0301</v>
@@ -7292,7 +7292,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M115" t="str">
-        <v>30000966118</v>
+        <v>30000467221</v>
       </c>
       <c r="N115" t="str">
         <v>State Bank of India</v>
@@ -7301,48 +7301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P115" t="str">
-        <v>SBIN0002851</v>
+        <v>SBIN0002467</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>0300020</v>
+        <v>0300075</v>
       </c>
       <c r="B116" t="str">
-        <v>VINOD RAM</v>
+        <v>FARHAT GUPTA</v>
       </c>
       <c r="C116" t="str">
-        <v>Headmaster</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D116" t="str">
-        <v>03004</v>
+        <v>03061</v>
       </c>
       <c r="E116" t="str">
-        <v>High School Sheohar</v>
+        <v>Primary School Tariyani</v>
       </c>
       <c r="F116" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G116" t="str">
-        <v>9003000020</v>
+        <v>9003000075</v>
       </c>
       <c r="H116" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I116" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J116" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K116" t="str">
         <v>0305</v>
       </c>
-      <c r="J116" t="str">
+      <c r="L116" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="K116" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L116" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M116" t="str">
-        <v>30000158380</v>
+        <v>30000593925</v>
       </c>
       <c r="N116" t="str">
         <v>State Bank of India</v>
@@ -7351,48 +7351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P116" t="str">
-        <v>SBIN0006794</v>
+        <v>SBIN0004103</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>0300118</v>
+        <v>0300087</v>
       </c>
       <c r="B117" t="str">
-        <v>DINESH VERMA</v>
+        <v>MANOJ ANSARI</v>
       </c>
       <c r="C117" t="str">
-        <v>Branch Manager</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D117" t="str">
-        <v>03080</v>
+        <v>03060</v>
       </c>
       <c r="E117" t="str">
-        <v>LIC Branch Office, Piprahi</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="F117" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G117" t="str">
-        <v>9003000118</v>
+        <v>9003000087</v>
       </c>
       <c r="H117" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I117" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J117" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K117" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L117" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M117" t="str">
-        <v>30000934442</v>
+        <v>30000688953</v>
       </c>
       <c r="N117" t="str">
         <v>State Bank of India</v>
@@ -7401,48 +7401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P117" t="str">
-        <v>SBIN0009592</v>
+        <v>SBIN0003473</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>0300050</v>
+        <v>0300084</v>
       </c>
       <c r="B118" t="str">
-        <v>SANJAY CHAUDHARY</v>
+        <v>SANJAY KUMAR</v>
       </c>
       <c r="C118" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Clerk</v>
       </c>
       <c r="D118" t="str">
-        <v>03042</v>
+        <v>03069</v>
       </c>
       <c r="E118" t="str">
-        <v>High School Piprahi No.3</v>
+        <v>Block Agriculture Office Sheohar No.3</v>
       </c>
       <c r="F118" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G118" t="str">
-        <v>9003000050</v>
+        <v>9003000084</v>
       </c>
       <c r="H118" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I118" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J118" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K118" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L118" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M118" t="str">
-        <v>30000395950</v>
+        <v>30000665196</v>
       </c>
       <c r="N118" t="str">
         <v>State Bank of India</v>
@@ -7451,48 +7451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P118" t="str">
-        <v>SBIN0004082</v>
+        <v>SBIN0005289</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>0300087</v>
+        <v>0300038</v>
       </c>
       <c r="B119" t="str">
-        <v>SUNITA MISHRA</v>
+        <v>MANOJ SINGH</v>
       </c>
       <c r="C119" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D119" t="str">
-        <v>03070</v>
+        <v>03034</v>
       </c>
       <c r="E119" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>CDPO Office Purnahiya</v>
       </c>
       <c r="F119" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G119" t="str">
-        <v>9003000087</v>
+        <v>9003000038</v>
       </c>
       <c r="H119" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I119" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J119" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="K119" t="str">
         <v>0303</v>
       </c>
-      <c r="J119" t="str">
+      <c r="L119" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="K119" t="str">
-        <v>0302</v>
-      </c>
-      <c r="L119" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="M119" t="str">
-        <v>30000688953</v>
+        <v>30000300922</v>
       </c>
       <c r="N119" t="str">
         <v>State Bank of India</v>
@@ -7501,48 +7501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P119" t="str">
-        <v>SBIN0009870</v>
+        <v>SBIN0008550</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>0300063</v>
+        <v>0300062</v>
       </c>
       <c r="B120" t="str">
-        <v>ABDUL KALAM GUPTA</v>
+        <v>VINOD KHATUN</v>
       </c>
       <c r="C120" t="str">
-        <v>Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D120" t="str">
-        <v>03026</v>
+        <v>03053</v>
       </c>
       <c r="E120" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>Panchayat Bhawan Dumri Katsari No.4</v>
       </c>
       <c r="F120" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G120" t="str">
-        <v>9003000063</v>
+        <v>9003000062</v>
       </c>
       <c r="H120" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I120" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J120" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K120" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L120" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M120" t="str">
-        <v>30000498897</v>
+        <v>30000490978</v>
       </c>
       <c r="N120" t="str">
         <v>State Bank of India</v>
@@ -7551,48 +7551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P120" t="str">
-        <v>SBIN0006011</v>
+        <v>SBIN0005080</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>0300107</v>
+        <v>0300061</v>
       </c>
       <c r="B121" t="str">
-        <v>VIJAY PANDEY E</v>
+        <v>NITISH ANSARI</v>
       </c>
       <c r="C121" t="str">
-        <v>Postmaster</v>
+        <v>Clerk</v>
       </c>
       <c r="D121" t="str">
-        <v>03081</v>
+        <v>03052</v>
       </c>
       <c r="E121" t="str">
-        <v>LIC Branch Office, Tariyani</v>
+        <v>Circle Office Purnahiya No.4</v>
       </c>
       <c r="F121" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G121" t="str">
-        <v>9003000107</v>
+        <v>9003000061</v>
       </c>
       <c r="H121" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I121" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J121" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K121" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L121" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M121" t="str">
-        <v>30000847333</v>
+        <v>30000483059</v>
       </c>
       <c r="N121" t="str">
         <v>State Bank of India</v>
@@ -7601,48 +7601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P121" t="str">
-        <v>SBIN0001070</v>
+        <v>SBIN0001631</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>0300066</v>
+        <v>0300034</v>
       </c>
       <c r="B122" t="str">
-        <v>RANJIT TIWARI</v>
+        <v>RAJESH ALAM</v>
       </c>
       <c r="C122" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D122" t="str">
-        <v>03054</v>
+        <v>03031</v>
       </c>
       <c r="E122" t="str">
-        <v>Block Education Office Piprahi</v>
+        <v>High School Tariyani No.3</v>
       </c>
       <c r="F122" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G122" t="str">
-        <v>9003000066</v>
+        <v>9003000034</v>
       </c>
       <c r="H122" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I122" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J122" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K122" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L122" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M122" t="str">
-        <v>30000522654</v>
+        <v>30000269246</v>
       </c>
       <c r="N122" t="str">
         <v>State Bank of India</v>
@@ -7651,48 +7651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P122" t="str">
-        <v>SBIN0009437</v>
+        <v>SBIN0005322</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>0300115</v>
+        <v>0300100</v>
       </c>
       <c r="B123" t="str">
-        <v>PANKAJ SINHA</v>
+        <v>KIRAN THAKUR</v>
       </c>
       <c r="C123" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D123" t="str">
-        <v>03082</v>
+        <v>03080</v>
       </c>
       <c r="E123" t="str">
-        <v>Head Post Office, Tariyani</v>
+        <v>Block Office Sheohar</v>
       </c>
       <c r="F123" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G123" t="str">
-        <v>9003000115</v>
+        <v>9003000100</v>
       </c>
       <c r="H123" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I123" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J123" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K123" t="str">
         <v>0301</v>
       </c>
-      <c r="J123" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K123" t="str">
-        <v>0305</v>
-      </c>
       <c r="L123" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M123" t="str">
-        <v>30000910685</v>
+        <v>30000791900</v>
       </c>
       <c r="N123" t="str">
         <v>State Bank of India</v>
@@ -7701,48 +7701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P123" t="str">
-        <v>SBIN0007683</v>
+        <v>SBIN0005211</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>0300030</v>
+        <v>0300067</v>
       </c>
       <c r="B124" t="str">
-        <v>RAVI DEVI</v>
+        <v>AMIT ALAM</v>
       </c>
       <c r="C124" t="str">
-        <v>Assistant Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D124" t="str">
-        <v>03027</v>
+        <v>03056</v>
       </c>
       <c r="E124" t="str">
-        <v>Block Office Tariyani</v>
+        <v>Project Girls High School Purnahiya</v>
       </c>
       <c r="F124" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G124" t="str">
-        <v>9003000030</v>
+        <v>9003000067</v>
       </c>
       <c r="H124" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I124" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J124" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K124" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L124" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M124" t="str">
-        <v>30000237570</v>
+        <v>30000530573</v>
       </c>
       <c r="N124" t="str">
         <v>State Bank of India</v>
@@ -7751,48 +7751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P124" t="str">
-        <v>SBIN0002578</v>
+        <v>SBIN0007750</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>0300071</v>
+        <v>0300112</v>
       </c>
       <c r="B125" t="str">
-        <v>VINOD CHAUDHARY</v>
+        <v>MD. SHAHID GUPTA</v>
       </c>
       <c r="C125" t="str">
-        <v>Office Assistant</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D125" t="str">
-        <v>03058</v>
+        <v>03086</v>
       </c>
       <c r="E125" t="str">
-        <v>PHC Purnahiya No.4</v>
+        <v>Bank of India, Sheohar</v>
       </c>
       <c r="F125" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G125" t="str">
-        <v>9003000071</v>
+        <v>9003000112</v>
       </c>
       <c r="H125" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I125" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J125" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K125" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L125" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M125" t="str">
-        <v>30000562249</v>
+        <v>30000886928</v>
       </c>
       <c r="N125" t="str">
         <v>State Bank of India</v>
@@ -7801,48 +7801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P125" t="str">
-        <v>SBIN0007996</v>
+        <v>SBIN0008896</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>0300106</v>
+        <v>0300044</v>
       </c>
       <c r="B126" t="str">
-        <v>SUNIL JHA</v>
+        <v>SANJAY SINGH</v>
       </c>
       <c r="C126" t="str">
-        <v>Assistant Manager</v>
+        <v>Accountant</v>
       </c>
       <c r="D126" t="str">
-        <v>03080</v>
+        <v>03020</v>
       </c>
       <c r="E126" t="str">
-        <v>LIC Branch Office, Piprahi</v>
+        <v>Circle Office Sheohar No.3</v>
       </c>
       <c r="F126" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G126" t="str">
-        <v>9003000106</v>
+        <v>9003000044</v>
       </c>
       <c r="H126" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I126" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J126" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K126" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L126" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M126" t="str">
-        <v>30000839414</v>
+        <v>30000348436</v>
       </c>
       <c r="N126" t="str">
         <v>State Bank of India</v>
@@ -7851,48 +7851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P126" t="str">
-        <v>SBIN0004723</v>
+        <v>SBIN0004319</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>0300023</v>
+        <v>0300064</v>
       </c>
       <c r="B127" t="str">
-        <v>MAHESH MAHTO</v>
+        <v>NEHA GUPTA</v>
       </c>
       <c r="C127" t="str">
-        <v>Senior Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D127" t="str">
-        <v>03021</v>
+        <v>03054</v>
       </c>
       <c r="E127" t="str">
-        <v>Primary School Purnahiya</v>
+        <v>Block Education Office Dumri Katsari</v>
       </c>
       <c r="F127" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G127" t="str">
-        <v>9003000023</v>
+        <v>9003000064</v>
       </c>
       <c r="H127" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I127" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J127" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K127" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L127" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M127" t="str">
-        <v>30000182137</v>
+        <v>30000506816</v>
       </c>
       <c r="N127" t="str">
         <v>State Bank of India</v>
@@ -7901,7 +7901,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P127" t="str">
-        <v>SBIN0003647</v>
+        <v>SBIN0003051</v>
       </c>
     </row>
   </sheetData>
@@ -7954,7 +7954,7 @@
         <v>Main</v>
       </c>
       <c r="D2" t="str">
-        <v>Middle School Sheohar, Room 2</v>
+        <v>High School Sheohar, Room 2</v>
       </c>
       <c r="E2" t="str">
         <v>0301</v>
@@ -7974,7 +7974,7 @@
         <v>Main</v>
       </c>
       <c r="D3" t="str">
-        <v>Panchayat Bhawan Piprahi, Room 3</v>
+        <v>Kanya Middle School Piprahi, Room 3</v>
       </c>
       <c r="E3" t="str">
         <v>0302</v>
@@ -8034,7 +8034,7 @@
         <v>Main</v>
       </c>
       <c r="D6" t="str">
-        <v>High School Tariyani, Room 3</v>
+        <v>Block Office Hall Tariyani, Room 3</v>
       </c>
       <c r="E6" t="str">
         <v>0305</v>
@@ -8054,7 +8054,7 @@
         <v>Main</v>
       </c>
       <c r="D7" t="str">
-        <v>Block Office Hall Sheohar, Room 1</v>
+        <v>Kanya Middle School Sheohar, Room 1</v>
       </c>
       <c r="E7" t="str">
         <v>0301</v>
@@ -8074,7 +8074,7 @@
         <v>Main</v>
       </c>
       <c r="D8" t="str">
-        <v>Kanya Middle School Purnahiya, Room 2</v>
+        <v>Panchayat Bhawan Purnahiya, Room 2</v>
       </c>
       <c r="E8" t="str">
         <v>0303</v>
@@ -8094,7 +8094,7 @@
         <v>Main</v>
       </c>
       <c r="D9" t="str">
-        <v>Middle School Dumri Katsari, Room 3</v>
+        <v>Block Office Hall Dumri Katsari, Room 3</v>
       </c>
       <c r="E9" t="str">
         <v>0304</v>
@@ -8114,7 +8114,7 @@
         <v>Main</v>
       </c>
       <c r="D10" t="str">
-        <v>Panchayat Bhawan Tariyani, Room 1</v>
+        <v>Block Office Hall Tariyani, Room 1</v>
       </c>
       <c r="E10" t="str">
         <v>0305</v>
@@ -8134,7 +8134,7 @@
         <v>Main</v>
       </c>
       <c r="D11" t="str">
-        <v>High School Sheohar, Room 2</v>
+        <v>Kanya Middle School Sheohar, Room 2</v>
       </c>
       <c r="E11" t="str">
         <v>0301</v>
@@ -8174,7 +8174,7 @@
         <v>Main</v>
       </c>
       <c r="D13" t="str">
-        <v>Panchayat Bhawan Purnahiya, Room 1</v>
+        <v>Block Office Hall Purnahiya, Room 1</v>
       </c>
       <c r="E13" t="str">
         <v>0303</v>

--- a/test-data/TEST_Sheohar_Project.xlsx
+++ b/test-data/TEST_Sheohar_Project.xlsx
@@ -613,7 +613,7 @@
         <v>Saved at</v>
       </c>
       <c r="B4" t="str">
-        <v>13-10-2026 06:23:20</v>
+        <v>13-10-2026 09:45:51</v>
       </c>
     </row>
     <row r="5">
@@ -792,7 +792,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>13-10-2026 06:23:20</v>
+        <v>13-10-2026 09:45:51</v>
       </c>
       <c r="B2" t="str">
         <v>Test data generated (Small — Sheohar style (5 blocks, 6 TC + 6 GC booths))</v>
@@ -1606,43 +1606,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0300040</v>
+        <v>0300017</v>
       </c>
       <c r="B2" t="str">
-        <v>ALOK JHA</v>
+        <v>MAMTA CHAUDHARY</v>
       </c>
       <c r="C2" t="str">
-        <v>Senior Clerk</v>
+        <v>Section Officer</v>
       </c>
       <c r="D2" t="str">
-        <v>03036</v>
+        <v>03015</v>
       </c>
       <c r="E2" t="str">
-        <v>High School Purnahiya</v>
+        <v>Panchayat Bhawan Dumri Katsari</v>
       </c>
       <c r="F2" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G2" t="str">
-        <v>9003000040</v>
+        <v>9003000017</v>
       </c>
       <c r="H2" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I2" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J2" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K2" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L2" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M2" t="str">
-        <v>30000316760</v>
+        <v>30000134623</v>
       </c>
       <c r="N2" t="str">
         <v>State Bank of India</v>
@@ -1651,48 +1651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P2" t="str">
-        <v>SBIN0002676</v>
+        <v>SBIN0009018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0300095</v>
+        <v>0300041</v>
       </c>
       <c r="B3" t="str">
-        <v>MANOJ KUMAR</v>
+        <v>NIRMALA SHARMA</v>
       </c>
       <c r="C3" t="str">
-        <v>Assistant Engineer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D3" t="str">
-        <v>03076</v>
+        <v>03022</v>
       </c>
       <c r="E3" t="str">
-        <v>Block Office Tariyani</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F3" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G3" t="str">
-        <v>9003000095</v>
+        <v>9003000041</v>
       </c>
       <c r="H3" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I3" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J3" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K3" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L3" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M3" t="str">
-        <v>30000752305</v>
+        <v>30000324679</v>
       </c>
       <c r="N3" t="str">
         <v>State Bank of India</v>
@@ -1701,33 +1701,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P3" t="str">
-        <v>SBIN0008847</v>
+        <v>SBIN0002952</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0300009</v>
+        <v>0300085</v>
       </c>
       <c r="B4" t="str">
-        <v>VINOD JHA</v>
+        <v>SAVITA SAH</v>
       </c>
       <c r="C4" t="str">
-        <v>Lecturer</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D4" t="str">
-        <v>03009</v>
+        <v>03001</v>
       </c>
       <c r="E4" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F4" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G4" t="str">
-        <v>9003000009</v>
+        <v>9003000085</v>
       </c>
       <c r="H4" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I4" t="str">
         <v>0304</v>
@@ -1736,13 +1736,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K4" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L4" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M4" t="str">
-        <v>30000071271</v>
+        <v>30000673115</v>
       </c>
       <c r="N4" t="str">
         <v>State Bank of India</v>
@@ -1751,48 +1751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P4" t="str">
-        <v>SBIN0006341</v>
+        <v>SBIN0007364</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0300073</v>
+        <v>0300036</v>
       </c>
       <c r="B5" t="str">
-        <v>FARHAT SHARMA</v>
+        <v>MAHESH ALAM</v>
       </c>
       <c r="C5" t="str">
-        <v>Data Entry Operator</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D5" t="str">
-        <v>03060</v>
+        <v>03005</v>
       </c>
       <c r="E5" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F5" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G5" t="str">
-        <v>9003000073</v>
+        <v>9003000036</v>
       </c>
       <c r="H5" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I5" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J5" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K5" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L5" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M5" t="str">
-        <v>30000578087</v>
+        <v>30000285084</v>
       </c>
       <c r="N5" t="str">
         <v>State Bank of India</v>
@@ -1801,48 +1801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P5" t="str">
-        <v>SBIN0006835</v>
+        <v>SBIN0001900</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0300046</v>
+        <v>0300023</v>
       </c>
       <c r="B6" t="str">
-        <v>RAJESH KUMAR</v>
+        <v>RANJIT CHAUDHARY</v>
       </c>
       <c r="C6" t="str">
-        <v>Clerk</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D6" t="str">
-        <v>03040</v>
+        <v>03021</v>
       </c>
       <c r="E6" t="str">
-        <v>Block Education Office Tariyani No.3</v>
+        <v>Panchayat Bhawan Piprahi</v>
       </c>
       <c r="F6" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G6" t="str">
-        <v>9003000046</v>
+        <v>9003000023</v>
       </c>
       <c r="H6" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I6" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J6" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K6" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L6" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M6" t="str">
-        <v>30000364274</v>
+        <v>30000182137</v>
       </c>
       <c r="N6" t="str">
         <v>State Bank of India</v>
@@ -1851,48 +1851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P6" t="str">
-        <v>SBIN0001680</v>
+        <v>SBIN0009118</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>0300125</v>
+        <v>0300028</v>
       </c>
       <c r="B7" t="str">
-        <v>KIRAN SINGH</v>
+        <v>MAMTA ANSARI</v>
       </c>
       <c r="C7" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D7" t="str">
-        <v>03098</v>
+        <v>03006</v>
       </c>
       <c r="E7" t="str">
-        <v>State Bank of India, Dumri Katsari</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F7" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G7" t="str">
-        <v>9003000125</v>
+        <v>9003000028</v>
       </c>
       <c r="H7" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I7" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J7" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K7" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L7" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M7" t="str">
-        <v>30000989875</v>
+        <v>30000221732</v>
       </c>
       <c r="N7" t="str">
         <v>State Bank of India</v>
@@ -1901,48 +1901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P7" t="str">
-        <v>SBIN0006947</v>
+        <v>SBIN0005357</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0300054</v>
+        <v>0300096</v>
       </c>
       <c r="B8" t="str">
-        <v>SHAILESH MAHTO</v>
+        <v>SANJAY YADAV</v>
       </c>
       <c r="C8" t="str">
-        <v>Accountant</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D8" t="str">
-        <v>03047</v>
+        <v>03077</v>
       </c>
       <c r="E8" t="str">
-        <v>Block Office Sheohar No.2</v>
+        <v>RWD Sub-Division Piprahi</v>
       </c>
       <c r="F8" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G8" t="str">
-        <v>9003000054</v>
+        <v>9003000096</v>
       </c>
       <c r="H8" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I8" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K8" t="str">
         <v>0302</v>
       </c>
-      <c r="J8" t="str">
+      <c r="L8" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K8" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M8" t="str">
-        <v>30000427626</v>
+        <v>30000760224</v>
       </c>
       <c r="N8" t="str">
         <v>State Bank of India</v>
@@ -1951,39 +1951,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P8" t="str">
-        <v>SBIN0006264</v>
+        <v>SBIN0002123</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0300126</v>
+        <v>0300020</v>
       </c>
       <c r="B9" t="str">
-        <v>MUKESH RAM</v>
+        <v>ARVIND THAKUR</v>
       </c>
       <c r="C9" t="str">
-        <v>Assistant Manager</v>
+        <v>Section Officer</v>
       </c>
       <c r="D9" t="str">
-        <v>03085</v>
+        <v>03018</v>
       </c>
       <c r="E9" t="str">
-        <v>BSNL Exchange, Purnahiya</v>
+        <v>Middle School Purnahiya No.4</v>
       </c>
       <c r="F9" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G9" t="str">
-        <v>9003000126</v>
+        <v>9003000020</v>
       </c>
       <c r="H9" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I9" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J9" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K9" t="str">
         <v>0303</v>
@@ -1992,7 +1992,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M9" t="str">
-        <v>30000997794</v>
+        <v>30000158380</v>
       </c>
       <c r="N9" t="str">
         <v>State Bank of India</v>
@@ -2001,33 +2001,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P9" t="str">
-        <v>SBIN0001846</v>
+        <v>SBIN0008340</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0300007</v>
+        <v>0300044</v>
       </c>
       <c r="B10" t="str">
-        <v>MANOJ JHA</v>
+        <v>PRAMOD MISHRA</v>
       </c>
       <c r="C10" t="str">
-        <v>Headmaster</v>
+        <v>Clerk</v>
       </c>
       <c r="D10" t="str">
-        <v>03007</v>
+        <v>03006</v>
       </c>
       <c r="E10" t="str">
-        <v>High School Tariyani No.1</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F10" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G10" t="str">
-        <v>9003000007</v>
+        <v>9003000044</v>
       </c>
       <c r="H10" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I10" t="str">
         <v>0301</v>
@@ -2036,13 +2036,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K10" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L10" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M10" t="str">
-        <v>30000055433</v>
+        <v>30000348436</v>
       </c>
       <c r="N10" t="str">
         <v>State Bank of India</v>
@@ -2051,48 +2051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P10" t="str">
-        <v>SBIN0002582</v>
+        <v>SBIN0001875</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>0300010</v>
+        <v>0300106</v>
       </c>
       <c r="B11" t="str">
-        <v>DINESH PANDEY</v>
+        <v>USHA VERMA</v>
       </c>
       <c r="C11" t="str">
-        <v>Lecturer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D11" t="str">
-        <v>03010</v>
+        <v>03083</v>
       </c>
       <c r="E11" t="str">
-        <v>Block Agriculture Office Purnahiya No.4</v>
+        <v>Bank of India, Tariyani</v>
       </c>
       <c r="F11" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G11" t="str">
-        <v>9003000010</v>
+        <v>9003000106</v>
       </c>
       <c r="H11" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I11" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J11" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K11" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L11" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M11" t="str">
-        <v>30000079190</v>
+        <v>30000839414</v>
       </c>
       <c r="N11" t="str">
         <v>State Bank of India</v>
@@ -2101,48 +2101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P11" t="str">
-        <v>SBIN0006148</v>
+        <v>SBIN0009224</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>0300079</v>
+        <v>0300102</v>
       </c>
       <c r="B12" t="str">
-        <v>VINOD RAI</v>
+        <v>SURESH MISHRA</v>
       </c>
       <c r="C12" t="str">
-        <v>Data Entry Operator</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D12" t="str">
-        <v>03064</v>
+        <v>03081</v>
       </c>
       <c r="E12" t="str">
-        <v>Project Girls High School Piprahi No.4</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F12" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G12" t="str">
-        <v>9003000079</v>
+        <v>9003000102</v>
       </c>
       <c r="H12" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I12" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K12" t="str">
         <v>0303</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="K12" t="str">
-        <v>0302</v>
-      </c>
-      <c r="L12" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="M12" t="str">
-        <v>30000625601</v>
+        <v>30000807738</v>
       </c>
       <c r="N12" t="str">
         <v>State Bank of India</v>
@@ -2151,48 +2151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P12" t="str">
-        <v>SBIN0006217</v>
+        <v>SBIN0008448</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0300105</v>
+        <v>0300065</v>
       </c>
       <c r="B13" t="str">
-        <v>REKHA VERMA</v>
+        <v>SUNITA DEVI</v>
       </c>
       <c r="C13" t="str">
-        <v>Assistant Engineer</v>
+        <v>Teacher</v>
       </c>
       <c r="D13" t="str">
-        <v>03077</v>
+        <v>03055</v>
       </c>
       <c r="E13" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>Middle School Dumri Katsari No.2</v>
       </c>
       <c r="F13" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G13" t="str">
-        <v>9003000105</v>
+        <v>9003000065</v>
       </c>
       <c r="H13" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I13" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J13" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K13" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L13" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M13" t="str">
-        <v>30000831495</v>
+        <v>30000514735</v>
       </c>
       <c r="N13" t="str">
         <v>State Bank of India</v>
@@ -2201,33 +2201,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P13" t="str">
-        <v>SBIN0006816</v>
+        <v>SBIN0006422</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0300057</v>
+        <v>0300112</v>
       </c>
       <c r="B14" t="str">
-        <v>PRAMOD KUMAR</v>
+        <v>SHAILESH RAM</v>
       </c>
       <c r="C14" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Postmaster</v>
       </c>
       <c r="D14" t="str">
-        <v>03050</v>
+        <v>03088</v>
       </c>
       <c r="E14" t="str">
-        <v>High School Tariyani</v>
+        <v>BSNL Exchange, Sheohar</v>
       </c>
       <c r="F14" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G14" t="str">
-        <v>9003000057</v>
+        <v>9003000112</v>
       </c>
       <c r="H14" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I14" t="str">
         <v>0303</v>
@@ -2236,13 +2236,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K14" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L14" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M14" t="str">
-        <v>30000451383</v>
+        <v>30000886928</v>
       </c>
       <c r="N14" t="str">
         <v>State Bank of India</v>
@@ -2251,48 +2251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P14" t="str">
-        <v>SBIN0001242</v>
+        <v>SBIN0008892</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>0300069</v>
+        <v>0300011</v>
       </c>
       <c r="B15" t="str">
-        <v>POONAM ALAM</v>
+        <v>DINESH VERMA</v>
       </c>
       <c r="C15" t="str">
-        <v>Clerk</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D15" t="str">
-        <v>03057</v>
+        <v>03010</v>
       </c>
       <c r="E15" t="str">
-        <v>CDPO Office Dumri Katsari</v>
+        <v>Block Office Sheohar No.1</v>
       </c>
       <c r="F15" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G15" t="str">
-        <v>9003000069</v>
+        <v>9003000011</v>
       </c>
       <c r="H15" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I15" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J15" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K15" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L15" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M15" t="str">
-        <v>30000546411</v>
+        <v>30000087109</v>
       </c>
       <c r="N15" t="str">
         <v>State Bank of India</v>
@@ -2301,48 +2301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P15" t="str">
-        <v>SBIN0007965</v>
+        <v>SBIN0009857</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>0300110</v>
+        <v>0300048</v>
       </c>
       <c r="B16" t="str">
-        <v>PRIYANKA OJHA</v>
+        <v>KIRAN KUMAR</v>
       </c>
       <c r="C16" t="str">
-        <v>Assistant Manager</v>
+        <v>Accountant</v>
       </c>
       <c r="D16" t="str">
-        <v>03087</v>
+        <v>03006</v>
       </c>
       <c r="E16" t="str">
-        <v>Head Post Office, Purnahiya</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F16" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G16" t="str">
-        <v>9003000110</v>
+        <v>9003000048</v>
       </c>
       <c r="H16" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I16" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J16" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K16" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L16" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M16" t="str">
-        <v>30000871090</v>
+        <v>30000380112</v>
       </c>
       <c r="N16" t="str">
         <v>State Bank of India</v>
@@ -2351,48 +2351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P16" t="str">
-        <v>SBIN0001067</v>
+        <v>SBIN0002504</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>0300120</v>
+        <v>0300099</v>
       </c>
       <c r="B17" t="str">
-        <v>MUKESH PRASAD</v>
+        <v>SURESH RAM</v>
       </c>
       <c r="C17" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D17" t="str">
-        <v>03094</v>
+        <v>03079</v>
       </c>
       <c r="E17" t="str">
-        <v>BSNL Exchange, Sheohar</v>
+        <v>Collectorate (deputed from other district)</v>
       </c>
       <c r="F17" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G17" t="str">
-        <v>9003000120</v>
+        <v>9003000099</v>
       </c>
       <c r="H17" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I17" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J17" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K17" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="L17" t="str">
-        <v>Sheohar</v>
+        <v>Other District</v>
       </c>
       <c r="M17" t="str">
-        <v>30000950280</v>
+        <v>30000783981</v>
       </c>
       <c r="N17" t="str">
         <v>State Bank of India</v>
@@ -2401,33 +2401,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P17" t="str">
-        <v>SBIN0001348</v>
+        <v>SBIN0002337</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>0300002</v>
+        <v>0300031</v>
       </c>
       <c r="B18" t="str">
-        <v>MAHESH RAI</v>
+        <v>AMIT ALAM</v>
       </c>
       <c r="C18" t="str">
-        <v>Senior Teacher</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D18" t="str">
-        <v>03002</v>
+        <v>03028</v>
       </c>
       <c r="E18" t="str">
-        <v>Primary School Tariyani No.2</v>
+        <v>Panchayat Bhawan Tariyani</v>
       </c>
       <c r="F18" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G18" t="str">
-        <v>9003000002</v>
+        <v>9003000031</v>
       </c>
       <c r="H18" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I18" t="str">
         <v>0305</v>
@@ -2442,7 +2442,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M18" t="str">
-        <v>30000015838</v>
+        <v>30000245489</v>
       </c>
       <c r="N18" t="str">
         <v>State Bank of India</v>
@@ -2451,48 +2451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P18" t="str">
-        <v>SBIN0005230</v>
+        <v>SBIN0003021</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>0300005</v>
+        <v>0300067</v>
       </c>
       <c r="B19" t="str">
-        <v>POONAM OJHA</v>
+        <v>MANOJ YADAV P</v>
       </c>
       <c r="C19" t="str">
-        <v>Lecturer</v>
+        <v>Clerk</v>
       </c>
       <c r="D19" t="str">
-        <v>03005</v>
+        <v>03057</v>
       </c>
       <c r="E19" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>Middle School Dumri Katsari</v>
       </c>
       <c r="F19" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G19" t="str">
-        <v>9003000005</v>
+        <v>9003000067</v>
       </c>
       <c r="H19" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I19" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J19" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K19" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L19" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M19" t="str">
-        <v>30000039595</v>
+        <v>30000530573</v>
       </c>
       <c r="N19" t="str">
         <v>State Bank of India</v>
@@ -2501,48 +2501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P19" t="str">
-        <v>SBIN0004196</v>
+        <v>SBIN0003810</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>0300028</v>
+        <v>0300066</v>
       </c>
       <c r="B20" t="str">
-        <v>RAKESH CHAUDHARY</v>
+        <v>ALOK TIWARI</v>
       </c>
       <c r="C20" t="str">
-        <v>Senior Clerk</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D20" t="str">
-        <v>03026</v>
+        <v>03056</v>
       </c>
       <c r="E20" t="str">
-        <v>Project Girls High School Dumri Katsari No.1</v>
+        <v>PHC Sheohar No.4</v>
       </c>
       <c r="F20" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G20" t="str">
-        <v>9003000028</v>
+        <v>9003000066</v>
       </c>
       <c r="H20" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I20" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="K20" t="str">
         <v>0301</v>
       </c>
-      <c r="J20" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K20" t="str">
-        <v>0304</v>
-      </c>
       <c r="L20" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M20" t="str">
-        <v>30000221732</v>
+        <v>30000522654</v>
       </c>
       <c r="N20" t="str">
         <v>State Bank of India</v>
@@ -2551,48 +2551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P20" t="str">
-        <v>SBIN0004117</v>
+        <v>SBIN0005292</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>0300024</v>
+        <v>0300097</v>
       </c>
       <c r="B21" t="str">
-        <v>PRAMOD RAM</v>
+        <v>MD. IRFAN YADAV</v>
       </c>
       <c r="C21" t="str">
-        <v>Senior Clerk</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D21" t="str">
-        <v>03022</v>
+        <v>03070</v>
       </c>
       <c r="E21" t="str">
-        <v>Middle School Tariyani No.2</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F21" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G21" t="str">
-        <v>9003000024</v>
+        <v>9003000097</v>
       </c>
       <c r="H21" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I21" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J21" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K21" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L21" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M21" t="str">
-        <v>30000190056</v>
+        <v>30000768143</v>
       </c>
       <c r="N21" t="str">
         <v>State Bank of India</v>
@@ -2601,48 +2601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P21" t="str">
-        <v>SBIN0009111</v>
+        <v>SBIN0001486</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>0300104</v>
+        <v>0300040</v>
       </c>
       <c r="B22" t="str">
-        <v>PRAMOD PASWAN</v>
+        <v>MAHESH ALAM N</v>
       </c>
       <c r="C22" t="str">
-        <v>Revenue Officer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D22" t="str">
-        <v>03077</v>
+        <v>03036</v>
       </c>
       <c r="E22" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>Block Education Office Purnahiya</v>
       </c>
       <c r="F22" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G22" t="str">
-        <v>9003000104</v>
+        <v>9003000040</v>
       </c>
       <c r="H22" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I22" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J22" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K22" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L22" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M22" t="str">
-        <v>30000823576</v>
+        <v>30000316760</v>
       </c>
       <c r="N22" t="str">
         <v>State Bank of India</v>
@@ -2651,48 +2651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P22" t="str">
-        <v>SBIN0006055</v>
+        <v>SBIN0008166</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>0300050</v>
+        <v>0300086</v>
       </c>
       <c r="B23" t="str">
-        <v>SUNIL DEVI</v>
+        <v>FARHAT PRASAD</v>
       </c>
       <c r="C23" t="str">
-        <v>Accountant</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D23" t="str">
-        <v>03043</v>
+        <v>03070</v>
       </c>
       <c r="E23" t="str">
-        <v>High School Piprahi No.1</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F23" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G23" t="str">
-        <v>9003000050</v>
+        <v>9003000086</v>
       </c>
       <c r="H23" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I23" t="str">
-        <v>999999</v>
+        <v>0303</v>
       </c>
       <c r="J23" t="str">
-        <v>Others</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K23" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L23" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M23" t="str">
-        <v>30000395950</v>
+        <v>30000681034</v>
       </c>
       <c r="N23" t="str">
         <v>State Bank of India</v>
@@ -2701,48 +2701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P23" t="str">
-        <v>SBIN0006799</v>
+        <v>SBIN0006039</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>0300053</v>
+        <v>0300108</v>
       </c>
       <c r="B24" t="str">
-        <v>RAVI PRASAD</v>
+        <v>MANOJ RAI</v>
       </c>
       <c r="C24" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D24" t="str">
-        <v>03046</v>
+        <v>03083</v>
       </c>
       <c r="E24" t="str">
-        <v>Panchayat Bhawan Piprahi No.3</v>
+        <v>Bank of India, Tariyani</v>
       </c>
       <c r="F24" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G24" t="str">
-        <v>9003000053</v>
+        <v>9003000108</v>
       </c>
       <c r="H24" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I24" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J24" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K24" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L24" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M24" t="str">
-        <v>30000419707</v>
+        <v>30000855252</v>
       </c>
       <c r="N24" t="str">
         <v>State Bank of India</v>
@@ -2751,48 +2751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P24" t="str">
-        <v>SBIN0007055</v>
+        <v>SBIN0002579</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0300070</v>
+        <v>0300111</v>
       </c>
       <c r="B25" t="str">
-        <v>RAMESH RAM</v>
+        <v>DINESH ALAM</v>
       </c>
       <c r="C25" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D25" t="str">
-        <v>03058</v>
+        <v>03087</v>
       </c>
       <c r="E25" t="str">
-        <v>Kanya Middle School Piprahi No.4</v>
+        <v>Central Bank of India, Tariyani</v>
       </c>
       <c r="F25" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G25" t="str">
-        <v>9003000070</v>
+        <v>9003000111</v>
       </c>
       <c r="H25" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I25" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J25" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K25" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L25" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M25" t="str">
-        <v>30000554330</v>
+        <v>30000879009</v>
       </c>
       <c r="N25" t="str">
         <v>State Bank of India</v>
@@ -2801,33 +2801,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P25" t="str">
-        <v>SBIN0008096</v>
+        <v>SBIN0006002</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>0300035</v>
+        <v>0300063</v>
       </c>
       <c r="B26" t="str">
-        <v>MAMTA MAHTO</v>
+        <v>UMESH SHARMA</v>
       </c>
       <c r="C26" t="str">
-        <v>Head Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D26" t="str">
-        <v>03027</v>
+        <v>03053</v>
       </c>
       <c r="E26" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>CDPO Office Dumri Katsari No.2</v>
       </c>
       <c r="F26" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G26" t="str">
-        <v>9003000035</v>
+        <v>9003000063</v>
       </c>
       <c r="H26" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I26" t="str">
         <v>0304</v>
@@ -2836,13 +2836,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K26" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L26" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M26" t="str">
-        <v>30000277165</v>
+        <v>30000498897</v>
       </c>
       <c r="N26" t="str">
         <v>State Bank of India</v>
@@ -2851,39 +2851,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P26" t="str">
-        <v>SBIN0007546</v>
+        <v>SBIN0002990</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>0300027</v>
+        <v>0300039</v>
       </c>
       <c r="B27" t="str">
-        <v>RINKU SINGH</v>
+        <v>AMIT SHARMA</v>
       </c>
       <c r="C27" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D27" t="str">
-        <v>03025</v>
+        <v>03035</v>
       </c>
       <c r="E27" t="str">
-        <v>High School Dumri Katsari No.4</v>
+        <v>Kanya Middle School Dumri Katsari No.3</v>
       </c>
       <c r="F27" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G27" t="str">
-        <v>9003000027</v>
+        <v>9003000039</v>
       </c>
       <c r="H27" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I27" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J27" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K27" t="str">
         <v>0304</v>
@@ -2892,7 +2892,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M27" t="str">
-        <v>30000213813</v>
+        <v>30000308841</v>
       </c>
       <c r="N27" t="str">
         <v>State Bank of India</v>
@@ -2901,39 +2901,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P27" t="str">
-        <v>SBIN0001764</v>
+        <v>SBIN0003027</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>0300093</v>
+        <v>0300122</v>
       </c>
       <c r="B28" t="str">
-        <v>ANITA SAH</v>
+        <v>ALOK ALAM</v>
       </c>
       <c r="C28" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D28" t="str">
-        <v>03074</v>
+        <v>03096</v>
       </c>
       <c r="E28" t="str">
-        <v>RWD Sub-Division Dumri Katsari</v>
+        <v>Punjab National Bank, Dumri Katsari</v>
       </c>
       <c r="F28" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G28" t="str">
-        <v>9003000093</v>
+        <v>9003000122</v>
       </c>
       <c r="H28" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I28" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J28" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K28" t="str">
         <v>0304</v>
@@ -2942,7 +2942,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M28" t="str">
-        <v>30000736467</v>
+        <v>30000966118</v>
       </c>
       <c r="N28" t="str">
         <v>State Bank of India</v>
@@ -2951,48 +2951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P28" t="str">
-        <v>SBIN0006302</v>
+        <v>SBIN0001559</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>0300048</v>
+        <v>0300058</v>
       </c>
       <c r="B29" t="str">
-        <v>MD. IRFAN DEVI</v>
+        <v>ASHA MISHRA</v>
       </c>
       <c r="C29" t="str">
-        <v>Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D29" t="str">
-        <v>03041</v>
+        <v>03028</v>
       </c>
       <c r="E29" t="str">
-        <v>PHC Sheohar</v>
+        <v>Panchayat Bhawan Tariyani</v>
       </c>
       <c r="F29" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G29" t="str">
-        <v>9003000048</v>
+        <v>9003000058</v>
       </c>
       <c r="H29" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I29" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J29" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K29" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L29" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M29" t="str">
-        <v>30000380112</v>
+        <v>30000459302</v>
       </c>
       <c r="N29" t="str">
         <v>State Bank of India</v>
@@ -3001,33 +3001,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P29" t="str">
-        <v>SBIN0006186</v>
+        <v>SBIN0005604</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>0300124</v>
+        <v>0300103</v>
       </c>
       <c r="B30" t="str">
-        <v>ANITA RAM</v>
+        <v>USHA PASWAN</v>
       </c>
       <c r="C30" t="str">
-        <v>Branch Manager</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D30" t="str">
-        <v>03097</v>
+        <v>03082</v>
       </c>
       <c r="E30" t="str">
-        <v>Central Bank of India, Purnahiya</v>
+        <v>RWD Sub-Division Dumri Katsari</v>
       </c>
       <c r="F30" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G30" t="str">
-        <v>9003000124</v>
+        <v>9003000103</v>
       </c>
       <c r="H30" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I30" t="str">
         <v>0304</v>
@@ -3036,13 +3036,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K30" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L30" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M30" t="str">
-        <v>30000981956</v>
+        <v>30000815657</v>
       </c>
       <c r="N30" t="str">
         <v>State Bank of India</v>
@@ -3051,33 +3051,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P30" t="str">
-        <v>SBIN0007366</v>
+        <v>SBIN0004879</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>0300029</v>
+        <v>0300060</v>
       </c>
       <c r="B31" t="str">
-        <v>USHA PRASAD</v>
+        <v>PRAMOD VERMA</v>
       </c>
       <c r="C31" t="str">
-        <v>Head Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D31" t="str">
-        <v>03027</v>
+        <v>03051</v>
       </c>
       <c r="E31" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>Panchayat Bhawan Sheohar</v>
       </c>
       <c r="F31" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G31" t="str">
-        <v>9003000029</v>
+        <v>9003000060</v>
       </c>
       <c r="H31" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I31" t="str">
         <v>0301</v>
@@ -3092,7 +3092,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M31" t="str">
-        <v>30000229651</v>
+        <v>30000475140</v>
       </c>
       <c r="N31" t="str">
         <v>State Bank of India</v>
@@ -3101,33 +3101,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P31" t="str">
-        <v>SBIN0008202</v>
+        <v>SBIN0005770</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>0300106</v>
+        <v>0300089</v>
       </c>
       <c r="B32" t="str">
-        <v>NASREEN KUMAR</v>
+        <v>ANIL DEVI</v>
       </c>
       <c r="C32" t="str">
-        <v>Administrative Officer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D32" t="str">
-        <v>03083</v>
+        <v>03072</v>
       </c>
       <c r="E32" t="str">
-        <v>UCO Bank, Tariyani</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="F32" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G32" t="str">
-        <v>9003000106</v>
+        <v>9003000089</v>
       </c>
       <c r="H32" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I32" t="str">
         <v>0305</v>
@@ -3142,7 +3142,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M32" t="str">
-        <v>30000839414</v>
+        <v>30000704791</v>
       </c>
       <c r="N32" t="str">
         <v>State Bank of India</v>
@@ -3151,48 +3151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P32" t="str">
-        <v>SBIN0003197</v>
+        <v>SBIN0008564</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>0300015</v>
+        <v>0300091</v>
       </c>
       <c r="B33" t="str">
-        <v>ARVIND TIWARI</v>
+        <v>SHAILESH ANSARI</v>
       </c>
       <c r="C33" t="str">
-        <v>Section Officer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D33" t="str">
-        <v>03015</v>
+        <v>03024</v>
       </c>
       <c r="E33" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F33" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G33" t="str">
-        <v>9003000015</v>
+        <v>9003000091</v>
       </c>
       <c r="H33" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I33" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K33" t="str">
         <v>0303</v>
       </c>
-      <c r="J33" t="str">
+      <c r="L33" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="K33" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L33" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M33" t="str">
-        <v>30000118785</v>
+        <v>30000720629</v>
       </c>
       <c r="N33" t="str">
         <v>State Bank of India</v>
@@ -3201,39 +3201,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P33" t="str">
-        <v>SBIN0003975</v>
+        <v>SBIN0004862</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>0300122</v>
+        <v>0300104</v>
       </c>
       <c r="B34" t="str">
-        <v>PRIYANKA YADAV</v>
+        <v>ARVIND SINGH O</v>
       </c>
       <c r="C34" t="str">
-        <v>Postmaster</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D34" t="str">
-        <v>03095</v>
+        <v>03078</v>
       </c>
       <c r="E34" t="str">
-        <v>Central Bank of India, Piprahi</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F34" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G34" t="str">
-        <v>9003000122</v>
+        <v>9003000104</v>
       </c>
       <c r="H34" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I34" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J34" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K34" t="str">
         <v>0302</v>
@@ -3242,7 +3242,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M34" t="str">
-        <v>30000966118</v>
+        <v>30000823576</v>
       </c>
       <c r="N34" t="str">
         <v>State Bank of India</v>
@@ -3251,48 +3251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P34" t="str">
-        <v>SBIN0006826</v>
+        <v>SBIN0004195</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>0300115</v>
+        <v>0300003</v>
       </c>
       <c r="B35" t="str">
-        <v>MANOJ RAM</v>
+        <v>MANOJ YADAV</v>
       </c>
       <c r="C35" t="str">
-        <v>Assistant Manager</v>
+        <v>Headmaster</v>
       </c>
       <c r="D35" t="str">
-        <v>03091</v>
+        <v>03003</v>
       </c>
       <c r="E35" t="str">
-        <v>LIC Branch Office, Purnahiya</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F35" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G35" t="str">
-        <v>9003000115</v>
+        <v>9003000003</v>
       </c>
       <c r="H35" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I35" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J35" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K35" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L35" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M35" t="str">
-        <v>30000910685</v>
+        <v>30000023757</v>
       </c>
       <c r="N35" t="str">
         <v>State Bank of India</v>
@@ -3301,48 +3301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P35" t="str">
-        <v>SBIN0009617</v>
+        <v>SBIN0009244</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>0300108</v>
+        <v>0300033</v>
       </c>
       <c r="B36" t="str">
-        <v>DEEPAK VERMA</v>
+        <v>ALOK PRASAD</v>
       </c>
       <c r="C36" t="str">
-        <v>Postmaster</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D36" t="str">
-        <v>03085</v>
+        <v>03030</v>
       </c>
       <c r="E36" t="str">
-        <v>BSNL Exchange, Purnahiya</v>
+        <v>PHED Division Sheohar</v>
       </c>
       <c r="F36" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G36" t="str">
-        <v>9003000108</v>
+        <v>9003000033</v>
       </c>
       <c r="H36" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I36" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J36" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K36" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L36" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M36" t="str">
-        <v>30000855252</v>
+        <v>30000261327</v>
       </c>
       <c r="N36" t="str">
         <v>State Bank of India</v>
@@ -3351,39 +3351,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P36" t="str">
-        <v>SBIN0002418</v>
+        <v>SBIN0004267</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>0300056</v>
+        <v>0300072</v>
       </c>
       <c r="B37" t="str">
-        <v>RAMESH PANDEY</v>
+        <v>PRAMOD MISHRA D</v>
       </c>
       <c r="C37" t="str">
-        <v>Teacher</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D37" t="str">
-        <v>03049</v>
+        <v>03037</v>
       </c>
       <c r="E37" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>PHC Piprahi</v>
       </c>
       <c r="F37" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G37" t="str">
-        <v>9003000056</v>
+        <v>9003000072</v>
       </c>
       <c r="H37" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I37" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J37" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K37" t="str">
         <v>0302</v>
@@ -3392,7 +3392,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M37" t="str">
-        <v>30000443464</v>
+        <v>30000570168</v>
       </c>
       <c r="N37" t="str">
         <v>State Bank of India</v>
@@ -3401,48 +3401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P37" t="str">
-        <v>SBIN0006959</v>
+        <v>SBIN0009200</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>0300099</v>
+        <v>0300061</v>
       </c>
       <c r="B38" t="str">
-        <v>ANIL GUPTA</v>
+        <v>MAHESH ANSARI</v>
       </c>
       <c r="C38" t="str">
-        <v>Junior Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D38" t="str">
-        <v>03072</v>
+        <v>03052</v>
       </c>
       <c r="E38" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>Panchayat Bhawan Dumri Katsari No.4</v>
       </c>
       <c r="F38" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G38" t="str">
-        <v>9003000099</v>
+        <v>9003000061</v>
       </c>
       <c r="H38" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I38" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J38" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K38" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L38" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M38" t="str">
-        <v>30000783981</v>
+        <v>30000483059</v>
       </c>
       <c r="N38" t="str">
         <v>State Bank of India</v>
@@ -3451,48 +3451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P38" t="str">
-        <v>SBIN0004895</v>
+        <v>SBIN0006879</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>0300121</v>
+        <v>0300042</v>
       </c>
       <c r="B39" t="str">
-        <v>MAHESH KHATUN</v>
+        <v>MD. IRFAN SHARMA</v>
       </c>
       <c r="C39" t="str">
-        <v>Postmaster</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D39" t="str">
-        <v>03089</v>
+        <v>03037</v>
       </c>
       <c r="E39" t="str">
-        <v>LIC Branch Office, Tariyani</v>
+        <v>PHC Piprahi</v>
       </c>
       <c r="F39" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G39" t="str">
-        <v>9003000121</v>
+        <v>9003000042</v>
       </c>
       <c r="H39" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I39" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J39" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K39" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L39" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M39" t="str">
-        <v>30000958199</v>
+        <v>30000332598</v>
       </c>
       <c r="N39" t="str">
         <v>State Bank of India</v>
@@ -3501,48 +3501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P39" t="str">
-        <v>SBIN0005548</v>
+        <v>SBIN0009470</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>0300111</v>
+        <v>0300070</v>
       </c>
       <c r="B40" t="str">
-        <v>DEEPAK KHATUN</v>
+        <v>ARVIND KHATUN R</v>
       </c>
       <c r="C40" t="str">
-        <v>Assistant Manager</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D40" t="str">
-        <v>03088</v>
+        <v>03060</v>
       </c>
       <c r="E40" t="str">
-        <v>UCO Bank, Sheohar</v>
+        <v>Project Girls High School Piprahi No.1</v>
       </c>
       <c r="F40" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G40" t="str">
-        <v>9003000111</v>
+        <v>9003000070</v>
       </c>
       <c r="H40" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I40" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J40" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K40" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L40" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M40" t="str">
-        <v>30000879009</v>
+        <v>30000554330</v>
       </c>
       <c r="N40" t="str">
         <v>State Bank of India</v>
@@ -3551,48 +3551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P40" t="str">
-        <v>SBIN0008626</v>
+        <v>SBIN0005633</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>0300114</v>
+        <v>0300118</v>
       </c>
       <c r="B41" t="str">
-        <v>ABDUL KALAM KHATUN</v>
+        <v>VINOD SAH</v>
       </c>
       <c r="C41" t="str">
-        <v>Administrative Officer</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D41" t="str">
-        <v>03090</v>
+        <v>03093</v>
       </c>
       <c r="E41" t="str">
-        <v>State Bank of India, Purnahiya</v>
+        <v>State Bank of India, Dumri Katsari</v>
       </c>
       <c r="F41" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G41" t="str">
-        <v>9003000114</v>
+        <v>9003000118</v>
       </c>
       <c r="H41" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I41" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="J41" t="str">
-        <v>Others</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K41" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L41" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M41" t="str">
-        <v>30000902766</v>
+        <v>30000934442</v>
       </c>
       <c r="N41" t="str">
         <v>State Bank of India</v>
@@ -3601,48 +3601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P41" t="str">
-        <v>SBIN0003588</v>
+        <v>SBIN0003796</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>0300072</v>
+        <v>0300018</v>
       </c>
       <c r="B42" t="str">
-        <v>SANTOSH RAI</v>
+        <v>SURESH CHAUDHARY</v>
       </c>
       <c r="C42" t="str">
-        <v>Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D42" t="str">
-        <v>03053</v>
+        <v>03016</v>
       </c>
       <c r="E42" t="str">
-        <v>Panchayat Bhawan Dumri Katsari No.4</v>
+        <v>Block Education Office Tariyani</v>
       </c>
       <c r="F42" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G42" t="str">
-        <v>9003000072</v>
+        <v>9003000018</v>
       </c>
       <c r="H42" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I42" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J42" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K42" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L42" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M42" t="str">
-        <v>30000570168</v>
+        <v>30000142542</v>
       </c>
       <c r="N42" t="str">
         <v>State Bank of India</v>
@@ -3651,48 +3651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P42" t="str">
-        <v>SBIN0001520</v>
+        <v>SBIN0005275</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>0300020</v>
+        <v>0300027</v>
       </c>
       <c r="B43" t="str">
-        <v>ANITA PRASAD</v>
+        <v>NEHA PRASAD</v>
       </c>
       <c r="C43" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D43" t="str">
-        <v>03019</v>
+        <v>03025</v>
       </c>
       <c r="E43" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Block Office Tariyani No.1</v>
       </c>
       <c r="F43" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G43" t="str">
-        <v>9003000020</v>
+        <v>9003000027</v>
       </c>
       <c r="H43" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I43" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J43" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K43" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L43" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M43" t="str">
-        <v>30000158380</v>
+        <v>30000213813</v>
       </c>
       <c r="N43" t="str">
         <v>State Bank of India</v>
@@ -3701,39 +3701,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P43" t="str">
-        <v>SBIN0006494</v>
+        <v>SBIN0001600</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>0300019</v>
+        <v>0300113</v>
       </c>
       <c r="B44" t="str">
-        <v>ANIL VERMA</v>
+        <v>SAVITA PASWAN</v>
       </c>
       <c r="C44" t="str">
-        <v>Section Officer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D44" t="str">
-        <v>03019</v>
+        <v>03089</v>
       </c>
       <c r="E44" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>State Bank of India, Sheohar</v>
       </c>
       <c r="F44" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G44" t="str">
-        <v>9003000019</v>
+        <v>9003000113</v>
       </c>
       <c r="H44" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I44" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J44" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K44" t="str">
         <v>0301</v>
@@ -3742,7 +3742,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M44" t="str">
-        <v>30000150461</v>
+        <v>30000894847</v>
       </c>
       <c r="N44" t="str">
         <v>State Bank of India</v>
@@ -3751,48 +3751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P44" t="str">
-        <v>SBIN0008162</v>
+        <v>SBIN0002253</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>0300083</v>
+        <v>0300030</v>
       </c>
       <c r="B45" t="str">
-        <v>MAHESH PANDEY</v>
+        <v>FARHAT KUMAR</v>
       </c>
       <c r="C45" t="str">
-        <v>Data Entry Operator</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D45" t="str">
-        <v>03068</v>
+        <v>03027</v>
       </c>
       <c r="E45" t="str">
-        <v>Block Education Office Purnahiya No.4</v>
+        <v>High School Dumri Katsari No.3</v>
       </c>
       <c r="F45" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G45" t="str">
-        <v>9003000083</v>
+        <v>9003000030</v>
       </c>
       <c r="H45" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I45" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J45" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K45" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L45" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M45" t="str">
-        <v>30000657277</v>
+        <v>30000237570</v>
       </c>
       <c r="N45" t="str">
         <v>State Bank of India</v>
@@ -3801,48 +3801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P45" t="str">
-        <v>SBIN0001295</v>
+        <v>SBIN0007251</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>0300011</v>
+        <v>0300001</v>
       </c>
       <c r="B46" t="str">
-        <v>MD. SHAHID SINHA</v>
+        <v>ANITA VERMA</v>
       </c>
       <c r="C46" t="str">
-        <v>Section Officer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D46" t="str">
-        <v>03011</v>
+        <v>03001</v>
       </c>
       <c r="E46" t="str">
-        <v>Project Girls High School Sheohar No.2</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F46" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G46" t="str">
-        <v>9003000011</v>
+        <v>9003000001</v>
       </c>
       <c r="H46" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I46" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J46" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K46" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L46" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M46" t="str">
-        <v>30000087109</v>
+        <v>30000007919</v>
       </c>
       <c r="N46" t="str">
         <v>State Bank of India</v>
@@ -3851,39 +3851,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P46" t="str">
-        <v>SBIN0006751</v>
+        <v>SBIN0009441</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0300051</v>
+        <v>0300045</v>
       </c>
       <c r="B47" t="str">
-        <v>PRAMOD THAKUR</v>
+        <v>NIRMALA PRASAD</v>
       </c>
       <c r="C47" t="str">
         <v>Revenue Karmachari</v>
       </c>
       <c r="D47" t="str">
-        <v>03044</v>
+        <v>03039</v>
       </c>
       <c r="E47" t="str">
-        <v>Middle School Purnahiya No.1</v>
+        <v>Panchayat Bhawan Purnahiya</v>
       </c>
       <c r="F47" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G47" t="str">
-        <v>9003000051</v>
+        <v>9003000045</v>
       </c>
       <c r="H47" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I47" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J47" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K47" t="str">
         <v>0303</v>
@@ -3892,7 +3892,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M47" t="str">
-        <v>30000403869</v>
+        <v>30000356355</v>
       </c>
       <c r="N47" t="str">
         <v>State Bank of India</v>
@@ -3901,48 +3901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P47" t="str">
-        <v>SBIN0003499</v>
+        <v>SBIN0006291</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0300109</v>
+        <v>0300068</v>
       </c>
       <c r="B48" t="str">
-        <v>PANKAJ TIWARI</v>
+        <v>RAJESH KHATUN</v>
       </c>
       <c r="C48" t="str">
-        <v>Assistant Manager</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D48" t="str">
-        <v>03086</v>
+        <v>03058</v>
       </c>
       <c r="E48" t="str">
-        <v>Bank of India, Sheohar</v>
+        <v>Project Girls High School Tariyani No.3</v>
       </c>
       <c r="F48" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G48" t="str">
-        <v>9003000109</v>
+        <v>9003000068</v>
       </c>
       <c r="H48" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I48" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J48" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K48" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L48" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M48" t="str">
-        <v>30000863171</v>
+        <v>30000538492</v>
       </c>
       <c r="N48" t="str">
         <v>State Bank of India</v>
@@ -3951,33 +3951,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P48" t="str">
-        <v>SBIN0006944</v>
+        <v>SBIN0009159</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0300068</v>
+        <v>0300054</v>
       </c>
       <c r="B49" t="str">
-        <v>SAVITA MAHTO</v>
+        <v>MAHESH MAHTO</v>
       </c>
       <c r="C49" t="str">
-        <v>Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D49" t="str">
-        <v>03009</v>
+        <v>03046</v>
       </c>
       <c r="E49" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>Panchayat Bhawan Dumri Katsari No.2</v>
       </c>
       <c r="F49" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G49" t="str">
-        <v>9003000068</v>
+        <v>9003000054</v>
       </c>
       <c r="H49" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I49" t="str">
         <v>0301</v>
@@ -3986,13 +3986,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K49" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L49" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M49" t="str">
-        <v>30000538492</v>
+        <v>30000427626</v>
       </c>
       <c r="N49" t="str">
         <v>State Bank of India</v>
@@ -4001,33 +4001,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P49" t="str">
-        <v>SBIN0005700</v>
+        <v>SBIN0007387</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0300021</v>
+        <v>0300037</v>
       </c>
       <c r="B50" t="str">
-        <v>VIJAY KUMAR</v>
+        <v>RAJESH YADAV</v>
       </c>
       <c r="C50" t="str">
-        <v>Assistant Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D50" t="str">
-        <v>03020</v>
+        <v>03033</v>
       </c>
       <c r="E50" t="str">
-        <v>Circle Office Sheohar No.3</v>
+        <v>Block Office Purnahiya No.4</v>
       </c>
       <c r="F50" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G50" t="str">
-        <v>9003000021</v>
+        <v>9003000037</v>
       </c>
       <c r="H50" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I50" t="str">
         <v>0305</v>
@@ -4036,13 +4036,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K50" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L50" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M50" t="str">
-        <v>30000166299</v>
+        <v>30000293003</v>
       </c>
       <c r="N50" t="str">
         <v>State Bank of India</v>
@@ -4051,48 +4051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P50" t="str">
-        <v>SBIN0007266</v>
+        <v>SBIN0009907</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>0300092</v>
+        <v>0300077</v>
       </c>
       <c r="B51" t="str">
-        <v>MD. IRFAN ANSARI</v>
+        <v>UMESH VERMA</v>
       </c>
       <c r="C51" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D51" t="str">
-        <v>03073</v>
+        <v>03065</v>
       </c>
       <c r="E51" t="str">
-        <v>Minor Irrigation Office Dumri Katsari</v>
+        <v>Block Office Purnahiya No.3</v>
       </c>
       <c r="F51" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G51" t="str">
-        <v>9003000092</v>
+        <v>9003000077</v>
       </c>
       <c r="H51" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I51" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J51" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K51" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L51" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M51" t="str">
-        <v>30000728548</v>
+        <v>30000609763</v>
       </c>
       <c r="N51" t="str">
         <v>State Bank of India</v>
@@ -4101,48 +4101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P51" t="str">
-        <v>SBIN0004203</v>
+        <v>SBIN0005807</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>0300031</v>
+        <v>0300082</v>
       </c>
       <c r="B52" t="str">
-        <v>RAKESH PASWAN</v>
+        <v>MAMTA SINGH I</v>
       </c>
       <c r="C52" t="str">
-        <v>Head Clerk</v>
+        <v>Clerk</v>
       </c>
       <c r="D52" t="str">
-        <v>03027</v>
+        <v>03067</v>
       </c>
       <c r="E52" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>Block Office Piprahi No.4</v>
       </c>
       <c r="F52" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G52" t="str">
-        <v>9003000031</v>
+        <v>9003000082</v>
       </c>
       <c r="H52" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I52" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J52" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K52" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L52" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M52" t="str">
-        <v>30000245489</v>
+        <v>30000649358</v>
       </c>
       <c r="N52" t="str">
         <v>State Bank of India</v>
@@ -4151,48 +4151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P52" t="str">
-        <v>SBIN0004511</v>
+        <v>SBIN0005698</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>0300066</v>
+        <v>0300015</v>
       </c>
       <c r="B53" t="str">
-        <v>SHAILESH RAI J</v>
+        <v>SANTOSH OJHA</v>
       </c>
       <c r="C53" t="str">
-        <v>Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D53" t="str">
-        <v>03055</v>
+        <v>03013</v>
       </c>
       <c r="E53" t="str">
-        <v>CDPO Office Piprahi</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="F53" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G53" t="str">
-        <v>9003000066</v>
+        <v>9003000015</v>
       </c>
       <c r="H53" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I53" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J53" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K53" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L53" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M53" t="str">
-        <v>30000522654</v>
+        <v>30000118785</v>
       </c>
       <c r="N53" t="str">
         <v>State Bank of India</v>
@@ -4201,48 +4201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P53" t="str">
-        <v>SBIN0009025</v>
+        <v>SBIN0004561</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>0300042</v>
+        <v>0300049</v>
       </c>
       <c r="B54" t="str">
-        <v>ABDUL KALAM YADAV</v>
+        <v>RAMESH SINGH</v>
       </c>
       <c r="C54" t="str">
-        <v>Senior Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D54" t="str">
-        <v>03037</v>
+        <v>03041</v>
       </c>
       <c r="E54" t="str">
-        <v>Primary School Piprahi No.2</v>
+        <v>Kanya Middle School Tariyani No.3</v>
       </c>
       <c r="F54" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G54" t="str">
-        <v>9003000042</v>
+        <v>9003000049</v>
       </c>
       <c r="H54" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I54" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J54" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K54" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L54" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M54" t="str">
-        <v>30000332598</v>
+        <v>30000388031</v>
       </c>
       <c r="N54" t="str">
         <v>State Bank of India</v>
@@ -4251,48 +4251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P54" t="str">
-        <v>SBIN0001297</v>
+        <v>SBIN0003764</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>0300097</v>
+        <v>0300010</v>
       </c>
       <c r="B55" t="str">
-        <v>ANIL SINGH C</v>
+        <v>ARVIND SINGH</v>
       </c>
       <c r="C55" t="str">
-        <v>Revenue Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D55" t="str">
-        <v>03078</v>
+        <v>03005</v>
       </c>
       <c r="E55" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F55" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G55" t="str">
-        <v>9003000097</v>
+        <v>9003000010</v>
       </c>
       <c r="H55" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I55" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J55" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K55" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L55" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M55" t="str">
-        <v>30000768143</v>
+        <v>30000079190</v>
       </c>
       <c r="N55" t="str">
         <v>State Bank of India</v>
@@ -4301,48 +4301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P55" t="str">
-        <v>SBIN0001056</v>
+        <v>SBIN0004077</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>0300063</v>
+        <v>0300110</v>
       </c>
       <c r="B56" t="str">
-        <v>UMESH OJHA</v>
+        <v>SHAILESH OJHA</v>
       </c>
       <c r="C56" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D56" t="str">
-        <v>03027</v>
+        <v>03086</v>
       </c>
       <c r="E56" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>Bank of India, Piprahi</v>
       </c>
       <c r="F56" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G56" t="str">
-        <v>9003000063</v>
+        <v>9003000110</v>
       </c>
       <c r="H56" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I56" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J56" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K56" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L56" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M56" t="str">
-        <v>30000498897</v>
+        <v>30000871090</v>
       </c>
       <c r="N56" t="str">
         <v>State Bank of India</v>
@@ -4351,33 +4351,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P56" t="str">
-        <v>SBIN0006132</v>
+        <v>SBIN0006641</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>0300055</v>
+        <v>0300012</v>
       </c>
       <c r="B57" t="str">
-        <v>ABDUL KALAM RAI V</v>
+        <v>SANJAY CHAUDHARY</v>
       </c>
       <c r="C57" t="str">
-        <v>Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D57" t="str">
-        <v>03048</v>
+        <v>03011</v>
       </c>
       <c r="E57" t="str">
-        <v>High School Sheohar No.1</v>
+        <v>High School Tariyani No.3</v>
       </c>
       <c r="F57" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G57" t="str">
-        <v>9003000055</v>
+        <v>9003000012</v>
       </c>
       <c r="H57" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I57" t="str">
         <v>0301</v>
@@ -4386,13 +4386,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K57" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L57" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M57" t="str">
-        <v>30000435545</v>
+        <v>30000095028</v>
       </c>
       <c r="N57" t="str">
         <v>State Bank of India</v>
@@ -4401,48 +4401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P57" t="str">
-        <v>SBIN0009410</v>
+        <v>SBIN0006846</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>0300039</v>
+        <v>0300022</v>
       </c>
       <c r="B58" t="str">
-        <v>SUNIL JHA T</v>
+        <v>SANTOSH MISHRA</v>
       </c>
       <c r="C58" t="str">
         <v>Senior Clerk</v>
       </c>
       <c r="D58" t="str">
-        <v>03035</v>
+        <v>03020</v>
       </c>
       <c r="E58" t="str">
-        <v>Panchayat Bhawan Dumri Katsari No.2</v>
+        <v>Kanya Middle School Purnahiya No.4</v>
       </c>
       <c r="F58" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G58" t="str">
-        <v>9003000039</v>
+        <v>9003000022</v>
       </c>
       <c r="H58" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I58" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J58" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K58" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L58" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M58" t="str">
-        <v>30000308841</v>
+        <v>30000174218</v>
       </c>
       <c r="N58" t="str">
         <v>State Bank of India</v>
@@ -4451,39 +4451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P58" t="str">
-        <v>SBIN0007041</v>
+        <v>SBIN0009465</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>0300018</v>
+        <v>0300100</v>
       </c>
       <c r="B59" t="str">
-        <v>PRIYANKA TIWARI</v>
+        <v>MD. IRFAN VERMA</v>
       </c>
       <c r="C59" t="str">
-        <v>Section Officer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D59" t="str">
-        <v>03018</v>
+        <v>03080</v>
       </c>
       <c r="E59" t="str">
-        <v>CDPO Office Dumri Katsari No.4</v>
+        <v>Minor Irrigation Office Dumri Katsari</v>
       </c>
       <c r="F59" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G59" t="str">
-        <v>9003000018</v>
+        <v>9003000100</v>
       </c>
       <c r="H59" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I59" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J59" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K59" t="str">
         <v>0304</v>
@@ -4492,7 +4492,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M59" t="str">
-        <v>30000142542</v>
+        <v>30000791900</v>
       </c>
       <c r="N59" t="str">
         <v>State Bank of India</v>
@@ -4501,48 +4501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P59" t="str">
-        <v>SBIN0006103</v>
+        <v>SBIN0003009</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>0300071</v>
+        <v>0300098</v>
       </c>
       <c r="B60" t="str">
-        <v>NIRMALA SHARMA</v>
+        <v>MD. IRFAN PANDEY</v>
       </c>
       <c r="C60" t="str">
-        <v>Clerk</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D60" t="str">
-        <v>03059</v>
+        <v>03078</v>
       </c>
       <c r="E60" t="str">
-        <v>Project Girls High School Purnahiya No.2</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F60" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G60" t="str">
-        <v>9003000071</v>
+        <v>9003000098</v>
       </c>
       <c r="H60" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I60" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J60" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K60" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L60" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M60" t="str">
-        <v>30000562249</v>
+        <v>30000776062</v>
       </c>
       <c r="N60" t="str">
         <v>State Bank of India</v>
@@ -4551,48 +4551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P60" t="str">
-        <v>SBIN0004237</v>
+        <v>SBIN0001147</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>0300088</v>
+        <v>0300078</v>
       </c>
       <c r="B61" t="str">
-        <v>FARHAT ANSARI</v>
+        <v>NEHA SHARMA</v>
       </c>
       <c r="C61" t="str">
-        <v>Assistant Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D61" t="str">
-        <v>03070</v>
+        <v>03063</v>
       </c>
       <c r="E61" t="str">
-        <v>RWD Sub-Division Tariyani</v>
+        <v>Block Office Dumri Katsari</v>
       </c>
       <c r="F61" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G61" t="str">
-        <v>9003000088</v>
+        <v>9003000078</v>
       </c>
       <c r="H61" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I61" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J61" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K61" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L61" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M61" t="str">
-        <v>30000696872</v>
+        <v>30000617682</v>
       </c>
       <c r="N61" t="str">
         <v>State Bank of India</v>
@@ -4601,39 +4601,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P61" t="str">
-        <v>SBIN0009209</v>
+        <v>SBIN0005590</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>0300116</v>
+        <v>0300014</v>
       </c>
       <c r="B62" t="str">
-        <v>MUKESH KUMAR</v>
+        <v>DEEPAK YADAV</v>
       </c>
       <c r="C62" t="str">
-        <v>Branch Manager</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D62" t="str">
-        <v>03092</v>
+        <v>03006</v>
       </c>
       <c r="E62" t="str">
-        <v>State Bank of India, Sheohar</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F62" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G62" t="str">
-        <v>9003000116</v>
+        <v>9003000014</v>
       </c>
       <c r="H62" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I62" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J62" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K62" t="str">
         <v>0301</v>
@@ -4642,7 +4642,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M62" t="str">
-        <v>30000918604</v>
+        <v>30000110866</v>
       </c>
       <c r="N62" t="str">
         <v>State Bank of India</v>
@@ -4651,48 +4651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P62" t="str">
-        <v>SBIN0004804</v>
+        <v>SBIN0001472</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>0300058</v>
+        <v>0300062</v>
       </c>
       <c r="B63" t="str">
-        <v>SUNITA SHARMA</v>
+        <v>RAVI RAM</v>
       </c>
       <c r="C63" t="str">
         <v>Revenue Karmachari</v>
       </c>
       <c r="D63" t="str">
-        <v>03038</v>
+        <v>03002</v>
       </c>
       <c r="E63" t="str">
-        <v>High School Sheohar</v>
+        <v>Block Agriculture Office Tariyani No.3</v>
       </c>
       <c r="F63" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G63" t="str">
-        <v>9003000058</v>
+        <v>9003000062</v>
       </c>
       <c r="H63" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I63" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J63" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K63" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L63" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M63" t="str">
-        <v>30000459302</v>
+        <v>30000490978</v>
       </c>
       <c r="N63" t="str">
         <v>State Bank of India</v>
@@ -4701,33 +4701,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P63" t="str">
-        <v>SBIN0003831</v>
+        <v>SBIN0002673</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>0300065</v>
+        <v>0300046</v>
       </c>
       <c r="B64" t="str">
-        <v>SURESH PANDEY</v>
+        <v>MAHESH GUPTA</v>
       </c>
       <c r="C64" t="str">
         <v>Clerk</v>
       </c>
       <c r="D64" t="str">
-        <v>03051</v>
+        <v>03040</v>
       </c>
       <c r="E64" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>Circle Office Sheohar</v>
       </c>
       <c r="F64" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G64" t="str">
-        <v>9003000065</v>
+        <v>9003000046</v>
       </c>
       <c r="H64" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I64" t="str">
         <v>0305</v>
@@ -4742,7 +4742,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M64" t="str">
-        <v>30000514735</v>
+        <v>30000364274</v>
       </c>
       <c r="N64" t="str">
         <v>State Bank of India</v>
@@ -4751,39 +4751,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P64" t="str">
-        <v>SBIN0005959</v>
+        <v>SBIN0004967</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>0300052</v>
+        <v>0300005</v>
       </c>
       <c r="B65" t="str">
-        <v>RANJIT ALAM</v>
+        <v>DINESH CHAUDHARY</v>
       </c>
       <c r="C65" t="str">
-        <v>Clerk</v>
+        <v>Headmaster</v>
       </c>
       <c r="D65" t="str">
-        <v>03045</v>
+        <v>03005</v>
       </c>
       <c r="E65" t="str">
-        <v>CDPO Office Sheohar No.1</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F65" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G65" t="str">
-        <v>9003000052</v>
+        <v>9003000005</v>
       </c>
       <c r="H65" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I65" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J65" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K65" t="str">
         <v>0301</v>
@@ -4792,7 +4792,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M65" t="str">
-        <v>30000411788</v>
+        <v>30000039595</v>
       </c>
       <c r="N65" t="str">
         <v>State Bank of India</v>
@@ -4801,33 +4801,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P65" t="str">
-        <v>SBIN0004095</v>
+        <v>SBIN0003186</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>0300096</v>
+        <v>0300073</v>
       </c>
       <c r="B66" t="str">
-        <v>UMESH MISHRA</v>
+        <v>NEHA SAH</v>
       </c>
       <c r="C66" t="str">
-        <v>Assistant Engineer</v>
+        <v>Teacher</v>
       </c>
       <c r="D66" t="str">
-        <v>03077</v>
+        <v>03062</v>
       </c>
       <c r="E66" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>Circle Office Tariyani No.2</v>
       </c>
       <c r="F66" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G66" t="str">
-        <v>9003000096</v>
+        <v>9003000073</v>
       </c>
       <c r="H66" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I66" t="str">
         <v>0305</v>
@@ -4836,13 +4836,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K66" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L66" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M66" t="str">
-        <v>30000760224</v>
+        <v>30000578087</v>
       </c>
       <c r="N66" t="str">
         <v>State Bank of India</v>
@@ -4851,48 +4851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P66" t="str">
-        <v>SBIN0004158</v>
+        <v>SBIN0002421</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>0300003</v>
+        <v>0300080</v>
       </c>
       <c r="B67" t="str">
-        <v>NASREEN RAI</v>
+        <v>MAMTA ANSARI B</v>
       </c>
       <c r="C67" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D67" t="str">
-        <v>03003</v>
+        <v>03006</v>
       </c>
       <c r="E67" t="str">
-        <v>Primary School Dumri Katsari No.1</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F67" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G67" t="str">
-        <v>9003000003</v>
+        <v>9003000080</v>
       </c>
       <c r="H67" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I67" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J67" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K67" t="str">
         <v>0301</v>
       </c>
-      <c r="J67" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K67" t="str">
-        <v>0304</v>
-      </c>
       <c r="L67" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M67" t="str">
-        <v>30000023757</v>
+        <v>30000633520</v>
       </c>
       <c r="N67" t="str">
         <v>State Bank of India</v>
@@ -4901,48 +4901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P67" t="str">
-        <v>SBIN0008941</v>
+        <v>SBIN0004644</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>0300041</v>
+        <v>0300025</v>
       </c>
       <c r="B68" t="str">
-        <v>ABDUL KALAM RAI</v>
+        <v>FARHAT ANSARI</v>
       </c>
       <c r="C68" t="str">
         <v>Assistant Teacher</v>
       </c>
       <c r="D68" t="str">
-        <v>03005</v>
+        <v>03023</v>
       </c>
       <c r="E68" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>CDPO Office Dumri Katsari No.1</v>
       </c>
       <c r="F68" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G68" t="str">
-        <v>9003000041</v>
+        <v>9003000025</v>
       </c>
       <c r="H68" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I68" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J68" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K68" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L68" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M68" t="str">
-        <v>30000324679</v>
+        <v>30000197975</v>
       </c>
       <c r="N68" t="str">
         <v>State Bank of India</v>
@@ -4951,48 +4951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P68" t="str">
-        <v>SBIN0009719</v>
+        <v>SBIN0009826</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>0300102</v>
+        <v>0300121</v>
       </c>
       <c r="B69" t="str">
-        <v>SAVITA PANDEY</v>
+        <v>NIRMALA RAM</v>
       </c>
       <c r="C69" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D69" t="str">
-        <v>03077</v>
+        <v>03095</v>
       </c>
       <c r="E69" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>Punjab National Bank, Sheohar</v>
       </c>
       <c r="F69" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G69" t="str">
-        <v>9003000102</v>
+        <v>9003000121</v>
       </c>
       <c r="H69" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I69" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J69" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K69" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L69" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M69" t="str">
-        <v>30000807738</v>
+        <v>30000958199</v>
       </c>
       <c r="N69" t="str">
         <v>State Bank of India</v>
@@ -5001,48 +5001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P69" t="str">
-        <v>SBIN0007610</v>
+        <v>SBIN0004833</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>0300103</v>
+        <v>0300120</v>
       </c>
       <c r="B70" t="str">
-        <v>REKHA DEVI</v>
+        <v>MD. SHAHID YADAV</v>
       </c>
       <c r="C70" t="str">
-        <v>Revenue Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D70" t="str">
-        <v>03082</v>
+        <v>03095</v>
       </c>
       <c r="E70" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>Punjab National Bank, Sheohar</v>
       </c>
       <c r="F70" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G70" t="str">
-        <v>9003000103</v>
+        <v>9003000120</v>
       </c>
       <c r="H70" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I70" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J70" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K70" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L70" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M70" t="str">
-        <v>30000815657</v>
+        <v>30000950280</v>
       </c>
       <c r="N70" t="str">
         <v>State Bank of India</v>
@@ -5051,48 +5051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P70" t="str">
-        <v>SBIN0007608</v>
+        <v>SBIN0009688</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>0300086</v>
+        <v>0300021</v>
       </c>
       <c r="B71" t="str">
-        <v>RANJIT PASWAN</v>
+        <v>MD. SHAHID SHARMA</v>
       </c>
       <c r="C71" t="str">
         <v>Assistant Engineer</v>
       </c>
       <c r="D71" t="str">
-        <v>03049</v>
+        <v>03019</v>
       </c>
       <c r="E71" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>CDPO Office Sheohar</v>
       </c>
       <c r="F71" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G71" t="str">
-        <v>9003000086</v>
+        <v>9003000021</v>
       </c>
       <c r="H71" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I71" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="J71" t="str">
-        <v>Others</v>
+        <v>Tariyani</v>
       </c>
       <c r="K71" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L71" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M71" t="str">
-        <v>30000681034</v>
+        <v>30000166299</v>
       </c>
       <c r="N71" t="str">
         <v>State Bank of India</v>
@@ -5101,48 +5101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P71" t="str">
-        <v>SBIN0006823</v>
+        <v>SBIN0006272</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>0300012</v>
+        <v>0300093</v>
       </c>
       <c r="B72" t="str">
-        <v>SURESH RAM</v>
+        <v>ASHA ALAM</v>
       </c>
       <c r="C72" t="str">
-        <v>Headmaster</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D72" t="str">
-        <v>03012</v>
+        <v>03075</v>
       </c>
       <c r="E72" t="str">
-        <v>CDPO Office Piprahi No.1</v>
+        <v>Minor Irrigation Office Purnahiya</v>
       </c>
       <c r="F72" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G72" t="str">
-        <v>9003000012</v>
+        <v>9003000093</v>
       </c>
       <c r="H72" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I72" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J72" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K72" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L72" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M72" t="str">
-        <v>30000095028</v>
+        <v>30000736467</v>
       </c>
       <c r="N72" t="str">
         <v>State Bank of India</v>
@@ -5151,33 +5151,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P72" t="str">
-        <v>SBIN0003109</v>
+        <v>SBIN0001663</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>0300022</v>
+        <v>0300115</v>
       </c>
       <c r="B73" t="str">
-        <v>SURESH KUMAR</v>
+        <v>ANITA PRASAD</v>
       </c>
       <c r="C73" t="str">
-        <v>Senior Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D73" t="str">
-        <v>03006</v>
+        <v>03090</v>
       </c>
       <c r="E73" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>LIC Branch Office, Sheohar</v>
       </c>
       <c r="F73" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G73" t="str">
-        <v>9003000022</v>
+        <v>9003000115</v>
       </c>
       <c r="H73" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I73" t="str">
         <v>0305</v>
@@ -5192,7 +5192,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M73" t="str">
-        <v>30000174218</v>
+        <v>30000910685</v>
       </c>
       <c r="N73" t="str">
         <v>State Bank of India</v>
@@ -5201,48 +5201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P73" t="str">
-        <v>SBIN0006941</v>
+        <v>SBIN0004343</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>0300123</v>
+        <v>0300043</v>
       </c>
       <c r="B74" t="str">
-        <v>ANITA YADAV</v>
+        <v>NEHA SINGH</v>
       </c>
       <c r="C74" t="str">
-        <v>Branch Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D74" t="str">
-        <v>03096</v>
+        <v>03038</v>
       </c>
       <c r="E74" t="str">
-        <v>Central Bank of India, Sheohar</v>
+        <v>Middle School Piprahi No.3</v>
       </c>
       <c r="F74" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G74" t="str">
-        <v>9003000123</v>
+        <v>9003000043</v>
       </c>
       <c r="H74" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I74" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J74" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K74" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L74" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M74" t="str">
-        <v>30000974037</v>
+        <v>30000340517</v>
       </c>
       <c r="N74" t="str">
         <v>State Bank of India</v>
@@ -5251,48 +5251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P74" t="str">
-        <v>SBIN0005507</v>
+        <v>SBIN0001884</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>0300090</v>
+        <v>0300053</v>
       </c>
       <c r="B75" t="str">
-        <v>AJAY RAM</v>
+        <v>ASHA YADAV</v>
       </c>
       <c r="C75" t="str">
-        <v>Junior Engineer</v>
+        <v>Accountant</v>
       </c>
       <c r="D75" t="str">
-        <v>03072</v>
+        <v>03045</v>
       </c>
       <c r="E75" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>Block Education Office Tariyani No.1</v>
       </c>
       <c r="F75" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G75" t="str">
-        <v>9003000090</v>
+        <v>9003000053</v>
       </c>
       <c r="H75" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I75" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J75" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K75" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L75" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M75" t="str">
-        <v>30000712710</v>
+        <v>30000419707</v>
       </c>
       <c r="N75" t="str">
         <v>State Bank of India</v>
@@ -5301,48 +5301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P75" t="str">
-        <v>SBIN0005348</v>
+        <v>SBIN0002670</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>0300033</v>
+        <v>0300035</v>
       </c>
       <c r="B76" t="str">
-        <v>UMESH SHARMA</v>
+        <v>KIRAN OJHA</v>
       </c>
       <c r="C76" t="str">
-        <v>Assistant Teacher</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D76" t="str">
-        <v>03030</v>
+        <v>03032</v>
       </c>
       <c r="E76" t="str">
-        <v>Primary School Dumri Katsari</v>
+        <v>Middle School Piprahi No.4</v>
       </c>
       <c r="F76" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G76" t="str">
-        <v>9003000033</v>
+        <v>9003000035</v>
       </c>
       <c r="H76" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I76" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J76" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K76" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L76" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M76" t="str">
-        <v>30000261327</v>
+        <v>30000277165</v>
       </c>
       <c r="N76" t="str">
         <v>State Bank of India</v>
@@ -5351,48 +5351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P76" t="str">
-        <v>SBIN0008849</v>
+        <v>SBIN0008481</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>0300043</v>
+        <v>0300074</v>
       </c>
       <c r="B77" t="str">
-        <v>RINKU TIWARI</v>
+        <v>SHAILESH THAKUR</v>
       </c>
       <c r="C77" t="str">
-        <v>Clerk</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D77" t="str">
-        <v>03038</v>
+        <v>03063</v>
       </c>
       <c r="E77" t="str">
-        <v>High School Sheohar</v>
+        <v>Block Office Dumri Katsari</v>
       </c>
       <c r="F77" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G77" t="str">
-        <v>9003000043</v>
+        <v>9003000074</v>
       </c>
       <c r="H77" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I77" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J77" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K77" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L77" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M77" t="str">
-        <v>30000340517</v>
+        <v>30000586006</v>
       </c>
       <c r="N77" t="str">
         <v>State Bank of India</v>
@@ -5401,39 +5401,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P77" t="str">
-        <v>SBIN0007367</v>
+        <v>SBIN0008509</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>0300008</v>
+        <v>0300059</v>
       </c>
       <c r="B78" t="str">
-        <v>VINOD ALAM</v>
+        <v>NEHA PASWAN</v>
       </c>
       <c r="C78" t="str">
-        <v>Lecturer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D78" t="str">
-        <v>03008</v>
+        <v>03050</v>
       </c>
       <c r="E78" t="str">
-        <v>Kanya Middle School Tariyani No.1</v>
+        <v>Kanya Middle School Tariyani No.4</v>
       </c>
       <c r="F78" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G78" t="str">
-        <v>9003000008</v>
+        <v>9003000059</v>
       </c>
       <c r="H78" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I78" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="J78" t="str">
-        <v>Others</v>
+        <v>Tariyani</v>
       </c>
       <c r="K78" t="str">
         <v>0305</v>
@@ -5442,7 +5442,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M78" t="str">
-        <v>30000063352</v>
+        <v>30000467221</v>
       </c>
       <c r="N78" t="str">
         <v>State Bank of India</v>
@@ -5451,39 +5451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P78" t="str">
-        <v>SBIN0003276</v>
+        <v>SBIN0002797</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0300117</v>
+        <v>0300056</v>
       </c>
       <c r="B79" t="str">
-        <v>SURESH SINHA</v>
+        <v>SURESH KUMAR</v>
       </c>
       <c r="C79" t="str">
-        <v>Postmaster</v>
+        <v>Accountant</v>
       </c>
       <c r="D79" t="str">
-        <v>03088</v>
+        <v>03048</v>
       </c>
       <c r="E79" t="str">
-        <v>UCO Bank, Sheohar</v>
+        <v>District Treasury Sheohar</v>
       </c>
       <c r="F79" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G79" t="str">
-        <v>9003000117</v>
+        <v>9003000056</v>
       </c>
       <c r="H79" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I79" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J79" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K79" t="str">
         <v>0301</v>
@@ -5492,7 +5492,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M79" t="str">
-        <v>30000926523</v>
+        <v>30000443464</v>
       </c>
       <c r="N79" t="str">
         <v>State Bank of India</v>
@@ -5501,48 +5501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P79" t="str">
-        <v>SBIN0005736</v>
+        <v>SBIN0007260</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>0300094</v>
+        <v>0300034</v>
       </c>
       <c r="B80" t="str">
-        <v>ANIL RAI</v>
+        <v>NASREEN GUPTA</v>
       </c>
       <c r="C80" t="str">
-        <v>Junior Engineer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D80" t="str">
-        <v>03075</v>
+        <v>03031</v>
       </c>
       <c r="E80" t="str">
-        <v>Minor Irrigation Office Sheohar</v>
+        <v>Block Agriculture Office Piprahi No.1</v>
       </c>
       <c r="F80" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G80" t="str">
-        <v>9003000094</v>
+        <v>9003000034</v>
       </c>
       <c r="H80" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I80" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J80" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K80" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L80" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M80" t="str">
-        <v>30000744386</v>
+        <v>30000269246</v>
       </c>
       <c r="N80" t="str">
         <v>State Bank of India</v>
@@ -5551,39 +5551,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P80" t="str">
-        <v>SBIN0005339</v>
+        <v>SBIN0007880</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>0300016</v>
+        <v>0300064</v>
       </c>
       <c r="B81" t="str">
-        <v>ANIL PANDEY</v>
+        <v>ARVIND ANSARI</v>
       </c>
       <c r="C81" t="str">
-        <v>Section Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D81" t="str">
-        <v>03016</v>
+        <v>03054</v>
       </c>
       <c r="E81" t="str">
-        <v>Block Office Purnahiya No.3</v>
+        <v>Panchayat Bhawan Purnahiya No.4</v>
       </c>
       <c r="F81" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G81" t="str">
-        <v>9003000016</v>
+        <v>9003000064</v>
       </c>
       <c r="H81" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I81" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J81" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K81" t="str">
         <v>0303</v>
@@ -5592,7 +5592,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M81" t="str">
-        <v>30000126704</v>
+        <v>30000506816</v>
       </c>
       <c r="N81" t="str">
         <v>State Bank of India</v>
@@ -5601,33 +5601,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P81" t="str">
-        <v>SBIN0009715</v>
+        <v>SBIN0007855</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>0300060</v>
+        <v>0300083</v>
       </c>
       <c r="B82" t="str">
-        <v>MAMTA CHAUDHARY</v>
+        <v>RAKESH TIWARI</v>
       </c>
       <c r="C82" t="str">
-        <v>Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D82" t="str">
-        <v>03019</v>
+        <v>03068</v>
       </c>
       <c r="E82" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Middle School Piprahi</v>
       </c>
       <c r="F82" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G82" t="str">
-        <v>9003000060</v>
+        <v>9003000083</v>
       </c>
       <c r="H82" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I82" t="str">
         <v>0301</v>
@@ -5636,13 +5636,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K82" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L82" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M82" t="str">
-        <v>30000475140</v>
+        <v>30000657277</v>
       </c>
       <c r="N82" t="str">
         <v>State Bank of India</v>
@@ -5651,48 +5651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P82" t="str">
-        <v>SBIN0005919</v>
+        <v>SBIN0001974</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>0300098</v>
+        <v>0300107</v>
       </c>
       <c r="B83" t="str">
-        <v>RAKESH RAM</v>
+        <v>ABDUL KALAM KUMAR</v>
       </c>
       <c r="C83" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D83" t="str">
-        <v>03079</v>
+        <v>03084</v>
       </c>
       <c r="E83" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>UCO Bank, Piprahi</v>
       </c>
       <c r="F83" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G83" t="str">
-        <v>9003000098</v>
+        <v>9003000107</v>
       </c>
       <c r="H83" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I83" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J83" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K83" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L83" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M83" t="str">
-        <v>30000776062</v>
+        <v>30000847333</v>
       </c>
       <c r="N83" t="str">
         <v>State Bank of India</v>
@@ -5701,33 +5701,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P83" t="str">
-        <v>SBIN0003941</v>
+        <v>SBIN0008073</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>0300032</v>
+        <v>0300124</v>
       </c>
       <c r="B84" t="str">
-        <v>RINKU SINGH B</v>
+        <v>ASHA MAHTO</v>
       </c>
       <c r="C84" t="str">
-        <v>Assistant Teacher</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D84" t="str">
-        <v>03029</v>
+        <v>03089</v>
       </c>
       <c r="E84" t="str">
-        <v>Block Office Piprahi No.4</v>
+        <v>State Bank of India, Sheohar</v>
       </c>
       <c r="F84" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G84" t="str">
-        <v>9003000032</v>
+        <v>9003000124</v>
       </c>
       <c r="H84" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I84" t="str">
         <v>0302</v>
@@ -5736,13 +5736,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K84" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L84" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M84" t="str">
-        <v>30000253408</v>
+        <v>30000981956</v>
       </c>
       <c r="N84" t="str">
         <v>State Bank of India</v>
@@ -5751,48 +5751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P84" t="str">
-        <v>SBIN0006216</v>
+        <v>SBIN0004264</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>0300013</v>
+        <v>0300071</v>
       </c>
       <c r="B85" t="str">
-        <v>PRAMOD VERMA</v>
+        <v>VIJAY SHARMA</v>
       </c>
       <c r="C85" t="str">
-        <v>Lecturer</v>
+        <v>Clerk</v>
       </c>
       <c r="D85" t="str">
-        <v>03013</v>
+        <v>03061</v>
       </c>
       <c r="E85" t="str">
-        <v>High School Dumri Katsari No.2</v>
+        <v>District Welfare Office (deputed from other district)</v>
       </c>
       <c r="F85" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G85" t="str">
-        <v>9003000013</v>
+        <v>9003000071</v>
       </c>
       <c r="H85" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I85" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J85" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K85" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="L85" t="str">
-        <v>Dumri Katsari</v>
+        <v>Other District</v>
       </c>
       <c r="M85" t="str">
-        <v>30000102947</v>
+        <v>30000562249</v>
       </c>
       <c r="N85" t="str">
         <v>State Bank of India</v>
@@ -5801,48 +5801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P85" t="str">
-        <v>SBIN0003055</v>
+        <v>SBIN0006567</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>0300014</v>
+        <v>0300126</v>
       </c>
       <c r="B86" t="str">
-        <v>ALOK YADAV</v>
+        <v>NASREEN THAKUR</v>
       </c>
       <c r="C86" t="str">
-        <v>Senior Teacher</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D86" t="str">
-        <v>03014</v>
+        <v>03090</v>
       </c>
       <c r="E86" t="str">
-        <v>Block Agriculture Office Purnahiya No.3</v>
+        <v>LIC Branch Office, Sheohar</v>
       </c>
       <c r="F86" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G86" t="str">
-        <v>9003000014</v>
+        <v>9003000126</v>
       </c>
       <c r="H86" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I86" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J86" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K86" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L86" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M86" t="str">
-        <v>30000110866</v>
+        <v>30000997794</v>
       </c>
       <c r="N86" t="str">
         <v>State Bank of India</v>
@@ -5851,48 +5851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P86" t="str">
-        <v>SBIN0001319</v>
+        <v>SBIN0002756</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>0300030</v>
+        <v>0300109</v>
       </c>
       <c r="B87" t="str">
-        <v>SHAILESH OJHA</v>
+        <v>DINESH MAHTO</v>
       </c>
       <c r="C87" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D87" t="str">
-        <v>03028</v>
+        <v>03085</v>
       </c>
       <c r="E87" t="str">
-        <v>Middle School Sheohar</v>
+        <v>Bank of India, Dumri Katsari</v>
       </c>
       <c r="F87" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G87" t="str">
-        <v>9003000030</v>
+        <v>9003000109</v>
       </c>
       <c r="H87" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I87" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J87" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K87" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L87" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M87" t="str">
-        <v>30000237570</v>
+        <v>30000863171</v>
       </c>
       <c r="N87" t="str">
         <v>State Bank of India</v>
@@ -5901,48 +5901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P87" t="str">
-        <v>SBIN0005689</v>
+        <v>SBIN0006916</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>0300036</v>
+        <v>0300119</v>
       </c>
       <c r="B88" t="str">
-        <v>NEHA MAHTO</v>
+        <v>RAKESH KUMAR</v>
       </c>
       <c r="C88" t="str">
-        <v>Assistant Teacher</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D88" t="str">
-        <v>03032</v>
+        <v>03094</v>
       </c>
       <c r="E88" t="str">
-        <v>Block Education Office Piprahi No.4</v>
+        <v>LIC Branch Office, Tariyani</v>
       </c>
       <c r="F88" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G88" t="str">
-        <v>9003000036</v>
+        <v>9003000119</v>
       </c>
       <c r="H88" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I88" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J88" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K88" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L88" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M88" t="str">
-        <v>30000285084</v>
+        <v>30000942361</v>
       </c>
       <c r="N88" t="str">
         <v>State Bank of India</v>
@@ -5951,48 +5951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P88" t="str">
-        <v>SBIN0007040</v>
+        <v>SBIN0005556</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>0300082</v>
+        <v>0300026</v>
       </c>
       <c r="B89" t="str">
-        <v>VIJAY OJHA</v>
+        <v>SAVITA KHATUN</v>
       </c>
       <c r="C89" t="str">
-        <v>Office Assistant</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D89" t="str">
-        <v>03067</v>
+        <v>03024</v>
       </c>
       <c r="E89" t="str">
-        <v>Middle School Piprahi No.4</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F89" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G89" t="str">
-        <v>9003000082</v>
+        <v>9003000026</v>
       </c>
       <c r="H89" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I89" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J89" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K89" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L89" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M89" t="str">
-        <v>30000649358</v>
+        <v>30000205894</v>
       </c>
       <c r="N89" t="str">
         <v>State Bank of India</v>
@@ -6001,48 +6001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P89" t="str">
-        <v>SBIN0005974</v>
+        <v>SBIN0008930</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>0300091</v>
+        <v>0300055</v>
       </c>
       <c r="B90" t="str">
-        <v>SHAILESH MISHRA P</v>
+        <v>SANJAY TIWARI M</v>
       </c>
       <c r="C90" t="str">
-        <v>Revenue Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D90" t="str">
-        <v>03049</v>
+        <v>03047</v>
       </c>
       <c r="E90" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>CDPO Office Purnahiya</v>
       </c>
       <c r="F90" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G90" t="str">
-        <v>9003000091</v>
+        <v>9003000055</v>
       </c>
       <c r="H90" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I90" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J90" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K90" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L90" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M90" t="str">
-        <v>30000720629</v>
+        <v>30000435545</v>
       </c>
       <c r="N90" t="str">
         <v>State Bank of India</v>
@@ -6051,48 +6051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P90" t="str">
-        <v>SBIN0007378</v>
+        <v>SBIN0002142</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>0300080</v>
+        <v>0300087</v>
       </c>
       <c r="B91" t="str">
-        <v>VIJAY RAI</v>
+        <v>NIRMALA RAI</v>
       </c>
       <c r="C91" t="str">
-        <v>Clerk</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D91" t="str">
-        <v>03065</v>
+        <v>03024</v>
       </c>
       <c r="E91" t="str">
-        <v>High School Tariyani No.4</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F91" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G91" t="str">
-        <v>9003000080</v>
+        <v>9003000087</v>
       </c>
       <c r="H91" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I91" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J91" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K91" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L91" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M91" t="str">
-        <v>30000633520</v>
+        <v>30000688953</v>
       </c>
       <c r="N91" t="str">
         <v>State Bank of India</v>
@@ -6101,48 +6101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P91" t="str">
-        <v>SBIN0002487</v>
+        <v>SBIN0004429</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>0300047</v>
+        <v>0300052</v>
       </c>
       <c r="B92" t="str">
-        <v>MANOJ MISHRA</v>
+        <v>MD. SHAHID THAKUR</v>
       </c>
       <c r="C92" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Accountant</v>
       </c>
       <c r="D92" t="str">
-        <v>03005</v>
+        <v>03044</v>
       </c>
       <c r="E92" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>Panchayat Bhawan Tariyani No.4</v>
       </c>
       <c r="F92" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G92" t="str">
-        <v>9003000047</v>
+        <v>9003000052</v>
       </c>
       <c r="H92" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I92" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J92" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K92" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L92" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M92" t="str">
-        <v>30000372193</v>
+        <v>30000411788</v>
       </c>
       <c r="N92" t="str">
         <v>State Bank of India</v>
@@ -6151,48 +6151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P92" t="str">
-        <v>SBIN0006548</v>
+        <v>SBIN0004816</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>0300006</v>
+        <v>0300125</v>
       </c>
       <c r="B93" t="str">
-        <v>REKHA OJHA</v>
+        <v>SAVITA RAI</v>
       </c>
       <c r="C93" t="str">
-        <v>Headmaster</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D93" t="str">
-        <v>03006</v>
+        <v>03097</v>
       </c>
       <c r="E93" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Head Post Office, Piprahi</v>
       </c>
       <c r="F93" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G93" t="str">
-        <v>9003000006</v>
+        <v>9003000125</v>
       </c>
       <c r="H93" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I93" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J93" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K93" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L93" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M93" t="str">
-        <v>30000047514</v>
+        <v>30000989875</v>
       </c>
       <c r="N93" t="str">
         <v>State Bank of India</v>
@@ -6201,48 +6201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P93" t="str">
-        <v>SBIN0001521</v>
+        <v>SBIN0003720</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>0300078</v>
+        <v>0300038</v>
       </c>
       <c r="B94" t="str">
-        <v>RANJIT JHA</v>
+        <v>RAVI SINGH</v>
       </c>
       <c r="C94" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D94" t="str">
-        <v>03006</v>
+        <v>03034</v>
       </c>
       <c r="E94" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Block Education Office Tariyani No.4</v>
       </c>
       <c r="F94" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G94" t="str">
-        <v>9003000078</v>
+        <v>9003000038</v>
       </c>
       <c r="H94" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I94" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J94" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K94" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L94" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M94" t="str">
-        <v>30000617682</v>
+        <v>30000300922</v>
       </c>
       <c r="N94" t="str">
         <v>State Bank of India</v>
@@ -6251,48 +6251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P94" t="str">
-        <v>SBIN0009926</v>
+        <v>SBIN0005246</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>0300037</v>
+        <v>0300004</v>
       </c>
       <c r="B95" t="str">
-        <v>USHA DEVI</v>
+        <v>SANTOSH JHA</v>
       </c>
       <c r="C95" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Lecturer</v>
       </c>
       <c r="D95" t="str">
-        <v>03033</v>
+        <v>03004</v>
       </c>
       <c r="E95" t="str">
-        <v>Panchayat Bhawan Sheohar No.3</v>
+        <v>Block Office Piprahi No.3</v>
       </c>
       <c r="F95" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G95" t="str">
-        <v>9003000037</v>
+        <v>9003000004</v>
       </c>
       <c r="H95" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I95" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J95" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K95" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L95" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M95" t="str">
-        <v>30000293003</v>
+        <v>30000031676</v>
       </c>
       <c r="N95" t="str">
         <v>State Bank of India</v>
@@ -6301,48 +6301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P95" t="str">
-        <v>SBIN0006396</v>
+        <v>SBIN0002119</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>0300085</v>
+        <v>0300002</v>
       </c>
       <c r="B96" t="str">
-        <v>MAHESH SINGH</v>
+        <v>REKHA RAM</v>
       </c>
       <c r="C96" t="str">
-        <v>Assistant Engineer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D96" t="str">
-        <v>03005</v>
+        <v>03002</v>
       </c>
       <c r="E96" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>Block Agriculture Office Tariyani No.3</v>
       </c>
       <c r="F96" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G96" t="str">
-        <v>9003000085</v>
+        <v>9003000002</v>
       </c>
       <c r="H96" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I96" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J96" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K96" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L96" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M96" t="str">
-        <v>30000673115</v>
+        <v>30000015838</v>
       </c>
       <c r="N96" t="str">
         <v>State Bank of India</v>
@@ -6351,48 +6351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P96" t="str">
-        <v>SBIN0005101</v>
+        <v>SBIN0003954</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0300025</v>
+        <v>0300123</v>
       </c>
       <c r="B97" t="str">
-        <v>ABDUL KALAM SINGH</v>
+        <v>RINKU DEVI</v>
       </c>
       <c r="C97" t="str">
-        <v>Assistant Teacher</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D97" t="str">
-        <v>03023</v>
+        <v>03094</v>
       </c>
       <c r="E97" t="str">
-        <v>Middle School Piprahi No.3</v>
+        <v>LIC Branch Office, Tariyani</v>
       </c>
       <c r="F97" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G97" t="str">
-        <v>9003000025</v>
+        <v>9003000123</v>
       </c>
       <c r="H97" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I97" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="J97" t="str">
-        <v>Others</v>
+        <v>Tariyani</v>
       </c>
       <c r="K97" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L97" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M97" t="str">
-        <v>30000197975</v>
+        <v>30000974037</v>
       </c>
       <c r="N97" t="str">
         <v>State Bank of India</v>
@@ -6401,48 +6401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P97" t="str">
-        <v>SBIN0006498</v>
+        <v>SBIN0001025</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>0300107</v>
+        <v>0300057</v>
       </c>
       <c r="B98" t="str">
-        <v>DEEPAK SINGH</v>
+        <v>MANOJ SINGH</v>
       </c>
       <c r="C98" t="str">
-        <v>Postmaster</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D98" t="str">
-        <v>03084</v>
+        <v>03049</v>
       </c>
       <c r="E98" t="str">
-        <v>Punjab National Bank, Tariyani</v>
+        <v>Block Agriculture Office Purnahiya No.4</v>
       </c>
       <c r="F98" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G98" t="str">
-        <v>9003000107</v>
+        <v>9003000057</v>
       </c>
       <c r="H98" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I98" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J98" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K98" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L98" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M98" t="str">
-        <v>30000847333</v>
+        <v>30000451383</v>
       </c>
       <c r="N98" t="str">
         <v>State Bank of India</v>
@@ -6451,39 +6451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P98" t="str">
-        <v>SBIN0004325</v>
+        <v>SBIN0004762</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>0300074</v>
+        <v>0300032</v>
       </c>
       <c r="B99" t="str">
-        <v>MUKESH PANDEY</v>
+        <v>KIRAN MISHRA</v>
       </c>
       <c r="C99" t="str">
-        <v>Clerk</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D99" t="str">
-        <v>03019</v>
+        <v>03029</v>
       </c>
       <c r="E99" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Panchayat Bhawan Sheohar No.1</v>
       </c>
       <c r="F99" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G99" t="str">
-        <v>9003000074</v>
+        <v>9003000032</v>
       </c>
       <c r="H99" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I99" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J99" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K99" t="str">
         <v>0301</v>
@@ -6492,7 +6492,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M99" t="str">
-        <v>30000586006</v>
+        <v>30000253408</v>
       </c>
       <c r="N99" t="str">
         <v>State Bank of India</v>
@@ -6501,48 +6501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P99" t="str">
-        <v>SBIN0004743</v>
+        <v>SBIN0006111</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>0300023</v>
+        <v>0300006</v>
       </c>
       <c r="B100" t="str">
-        <v>RAJESH MAHTO</v>
+        <v>AJAY KHATUN</v>
       </c>
       <c r="C100" t="str">
-        <v>Head Clerk</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D100" t="str">
-        <v>03021</v>
+        <v>03006</v>
       </c>
       <c r="E100" t="str">
-        <v>Project Girls High School Dumri Katsari</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F100" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G100" t="str">
-        <v>9003000023</v>
+        <v>9003000006</v>
       </c>
       <c r="H100" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I100" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J100" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K100" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L100" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M100" t="str">
-        <v>30000182137</v>
+        <v>30000047514</v>
       </c>
       <c r="N100" t="str">
         <v>State Bank of India</v>
@@ -6551,48 +6551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P100" t="str">
-        <v>SBIN0007425</v>
+        <v>SBIN0006535</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>0300089</v>
+        <v>0300069</v>
       </c>
       <c r="B101" t="str">
-        <v>SHAILESH MISHRA</v>
+        <v>PRIYANKA VERMA</v>
       </c>
       <c r="C101" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D101" t="str">
-        <v>03071</v>
+        <v>03059</v>
       </c>
       <c r="E101" t="str">
-        <v>Minor Irrigation Office Purnahiya</v>
+        <v>Project Girls High School Piprahi</v>
       </c>
       <c r="F101" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G101" t="str">
-        <v>9003000089</v>
+        <v>9003000069</v>
       </c>
       <c r="H101" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I101" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J101" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K101" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L101" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M101" t="str">
-        <v>30000704791</v>
+        <v>30000546411</v>
       </c>
       <c r="N101" t="str">
         <v>State Bank of India</v>
@@ -6601,48 +6601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P101" t="str">
-        <v>SBIN0008271</v>
+        <v>SBIN0009268</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>0300101</v>
+        <v>0300116</v>
       </c>
       <c r="B102" t="str">
-        <v>DINESH ALAM</v>
+        <v>VIJAY KUMAR</v>
       </c>
       <c r="C102" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D102" t="str">
-        <v>03081</v>
+        <v>03091</v>
       </c>
       <c r="E102" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>BSNL Exchange, Dumri Katsari</v>
       </c>
       <c r="F102" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G102" t="str">
-        <v>9003000101</v>
+        <v>9003000116</v>
       </c>
       <c r="H102" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I102" t="str">
+        <v>999999</v>
+      </c>
+      <c r="J102" t="str">
+        <v>Others</v>
+      </c>
+      <c r="K102" t="str">
         <v>0304</v>
       </c>
-      <c r="J102" t="str">
+      <c r="L102" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="K102" t="str">
-        <v>0302</v>
-      </c>
-      <c r="L102" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="M102" t="str">
-        <v>30000799819</v>
+        <v>30000918604</v>
       </c>
       <c r="N102" t="str">
         <v>State Bank of India</v>
@@ -6651,33 +6651,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P102" t="str">
-        <v>SBIN0005381</v>
+        <v>SBIN0007763</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>0300049</v>
+        <v>0300088</v>
       </c>
       <c r="B103" t="str">
-        <v>ANIL SINGH</v>
+        <v>RINKU OJHA</v>
       </c>
       <c r="C103" t="str">
-        <v>Accountant</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D103" t="str">
-        <v>03042</v>
+        <v>03071</v>
       </c>
       <c r="E103" t="str">
-        <v>Block Office Dumri Katsari No.1</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="F103" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G103" t="str">
-        <v>9003000049</v>
+        <v>9003000088</v>
       </c>
       <c r="H103" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I103" t="str">
         <v>0302</v>
@@ -6686,13 +6686,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K103" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L103" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M103" t="str">
-        <v>30000388031</v>
+        <v>30000696872</v>
       </c>
       <c r="N103" t="str">
         <v>State Bank of India</v>
@@ -6701,33 +6701,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P103" t="str">
-        <v>SBIN0007320</v>
+        <v>SBIN0003089</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>0300026</v>
+        <v>0300047</v>
       </c>
       <c r="B104" t="str">
-        <v>SAVITA SINHA</v>
+        <v>SURESH CHAUDHARY E</v>
       </c>
       <c r="C104" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Teacher</v>
       </c>
       <c r="D104" t="str">
-        <v>03024</v>
+        <v>03010</v>
       </c>
       <c r="E104" t="str">
-        <v>Kanya Middle School Dumri Katsari No.4</v>
+        <v>Block Office Sheohar No.1</v>
       </c>
       <c r="F104" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G104" t="str">
-        <v>9003000026</v>
+        <v>9003000047</v>
       </c>
       <c r="H104" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I104" t="str">
         <v>0303</v>
@@ -6736,13 +6736,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K104" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L104" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M104" t="str">
-        <v>30000205894</v>
+        <v>30000372193</v>
       </c>
       <c r="N104" t="str">
         <v>State Bank of India</v>
@@ -6751,48 +6751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P104" t="str">
-        <v>SBIN0008622</v>
+        <v>SBIN0008239</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>0300113</v>
+        <v>0300117</v>
       </c>
       <c r="B105" t="str">
-        <v>SUNITA PASWAN</v>
+        <v>ASHA ALAM T</v>
       </c>
       <c r="C105" t="str">
-        <v>Branch Manager</v>
+        <v>Postmaster</v>
       </c>
       <c r="D105" t="str">
-        <v>03089</v>
+        <v>03092</v>
       </c>
       <c r="E105" t="str">
-        <v>LIC Branch Office, Tariyani</v>
+        <v>Head Post Office, Dumri Katsari</v>
       </c>
       <c r="F105" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G105" t="str">
-        <v>9003000113</v>
+        <v>9003000117</v>
       </c>
       <c r="H105" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I105" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J105" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K105" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L105" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M105" t="str">
-        <v>30000894847</v>
+        <v>30000926523</v>
       </c>
       <c r="N105" t="str">
         <v>State Bank of India</v>
@@ -6801,48 +6801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P105" t="str">
-        <v>SBIN0003641</v>
+        <v>SBIN0008359</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>0300004</v>
+        <v>0300094</v>
       </c>
       <c r="B106" t="str">
-        <v>SHAILESH RAI</v>
+        <v>SAVITA KUMAR</v>
       </c>
       <c r="C106" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D106" t="str">
-        <v>03004</v>
+        <v>03072</v>
       </c>
       <c r="E106" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="F106" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G106" t="str">
-        <v>9003000004</v>
+        <v>9003000094</v>
       </c>
       <c r="H106" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I106" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J106" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K106" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L106" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M106" t="str">
-        <v>30000031676</v>
+        <v>30000744386</v>
       </c>
       <c r="N106" t="str">
         <v>State Bank of India</v>
@@ -6851,48 +6851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P106" t="str">
-        <v>SBIN0006357</v>
+        <v>SBIN0005397</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>0300077</v>
+        <v>0300019</v>
       </c>
       <c r="B107" t="str">
-        <v>RAKESH MAHTO</v>
+        <v>SANJAY PRASAD</v>
       </c>
       <c r="C107" t="str">
-        <v>Teacher</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D107" t="str">
-        <v>03063</v>
+        <v>03017</v>
       </c>
       <c r="E107" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>Block Agriculture Office Sheohar No.1</v>
       </c>
       <c r="F107" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G107" t="str">
-        <v>9003000077</v>
+        <v>9003000019</v>
       </c>
       <c r="H107" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I107" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J107" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K107" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L107" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M107" t="str">
-        <v>30000609763</v>
+        <v>30000150461</v>
       </c>
       <c r="N107" t="str">
         <v>State Bank of India</v>
@@ -6901,48 +6901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P107" t="str">
-        <v>SBIN0006008</v>
+        <v>SBIN0005701</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>0300076</v>
+        <v>0300081</v>
       </c>
       <c r="B108" t="str">
-        <v>KUMARI ANJALI OJHA</v>
+        <v>ANITA ANSARI</v>
       </c>
       <c r="C108" t="str">
-        <v>Office Assistant</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D108" t="str">
-        <v>03062</v>
+        <v>03066</v>
       </c>
       <c r="E108" t="str">
-        <v>Primary School Piprahi No.3</v>
+        <v>High School Tariyani No.4</v>
       </c>
       <c r="F108" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G108" t="str">
-        <v>9003000076</v>
+        <v>9003000081</v>
       </c>
       <c r="H108" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I108" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J108" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K108" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L108" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M108" t="str">
-        <v>30000601844</v>
+        <v>30000641439</v>
       </c>
       <c r="N108" t="str">
         <v>State Bank of India</v>
@@ -6951,33 +6951,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P108" t="str">
-        <v>SBIN0006145</v>
+        <v>SBIN0005245</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>0300017</v>
+        <v>0300024</v>
       </c>
       <c r="B109" t="str">
-        <v>SUNIL JHA</v>
+        <v>PRAMOD SINHA</v>
       </c>
       <c r="C109" t="str">
-        <v>Assistant Engineer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D109" t="str">
-        <v>03017</v>
+        <v>03022</v>
       </c>
       <c r="E109" t="str">
-        <v>Kanya Middle School Tariyani No.2</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F109" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G109" t="str">
-        <v>9003000017</v>
+        <v>9003000024</v>
       </c>
       <c r="H109" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I109" t="str">
         <v>0303</v>
@@ -6986,13 +6986,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K109" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L109" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M109" t="str">
-        <v>30000134623</v>
+        <v>30000190056</v>
       </c>
       <c r="N109" t="str">
         <v>State Bank of India</v>
@@ -7001,48 +7001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P109" t="str">
-        <v>SBIN0008419</v>
+        <v>SBIN0007218</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>0300001</v>
+        <v>0300101</v>
       </c>
       <c r="B110" t="str">
-        <v>ALOK TIWARI</v>
+        <v>MD. IRFAN CHAUDHARY</v>
       </c>
       <c r="C110" t="str">
-        <v>Section Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D110" t="str">
-        <v>03001</v>
+        <v>03074</v>
       </c>
       <c r="E110" t="str">
-        <v>Panchayat Bhawan Piprahi No.4</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="F110" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G110" t="str">
-        <v>9003000001</v>
+        <v>9003000101</v>
       </c>
       <c r="H110" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I110" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J110" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K110" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L110" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M110" t="str">
-        <v>30000007919</v>
+        <v>30000799819</v>
       </c>
       <c r="N110" t="str">
         <v>State Bank of India</v>
@@ -7051,48 +7051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P110" t="str">
-        <v>SBIN0003170</v>
+        <v>SBIN0003386</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>0300045</v>
+        <v>0300090</v>
       </c>
       <c r="B111" t="str">
-        <v>MAHESH RAM</v>
+        <v>ANITA ANSARI Y</v>
       </c>
       <c r="C111" t="str">
-        <v>Accountant</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D111" t="str">
-        <v>03039</v>
+        <v>03073</v>
       </c>
       <c r="E111" t="str">
-        <v>Block Education Office Tariyani No.4</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="F111" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G111" t="str">
-        <v>9003000045</v>
+        <v>9003000090</v>
       </c>
       <c r="H111" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I111" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J111" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K111" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L111" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M111" t="str">
-        <v>30000356355</v>
+        <v>30000712710</v>
       </c>
       <c r="N111" t="str">
         <v>State Bank of India</v>
@@ -7101,48 +7101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P111" t="str">
-        <v>SBIN0003791</v>
+        <v>SBIN0005629</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>0300081</v>
+        <v>0300029</v>
       </c>
       <c r="B112" t="str">
-        <v>FARHAT RAI</v>
+        <v>SURESH KHATUN</v>
       </c>
       <c r="C112" t="str">
-        <v>Data Entry Operator</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D112" t="str">
-        <v>03066</v>
+        <v>03026</v>
       </c>
       <c r="E112" t="str">
-        <v>PHC Purnahiya</v>
+        <v>Block Agriculture Office Dumri Katsari No.2</v>
       </c>
       <c r="F112" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G112" t="str">
-        <v>9003000081</v>
+        <v>9003000029</v>
       </c>
       <c r="H112" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I112" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J112" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K112" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L112" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M112" t="str">
-        <v>30000641439</v>
+        <v>30000229651</v>
       </c>
       <c r="N112" t="str">
         <v>State Bank of India</v>
@@ -7151,48 +7151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P112" t="str">
-        <v>SBIN0007534</v>
+        <v>SBIN0002957</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>0300119</v>
+        <v>0300079</v>
       </c>
       <c r="B113" t="str">
-        <v>ANIL RAI V</v>
+        <v>DEEPAK SINHA</v>
       </c>
       <c r="C113" t="str">
-        <v>Administrative Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D113" t="str">
-        <v>03083</v>
+        <v>03059</v>
       </c>
       <c r="E113" t="str">
-        <v>UCO Bank, Tariyani</v>
+        <v>Project Girls High School Piprahi</v>
       </c>
       <c r="F113" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G113" t="str">
-        <v>9003000119</v>
+        <v>9003000079</v>
       </c>
       <c r="H113" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I113" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J113" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K113" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L113" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M113" t="str">
-        <v>30000942361</v>
+        <v>30000625601</v>
       </c>
       <c r="N113" t="str">
         <v>State Bank of India</v>
@@ -7201,39 +7201,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P113" t="str">
-        <v>SBIN0003366</v>
+        <v>SBIN0008838</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>0300118</v>
+        <v>0300092</v>
       </c>
       <c r="B114" t="str">
-        <v>SANTOSH SINGH</v>
+        <v>POONAM PANDEY</v>
       </c>
       <c r="C114" t="str">
-        <v>Postmaster</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D114" t="str">
-        <v>03093</v>
+        <v>03074</v>
       </c>
       <c r="E114" t="str">
-        <v>Bank of India, Tariyani</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="F114" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G114" t="str">
-        <v>9003000118</v>
+        <v>9003000092</v>
       </c>
       <c r="H114" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I114" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J114" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K114" t="str">
         <v>0305</v>
@@ -7242,7 +7242,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M114" t="str">
-        <v>30000934442</v>
+        <v>30000728548</v>
       </c>
       <c r="N114" t="str">
         <v>State Bank of India</v>
@@ -7251,48 +7251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P114" t="str">
-        <v>SBIN0007771</v>
+        <v>SBIN0005527</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>0300059</v>
+        <v>0300009</v>
       </c>
       <c r="B115" t="str">
-        <v>RINKU RAM</v>
+        <v>DEEPAK KUMAR</v>
       </c>
       <c r="C115" t="str">
-        <v>Clerk</v>
+        <v>Section Officer</v>
       </c>
       <c r="D115" t="str">
-        <v>03051</v>
+        <v>03009</v>
       </c>
       <c r="E115" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>High School Dumri Katsari No.1</v>
       </c>
       <c r="F115" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G115" t="str">
-        <v>9003000059</v>
+        <v>9003000009</v>
       </c>
       <c r="H115" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I115" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J115" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K115" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L115" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M115" t="str">
-        <v>30000467221</v>
+        <v>30000071271</v>
       </c>
       <c r="N115" t="str">
         <v>State Bank of India</v>
@@ -7301,39 +7301,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P115" t="str">
-        <v>SBIN0002467</v>
+        <v>SBIN0001643</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>0300075</v>
+        <v>0300013</v>
       </c>
       <c r="B116" t="str">
-        <v>FARHAT GUPTA</v>
+        <v>ARVIND KHATUN</v>
       </c>
       <c r="C116" t="str">
-        <v>Office Assistant</v>
+        <v>Headmaster</v>
       </c>
       <c r="D116" t="str">
-        <v>03061</v>
+        <v>03012</v>
       </c>
       <c r="E116" t="str">
-        <v>Primary School Tariyani</v>
+        <v>PHC Tariyani No.3</v>
       </c>
       <c r="F116" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G116" t="str">
-        <v>9003000075</v>
+        <v>9003000013</v>
       </c>
       <c r="H116" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I116" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J116" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K116" t="str">
         <v>0305</v>
@@ -7342,7 +7342,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M116" t="str">
-        <v>30000593925</v>
+        <v>30000102947</v>
       </c>
       <c r="N116" t="str">
         <v>State Bank of India</v>
@@ -7351,33 +7351,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P116" t="str">
-        <v>SBIN0004103</v>
+        <v>SBIN0007505</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>0300087</v>
+        <v>0300076</v>
       </c>
       <c r="B117" t="str">
-        <v>MANOJ ANSARI</v>
+        <v>ASHA KUMAR</v>
       </c>
       <c r="C117" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D117" t="str">
-        <v>03060</v>
+        <v>03064</v>
       </c>
       <c r="E117" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>CDPO Office Tariyani</v>
       </c>
       <c r="F117" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G117" t="str">
-        <v>9003000087</v>
+        <v>9003000076</v>
       </c>
       <c r="H117" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I117" t="str">
         <v>0305</v>
@@ -7392,7 +7392,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M117" t="str">
-        <v>30000688953</v>
+        <v>30000601844</v>
       </c>
       <c r="N117" t="str">
         <v>State Bank of India</v>
@@ -7401,48 +7401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P117" t="str">
-        <v>SBIN0003473</v>
+        <v>SBIN0004817</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>0300084</v>
+        <v>0300050</v>
       </c>
       <c r="B118" t="str">
-        <v>SANJAY KUMAR</v>
+        <v>SUNIL PRASAD</v>
       </c>
       <c r="C118" t="str">
-        <v>Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D118" t="str">
-        <v>03069</v>
+        <v>03042</v>
       </c>
       <c r="E118" t="str">
-        <v>Block Agriculture Office Sheohar No.3</v>
+        <v>PHC Purnahiya No.1</v>
       </c>
       <c r="F118" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G118" t="str">
-        <v>9003000084</v>
+        <v>9003000050</v>
       </c>
       <c r="H118" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I118" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J118" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K118" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L118" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M118" t="str">
-        <v>30000665196</v>
+        <v>30000395950</v>
       </c>
       <c r="N118" t="str">
         <v>State Bank of India</v>
@@ -7451,48 +7451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P118" t="str">
-        <v>SBIN0005289</v>
+        <v>SBIN0004956</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>0300038</v>
+        <v>0300007</v>
       </c>
       <c r="B119" t="str">
-        <v>MANOJ SINGH</v>
+        <v>SANJAY TIWARI</v>
       </c>
       <c r="C119" t="str">
-        <v>Senior Clerk</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D119" t="str">
-        <v>03034</v>
+        <v>03007</v>
       </c>
       <c r="E119" t="str">
-        <v>CDPO Office Purnahiya</v>
+        <v>CDPO Office Piprahi No.2</v>
       </c>
       <c r="F119" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G119" t="str">
-        <v>9003000038</v>
+        <v>9003000007</v>
       </c>
       <c r="H119" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I119" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J119" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K119" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L119" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M119" t="str">
-        <v>30000300922</v>
+        <v>30000055433</v>
       </c>
       <c r="N119" t="str">
         <v>State Bank of India</v>
@@ -7501,33 +7501,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P119" t="str">
-        <v>SBIN0008550</v>
+        <v>SBIN0006576</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>0300062</v>
+        <v>0300075</v>
       </c>
       <c r="B120" t="str">
-        <v>VINOD KHATUN</v>
+        <v>KUMARI ANJALI MAHTO</v>
       </c>
       <c r="C120" t="str">
-        <v>Accountant</v>
+        <v>Clerk</v>
       </c>
       <c r="D120" t="str">
-        <v>03053</v>
+        <v>03063</v>
       </c>
       <c r="E120" t="str">
-        <v>Panchayat Bhawan Dumri Katsari No.4</v>
+        <v>Block Office Dumri Katsari</v>
       </c>
       <c r="F120" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G120" t="str">
-        <v>9003000062</v>
+        <v>9003000075</v>
       </c>
       <c r="H120" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I120" t="str">
         <v>0304</v>
@@ -7542,7 +7542,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M120" t="str">
-        <v>30000490978</v>
+        <v>30000593925</v>
       </c>
       <c r="N120" t="str">
         <v>State Bank of India</v>
@@ -7551,48 +7551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P120" t="str">
-        <v>SBIN0005080</v>
+        <v>SBIN0006779</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>0300061</v>
+        <v>0300114</v>
       </c>
       <c r="B121" t="str">
-        <v>NITISH ANSARI</v>
+        <v>SANTOSH PRASAD</v>
       </c>
       <c r="C121" t="str">
-        <v>Clerk</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D121" t="str">
-        <v>03052</v>
+        <v>03086</v>
       </c>
       <c r="E121" t="str">
-        <v>Circle Office Purnahiya No.4</v>
+        <v>Bank of India, Piprahi</v>
       </c>
       <c r="F121" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G121" t="str">
-        <v>9003000061</v>
+        <v>9003000114</v>
       </c>
       <c r="H121" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I121" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J121" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K121" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L121" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M121" t="str">
-        <v>30000483059</v>
+        <v>30000902766</v>
       </c>
       <c r="N121" t="str">
         <v>State Bank of India</v>
@@ -7601,48 +7601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P121" t="str">
-        <v>SBIN0001631</v>
+        <v>SBIN0004192</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>0300034</v>
+        <v>0300008</v>
       </c>
       <c r="B122" t="str">
-        <v>RAJESH ALAM</v>
+        <v>REKHA DEVI</v>
       </c>
       <c r="C122" t="str">
-        <v>Assistant Teacher</v>
+        <v>Lecturer</v>
       </c>
       <c r="D122" t="str">
-        <v>03031</v>
+        <v>03008</v>
       </c>
       <c r="E122" t="str">
-        <v>High School Tariyani No.3</v>
+        <v>Project Girls High School Purnahiya No.3</v>
       </c>
       <c r="F122" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G122" t="str">
-        <v>9003000034</v>
+        <v>9003000008</v>
       </c>
       <c r="H122" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I122" t="str">
-        <v>999999</v>
+        <v>0303</v>
       </c>
       <c r="J122" t="str">
-        <v>Others</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K122" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L122" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M122" t="str">
-        <v>30000269246</v>
+        <v>30000063352</v>
       </c>
       <c r="N122" t="str">
         <v>State Bank of India</v>
@@ -7651,48 +7651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P122" t="str">
-        <v>SBIN0005322</v>
+        <v>SBIN0002228</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>0300100</v>
+        <v>0300105</v>
       </c>
       <c r="B123" t="str">
-        <v>KIRAN THAKUR</v>
+        <v>MANOJ MAHTO</v>
       </c>
       <c r="C123" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D123" t="str">
-        <v>03080</v>
+        <v>03077</v>
       </c>
       <c r="E123" t="str">
-        <v>Block Office Sheohar</v>
+        <v>RWD Sub-Division Piprahi</v>
       </c>
       <c r="F123" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G123" t="str">
-        <v>9003000100</v>
+        <v>9003000105</v>
       </c>
       <c r="H123" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I123" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J123" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="K123" t="str">
         <v>0302</v>
       </c>
-      <c r="J123" t="str">
+      <c r="L123" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K123" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L123" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M123" t="str">
-        <v>30000791900</v>
+        <v>30000831495</v>
       </c>
       <c r="N123" t="str">
         <v>State Bank of India</v>
@@ -7701,48 +7701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P123" t="str">
-        <v>SBIN0005211</v>
+        <v>SBIN0005258</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>0300067</v>
+        <v>0300051</v>
       </c>
       <c r="B124" t="str">
-        <v>AMIT ALAM</v>
+        <v>MAMTA SINGH</v>
       </c>
       <c r="C124" t="str">
         <v>Clerk</v>
       </c>
       <c r="D124" t="str">
-        <v>03056</v>
+        <v>03043</v>
       </c>
       <c r="E124" t="str">
-        <v>Project Girls High School Purnahiya</v>
+        <v>Primary School Dumri Katsari No.1</v>
       </c>
       <c r="F124" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G124" t="str">
-        <v>9003000067</v>
+        <v>9003000051</v>
       </c>
       <c r="H124" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I124" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J124" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K124" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L124" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M124" t="str">
-        <v>30000530573</v>
+        <v>30000403869</v>
       </c>
       <c r="N124" t="str">
         <v>State Bank of India</v>
@@ -7751,48 +7751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P124" t="str">
-        <v>SBIN0007750</v>
+        <v>SBIN0006178</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>0300112</v>
+        <v>0300095</v>
       </c>
       <c r="B125" t="str">
-        <v>MD. SHAHID GUPTA</v>
+        <v>AJAY GUPTA</v>
       </c>
       <c r="C125" t="str">
-        <v>Branch Manager</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D125" t="str">
-        <v>03086</v>
+        <v>03076</v>
       </c>
       <c r="E125" t="str">
-        <v>Bank of India, Sheohar</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F125" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G125" t="str">
-        <v>9003000112</v>
+        <v>9003000095</v>
       </c>
       <c r="H125" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I125" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J125" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K125" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L125" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M125" t="str">
-        <v>30000886928</v>
+        <v>30000752305</v>
       </c>
       <c r="N125" t="str">
         <v>State Bank of India</v>
@@ -7801,48 +7801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P125" t="str">
-        <v>SBIN0008896</v>
+        <v>SBIN0001075</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>0300044</v>
+        <v>0300084</v>
       </c>
       <c r="B126" t="str">
-        <v>SANJAY SINGH</v>
+        <v>USHA DEVI</v>
       </c>
       <c r="C126" t="str">
-        <v>Accountant</v>
+        <v>Teacher</v>
       </c>
       <c r="D126" t="str">
-        <v>03020</v>
+        <v>03069</v>
       </c>
       <c r="E126" t="str">
-        <v>Circle Office Sheohar No.3</v>
+        <v>Project Girls High School Purnahiya No.2</v>
       </c>
       <c r="F126" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G126" t="str">
-        <v>9003000044</v>
+        <v>9003000084</v>
       </c>
       <c r="H126" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I126" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J126" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K126" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L126" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M126" t="str">
-        <v>30000348436</v>
+        <v>30000665196</v>
       </c>
       <c r="N126" t="str">
         <v>State Bank of India</v>
@@ -7851,48 +7851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P126" t="str">
-        <v>SBIN0004319</v>
+        <v>SBIN0005115</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>0300064</v>
+        <v>0300016</v>
       </c>
       <c r="B127" t="str">
-        <v>NEHA GUPTA</v>
+        <v>SANTOSH RAM</v>
       </c>
       <c r="C127" t="str">
-        <v>Teacher</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D127" t="str">
-        <v>03054</v>
+        <v>03014</v>
       </c>
       <c r="E127" t="str">
-        <v>Block Education Office Dumri Katsari</v>
+        <v>Primary School Sheohar No.4</v>
       </c>
       <c r="F127" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G127" t="str">
-        <v>9003000064</v>
+        <v>9003000016</v>
       </c>
       <c r="H127" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I127" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J127" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K127" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L127" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M127" t="str">
-        <v>30000506816</v>
+        <v>30000126704</v>
       </c>
       <c r="N127" t="str">
         <v>State Bank of India</v>
@@ -7901,7 +7901,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P127" t="str">
-        <v>SBIN0003051</v>
+        <v>SBIN0003432</v>
       </c>
     </row>
   </sheetData>
@@ -7954,7 +7954,7 @@
         <v>Main</v>
       </c>
       <c r="D2" t="str">
-        <v>High School Sheohar, Room 2</v>
+        <v>Block Office Hall Sheohar, Room 2</v>
       </c>
       <c r="E2" t="str">
         <v>0301</v>
@@ -7974,7 +7974,7 @@
         <v>Main</v>
       </c>
       <c r="D3" t="str">
-        <v>Kanya Middle School Piprahi, Room 3</v>
+        <v>Panchayat Bhawan Piprahi, Room 3</v>
       </c>
       <c r="E3" t="str">
         <v>0302</v>
@@ -7994,7 +7994,7 @@
         <v>Main</v>
       </c>
       <c r="D4" t="str">
-        <v>High School Purnahiya, Room 1</v>
+        <v>Kanya Middle School Purnahiya, Room 1</v>
       </c>
       <c r="E4" t="str">
         <v>0303</v>
@@ -8014,7 +8014,7 @@
         <v>Main</v>
       </c>
       <c r="D5" t="str">
-        <v>Panchayat Bhawan Dumri Katsari, Room 2</v>
+        <v>High School Dumri Katsari, Room 2</v>
       </c>
       <c r="E5" t="str">
         <v>0304</v>
@@ -8034,7 +8034,7 @@
         <v>Main</v>
       </c>
       <c r="D6" t="str">
-        <v>Block Office Hall Tariyani, Room 3</v>
+        <v>Kanya Middle School Tariyani, Room 3</v>
       </c>
       <c r="E6" t="str">
         <v>0305</v>
@@ -8054,7 +8054,7 @@
         <v>Main</v>
       </c>
       <c r="D7" t="str">
-        <v>Kanya Middle School Sheohar, Room 1</v>
+        <v>Block Office Hall Sheohar, Room 1</v>
       </c>
       <c r="E7" t="str">
         <v>0301</v>
@@ -8074,7 +8074,7 @@
         <v>Main</v>
       </c>
       <c r="D8" t="str">
-        <v>Panchayat Bhawan Purnahiya, Room 2</v>
+        <v>High School Purnahiya, Room 2</v>
       </c>
       <c r="E8" t="str">
         <v>0303</v>
@@ -8114,7 +8114,7 @@
         <v>Main</v>
       </c>
       <c r="D10" t="str">
-        <v>Block Office Hall Tariyani, Room 1</v>
+        <v>Kanya Middle School Tariyani, Room 1</v>
       </c>
       <c r="E10" t="str">
         <v>0305</v>
@@ -8134,7 +8134,7 @@
         <v>Main</v>
       </c>
       <c r="D11" t="str">
-        <v>Kanya Middle School Sheohar, Room 2</v>
+        <v>High School Sheohar, Room 2</v>
       </c>
       <c r="E11" t="str">
         <v>0301</v>
@@ -8154,7 +8154,7 @@
         <v>Main</v>
       </c>
       <c r="D12" t="str">
-        <v>Middle School Piprahi, Room 3</v>
+        <v>Kanya Middle School Piprahi, Room 3</v>
       </c>
       <c r="E12" t="str">
         <v>0302</v>
@@ -8174,7 +8174,7 @@
         <v>Main</v>
       </c>
       <c r="D13" t="str">
-        <v>Block Office Hall Purnahiya, Room 1</v>
+        <v>Panchayat Bhawan Purnahiya, Room 1</v>
       </c>
       <c r="E13" t="str">
         <v>0303</v>

--- a/test-data/TEST_Sheohar_Project.xlsx
+++ b/test-data/TEST_Sheohar_Project.xlsx
@@ -613,7 +613,7 @@
         <v>Saved at</v>
       </c>
       <c r="B4" t="str">
-        <v>13-10-2026 09:45:51</v>
+        <v>13-10-2026 17:15:51</v>
       </c>
     </row>
     <row r="5">
@@ -792,7 +792,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>13-10-2026 09:45:51</v>
+        <v>13-10-2026 17:15:51</v>
       </c>
       <c r="B2" t="str">
         <v>Test data generated (Small — Sheohar style (5 blocks, 6 TC + 6 GC booths))</v>
@@ -1606,43 +1606,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0300017</v>
+        <v>0300097</v>
       </c>
       <c r="B2" t="str">
-        <v>MAMTA CHAUDHARY</v>
+        <v>SURESH THAKUR</v>
       </c>
       <c r="C2" t="str">
-        <v>Section Officer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D2" t="str">
-        <v>03015</v>
+        <v>03079</v>
       </c>
       <c r="E2" t="str">
-        <v>Panchayat Bhawan Dumri Katsari</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="F2" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G2" t="str">
-        <v>9003000017</v>
+        <v>9003000097</v>
       </c>
       <c r="H2" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I2" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J2" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K2" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L2" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M2" t="str">
-        <v>30000134623</v>
+        <v>30000768143</v>
       </c>
       <c r="N2" t="str">
         <v>State Bank of India</v>
@@ -1651,39 +1651,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P2" t="str">
-        <v>SBIN0009018</v>
+        <v>SBIN0009163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0300041</v>
+        <v>0300093</v>
       </c>
       <c r="B3" t="str">
-        <v>NIRMALA SHARMA</v>
+        <v>SUNITA MAHTO</v>
       </c>
       <c r="C3" t="str">
-        <v>Assistant Teacher</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D3" t="str">
-        <v>03022</v>
+        <v>03076</v>
       </c>
       <c r="E3" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>Circle Office Sheohar</v>
       </c>
       <c r="F3" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G3" t="str">
-        <v>9003000041</v>
+        <v>9003000093</v>
       </c>
       <c r="H3" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I3" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J3" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K3" t="str">
         <v>0301</v>
@@ -1692,7 +1692,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M3" t="str">
-        <v>30000324679</v>
+        <v>30000736467</v>
       </c>
       <c r="N3" t="str">
         <v>State Bank of India</v>
@@ -1701,48 +1701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P3" t="str">
-        <v>SBIN0002952</v>
+        <v>SBIN0009597</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0300085</v>
+        <v>0300082</v>
       </c>
       <c r="B4" t="str">
-        <v>SAVITA SAH</v>
+        <v>MANOJ PRASAD</v>
       </c>
       <c r="C4" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D4" t="str">
-        <v>03001</v>
+        <v>03069</v>
       </c>
       <c r="E4" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>Civil Surgeon Office (deputed from other district)</v>
       </c>
       <c r="F4" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G4" t="str">
-        <v>9003000085</v>
+        <v>9003000082</v>
       </c>
       <c r="H4" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I4" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J4" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K4" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="L4" t="str">
-        <v>Dumri Katsari</v>
+        <v>Other District</v>
       </c>
       <c r="M4" t="str">
-        <v>30000673115</v>
+        <v>30000649358</v>
       </c>
       <c r="N4" t="str">
         <v>State Bank of India</v>
@@ -1751,48 +1751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P4" t="str">
-        <v>SBIN0007364</v>
+        <v>SBIN0004502</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0300036</v>
+        <v>0300121</v>
       </c>
       <c r="B5" t="str">
-        <v>MAHESH ALAM</v>
+        <v>FARHAT YADAV</v>
       </c>
       <c r="C5" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D5" t="str">
-        <v>03005</v>
+        <v>03093</v>
       </c>
       <c r="E5" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>Bank of India, Piprahi</v>
       </c>
       <c r="F5" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G5" t="str">
-        <v>9003000036</v>
+        <v>9003000121</v>
       </c>
       <c r="H5" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I5" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J5" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K5" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L5" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M5" t="str">
-        <v>30000285084</v>
+        <v>30000958199</v>
       </c>
       <c r="N5" t="str">
         <v>State Bank of India</v>
@@ -1801,39 +1801,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P5" t="str">
-        <v>SBIN0001900</v>
+        <v>SBIN0009680</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0300023</v>
+        <v>0300021</v>
       </c>
       <c r="B6" t="str">
-        <v>RANJIT CHAUDHARY</v>
+        <v>NITISH ANSARI</v>
       </c>
       <c r="C6" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D6" t="str">
         <v>03021</v>
       </c>
       <c r="E6" t="str">
-        <v>Panchayat Bhawan Piprahi</v>
+        <v>CDPO Office Piprahi</v>
       </c>
       <c r="F6" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G6" t="str">
-        <v>9003000023</v>
+        <v>9003000021</v>
       </c>
       <c r="H6" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I6" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J6" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K6" t="str">
         <v>0302</v>
@@ -1842,7 +1842,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M6" t="str">
-        <v>30000182137</v>
+        <v>30000166299</v>
       </c>
       <c r="N6" t="str">
         <v>State Bank of India</v>
@@ -1851,39 +1851,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P6" t="str">
-        <v>SBIN0009118</v>
+        <v>SBIN0006909</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>0300028</v>
+        <v>0300035</v>
       </c>
       <c r="B7" t="str">
-        <v>MAMTA ANSARI</v>
+        <v>NITISH CHAUDHARY</v>
       </c>
       <c r="C7" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D7" t="str">
-        <v>03006</v>
+        <v>03033</v>
       </c>
       <c r="E7" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>High School Sheohar No.1</v>
       </c>
       <c r="F7" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G7" t="str">
-        <v>9003000028</v>
+        <v>9003000035</v>
       </c>
       <c r="H7" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I7" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J7" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K7" t="str">
         <v>0301</v>
@@ -1892,7 +1892,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M7" t="str">
-        <v>30000221732</v>
+        <v>30000277165</v>
       </c>
       <c r="N7" t="str">
         <v>State Bank of India</v>
@@ -1901,48 +1901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P7" t="str">
-        <v>SBIN0005357</v>
+        <v>SBIN0009939</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0300096</v>
+        <v>0300040</v>
       </c>
       <c r="B8" t="str">
-        <v>SANJAY YADAV</v>
+        <v>SHAILESH MISHRA</v>
       </c>
       <c r="C8" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D8" t="str">
-        <v>03077</v>
+        <v>03037</v>
       </c>
       <c r="E8" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>Kanya Middle School Purnahiya No.2</v>
       </c>
       <c r="F8" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G8" t="str">
-        <v>9003000096</v>
+        <v>9003000040</v>
       </c>
       <c r="H8" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I8" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J8" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K8" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L8" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M8" t="str">
-        <v>30000760224</v>
+        <v>30000316760</v>
       </c>
       <c r="N8" t="str">
         <v>State Bank of India</v>
@@ -1951,48 +1951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P8" t="str">
-        <v>SBIN0002123</v>
+        <v>SBIN0002311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0300020</v>
+        <v>0300051</v>
       </c>
       <c r="B9" t="str">
-        <v>ARVIND THAKUR</v>
+        <v>ANITA OJHA</v>
       </c>
       <c r="C9" t="str">
-        <v>Section Officer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D9" t="str">
-        <v>03018</v>
+        <v>03027</v>
       </c>
       <c r="E9" t="str">
-        <v>Middle School Purnahiya No.4</v>
+        <v>Middle School Piprahi</v>
       </c>
       <c r="F9" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G9" t="str">
-        <v>9003000020</v>
+        <v>9003000051</v>
       </c>
       <c r="H9" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I9" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J9" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K9" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L9" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M9" t="str">
-        <v>30000158380</v>
+        <v>30000403869</v>
       </c>
       <c r="N9" t="str">
         <v>State Bank of India</v>
@@ -2001,48 +2001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P9" t="str">
-        <v>SBIN0008340</v>
+        <v>SBIN0008309</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0300044</v>
+        <v>0300083</v>
       </c>
       <c r="B10" t="str">
-        <v>PRAMOD MISHRA</v>
+        <v>RAMESH PRASAD</v>
       </c>
       <c r="C10" t="str">
-        <v>Clerk</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D10" t="str">
-        <v>03006</v>
+        <v>03070</v>
       </c>
       <c r="E10" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Block Office Dumri Katsari</v>
       </c>
       <c r="F10" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G10" t="str">
-        <v>9003000044</v>
+        <v>9003000083</v>
       </c>
       <c r="H10" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I10" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J10" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K10" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L10" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M10" t="str">
-        <v>30000348436</v>
+        <v>30000657277</v>
       </c>
       <c r="N10" t="str">
         <v>State Bank of India</v>
@@ -2051,48 +2051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P10" t="str">
-        <v>SBIN0001875</v>
+        <v>SBIN0006101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>0300106</v>
+        <v>0300086</v>
       </c>
       <c r="B11" t="str">
-        <v>USHA VERMA</v>
+        <v>ABDUL KALAM RAI</v>
       </c>
       <c r="C11" t="str">
-        <v>Branch Manager</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D11" t="str">
-        <v>03083</v>
+        <v>03072</v>
       </c>
       <c r="E11" t="str">
-        <v>Bank of India, Tariyani</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F11" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G11" t="str">
-        <v>9003000106</v>
+        <v>9003000086</v>
       </c>
       <c r="H11" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I11" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J11" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K11" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L11" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M11" t="str">
-        <v>30000839414</v>
+        <v>30000681034</v>
       </c>
       <c r="N11" t="str">
         <v>State Bank of India</v>
@@ -2101,48 +2101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P11" t="str">
-        <v>SBIN0009224</v>
+        <v>SBIN0003466</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>0300102</v>
+        <v>0300019</v>
       </c>
       <c r="B12" t="str">
-        <v>SURESH MISHRA</v>
+        <v>SUNIL YADAV</v>
       </c>
       <c r="C12" t="str">
-        <v>Junior Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D12" t="str">
-        <v>03081</v>
+        <v>03019</v>
       </c>
       <c r="E12" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>PHC Sheohar</v>
       </c>
       <c r="F12" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G12" t="str">
-        <v>9003000102</v>
+        <v>9003000019</v>
       </c>
       <c r="H12" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I12" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J12" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K12" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L12" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M12" t="str">
-        <v>30000807738</v>
+        <v>30000150461</v>
       </c>
       <c r="N12" t="str">
         <v>State Bank of India</v>
@@ -2151,48 +2151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P12" t="str">
-        <v>SBIN0008448</v>
+        <v>SBIN0005597</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0300065</v>
+        <v>0300049</v>
       </c>
       <c r="B13" t="str">
-        <v>SUNITA DEVI</v>
+        <v>PRAMOD VERMA</v>
       </c>
       <c r="C13" t="str">
-        <v>Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D13" t="str">
-        <v>03055</v>
+        <v>03045</v>
       </c>
       <c r="E13" t="str">
-        <v>Middle School Dumri Katsari No.2</v>
+        <v>CDPO Office Sheohar No.1</v>
       </c>
       <c r="F13" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G13" t="str">
-        <v>9003000065</v>
+        <v>9003000049</v>
       </c>
       <c r="H13" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I13" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J13" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K13" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L13" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M13" t="str">
-        <v>30000514735</v>
+        <v>30000388031</v>
       </c>
       <c r="N13" t="str">
         <v>State Bank of India</v>
@@ -2201,39 +2201,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P13" t="str">
-        <v>SBIN0006422</v>
+        <v>SBIN0003234</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0300112</v>
+        <v>0300054</v>
       </c>
       <c r="B14" t="str">
-        <v>SHAILESH RAM</v>
+        <v>NITISH RAM</v>
       </c>
       <c r="C14" t="str">
-        <v>Postmaster</v>
+        <v>Clerk</v>
       </c>
       <c r="D14" t="str">
-        <v>03088</v>
+        <v>03048</v>
       </c>
       <c r="E14" t="str">
-        <v>BSNL Exchange, Sheohar</v>
+        <v>Project Girls High School Sheohar No.1</v>
       </c>
       <c r="F14" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G14" t="str">
-        <v>9003000112</v>
+        <v>9003000054</v>
       </c>
       <c r="H14" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I14" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J14" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K14" t="str">
         <v>0301</v>
@@ -2242,7 +2242,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M14" t="str">
-        <v>30000886928</v>
+        <v>30000427626</v>
       </c>
       <c r="N14" t="str">
         <v>State Bank of India</v>
@@ -2251,33 +2251,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P14" t="str">
-        <v>SBIN0008892</v>
+        <v>SBIN0004473</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>0300011</v>
+        <v>0300070</v>
       </c>
       <c r="B15" t="str">
-        <v>DINESH VERMA</v>
+        <v>VIJAY KUMAR</v>
       </c>
       <c r="C15" t="str">
-        <v>Senior Teacher</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D15" t="str">
-        <v>03010</v>
+        <v>03035</v>
       </c>
       <c r="E15" t="str">
-        <v>Block Office Sheohar No.1</v>
+        <v>CDPO Office Sheohar</v>
       </c>
       <c r="F15" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G15" t="str">
-        <v>9003000011</v>
+        <v>9003000070</v>
       </c>
       <c r="H15" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I15" t="str">
         <v>0301</v>
@@ -2292,7 +2292,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M15" t="str">
-        <v>30000087109</v>
+        <v>30000554330</v>
       </c>
       <c r="N15" t="str">
         <v>State Bank of India</v>
@@ -2301,48 +2301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P15" t="str">
-        <v>SBIN0009857</v>
+        <v>SBIN0007959</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>0300048</v>
+        <v>0300023</v>
       </c>
       <c r="B16" t="str">
-        <v>KIRAN KUMAR</v>
+        <v>SUNIL KHATUN</v>
       </c>
       <c r="C16" t="str">
-        <v>Accountant</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D16" t="str">
-        <v>03006</v>
+        <v>03023</v>
       </c>
       <c r="E16" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>High School Tariyani No.1</v>
       </c>
       <c r="F16" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G16" t="str">
-        <v>9003000048</v>
+        <v>9003000023</v>
       </c>
       <c r="H16" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I16" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J16" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K16" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L16" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M16" t="str">
-        <v>30000380112</v>
+        <v>30000182137</v>
       </c>
       <c r="N16" t="str">
         <v>State Bank of India</v>
@@ -2351,48 +2351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P16" t="str">
-        <v>SBIN0002504</v>
+        <v>SBIN0002243</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>0300099</v>
+        <v>0300050</v>
       </c>
       <c r="B17" t="str">
-        <v>SURESH RAM</v>
+        <v>NITISH THAKUR</v>
       </c>
       <c r="C17" t="str">
-        <v>Assistant Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D17" t="str">
-        <v>03079</v>
+        <v>03018</v>
       </c>
       <c r="E17" t="str">
-        <v>Collectorate (deputed from other district)</v>
+        <v>Primary School Purnahiya No.4</v>
       </c>
       <c r="F17" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G17" t="str">
-        <v>9003000099</v>
+        <v>9003000050</v>
       </c>
       <c r="H17" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I17" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J17" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K17" t="str">
-        <v>999999</v>
+        <v>0303</v>
       </c>
       <c r="L17" t="str">
-        <v>Other District</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M17" t="str">
-        <v>30000783981</v>
+        <v>30000395950</v>
       </c>
       <c r="N17" t="str">
         <v>State Bank of India</v>
@@ -2401,39 +2401,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P17" t="str">
-        <v>SBIN0002337</v>
+        <v>SBIN0006677</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>0300031</v>
+        <v>0300060</v>
       </c>
       <c r="B18" t="str">
-        <v>AMIT ALAM</v>
+        <v>AJAY RAI</v>
       </c>
       <c r="C18" t="str">
-        <v>Assistant Teacher</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D18" t="str">
-        <v>03028</v>
+        <v>03054</v>
       </c>
       <c r="E18" t="str">
-        <v>Panchayat Bhawan Tariyani</v>
+        <v>Panchayat Bhawan Tariyani No.2</v>
       </c>
       <c r="F18" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G18" t="str">
-        <v>9003000031</v>
+        <v>9003000060</v>
       </c>
       <c r="H18" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I18" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J18" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K18" t="str">
         <v>0305</v>
@@ -2442,7 +2442,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M18" t="str">
-        <v>30000245489</v>
+        <v>30000475140</v>
       </c>
       <c r="N18" t="str">
         <v>State Bank of India</v>
@@ -2451,48 +2451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P18" t="str">
-        <v>SBIN0003021</v>
+        <v>SBIN0003910</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>0300067</v>
+        <v>0300098</v>
       </c>
       <c r="B19" t="str">
-        <v>MANOJ YADAV P</v>
+        <v>FARHAT RAI</v>
       </c>
       <c r="C19" t="str">
-        <v>Clerk</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D19" t="str">
-        <v>03057</v>
+        <v>03030</v>
       </c>
       <c r="E19" t="str">
-        <v>Middle School Dumri Katsari</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F19" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G19" t="str">
-        <v>9003000067</v>
+        <v>9003000098</v>
       </c>
       <c r="H19" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I19" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J19" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K19" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L19" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M19" t="str">
-        <v>30000530573</v>
+        <v>30000776062</v>
       </c>
       <c r="N19" t="str">
         <v>State Bank of India</v>
@@ -2501,39 +2501,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P19" t="str">
-        <v>SBIN0003810</v>
+        <v>SBIN0007915</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>0300066</v>
+        <v>0300067</v>
       </c>
       <c r="B20" t="str">
-        <v>ALOK TIWARI</v>
+        <v>MAHESH RAI</v>
       </c>
       <c r="C20" t="str">
-        <v>Office Assistant</v>
+        <v>Teacher</v>
       </c>
       <c r="D20" t="str">
-        <v>03056</v>
+        <v>03034</v>
       </c>
       <c r="E20" t="str">
-        <v>PHC Sheohar No.4</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F20" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G20" t="str">
-        <v>9003000066</v>
+        <v>9003000067</v>
       </c>
       <c r="H20" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I20" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J20" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K20" t="str">
         <v>0301</v>
@@ -2542,7 +2542,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M20" t="str">
-        <v>30000522654</v>
+        <v>30000530573</v>
       </c>
       <c r="N20" t="str">
         <v>State Bank of India</v>
@@ -2551,48 +2551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P20" t="str">
-        <v>SBIN0005292</v>
+        <v>SBIN0001240</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>0300097</v>
+        <v>0300080</v>
       </c>
       <c r="B21" t="str">
-        <v>MD. IRFAN YADAV</v>
+        <v>SAVITA THAKUR</v>
       </c>
       <c r="C21" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D21" t="str">
-        <v>03070</v>
+        <v>03009</v>
       </c>
       <c r="E21" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F21" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G21" t="str">
-        <v>9003000097</v>
+        <v>9003000080</v>
       </c>
       <c r="H21" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I21" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J21" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K21" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L21" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M21" t="str">
-        <v>30000768143</v>
+        <v>30000633520</v>
       </c>
       <c r="N21" t="str">
         <v>State Bank of India</v>
@@ -2601,48 +2601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P21" t="str">
-        <v>SBIN0001486</v>
+        <v>SBIN0001511</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>0300040</v>
+        <v>0300027</v>
       </c>
       <c r="B22" t="str">
-        <v>MAHESH ALAM N</v>
+        <v>MAMTA PASWAN</v>
       </c>
       <c r="C22" t="str">
         <v>Senior Clerk</v>
       </c>
       <c r="D22" t="str">
-        <v>03036</v>
+        <v>03027</v>
       </c>
       <c r="E22" t="str">
-        <v>Block Education Office Purnahiya</v>
+        <v>Middle School Piprahi</v>
       </c>
       <c r="F22" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G22" t="str">
-        <v>9003000040</v>
+        <v>9003000027</v>
       </c>
       <c r="H22" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I22" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J22" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K22" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L22" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M22" t="str">
-        <v>30000316760</v>
+        <v>30000213813</v>
       </c>
       <c r="N22" t="str">
         <v>State Bank of India</v>
@@ -2651,33 +2651,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P22" t="str">
-        <v>SBIN0008166</v>
+        <v>SBIN0003882</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>0300086</v>
+        <v>0300117</v>
       </c>
       <c r="B23" t="str">
-        <v>FARHAT PRASAD</v>
+        <v>RANJIT OJHA</v>
       </c>
       <c r="C23" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D23" t="str">
-        <v>03070</v>
+        <v>03084</v>
       </c>
       <c r="E23" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>Head Post Office, Piprahi</v>
       </c>
       <c r="F23" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G23" t="str">
-        <v>9003000086</v>
+        <v>9003000117</v>
       </c>
       <c r="H23" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I23" t="str">
         <v>0303</v>
@@ -2686,13 +2686,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K23" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L23" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M23" t="str">
-        <v>30000681034</v>
+        <v>30000926523</v>
       </c>
       <c r="N23" t="str">
         <v>State Bank of India</v>
@@ -2701,48 +2701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P23" t="str">
-        <v>SBIN0006039</v>
+        <v>SBIN0005140</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>0300108</v>
+        <v>0300006</v>
       </c>
       <c r="B24" t="str">
-        <v>MANOJ RAI</v>
+        <v>RAMESH CHAUDHARY</v>
       </c>
       <c r="C24" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D24" t="str">
-        <v>03083</v>
+        <v>03006</v>
       </c>
       <c r="E24" t="str">
-        <v>Bank of India, Tariyani</v>
+        <v>Middle School Purnahiya No.1</v>
       </c>
       <c r="F24" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G24" t="str">
-        <v>9003000108</v>
+        <v>9003000006</v>
       </c>
       <c r="H24" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I24" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K24" t="str">
         <v>0303</v>
       </c>
-      <c r="J24" t="str">
+      <c r="L24" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="K24" t="str">
-        <v>0305</v>
-      </c>
-      <c r="L24" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="M24" t="str">
-        <v>30000855252</v>
+        <v>30000047514</v>
       </c>
       <c r="N24" t="str">
         <v>State Bank of India</v>
@@ -2751,48 +2751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P24" t="str">
-        <v>SBIN0002579</v>
+        <v>SBIN0005235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0300111</v>
+        <v>0300089</v>
       </c>
       <c r="B25" t="str">
-        <v>DINESH ALAM</v>
+        <v>AMIT DEVI</v>
       </c>
       <c r="C25" t="str">
-        <v>Assistant Manager</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D25" t="str">
-        <v>03087</v>
+        <v>03075</v>
       </c>
       <c r="E25" t="str">
-        <v>Central Bank of India, Tariyani</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F25" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G25" t="str">
-        <v>9003000111</v>
+        <v>9003000089</v>
       </c>
       <c r="H25" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I25" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J25" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K25" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L25" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M25" t="str">
-        <v>30000879009</v>
+        <v>30000704791</v>
       </c>
       <c r="N25" t="str">
         <v>State Bank of India</v>
@@ -2801,48 +2801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P25" t="str">
-        <v>SBIN0006002</v>
+        <v>SBIN0005007</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>0300063</v>
+        <v>0300062</v>
       </c>
       <c r="B26" t="str">
-        <v>UMESH SHARMA</v>
+        <v>ALOK OJHA</v>
       </c>
       <c r="C26" t="str">
-        <v>Teacher</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D26" t="str">
-        <v>03053</v>
+        <v>03041</v>
       </c>
       <c r="E26" t="str">
-        <v>CDPO Office Dumri Katsari No.2</v>
+        <v>Block Education Office Tariyani No.2</v>
       </c>
       <c r="F26" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G26" t="str">
-        <v>9003000063</v>
+        <v>9003000062</v>
       </c>
       <c r="H26" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I26" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J26" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K26" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L26" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M26" t="str">
-        <v>30000498897</v>
+        <v>30000490978</v>
       </c>
       <c r="N26" t="str">
         <v>State Bank of India</v>
@@ -2851,39 +2851,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P26" t="str">
-        <v>SBIN0002990</v>
+        <v>SBIN0001646</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>0300039</v>
+        <v>0300095</v>
       </c>
       <c r="B27" t="str">
-        <v>AMIT SHARMA</v>
+        <v>SUNIL SINGH</v>
       </c>
       <c r="C27" t="str">
-        <v>Senior Clerk</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D27" t="str">
-        <v>03035</v>
+        <v>03077</v>
       </c>
       <c r="E27" t="str">
-        <v>Kanya Middle School Dumri Katsari No.3</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F27" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G27" t="str">
-        <v>9003000039</v>
+        <v>9003000095</v>
       </c>
       <c r="H27" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I27" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J27" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K27" t="str">
         <v>0304</v>
@@ -2892,7 +2892,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M27" t="str">
-        <v>30000308841</v>
+        <v>30000752305</v>
       </c>
       <c r="N27" t="str">
         <v>State Bank of India</v>
@@ -2901,39 +2901,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P27" t="str">
-        <v>SBIN0003027</v>
+        <v>SBIN0008087</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>0300122</v>
+        <v>0300106</v>
       </c>
       <c r="B28" t="str">
-        <v>ALOK ALAM</v>
+        <v>MAMTA DEVI</v>
       </c>
       <c r="C28" t="str">
-        <v>Assistant Manager</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D28" t="str">
-        <v>03096</v>
+        <v>03081</v>
       </c>
       <c r="E28" t="str">
-        <v>Punjab National Bank, Dumri Katsari</v>
+        <v>Bank of India, Dumri Katsari</v>
       </c>
       <c r="F28" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G28" t="str">
-        <v>9003000122</v>
+        <v>9003000106</v>
       </c>
       <c r="H28" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I28" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J28" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K28" t="str">
         <v>0304</v>
@@ -2942,7 +2942,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M28" t="str">
-        <v>30000966118</v>
+        <v>30000839414</v>
       </c>
       <c r="N28" t="str">
         <v>State Bank of India</v>
@@ -2951,39 +2951,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P28" t="str">
-        <v>SBIN0001559</v>
+        <v>SBIN0009587</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>0300058</v>
+        <v>0300073</v>
       </c>
       <c r="B29" t="str">
-        <v>ASHA MISHRA</v>
+        <v>MUKESH THAKUR</v>
       </c>
       <c r="C29" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Clerk</v>
       </c>
       <c r="D29" t="str">
-        <v>03028</v>
+        <v>03064</v>
       </c>
       <c r="E29" t="str">
-        <v>Panchayat Bhawan Tariyani</v>
+        <v>Block Education Office Tariyani</v>
       </c>
       <c r="F29" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G29" t="str">
-        <v>9003000058</v>
+        <v>9003000073</v>
       </c>
       <c r="H29" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I29" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J29" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K29" t="str">
         <v>0305</v>
@@ -2992,7 +2992,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M29" t="str">
-        <v>30000459302</v>
+        <v>30000578087</v>
       </c>
       <c r="N29" t="str">
         <v>State Bank of India</v>
@@ -3001,48 +3001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P29" t="str">
-        <v>SBIN0005604</v>
+        <v>SBIN0005772</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>0300103</v>
+        <v>0300066</v>
       </c>
       <c r="B30" t="str">
-        <v>USHA PASWAN</v>
+        <v>MANOJ PASWAN</v>
       </c>
       <c r="C30" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D30" t="str">
-        <v>03082</v>
+        <v>03059</v>
       </c>
       <c r="E30" t="str">
-        <v>RWD Sub-Division Dumri Katsari</v>
+        <v>Project Girls High School Sheohar No.2</v>
       </c>
       <c r="F30" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G30" t="str">
-        <v>9003000103</v>
+        <v>9003000066</v>
       </c>
       <c r="H30" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I30" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J30" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K30" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L30" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M30" t="str">
-        <v>30000815657</v>
+        <v>30000522654</v>
       </c>
       <c r="N30" t="str">
         <v>State Bank of India</v>
@@ -3051,48 +3051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P30" t="str">
-        <v>SBIN0004879</v>
+        <v>SBIN0008202</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>0300060</v>
+        <v>0300033</v>
       </c>
       <c r="B31" t="str">
-        <v>PRAMOD VERMA</v>
+        <v>NASREEN GUPTA</v>
       </c>
       <c r="C31" t="str">
-        <v>Accountant</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D31" t="str">
-        <v>03051</v>
+        <v>03032</v>
       </c>
       <c r="E31" t="str">
-        <v>Panchayat Bhawan Sheohar</v>
+        <v>PHC Piprahi No.3</v>
       </c>
       <c r="F31" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G31" t="str">
-        <v>9003000060</v>
+        <v>9003000033</v>
       </c>
       <c r="H31" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I31" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J31" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K31" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L31" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M31" t="str">
-        <v>30000475140</v>
+        <v>30000261327</v>
       </c>
       <c r="N31" t="str">
         <v>State Bank of India</v>
@@ -3101,48 +3101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P31" t="str">
-        <v>SBIN0005770</v>
+        <v>SBIN0005708</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>0300089</v>
+        <v>0300036</v>
       </c>
       <c r="B32" t="str">
-        <v>ANIL DEVI</v>
+        <v>SUNITA KUMAR</v>
       </c>
       <c r="C32" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D32" t="str">
-        <v>03072</v>
+        <v>03034</v>
       </c>
       <c r="E32" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F32" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G32" t="str">
-        <v>9003000089</v>
+        <v>9003000036</v>
       </c>
       <c r="H32" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I32" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J32" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K32" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L32" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M32" t="str">
-        <v>30000704791</v>
+        <v>30000285084</v>
       </c>
       <c r="N32" t="str">
         <v>State Bank of India</v>
@@ -3151,48 +3151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P32" t="str">
-        <v>SBIN0008564</v>
+        <v>SBIN0008256</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>0300091</v>
+        <v>0300011</v>
       </c>
       <c r="B33" t="str">
-        <v>SHAILESH ANSARI</v>
+        <v>SAVITA ANSARI</v>
       </c>
       <c r="C33" t="str">
-        <v>Revenue Officer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D33" t="str">
-        <v>03024</v>
+        <v>03011</v>
       </c>
       <c r="E33" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Circle Office Dumri Katsari No.3</v>
       </c>
       <c r="F33" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G33" t="str">
-        <v>9003000091</v>
+        <v>9003000011</v>
       </c>
       <c r="H33" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I33" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J33" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K33" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L33" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M33" t="str">
-        <v>30000720629</v>
+        <v>30000087109</v>
       </c>
       <c r="N33" t="str">
         <v>State Bank of India</v>
@@ -3201,48 +3201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P33" t="str">
-        <v>SBIN0004862</v>
+        <v>SBIN0004368</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>0300104</v>
+        <v>0300045</v>
       </c>
       <c r="B34" t="str">
-        <v>ARVIND SINGH O</v>
+        <v>NASREEN THAKUR</v>
       </c>
       <c r="C34" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D34" t="str">
-        <v>03078</v>
+        <v>03042</v>
       </c>
       <c r="E34" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>CDPO Office Sheohar No.4</v>
       </c>
       <c r="F34" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G34" t="str">
-        <v>9003000104</v>
+        <v>9003000045</v>
       </c>
       <c r="H34" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I34" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K34" t="str">
         <v>0301</v>
       </c>
-      <c r="J34" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K34" t="str">
-        <v>0302</v>
-      </c>
       <c r="L34" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M34" t="str">
-        <v>30000823576</v>
+        <v>30000356355</v>
       </c>
       <c r="N34" t="str">
         <v>State Bank of India</v>
@@ -3251,48 +3251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P34" t="str">
-        <v>SBIN0004195</v>
+        <v>SBIN0002577</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>0300003</v>
+        <v>0300012</v>
       </c>
       <c r="B35" t="str">
-        <v>MANOJ YADAV</v>
+        <v>RAKESH SAH</v>
       </c>
       <c r="C35" t="str">
-        <v>Headmaster</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D35" t="str">
-        <v>03003</v>
+        <v>03012</v>
       </c>
       <c r="E35" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Panchayat Bhawan Tariyani No.1</v>
       </c>
       <c r="F35" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G35" t="str">
-        <v>9003000003</v>
+        <v>9003000012</v>
       </c>
       <c r="H35" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I35" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J35" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K35" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L35" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M35" t="str">
-        <v>30000023757</v>
+        <v>30000095028</v>
       </c>
       <c r="N35" t="str">
         <v>State Bank of India</v>
@@ -3301,48 +3301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P35" t="str">
-        <v>SBIN0009244</v>
+        <v>SBIN0001259</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>0300033</v>
+        <v>0300069</v>
       </c>
       <c r="B36" t="str">
-        <v>ALOK PRASAD</v>
+        <v>POONAM PRASAD</v>
       </c>
       <c r="C36" t="str">
-        <v>Assistant Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D36" t="str">
-        <v>03030</v>
+        <v>03061</v>
       </c>
       <c r="E36" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>Circle Office Dumri Katsari No.4</v>
       </c>
       <c r="F36" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G36" t="str">
-        <v>9003000033</v>
+        <v>9003000069</v>
       </c>
       <c r="H36" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I36" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J36" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K36" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L36" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M36" t="str">
-        <v>30000261327</v>
+        <v>30000546411</v>
       </c>
       <c r="N36" t="str">
         <v>State Bank of India</v>
@@ -3351,48 +3351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P36" t="str">
-        <v>SBIN0004267</v>
+        <v>SBIN0002063</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>0300072</v>
+        <v>0300046</v>
       </c>
       <c r="B37" t="str">
-        <v>PRAMOD MISHRA D</v>
+        <v>USHA YADAV</v>
       </c>
       <c r="C37" t="str">
-        <v>Data Entry Operator</v>
+        <v>Teacher</v>
       </c>
       <c r="D37" t="str">
-        <v>03037</v>
+        <v>03009</v>
       </c>
       <c r="E37" t="str">
-        <v>PHC Piprahi</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F37" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G37" t="str">
-        <v>9003000072</v>
+        <v>9003000046</v>
       </c>
       <c r="H37" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I37" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J37" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K37" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L37" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M37" t="str">
-        <v>30000570168</v>
+        <v>30000364274</v>
       </c>
       <c r="N37" t="str">
         <v>State Bank of India</v>
@@ -3401,48 +3401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P37" t="str">
-        <v>SBIN0009200</v>
+        <v>SBIN0002894</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>0300061</v>
+        <v>0300111</v>
       </c>
       <c r="B38" t="str">
-        <v>MAHESH ANSARI</v>
+        <v>KIRAN RAI H</v>
       </c>
       <c r="C38" t="str">
-        <v>Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D38" t="str">
-        <v>03052</v>
+        <v>03086</v>
       </c>
       <c r="E38" t="str">
-        <v>Panchayat Bhawan Dumri Katsari No.4</v>
+        <v>UCO Bank, Purnahiya</v>
       </c>
       <c r="F38" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G38" t="str">
-        <v>9003000061</v>
+        <v>9003000111</v>
       </c>
       <c r="H38" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I38" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J38" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K38" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L38" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M38" t="str">
-        <v>30000483059</v>
+        <v>30000879009</v>
       </c>
       <c r="N38" t="str">
         <v>State Bank of India</v>
@@ -3451,39 +3451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P38" t="str">
-        <v>SBIN0006879</v>
+        <v>SBIN0009568</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>0300042</v>
+        <v>0300029</v>
       </c>
       <c r="B39" t="str">
-        <v>MD. IRFAN SHARMA</v>
+        <v>PRIYANKA ALAM</v>
       </c>
       <c r="C39" t="str">
         <v>Panchayat Secretary</v>
       </c>
       <c r="D39" t="str">
-        <v>03037</v>
+        <v>03020</v>
       </c>
       <c r="E39" t="str">
-        <v>PHC Piprahi</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="F39" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G39" t="str">
-        <v>9003000042</v>
+        <v>9003000029</v>
       </c>
       <c r="H39" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I39" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J39" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K39" t="str">
         <v>0302</v>
@@ -3492,7 +3492,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M39" t="str">
-        <v>30000332598</v>
+        <v>30000229651</v>
       </c>
       <c r="N39" t="str">
         <v>State Bank of India</v>
@@ -3501,30 +3501,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P39" t="str">
-        <v>SBIN0009470</v>
+        <v>SBIN0003147</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>0300070</v>
+        <v>0300077</v>
       </c>
       <c r="B40" t="str">
-        <v>ARVIND KHATUN R</v>
+        <v>RANJIT TIWARI</v>
       </c>
       <c r="C40" t="str">
-        <v>Data Entry Operator</v>
+        <v>Teacher</v>
       </c>
       <c r="D40" t="str">
-        <v>03060</v>
+        <v>03066</v>
       </c>
       <c r="E40" t="str">
-        <v>Project Girls High School Piprahi No.1</v>
+        <v>High School Purnahiya No.2</v>
       </c>
       <c r="F40" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G40" t="str">
-        <v>9003000070</v>
+        <v>9003000077</v>
       </c>
       <c r="H40" t="str">
         <v>POLLING OFFICER-3</v>
@@ -3536,13 +3536,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K40" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L40" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M40" t="str">
-        <v>30000554330</v>
+        <v>30000609763</v>
       </c>
       <c r="N40" t="str">
         <v>State Bank of India</v>
@@ -3551,48 +3551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P40" t="str">
-        <v>SBIN0005633</v>
+        <v>SBIN0001434</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>0300118</v>
+        <v>0300032</v>
       </c>
       <c r="B41" t="str">
-        <v>VINOD SAH</v>
+        <v>RAVI RAM</v>
       </c>
       <c r="C41" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D41" t="str">
-        <v>03093</v>
+        <v>03031</v>
       </c>
       <c r="E41" t="str">
-        <v>State Bank of India, Dumri Katsari</v>
+        <v>PHC Piprahi</v>
       </c>
       <c r="F41" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G41" t="str">
-        <v>9003000118</v>
+        <v>9003000032</v>
       </c>
       <c r="H41" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I41" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J41" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K41" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L41" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M41" t="str">
-        <v>30000934442</v>
+        <v>30000253408</v>
       </c>
       <c r="N41" t="str">
         <v>State Bank of India</v>
@@ -3601,7 +3601,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P41" t="str">
-        <v>SBIN0003796</v>
+        <v>SBIN0008286</v>
       </c>
     </row>
     <row r="42">
@@ -3609,19 +3609,19 @@
         <v>0300018</v>
       </c>
       <c r="B42" t="str">
-        <v>SURESH CHAUDHARY</v>
+        <v>ARVIND CHAUDHARY</v>
       </c>
       <c r="C42" t="str">
-        <v>Assistant Engineer</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D42" t="str">
-        <v>03016</v>
+        <v>03018</v>
       </c>
       <c r="E42" t="str">
-        <v>Block Education Office Tariyani</v>
+        <v>Primary School Purnahiya No.4</v>
       </c>
       <c r="F42" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G42" t="str">
         <v>9003000018</v>
@@ -3630,16 +3630,16 @@
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I42" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J42" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K42" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L42" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M42" t="str">
         <v>30000142542</v>
@@ -3651,48 +3651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P42" t="str">
-        <v>SBIN0005275</v>
+        <v>SBIN0005653</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>0300027</v>
+        <v>0300034</v>
       </c>
       <c r="B43" t="str">
-        <v>NEHA PRASAD</v>
+        <v>ASHA OJHA</v>
       </c>
       <c r="C43" t="str">
-        <v>Assistant Teacher</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D43" t="str">
-        <v>03025</v>
+        <v>03030</v>
       </c>
       <c r="E43" t="str">
-        <v>Block Office Tariyani No.1</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F43" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G43" t="str">
-        <v>9003000027</v>
+        <v>9003000034</v>
       </c>
       <c r="H43" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I43" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J43" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K43" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L43" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M43" t="str">
-        <v>30000213813</v>
+        <v>30000269246</v>
       </c>
       <c r="N43" t="str">
         <v>State Bank of India</v>
@@ -3701,48 +3701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P43" t="str">
-        <v>SBIN0001600</v>
+        <v>SBIN0005005</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>0300113</v>
+        <v>0300052</v>
       </c>
       <c r="B44" t="str">
-        <v>SAVITA PASWAN</v>
+        <v>KIRAN SAH</v>
       </c>
       <c r="C44" t="str">
-        <v>Administrative Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D44" t="str">
-        <v>03089</v>
+        <v>03046</v>
       </c>
       <c r="E44" t="str">
-        <v>State Bank of India, Sheohar</v>
+        <v>Primary School Piprahi No.3</v>
       </c>
       <c r="F44" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G44" t="str">
-        <v>9003000113</v>
+        <v>9003000052</v>
       </c>
       <c r="H44" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I44" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J44" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K44" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L44" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M44" t="str">
-        <v>30000894847</v>
+        <v>30000411788</v>
       </c>
       <c r="N44" t="str">
         <v>State Bank of India</v>
@@ -3751,33 +3751,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P44" t="str">
-        <v>SBIN0002253</v>
+        <v>SBIN0003746</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>0300030</v>
+        <v>0300103</v>
       </c>
       <c r="B45" t="str">
-        <v>FARHAT KUMAR</v>
+        <v>ABDUL KALAM SINHA</v>
       </c>
       <c r="C45" t="str">
-        <v>Head Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D45" t="str">
-        <v>03027</v>
+        <v>03080</v>
       </c>
       <c r="E45" t="str">
-        <v>High School Dumri Katsari No.3</v>
+        <v>RWD Sub-Division Dumri Katsari</v>
       </c>
       <c r="F45" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G45" t="str">
-        <v>9003000030</v>
+        <v>9003000103</v>
       </c>
       <c r="H45" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I45" t="str">
         <v>0304</v>
@@ -3792,7 +3792,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M45" t="str">
-        <v>30000237570</v>
+        <v>30000815657</v>
       </c>
       <c r="N45" t="str">
         <v>State Bank of India</v>
@@ -3801,48 +3801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P45" t="str">
-        <v>SBIN0007251</v>
+        <v>SBIN0007186</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>0300001</v>
+        <v>0300005</v>
       </c>
       <c r="B46" t="str">
-        <v>ANITA VERMA</v>
+        <v>SURESH SINHA</v>
       </c>
       <c r="C46" t="str">
-        <v>Headmaster</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D46" t="str">
-        <v>03001</v>
+        <v>03005</v>
       </c>
       <c r="E46" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>CDPO Office Tariyani No.3</v>
       </c>
       <c r="F46" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G46" t="str">
-        <v>9003000001</v>
+        <v>9003000005</v>
       </c>
       <c r="H46" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I46" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="J46" t="str">
-        <v>Dumri Katsari</v>
+        <v>Others</v>
       </c>
       <c r="K46" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L46" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M46" t="str">
-        <v>30000007919</v>
+        <v>30000039595</v>
       </c>
       <c r="N46" t="str">
         <v>State Bank of India</v>
@@ -3851,48 +3851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P46" t="str">
-        <v>SBIN0009441</v>
+        <v>SBIN0001761</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0300045</v>
+        <v>0300091</v>
       </c>
       <c r="B47" t="str">
-        <v>NIRMALA PRASAD</v>
+        <v>MANOJ SHARMA</v>
       </c>
       <c r="C47" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D47" t="str">
-        <v>03039</v>
+        <v>03072</v>
       </c>
       <c r="E47" t="str">
-        <v>Panchayat Bhawan Purnahiya</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F47" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G47" t="str">
-        <v>9003000045</v>
+        <v>9003000091</v>
       </c>
       <c r="H47" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I47" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J47" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K47" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L47" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M47" t="str">
-        <v>30000356355</v>
+        <v>30000720629</v>
       </c>
       <c r="N47" t="str">
         <v>State Bank of India</v>
@@ -3901,48 +3901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P47" t="str">
-        <v>SBIN0006291</v>
+        <v>SBIN0009393</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0300068</v>
+        <v>0300063</v>
       </c>
       <c r="B48" t="str">
-        <v>RAJESH KHATUN</v>
+        <v>VIJAY KHATUN</v>
       </c>
       <c r="C48" t="str">
-        <v>Data Entry Operator</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D48" t="str">
-        <v>03058</v>
+        <v>03056</v>
       </c>
       <c r="E48" t="str">
-        <v>Project Girls High School Tariyani No.3</v>
+        <v>PHC Dumri Katsari No.1</v>
       </c>
       <c r="F48" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G48" t="str">
-        <v>9003000068</v>
+        <v>9003000063</v>
       </c>
       <c r="H48" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I48" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J48" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K48" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L48" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M48" t="str">
-        <v>30000538492</v>
+        <v>30000498897</v>
       </c>
       <c r="N48" t="str">
         <v>State Bank of India</v>
@@ -3951,48 +3951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P48" t="str">
-        <v>SBIN0009159</v>
+        <v>SBIN0008458</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0300054</v>
+        <v>0300110</v>
       </c>
       <c r="B49" t="str">
-        <v>MAHESH MAHTO</v>
+        <v>KUMARI ANJALI THAKUR</v>
       </c>
       <c r="C49" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D49" t="str">
-        <v>03046</v>
+        <v>03085</v>
       </c>
       <c r="E49" t="str">
-        <v>Panchayat Bhawan Dumri Katsari No.2</v>
+        <v>LIC Branch Office, Sheohar</v>
       </c>
       <c r="F49" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G49" t="str">
-        <v>9003000054</v>
+        <v>9003000110</v>
       </c>
       <c r="H49" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I49" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K49" t="str">
         <v>0301</v>
       </c>
-      <c r="J49" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K49" t="str">
-        <v>0304</v>
-      </c>
       <c r="L49" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M49" t="str">
-        <v>30000427626</v>
+        <v>30000871090</v>
       </c>
       <c r="N49" t="str">
         <v>State Bank of India</v>
@@ -4001,33 +4001,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P49" t="str">
-        <v>SBIN0007387</v>
+        <v>SBIN0007400</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0300037</v>
+        <v>0300104</v>
       </c>
       <c r="B50" t="str">
-        <v>RAJESH YADAV</v>
+        <v>ARVIND DEVI</v>
       </c>
       <c r="C50" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D50" t="str">
-        <v>03033</v>
+        <v>03070</v>
       </c>
       <c r="E50" t="str">
-        <v>Block Office Purnahiya No.4</v>
+        <v>Block Office Dumri Katsari</v>
       </c>
       <c r="F50" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G50" t="str">
-        <v>9003000037</v>
+        <v>9003000104</v>
       </c>
       <c r="H50" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I50" t="str">
         <v>0305</v>
@@ -4036,13 +4036,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K50" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L50" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M50" t="str">
-        <v>30000293003</v>
+        <v>30000823576</v>
       </c>
       <c r="N50" t="str">
         <v>State Bank of India</v>
@@ -4051,48 +4051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P50" t="str">
-        <v>SBIN0009907</v>
+        <v>SBIN0009922</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>0300077</v>
+        <v>0300088</v>
       </c>
       <c r="B51" t="str">
-        <v>UMESH VERMA</v>
+        <v>MANOJ VERMA</v>
       </c>
       <c r="C51" t="str">
-        <v>Data Entry Operator</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D51" t="str">
-        <v>03065</v>
+        <v>03074</v>
       </c>
       <c r="E51" t="str">
-        <v>Block Office Purnahiya No.3</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="F51" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G51" t="str">
-        <v>9003000077</v>
+        <v>9003000088</v>
       </c>
       <c r="H51" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I51" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J51" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K51" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L51" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M51" t="str">
-        <v>30000609763</v>
+        <v>30000696872</v>
       </c>
       <c r="N51" t="str">
         <v>State Bank of India</v>
@@ -4101,48 +4101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P51" t="str">
-        <v>SBIN0005807</v>
+        <v>SBIN0007849</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>0300082</v>
+        <v>0300090</v>
       </c>
       <c r="B52" t="str">
-        <v>MAMTA SINGH I</v>
+        <v>RAVI ALAM</v>
       </c>
       <c r="C52" t="str">
-        <v>Clerk</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D52" t="str">
-        <v>03067</v>
+        <v>03039</v>
       </c>
       <c r="E52" t="str">
-        <v>Block Office Piprahi No.4</v>
+        <v>District Agriculture Office (deputed from other district)</v>
       </c>
       <c r="F52" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G52" t="str">
-        <v>9003000082</v>
+        <v>9003000090</v>
       </c>
       <c r="H52" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I52" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J52" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K52" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="L52" t="str">
-        <v>Piprahi</v>
+        <v>Other District</v>
       </c>
       <c r="M52" t="str">
-        <v>30000649358</v>
+        <v>30000712710</v>
       </c>
       <c r="N52" t="str">
         <v>State Bank of India</v>
@@ -4151,39 +4151,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P52" t="str">
-        <v>SBIN0005698</v>
+        <v>SBIN0009488</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>0300015</v>
+        <v>0300071</v>
       </c>
       <c r="B53" t="str">
-        <v>SANTOSH OJHA</v>
+        <v>KUMARI ANJALI GUPTA</v>
       </c>
       <c r="C53" t="str">
-        <v>Assistant Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D53" t="str">
-        <v>03013</v>
+        <v>03062</v>
       </c>
       <c r="E53" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Primary School Sheohar</v>
       </c>
       <c r="F53" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G53" t="str">
-        <v>9003000015</v>
+        <v>9003000071</v>
       </c>
       <c r="H53" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I53" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J53" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K53" t="str">
         <v>0301</v>
@@ -4192,7 +4192,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M53" t="str">
-        <v>30000118785</v>
+        <v>30000562249</v>
       </c>
       <c r="N53" t="str">
         <v>State Bank of India</v>
@@ -4201,33 +4201,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P53" t="str">
-        <v>SBIN0004561</v>
+        <v>SBIN0006503</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>0300049</v>
+        <v>0300042</v>
       </c>
       <c r="B54" t="str">
-        <v>RAMESH SINGH</v>
+        <v>RANJIT SINGH</v>
       </c>
       <c r="C54" t="str">
-        <v>Accountant</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D54" t="str">
-        <v>03041</v>
+        <v>03039</v>
       </c>
       <c r="E54" t="str">
-        <v>Kanya Middle School Tariyani No.3</v>
+        <v>District Agriculture Office (deputed from other district)</v>
       </c>
       <c r="F54" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G54" t="str">
-        <v>9003000049</v>
+        <v>9003000042</v>
       </c>
       <c r="H54" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I54" t="str">
         <v>0305</v>
@@ -4236,13 +4236,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K54" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="L54" t="str">
-        <v>Tariyani</v>
+        <v>Other District</v>
       </c>
       <c r="M54" t="str">
-        <v>30000388031</v>
+        <v>30000332598</v>
       </c>
       <c r="N54" t="str">
         <v>State Bank of India</v>
@@ -4251,48 +4251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P54" t="str">
-        <v>SBIN0003764</v>
+        <v>SBIN0009201</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>0300010</v>
+        <v>0300022</v>
       </c>
       <c r="B55" t="str">
-        <v>ARVIND SINGH</v>
+        <v>DINESH ANSARI</v>
       </c>
       <c r="C55" t="str">
-        <v>Assistant Engineer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D55" t="str">
-        <v>03005</v>
+        <v>03022</v>
       </c>
       <c r="E55" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>Circle Office Purnahiya No.3</v>
       </c>
       <c r="F55" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G55" t="str">
-        <v>9003000010</v>
+        <v>9003000022</v>
       </c>
       <c r="H55" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I55" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J55" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K55" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L55" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M55" t="str">
-        <v>30000079190</v>
+        <v>30000174218</v>
       </c>
       <c r="N55" t="str">
         <v>State Bank of India</v>
@@ -4301,48 +4301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P55" t="str">
-        <v>SBIN0004077</v>
+        <v>SBIN0005859</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>0300110</v>
+        <v>0300055</v>
       </c>
       <c r="B56" t="str">
-        <v>SHAILESH OJHA</v>
+        <v>MAMTA SAH</v>
       </c>
       <c r="C56" t="str">
-        <v>Administrative Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D56" t="str">
-        <v>03086</v>
+        <v>03049</v>
       </c>
       <c r="E56" t="str">
-        <v>Bank of India, Piprahi</v>
+        <v>CDPO Office Tariyani</v>
       </c>
       <c r="F56" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G56" t="str">
-        <v>9003000110</v>
+        <v>9003000055</v>
       </c>
       <c r="H56" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I56" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J56" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K56" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L56" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M56" t="str">
-        <v>30000871090</v>
+        <v>30000435545</v>
       </c>
       <c r="N56" t="str">
         <v>State Bank of India</v>
@@ -4351,48 +4351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P56" t="str">
-        <v>SBIN0006641</v>
+        <v>SBIN0008137</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>0300012</v>
+        <v>0300068</v>
       </c>
       <c r="B57" t="str">
-        <v>SANJAY CHAUDHARY</v>
+        <v>ARVIND ALAM</v>
       </c>
       <c r="C57" t="str">
-        <v>Assistant Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D57" t="str">
-        <v>03011</v>
+        <v>03060</v>
       </c>
       <c r="E57" t="str">
-        <v>High School Tariyani No.3</v>
+        <v>Primary School Dumri Katsari</v>
       </c>
       <c r="F57" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G57" t="str">
-        <v>9003000012</v>
+        <v>9003000068</v>
       </c>
       <c r="H57" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I57" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J57" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K57" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L57" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M57" t="str">
-        <v>30000095028</v>
+        <v>30000538492</v>
       </c>
       <c r="N57" t="str">
         <v>State Bank of India</v>
@@ -4401,48 +4401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P57" t="str">
-        <v>SBIN0006846</v>
+        <v>SBIN0004392</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>0300022</v>
+        <v>0300010</v>
       </c>
       <c r="B58" t="str">
-        <v>SANTOSH MISHRA</v>
+        <v>RAKESH KHATUN</v>
       </c>
       <c r="C58" t="str">
-        <v>Senior Clerk</v>
+        <v>Lecturer</v>
       </c>
       <c r="D58" t="str">
-        <v>03020</v>
+        <v>03010</v>
       </c>
       <c r="E58" t="str">
-        <v>Kanya Middle School Purnahiya No.4</v>
+        <v>CDPO Office Dumri Katsari</v>
       </c>
       <c r="F58" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G58" t="str">
-        <v>9003000022</v>
+        <v>9003000010</v>
       </c>
       <c r="H58" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I58" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J58" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K58" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L58" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M58" t="str">
-        <v>30000174218</v>
+        <v>30000079190</v>
       </c>
       <c r="N58" t="str">
         <v>State Bank of India</v>
@@ -4451,39 +4451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P58" t="str">
-        <v>SBIN0009465</v>
+        <v>SBIN0003598</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>0300100</v>
+        <v>0300037</v>
       </c>
       <c r="B59" t="str">
-        <v>MD. IRFAN VERMA</v>
+        <v>KIRAN MAHTO</v>
       </c>
       <c r="C59" t="str">
-        <v>Revenue Officer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D59" t="str">
-        <v>03080</v>
+        <v>03011</v>
       </c>
       <c r="E59" t="str">
-        <v>Minor Irrigation Office Dumri Katsari</v>
+        <v>Circle Office Dumri Katsari No.3</v>
       </c>
       <c r="F59" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G59" t="str">
-        <v>9003000100</v>
+        <v>9003000037</v>
       </c>
       <c r="H59" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I59" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J59" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K59" t="str">
         <v>0304</v>
@@ -4492,7 +4492,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M59" t="str">
-        <v>30000791900</v>
+        <v>30000293003</v>
       </c>
       <c r="N59" t="str">
         <v>State Bank of India</v>
@@ -4501,48 +4501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P59" t="str">
-        <v>SBIN0003009</v>
+        <v>SBIN0007068</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>0300098</v>
+        <v>0300057</v>
       </c>
       <c r="B60" t="str">
-        <v>MD. IRFAN PANDEY</v>
+        <v>SUNIL ALAM</v>
       </c>
       <c r="C60" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D60" t="str">
-        <v>03078</v>
+        <v>03051</v>
       </c>
       <c r="E60" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="F60" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G60" t="str">
-        <v>9003000098</v>
+        <v>9003000057</v>
       </c>
       <c r="H60" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I60" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J60" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K60" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L60" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M60" t="str">
-        <v>30000776062</v>
+        <v>30000451383</v>
       </c>
       <c r="N60" t="str">
         <v>State Bank of India</v>
@@ -4551,48 +4551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P60" t="str">
-        <v>SBIN0001147</v>
+        <v>SBIN0004193</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>0300078</v>
+        <v>0300102</v>
       </c>
       <c r="B61" t="str">
-        <v>NEHA SHARMA</v>
+        <v>VINOD PANDEY</v>
       </c>
       <c r="C61" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D61" t="str">
-        <v>03063</v>
+        <v>03075</v>
       </c>
       <c r="E61" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F61" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G61" t="str">
-        <v>9003000078</v>
+        <v>9003000102</v>
       </c>
       <c r="H61" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I61" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J61" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K61" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L61" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M61" t="str">
-        <v>30000617682</v>
+        <v>30000807738</v>
       </c>
       <c r="N61" t="str">
         <v>State Bank of India</v>
@@ -4601,48 +4601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P61" t="str">
-        <v>SBIN0005590</v>
+        <v>SBIN0005486</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>0300014</v>
+        <v>0300114</v>
       </c>
       <c r="B62" t="str">
-        <v>DEEPAK YADAV</v>
+        <v>VIJAY YADAV</v>
       </c>
       <c r="C62" t="str">
-        <v>Senior Teacher</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D62" t="str">
-        <v>03006</v>
+        <v>03089</v>
       </c>
       <c r="E62" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Central Bank of India, Tariyani</v>
       </c>
       <c r="F62" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G62" t="str">
-        <v>9003000014</v>
+        <v>9003000114</v>
       </c>
       <c r="H62" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I62" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J62" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K62" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L62" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M62" t="str">
-        <v>30000110866</v>
+        <v>30000902766</v>
       </c>
       <c r="N62" t="str">
         <v>State Bank of India</v>
@@ -4651,48 +4651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P62" t="str">
-        <v>SBIN0001472</v>
+        <v>SBIN0002713</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>0300062</v>
+        <v>0300105</v>
       </c>
       <c r="B63" t="str">
-        <v>RAVI RAM</v>
+        <v>DEEPAK SINGH</v>
       </c>
       <c r="C63" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D63" t="str">
-        <v>03002</v>
+        <v>03080</v>
       </c>
       <c r="E63" t="str">
-        <v>Block Agriculture Office Tariyani No.3</v>
+        <v>RWD Sub-Division Dumri Katsari</v>
       </c>
       <c r="F63" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G63" t="str">
-        <v>9003000062</v>
+        <v>9003000105</v>
       </c>
       <c r="H63" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I63" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J63" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K63" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L63" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M63" t="str">
-        <v>30000490978</v>
+        <v>30000831495</v>
       </c>
       <c r="N63" t="str">
         <v>State Bank of India</v>
@@ -4701,33 +4701,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P63" t="str">
-        <v>SBIN0002673</v>
+        <v>SBIN0003716</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>0300046</v>
+        <v>0300074</v>
       </c>
       <c r="B64" t="str">
-        <v>MAHESH GUPTA</v>
+        <v>UMESH MISHRA</v>
       </c>
       <c r="C64" t="str">
-        <v>Clerk</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D64" t="str">
-        <v>03040</v>
+        <v>03034</v>
       </c>
       <c r="E64" t="str">
-        <v>Circle Office Sheohar</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F64" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G64" t="str">
-        <v>9003000046</v>
+        <v>9003000074</v>
       </c>
       <c r="H64" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I64" t="str">
         <v>0305</v>
@@ -4742,7 +4742,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M64" t="str">
-        <v>30000364274</v>
+        <v>30000586006</v>
       </c>
       <c r="N64" t="str">
         <v>State Bank of India</v>
@@ -4751,48 +4751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P64" t="str">
-        <v>SBIN0004967</v>
+        <v>SBIN0004456</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>0300005</v>
+        <v>0300107</v>
       </c>
       <c r="B65" t="str">
-        <v>DINESH CHAUDHARY</v>
+        <v>DINESH GUPTA</v>
       </c>
       <c r="C65" t="str">
-        <v>Headmaster</v>
+        <v>Postmaster</v>
       </c>
       <c r="D65" t="str">
-        <v>03005</v>
+        <v>03082</v>
       </c>
       <c r="E65" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>State Bank of India, Piprahi</v>
       </c>
       <c r="F65" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G65" t="str">
-        <v>9003000005</v>
+        <v>9003000107</v>
       </c>
       <c r="H65" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I65" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J65" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K65" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L65" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M65" t="str">
-        <v>30000039595</v>
+        <v>30000847333</v>
       </c>
       <c r="N65" t="str">
         <v>State Bank of India</v>
@@ -4801,48 +4801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P65" t="str">
-        <v>SBIN0003186</v>
+        <v>SBIN0007768</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>0300073</v>
+        <v>0300001</v>
       </c>
       <c r="B66" t="str">
-        <v>NEHA SAH</v>
+        <v>ANITA MISHRA</v>
       </c>
       <c r="C66" t="str">
-        <v>Teacher</v>
+        <v>Lecturer</v>
       </c>
       <c r="D66" t="str">
-        <v>03062</v>
+        <v>03001</v>
       </c>
       <c r="E66" t="str">
-        <v>Circle Office Tariyani No.2</v>
+        <v>Primary School Purnahiya</v>
       </c>
       <c r="F66" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G66" t="str">
-        <v>9003000073</v>
+        <v>9003000001</v>
       </c>
       <c r="H66" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I66" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J66" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K66" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L66" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M66" t="str">
-        <v>30000578087</v>
+        <v>30000007919</v>
       </c>
       <c r="N66" t="str">
         <v>State Bank of India</v>
@@ -4851,39 +4851,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P66" t="str">
-        <v>SBIN0002421</v>
+        <v>SBIN0006969</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>0300080</v>
+        <v>0300048</v>
       </c>
       <c r="B67" t="str">
-        <v>MAMTA ANSARI B</v>
+        <v>RAKESH DEVI</v>
       </c>
       <c r="C67" t="str">
-        <v>Teacher</v>
+        <v>Accountant</v>
       </c>
       <c r="D67" t="str">
-        <v>03006</v>
+        <v>03044</v>
       </c>
       <c r="E67" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Kanya Middle School Sheohar No.3</v>
       </c>
       <c r="F67" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G67" t="str">
-        <v>9003000080</v>
+        <v>9003000048</v>
       </c>
       <c r="H67" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I67" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J67" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K67" t="str">
         <v>0301</v>
@@ -4892,7 +4892,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M67" t="str">
-        <v>30000633520</v>
+        <v>30000380112</v>
       </c>
       <c r="N67" t="str">
         <v>State Bank of India</v>
@@ -4901,48 +4901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P67" t="str">
-        <v>SBIN0004644</v>
+        <v>SBIN0007577</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>0300025</v>
+        <v>0300079</v>
       </c>
       <c r="B68" t="str">
-        <v>FARHAT ANSARI</v>
+        <v>KIRAN GUPTA</v>
       </c>
       <c r="C68" t="str">
-        <v>Assistant Teacher</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D68" t="str">
-        <v>03023</v>
+        <v>03067</v>
       </c>
       <c r="E68" t="str">
-        <v>CDPO Office Dumri Katsari No.1</v>
+        <v>Block Education Office Sheohar No.4</v>
       </c>
       <c r="F68" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G68" t="str">
-        <v>9003000025</v>
+        <v>9003000079</v>
       </c>
       <c r="H68" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I68" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J68" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K68" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L68" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M68" t="str">
-        <v>30000197975</v>
+        <v>30000625601</v>
       </c>
       <c r="N68" t="str">
         <v>State Bank of India</v>
@@ -4951,48 +4951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P68" t="str">
-        <v>SBIN0009826</v>
+        <v>SBIN0007111</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>0300121</v>
+        <v>0300020</v>
       </c>
       <c r="B69" t="str">
-        <v>NIRMALA RAM</v>
+        <v>MD. IRFAN TIWARI</v>
       </c>
       <c r="C69" t="str">
-        <v>Branch Manager</v>
+        <v>Headmaster</v>
       </c>
       <c r="D69" t="str">
-        <v>03095</v>
+        <v>03020</v>
       </c>
       <c r="E69" t="str">
-        <v>Punjab National Bank, Sheohar</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="F69" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G69" t="str">
-        <v>9003000121</v>
+        <v>9003000020</v>
       </c>
       <c r="H69" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I69" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J69" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K69" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L69" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M69" t="str">
-        <v>30000958199</v>
+        <v>30000158380</v>
       </c>
       <c r="N69" t="str">
         <v>State Bank of India</v>
@@ -5001,48 +5001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P69" t="str">
-        <v>SBIN0004833</v>
+        <v>SBIN0008222</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>0300120</v>
+        <v>0300041</v>
       </c>
       <c r="B70" t="str">
-        <v>MD. SHAHID YADAV</v>
+        <v>FARHAT PANDEY</v>
       </c>
       <c r="C70" t="str">
-        <v>Assistant Manager</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D70" t="str">
-        <v>03095</v>
+        <v>03038</v>
       </c>
       <c r="E70" t="str">
-        <v>Punjab National Bank, Sheohar</v>
+        <v>Kanya Middle School Piprahi No.1</v>
       </c>
       <c r="F70" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G70" t="str">
-        <v>9003000120</v>
+        <v>9003000041</v>
       </c>
       <c r="H70" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I70" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J70" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K70" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L70" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M70" t="str">
-        <v>30000950280</v>
+        <v>30000324679</v>
       </c>
       <c r="N70" t="str">
         <v>State Bank of India</v>
@@ -5051,48 +5051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P70" t="str">
-        <v>SBIN0009688</v>
+        <v>SBIN0002192</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>0300021</v>
+        <v>0300002</v>
       </c>
       <c r="B71" t="str">
-        <v>MD. SHAHID SHARMA</v>
+        <v>SANJAY SHARMA</v>
       </c>
       <c r="C71" t="str">
-        <v>Assistant Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D71" t="str">
-        <v>03019</v>
+        <v>03002</v>
       </c>
       <c r="E71" t="str">
-        <v>CDPO Office Sheohar</v>
+        <v>Block Education Office Tariyani No.1</v>
       </c>
       <c r="F71" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G71" t="str">
-        <v>9003000021</v>
+        <v>9003000002</v>
       </c>
       <c r="H71" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I71" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J71" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="K71" t="str">
         <v>0305</v>
       </c>
-      <c r="J71" t="str">
+      <c r="L71" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="K71" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L71" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M71" t="str">
-        <v>30000166299</v>
+        <v>30000015838</v>
       </c>
       <c r="N71" t="str">
         <v>State Bank of India</v>
@@ -5101,48 +5101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P71" t="str">
-        <v>SBIN0006272</v>
+        <v>SBIN0009116</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>0300093</v>
+        <v>0300078</v>
       </c>
       <c r="B72" t="str">
-        <v>ASHA ALAM</v>
+        <v>NASREEN TIWARI</v>
       </c>
       <c r="C72" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D72" t="str">
-        <v>03075</v>
+        <v>03034</v>
       </c>
       <c r="E72" t="str">
-        <v>Minor Irrigation Office Purnahiya</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F72" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G72" t="str">
-        <v>9003000093</v>
+        <v>9003000078</v>
       </c>
       <c r="H72" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I72" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J72" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K72" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L72" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M72" t="str">
-        <v>30000736467</v>
+        <v>30000617682</v>
       </c>
       <c r="N72" t="str">
         <v>State Bank of India</v>
@@ -5151,48 +5151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P72" t="str">
-        <v>SBIN0001663</v>
+        <v>SBIN0008495</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>0300115</v>
+        <v>0300122</v>
       </c>
       <c r="B73" t="str">
-        <v>ANITA PRASAD</v>
+        <v>NASREEN CHAUDHARY</v>
       </c>
       <c r="C73" t="str">
-        <v>Assistant Manager</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D73" t="str">
-        <v>03090</v>
+        <v>03094</v>
       </c>
       <c r="E73" t="str">
-        <v>LIC Branch Office, Sheohar</v>
+        <v>Head Post Office, Tariyani</v>
       </c>
       <c r="F73" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G73" t="str">
-        <v>9003000115</v>
+        <v>9003000122</v>
       </c>
       <c r="H73" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I73" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J73" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K73" t="str">
         <v>0305</v>
       </c>
-      <c r="J73" t="str">
+      <c r="L73" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="K73" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L73" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M73" t="str">
-        <v>30000910685</v>
+        <v>30000966118</v>
       </c>
       <c r="N73" t="str">
         <v>State Bank of India</v>
@@ -5201,48 +5201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P73" t="str">
-        <v>SBIN0004343</v>
+        <v>SBIN0006613</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>0300043</v>
+        <v>0300016</v>
       </c>
       <c r="B74" t="str">
-        <v>NEHA SINGH</v>
+        <v>NASREEN KUMAR</v>
       </c>
       <c r="C74" t="str">
-        <v>Teacher</v>
+        <v>Headmaster</v>
       </c>
       <c r="D74" t="str">
-        <v>03038</v>
+        <v>03016</v>
       </c>
       <c r="E74" t="str">
-        <v>Middle School Piprahi No.3</v>
+        <v>Project Girls High School Dumri Katsari</v>
       </c>
       <c r="F74" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G74" t="str">
-        <v>9003000043</v>
+        <v>9003000016</v>
       </c>
       <c r="H74" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I74" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J74" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K74" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L74" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M74" t="str">
-        <v>30000340517</v>
+        <v>30000126704</v>
       </c>
       <c r="N74" t="str">
         <v>State Bank of India</v>
@@ -5251,48 +5251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P74" t="str">
-        <v>SBIN0001884</v>
+        <v>SBIN0001904</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>0300053</v>
+        <v>0300120</v>
       </c>
       <c r="B75" t="str">
-        <v>ASHA YADAV</v>
+        <v>KUMARI ANJALI VERMA</v>
       </c>
       <c r="C75" t="str">
-        <v>Accountant</v>
+        <v>Postmaster</v>
       </c>
       <c r="D75" t="str">
-        <v>03045</v>
+        <v>03092</v>
       </c>
       <c r="E75" t="str">
-        <v>Block Education Office Tariyani No.1</v>
+        <v>Central Bank of India, Purnahiya</v>
       </c>
       <c r="F75" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G75" t="str">
-        <v>9003000053</v>
+        <v>9003000120</v>
       </c>
       <c r="H75" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I75" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J75" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K75" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L75" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M75" t="str">
-        <v>30000419707</v>
+        <v>30000950280</v>
       </c>
       <c r="N75" t="str">
         <v>State Bank of India</v>
@@ -5301,48 +5301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P75" t="str">
-        <v>SBIN0002670</v>
+        <v>SBIN0009210</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>0300035</v>
+        <v>0300084</v>
       </c>
       <c r="B76" t="str">
-        <v>KIRAN OJHA</v>
+        <v>ASHA PANDEY U</v>
       </c>
       <c r="C76" t="str">
-        <v>Senior Clerk</v>
+        <v>Clerk</v>
       </c>
       <c r="D76" t="str">
-        <v>03032</v>
+        <v>03071</v>
       </c>
       <c r="E76" t="str">
-        <v>Middle School Piprahi No.4</v>
+        <v>Block Office Sheohar</v>
       </c>
       <c r="F76" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G76" t="str">
-        <v>9003000035</v>
+        <v>9003000084</v>
       </c>
       <c r="H76" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I76" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J76" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K76" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L76" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M76" t="str">
-        <v>30000277165</v>
+        <v>30000665196</v>
       </c>
       <c r="N76" t="str">
         <v>State Bank of India</v>
@@ -5351,33 +5351,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P76" t="str">
-        <v>SBIN0008481</v>
+        <v>SBIN0001587</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>0300074</v>
+        <v>0300124</v>
       </c>
       <c r="B77" t="str">
-        <v>SHAILESH THAKUR</v>
+        <v>DINESH THAKUR</v>
       </c>
       <c r="C77" t="str">
-        <v>Office Assistant</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D77" t="str">
-        <v>03063</v>
+        <v>03096</v>
       </c>
       <c r="E77" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>UCO Bank, Piprahi</v>
       </c>
       <c r="F77" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G77" t="str">
-        <v>9003000074</v>
+        <v>9003000124</v>
       </c>
       <c r="H77" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I77" t="str">
         <v>0302</v>
@@ -5386,13 +5386,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K77" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L77" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M77" t="str">
-        <v>30000586006</v>
+        <v>30000981956</v>
       </c>
       <c r="N77" t="str">
         <v>State Bank of India</v>
@@ -5401,30 +5401,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P77" t="str">
-        <v>SBIN0008509</v>
+        <v>SBIN0003677</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>0300059</v>
+        <v>0300053</v>
       </c>
       <c r="B78" t="str">
-        <v>NEHA PASWAN</v>
+        <v>DEEPAK GUPTA</v>
       </c>
       <c r="C78" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Clerk</v>
       </c>
       <c r="D78" t="str">
-        <v>03050</v>
+        <v>03047</v>
       </c>
       <c r="E78" t="str">
-        <v>Kanya Middle School Tariyani No.4</v>
+        <v>District Treasury (deputed from other district)</v>
       </c>
       <c r="F78" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G78" t="str">
-        <v>9003000059</v>
+        <v>9003000053</v>
       </c>
       <c r="H78" t="str">
         <v>POLLING OFFICER-2</v>
@@ -5436,13 +5436,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K78" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="L78" t="str">
-        <v>Tariyani</v>
+        <v>Other District</v>
       </c>
       <c r="M78" t="str">
-        <v>30000467221</v>
+        <v>30000419707</v>
       </c>
       <c r="N78" t="str">
         <v>State Bank of India</v>
@@ -5451,39 +5451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P78" t="str">
-        <v>SBIN0002797</v>
+        <v>SBIN0009215</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0300056</v>
+        <v>0300008</v>
       </c>
       <c r="B79" t="str">
-        <v>SURESH KUMAR</v>
+        <v>ASHA PANDEY</v>
       </c>
       <c r="C79" t="str">
-        <v>Accountant</v>
+        <v>Lecturer</v>
       </c>
       <c r="D79" t="str">
-        <v>03048</v>
+        <v>03008</v>
       </c>
       <c r="E79" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>Block Agriculture Office Sheohar No.4</v>
       </c>
       <c r="F79" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G79" t="str">
-        <v>9003000056</v>
+        <v>9003000008</v>
       </c>
       <c r="H79" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I79" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J79" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K79" t="str">
         <v>0301</v>
@@ -5492,7 +5492,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M79" t="str">
-        <v>30000443464</v>
+        <v>30000063352</v>
       </c>
       <c r="N79" t="str">
         <v>State Bank of India</v>
@@ -5501,39 +5501,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P79" t="str">
-        <v>SBIN0007260</v>
+        <v>SBIN0001650</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>0300034</v>
+        <v>0300109</v>
       </c>
       <c r="B80" t="str">
-        <v>NASREEN GUPTA</v>
+        <v>MANOJ JHA</v>
       </c>
       <c r="C80" t="str">
-        <v>Senior Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D80" t="str">
-        <v>03031</v>
+        <v>03084</v>
       </c>
       <c r="E80" t="str">
-        <v>Block Agriculture Office Piprahi No.1</v>
+        <v>Head Post Office, Piprahi</v>
       </c>
       <c r="F80" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G80" t="str">
-        <v>9003000034</v>
+        <v>9003000109</v>
       </c>
       <c r="H80" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I80" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J80" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K80" t="str">
         <v>0302</v>
@@ -5542,7 +5542,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M80" t="str">
-        <v>30000269246</v>
+        <v>30000863171</v>
       </c>
       <c r="N80" t="str">
         <v>State Bank of India</v>
@@ -5551,7 +5551,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P80" t="str">
-        <v>SBIN0007880</v>
+        <v>SBIN0005823</v>
       </c>
     </row>
     <row r="81">
@@ -5559,19 +5559,19 @@
         <v>0300064</v>
       </c>
       <c r="B81" t="str">
-        <v>ARVIND ANSARI</v>
+        <v>AMIT KUMAR</v>
       </c>
       <c r="C81" t="str">
-        <v>Office Assistant</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D81" t="str">
-        <v>03054</v>
+        <v>03057</v>
       </c>
       <c r="E81" t="str">
-        <v>Panchayat Bhawan Purnahiya No.4</v>
+        <v>Project Girls High School Sheohar</v>
       </c>
       <c r="F81" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G81" t="str">
         <v>9003000064</v>
@@ -5580,16 +5580,16 @@
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I81" t="str">
-        <v>999999</v>
+        <v>0303</v>
       </c>
       <c r="J81" t="str">
-        <v>Others</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K81" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L81" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M81" t="str">
         <v>30000506816</v>
@@ -5601,48 +5601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P81" t="str">
-        <v>SBIN0007855</v>
+        <v>SBIN0007550</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>0300083</v>
+        <v>0300118</v>
       </c>
       <c r="B82" t="str">
-        <v>RAKESH TIWARI</v>
+        <v>MANOJ CHAUDHARY</v>
       </c>
       <c r="C82" t="str">
-        <v>Clerk</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D82" t="str">
-        <v>03068</v>
+        <v>03091</v>
       </c>
       <c r="E82" t="str">
-        <v>Middle School Piprahi</v>
+        <v>Punjab National Bank, Dumri Katsari</v>
       </c>
       <c r="F82" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G82" t="str">
-        <v>9003000083</v>
+        <v>9003000118</v>
       </c>
       <c r="H82" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I82" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J82" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K82" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L82" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M82" t="str">
-        <v>30000657277</v>
+        <v>30000934442</v>
       </c>
       <c r="N82" t="str">
         <v>State Bank of India</v>
@@ -5651,48 +5651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P82" t="str">
-        <v>SBIN0001974</v>
+        <v>SBIN0006558</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>0300107</v>
+        <v>0300014</v>
       </c>
       <c r="B83" t="str">
-        <v>ABDUL KALAM KUMAR</v>
+        <v>SANJAY OJHA</v>
       </c>
       <c r="C83" t="str">
-        <v>Administrative Officer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D83" t="str">
-        <v>03084</v>
+        <v>03014</v>
       </c>
       <c r="E83" t="str">
-        <v>UCO Bank, Piprahi</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F83" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G83" t="str">
-        <v>9003000107</v>
+        <v>9003000014</v>
       </c>
       <c r="H83" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I83" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J83" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K83" t="str">
         <v>0301</v>
       </c>
-      <c r="J83" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K83" t="str">
-        <v>0302</v>
-      </c>
       <c r="L83" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M83" t="str">
-        <v>30000847333</v>
+        <v>30000110866</v>
       </c>
       <c r="N83" t="str">
         <v>State Bank of India</v>
@@ -5701,33 +5701,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P83" t="str">
-        <v>SBIN0008073</v>
+        <v>SBIN0008561</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>0300124</v>
+        <v>0300025</v>
       </c>
       <c r="B84" t="str">
-        <v>ASHA MAHTO</v>
+        <v>POONAM TIWARI</v>
       </c>
       <c r="C84" t="str">
-        <v>Administrative Officer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D84" t="str">
-        <v>03089</v>
+        <v>03025</v>
       </c>
       <c r="E84" t="str">
-        <v>State Bank of India, Sheohar</v>
+        <v>CDPO Office Sheohar No.2</v>
       </c>
       <c r="F84" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G84" t="str">
-        <v>9003000124</v>
+        <v>9003000025</v>
       </c>
       <c r="H84" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I84" t="str">
         <v>0302</v>
@@ -5742,7 +5742,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M84" t="str">
-        <v>30000981956</v>
+        <v>30000197975</v>
       </c>
       <c r="N84" t="str">
         <v>State Bank of India</v>
@@ -5751,48 +5751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P84" t="str">
-        <v>SBIN0004264</v>
+        <v>SBIN0004229</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>0300071</v>
+        <v>0300061</v>
       </c>
       <c r="B85" t="str">
-        <v>VIJAY SHARMA</v>
+        <v>MANOJ SAH</v>
       </c>
       <c r="C85" t="str">
-        <v>Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D85" t="str">
-        <v>03061</v>
+        <v>03055</v>
       </c>
       <c r="E85" t="str">
-        <v>District Welfare Office (deputed from other district)</v>
+        <v>PHC Dumri Katsari No.2</v>
       </c>
       <c r="F85" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G85" t="str">
-        <v>9003000071</v>
+        <v>9003000061</v>
       </c>
       <c r="H85" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I85" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J85" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K85" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="L85" t="str">
-        <v>Other District</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M85" t="str">
-        <v>30000562249</v>
+        <v>30000483059</v>
       </c>
       <c r="N85" t="str">
         <v>State Bank of India</v>
@@ -5801,48 +5801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P85" t="str">
-        <v>SBIN0006567</v>
+        <v>SBIN0006532</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>0300126</v>
+        <v>0300004</v>
       </c>
       <c r="B86" t="str">
-        <v>NASREEN THAKUR</v>
+        <v>SANTOSH MISHRA</v>
       </c>
       <c r="C86" t="str">
-        <v>Assistant Manager</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D86" t="str">
-        <v>03090</v>
+        <v>03004</v>
       </c>
       <c r="E86" t="str">
-        <v>LIC Branch Office, Sheohar</v>
+        <v>High School Dumri Katsari</v>
       </c>
       <c r="F86" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G86" t="str">
-        <v>9003000126</v>
+        <v>9003000004</v>
       </c>
       <c r="H86" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I86" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J86" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K86" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L86" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M86" t="str">
-        <v>30000997794</v>
+        <v>30000031676</v>
       </c>
       <c r="N86" t="str">
         <v>State Bank of India</v>
@@ -5851,48 +5851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P86" t="str">
-        <v>SBIN0002756</v>
+        <v>SBIN0009970</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>0300109</v>
+        <v>0300038</v>
       </c>
       <c r="B87" t="str">
-        <v>DINESH MAHTO</v>
+        <v>MANOJ GUPTA</v>
       </c>
       <c r="C87" t="str">
-        <v>Administrative Officer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D87" t="str">
-        <v>03085</v>
+        <v>03035</v>
       </c>
       <c r="E87" t="str">
-        <v>Bank of India, Dumri Katsari</v>
+        <v>CDPO Office Sheohar</v>
       </c>
       <c r="F87" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G87" t="str">
-        <v>9003000109</v>
+        <v>9003000038</v>
       </c>
       <c r="H87" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I87" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J87" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K87" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L87" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M87" t="str">
-        <v>30000863171</v>
+        <v>30000300922</v>
       </c>
       <c r="N87" t="str">
         <v>State Bank of India</v>
@@ -5901,33 +5901,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P87" t="str">
-        <v>SBIN0006916</v>
+        <v>SBIN0002722</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>0300119</v>
+        <v>0300044</v>
       </c>
       <c r="B88" t="str">
-        <v>RAKESH KUMAR</v>
+        <v>ABDUL KALAM ANSARI</v>
       </c>
       <c r="C88" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D88" t="str">
-        <v>03094</v>
+        <v>03041</v>
       </c>
       <c r="E88" t="str">
-        <v>LIC Branch Office, Tariyani</v>
+        <v>Block Education Office Tariyani No.2</v>
       </c>
       <c r="F88" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G88" t="str">
-        <v>9003000119</v>
+        <v>9003000044</v>
       </c>
       <c r="H88" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I88" t="str">
         <v>0304</v>
@@ -5942,7 +5942,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M88" t="str">
-        <v>30000942361</v>
+        <v>30000348436</v>
       </c>
       <c r="N88" t="str">
         <v>State Bank of India</v>
@@ -5951,48 +5951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P88" t="str">
-        <v>SBIN0005556</v>
+        <v>SBIN0003486</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>0300026</v>
+        <v>0300072</v>
       </c>
       <c r="B89" t="str">
-        <v>SAVITA KHATUN</v>
+        <v>RANJIT MAHTO</v>
       </c>
       <c r="C89" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D89" t="str">
-        <v>03024</v>
+        <v>03063</v>
       </c>
       <c r="E89" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Primary School Piprahi No.2</v>
       </c>
       <c r="F89" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G89" t="str">
-        <v>9003000026</v>
+        <v>9003000072</v>
       </c>
       <c r="H89" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I89" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J89" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K89" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L89" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M89" t="str">
-        <v>30000205894</v>
+        <v>30000570168</v>
       </c>
       <c r="N89" t="str">
         <v>State Bank of India</v>
@@ -6001,48 +6001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P89" t="str">
-        <v>SBIN0008930</v>
+        <v>SBIN0001122</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>0300055</v>
+        <v>0300030</v>
       </c>
       <c r="B90" t="str">
-        <v>SANJAY TIWARI M</v>
+        <v>ANITA TIWARI</v>
       </c>
       <c r="C90" t="str">
-        <v>Teacher</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D90" t="str">
-        <v>03047</v>
+        <v>03029</v>
       </c>
       <c r="E90" t="str">
-        <v>CDPO Office Purnahiya</v>
+        <v>Project Girls High School Tariyani No.2</v>
       </c>
       <c r="F90" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G90" t="str">
-        <v>9003000055</v>
+        <v>9003000030</v>
       </c>
       <c r="H90" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I90" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J90" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K90" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L90" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M90" t="str">
-        <v>30000435545</v>
+        <v>30000237570</v>
       </c>
       <c r="N90" t="str">
         <v>State Bank of India</v>
@@ -6051,48 +6051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P90" t="str">
-        <v>SBIN0002142</v>
+        <v>SBIN0009135</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>0300087</v>
+        <v>0300119</v>
       </c>
       <c r="B91" t="str">
-        <v>NIRMALA RAI</v>
+        <v>ABDUL KALAM PRASAD</v>
       </c>
       <c r="C91" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D91" t="str">
-        <v>03024</v>
+        <v>03090</v>
       </c>
       <c r="E91" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>UCO Bank, Sheohar</v>
       </c>
       <c r="F91" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G91" t="str">
-        <v>9003000087</v>
+        <v>9003000119</v>
       </c>
       <c r="H91" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I91" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J91" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K91" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L91" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M91" t="str">
-        <v>30000688953</v>
+        <v>30000942361</v>
       </c>
       <c r="N91" t="str">
         <v>State Bank of India</v>
@@ -6101,39 +6101,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P91" t="str">
-        <v>SBIN0004429</v>
+        <v>SBIN0008032</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>0300052</v>
+        <v>0300112</v>
       </c>
       <c r="B92" t="str">
-        <v>MD. SHAHID THAKUR</v>
+        <v>PRIYANKA DEVI</v>
       </c>
       <c r="C92" t="str">
-        <v>Accountant</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D92" t="str">
-        <v>03044</v>
+        <v>03087</v>
       </c>
       <c r="E92" t="str">
-        <v>Panchayat Bhawan Tariyani No.4</v>
+        <v>Punjab National Bank, Tariyani</v>
       </c>
       <c r="F92" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G92" t="str">
-        <v>9003000052</v>
+        <v>9003000112</v>
       </c>
       <c r="H92" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I92" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J92" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K92" t="str">
         <v>0305</v>
@@ -6142,7 +6142,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M92" t="str">
-        <v>30000411788</v>
+        <v>30000886928</v>
       </c>
       <c r="N92" t="str">
         <v>State Bank of India</v>
@@ -6151,33 +6151,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P92" t="str">
-        <v>SBIN0004816</v>
+        <v>SBIN0009218</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>0300125</v>
+        <v>0300059</v>
       </c>
       <c r="B93" t="str">
-        <v>SAVITA RAI</v>
+        <v>VINOD SINGH</v>
       </c>
       <c r="C93" t="str">
-        <v>Assistant Manager</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D93" t="str">
-        <v>03097</v>
+        <v>03053</v>
       </c>
       <c r="E93" t="str">
-        <v>Head Post Office, Piprahi</v>
+        <v>Panchayat Bhawan Purnahiya No.2</v>
       </c>
       <c r="F93" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G93" t="str">
-        <v>9003000125</v>
+        <v>9003000059</v>
       </c>
       <c r="H93" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I93" t="str">
         <v>0302</v>
@@ -6186,13 +6186,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K93" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L93" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M93" t="str">
-        <v>30000989875</v>
+        <v>30000467221</v>
       </c>
       <c r="N93" t="str">
         <v>State Bank of India</v>
@@ -6201,39 +6201,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P93" t="str">
-        <v>SBIN0003720</v>
+        <v>SBIN0005258</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>0300038</v>
+        <v>0300047</v>
       </c>
       <c r="B94" t="str">
-        <v>RAVI SINGH</v>
+        <v>MANOJ DEVI</v>
       </c>
       <c r="C94" t="str">
-        <v>Assistant Teacher</v>
+        <v>Accountant</v>
       </c>
       <c r="D94" t="str">
-        <v>03034</v>
+        <v>03043</v>
       </c>
       <c r="E94" t="str">
-        <v>Block Education Office Tariyani No.4</v>
+        <v>Block Office Tariyani No.4</v>
       </c>
       <c r="F94" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G94" t="str">
-        <v>9003000038</v>
+        <v>9003000047</v>
       </c>
       <c r="H94" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I94" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J94" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K94" t="str">
         <v>0305</v>
@@ -6242,7 +6242,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M94" t="str">
-        <v>30000300922</v>
+        <v>30000372193</v>
       </c>
       <c r="N94" t="str">
         <v>State Bank of India</v>
@@ -6251,48 +6251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P94" t="str">
-        <v>SBIN0005246</v>
+        <v>SBIN0002609</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>0300004</v>
+        <v>0300026</v>
       </c>
       <c r="B95" t="str">
-        <v>SANTOSH JHA</v>
+        <v>SUNIL OJHA</v>
       </c>
       <c r="C95" t="str">
-        <v>Lecturer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D95" t="str">
-        <v>03004</v>
+        <v>03026</v>
       </c>
       <c r="E95" t="str">
-        <v>Block Office Piprahi No.3</v>
+        <v>Kanya Middle School Purnahiya</v>
       </c>
       <c r="F95" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G95" t="str">
-        <v>9003000004</v>
+        <v>9003000026</v>
       </c>
       <c r="H95" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I95" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J95" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K95" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L95" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M95" t="str">
-        <v>30000031676</v>
+        <v>30000205894</v>
       </c>
       <c r="N95" t="str">
         <v>State Bank of India</v>
@@ -6301,39 +6301,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P95" t="str">
-        <v>SBIN0002119</v>
+        <v>SBIN0003302</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>0300002</v>
+        <v>0300003</v>
       </c>
       <c r="B96" t="str">
-        <v>REKHA RAM</v>
+        <v>NITISH DEVI</v>
       </c>
       <c r="C96" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D96" t="str">
-        <v>03002</v>
+        <v>03003</v>
       </c>
       <c r="E96" t="str">
-        <v>Block Agriculture Office Tariyani No.3</v>
+        <v>Middle School Tariyani No.4</v>
       </c>
       <c r="F96" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G96" t="str">
-        <v>9003000002</v>
+        <v>9003000003</v>
       </c>
       <c r="H96" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I96" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J96" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K96" t="str">
         <v>0305</v>
@@ -6342,7 +6342,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M96" t="str">
-        <v>30000015838</v>
+        <v>30000023757</v>
       </c>
       <c r="N96" t="str">
         <v>State Bank of India</v>
@@ -6351,48 +6351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P96" t="str">
-        <v>SBIN0003954</v>
+        <v>SBIN0005498</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0300123</v>
+        <v>0300126</v>
       </c>
       <c r="B97" t="str">
-        <v>RINKU DEVI</v>
+        <v>SURESH PASWAN</v>
       </c>
       <c r="C97" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D97" t="str">
-        <v>03094</v>
+        <v>03097</v>
       </c>
       <c r="E97" t="str">
-        <v>LIC Branch Office, Tariyani</v>
+        <v>Central Bank of India, Sheohar</v>
       </c>
       <c r="F97" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G97" t="str">
-        <v>9003000123</v>
+        <v>9003000126</v>
       </c>
       <c r="H97" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I97" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J97" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K97" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L97" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M97" t="str">
-        <v>30000974037</v>
+        <v>30000997794</v>
       </c>
       <c r="N97" t="str">
         <v>State Bank of India</v>
@@ -6401,48 +6401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P97" t="str">
-        <v>SBIN0001025</v>
+        <v>SBIN0005768</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>0300057</v>
+        <v>0300096</v>
       </c>
       <c r="B98" t="str">
-        <v>MANOJ SINGH</v>
+        <v>KIRAN RAI</v>
       </c>
       <c r="C98" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D98" t="str">
-        <v>03049</v>
+        <v>03078</v>
       </c>
       <c r="E98" t="str">
-        <v>Block Agriculture Office Purnahiya No.4</v>
+        <v>Minor Irrigation Office Dumri Katsari</v>
       </c>
       <c r="F98" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G98" t="str">
-        <v>9003000057</v>
+        <v>9003000096</v>
       </c>
       <c r="H98" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I98" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J98" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K98" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L98" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M98" t="str">
-        <v>30000451383</v>
+        <v>30000760224</v>
       </c>
       <c r="N98" t="str">
         <v>State Bank of India</v>
@@ -6451,39 +6451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P98" t="str">
-        <v>SBIN0004762</v>
+        <v>SBIN0007447</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>0300032</v>
+        <v>0300115</v>
       </c>
       <c r="B99" t="str">
-        <v>KIRAN MISHRA</v>
+        <v>RANJIT PRASAD</v>
       </c>
       <c r="C99" t="str">
-        <v>Senior Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D99" t="str">
-        <v>03029</v>
+        <v>03090</v>
       </c>
       <c r="E99" t="str">
-        <v>Panchayat Bhawan Sheohar No.1</v>
+        <v>UCO Bank, Sheohar</v>
       </c>
       <c r="F99" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G99" t="str">
-        <v>9003000032</v>
+        <v>9003000115</v>
       </c>
       <c r="H99" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I99" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J99" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K99" t="str">
         <v>0301</v>
@@ -6492,7 +6492,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M99" t="str">
-        <v>30000253408</v>
+        <v>30000910685</v>
       </c>
       <c r="N99" t="str">
         <v>State Bank of India</v>
@@ -6501,48 +6501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P99" t="str">
-        <v>SBIN0006111</v>
+        <v>SBIN0002869</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>0300006</v>
+        <v>0300087</v>
       </c>
       <c r="B100" t="str">
-        <v>AJAY KHATUN</v>
+        <v>ANIL KUMAR</v>
       </c>
       <c r="C100" t="str">
-        <v>Senior Teacher</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D100" t="str">
-        <v>03006</v>
+        <v>03073</v>
       </c>
       <c r="E100" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F100" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G100" t="str">
-        <v>9003000006</v>
+        <v>9003000087</v>
       </c>
       <c r="H100" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I100" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J100" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K100" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L100" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M100" t="str">
-        <v>30000047514</v>
+        <v>30000688953</v>
       </c>
       <c r="N100" t="str">
         <v>State Bank of India</v>
@@ -6551,39 +6551,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P100" t="str">
-        <v>SBIN0006535</v>
+        <v>SBIN0009485</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>0300069</v>
+        <v>0300081</v>
       </c>
       <c r="B101" t="str">
-        <v>PRIYANKA VERMA</v>
+        <v>SANTOSH VERMA</v>
       </c>
       <c r="C101" t="str">
-        <v>Data Entry Operator</v>
+        <v>Clerk</v>
       </c>
       <c r="D101" t="str">
-        <v>03059</v>
+        <v>03068</v>
       </c>
       <c r="E101" t="str">
-        <v>Project Girls High School Piprahi</v>
+        <v>CDPO Office Piprahi No.3</v>
       </c>
       <c r="F101" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G101" t="str">
-        <v>9003000069</v>
+        <v>9003000081</v>
       </c>
       <c r="H101" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I101" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J101" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K101" t="str">
         <v>0302</v>
@@ -6592,7 +6592,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M101" t="str">
-        <v>30000546411</v>
+        <v>30000641439</v>
       </c>
       <c r="N101" t="str">
         <v>State Bank of India</v>
@@ -6601,48 +6601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P101" t="str">
-        <v>SBIN0009268</v>
+        <v>SBIN0001969</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>0300116</v>
+        <v>0300013</v>
       </c>
       <c r="B102" t="str">
-        <v>VIJAY KUMAR</v>
+        <v>SANTOSH SINGH</v>
       </c>
       <c r="C102" t="str">
-        <v>Assistant Manager</v>
+        <v>Section Officer</v>
       </c>
       <c r="D102" t="str">
-        <v>03091</v>
+        <v>03013</v>
       </c>
       <c r="E102" t="str">
-        <v>BSNL Exchange, Dumri Katsari</v>
+        <v>Primary School Tariyani</v>
       </c>
       <c r="F102" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G102" t="str">
-        <v>9003000116</v>
+        <v>9003000013</v>
       </c>
       <c r="H102" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I102" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="J102" t="str">
-        <v>Others</v>
+        <v>Tariyani</v>
       </c>
       <c r="K102" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L102" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M102" t="str">
-        <v>30000918604</v>
+        <v>30000102947</v>
       </c>
       <c r="N102" t="str">
         <v>State Bank of India</v>
@@ -6651,48 +6651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P102" t="str">
-        <v>SBIN0007763</v>
+        <v>SBIN0003934</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>0300088</v>
+        <v>0300065</v>
       </c>
       <c r="B103" t="str">
-        <v>RINKU OJHA</v>
+        <v>SUNITA PRASAD</v>
       </c>
       <c r="C103" t="str">
-        <v>Junior Engineer</v>
+        <v>Teacher</v>
       </c>
       <c r="D103" t="str">
-        <v>03071</v>
+        <v>03058</v>
       </c>
       <c r="E103" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>Block Education Office Sheohar</v>
       </c>
       <c r="F103" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G103" t="str">
-        <v>9003000088</v>
+        <v>9003000065</v>
       </c>
       <c r="H103" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I103" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J103" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K103" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L103" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M103" t="str">
-        <v>30000696872</v>
+        <v>30000514735</v>
       </c>
       <c r="N103" t="str">
         <v>State Bank of India</v>
@@ -6701,39 +6701,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P103" t="str">
-        <v>SBIN0003089</v>
+        <v>SBIN0009716</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>0300047</v>
+        <v>0300009</v>
       </c>
       <c r="B104" t="str">
-        <v>SURESH CHAUDHARY E</v>
+        <v>MAHESH PASWAN</v>
       </c>
       <c r="C104" t="str">
-        <v>Teacher</v>
+        <v>Lecturer</v>
       </c>
       <c r="D104" t="str">
-        <v>03010</v>
+        <v>03009</v>
       </c>
       <c r="E104" t="str">
-        <v>Block Office Sheohar No.1</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F104" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G104" t="str">
-        <v>9003000047</v>
+        <v>9003000009</v>
       </c>
       <c r="H104" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I104" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J104" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K104" t="str">
         <v>0301</v>
@@ -6742,7 +6742,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M104" t="str">
-        <v>30000372193</v>
+        <v>30000071271</v>
       </c>
       <c r="N104" t="str">
         <v>State Bank of India</v>
@@ -6751,48 +6751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P104" t="str">
-        <v>SBIN0008239</v>
+        <v>SBIN0008638</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>0300117</v>
+        <v>0300075</v>
       </c>
       <c r="B105" t="str">
-        <v>ASHA ALAM T</v>
+        <v>MD. IRFAN SAH</v>
       </c>
       <c r="C105" t="str">
-        <v>Postmaster</v>
+        <v>Clerk</v>
       </c>
       <c r="D105" t="str">
-        <v>03092</v>
+        <v>03028</v>
       </c>
       <c r="E105" t="str">
-        <v>Head Post Office, Dumri Katsari</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F105" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G105" t="str">
-        <v>9003000117</v>
+        <v>9003000075</v>
       </c>
       <c r="H105" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I105" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J105" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K105" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L105" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M105" t="str">
-        <v>30000926523</v>
+        <v>30000593925</v>
       </c>
       <c r="N105" t="str">
         <v>State Bank of India</v>
@@ -6801,48 +6801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P105" t="str">
-        <v>SBIN0008359</v>
+        <v>SBIN0008790</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>0300094</v>
+        <v>0300015</v>
       </c>
       <c r="B106" t="str">
-        <v>SAVITA KUMAR</v>
+        <v>MUKESH JHA</v>
       </c>
       <c r="C106" t="str">
-        <v>Revenue Officer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D106" t="str">
-        <v>03072</v>
+        <v>03015</v>
       </c>
       <c r="E106" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>Middle School Sheohar No.4</v>
       </c>
       <c r="F106" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G106" t="str">
-        <v>9003000094</v>
+        <v>9003000015</v>
       </c>
       <c r="H106" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I106" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J106" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K106" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L106" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M106" t="str">
-        <v>30000744386</v>
+        <v>30000118785</v>
       </c>
       <c r="N106" t="str">
         <v>State Bank of India</v>
@@ -6851,48 +6851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P106" t="str">
-        <v>SBIN0005397</v>
+        <v>SBIN0008562</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>0300019</v>
+        <v>0300024</v>
       </c>
       <c r="B107" t="str">
-        <v>SANJAY PRASAD</v>
+        <v>ANITA MISHRA I</v>
       </c>
       <c r="C107" t="str">
-        <v>Senior Teacher</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D107" t="str">
-        <v>03017</v>
+        <v>03024</v>
       </c>
       <c r="E107" t="str">
-        <v>Block Agriculture Office Sheohar No.1</v>
+        <v>Primary School Piprahi No.4</v>
       </c>
       <c r="F107" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G107" t="str">
-        <v>9003000019</v>
+        <v>9003000024</v>
       </c>
       <c r="H107" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I107" t="str">
+        <v>999999</v>
+      </c>
+      <c r="J107" t="str">
+        <v>Others</v>
+      </c>
+      <c r="K107" t="str">
         <v>0302</v>
       </c>
-      <c r="J107" t="str">
+      <c r="L107" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K107" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L107" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M107" t="str">
-        <v>30000150461</v>
+        <v>30000190056</v>
       </c>
       <c r="N107" t="str">
         <v>State Bank of India</v>
@@ -6901,48 +6901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P107" t="str">
-        <v>SBIN0005701</v>
+        <v>SBIN0004222</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>0300081</v>
+        <v>0300039</v>
       </c>
       <c r="B108" t="str">
-        <v>ANITA ANSARI</v>
+        <v>SUNIL GUPTA</v>
       </c>
       <c r="C108" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D108" t="str">
-        <v>03066</v>
+        <v>03036</v>
       </c>
       <c r="E108" t="str">
-        <v>High School Tariyani No.4</v>
+        <v>High School Dumri Katsari No.3</v>
       </c>
       <c r="F108" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G108" t="str">
-        <v>9003000081</v>
+        <v>9003000039</v>
       </c>
       <c r="H108" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I108" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J108" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K108" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L108" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M108" t="str">
-        <v>30000641439</v>
+        <v>30000308841</v>
       </c>
       <c r="N108" t="str">
         <v>State Bank of India</v>
@@ -6951,48 +6951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P108" t="str">
-        <v>SBIN0005245</v>
+        <v>SBIN0007984</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>0300024</v>
+        <v>0300076</v>
       </c>
       <c r="B109" t="str">
-        <v>PRAMOD SINHA</v>
+        <v>MD. SHAHID MISHRA</v>
       </c>
       <c r="C109" t="str">
-        <v>Assistant Teacher</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D109" t="str">
-        <v>03022</v>
+        <v>03065</v>
       </c>
       <c r="E109" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>PHC Purnahiya No.1</v>
       </c>
       <c r="F109" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G109" t="str">
-        <v>9003000024</v>
+        <v>9003000076</v>
       </c>
       <c r="H109" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I109" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J109" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K109" t="str">
         <v>0303</v>
       </c>
-      <c r="J109" t="str">
+      <c r="L109" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="K109" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L109" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M109" t="str">
-        <v>30000190056</v>
+        <v>30000601844</v>
       </c>
       <c r="N109" t="str">
         <v>State Bank of India</v>
@@ -7001,39 +7001,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P109" t="str">
-        <v>SBIN0007218</v>
+        <v>SBIN0009536</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>0300101</v>
+        <v>0300123</v>
       </c>
       <c r="B110" t="str">
-        <v>MD. IRFAN CHAUDHARY</v>
+        <v>MD. SHAHID JHA</v>
       </c>
       <c r="C110" t="str">
-        <v>Assistant Engineer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D110" t="str">
-        <v>03074</v>
+        <v>03095</v>
       </c>
       <c r="E110" t="str">
-        <v>Block Office Tariyani</v>
+        <v>State Bank of India, Tariyani</v>
       </c>
       <c r="F110" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G110" t="str">
-        <v>9003000101</v>
+        <v>9003000123</v>
       </c>
       <c r="H110" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I110" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J110" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K110" t="str">
         <v>0305</v>
@@ -7042,7 +7042,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M110" t="str">
-        <v>30000799819</v>
+        <v>30000974037</v>
       </c>
       <c r="N110" t="str">
         <v>State Bank of India</v>
@@ -7051,33 +7051,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P110" t="str">
-        <v>SBIN0003386</v>
+        <v>SBIN0006515</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>0300090</v>
+        <v>0300056</v>
       </c>
       <c r="B111" t="str">
-        <v>ANITA ANSARI Y</v>
+        <v>NASREEN SINHA</v>
       </c>
       <c r="C111" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D111" t="str">
-        <v>03073</v>
+        <v>03050</v>
       </c>
       <c r="E111" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Block Office Dumri Katsari No.2</v>
       </c>
       <c r="F111" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G111" t="str">
-        <v>9003000090</v>
+        <v>9003000056</v>
       </c>
       <c r="H111" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I111" t="str">
         <v>0304</v>
@@ -7086,13 +7086,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K111" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L111" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M111" t="str">
-        <v>30000712710</v>
+        <v>30000443464</v>
       </c>
       <c r="N111" t="str">
         <v>State Bank of India</v>
@@ -7101,48 +7101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P111" t="str">
-        <v>SBIN0005629</v>
+        <v>SBIN0005035</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>0300029</v>
+        <v>0300092</v>
       </c>
       <c r="B112" t="str">
-        <v>SURESH KHATUN</v>
+        <v>ALOK OJHA V</v>
       </c>
       <c r="C112" t="str">
-        <v>Head Clerk</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D112" t="str">
-        <v>03026</v>
+        <v>03073</v>
       </c>
       <c r="E112" t="str">
-        <v>Block Agriculture Office Dumri Katsari No.2</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F112" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G112" t="str">
-        <v>9003000029</v>
+        <v>9003000092</v>
       </c>
       <c r="H112" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I112" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="J112" t="str">
-        <v>Dumri Katsari</v>
+        <v>Others</v>
       </c>
       <c r="K112" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L112" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M112" t="str">
-        <v>30000229651</v>
+        <v>30000728548</v>
       </c>
       <c r="N112" t="str">
         <v>State Bank of India</v>
@@ -7151,39 +7151,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P112" t="str">
-        <v>SBIN0002957</v>
+        <v>SBIN0006064</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>0300079</v>
+        <v>0300031</v>
       </c>
       <c r="B113" t="str">
-        <v>DEEPAK SINHA</v>
+        <v>RINKU VERMA</v>
       </c>
       <c r="C113" t="str">
-        <v>Clerk</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D113" t="str">
-        <v>03059</v>
+        <v>03030</v>
       </c>
       <c r="E113" t="str">
-        <v>Project Girls High School Piprahi</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F113" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G113" t="str">
-        <v>9003000079</v>
+        <v>9003000031</v>
       </c>
       <c r="H113" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I113" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J113" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K113" t="str">
         <v>0302</v>
@@ -7192,7 +7192,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M113" t="str">
-        <v>30000625601</v>
+        <v>30000245489</v>
       </c>
       <c r="N113" t="str">
         <v>State Bank of India</v>
@@ -7201,39 +7201,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P113" t="str">
-        <v>SBIN0008838</v>
+        <v>SBIN0006302</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>0300092</v>
+        <v>0300125</v>
       </c>
       <c r="B114" t="str">
-        <v>POONAM PANDEY</v>
+        <v>REKHA CHAUDHARY</v>
       </c>
       <c r="C114" t="str">
-        <v>Revenue Officer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D114" t="str">
-        <v>03074</v>
+        <v>03095</v>
       </c>
       <c r="E114" t="str">
-        <v>Block Office Tariyani</v>
+        <v>State Bank of India, Tariyani</v>
       </c>
       <c r="F114" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G114" t="str">
-        <v>9003000092</v>
+        <v>9003000125</v>
       </c>
       <c r="H114" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I114" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J114" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K114" t="str">
         <v>0305</v>
@@ -7242,7 +7242,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M114" t="str">
-        <v>30000728548</v>
+        <v>30000989875</v>
       </c>
       <c r="N114" t="str">
         <v>State Bank of India</v>
@@ -7251,48 +7251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P114" t="str">
-        <v>SBIN0005527</v>
+        <v>SBIN0008440</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>0300009</v>
+        <v>0300113</v>
       </c>
       <c r="B115" t="str">
-        <v>DEEPAK KUMAR</v>
+        <v>VINOD ANSARI</v>
       </c>
       <c r="C115" t="str">
-        <v>Section Officer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D115" t="str">
-        <v>03009</v>
+        <v>03088</v>
       </c>
       <c r="E115" t="str">
-        <v>High School Dumri Katsari No.1</v>
+        <v>Punjab National Bank, Piprahi</v>
       </c>
       <c r="F115" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G115" t="str">
-        <v>9003000009</v>
+        <v>9003000113</v>
       </c>
       <c r="H115" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I115" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J115" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K115" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L115" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M115" t="str">
-        <v>30000071271</v>
+        <v>30000894847</v>
       </c>
       <c r="N115" t="str">
         <v>State Bank of India</v>
@@ -7301,48 +7301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P115" t="str">
-        <v>SBIN0001643</v>
+        <v>SBIN0007696</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>0300013</v>
+        <v>0300100</v>
       </c>
       <c r="B116" t="str">
-        <v>ARVIND KHATUN</v>
+        <v>USHA SINGH</v>
       </c>
       <c r="C116" t="str">
-        <v>Headmaster</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D116" t="str">
-        <v>03012</v>
+        <v>03078</v>
       </c>
       <c r="E116" t="str">
-        <v>PHC Tariyani No.3</v>
+        <v>Minor Irrigation Office Dumri Katsari</v>
       </c>
       <c r="F116" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G116" t="str">
-        <v>9003000013</v>
+        <v>9003000100</v>
       </c>
       <c r="H116" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I116" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J116" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K116" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L116" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M116" t="str">
-        <v>30000102947</v>
+        <v>30000791900</v>
       </c>
       <c r="N116" t="str">
         <v>State Bank of India</v>
@@ -7351,48 +7351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P116" t="str">
-        <v>SBIN0007505</v>
+        <v>SBIN0007623</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>0300076</v>
+        <v>0300101</v>
       </c>
       <c r="B117" t="str">
-        <v>ASHA KUMAR</v>
+        <v>SUNITA RAI</v>
       </c>
       <c r="C117" t="str">
-        <v>Teacher</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D117" t="str">
-        <v>03064</v>
+        <v>03007</v>
       </c>
       <c r="E117" t="str">
-        <v>CDPO Office Tariyani</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="F117" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G117" t="str">
-        <v>9003000076</v>
+        <v>9003000101</v>
       </c>
       <c r="H117" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I117" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J117" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K117" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L117" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M117" t="str">
-        <v>30000601844</v>
+        <v>30000799819</v>
       </c>
       <c r="N117" t="str">
         <v>State Bank of India</v>
@@ -7401,48 +7401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P117" t="str">
-        <v>SBIN0004817</v>
+        <v>SBIN0008014</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>0300050</v>
+        <v>0300017</v>
       </c>
       <c r="B118" t="str">
-        <v>SUNIL PRASAD</v>
+        <v>SUNITA OJHA</v>
       </c>
       <c r="C118" t="str">
-        <v>Accountant</v>
+        <v>Headmaster</v>
       </c>
       <c r="D118" t="str">
-        <v>03042</v>
+        <v>03017</v>
       </c>
       <c r="E118" t="str">
-        <v>PHC Purnahiya No.1</v>
+        <v>Primary School Dumri Katsari No.1</v>
       </c>
       <c r="F118" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G118" t="str">
-        <v>9003000050</v>
+        <v>9003000017</v>
       </c>
       <c r="H118" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I118" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J118" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K118" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L118" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M118" t="str">
-        <v>30000395950</v>
+        <v>30000134623</v>
       </c>
       <c r="N118" t="str">
         <v>State Bank of India</v>
@@ -7451,48 +7451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P118" t="str">
-        <v>SBIN0004956</v>
+        <v>SBIN0001827</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>0300007</v>
+        <v>0300116</v>
       </c>
       <c r="B119" t="str">
-        <v>SANJAY TIWARI</v>
+        <v>REKHA RAI</v>
       </c>
       <c r="C119" t="str">
-        <v>Senior Teacher</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D119" t="str">
-        <v>03007</v>
+        <v>03091</v>
       </c>
       <c r="E119" t="str">
-        <v>CDPO Office Piprahi No.2</v>
+        <v>Punjab National Bank, Dumri Katsari</v>
       </c>
       <c r="F119" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G119" t="str">
-        <v>9003000007</v>
+        <v>9003000116</v>
       </c>
       <c r="H119" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I119" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J119" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K119" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L119" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M119" t="str">
-        <v>30000055433</v>
+        <v>30000918604</v>
       </c>
       <c r="N119" t="str">
         <v>State Bank of India</v>
@@ -7501,48 +7501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P119" t="str">
-        <v>SBIN0006576</v>
+        <v>SBIN0009603</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>0300075</v>
+        <v>0300094</v>
       </c>
       <c r="B120" t="str">
-        <v>KUMARI ANJALI MAHTO</v>
+        <v>FARHAT SAH</v>
       </c>
       <c r="C120" t="str">
-        <v>Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D120" t="str">
-        <v>03063</v>
+        <v>03072</v>
       </c>
       <c r="E120" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F120" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G120" t="str">
-        <v>9003000075</v>
+        <v>9003000094</v>
       </c>
       <c r="H120" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I120" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J120" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K120" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L120" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M120" t="str">
-        <v>30000593925</v>
+        <v>30000744386</v>
       </c>
       <c r="N120" t="str">
         <v>State Bank of India</v>
@@ -7551,48 +7551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P120" t="str">
-        <v>SBIN0006779</v>
+        <v>SBIN0006065</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>0300114</v>
+        <v>0300028</v>
       </c>
       <c r="B121" t="str">
-        <v>SANTOSH PRASAD</v>
+        <v>ANITA VERMA</v>
       </c>
       <c r="C121" t="str">
-        <v>Administrative Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D121" t="str">
-        <v>03086</v>
+        <v>03028</v>
       </c>
       <c r="E121" t="str">
-        <v>Bank of India, Piprahi</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F121" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G121" t="str">
-        <v>9003000114</v>
+        <v>9003000028</v>
       </c>
       <c r="H121" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I121" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J121" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K121" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L121" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M121" t="str">
-        <v>30000902766</v>
+        <v>30000221732</v>
       </c>
       <c r="N121" t="str">
         <v>State Bank of India</v>
@@ -7601,48 +7601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P121" t="str">
-        <v>SBIN0004192</v>
+        <v>SBIN0004159</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>0300008</v>
+        <v>0300085</v>
       </c>
       <c r="B122" t="str">
-        <v>REKHA DEVI</v>
+        <v>MAHESH YADAV</v>
       </c>
       <c r="C122" t="str">
-        <v>Lecturer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D122" t="str">
-        <v>03008</v>
+        <v>03030</v>
       </c>
       <c r="E122" t="str">
-        <v>Project Girls High School Purnahiya No.3</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F122" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G122" t="str">
-        <v>9003000008</v>
+        <v>9003000085</v>
       </c>
       <c r="H122" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I122" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J122" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K122" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L122" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M122" t="str">
-        <v>30000063352</v>
+        <v>30000673115</v>
       </c>
       <c r="N122" t="str">
         <v>State Bank of India</v>
@@ -7651,48 +7651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P122" t="str">
-        <v>SBIN0002228</v>
+        <v>SBIN0001284</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>0300105</v>
+        <v>0300043</v>
       </c>
       <c r="B123" t="str">
-        <v>MANOJ MAHTO</v>
+        <v>NASREEN PASWAN</v>
       </c>
       <c r="C123" t="str">
-        <v>Junior Engineer</v>
+        <v>Accountant</v>
       </c>
       <c r="D123" t="str">
-        <v>03077</v>
+        <v>03040</v>
       </c>
       <c r="E123" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>High School Dumri Katsari No.4</v>
       </c>
       <c r="F123" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G123" t="str">
-        <v>9003000105</v>
+        <v>9003000043</v>
       </c>
       <c r="H123" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I123" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J123" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K123" t="str">
         <v>0304</v>
       </c>
-      <c r="J123" t="str">
+      <c r="L123" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="K123" t="str">
-        <v>0302</v>
-      </c>
-      <c r="L123" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="M123" t="str">
-        <v>30000831495</v>
+        <v>30000340517</v>
       </c>
       <c r="N123" t="str">
         <v>State Bank of India</v>
@@ -7701,33 +7701,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P123" t="str">
-        <v>SBIN0005258</v>
+        <v>SBIN0007841</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>0300051</v>
+        <v>0300108</v>
       </c>
       <c r="B124" t="str">
-        <v>MAMTA SINGH</v>
+        <v>FARHAT JHA</v>
       </c>
       <c r="C124" t="str">
-        <v>Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D124" t="str">
-        <v>03043</v>
+        <v>03083</v>
       </c>
       <c r="E124" t="str">
-        <v>Primary School Dumri Katsari No.1</v>
+        <v>Central Bank of India, Piprahi</v>
       </c>
       <c r="F124" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G124" t="str">
-        <v>9003000051</v>
+        <v>9003000108</v>
       </c>
       <c r="H124" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I124" t="str">
         <v>0302</v>
@@ -7736,13 +7736,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K124" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L124" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M124" t="str">
-        <v>30000403869</v>
+        <v>30000855252</v>
       </c>
       <c r="N124" t="str">
         <v>State Bank of India</v>
@@ -7751,21 +7751,21 @@
         <v>Sheohar</v>
       </c>
       <c r="P124" t="str">
-        <v>SBIN0006178</v>
+        <v>SBIN0001163</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>0300095</v>
+        <v>0300099</v>
       </c>
       <c r="B125" t="str">
-        <v>AJAY GUPTA</v>
+        <v>NEHA RAI</v>
       </c>
       <c r="C125" t="str">
         <v>Revenue Officer</v>
       </c>
       <c r="D125" t="str">
-        <v>03076</v>
+        <v>03052</v>
       </c>
       <c r="E125" t="str">
         <v>Circle Office Piprahi</v>
@@ -7774,16 +7774,16 @@
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G125" t="str">
-        <v>9003000095</v>
+        <v>9003000099</v>
       </c>
       <c r="H125" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I125" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J125" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K125" t="str">
         <v>0302</v>
@@ -7792,7 +7792,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M125" t="str">
-        <v>30000752305</v>
+        <v>30000783981</v>
       </c>
       <c r="N125" t="str">
         <v>State Bank of India</v>
@@ -7801,48 +7801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P125" t="str">
-        <v>SBIN0001075</v>
+        <v>SBIN0001926</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>0300084</v>
+        <v>0300058</v>
       </c>
       <c r="B126" t="str">
-        <v>USHA DEVI</v>
+        <v>MD. SHAHID TIWARI</v>
       </c>
       <c r="C126" t="str">
-        <v>Teacher</v>
+        <v>Accountant</v>
       </c>
       <c r="D126" t="str">
-        <v>03069</v>
+        <v>03052</v>
       </c>
       <c r="E126" t="str">
-        <v>Project Girls High School Purnahiya No.2</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F126" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G126" t="str">
-        <v>9003000084</v>
+        <v>9003000058</v>
       </c>
       <c r="H126" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I126" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J126" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K126" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L126" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M126" t="str">
-        <v>30000665196</v>
+        <v>30000459302</v>
       </c>
       <c r="N126" t="str">
         <v>State Bank of India</v>
@@ -7851,39 +7851,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P126" t="str">
-        <v>SBIN0005115</v>
+        <v>SBIN0007892</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>0300016</v>
+        <v>0300007</v>
       </c>
       <c r="B127" t="str">
-        <v>SANTOSH RAM</v>
+        <v>MAMTA KUMAR</v>
       </c>
       <c r="C127" t="str">
         <v>Senior Teacher</v>
       </c>
       <c r="D127" t="str">
-        <v>03014</v>
+        <v>03007</v>
       </c>
       <c r="E127" t="str">
-        <v>Primary School Sheohar No.4</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="F127" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G127" t="str">
-        <v>9003000016</v>
+        <v>9003000007</v>
       </c>
       <c r="H127" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I127" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J127" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K127" t="str">
         <v>0301</v>
@@ -7892,7 +7892,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M127" t="str">
-        <v>30000126704</v>
+        <v>30000055433</v>
       </c>
       <c r="N127" t="str">
         <v>State Bank of India</v>
@@ -7901,7 +7901,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P127" t="str">
-        <v>SBIN0003432</v>
+        <v>SBIN0006600</v>
       </c>
     </row>
   </sheetData>
@@ -7954,7 +7954,7 @@
         <v>Main</v>
       </c>
       <c r="D2" t="str">
-        <v>Block Office Hall Sheohar, Room 2</v>
+        <v>Middle School Sheohar, Room 2</v>
       </c>
       <c r="E2" t="str">
         <v>0301</v>
@@ -7994,7 +7994,7 @@
         <v>Main</v>
       </c>
       <c r="D4" t="str">
-        <v>Kanya Middle School Purnahiya, Room 1</v>
+        <v>Block Office Hall Purnahiya, Room 1</v>
       </c>
       <c r="E4" t="str">
         <v>0303</v>
@@ -8014,7 +8014,7 @@
         <v>Main</v>
       </c>
       <c r="D5" t="str">
-        <v>High School Dumri Katsari, Room 2</v>
+        <v>Panchayat Bhawan Dumri Katsari, Room 2</v>
       </c>
       <c r="E5" t="str">
         <v>0304</v>
@@ -8034,7 +8034,7 @@
         <v>Main</v>
       </c>
       <c r="D6" t="str">
-        <v>Kanya Middle School Tariyani, Room 3</v>
+        <v>Middle School Tariyani, Room 3</v>
       </c>
       <c r="E6" t="str">
         <v>0305</v>
@@ -8054,7 +8054,7 @@
         <v>Main</v>
       </c>
       <c r="D7" t="str">
-        <v>Block Office Hall Sheohar, Room 1</v>
+        <v>Panchayat Bhawan Sheohar, Room 1</v>
       </c>
       <c r="E7" t="str">
         <v>0301</v>
@@ -8074,7 +8074,7 @@
         <v>Main</v>
       </c>
       <c r="D8" t="str">
-        <v>High School Purnahiya, Room 2</v>
+        <v>Kanya Middle School Purnahiya, Room 2</v>
       </c>
       <c r="E8" t="str">
         <v>0303</v>
@@ -8094,7 +8094,7 @@
         <v>Main</v>
       </c>
       <c r="D9" t="str">
-        <v>Block Office Hall Dumri Katsari, Room 3</v>
+        <v>High School Dumri Katsari, Room 3</v>
       </c>
       <c r="E9" t="str">
         <v>0304</v>
@@ -8114,7 +8114,7 @@
         <v>Main</v>
       </c>
       <c r="D10" t="str">
-        <v>Kanya Middle School Tariyani, Room 1</v>
+        <v>Middle School Tariyani, Room 1</v>
       </c>
       <c r="E10" t="str">
         <v>0305</v>
@@ -8134,7 +8134,7 @@
         <v>Main</v>
       </c>
       <c r="D11" t="str">
-        <v>High School Sheohar, Room 2</v>
+        <v>Panchayat Bhawan Sheohar, Room 2</v>
       </c>
       <c r="E11" t="str">
         <v>0301</v>
@@ -8154,7 +8154,7 @@
         <v>Main</v>
       </c>
       <c r="D12" t="str">
-        <v>Kanya Middle School Piprahi, Room 3</v>
+        <v>Block Office Hall Piprahi, Room 3</v>
       </c>
       <c r="E12" t="str">
         <v>0302</v>
@@ -8174,7 +8174,7 @@
         <v>Main</v>
       </c>
       <c r="D13" t="str">
-        <v>Panchayat Bhawan Purnahiya, Room 1</v>
+        <v>High School Purnahiya, Room 1</v>
       </c>
       <c r="E13" t="str">
         <v>0303</v>

--- a/test-data/TEST_Sheohar_Project.xlsx
+++ b/test-data/TEST_Sheohar_Project.xlsx
@@ -613,7 +613,7 @@
         <v>Saved at</v>
       </c>
       <c r="B4" t="str">
-        <v>13-10-2026 17:15:51</v>
+        <v>13-10-2026 17:27:50</v>
       </c>
     </row>
     <row r="5">
@@ -792,7 +792,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>13-10-2026 17:15:51</v>
+        <v>13-10-2026 17:27:50</v>
       </c>
       <c r="B2" t="str">
         <v>Test data generated (Small — Sheohar style (5 blocks, 6 TC + 6 GC booths))</v>
@@ -1606,43 +1606,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0300097</v>
+        <v>0300053</v>
       </c>
       <c r="B2" t="str">
-        <v>SURESH THAKUR</v>
+        <v>NEHA GUPTA</v>
       </c>
       <c r="C2" t="str">
-        <v>Revenue Officer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D2" t="str">
-        <v>03079</v>
+        <v>03046</v>
       </c>
       <c r="E2" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>Civil Surgeon Office (deputed from other district)</v>
       </c>
       <c r="F2" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G2" t="str">
-        <v>9003000097</v>
+        <v>9003000053</v>
       </c>
       <c r="H2" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I2" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K2" t="str">
         <v>999999</v>
       </c>
-      <c r="J2" t="str">
-        <v>Others</v>
-      </c>
-      <c r="K2" t="str">
-        <v>0305</v>
-      </c>
       <c r="L2" t="str">
-        <v>Tariyani</v>
+        <v>Other District</v>
       </c>
       <c r="M2" t="str">
-        <v>30000768143</v>
+        <v>30000419707</v>
       </c>
       <c r="N2" t="str">
         <v>State Bank of India</v>
@@ -1651,48 +1651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P2" t="str">
-        <v>SBIN0009163</v>
+        <v>SBIN0008550</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0300093</v>
+        <v>0300043</v>
       </c>
       <c r="B3" t="str">
-        <v>SUNITA MAHTO</v>
+        <v>NIRMALA RAM</v>
       </c>
       <c r="C3" t="str">
-        <v>Junior Engineer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D3" t="str">
-        <v>03076</v>
+        <v>03039</v>
       </c>
       <c r="E3" t="str">
-        <v>Circle Office Sheohar</v>
+        <v>Primary School Tariyani No.3</v>
       </c>
       <c r="F3" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G3" t="str">
-        <v>9003000093</v>
+        <v>9003000043</v>
       </c>
       <c r="H3" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I3" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J3" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K3" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L3" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M3" t="str">
-        <v>30000736467</v>
+        <v>30000340517</v>
       </c>
       <c r="N3" t="str">
         <v>State Bank of India</v>
@@ -1701,48 +1701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P3" t="str">
-        <v>SBIN0009597</v>
+        <v>SBIN0009606</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0300082</v>
+        <v>0300001</v>
       </c>
       <c r="B4" t="str">
-        <v>MANOJ PRASAD</v>
+        <v>VIJAY MAHTO</v>
       </c>
       <c r="C4" t="str">
-        <v>Office Assistant</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D4" t="str">
-        <v>03069</v>
+        <v>03001</v>
       </c>
       <c r="E4" t="str">
-        <v>Civil Surgeon Office (deputed from other district)</v>
+        <v>Kanya Middle School Tariyani No.3</v>
       </c>
       <c r="F4" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G4" t="str">
-        <v>9003000082</v>
+        <v>9003000001</v>
       </c>
       <c r="H4" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I4" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J4" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K4" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="L4" t="str">
-        <v>Other District</v>
+        <v>Tariyani</v>
       </c>
       <c r="M4" t="str">
-        <v>30000649358</v>
+        <v>30000007919</v>
       </c>
       <c r="N4" t="str">
         <v>State Bank of India</v>
@@ -1751,48 +1751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P4" t="str">
-        <v>SBIN0004502</v>
+        <v>SBIN0002836</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0300121</v>
+        <v>0300062</v>
       </c>
       <c r="B5" t="str">
-        <v>FARHAT YADAV</v>
+        <v>ANIL SINHA</v>
       </c>
       <c r="C5" t="str">
-        <v>Assistant Manager</v>
+        <v>Clerk</v>
       </c>
       <c r="D5" t="str">
-        <v>03093</v>
+        <v>03054</v>
       </c>
       <c r="E5" t="str">
-        <v>Bank of India, Piprahi</v>
+        <v>Circle Office Purnahiya No.2</v>
       </c>
       <c r="F5" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G5" t="str">
-        <v>9003000121</v>
+        <v>9003000062</v>
       </c>
       <c r="H5" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I5" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J5" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K5" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L5" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M5" t="str">
-        <v>30000958199</v>
+        <v>30000490978</v>
       </c>
       <c r="N5" t="str">
         <v>State Bank of India</v>
@@ -1801,7 +1801,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P5" t="str">
-        <v>SBIN0009680</v>
+        <v>SBIN0003992</v>
       </c>
     </row>
     <row r="6">
@@ -1809,19 +1809,19 @@
         <v>0300021</v>
       </c>
       <c r="B6" t="str">
-        <v>NITISH ANSARI</v>
+        <v>PANKAJ KHATUN</v>
       </c>
       <c r="C6" t="str">
-        <v>Assistant Engineer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D6" t="str">
-        <v>03021</v>
+        <v>03018</v>
       </c>
       <c r="E6" t="str">
-        <v>CDPO Office Piprahi</v>
+        <v>PHED Division Sheohar</v>
       </c>
       <c r="F6" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G6" t="str">
         <v>9003000021</v>
@@ -1830,16 +1830,16 @@
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I6" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J6" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K6" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L6" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M6" t="str">
         <v>30000166299</v>
@@ -1851,48 +1851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P6" t="str">
-        <v>SBIN0006909</v>
+        <v>SBIN0006495</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>0300035</v>
+        <v>0300030</v>
       </c>
       <c r="B7" t="str">
-        <v>NITISH CHAUDHARY</v>
+        <v>SANTOSH YADAV</v>
       </c>
       <c r="C7" t="str">
-        <v>Assistant Teacher</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D7" t="str">
-        <v>03033</v>
+        <v>03026</v>
       </c>
       <c r="E7" t="str">
-        <v>High School Sheohar No.1</v>
+        <v>Circle Office Tariyani No.2</v>
       </c>
       <c r="F7" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G7" t="str">
-        <v>9003000035</v>
+        <v>9003000030</v>
       </c>
       <c r="H7" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I7" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J7" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K7" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L7" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M7" t="str">
-        <v>30000277165</v>
+        <v>30000237570</v>
       </c>
       <c r="N7" t="str">
         <v>State Bank of India</v>
@@ -1901,39 +1901,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P7" t="str">
-        <v>SBIN0009939</v>
+        <v>SBIN0007393</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0300040</v>
+        <v>0300044</v>
       </c>
       <c r="B8" t="str">
-        <v>SHAILESH MISHRA</v>
+        <v>NITISH MISHRA</v>
       </c>
       <c r="C8" t="str">
-        <v>Head Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D8" t="str">
-        <v>03037</v>
+        <v>03040</v>
       </c>
       <c r="E8" t="str">
-        <v>Kanya Middle School Purnahiya No.2</v>
+        <v>Project Girls High School Purnahiya</v>
       </c>
       <c r="F8" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G8" t="str">
-        <v>9003000040</v>
+        <v>9003000044</v>
       </c>
       <c r="H8" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I8" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J8" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K8" t="str">
         <v>0303</v>
@@ -1942,7 +1942,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M8" t="str">
-        <v>30000316760</v>
+        <v>30000348436</v>
       </c>
       <c r="N8" t="str">
         <v>State Bank of India</v>
@@ -1951,48 +1951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P8" t="str">
-        <v>SBIN0002311</v>
+        <v>SBIN0005920</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0300051</v>
+        <v>0300093</v>
       </c>
       <c r="B9" t="str">
-        <v>ANITA OJHA</v>
+        <v>PRIYANKA THAKUR</v>
       </c>
       <c r="C9" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D9" t="str">
-        <v>03027</v>
+        <v>03076</v>
       </c>
       <c r="E9" t="str">
-        <v>Middle School Piprahi</v>
+        <v>Minor Irrigation Office Tariyani</v>
       </c>
       <c r="F9" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G9" t="str">
-        <v>9003000051</v>
+        <v>9003000093</v>
       </c>
       <c r="H9" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I9" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J9" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K9" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L9" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M9" t="str">
-        <v>30000403869</v>
+        <v>30000736467</v>
       </c>
       <c r="N9" t="str">
         <v>State Bank of India</v>
@@ -2001,48 +2001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P9" t="str">
-        <v>SBIN0008309</v>
+        <v>SBIN0005987</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0300083</v>
+        <v>0300068</v>
       </c>
       <c r="B10" t="str">
-        <v>RAMESH PRASAD</v>
+        <v>DINESH YADAV</v>
       </c>
       <c r="C10" t="str">
-        <v>Data Entry Operator</v>
+        <v>Clerk</v>
       </c>
       <c r="D10" t="str">
-        <v>03070</v>
+        <v>03058</v>
       </c>
       <c r="E10" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>Circle Office Tariyani No.3</v>
       </c>
       <c r="F10" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G10" t="str">
-        <v>9003000083</v>
+        <v>9003000068</v>
       </c>
       <c r="H10" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I10" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J10" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K10" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L10" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M10" t="str">
-        <v>30000657277</v>
+        <v>30000538492</v>
       </c>
       <c r="N10" t="str">
         <v>State Bank of India</v>
@@ -2051,33 +2051,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P10" t="str">
-        <v>SBIN0006101</v>
+        <v>SBIN0009583</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>0300086</v>
+        <v>0300020</v>
       </c>
       <c r="B11" t="str">
-        <v>ABDUL KALAM RAI</v>
+        <v>RAJESH GUPTA</v>
       </c>
       <c r="C11" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D11" t="str">
-        <v>03072</v>
+        <v>03017</v>
       </c>
       <c r="E11" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F11" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G11" t="str">
-        <v>9003000086</v>
+        <v>9003000020</v>
       </c>
       <c r="H11" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I11" t="str">
         <v>0303</v>
@@ -2086,13 +2086,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K11" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L11" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M11" t="str">
-        <v>30000681034</v>
+        <v>30000158380</v>
       </c>
       <c r="N11" t="str">
         <v>State Bank of India</v>
@@ -2101,39 +2101,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P11" t="str">
-        <v>SBIN0003466</v>
+        <v>SBIN0006103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>0300019</v>
+        <v>0300040</v>
       </c>
       <c r="B12" t="str">
-        <v>SUNIL YADAV</v>
+        <v>RAKESH KHATUN</v>
       </c>
       <c r="C12" t="str">
-        <v>Headmaster</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D12" t="str">
-        <v>03019</v>
+        <v>03036</v>
       </c>
       <c r="E12" t="str">
-        <v>PHC Sheohar</v>
+        <v>Project Girls High School Sheohar</v>
       </c>
       <c r="F12" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G12" t="str">
-        <v>9003000019</v>
+        <v>9003000040</v>
       </c>
       <c r="H12" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I12" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J12" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K12" t="str">
         <v>0301</v>
@@ -2142,7 +2142,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M12" t="str">
-        <v>30000150461</v>
+        <v>30000316760</v>
       </c>
       <c r="N12" t="str">
         <v>State Bank of India</v>
@@ -2151,33 +2151,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P12" t="str">
-        <v>SBIN0005597</v>
+        <v>SBIN0009078</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0300049</v>
+        <v>0300097</v>
       </c>
       <c r="B13" t="str">
-        <v>PRAMOD VERMA</v>
+        <v>RAMESH ALAM</v>
       </c>
       <c r="C13" t="str">
-        <v>Clerk</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D13" t="str">
-        <v>03045</v>
+        <v>03077</v>
       </c>
       <c r="E13" t="str">
-        <v>CDPO Office Sheohar No.1</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="F13" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G13" t="str">
-        <v>9003000049</v>
+        <v>9003000097</v>
       </c>
       <c r="H13" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I13" t="str">
         <v>0301</v>
@@ -2186,13 +2186,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K13" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L13" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M13" t="str">
-        <v>30000388031</v>
+        <v>30000768143</v>
       </c>
       <c r="N13" t="str">
         <v>State Bank of India</v>
@@ -2201,33 +2201,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P13" t="str">
-        <v>SBIN0003234</v>
+        <v>SBIN0005356</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0300054</v>
+        <v>0300031</v>
       </c>
       <c r="B14" t="str">
-        <v>NITISH RAM</v>
+        <v>ASHA ALAM</v>
       </c>
       <c r="C14" t="str">
-        <v>Clerk</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D14" t="str">
-        <v>03048</v>
+        <v>03027</v>
       </c>
       <c r="E14" t="str">
-        <v>Project Girls High School Sheohar No.1</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="F14" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G14" t="str">
-        <v>9003000054</v>
+        <v>9003000031</v>
       </c>
       <c r="H14" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I14" t="str">
         <v>0301</v>
@@ -2242,7 +2242,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M14" t="str">
-        <v>30000427626</v>
+        <v>30000245489</v>
       </c>
       <c r="N14" t="str">
         <v>State Bank of India</v>
@@ -2251,48 +2251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P14" t="str">
-        <v>SBIN0004473</v>
+        <v>SBIN0005421</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>0300070</v>
+        <v>0300007</v>
       </c>
       <c r="B15" t="str">
-        <v>VIJAY KUMAR</v>
+        <v>ABDUL KALAM RAI</v>
       </c>
       <c r="C15" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D15" t="str">
-        <v>03035</v>
+        <v>03007</v>
       </c>
       <c r="E15" t="str">
-        <v>CDPO Office Sheohar</v>
+        <v>Project Girls High School Piprahi No.3</v>
       </c>
       <c r="F15" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G15" t="str">
-        <v>9003000070</v>
+        <v>9003000007</v>
       </c>
       <c r="H15" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I15" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J15" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K15" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L15" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M15" t="str">
-        <v>30000554330</v>
+        <v>30000055433</v>
       </c>
       <c r="N15" t="str">
         <v>State Bank of India</v>
@@ -2301,39 +2301,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P15" t="str">
-        <v>SBIN0007959</v>
+        <v>SBIN0004521</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>0300023</v>
+        <v>0300045</v>
       </c>
       <c r="B16" t="str">
-        <v>SUNIL KHATUN</v>
+        <v>DINESH SINHA</v>
       </c>
       <c r="C16" t="str">
-        <v>Assistant Teacher</v>
+        <v>Accountant</v>
       </c>
       <c r="D16" t="str">
-        <v>03023</v>
+        <v>03041</v>
       </c>
       <c r="E16" t="str">
-        <v>High School Tariyani No.1</v>
+        <v>Panchayat Bhawan Tariyani No.4</v>
       </c>
       <c r="F16" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G16" t="str">
-        <v>9003000023</v>
+        <v>9003000045</v>
       </c>
       <c r="H16" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I16" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J16" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K16" t="str">
         <v>0305</v>
@@ -2342,7 +2342,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M16" t="str">
-        <v>30000182137</v>
+        <v>30000356355</v>
       </c>
       <c r="N16" t="str">
         <v>State Bank of India</v>
@@ -2351,48 +2351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P16" t="str">
-        <v>SBIN0002243</v>
+        <v>SBIN0001444</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>0300050</v>
+        <v>0300023</v>
       </c>
       <c r="B17" t="str">
-        <v>NITISH THAKUR</v>
+        <v>VINOD VERMA</v>
       </c>
       <c r="C17" t="str">
-        <v>Clerk</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D17" t="str">
-        <v>03018</v>
+        <v>03017</v>
       </c>
       <c r="E17" t="str">
-        <v>Primary School Purnahiya No.4</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F17" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G17" t="str">
-        <v>9003000050</v>
+        <v>9003000023</v>
       </c>
       <c r="H17" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I17" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J17" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K17" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L17" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M17" t="str">
-        <v>30000395950</v>
+        <v>30000182137</v>
       </c>
       <c r="N17" t="str">
         <v>State Bank of India</v>
@@ -2401,48 +2401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P17" t="str">
-        <v>SBIN0006677</v>
+        <v>SBIN0007983</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>0300060</v>
+        <v>0300073</v>
       </c>
       <c r="B18" t="str">
-        <v>AJAY RAI</v>
+        <v>MD. SHAHID PANDEY</v>
       </c>
       <c r="C18" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Clerk</v>
       </c>
       <c r="D18" t="str">
-        <v>03054</v>
+        <v>03063</v>
       </c>
       <c r="E18" t="str">
-        <v>Panchayat Bhawan Tariyani No.2</v>
+        <v>Project Girls High School Piprahi No.2</v>
       </c>
       <c r="F18" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G18" t="str">
-        <v>9003000060</v>
+        <v>9003000073</v>
       </c>
       <c r="H18" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I18" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J18" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K18" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L18" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M18" t="str">
-        <v>30000475140</v>
+        <v>30000578087</v>
       </c>
       <c r="N18" t="str">
         <v>State Bank of India</v>
@@ -2451,48 +2451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P18" t="str">
-        <v>SBIN0003910</v>
+        <v>SBIN0007843</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>0300098</v>
+        <v>0300015</v>
       </c>
       <c r="B19" t="str">
-        <v>FARHAT RAI</v>
+        <v>SURESH THAKUR</v>
       </c>
       <c r="C19" t="str">
-        <v>Junior Engineer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D19" t="str">
-        <v>03030</v>
+        <v>03015</v>
       </c>
       <c r="E19" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Block Education Office Dumri Katsari No.1</v>
       </c>
       <c r="F19" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G19" t="str">
-        <v>9003000098</v>
+        <v>9003000015</v>
       </c>
       <c r="H19" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I19" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="J19" t="str">
-        <v>Others</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K19" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L19" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M19" t="str">
-        <v>30000776062</v>
+        <v>30000118785</v>
       </c>
       <c r="N19" t="str">
         <v>State Bank of India</v>
@@ -2501,48 +2501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P19" t="str">
-        <v>SBIN0007915</v>
+        <v>SBIN0008928</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>0300067</v>
+        <v>0300100</v>
       </c>
       <c r="B20" t="str">
-        <v>MAHESH RAI</v>
+        <v>MD. SHAHID MAHTO</v>
       </c>
       <c r="C20" t="str">
-        <v>Teacher</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D20" t="str">
-        <v>03034</v>
+        <v>03074</v>
       </c>
       <c r="E20" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F20" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G20" t="str">
-        <v>9003000067</v>
+        <v>9003000100</v>
       </c>
       <c r="H20" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I20" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K20" t="str">
         <v>0302</v>
       </c>
-      <c r="J20" t="str">
+      <c r="L20" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K20" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L20" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M20" t="str">
-        <v>30000530573</v>
+        <v>30000791900</v>
       </c>
       <c r="N20" t="str">
         <v>State Bank of India</v>
@@ -2551,33 +2551,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P20" t="str">
-        <v>SBIN0001240</v>
+        <v>SBIN0004933</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>0300080</v>
+        <v>0300017</v>
       </c>
       <c r="B21" t="str">
-        <v>SAVITA THAKUR</v>
+        <v>KUMARI ANJALI TIWARI</v>
       </c>
       <c r="C21" t="str">
-        <v>Office Assistant</v>
+        <v>Section Officer</v>
       </c>
       <c r="D21" t="str">
-        <v>03009</v>
+        <v>03017</v>
       </c>
       <c r="E21" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F21" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G21" t="str">
-        <v>9003000080</v>
+        <v>9003000017</v>
       </c>
       <c r="H21" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I21" t="str">
         <v>0301</v>
@@ -2592,7 +2592,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M21" t="str">
-        <v>30000633520</v>
+        <v>30000134623</v>
       </c>
       <c r="N21" t="str">
         <v>State Bank of India</v>
@@ -2601,33 +2601,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P21" t="str">
-        <v>SBIN0001511</v>
+        <v>SBIN0009639</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>0300027</v>
+        <v>0300064</v>
       </c>
       <c r="B22" t="str">
-        <v>MAMTA PASWAN</v>
+        <v>MUKESH OJHA</v>
       </c>
       <c r="C22" t="str">
-        <v>Senior Clerk</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D22" t="str">
-        <v>03027</v>
+        <v>03023</v>
       </c>
       <c r="E22" t="str">
-        <v>Middle School Piprahi</v>
+        <v>Project Girls High School Tariyani No.1</v>
       </c>
       <c r="F22" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G22" t="str">
-        <v>9003000027</v>
+        <v>9003000064</v>
       </c>
       <c r="H22" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I22" t="str">
         <v>0303</v>
@@ -2636,13 +2636,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K22" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L22" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M22" t="str">
-        <v>30000213813</v>
+        <v>30000506816</v>
       </c>
       <c r="N22" t="str">
         <v>State Bank of India</v>
@@ -2651,48 +2651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P22" t="str">
-        <v>SBIN0003882</v>
+        <v>SBIN0009403</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>0300117</v>
+        <v>0300079</v>
       </c>
       <c r="B23" t="str">
-        <v>RANJIT OJHA</v>
+        <v>FARHAT KUMAR</v>
       </c>
       <c r="C23" t="str">
-        <v>Branch Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D23" t="str">
-        <v>03084</v>
+        <v>03050</v>
       </c>
       <c r="E23" t="str">
-        <v>Head Post Office, Piprahi</v>
+        <v>Project Girls High School Tariyani</v>
       </c>
       <c r="F23" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G23" t="str">
-        <v>9003000117</v>
+        <v>9003000079</v>
       </c>
       <c r="H23" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I23" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J23" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K23" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L23" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M23" t="str">
-        <v>30000926523</v>
+        <v>30000625601</v>
       </c>
       <c r="N23" t="str">
         <v>State Bank of India</v>
@@ -2701,48 +2701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P23" t="str">
-        <v>SBIN0005140</v>
+        <v>SBIN0004649</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>0300006</v>
+        <v>0300082</v>
       </c>
       <c r="B24" t="str">
-        <v>RAMESH CHAUDHARY</v>
+        <v>MD. SHAHID SAH</v>
       </c>
       <c r="C24" t="str">
-        <v>Lecturer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D24" t="str">
-        <v>03006</v>
+        <v>03069</v>
       </c>
       <c r="E24" t="str">
-        <v>Middle School Purnahiya No.1</v>
+        <v>Block Education Office Tariyani No.2</v>
       </c>
       <c r="F24" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G24" t="str">
-        <v>9003000006</v>
+        <v>9003000082</v>
       </c>
       <c r="H24" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I24" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J24" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K24" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L24" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M24" t="str">
-        <v>30000047514</v>
+        <v>30000649358</v>
       </c>
       <c r="N24" t="str">
         <v>State Bank of India</v>
@@ -2751,48 +2751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P24" t="str">
-        <v>SBIN0005235</v>
+        <v>SBIN0006652</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0300089</v>
+        <v>0300095</v>
       </c>
       <c r="B25" t="str">
-        <v>AMIT DEVI</v>
+        <v>RAVI YADAV</v>
       </c>
       <c r="C25" t="str">
         <v>Revenue Officer</v>
       </c>
       <c r="D25" t="str">
-        <v>03075</v>
+        <v>03076</v>
       </c>
       <c r="E25" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Minor Irrigation Office Tariyani</v>
       </c>
       <c r="F25" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G25" t="str">
-        <v>9003000089</v>
+        <v>9003000095</v>
       </c>
       <c r="H25" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I25" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J25" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K25" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L25" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M25" t="str">
-        <v>30000704791</v>
+        <v>30000752305</v>
       </c>
       <c r="N25" t="str">
         <v>State Bank of India</v>
@@ -2801,48 +2801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P25" t="str">
-        <v>SBIN0005007</v>
+        <v>SBIN0006486</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>0300062</v>
+        <v>0300115</v>
       </c>
       <c r="B26" t="str">
-        <v>ALOK OJHA</v>
+        <v>SURESH VERMA</v>
       </c>
       <c r="C26" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Postmaster</v>
       </c>
       <c r="D26" t="str">
-        <v>03041</v>
+        <v>03091</v>
       </c>
       <c r="E26" t="str">
-        <v>Block Education Office Tariyani No.2</v>
+        <v>BSNL Exchange, Dumri Katsari</v>
       </c>
       <c r="F26" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G26" t="str">
-        <v>9003000062</v>
+        <v>9003000115</v>
       </c>
       <c r="H26" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I26" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J26" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K26" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L26" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M26" t="str">
-        <v>30000490978</v>
+        <v>30000910685</v>
       </c>
       <c r="N26" t="str">
         <v>State Bank of India</v>
@@ -2851,48 +2851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P26" t="str">
-        <v>SBIN0001646</v>
+        <v>SBIN0002417</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>0300095</v>
+        <v>0300047</v>
       </c>
       <c r="B27" t="str">
-        <v>SUNIL SINGH</v>
+        <v>USHA RAM</v>
       </c>
       <c r="C27" t="str">
-        <v>Junior Engineer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D27" t="str">
-        <v>03077</v>
+        <v>03043</v>
       </c>
       <c r="E27" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>Panchayat Bhawan Sheohar</v>
       </c>
       <c r="F27" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G27" t="str">
-        <v>9003000095</v>
+        <v>9003000047</v>
       </c>
       <c r="H27" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I27" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J27" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K27" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L27" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M27" t="str">
-        <v>30000752305</v>
+        <v>30000372193</v>
       </c>
       <c r="N27" t="str">
         <v>State Bank of India</v>
@@ -2901,33 +2901,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P27" t="str">
-        <v>SBIN0008087</v>
+        <v>SBIN0004946</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>0300106</v>
+        <v>0300067</v>
       </c>
       <c r="B28" t="str">
-        <v>MAMTA DEVI</v>
+        <v>RAKESH OJHA</v>
       </c>
       <c r="C28" t="str">
-        <v>Branch Manager</v>
+        <v>Clerk</v>
       </c>
       <c r="D28" t="str">
-        <v>03081</v>
+        <v>03057</v>
       </c>
       <c r="E28" t="str">
-        <v>Bank of India, Dumri Katsari</v>
+        <v>Panchayat Bhawan Piprahi</v>
       </c>
       <c r="F28" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G28" t="str">
-        <v>9003000106</v>
+        <v>9003000067</v>
       </c>
       <c r="H28" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I28" t="str">
         <v>0301</v>
@@ -2936,13 +2936,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K28" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L28" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M28" t="str">
-        <v>30000839414</v>
+        <v>30000530573</v>
       </c>
       <c r="N28" t="str">
         <v>State Bank of India</v>
@@ -2951,48 +2951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P28" t="str">
-        <v>SBIN0009587</v>
+        <v>SBIN0006413</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>0300073</v>
+        <v>0300112</v>
       </c>
       <c r="B29" t="str">
-        <v>MUKESH THAKUR</v>
+        <v>RAJESH RAI</v>
       </c>
       <c r="C29" t="str">
-        <v>Clerk</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D29" t="str">
-        <v>03064</v>
+        <v>03089</v>
       </c>
       <c r="E29" t="str">
-        <v>Block Education Office Tariyani</v>
+        <v>Central Bank of India, Purnahiya</v>
       </c>
       <c r="F29" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G29" t="str">
-        <v>9003000073</v>
+        <v>9003000112</v>
       </c>
       <c r="H29" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I29" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J29" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K29" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L29" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M29" t="str">
-        <v>30000578087</v>
+        <v>30000886928</v>
       </c>
       <c r="N29" t="str">
         <v>State Bank of India</v>
@@ -3001,33 +3001,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P29" t="str">
-        <v>SBIN0005772</v>
+        <v>SBIN0004350</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>0300066</v>
+        <v>0300038</v>
       </c>
       <c r="B30" t="str">
-        <v>MANOJ PASWAN</v>
+        <v>DINESH RAM</v>
       </c>
       <c r="C30" t="str">
-        <v>Office Assistant</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D30" t="str">
-        <v>03059</v>
+        <v>03034</v>
       </c>
       <c r="E30" t="str">
-        <v>Project Girls High School Sheohar No.2</v>
+        <v>District Treasury Sheohar</v>
       </c>
       <c r="F30" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G30" t="str">
-        <v>9003000066</v>
+        <v>9003000038</v>
       </c>
       <c r="H30" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I30" t="str">
         <v>0301</v>
@@ -3042,7 +3042,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M30" t="str">
-        <v>30000522654</v>
+        <v>30000300922</v>
       </c>
       <c r="N30" t="str">
         <v>State Bank of India</v>
@@ -3051,33 +3051,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P30" t="str">
-        <v>SBIN0008202</v>
+        <v>SBIN0007235</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>0300033</v>
+        <v>0300121</v>
       </c>
       <c r="B31" t="str">
-        <v>NASREEN GUPTA</v>
+        <v>RAKESH TIWARI</v>
       </c>
       <c r="C31" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D31" t="str">
-        <v>03032</v>
+        <v>03095</v>
       </c>
       <c r="E31" t="str">
-        <v>PHC Piprahi No.3</v>
+        <v>Punjab National Bank, Piprahi</v>
       </c>
       <c r="F31" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G31" t="str">
-        <v>9003000033</v>
+        <v>9003000121</v>
       </c>
       <c r="H31" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I31" t="str">
         <v>0302</v>
@@ -3092,7 +3092,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M31" t="str">
-        <v>30000261327</v>
+        <v>30000958199</v>
       </c>
       <c r="N31" t="str">
         <v>State Bank of India</v>
@@ -3101,30 +3101,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P31" t="str">
-        <v>SBIN0005708</v>
+        <v>SBIN0009242</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>0300036</v>
+        <v>0300034</v>
       </c>
       <c r="B32" t="str">
-        <v>SUNITA KUMAR</v>
+        <v>REKHA ANSARI</v>
       </c>
       <c r="C32" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D32" t="str">
-        <v>03034</v>
+        <v>03030</v>
       </c>
       <c r="E32" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Project Girls High School Sheohar No.3</v>
       </c>
       <c r="F32" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G32" t="str">
-        <v>9003000036</v>
+        <v>9003000034</v>
       </c>
       <c r="H32" t="str">
         <v>POLLING OFFICER-1</v>
@@ -3142,7 +3142,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M32" t="str">
-        <v>30000285084</v>
+        <v>30000269246</v>
       </c>
       <c r="N32" t="str">
         <v>State Bank of India</v>
@@ -3151,48 +3151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P32" t="str">
-        <v>SBIN0008256</v>
+        <v>SBIN0007918</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>0300011</v>
+        <v>0300108</v>
       </c>
       <c r="B33" t="str">
-        <v>SAVITA ANSARI</v>
+        <v>SHAILESH SINGH</v>
       </c>
       <c r="C33" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D33" t="str">
-        <v>03011</v>
+        <v>03085</v>
       </c>
       <c r="E33" t="str">
-        <v>Circle Office Dumri Katsari No.3</v>
+        <v>Head Post Office, Sheohar</v>
       </c>
       <c r="F33" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G33" t="str">
-        <v>9003000011</v>
+        <v>9003000108</v>
       </c>
       <c r="H33" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I33" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K33" t="str">
         <v>0301</v>
       </c>
-      <c r="J33" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K33" t="str">
-        <v>0304</v>
-      </c>
       <c r="L33" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M33" t="str">
-        <v>30000087109</v>
+        <v>30000855252</v>
       </c>
       <c r="N33" t="str">
         <v>State Bank of India</v>
@@ -3201,33 +3201,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P33" t="str">
-        <v>SBIN0004368</v>
+        <v>SBIN0006138</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>0300045</v>
+        <v>0300032</v>
       </c>
       <c r="B34" t="str">
-        <v>NASREEN THAKUR</v>
+        <v>SUNITA YADAV</v>
       </c>
       <c r="C34" t="str">
-        <v>Clerk</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D34" t="str">
-        <v>03042</v>
+        <v>03028</v>
       </c>
       <c r="E34" t="str">
-        <v>CDPO Office Sheohar No.4</v>
+        <v>Panchayat Bhawan Dumri Katsari No.1</v>
       </c>
       <c r="F34" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G34" t="str">
-        <v>9003000045</v>
+        <v>9003000032</v>
       </c>
       <c r="H34" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I34" t="str">
         <v>0303</v>
@@ -3236,13 +3236,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K34" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L34" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M34" t="str">
-        <v>30000356355</v>
+        <v>30000253408</v>
       </c>
       <c r="N34" t="str">
         <v>State Bank of India</v>
@@ -3251,48 +3251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P34" t="str">
-        <v>SBIN0002577</v>
+        <v>SBIN0004950</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>0300012</v>
+        <v>0300009</v>
       </c>
       <c r="B35" t="str">
-        <v>RAKESH SAH</v>
+        <v>FARHAT SINGH</v>
       </c>
       <c r="C35" t="str">
-        <v>Senior Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D35" t="str">
-        <v>03012</v>
+        <v>03009</v>
       </c>
       <c r="E35" t="str">
-        <v>Panchayat Bhawan Tariyani No.1</v>
+        <v>High School Dumri Katsari No.3</v>
       </c>
       <c r="F35" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G35" t="str">
-        <v>9003000012</v>
+        <v>9003000009</v>
       </c>
       <c r="H35" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I35" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J35" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K35" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L35" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M35" t="str">
-        <v>30000095028</v>
+        <v>30000071271</v>
       </c>
       <c r="N35" t="str">
         <v>State Bank of India</v>
@@ -3301,48 +3301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P35" t="str">
-        <v>SBIN0001259</v>
+        <v>SBIN0003534</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>0300069</v>
+        <v>0300029</v>
       </c>
       <c r="B36" t="str">
-        <v>POONAM PRASAD</v>
+        <v>PRIYANKA PRASAD</v>
       </c>
       <c r="C36" t="str">
-        <v>Clerk</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D36" t="str">
-        <v>03061</v>
+        <v>03025</v>
       </c>
       <c r="E36" t="str">
-        <v>Circle Office Dumri Katsari No.4</v>
+        <v>Block Office Sheohar No.3</v>
       </c>
       <c r="F36" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G36" t="str">
-        <v>9003000069</v>
+        <v>9003000029</v>
       </c>
       <c r="H36" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I36" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J36" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K36" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L36" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M36" t="str">
-        <v>30000546411</v>
+        <v>30000229651</v>
       </c>
       <c r="N36" t="str">
         <v>State Bank of India</v>
@@ -3351,33 +3351,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P36" t="str">
-        <v>SBIN0002063</v>
+        <v>SBIN0009606</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>0300046</v>
+        <v>0300101</v>
       </c>
       <c r="B37" t="str">
-        <v>USHA YADAV</v>
+        <v>SANTOSH PRASAD</v>
       </c>
       <c r="C37" t="str">
-        <v>Teacher</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D37" t="str">
-        <v>03009</v>
+        <v>03079</v>
       </c>
       <c r="E37" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Minor Irrigation Office Piprahi</v>
       </c>
       <c r="F37" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G37" t="str">
-        <v>9003000046</v>
+        <v>9003000101</v>
       </c>
       <c r="H37" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I37" t="str">
         <v>0301</v>
@@ -3386,13 +3386,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K37" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L37" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M37" t="str">
-        <v>30000364274</v>
+        <v>30000799819</v>
       </c>
       <c r="N37" t="str">
         <v>State Bank of India</v>
@@ -3401,48 +3401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P37" t="str">
-        <v>SBIN0002894</v>
+        <v>SBIN0005802</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>0300111</v>
+        <v>0300072</v>
       </c>
       <c r="B38" t="str">
-        <v>KIRAN RAI H</v>
+        <v>RANJIT THAKUR</v>
       </c>
       <c r="C38" t="str">
-        <v>Assistant Manager</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D38" t="str">
-        <v>03086</v>
+        <v>03062</v>
       </c>
       <c r="E38" t="str">
-        <v>UCO Bank, Purnahiya</v>
+        <v>Block Office Dumri Katsari No.3</v>
       </c>
       <c r="F38" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G38" t="str">
-        <v>9003000111</v>
+        <v>9003000072</v>
       </c>
       <c r="H38" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I38" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K38" t="str">
         <v>0304</v>
       </c>
-      <c r="J38" t="str">
+      <c r="L38" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="K38" t="str">
-        <v>0303</v>
-      </c>
-      <c r="L38" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="M38" t="str">
-        <v>30000879009</v>
+        <v>30000570168</v>
       </c>
       <c r="N38" t="str">
         <v>State Bank of India</v>
@@ -3451,48 +3451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P38" t="str">
-        <v>SBIN0009568</v>
+        <v>SBIN0009704</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>0300029</v>
+        <v>0300005</v>
       </c>
       <c r="B39" t="str">
-        <v>PRIYANKA ALAM</v>
+        <v>PANKAJ RAM</v>
       </c>
       <c r="C39" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D39" t="str">
-        <v>03020</v>
+        <v>03005</v>
       </c>
       <c r="E39" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Primary School Sheohar No.4</v>
       </c>
       <c r="F39" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G39" t="str">
-        <v>9003000029</v>
+        <v>9003000005</v>
       </c>
       <c r="H39" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I39" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J39" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K39" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L39" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M39" t="str">
-        <v>30000229651</v>
+        <v>30000039595</v>
       </c>
       <c r="N39" t="str">
         <v>State Bank of India</v>
@@ -3501,48 +3501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P39" t="str">
-        <v>SBIN0003147</v>
+        <v>SBIN0002228</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>0300077</v>
+        <v>0300063</v>
       </c>
       <c r="B40" t="str">
-        <v>RANJIT TIWARI</v>
+        <v>SUNITA SAH</v>
       </c>
       <c r="C40" t="str">
         <v>Teacher</v>
       </c>
       <c r="D40" t="str">
-        <v>03066</v>
+        <v>03021</v>
       </c>
       <c r="E40" t="str">
-        <v>High School Purnahiya No.2</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F40" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G40" t="str">
-        <v>9003000077</v>
+        <v>9003000063</v>
       </c>
       <c r="H40" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I40" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J40" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K40" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L40" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M40" t="str">
-        <v>30000609763</v>
+        <v>30000498897</v>
       </c>
       <c r="N40" t="str">
         <v>State Bank of India</v>
@@ -3551,48 +3551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P40" t="str">
-        <v>SBIN0001434</v>
+        <v>SBIN0001246</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>0300032</v>
+        <v>0300006</v>
       </c>
       <c r="B41" t="str">
-        <v>RAVI RAM</v>
+        <v>RINKU VERMA</v>
       </c>
       <c r="C41" t="str">
-        <v>Senior Clerk</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D41" t="str">
-        <v>03031</v>
+        <v>03006</v>
       </c>
       <c r="E41" t="str">
-        <v>PHC Piprahi</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="F41" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G41" t="str">
-        <v>9003000032</v>
+        <v>9003000006</v>
       </c>
       <c r="H41" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I41" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J41" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K41" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L41" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M41" t="str">
-        <v>30000253408</v>
+        <v>30000047514</v>
       </c>
       <c r="N41" t="str">
         <v>State Bank of India</v>
@@ -3601,48 +3601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P41" t="str">
-        <v>SBIN0008286</v>
+        <v>SBIN0009695</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>0300018</v>
+        <v>0300039</v>
       </c>
       <c r="B42" t="str">
-        <v>ARVIND CHAUDHARY</v>
+        <v>SURESH SAH</v>
       </c>
       <c r="C42" t="str">
-        <v>Senior Teacher</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D42" t="str">
-        <v>03018</v>
+        <v>03035</v>
       </c>
       <c r="E42" t="str">
-        <v>Primary School Purnahiya No.4</v>
+        <v>Block Education Office Dumri Katsari No.2</v>
       </c>
       <c r="F42" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G42" t="str">
-        <v>9003000018</v>
+        <v>9003000039</v>
       </c>
       <c r="H42" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I42" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J42" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K42" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L42" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M42" t="str">
-        <v>30000142542</v>
+        <v>30000308841</v>
       </c>
       <c r="N42" t="str">
         <v>State Bank of India</v>
@@ -3651,48 +3651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P42" t="str">
-        <v>SBIN0005653</v>
+        <v>SBIN0002917</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>0300034</v>
+        <v>0300096</v>
       </c>
       <c r="B43" t="str">
-        <v>ASHA OJHA</v>
+        <v>RANJIT TIWARI</v>
       </c>
       <c r="C43" t="str">
-        <v>Head Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D43" t="str">
-        <v>03030</v>
+        <v>03072</v>
       </c>
       <c r="E43" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F43" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G43" t="str">
-        <v>9003000034</v>
+        <v>9003000096</v>
       </c>
       <c r="H43" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I43" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J43" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K43" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L43" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M43" t="str">
-        <v>30000269246</v>
+        <v>30000760224</v>
       </c>
       <c r="N43" t="str">
         <v>State Bank of India</v>
@@ -3701,48 +3701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P43" t="str">
-        <v>SBIN0005005</v>
+        <v>SBIN0009892</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>0300052</v>
+        <v>0300075</v>
       </c>
       <c r="B44" t="str">
-        <v>KIRAN SAH</v>
+        <v>RINKU GUPTA</v>
       </c>
       <c r="C44" t="str">
-        <v>Clerk</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D44" t="str">
-        <v>03046</v>
+        <v>03024</v>
       </c>
       <c r="E44" t="str">
-        <v>Primary School Piprahi No.3</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F44" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G44" t="str">
-        <v>9003000052</v>
+        <v>9003000075</v>
       </c>
       <c r="H44" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I44" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J44" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K44" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L44" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M44" t="str">
-        <v>30000411788</v>
+        <v>30000593925</v>
       </c>
       <c r="N44" t="str">
         <v>State Bank of India</v>
@@ -3751,48 +3751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P44" t="str">
-        <v>SBIN0003746</v>
+        <v>SBIN0003337</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>0300103</v>
+        <v>0300041</v>
       </c>
       <c r="B45" t="str">
-        <v>ABDUL KALAM SINHA</v>
+        <v>MAMTA THAKUR</v>
       </c>
       <c r="C45" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D45" t="str">
-        <v>03080</v>
+        <v>03037</v>
       </c>
       <c r="E45" t="str">
-        <v>RWD Sub-Division Dumri Katsari</v>
+        <v>Project Girls High School Piprahi No.1</v>
       </c>
       <c r="F45" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G45" t="str">
-        <v>9003000103</v>
+        <v>9003000041</v>
       </c>
       <c r="H45" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I45" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J45" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K45" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L45" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M45" t="str">
-        <v>30000815657</v>
+        <v>30000324679</v>
       </c>
       <c r="N45" t="str">
         <v>State Bank of India</v>
@@ -3801,33 +3801,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P45" t="str">
-        <v>SBIN0007186</v>
+        <v>SBIN0001168</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>0300005</v>
+        <v>0300061</v>
       </c>
       <c r="B46" t="str">
-        <v>SURESH SINHA</v>
+        <v>SUNIL THAKUR</v>
       </c>
       <c r="C46" t="str">
-        <v>Assistant Engineer</v>
+        <v>Accountant</v>
       </c>
       <c r="D46" t="str">
-        <v>03005</v>
+        <v>03053</v>
       </c>
       <c r="E46" t="str">
-        <v>CDPO Office Tariyani No.3</v>
+        <v>Middle School Purnahiya No.1</v>
       </c>
       <c r="F46" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G46" t="str">
-        <v>9003000005</v>
+        <v>9003000061</v>
       </c>
       <c r="H46" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I46" t="str">
         <v>999999</v>
@@ -3836,13 +3836,13 @@
         <v>Others</v>
       </c>
       <c r="K46" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L46" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M46" t="str">
-        <v>30000039595</v>
+        <v>30000483059</v>
       </c>
       <c r="N46" t="str">
         <v>State Bank of India</v>
@@ -3851,48 +3851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P46" t="str">
-        <v>SBIN0001761</v>
+        <v>SBIN0003127</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0300091</v>
+        <v>0300066</v>
       </c>
       <c r="B47" t="str">
-        <v>MANOJ SHARMA</v>
+        <v>REKHA JHA</v>
       </c>
       <c r="C47" t="str">
-        <v>Junior Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D47" t="str">
-        <v>03072</v>
+        <v>03056</v>
       </c>
       <c r="E47" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>PHC Tariyani No.2</v>
       </c>
       <c r="F47" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G47" t="str">
-        <v>9003000091</v>
+        <v>9003000066</v>
       </c>
       <c r="H47" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I47" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J47" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K47" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L47" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M47" t="str">
-        <v>30000720629</v>
+        <v>30000522654</v>
       </c>
       <c r="N47" t="str">
         <v>State Bank of India</v>
@@ -3901,48 +3901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P47" t="str">
-        <v>SBIN0009393</v>
+        <v>SBIN0006386</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0300063</v>
+        <v>0300107</v>
       </c>
       <c r="B48" t="str">
-        <v>VIJAY KHATUN</v>
+        <v>RAMESH PASWAN</v>
       </c>
       <c r="C48" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D48" t="str">
-        <v>03056</v>
+        <v>03084</v>
       </c>
       <c r="E48" t="str">
-        <v>PHC Dumri Katsari No.1</v>
+        <v>Bank of India, Sheohar</v>
       </c>
       <c r="F48" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G48" t="str">
-        <v>9003000063</v>
+        <v>9003000107</v>
       </c>
       <c r="H48" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I48" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K48" t="str">
         <v>0301</v>
       </c>
-      <c r="J48" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K48" t="str">
-        <v>0304</v>
-      </c>
       <c r="L48" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M48" t="str">
-        <v>30000498897</v>
+        <v>30000847333</v>
       </c>
       <c r="N48" t="str">
         <v>State Bank of India</v>
@@ -3951,48 +3951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P48" t="str">
-        <v>SBIN0008458</v>
+        <v>SBIN0009678</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0300110</v>
+        <v>0300090</v>
       </c>
       <c r="B49" t="str">
-        <v>KUMARI ANJALI THAKUR</v>
+        <v>NIRMALA MISHRA</v>
       </c>
       <c r="C49" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D49" t="str">
-        <v>03085</v>
+        <v>03073</v>
       </c>
       <c r="E49" t="str">
-        <v>LIC Branch Office, Sheohar</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="F49" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G49" t="str">
-        <v>9003000110</v>
+        <v>9003000090</v>
       </c>
       <c r="H49" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I49" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J49" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K49" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L49" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M49" t="str">
-        <v>30000871090</v>
+        <v>30000712710</v>
       </c>
       <c r="N49" t="str">
         <v>State Bank of India</v>
@@ -4001,48 +4001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P49" t="str">
-        <v>SBIN0007400</v>
+        <v>SBIN0009742</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0300104</v>
+        <v>0300052</v>
       </c>
       <c r="B50" t="str">
-        <v>ARVIND DEVI</v>
+        <v>MAMTA JHA</v>
       </c>
       <c r="C50" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D50" t="str">
-        <v>03070</v>
+        <v>03038</v>
       </c>
       <c r="E50" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>Primary School Sheohar</v>
       </c>
       <c r="F50" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G50" t="str">
-        <v>9003000104</v>
+        <v>9003000052</v>
       </c>
       <c r="H50" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I50" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J50" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K50" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L50" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M50" t="str">
-        <v>30000823576</v>
+        <v>30000411788</v>
       </c>
       <c r="N50" t="str">
         <v>State Bank of India</v>
@@ -4051,48 +4051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P50" t="str">
-        <v>SBIN0009922</v>
+        <v>SBIN0007064</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>0300088</v>
+        <v>0300060</v>
       </c>
       <c r="B51" t="str">
-        <v>MANOJ VERMA</v>
+        <v>SUNIL ALAM</v>
       </c>
       <c r="C51" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D51" t="str">
-        <v>03074</v>
+        <v>03052</v>
       </c>
       <c r="E51" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>Kanya Middle School Purnahiya No.4</v>
       </c>
       <c r="F51" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G51" t="str">
-        <v>9003000088</v>
+        <v>9003000060</v>
       </c>
       <c r="H51" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I51" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J51" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K51" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L51" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M51" t="str">
-        <v>30000696872</v>
+        <v>30000475140</v>
       </c>
       <c r="N51" t="str">
         <v>State Bank of India</v>
@@ -4101,48 +4101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P51" t="str">
-        <v>SBIN0007849</v>
+        <v>SBIN0001459</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>0300090</v>
+        <v>0300050</v>
       </c>
       <c r="B52" t="str">
-        <v>RAVI ALAM</v>
+        <v>MD. IRFAN MISHRA</v>
       </c>
       <c r="C52" t="str">
-        <v>Revenue Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D52" t="str">
-        <v>03039</v>
+        <v>03015</v>
       </c>
       <c r="E52" t="str">
-        <v>District Agriculture Office (deputed from other district)</v>
+        <v>Block Education Office Dumri Katsari No.1</v>
       </c>
       <c r="F52" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G52" t="str">
-        <v>9003000090</v>
+        <v>9003000050</v>
       </c>
       <c r="H52" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I52" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J52" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K52" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="L52" t="str">
-        <v>Other District</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M52" t="str">
-        <v>30000712710</v>
+        <v>30000395950</v>
       </c>
       <c r="N52" t="str">
         <v>State Bank of India</v>
@@ -4151,48 +4151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P52" t="str">
-        <v>SBIN0009488</v>
+        <v>SBIN0001663</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>0300071</v>
+        <v>0300077</v>
       </c>
       <c r="B53" t="str">
-        <v>KUMARI ANJALI GUPTA</v>
+        <v>UMESH RAM</v>
       </c>
       <c r="C53" t="str">
-        <v>Data Entry Operator</v>
+        <v>Clerk</v>
       </c>
       <c r="D53" t="str">
-        <v>03062</v>
+        <v>03066</v>
       </c>
       <c r="E53" t="str">
-        <v>Primary School Sheohar</v>
+        <v>CDPO Office Dumri Katsari No.4</v>
       </c>
       <c r="F53" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G53" t="str">
-        <v>9003000071</v>
+        <v>9003000077</v>
       </c>
       <c r="H53" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I53" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J53" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K53" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L53" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M53" t="str">
-        <v>30000562249</v>
+        <v>30000609763</v>
       </c>
       <c r="N53" t="str">
         <v>State Bank of India</v>
@@ -4201,48 +4201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P53" t="str">
-        <v>SBIN0006503</v>
+        <v>SBIN0006857</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>0300042</v>
+        <v>0300083</v>
       </c>
       <c r="B54" t="str">
-        <v>RANJIT SINGH</v>
+        <v>RAMESH SAH</v>
       </c>
       <c r="C54" t="str">
-        <v>Assistant Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D54" t="str">
-        <v>03039</v>
+        <v>03024</v>
       </c>
       <c r="E54" t="str">
-        <v>District Agriculture Office (deputed from other district)</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F54" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G54" t="str">
-        <v>9003000042</v>
+        <v>9003000083</v>
       </c>
       <c r="H54" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I54" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J54" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K54" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="L54" t="str">
-        <v>Other District</v>
+        <v>Sheohar</v>
       </c>
       <c r="M54" t="str">
-        <v>30000332598</v>
+        <v>30000657277</v>
       </c>
       <c r="N54" t="str">
         <v>State Bank of India</v>
@@ -4251,48 +4251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P54" t="str">
-        <v>SBIN0009201</v>
+        <v>SBIN0003128</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>0300022</v>
+        <v>0300024</v>
       </c>
       <c r="B55" t="str">
-        <v>DINESH ANSARI</v>
+        <v>SUNIL SHARMA</v>
       </c>
       <c r="C55" t="str">
-        <v>Senior Clerk</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D55" t="str">
-        <v>03022</v>
+        <v>03021</v>
       </c>
       <c r="E55" t="str">
-        <v>Circle Office Purnahiya No.3</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F55" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G55" t="str">
-        <v>9003000022</v>
+        <v>9003000024</v>
       </c>
       <c r="H55" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I55" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J55" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K55" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L55" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M55" t="str">
-        <v>30000174218</v>
+        <v>30000190056</v>
       </c>
       <c r="N55" t="str">
         <v>State Bank of India</v>
@@ -4301,48 +4301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P55" t="str">
-        <v>SBIN0005859</v>
+        <v>SBIN0008112</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>0300055</v>
+        <v>0300078</v>
       </c>
       <c r="B56" t="str">
-        <v>MAMTA SAH</v>
+        <v>MUKESH DEVI</v>
       </c>
       <c r="C56" t="str">
-        <v>Clerk</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D56" t="str">
-        <v>03049</v>
+        <v>03067</v>
       </c>
       <c r="E56" t="str">
-        <v>CDPO Office Tariyani</v>
+        <v>Middle School Dumri Katsari No.4</v>
       </c>
       <c r="F56" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G56" t="str">
-        <v>9003000055</v>
+        <v>9003000078</v>
       </c>
       <c r="H56" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I56" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J56" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K56" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L56" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M56" t="str">
-        <v>30000435545</v>
+        <v>30000617682</v>
       </c>
       <c r="N56" t="str">
         <v>State Bank of India</v>
@@ -4351,48 +4351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P56" t="str">
-        <v>SBIN0008137</v>
+        <v>SBIN0005975</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>0300068</v>
+        <v>0300116</v>
       </c>
       <c r="B57" t="str">
-        <v>ARVIND ALAM</v>
+        <v>SHAILESH CHAUDHARY</v>
       </c>
       <c r="C57" t="str">
-        <v>Data Entry Operator</v>
+        <v>Postmaster</v>
       </c>
       <c r="D57" t="str">
-        <v>03060</v>
+        <v>03092</v>
       </c>
       <c r="E57" t="str">
-        <v>Primary School Dumri Katsari</v>
+        <v>Central Bank of India, Piprahi</v>
       </c>
       <c r="F57" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G57" t="str">
-        <v>9003000068</v>
+        <v>9003000116</v>
       </c>
       <c r="H57" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I57" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J57" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K57" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L57" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M57" t="str">
-        <v>30000538492</v>
+        <v>30000918604</v>
       </c>
       <c r="N57" t="str">
         <v>State Bank of India</v>
@@ -4401,39 +4401,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P57" t="str">
-        <v>SBIN0004392</v>
+        <v>SBIN0001814</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>0300010</v>
+        <v>0300065</v>
       </c>
       <c r="B58" t="str">
-        <v>RAKESH KHATUN</v>
+        <v>RINKU THAKUR</v>
       </c>
       <c r="C58" t="str">
-        <v>Lecturer</v>
+        <v>Teacher</v>
       </c>
       <c r="D58" t="str">
-        <v>03010</v>
+        <v>03055</v>
       </c>
       <c r="E58" t="str">
-        <v>CDPO Office Dumri Katsari</v>
+        <v>Circle Office Dumri Katsari No.4</v>
       </c>
       <c r="F58" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G58" t="str">
-        <v>9003000010</v>
+        <v>9003000065</v>
       </c>
       <c r="H58" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I58" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J58" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K58" t="str">
         <v>0304</v>
@@ -4442,7 +4442,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M58" t="str">
-        <v>30000079190</v>
+        <v>30000514735</v>
       </c>
       <c r="N58" t="str">
         <v>State Bank of India</v>
@@ -4451,48 +4451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P58" t="str">
-        <v>SBIN0003598</v>
+        <v>SBIN0005890</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>0300037</v>
+        <v>0300027</v>
       </c>
       <c r="B59" t="str">
-        <v>KIRAN MAHTO</v>
+        <v>NIRMALA KHATUN</v>
       </c>
       <c r="C59" t="str">
-        <v>Head Clerk</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D59" t="str">
-        <v>03011</v>
+        <v>03023</v>
       </c>
       <c r="E59" t="str">
-        <v>Circle Office Dumri Katsari No.3</v>
+        <v>Project Girls High School Tariyani No.1</v>
       </c>
       <c r="F59" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G59" t="str">
-        <v>9003000037</v>
+        <v>9003000027</v>
       </c>
       <c r="H59" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I59" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="K59" t="str">
         <v>0305</v>
       </c>
-      <c r="J59" t="str">
+      <c r="L59" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="K59" t="str">
-        <v>0304</v>
-      </c>
-      <c r="L59" t="str">
-        <v>Dumri Katsari</v>
-      </c>
       <c r="M59" t="str">
-        <v>30000293003</v>
+        <v>30000213813</v>
       </c>
       <c r="N59" t="str">
         <v>State Bank of India</v>
@@ -4501,48 +4501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P59" t="str">
-        <v>SBIN0007068</v>
+        <v>SBIN0005014</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>0300057</v>
+        <v>0300120</v>
       </c>
       <c r="B60" t="str">
-        <v>SUNIL ALAM</v>
+        <v>SURESH SAH V</v>
       </c>
       <c r="C60" t="str">
-        <v>Accountant</v>
+        <v>Postmaster</v>
       </c>
       <c r="D60" t="str">
-        <v>03051</v>
+        <v>03086</v>
       </c>
       <c r="E60" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Punjab National Bank, Purnahiya</v>
       </c>
       <c r="F60" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G60" t="str">
-        <v>9003000057</v>
+        <v>9003000120</v>
       </c>
       <c r="H60" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I60" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J60" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K60" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L60" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M60" t="str">
-        <v>30000451383</v>
+        <v>30000950280</v>
       </c>
       <c r="N60" t="str">
         <v>State Bank of India</v>
@@ -4551,48 +4551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P60" t="str">
-        <v>SBIN0004193</v>
+        <v>SBIN0007443</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>0300102</v>
+        <v>0300070</v>
       </c>
       <c r="B61" t="str">
-        <v>VINOD PANDEY</v>
+        <v>MD. SHAHID SHARMA</v>
       </c>
       <c r="C61" t="str">
-        <v>Assistant Engineer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D61" t="str">
-        <v>03075</v>
+        <v>03060</v>
       </c>
       <c r="E61" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>CDPO Office Tariyani No.3</v>
       </c>
       <c r="F61" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G61" t="str">
-        <v>9003000102</v>
+        <v>9003000070</v>
       </c>
       <c r="H61" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I61" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J61" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K61" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L61" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M61" t="str">
-        <v>30000807738</v>
+        <v>30000554330</v>
       </c>
       <c r="N61" t="str">
         <v>State Bank of India</v>
@@ -4601,48 +4601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P61" t="str">
-        <v>SBIN0005486</v>
+        <v>SBIN0002882</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>0300114</v>
+        <v>0300118</v>
       </c>
       <c r="B62" t="str">
-        <v>VIJAY YADAV</v>
+        <v>ANIL JHA</v>
       </c>
       <c r="C62" t="str">
-        <v>Branch Manager</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D62" t="str">
-        <v>03089</v>
+        <v>03094</v>
       </c>
       <c r="E62" t="str">
-        <v>Central Bank of India, Tariyani</v>
+        <v>BSNL Exchange, Sheohar</v>
       </c>
       <c r="F62" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G62" t="str">
-        <v>9003000114</v>
+        <v>9003000118</v>
       </c>
       <c r="H62" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I62" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J62" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K62" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L62" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M62" t="str">
-        <v>30000902766</v>
+        <v>30000934442</v>
       </c>
       <c r="N62" t="str">
         <v>State Bank of India</v>
@@ -4651,33 +4651,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P62" t="str">
-        <v>SBIN0002713</v>
+        <v>SBIN0003896</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>0300105</v>
+        <v>0300058</v>
       </c>
       <c r="B63" t="str">
-        <v>DEEPAK SINGH</v>
+        <v>KUMARI ANJALI KUMAR</v>
       </c>
       <c r="C63" t="str">
-        <v>Junior Engineer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D63" t="str">
-        <v>03080</v>
+        <v>03033</v>
       </c>
       <c r="E63" t="str">
-        <v>RWD Sub-Division Dumri Katsari</v>
+        <v>Project Girls High School Dumri Katsari</v>
       </c>
       <c r="F63" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G63" t="str">
-        <v>9003000105</v>
+        <v>9003000058</v>
       </c>
       <c r="H63" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I63" t="str">
         <v>0304</v>
@@ -4692,7 +4692,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M63" t="str">
-        <v>30000831495</v>
+        <v>30000459302</v>
       </c>
       <c r="N63" t="str">
         <v>State Bank of India</v>
@@ -4701,33 +4701,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P63" t="str">
-        <v>SBIN0003716</v>
+        <v>SBIN0007956</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>0300074</v>
+        <v>0300037</v>
       </c>
       <c r="B64" t="str">
-        <v>UMESH MISHRA</v>
+        <v>USHA PANDEY</v>
       </c>
       <c r="C64" t="str">
-        <v>Data Entry Operator</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D64" t="str">
-        <v>03034</v>
+        <v>03033</v>
       </c>
       <c r="E64" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Project Girls High School Dumri Katsari</v>
       </c>
       <c r="F64" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G64" t="str">
-        <v>9003000074</v>
+        <v>9003000037</v>
       </c>
       <c r="H64" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I64" t="str">
         <v>0305</v>
@@ -4736,13 +4736,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K64" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L64" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M64" t="str">
-        <v>30000586006</v>
+        <v>30000293003</v>
       </c>
       <c r="N64" t="str">
         <v>State Bank of India</v>
@@ -4751,39 +4751,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P64" t="str">
-        <v>SBIN0004456</v>
+        <v>SBIN0004692</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>0300107</v>
+        <v>0300055</v>
       </c>
       <c r="B65" t="str">
-        <v>DINESH GUPTA</v>
+        <v>FARHAT PANDEY</v>
       </c>
       <c r="C65" t="str">
-        <v>Postmaster</v>
+        <v>Clerk</v>
       </c>
       <c r="D65" t="str">
-        <v>03082</v>
+        <v>03048</v>
       </c>
       <c r="E65" t="str">
-        <v>State Bank of India, Piprahi</v>
+        <v>Project Girls High School Piprahi No.4</v>
       </c>
       <c r="F65" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G65" t="str">
-        <v>9003000107</v>
+        <v>9003000055</v>
       </c>
       <c r="H65" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I65" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J65" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K65" t="str">
         <v>0302</v>
@@ -4792,7 +4792,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M65" t="str">
-        <v>30000847333</v>
+        <v>30000435545</v>
       </c>
       <c r="N65" t="str">
         <v>State Bank of India</v>
@@ -4801,48 +4801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P65" t="str">
-        <v>SBIN0007768</v>
+        <v>SBIN0007309</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>0300001</v>
+        <v>0300008</v>
       </c>
       <c r="B66" t="str">
-        <v>ANITA MISHRA</v>
+        <v>KIRAN DEVI</v>
       </c>
       <c r="C66" t="str">
-        <v>Lecturer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D66" t="str">
-        <v>03001</v>
+        <v>03008</v>
       </c>
       <c r="E66" t="str">
-        <v>Primary School Purnahiya</v>
+        <v>Block Office Tariyani No.2</v>
       </c>
       <c r="F66" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G66" t="str">
-        <v>9003000001</v>
+        <v>9003000008</v>
       </c>
       <c r="H66" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I66" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J66" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K66" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L66" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M66" t="str">
-        <v>30000007919</v>
+        <v>30000063352</v>
       </c>
       <c r="N66" t="str">
         <v>State Bank of India</v>
@@ -4851,48 +4851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P66" t="str">
-        <v>SBIN0006969</v>
+        <v>SBIN0007461</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>0300048</v>
+        <v>0300086</v>
       </c>
       <c r="B67" t="str">
-        <v>RAKESH DEVI</v>
+        <v>VINOD ALAM C</v>
       </c>
       <c r="C67" t="str">
-        <v>Accountant</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D67" t="str">
-        <v>03044</v>
+        <v>03070</v>
       </c>
       <c r="E67" t="str">
-        <v>Kanya Middle School Sheohar No.3</v>
+        <v>RWD Sub-Division Purnahiya</v>
       </c>
       <c r="F67" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G67" t="str">
-        <v>9003000048</v>
+        <v>9003000086</v>
       </c>
       <c r="H67" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I67" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J67" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K67" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L67" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M67" t="str">
-        <v>30000380112</v>
+        <v>30000681034</v>
       </c>
       <c r="N67" t="str">
         <v>State Bank of India</v>
@@ -4901,48 +4901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P67" t="str">
-        <v>SBIN0007577</v>
+        <v>SBIN0004377</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>0300079</v>
+        <v>0300019</v>
       </c>
       <c r="B68" t="str">
-        <v>KIRAN GUPTA</v>
+        <v>ARVIND DEVI</v>
       </c>
       <c r="C68" t="str">
-        <v>Office Assistant</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D68" t="str">
-        <v>03067</v>
+        <v>03019</v>
       </c>
       <c r="E68" t="str">
-        <v>Block Education Office Sheohar No.4</v>
+        <v>High School Piprahi No.2</v>
       </c>
       <c r="F68" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G68" t="str">
-        <v>9003000079</v>
+        <v>9003000019</v>
       </c>
       <c r="H68" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I68" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J68" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K68" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L68" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M68" t="str">
-        <v>30000625601</v>
+        <v>30000150461</v>
       </c>
       <c r="N68" t="str">
         <v>State Bank of India</v>
@@ -4951,48 +4951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P68" t="str">
-        <v>SBIN0007111</v>
+        <v>SBIN0008535</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>0300020</v>
+        <v>0300104</v>
       </c>
       <c r="B69" t="str">
-        <v>MD. IRFAN TIWARI</v>
+        <v>USHA ALAM</v>
       </c>
       <c r="C69" t="str">
-        <v>Headmaster</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D69" t="str">
-        <v>03020</v>
+        <v>03082</v>
       </c>
       <c r="E69" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F69" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G69" t="str">
-        <v>9003000020</v>
+        <v>9003000104</v>
       </c>
       <c r="H69" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I69" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J69" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K69" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L69" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M69" t="str">
-        <v>30000158380</v>
+        <v>30000823576</v>
       </c>
       <c r="N69" t="str">
         <v>State Bank of India</v>
@@ -5001,33 +5001,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P69" t="str">
-        <v>SBIN0008222</v>
+        <v>SBIN0005259</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>0300041</v>
+        <v>0300106</v>
       </c>
       <c r="B70" t="str">
-        <v>FARHAT PANDEY</v>
+        <v>DINESH KHATUN</v>
       </c>
       <c r="C70" t="str">
-        <v>Head Clerk</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D70" t="str">
-        <v>03038</v>
+        <v>03083</v>
       </c>
       <c r="E70" t="str">
-        <v>Kanya Middle School Piprahi No.1</v>
+        <v>LIC Branch Office, Tariyani</v>
       </c>
       <c r="F70" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G70" t="str">
-        <v>9003000041</v>
+        <v>9003000106</v>
       </c>
       <c r="H70" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I70" t="str">
         <v>0302</v>
@@ -5036,13 +5036,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K70" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L70" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M70" t="str">
-        <v>30000324679</v>
+        <v>30000839414</v>
       </c>
       <c r="N70" t="str">
         <v>State Bank of India</v>
@@ -5051,33 +5051,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P70" t="str">
-        <v>SBIN0002192</v>
+        <v>SBIN0005986</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>0300002</v>
+        <v>0300059</v>
       </c>
       <c r="B71" t="str">
-        <v>SANJAY SHARMA</v>
+        <v>NASREEN PASWAN</v>
       </c>
       <c r="C71" t="str">
-        <v>Headmaster</v>
+        <v>Accountant</v>
       </c>
       <c r="D71" t="str">
-        <v>03002</v>
+        <v>03051</v>
       </c>
       <c r="E71" t="str">
-        <v>Block Education Office Tariyani No.1</v>
+        <v>Middle School Dumri Katsari</v>
       </c>
       <c r="F71" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G71" t="str">
-        <v>9003000002</v>
+        <v>9003000059</v>
       </c>
       <c r="H71" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I71" t="str">
         <v>0304</v>
@@ -5086,13 +5086,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K71" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L71" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M71" t="str">
-        <v>30000015838</v>
+        <v>30000467221</v>
       </c>
       <c r="N71" t="str">
         <v>State Bank of India</v>
@@ -5101,48 +5101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P71" t="str">
-        <v>SBIN0009116</v>
+        <v>SBIN0003781</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>0300078</v>
+        <v>0300089</v>
       </c>
       <c r="B72" t="str">
-        <v>NASREEN TIWARI</v>
+        <v>PANKAJ VERMA</v>
       </c>
       <c r="C72" t="str">
-        <v>Teacher</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D72" t="str">
-        <v>03034</v>
+        <v>03072</v>
       </c>
       <c r="E72" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F72" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G72" t="str">
-        <v>9003000078</v>
+        <v>9003000089</v>
       </c>
       <c r="H72" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I72" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J72" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K72" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L72" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M72" t="str">
-        <v>30000617682</v>
+        <v>30000704791</v>
       </c>
       <c r="N72" t="str">
         <v>State Bank of India</v>
@@ -5151,48 +5151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P72" t="str">
-        <v>SBIN0008495</v>
+        <v>SBIN0009828</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>0300122</v>
+        <v>0300048</v>
       </c>
       <c r="B73" t="str">
-        <v>NASREEN CHAUDHARY</v>
+        <v>VINOD ALAM</v>
       </c>
       <c r="C73" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Teacher</v>
       </c>
       <c r="D73" t="str">
-        <v>03094</v>
+        <v>03044</v>
       </c>
       <c r="E73" t="str">
-        <v>Head Post Office, Tariyani</v>
+        <v>Block Office Sheohar No.4</v>
       </c>
       <c r="F73" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G73" t="str">
-        <v>9003000122</v>
+        <v>9003000048</v>
       </c>
       <c r="H73" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I73" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J73" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="K73" t="str">
         <v>0301</v>
       </c>
-      <c r="J73" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K73" t="str">
-        <v>0305</v>
-      </c>
       <c r="L73" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M73" t="str">
-        <v>30000966118</v>
+        <v>30000380112</v>
       </c>
       <c r="N73" t="str">
         <v>State Bank of India</v>
@@ -5201,48 +5201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P73" t="str">
-        <v>SBIN0006613</v>
+        <v>SBIN0001235</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>0300016</v>
+        <v>0300117</v>
       </c>
       <c r="B74" t="str">
-        <v>NASREEN KUMAR</v>
+        <v>DINESH ALAM</v>
       </c>
       <c r="C74" t="str">
-        <v>Headmaster</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D74" t="str">
-        <v>03016</v>
+        <v>03093</v>
       </c>
       <c r="E74" t="str">
-        <v>Project Girls High School Dumri Katsari</v>
+        <v>UCO Bank, Tariyani</v>
       </c>
       <c r="F74" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G74" t="str">
-        <v>9003000016</v>
+        <v>9003000117</v>
       </c>
       <c r="H74" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I74" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J74" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K74" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L74" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M74" t="str">
-        <v>30000126704</v>
+        <v>30000926523</v>
       </c>
       <c r="N74" t="str">
         <v>State Bank of India</v>
@@ -5251,48 +5251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P74" t="str">
-        <v>SBIN0001904</v>
+        <v>SBIN0004177</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>0300120</v>
+        <v>0300122</v>
       </c>
       <c r="B75" t="str">
-        <v>KUMARI ANJALI VERMA</v>
+        <v>ABDUL KALAM GUPTA</v>
       </c>
       <c r="C75" t="str">
         <v>Postmaster</v>
       </c>
       <c r="D75" t="str">
-        <v>03092</v>
+        <v>03096</v>
       </c>
       <c r="E75" t="str">
-        <v>Central Bank of India, Purnahiya</v>
+        <v>UCO Bank, Dumri Katsari</v>
       </c>
       <c r="F75" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G75" t="str">
-        <v>9003000120</v>
+        <v>9003000122</v>
       </c>
       <c r="H75" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I75" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J75" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K75" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L75" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M75" t="str">
-        <v>30000950280</v>
+        <v>30000966118</v>
       </c>
       <c r="N75" t="str">
         <v>State Bank of India</v>
@@ -5301,48 +5301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P75" t="str">
-        <v>SBIN0009210</v>
+        <v>SBIN0005596</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>0300084</v>
+        <v>0300103</v>
       </c>
       <c r="B76" t="str">
-        <v>ASHA PANDEY U</v>
+        <v>AJAY RAI</v>
       </c>
       <c r="C76" t="str">
-        <v>Clerk</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D76" t="str">
-        <v>03071</v>
+        <v>03081</v>
       </c>
       <c r="E76" t="str">
-        <v>Block Office Sheohar</v>
+        <v>RWD Sub-Division Piprahi</v>
       </c>
       <c r="F76" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G76" t="str">
-        <v>9003000084</v>
+        <v>9003000103</v>
       </c>
       <c r="H76" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I76" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J76" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K76" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L76" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M76" t="str">
-        <v>30000665196</v>
+        <v>30000815657</v>
       </c>
       <c r="N76" t="str">
         <v>State Bank of India</v>
@@ -5351,48 +5351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P76" t="str">
-        <v>SBIN0001587</v>
+        <v>SBIN0006586</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>0300124</v>
+        <v>0300081</v>
       </c>
       <c r="B77" t="str">
-        <v>DINESH THAKUR</v>
+        <v>SANTOSH SHARMA</v>
       </c>
       <c r="C77" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D77" t="str">
-        <v>03096</v>
+        <v>03068</v>
       </c>
       <c r="E77" t="str">
-        <v>UCO Bank, Piprahi</v>
+        <v>CDPO Office Dumri Katsari No.2</v>
       </c>
       <c r="F77" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G77" t="str">
-        <v>9003000124</v>
+        <v>9003000081</v>
       </c>
       <c r="H77" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I77" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J77" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K77" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L77" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M77" t="str">
-        <v>30000981956</v>
+        <v>30000641439</v>
       </c>
       <c r="N77" t="str">
         <v>State Bank of India</v>
@@ -5401,48 +5401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P77" t="str">
-        <v>SBIN0003677</v>
+        <v>SBIN0006850</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>0300053</v>
+        <v>0300088</v>
       </c>
       <c r="B78" t="str">
-        <v>DEEPAK GUPTA</v>
+        <v>SHAILESH ALAM</v>
       </c>
       <c r="C78" t="str">
-        <v>Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D78" t="str">
-        <v>03047</v>
+        <v>03071</v>
       </c>
       <c r="E78" t="str">
-        <v>District Treasury (deputed from other district)</v>
+        <v>RWD Sub-Division Sheohar</v>
       </c>
       <c r="F78" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G78" t="str">
-        <v>9003000053</v>
+        <v>9003000088</v>
       </c>
       <c r="H78" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I78" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J78" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K78" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="L78" t="str">
-        <v>Other District</v>
+        <v>Sheohar</v>
       </c>
       <c r="M78" t="str">
-        <v>30000419707</v>
+        <v>30000696872</v>
       </c>
       <c r="N78" t="str">
         <v>State Bank of India</v>
@@ -5451,39 +5451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P78" t="str">
-        <v>SBIN0009215</v>
+        <v>SBIN0001296</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0300008</v>
+        <v>0300028</v>
       </c>
       <c r="B79" t="str">
-        <v>ASHA PANDEY</v>
+        <v>VINOD ANSARI</v>
       </c>
       <c r="C79" t="str">
-        <v>Lecturer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D79" t="str">
-        <v>03008</v>
+        <v>03024</v>
       </c>
       <c r="E79" t="str">
-        <v>Block Agriculture Office Sheohar No.4</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F79" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G79" t="str">
-        <v>9003000008</v>
+        <v>9003000028</v>
       </c>
       <c r="H79" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I79" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="J79" t="str">
-        <v>Others</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K79" t="str">
         <v>0301</v>
@@ -5492,7 +5492,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M79" t="str">
-        <v>30000063352</v>
+        <v>30000221732</v>
       </c>
       <c r="N79" t="str">
         <v>State Bank of India</v>
@@ -5501,48 +5501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P79" t="str">
-        <v>SBIN0001650</v>
+        <v>SBIN0003267</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>0300109</v>
+        <v>0300056</v>
       </c>
       <c r="B80" t="str">
-        <v>MANOJ JHA</v>
+        <v>RAKESH SHARMA</v>
       </c>
       <c r="C80" t="str">
-        <v>Assistant Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D80" t="str">
-        <v>03084</v>
+        <v>03049</v>
       </c>
       <c r="E80" t="str">
-        <v>Head Post Office, Piprahi</v>
+        <v>Block Office Purnahiya No.4</v>
       </c>
       <c r="F80" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G80" t="str">
-        <v>9003000109</v>
+        <v>9003000056</v>
       </c>
       <c r="H80" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I80" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J80" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K80" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L80" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M80" t="str">
-        <v>30000863171</v>
+        <v>30000443464</v>
       </c>
       <c r="N80" t="str">
         <v>State Bank of India</v>
@@ -5551,48 +5551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P80" t="str">
-        <v>SBIN0005823</v>
+        <v>SBIN0004276</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>0300064</v>
+        <v>0300126</v>
       </c>
       <c r="B81" t="str">
-        <v>AMIT KUMAR</v>
+        <v>FARHAT MAHTO</v>
       </c>
       <c r="C81" t="str">
-        <v>Data Entry Operator</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D81" t="str">
-        <v>03057</v>
+        <v>03099</v>
       </c>
       <c r="E81" t="str">
-        <v>Project Girls High School Sheohar</v>
+        <v>BSNL Exchange, Purnahiya</v>
       </c>
       <c r="F81" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G81" t="str">
-        <v>9003000064</v>
+        <v>9003000126</v>
       </c>
       <c r="H81" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I81" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J81" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K81" t="str">
         <v>0303</v>
       </c>
-      <c r="J81" t="str">
+      <c r="L81" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="K81" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L81" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M81" t="str">
-        <v>30000506816</v>
+        <v>30000997794</v>
       </c>
       <c r="N81" t="str">
         <v>State Bank of India</v>
@@ -5601,39 +5601,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P81" t="str">
-        <v>SBIN0007550</v>
+        <v>SBIN0007293</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>0300118</v>
+        <v>0300099</v>
       </c>
       <c r="B82" t="str">
-        <v>MANOJ CHAUDHARY</v>
+        <v>ASHA ALAM T</v>
       </c>
       <c r="C82" t="str">
-        <v>Administrative Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D82" t="str">
-        <v>03091</v>
+        <v>03078</v>
       </c>
       <c r="E82" t="str">
-        <v>Punjab National Bank, Dumri Katsari</v>
+        <v>Minor Irrigation Office Dumri Katsari</v>
       </c>
       <c r="F82" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G82" t="str">
-        <v>9003000118</v>
+        <v>9003000099</v>
       </c>
       <c r="H82" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I82" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J82" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K82" t="str">
         <v>0304</v>
@@ -5642,7 +5642,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M82" t="str">
-        <v>30000934442</v>
+        <v>30000783981</v>
       </c>
       <c r="N82" t="str">
         <v>State Bank of India</v>
@@ -5651,48 +5651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P82" t="str">
-        <v>SBIN0006558</v>
+        <v>SBIN0009105</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>0300014</v>
+        <v>0300125</v>
       </c>
       <c r="B83" t="str">
-        <v>SANJAY OJHA</v>
+        <v>SUNIL KHATUN</v>
       </c>
       <c r="C83" t="str">
-        <v>Lecturer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D83" t="str">
-        <v>03014</v>
+        <v>03096</v>
       </c>
       <c r="E83" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>UCO Bank, Dumri Katsari</v>
       </c>
       <c r="F83" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G83" t="str">
-        <v>9003000014</v>
+        <v>9003000125</v>
       </c>
       <c r="H83" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I83" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J83" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K83" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L83" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M83" t="str">
-        <v>30000110866</v>
+        <v>30000989875</v>
       </c>
       <c r="N83" t="str">
         <v>State Bank of India</v>
@@ -5701,48 +5701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P83" t="str">
-        <v>SBIN0008561</v>
+        <v>SBIN0002152</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>0300025</v>
+        <v>0300114</v>
       </c>
       <c r="B84" t="str">
-        <v>POONAM TIWARI</v>
+        <v>NEHA VERMA</v>
       </c>
       <c r="C84" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D84" t="str">
-        <v>03025</v>
+        <v>03090</v>
       </c>
       <c r="E84" t="str">
-        <v>CDPO Office Sheohar No.2</v>
+        <v>State Bank of India, Piprahi</v>
       </c>
       <c r="F84" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G84" t="str">
-        <v>9003000025</v>
+        <v>9003000114</v>
       </c>
       <c r="H84" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I84" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J84" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K84" t="str">
         <v>0302</v>
       </c>
-      <c r="J84" t="str">
+      <c r="L84" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K84" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L84" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M84" t="str">
-        <v>30000197975</v>
+        <v>30000902766</v>
       </c>
       <c r="N84" t="str">
         <v>State Bank of India</v>
@@ -5751,48 +5751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P84" t="str">
-        <v>SBIN0004229</v>
+        <v>SBIN0007919</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>0300061</v>
+        <v>0300002</v>
       </c>
       <c r="B85" t="str">
-        <v>MANOJ SAH</v>
+        <v>ARVIND SINGH</v>
       </c>
       <c r="C85" t="str">
-        <v>Accountant</v>
+        <v>Headmaster</v>
       </c>
       <c r="D85" t="str">
-        <v>03055</v>
+        <v>03002</v>
       </c>
       <c r="E85" t="str">
-        <v>PHC Dumri Katsari No.2</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="F85" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G85" t="str">
-        <v>9003000061</v>
+        <v>9003000002</v>
       </c>
       <c r="H85" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I85" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J85" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K85" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L85" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M85" t="str">
-        <v>30000483059</v>
+        <v>30000015838</v>
       </c>
       <c r="N85" t="str">
         <v>State Bank of India</v>
@@ -5801,48 +5801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P85" t="str">
-        <v>SBIN0006532</v>
+        <v>SBIN0005659</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>0300004</v>
+        <v>0300124</v>
       </c>
       <c r="B86" t="str">
-        <v>SANTOSH MISHRA</v>
+        <v>SANJAY THAKUR</v>
       </c>
       <c r="C86" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D86" t="str">
-        <v>03004</v>
+        <v>03098</v>
       </c>
       <c r="E86" t="str">
-        <v>High School Dumri Katsari</v>
+        <v>Head Post Office, Tariyani</v>
       </c>
       <c r="F86" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G86" t="str">
-        <v>9003000004</v>
+        <v>9003000124</v>
       </c>
       <c r="H86" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I86" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J86" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K86" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L86" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M86" t="str">
-        <v>30000031676</v>
+        <v>30000981956</v>
       </c>
       <c r="N86" t="str">
         <v>State Bank of India</v>
@@ -5851,48 +5851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P86" t="str">
-        <v>SBIN0009970</v>
+        <v>SBIN0003498</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>0300038</v>
+        <v>0300110</v>
       </c>
       <c r="B87" t="str">
-        <v>MANOJ GUPTA</v>
+        <v>USHA GUPTA</v>
       </c>
       <c r="C87" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D87" t="str">
-        <v>03035</v>
+        <v>03087</v>
       </c>
       <c r="E87" t="str">
-        <v>CDPO Office Sheohar</v>
+        <v>Central Bank of India, Dumri Katsari</v>
       </c>
       <c r="F87" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G87" t="str">
-        <v>9003000038</v>
+        <v>9003000110</v>
       </c>
       <c r="H87" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I87" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J87" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K87" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L87" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M87" t="str">
-        <v>30000300922</v>
+        <v>30000871090</v>
       </c>
       <c r="N87" t="str">
         <v>State Bank of India</v>
@@ -5901,48 +5901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P87" t="str">
-        <v>SBIN0002722</v>
+        <v>SBIN0008781</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>0300044</v>
+        <v>0300026</v>
       </c>
       <c r="B88" t="str">
-        <v>ABDUL KALAM ANSARI</v>
+        <v>KIRAN DEVI P</v>
       </c>
       <c r="C88" t="str">
-        <v>Clerk</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D88" t="str">
-        <v>03041</v>
+        <v>03015</v>
       </c>
       <c r="E88" t="str">
-        <v>Block Education Office Tariyani No.2</v>
+        <v>Block Education Office Dumri Katsari No.1</v>
       </c>
       <c r="F88" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G88" t="str">
-        <v>9003000044</v>
+        <v>9003000026</v>
       </c>
       <c r="H88" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I88" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J88" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K88" t="str">
         <v>0304</v>
       </c>
-      <c r="J88" t="str">
+      <c r="L88" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="K88" t="str">
-        <v>0305</v>
-      </c>
-      <c r="L88" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="M88" t="str">
-        <v>30000348436</v>
+        <v>30000205894</v>
       </c>
       <c r="N88" t="str">
         <v>State Bank of India</v>
@@ -5951,48 +5951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P88" t="str">
-        <v>SBIN0003486</v>
+        <v>SBIN0002883</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>0300072</v>
+        <v>0300069</v>
       </c>
       <c r="B89" t="str">
-        <v>RANJIT MAHTO</v>
+        <v>VIJAY CHAUDHARY Q</v>
       </c>
       <c r="C89" t="str">
-        <v>Office Assistant</v>
+        <v>Clerk</v>
       </c>
       <c r="D89" t="str">
-        <v>03063</v>
+        <v>03059</v>
       </c>
       <c r="E89" t="str">
-        <v>Primary School Piprahi No.2</v>
+        <v>Primary School Purnahiya No.3</v>
       </c>
       <c r="F89" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G89" t="str">
-        <v>9003000072</v>
+        <v>9003000069</v>
       </c>
       <c r="H89" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I89" t="str">
+        <v>999999</v>
+      </c>
+      <c r="J89" t="str">
+        <v>Others</v>
+      </c>
+      <c r="K89" t="str">
         <v>0303</v>
       </c>
-      <c r="J89" t="str">
+      <c r="L89" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="K89" t="str">
-        <v>0302</v>
-      </c>
-      <c r="L89" t="str">
-        <v>Piprahi</v>
-      </c>
       <c r="M89" t="str">
-        <v>30000570168</v>
+        <v>30000546411</v>
       </c>
       <c r="N89" t="str">
         <v>State Bank of India</v>
@@ -6001,48 +6001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P89" t="str">
-        <v>SBIN0001122</v>
+        <v>SBIN0002001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>0300030</v>
+        <v>0300109</v>
       </c>
       <c r="B90" t="str">
-        <v>ANITA TIWARI</v>
+        <v>PANKAJ KHATUN P</v>
       </c>
       <c r="C90" t="str">
-        <v>Assistant Teacher</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D90" t="str">
-        <v>03029</v>
+        <v>03086</v>
       </c>
       <c r="E90" t="str">
-        <v>Project Girls High School Tariyani No.2</v>
+        <v>Punjab National Bank, Purnahiya</v>
       </c>
       <c r="F90" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G90" t="str">
-        <v>9003000030</v>
+        <v>9003000109</v>
       </c>
       <c r="H90" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I90" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="J90" t="str">
-        <v>Others</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K90" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L90" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M90" t="str">
-        <v>30000237570</v>
+        <v>30000863171</v>
       </c>
       <c r="N90" t="str">
         <v>State Bank of India</v>
@@ -6051,48 +6051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P90" t="str">
-        <v>SBIN0009135</v>
+        <v>SBIN0002528</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>0300119</v>
+        <v>0300092</v>
       </c>
       <c r="B91" t="str">
-        <v>ABDUL KALAM PRASAD</v>
+        <v>SUNITA KHATUN</v>
       </c>
       <c r="C91" t="str">
-        <v>Postmaster</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D91" t="str">
-        <v>03090</v>
+        <v>03075</v>
       </c>
       <c r="E91" t="str">
-        <v>UCO Bank, Sheohar</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F91" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G91" t="str">
-        <v>9003000119</v>
+        <v>9003000092</v>
       </c>
       <c r="H91" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I91" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J91" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K91" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L91" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M91" t="str">
-        <v>30000942361</v>
+        <v>30000728548</v>
       </c>
       <c r="N91" t="str">
         <v>State Bank of India</v>
@@ -6101,39 +6101,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P91" t="str">
-        <v>SBIN0008032</v>
+        <v>SBIN0003145</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>0300112</v>
+        <v>0300071</v>
       </c>
       <c r="B92" t="str">
-        <v>PRIYANKA DEVI</v>
+        <v>NITISH CHAUDHARY</v>
       </c>
       <c r="C92" t="str">
-        <v>Branch Manager</v>
+        <v>Clerk</v>
       </c>
       <c r="D92" t="str">
-        <v>03087</v>
+        <v>03061</v>
       </c>
       <c r="E92" t="str">
-        <v>Punjab National Bank, Tariyani</v>
+        <v>Kanya Middle School Tariyani No.1</v>
       </c>
       <c r="F92" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G92" t="str">
-        <v>9003000112</v>
+        <v>9003000071</v>
       </c>
       <c r="H92" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I92" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J92" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K92" t="str">
         <v>0305</v>
@@ -6142,7 +6142,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M92" t="str">
-        <v>30000886928</v>
+        <v>30000562249</v>
       </c>
       <c r="N92" t="str">
         <v>State Bank of India</v>
@@ -6151,48 +6151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P92" t="str">
-        <v>SBIN0009218</v>
+        <v>SBIN0008181</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>0300059</v>
+        <v>0300051</v>
       </c>
       <c r="B93" t="str">
-        <v>VINOD SINGH</v>
+        <v>NIRMALA SHARMA</v>
       </c>
       <c r="C93" t="str">
         <v>Revenue Karmachari</v>
       </c>
       <c r="D93" t="str">
-        <v>03053</v>
+        <v>03005</v>
       </c>
       <c r="E93" t="str">
-        <v>Panchayat Bhawan Purnahiya No.2</v>
+        <v>Primary School Sheohar No.4</v>
       </c>
       <c r="F93" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G93" t="str">
-        <v>9003000059</v>
+        <v>9003000051</v>
       </c>
       <c r="H93" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I93" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J93" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K93" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L93" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M93" t="str">
-        <v>30000467221</v>
+        <v>30000403869</v>
       </c>
       <c r="N93" t="str">
         <v>State Bank of India</v>
@@ -6201,39 +6201,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P93" t="str">
-        <v>SBIN0005258</v>
+        <v>SBIN0001738</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>0300047</v>
+        <v>0300057</v>
       </c>
       <c r="B94" t="str">
-        <v>MANOJ DEVI</v>
+        <v>PRAMOD PASWAN</v>
       </c>
       <c r="C94" t="str">
-        <v>Accountant</v>
+        <v>Clerk</v>
       </c>
       <c r="D94" t="str">
-        <v>03043</v>
+        <v>03050</v>
       </c>
       <c r="E94" t="str">
-        <v>Block Office Tariyani No.4</v>
+        <v>Project Girls High School Tariyani</v>
       </c>
       <c r="F94" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G94" t="str">
-        <v>9003000047</v>
+        <v>9003000057</v>
       </c>
       <c r="H94" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I94" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J94" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K94" t="str">
         <v>0305</v>
@@ -6242,7 +6242,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M94" t="str">
-        <v>30000372193</v>
+        <v>30000451383</v>
       </c>
       <c r="N94" t="str">
         <v>State Bank of India</v>
@@ -6251,48 +6251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P94" t="str">
-        <v>SBIN0002609</v>
+        <v>SBIN0004746</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>0300026</v>
+        <v>0300102</v>
       </c>
       <c r="B95" t="str">
-        <v>SUNIL OJHA</v>
+        <v>SHAILESH KUMAR</v>
       </c>
       <c r="C95" t="str">
-        <v>Head Clerk</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D95" t="str">
-        <v>03026</v>
+        <v>03080</v>
       </c>
       <c r="E95" t="str">
-        <v>Kanya Middle School Purnahiya</v>
+        <v>Minor Irrigation Office Sheohar</v>
       </c>
       <c r="F95" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G95" t="str">
-        <v>9003000026</v>
+        <v>9003000102</v>
       </c>
       <c r="H95" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I95" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J95" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K95" t="str">
         <v>0301</v>
       </c>
-      <c r="J95" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K95" t="str">
-        <v>0303</v>
-      </c>
       <c r="L95" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M95" t="str">
-        <v>30000205894</v>
+        <v>30000807738</v>
       </c>
       <c r="N95" t="str">
         <v>State Bank of India</v>
@@ -6301,30 +6301,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P95" t="str">
-        <v>SBIN0003302</v>
+        <v>SBIN0008078</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>0300003</v>
+        <v>0300018</v>
       </c>
       <c r="B96" t="str">
-        <v>NITISH DEVI</v>
+        <v>SANJAY SINHA</v>
       </c>
       <c r="C96" t="str">
-        <v>Lecturer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D96" t="str">
-        <v>03003</v>
+        <v>03018</v>
       </c>
       <c r="E96" t="str">
-        <v>Middle School Tariyani No.4</v>
+        <v>PHED Division Sheohar</v>
       </c>
       <c r="F96" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G96" t="str">
-        <v>9003000003</v>
+        <v>9003000018</v>
       </c>
       <c r="H96" t="str">
         <v>PRESIDING OFFICER</v>
@@ -6336,13 +6336,13 @@
         <v>Others</v>
       </c>
       <c r="K96" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L96" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M96" t="str">
-        <v>30000023757</v>
+        <v>30000142542</v>
       </c>
       <c r="N96" t="str">
         <v>State Bank of India</v>
@@ -6351,33 +6351,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P96" t="str">
-        <v>SBIN0005498</v>
+        <v>SBIN0009036</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0300126</v>
+        <v>0300022</v>
       </c>
       <c r="B97" t="str">
-        <v>SURESH PASWAN</v>
+        <v>SURESH KHATUN</v>
       </c>
       <c r="C97" t="str">
-        <v>Postmaster</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D97" t="str">
-        <v>03097</v>
+        <v>03020</v>
       </c>
       <c r="E97" t="str">
-        <v>Central Bank of India, Sheohar</v>
+        <v>Kanya Middle School Sheohar No.4</v>
       </c>
       <c r="F97" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G97" t="str">
-        <v>9003000126</v>
+        <v>9003000022</v>
       </c>
       <c r="H97" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I97" t="str">
         <v>0301</v>
@@ -6392,7 +6392,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M97" t="str">
-        <v>30000997794</v>
+        <v>30000174218</v>
       </c>
       <c r="N97" t="str">
         <v>State Bank of India</v>
@@ -6401,48 +6401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P97" t="str">
-        <v>SBIN0005768</v>
+        <v>SBIN0004140</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>0300096</v>
+        <v>0300074</v>
       </c>
       <c r="B98" t="str">
-        <v>KIRAN RAI</v>
+        <v>MAMTA OJHA</v>
       </c>
       <c r="C98" t="str">
-        <v>Assistant Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D98" t="str">
-        <v>03078</v>
+        <v>03064</v>
       </c>
       <c r="E98" t="str">
-        <v>Minor Irrigation Office Dumri Katsari</v>
+        <v>Block Agriculture Office Purnahiya No.4</v>
       </c>
       <c r="F98" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G98" t="str">
-        <v>9003000096</v>
+        <v>9003000074</v>
       </c>
       <c r="H98" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I98" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J98" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K98" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L98" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M98" t="str">
-        <v>30000760224</v>
+        <v>30000586006</v>
       </c>
       <c r="N98" t="str">
         <v>State Bank of India</v>
@@ -6451,33 +6451,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P98" t="str">
-        <v>SBIN0007447</v>
+        <v>SBIN0004121</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>0300115</v>
+        <v>0300011</v>
       </c>
       <c r="B99" t="str">
-        <v>RANJIT PRASAD</v>
+        <v>MAHESH OJHA</v>
       </c>
       <c r="C99" t="str">
-        <v>Assistant Manager</v>
+        <v>Section Officer</v>
       </c>
       <c r="D99" t="str">
-        <v>03090</v>
+        <v>03011</v>
       </c>
       <c r="E99" t="str">
-        <v>UCO Bank, Sheohar</v>
+        <v>High School Dumri Katsari No.2</v>
       </c>
       <c r="F99" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G99" t="str">
-        <v>9003000115</v>
+        <v>9003000011</v>
       </c>
       <c r="H99" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I99" t="str">
         <v>0303</v>
@@ -6486,13 +6486,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K99" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L99" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M99" t="str">
-        <v>30000910685</v>
+        <v>30000087109</v>
       </c>
       <c r="N99" t="str">
         <v>State Bank of India</v>
@@ -6501,33 +6501,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P99" t="str">
-        <v>SBIN0002869</v>
+        <v>SBIN0002313</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>0300087</v>
+        <v>0300010</v>
       </c>
       <c r="B100" t="str">
-        <v>ANIL KUMAR</v>
+        <v>ABDUL KALAM SINHA</v>
       </c>
       <c r="C100" t="str">
-        <v>Junior Engineer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D100" t="str">
-        <v>03073</v>
+        <v>03010</v>
       </c>
       <c r="E100" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>Middle School Purnahiya No.2</v>
       </c>
       <c r="F100" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G100" t="str">
-        <v>9003000087</v>
+        <v>9003000010</v>
       </c>
       <c r="H100" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I100" t="str">
         <v>999999</v>
@@ -6542,7 +6542,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M100" t="str">
-        <v>30000688953</v>
+        <v>30000079190</v>
       </c>
       <c r="N100" t="str">
         <v>State Bank of India</v>
@@ -6551,48 +6551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P100" t="str">
-        <v>SBIN0009485</v>
+        <v>SBIN0001036</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>0300081</v>
+        <v>0300025</v>
       </c>
       <c r="B101" t="str">
-        <v>SANTOSH VERMA</v>
+        <v>AMIT TIWARI</v>
       </c>
       <c r="C101" t="str">
-        <v>Clerk</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D101" t="str">
-        <v>03068</v>
+        <v>03022</v>
       </c>
       <c r="E101" t="str">
-        <v>CDPO Office Piprahi No.3</v>
+        <v>High School Purnahiya No.3</v>
       </c>
       <c r="F101" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G101" t="str">
-        <v>9003000081</v>
+        <v>9003000025</v>
       </c>
       <c r="H101" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I101" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J101" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K101" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L101" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M101" t="str">
-        <v>30000641439</v>
+        <v>30000197975</v>
       </c>
       <c r="N101" t="str">
         <v>State Bank of India</v>
@@ -6601,48 +6601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P101" t="str">
-        <v>SBIN0001969</v>
+        <v>SBIN0002393</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>0300013</v>
+        <v>0300087</v>
       </c>
       <c r="B102" t="str">
-        <v>SANTOSH SINGH</v>
+        <v>SUNIL MISHRA</v>
       </c>
       <c r="C102" t="str">
-        <v>Section Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D102" t="str">
-        <v>03013</v>
+        <v>03006</v>
       </c>
       <c r="E102" t="str">
-        <v>Primary School Tariyani</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="F102" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G102" t="str">
-        <v>9003000013</v>
+        <v>9003000087</v>
       </c>
       <c r="H102" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I102" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J102" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K102" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L102" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M102" t="str">
-        <v>30000102947</v>
+        <v>30000688953</v>
       </c>
       <c r="N102" t="str">
         <v>State Bank of India</v>
@@ -6651,39 +6651,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P102" t="str">
-        <v>SBIN0003934</v>
+        <v>SBIN0004844</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>0300065</v>
+        <v>0300042</v>
       </c>
       <c r="B103" t="str">
-        <v>SUNITA PRASAD</v>
+        <v>MANOJ KHATUN</v>
       </c>
       <c r="C103" t="str">
-        <v>Teacher</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D103" t="str">
-        <v>03058</v>
+        <v>03038</v>
       </c>
       <c r="E103" t="str">
-        <v>Block Education Office Sheohar</v>
+        <v>Primary School Sheohar</v>
       </c>
       <c r="F103" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G103" t="str">
-        <v>9003000065</v>
+        <v>9003000042</v>
       </c>
       <c r="H103" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I103" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J103" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K103" t="str">
         <v>0301</v>
@@ -6692,7 +6692,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M103" t="str">
-        <v>30000514735</v>
+        <v>30000332598</v>
       </c>
       <c r="N103" t="str">
         <v>State Bank of India</v>
@@ -6701,48 +6701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P103" t="str">
-        <v>SBIN0009716</v>
+        <v>SBIN0009030</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>0300009</v>
+        <v>0300054</v>
       </c>
       <c r="B104" t="str">
-        <v>MAHESH PASWAN</v>
+        <v>SURESH RAI</v>
       </c>
       <c r="C104" t="str">
-        <v>Lecturer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D104" t="str">
-        <v>03009</v>
+        <v>03047</v>
       </c>
       <c r="E104" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>CDPO Office Dumri Katsari No.3</v>
       </c>
       <c r="F104" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G104" t="str">
-        <v>9003000009</v>
+        <v>9003000054</v>
       </c>
       <c r="H104" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I104" t="str">
+        <v>999999</v>
+      </c>
+      <c r="J104" t="str">
+        <v>Others</v>
+      </c>
+      <c r="K104" t="str">
         <v>0304</v>
       </c>
-      <c r="J104" t="str">
+      <c r="L104" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="K104" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L104" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M104" t="str">
-        <v>30000071271</v>
+        <v>30000427626</v>
       </c>
       <c r="N104" t="str">
         <v>State Bank of India</v>
@@ -6751,39 +6751,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P104" t="str">
-        <v>SBIN0008638</v>
+        <v>SBIN0009023</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>0300075</v>
+        <v>0300012</v>
       </c>
       <c r="B105" t="str">
-        <v>MD. IRFAN SAH</v>
+        <v>POONAM KHATUN</v>
       </c>
       <c r="C105" t="str">
-        <v>Clerk</v>
+        <v>Headmaster</v>
       </c>
       <c r="D105" t="str">
-        <v>03028</v>
+        <v>03012</v>
       </c>
       <c r="E105" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>Block Office Sheohar</v>
       </c>
       <c r="F105" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G105" t="str">
-        <v>9003000075</v>
+        <v>9003000012</v>
       </c>
       <c r="H105" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I105" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J105" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K105" t="str">
         <v>0301</v>
@@ -6792,7 +6792,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M105" t="str">
-        <v>30000593925</v>
+        <v>30000095028</v>
       </c>
       <c r="N105" t="str">
         <v>State Bank of India</v>
@@ -6801,48 +6801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P105" t="str">
-        <v>SBIN0008790</v>
+        <v>SBIN0007689</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>0300015</v>
+        <v>0300085</v>
       </c>
       <c r="B106" t="str">
-        <v>MUKESH JHA</v>
+        <v>RAJESH YADAV</v>
       </c>
       <c r="C106" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D106" t="str">
-        <v>03015</v>
+        <v>03013</v>
       </c>
       <c r="E106" t="str">
-        <v>Middle School Sheohar No.4</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F106" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G106" t="str">
-        <v>9003000015</v>
+        <v>9003000085</v>
       </c>
       <c r="H106" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I106" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J106" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K106" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L106" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M106" t="str">
-        <v>30000118785</v>
+        <v>30000673115</v>
       </c>
       <c r="N106" t="str">
         <v>State Bank of India</v>
@@ -6851,48 +6851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P106" t="str">
-        <v>SBIN0008562</v>
+        <v>SBIN0005100</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>0300024</v>
+        <v>0300105</v>
       </c>
       <c r="B107" t="str">
-        <v>ANITA MISHRA I</v>
+        <v>MUKESH SAH</v>
       </c>
       <c r="C107" t="str">
-        <v>Senior Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D107" t="str">
-        <v>03024</v>
+        <v>03070</v>
       </c>
       <c r="E107" t="str">
-        <v>Primary School Piprahi No.4</v>
+        <v>RWD Sub-Division Purnahiya</v>
       </c>
       <c r="F107" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G107" t="str">
-        <v>9003000024</v>
+        <v>9003000105</v>
       </c>
       <c r="H107" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I107" t="str">
-        <v>999999</v>
+        <v>0303</v>
       </c>
       <c r="J107" t="str">
-        <v>Others</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K107" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L107" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M107" t="str">
-        <v>30000190056</v>
+        <v>30000831495</v>
       </c>
       <c r="N107" t="str">
         <v>State Bank of India</v>
@@ -6901,48 +6901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P107" t="str">
-        <v>SBIN0004222</v>
+        <v>SBIN0003683</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>0300039</v>
+        <v>0300036</v>
       </c>
       <c r="B108" t="str">
-        <v>SUNIL GUPTA</v>
+        <v>REKHA KHATUN</v>
       </c>
       <c r="C108" t="str">
         <v>Assistant Teacher</v>
       </c>
       <c r="D108" t="str">
-        <v>03036</v>
+        <v>03032</v>
       </c>
       <c r="E108" t="str">
-        <v>High School Dumri Katsari No.3</v>
+        <v>Primary School Purnahiya No.2</v>
       </c>
       <c r="F108" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G108" t="str">
-        <v>9003000039</v>
+        <v>9003000036</v>
       </c>
       <c r="H108" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I108" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J108" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K108" t="str">
         <v>0303</v>
       </c>
-      <c r="J108" t="str">
+      <c r="L108" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="K108" t="str">
-        <v>0304</v>
-      </c>
-      <c r="L108" t="str">
-        <v>Dumri Katsari</v>
-      </c>
       <c r="M108" t="str">
-        <v>30000308841</v>
+        <v>30000285084</v>
       </c>
       <c r="N108" t="str">
         <v>State Bank of India</v>
@@ -6951,48 +6951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P108" t="str">
-        <v>SBIN0007984</v>
+        <v>SBIN0007542</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>0300076</v>
+        <v>0300084</v>
       </c>
       <c r="B109" t="str">
-        <v>MD. SHAHID MISHRA</v>
+        <v>MAMTA JHA E</v>
       </c>
       <c r="C109" t="str">
         <v>Data Entry Operator</v>
       </c>
       <c r="D109" t="str">
-        <v>03065</v>
+        <v>03027</v>
       </c>
       <c r="E109" t="str">
-        <v>PHC Purnahiya No.1</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="F109" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G109" t="str">
-        <v>9003000076</v>
+        <v>9003000084</v>
       </c>
       <c r="H109" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I109" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J109" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K109" t="str">
         <v>0301</v>
       </c>
-      <c r="J109" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K109" t="str">
-        <v>0303</v>
-      </c>
       <c r="L109" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M109" t="str">
-        <v>30000601844</v>
+        <v>30000665196</v>
       </c>
       <c r="N109" t="str">
         <v>State Bank of India</v>
@@ -7001,48 +7001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P109" t="str">
-        <v>SBIN0009536</v>
+        <v>SBIN0008276</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>0300123</v>
+        <v>0300080</v>
       </c>
       <c r="B110" t="str">
-        <v>MD. SHAHID JHA</v>
+        <v>MAMTA SAH</v>
       </c>
       <c r="C110" t="str">
-        <v>Postmaster</v>
+        <v>Teacher</v>
       </c>
       <c r="D110" t="str">
-        <v>03095</v>
+        <v>03033</v>
       </c>
       <c r="E110" t="str">
-        <v>State Bank of India, Tariyani</v>
+        <v>Project Girls High School Dumri Katsari</v>
       </c>
       <c r="F110" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G110" t="str">
-        <v>9003000123</v>
+        <v>9003000080</v>
       </c>
       <c r="H110" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I110" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J110" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K110" t="str">
         <v>0304</v>
       </c>
-      <c r="J110" t="str">
+      <c r="L110" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="K110" t="str">
-        <v>0305</v>
-      </c>
-      <c r="L110" t="str">
-        <v>Tariyani</v>
-      </c>
       <c r="M110" t="str">
-        <v>30000974037</v>
+        <v>30000633520</v>
       </c>
       <c r="N110" t="str">
         <v>State Bank of India</v>
@@ -7051,48 +7051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P110" t="str">
-        <v>SBIN0006515</v>
+        <v>SBIN0009353</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>0300056</v>
+        <v>0300094</v>
       </c>
       <c r="B111" t="str">
-        <v>NASREEN SINHA</v>
+        <v>FARHAT SINGH U</v>
       </c>
       <c r="C111" t="str">
-        <v>Teacher</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D111" t="str">
-        <v>03050</v>
+        <v>03013</v>
       </c>
       <c r="E111" t="str">
-        <v>Block Office Dumri Katsari No.2</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F111" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G111" t="str">
-        <v>9003000056</v>
+        <v>9003000094</v>
       </c>
       <c r="H111" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I111" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J111" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K111" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L111" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M111" t="str">
-        <v>30000443464</v>
+        <v>30000744386</v>
       </c>
       <c r="N111" t="str">
         <v>State Bank of India</v>
@@ -7101,48 +7101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P111" t="str">
-        <v>SBIN0005035</v>
+        <v>SBIN0004075</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>0300092</v>
+        <v>0300111</v>
       </c>
       <c r="B112" t="str">
-        <v>ALOK OJHA V</v>
+        <v>NITISH PASWAN</v>
       </c>
       <c r="C112" t="str">
-        <v>Revenue Officer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D112" t="str">
-        <v>03073</v>
+        <v>03088</v>
       </c>
       <c r="E112" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>Head Post Office, Piprahi</v>
       </c>
       <c r="F112" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G112" t="str">
-        <v>9003000092</v>
+        <v>9003000111</v>
       </c>
       <c r="H112" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I112" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J112" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K112" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L112" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M112" t="str">
-        <v>30000728548</v>
+        <v>30000879009</v>
       </c>
       <c r="N112" t="str">
         <v>State Bank of India</v>
@@ -7151,48 +7151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P112" t="str">
-        <v>SBIN0006064</v>
+        <v>SBIN0002407</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>0300031</v>
+        <v>0300123</v>
       </c>
       <c r="B113" t="str">
-        <v>RINKU VERMA</v>
+        <v>FARHAT VERMA</v>
       </c>
       <c r="C113" t="str">
-        <v>Head Clerk</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D113" t="str">
-        <v>03030</v>
+        <v>03097</v>
       </c>
       <c r="E113" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>UCO Bank, Purnahiya</v>
       </c>
       <c r="F113" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G113" t="str">
-        <v>9003000031</v>
+        <v>9003000123</v>
       </c>
       <c r="H113" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I113" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J113" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K113" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L113" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M113" t="str">
-        <v>30000245489</v>
+        <v>30000974037</v>
       </c>
       <c r="N113" t="str">
         <v>State Bank of India</v>
@@ -7201,33 +7201,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P113" t="str">
-        <v>SBIN0006302</v>
+        <v>SBIN0007993</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>0300125</v>
+        <v>0300004</v>
       </c>
       <c r="B114" t="str">
-        <v>REKHA CHAUDHARY</v>
+        <v>NEHA YADAV</v>
       </c>
       <c r="C114" t="str">
-        <v>Postmaster</v>
+        <v>Headmaster</v>
       </c>
       <c r="D114" t="str">
-        <v>03095</v>
+        <v>03004</v>
       </c>
       <c r="E114" t="str">
-        <v>State Bank of India, Tariyani</v>
+        <v>Kanya Middle School Piprahi No.1</v>
       </c>
       <c r="F114" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G114" t="str">
-        <v>9003000125</v>
+        <v>9003000004</v>
       </c>
       <c r="H114" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I114" t="str">
         <v>0302</v>
@@ -7236,13 +7236,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K114" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L114" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M114" t="str">
-        <v>30000989875</v>
+        <v>30000031676</v>
       </c>
       <c r="N114" t="str">
         <v>State Bank of India</v>
@@ -7251,33 +7251,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P114" t="str">
-        <v>SBIN0008440</v>
+        <v>SBIN0004874</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>0300113</v>
+        <v>0300035</v>
       </c>
       <c r="B115" t="str">
-        <v>VINOD ANSARI</v>
+        <v>VIJAY CHAUDHARY</v>
       </c>
       <c r="C115" t="str">
-        <v>Branch Manager</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D115" t="str">
-        <v>03088</v>
+        <v>03031</v>
       </c>
       <c r="E115" t="str">
-        <v>Punjab National Bank, Piprahi</v>
+        <v>Middle School Tariyani No.4</v>
       </c>
       <c r="F115" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G115" t="str">
-        <v>9003000113</v>
+        <v>9003000035</v>
       </c>
       <c r="H115" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I115" t="str">
         <v>0303</v>
@@ -7286,13 +7286,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K115" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L115" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M115" t="str">
-        <v>30000894847</v>
+        <v>30000277165</v>
       </c>
       <c r="N115" t="str">
         <v>State Bank of India</v>
@@ -7301,48 +7301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P115" t="str">
-        <v>SBIN0007696</v>
+        <v>SBIN0005083</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>0300100</v>
+        <v>0300098</v>
       </c>
       <c r="B116" t="str">
-        <v>USHA SINGH</v>
+        <v>SURESH CHAUDHARY</v>
       </c>
       <c r="C116" t="str">
-        <v>Revenue Officer</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D116" t="str">
-        <v>03078</v>
+        <v>03070</v>
       </c>
       <c r="E116" t="str">
-        <v>Minor Irrigation Office Dumri Katsari</v>
+        <v>RWD Sub-Division Purnahiya</v>
       </c>
       <c r="F116" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G116" t="str">
-        <v>9003000100</v>
+        <v>9003000098</v>
       </c>
       <c r="H116" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I116" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J116" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K116" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L116" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M116" t="str">
-        <v>30000791900</v>
+        <v>30000776062</v>
       </c>
       <c r="N116" t="str">
         <v>State Bank of India</v>
@@ -7351,48 +7351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P116" t="str">
-        <v>SBIN0007623</v>
+        <v>SBIN0001601</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>0300101</v>
+        <v>0300049</v>
       </c>
       <c r="B117" t="str">
-        <v>SUNITA RAI</v>
+        <v>ABDUL KALAM SINHA M</v>
       </c>
       <c r="C117" t="str">
-        <v>Junior Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D117" t="str">
-        <v>03007</v>
+        <v>03045</v>
       </c>
       <c r="E117" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>High School Tariyani No.2</v>
       </c>
       <c r="F117" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G117" t="str">
-        <v>9003000101</v>
+        <v>9003000049</v>
       </c>
       <c r="H117" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I117" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="J117" t="str">
-        <v>Others</v>
+        <v>Tariyani</v>
       </c>
       <c r="K117" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L117" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M117" t="str">
-        <v>30000799819</v>
+        <v>30000388031</v>
       </c>
       <c r="N117" t="str">
         <v>State Bank of India</v>
@@ -7401,39 +7401,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P117" t="str">
-        <v>SBIN0008014</v>
+        <v>SBIN0006530</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>0300017</v>
+        <v>0300033</v>
       </c>
       <c r="B118" t="str">
         <v>SUNITA OJHA</v>
       </c>
       <c r="C118" t="str">
-        <v>Headmaster</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D118" t="str">
-        <v>03017</v>
+        <v>03029</v>
       </c>
       <c r="E118" t="str">
-        <v>Primary School Dumri Katsari No.1</v>
+        <v>Middle School Dumri Katsari No.2</v>
       </c>
       <c r="F118" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G118" t="str">
-        <v>9003000017</v>
+        <v>9003000033</v>
       </c>
       <c r="H118" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I118" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J118" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K118" t="str">
         <v>0304</v>
@@ -7442,7 +7442,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M118" t="str">
-        <v>30000134623</v>
+        <v>30000261327</v>
       </c>
       <c r="N118" t="str">
         <v>State Bank of India</v>
@@ -7451,33 +7451,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P118" t="str">
-        <v>SBIN0001827</v>
+        <v>SBIN0001765</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>0300116</v>
+        <v>0300046</v>
       </c>
       <c r="B119" t="str">
-        <v>REKHA RAI</v>
+        <v>ALOK VERMA</v>
       </c>
       <c r="C119" t="str">
-        <v>Assistant Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D119" t="str">
-        <v>03091</v>
+        <v>03042</v>
       </c>
       <c r="E119" t="str">
-        <v>Punjab National Bank, Dumri Katsari</v>
+        <v>Block Education Office Purnahiya No.4</v>
       </c>
       <c r="F119" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G119" t="str">
-        <v>9003000116</v>
+        <v>9003000046</v>
       </c>
       <c r="H119" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I119" t="str">
         <v>0304</v>
@@ -7486,13 +7486,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K119" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L119" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M119" t="str">
-        <v>30000918604</v>
+        <v>30000364274</v>
       </c>
       <c r="N119" t="str">
         <v>State Bank of India</v>
@@ -7501,48 +7501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P119" t="str">
-        <v>SBIN0009603</v>
+        <v>SBIN0008960</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>0300094</v>
+        <v>0300014</v>
       </c>
       <c r="B120" t="str">
-        <v>FARHAT SAH</v>
+        <v>RAVI MISHRA</v>
       </c>
       <c r="C120" t="str">
         <v>Assistant Engineer</v>
       </c>
       <c r="D120" t="str">
-        <v>03072</v>
+        <v>03014</v>
       </c>
       <c r="E120" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>Block Education Office Sheohar No.2</v>
       </c>
       <c r="F120" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G120" t="str">
-        <v>9003000094</v>
+        <v>9003000014</v>
       </c>
       <c r="H120" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I120" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J120" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K120" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L120" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M120" t="str">
-        <v>30000744386</v>
+        <v>30000110866</v>
       </c>
       <c r="N120" t="str">
         <v>State Bank of India</v>
@@ -7551,48 +7551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P120" t="str">
-        <v>SBIN0006065</v>
+        <v>SBIN0002617</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>0300028</v>
+        <v>0300091</v>
       </c>
       <c r="B121" t="str">
-        <v>ANITA VERMA</v>
+        <v>RINKU PASWAN</v>
       </c>
       <c r="C121" t="str">
-        <v>Assistant Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D121" t="str">
-        <v>03028</v>
+        <v>03074</v>
       </c>
       <c r="E121" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F121" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G121" t="str">
-        <v>9003000028</v>
+        <v>9003000091</v>
       </c>
       <c r="H121" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I121" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J121" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K121" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L121" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M121" t="str">
-        <v>30000221732</v>
+        <v>30000720629</v>
       </c>
       <c r="N121" t="str">
         <v>State Bank of India</v>
@@ -7601,48 +7601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P121" t="str">
-        <v>SBIN0004159</v>
+        <v>SBIN0006038</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>0300085</v>
+        <v>0300113</v>
       </c>
       <c r="B122" t="str">
-        <v>MAHESH YADAV</v>
+        <v>SHAILESH THAKUR</v>
       </c>
       <c r="C122" t="str">
-        <v>Assistant Engineer</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D122" t="str">
-        <v>03030</v>
+        <v>03085</v>
       </c>
       <c r="E122" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>Head Post Office, Sheohar</v>
       </c>
       <c r="F122" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G122" t="str">
-        <v>9003000085</v>
+        <v>9003000113</v>
       </c>
       <c r="H122" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I122" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J122" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K122" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L122" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M122" t="str">
-        <v>30000673115</v>
+        <v>30000894847</v>
       </c>
       <c r="N122" t="str">
         <v>State Bank of India</v>
@@ -7651,33 +7651,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P122" t="str">
-        <v>SBIN0001284</v>
+        <v>SBIN0009155</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>0300043</v>
+        <v>0300003</v>
       </c>
       <c r="B123" t="str">
-        <v>NASREEN PASWAN</v>
+        <v>FARHAT PASWAN</v>
       </c>
       <c r="C123" t="str">
-        <v>Accountant</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D123" t="str">
-        <v>03040</v>
+        <v>03003</v>
       </c>
       <c r="E123" t="str">
-        <v>High School Dumri Katsari No.4</v>
+        <v>PHC Purnahiya</v>
       </c>
       <c r="F123" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G123" t="str">
-        <v>9003000043</v>
+        <v>9003000003</v>
       </c>
       <c r="H123" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I123" t="str">
         <v>0305</v>
@@ -7686,13 +7686,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K123" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L123" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M123" t="str">
-        <v>30000340517</v>
+        <v>30000023757</v>
       </c>
       <c r="N123" t="str">
         <v>State Bank of India</v>
@@ -7701,48 +7701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P123" t="str">
-        <v>SBIN0007841</v>
+        <v>SBIN0007923</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>0300108</v>
+        <v>0300119</v>
       </c>
       <c r="B124" t="str">
-        <v>FARHAT JHA</v>
+        <v>ASHA RAM</v>
       </c>
       <c r="C124" t="str">
-        <v>Assistant Manager</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D124" t="str">
-        <v>03083</v>
+        <v>03093</v>
       </c>
       <c r="E124" t="str">
-        <v>Central Bank of India, Piprahi</v>
+        <v>UCO Bank, Tariyani</v>
       </c>
       <c r="F124" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G124" t="str">
-        <v>9003000108</v>
+        <v>9003000119</v>
       </c>
       <c r="H124" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I124" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J124" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K124" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L124" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M124" t="str">
-        <v>30000855252</v>
+        <v>30000942361</v>
       </c>
       <c r="N124" t="str">
         <v>State Bank of India</v>
@@ -7751,33 +7751,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P124" t="str">
-        <v>SBIN0001163</v>
+        <v>SBIN0007464</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>0300099</v>
+        <v>0300013</v>
       </c>
       <c r="B125" t="str">
-        <v>NEHA RAI</v>
+        <v>MAMTA VERMA</v>
       </c>
       <c r="C125" t="str">
-        <v>Revenue Officer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D125" t="str">
-        <v>03052</v>
+        <v>03013</v>
       </c>
       <c r="E125" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F125" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G125" t="str">
-        <v>9003000099</v>
+        <v>9003000013</v>
       </c>
       <c r="H125" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I125" t="str">
         <v>0302</v>
@@ -7786,13 +7786,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K125" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L125" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M125" t="str">
-        <v>30000783981</v>
+        <v>30000102947</v>
       </c>
       <c r="N125" t="str">
         <v>State Bank of India</v>
@@ -7801,33 +7801,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P125" t="str">
-        <v>SBIN0001926</v>
+        <v>SBIN0006750</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>0300058</v>
+        <v>0300016</v>
       </c>
       <c r="B126" t="str">
-        <v>MD. SHAHID TIWARI</v>
+        <v>RINKU VERMA G</v>
       </c>
       <c r="C126" t="str">
-        <v>Accountant</v>
+        <v>Section Officer</v>
       </c>
       <c r="D126" t="str">
-        <v>03052</v>
+        <v>03016</v>
       </c>
       <c r="E126" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>PHC Sheohar No.2</v>
       </c>
       <c r="F126" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G126" t="str">
-        <v>9003000058</v>
+        <v>9003000016</v>
       </c>
       <c r="H126" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I126" t="str">
         <v>0301</v>
@@ -7836,13 +7836,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K126" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L126" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M126" t="str">
-        <v>30000459302</v>
+        <v>30000126704</v>
       </c>
       <c r="N126" t="str">
         <v>State Bank of India</v>
@@ -7851,48 +7851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P126" t="str">
-        <v>SBIN0007892</v>
+        <v>SBIN0006468</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>0300007</v>
+        <v>0300076</v>
       </c>
       <c r="B127" t="str">
-        <v>MAMTA KUMAR</v>
+        <v>SUNIL OJHA</v>
       </c>
       <c r="C127" t="str">
-        <v>Senior Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D127" t="str">
-        <v>03007</v>
+        <v>03065</v>
       </c>
       <c r="E127" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>High School Piprahi No.1</v>
       </c>
       <c r="F127" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G127" t="str">
-        <v>9003000007</v>
+        <v>9003000076</v>
       </c>
       <c r="H127" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I127" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J127" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K127" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L127" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M127" t="str">
-        <v>30000055433</v>
+        <v>30000601844</v>
       </c>
       <c r="N127" t="str">
         <v>State Bank of India</v>
@@ -7901,7 +7901,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P127" t="str">
-        <v>SBIN0006600</v>
+        <v>SBIN0004740</v>
       </c>
     </row>
   </sheetData>
@@ -7954,7 +7954,7 @@
         <v>Main</v>
       </c>
       <c r="D2" t="str">
-        <v>Middle School Sheohar, Room 2</v>
+        <v>Block Office Hall Sheohar, Room 2</v>
       </c>
       <c r="E2" t="str">
         <v>0301</v>
@@ -7994,7 +7994,7 @@
         <v>Main</v>
       </c>
       <c r="D4" t="str">
-        <v>Block Office Hall Purnahiya, Room 1</v>
+        <v>Panchayat Bhawan Purnahiya, Room 1</v>
       </c>
       <c r="E4" t="str">
         <v>0303</v>
@@ -8014,7 +8014,7 @@
         <v>Main</v>
       </c>
       <c r="D5" t="str">
-        <v>Panchayat Bhawan Dumri Katsari, Room 2</v>
+        <v>Middle School Dumri Katsari, Room 2</v>
       </c>
       <c r="E5" t="str">
         <v>0304</v>
@@ -8034,7 +8034,7 @@
         <v>Main</v>
       </c>
       <c r="D6" t="str">
-        <v>Middle School Tariyani, Room 3</v>
+        <v>High School Tariyani, Room 3</v>
       </c>
       <c r="E6" t="str">
         <v>0305</v>
@@ -8114,7 +8114,7 @@
         <v>Main</v>
       </c>
       <c r="D10" t="str">
-        <v>Middle School Tariyani, Room 1</v>
+        <v>Panchayat Bhawan Tariyani, Room 1</v>
       </c>
       <c r="E10" t="str">
         <v>0305</v>
@@ -8154,7 +8154,7 @@
         <v>Main</v>
       </c>
       <c r="D12" t="str">
-        <v>Block Office Hall Piprahi, Room 3</v>
+        <v>Middle School Piprahi, Room 3</v>
       </c>
       <c r="E12" t="str">
         <v>0302</v>

--- a/test-data/TEST_Sheohar_Project.xlsx
+++ b/test-data/TEST_Sheohar_Project.xlsx
@@ -613,7 +613,7 @@
         <v>Saved at</v>
       </c>
       <c r="B4" t="str">
-        <v>13-10-2026 17:27:50</v>
+        <v>13-10-2026 17:30:35</v>
       </c>
     </row>
     <row r="5">
@@ -792,7 +792,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>13-10-2026 17:27:50</v>
+        <v>13-10-2026 17:30:35</v>
       </c>
       <c r="B2" t="str">
         <v>Test data generated (Small — Sheohar style (5 blocks, 6 TC + 6 GC booths))</v>
@@ -1606,43 +1606,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0300053</v>
+        <v>0300074</v>
       </c>
       <c r="B2" t="str">
-        <v>NEHA GUPTA</v>
+        <v>RAMESH MISHRA</v>
       </c>
       <c r="C2" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D2" t="str">
-        <v>03046</v>
+        <v>03032</v>
       </c>
       <c r="E2" t="str">
-        <v>Civil Surgeon Office (deputed from other district)</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F2" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G2" t="str">
-        <v>9003000053</v>
+        <v>9003000074</v>
       </c>
       <c r="H2" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I2" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J2" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K2" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="L2" t="str">
-        <v>Other District</v>
+        <v>Sheohar</v>
       </c>
       <c r="M2" t="str">
-        <v>30000419707</v>
+        <v>30000586006</v>
       </c>
       <c r="N2" t="str">
         <v>State Bank of India</v>
@@ -1651,48 +1651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P2" t="str">
-        <v>SBIN0008550</v>
+        <v>SBIN0007741</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0300043</v>
+        <v>0300006</v>
       </c>
       <c r="B3" t="str">
-        <v>NIRMALA RAM</v>
+        <v>RAKESH CHAUDHARY</v>
       </c>
       <c r="C3" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D3" t="str">
-        <v>03039</v>
+        <v>03006</v>
       </c>
       <c r="E3" t="str">
-        <v>Primary School Tariyani No.3</v>
+        <v>Primary School Dumri Katsari No.3</v>
       </c>
       <c r="F3" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G3" t="str">
-        <v>9003000043</v>
+        <v>9003000006</v>
       </c>
       <c r="H3" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I3" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J3" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K3" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L3" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M3" t="str">
-        <v>30000340517</v>
+        <v>30000047514</v>
       </c>
       <c r="N3" t="str">
         <v>State Bank of India</v>
@@ -1701,39 +1701,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P3" t="str">
-        <v>SBIN0009606</v>
+        <v>SBIN0006526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0300001</v>
+        <v>0300085</v>
       </c>
       <c r="B4" t="str">
-        <v>VIJAY MAHTO</v>
+        <v>UMESH DEVI</v>
       </c>
       <c r="C4" t="str">
-        <v>Senior Teacher</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D4" t="str">
-        <v>03001</v>
+        <v>03070</v>
       </c>
       <c r="E4" t="str">
-        <v>Kanya Middle School Tariyani No.3</v>
+        <v>RWD Sub-Division Tariyani</v>
       </c>
       <c r="F4" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G4" t="str">
-        <v>9003000001</v>
+        <v>9003000085</v>
       </c>
       <c r="H4" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I4" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J4" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K4" t="str">
         <v>0305</v>
@@ -1742,7 +1742,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M4" t="str">
-        <v>30000007919</v>
+        <v>30000673115</v>
       </c>
       <c r="N4" t="str">
         <v>State Bank of India</v>
@@ -1751,48 +1751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P4" t="str">
-        <v>SBIN0002836</v>
+        <v>SBIN0004680</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0300062</v>
+        <v>0300024</v>
       </c>
       <c r="B5" t="str">
-        <v>ANIL SINHA</v>
+        <v>VINOD PASWAN</v>
       </c>
       <c r="C5" t="str">
-        <v>Clerk</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D5" t="str">
-        <v>03054</v>
+        <v>03023</v>
       </c>
       <c r="E5" t="str">
-        <v>Circle Office Purnahiya No.2</v>
+        <v>Block Office Piprahi No.3</v>
       </c>
       <c r="F5" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G5" t="str">
-        <v>9003000062</v>
+        <v>9003000024</v>
       </c>
       <c r="H5" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I5" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J5" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K5" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L5" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M5" t="str">
-        <v>30000490978</v>
+        <v>30000190056</v>
       </c>
       <c r="N5" t="str">
         <v>State Bank of India</v>
@@ -1801,39 +1801,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P5" t="str">
-        <v>SBIN0003992</v>
+        <v>SBIN0002842</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0300021</v>
+        <v>0300057</v>
       </c>
       <c r="B6" t="str">
-        <v>PANKAJ KHATUN</v>
+        <v>RANJIT PRASAD</v>
       </c>
       <c r="C6" t="str">
-        <v>Section Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D6" t="str">
-        <v>03018</v>
+        <v>03049</v>
       </c>
       <c r="E6" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>Middle School Sheohar No.2</v>
       </c>
       <c r="F6" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G6" t="str">
-        <v>9003000021</v>
+        <v>9003000057</v>
       </c>
       <c r="H6" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I6" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J6" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K6" t="str">
         <v>0301</v>
@@ -1842,7 +1842,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M6" t="str">
-        <v>30000166299</v>
+        <v>30000451383</v>
       </c>
       <c r="N6" t="str">
         <v>State Bank of India</v>
@@ -1851,48 +1851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P6" t="str">
-        <v>SBIN0006495</v>
+        <v>SBIN0008873</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>0300030</v>
+        <v>0300116</v>
       </c>
       <c r="B7" t="str">
-        <v>SANTOSH YADAV</v>
+        <v>USHA ALAM</v>
       </c>
       <c r="C7" t="str">
-        <v>Senior Clerk</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D7" t="str">
-        <v>03026</v>
+        <v>03091</v>
       </c>
       <c r="E7" t="str">
-        <v>Circle Office Tariyani No.2</v>
+        <v>BSNL Exchange, Sheohar</v>
       </c>
       <c r="F7" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G7" t="str">
-        <v>9003000030</v>
+        <v>9003000116</v>
       </c>
       <c r="H7" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I7" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J7" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K7" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L7" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M7" t="str">
-        <v>30000237570</v>
+        <v>30000918604</v>
       </c>
       <c r="N7" t="str">
         <v>State Bank of India</v>
@@ -1901,48 +1901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P7" t="str">
-        <v>SBIN0007393</v>
+        <v>SBIN0002265</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0300044</v>
+        <v>0300086</v>
       </c>
       <c r="B8" t="str">
-        <v>NITISH MISHRA</v>
+        <v>AJAY ANSARI</v>
       </c>
       <c r="C8" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D8" t="str">
-        <v>03040</v>
+        <v>03071</v>
       </c>
       <c r="E8" t="str">
-        <v>Project Girls High School Purnahiya</v>
+        <v>Circle Office Sheohar</v>
       </c>
       <c r="F8" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G8" t="str">
-        <v>9003000044</v>
+        <v>9003000086</v>
       </c>
       <c r="H8" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I8" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J8" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K8" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L8" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M8" t="str">
-        <v>30000348436</v>
+        <v>30000681034</v>
       </c>
       <c r="N8" t="str">
         <v>State Bank of India</v>
@@ -1951,48 +1951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P8" t="str">
-        <v>SBIN0005920</v>
+        <v>SBIN0007878</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0300093</v>
+        <v>0300109</v>
       </c>
       <c r="B9" t="str">
-        <v>PRIYANKA THAKUR</v>
+        <v>USHA RAI</v>
       </c>
       <c r="C9" t="str">
-        <v>Revenue Officer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D9" t="str">
-        <v>03076</v>
+        <v>03086</v>
       </c>
       <c r="E9" t="str">
-        <v>Minor Irrigation Office Tariyani</v>
+        <v>State Bank of India, Dumri Katsari</v>
       </c>
       <c r="F9" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G9" t="str">
-        <v>9003000093</v>
+        <v>9003000109</v>
       </c>
       <c r="H9" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I9" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J9" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K9" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L9" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M9" t="str">
-        <v>30000736467</v>
+        <v>30000863171</v>
       </c>
       <c r="N9" t="str">
         <v>State Bank of India</v>
@@ -2001,48 +2001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P9" t="str">
-        <v>SBIN0005987</v>
+        <v>SBIN0007547</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0300068</v>
+        <v>0300106</v>
       </c>
       <c r="B10" t="str">
-        <v>DINESH YADAV</v>
+        <v>NIRMALA KHATUN</v>
       </c>
       <c r="C10" t="str">
-        <v>Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D10" t="str">
-        <v>03058</v>
+        <v>03084</v>
       </c>
       <c r="E10" t="str">
-        <v>Circle Office Tariyani No.3</v>
+        <v>LIC Branch Office, Dumri Katsari</v>
       </c>
       <c r="F10" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G10" t="str">
-        <v>9003000068</v>
+        <v>9003000106</v>
       </c>
       <c r="H10" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I10" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J10" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K10" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L10" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M10" t="str">
-        <v>30000538492</v>
+        <v>30000839414</v>
       </c>
       <c r="N10" t="str">
         <v>State Bank of India</v>
@@ -2051,48 +2051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P10" t="str">
-        <v>SBIN0009583</v>
+        <v>SBIN0004673</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>0300020</v>
+        <v>0300104</v>
       </c>
       <c r="B11" t="str">
-        <v>RAJESH GUPTA</v>
+        <v>DINESH MAHTO</v>
       </c>
       <c r="C11" t="str">
-        <v>Section Officer</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D11" t="str">
-        <v>03017</v>
+        <v>03076</v>
       </c>
       <c r="E11" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>RWD Sub-Division Piprahi</v>
       </c>
       <c r="F11" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G11" t="str">
-        <v>9003000020</v>
+        <v>9003000104</v>
       </c>
       <c r="H11" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I11" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J11" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K11" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L11" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M11" t="str">
-        <v>30000158380</v>
+        <v>30000823576</v>
       </c>
       <c r="N11" t="str">
         <v>State Bank of India</v>
@@ -2101,7 +2101,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P11" t="str">
-        <v>SBIN0006103</v>
+        <v>SBIN0001523</v>
       </c>
     </row>
     <row r="12">
@@ -2109,16 +2109,16 @@
         <v>0300040</v>
       </c>
       <c r="B12" t="str">
-        <v>RAKESH KHATUN</v>
+        <v>KUMARI ANJALI GUPTA</v>
       </c>
       <c r="C12" t="str">
-        <v>Assistant Teacher</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D12" t="str">
-        <v>03036</v>
+        <v>03007</v>
       </c>
       <c r="E12" t="str">
-        <v>Project Girls High School Sheohar</v>
+        <v>PHED Division Sheohar</v>
       </c>
       <c r="F12" t="str">
         <v>Sheohar, Sheohar</v>
@@ -2130,10 +2130,10 @@
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I12" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J12" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K12" t="str">
         <v>0301</v>
@@ -2151,48 +2151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P12" t="str">
-        <v>SBIN0009078</v>
+        <v>SBIN0004065</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0300097</v>
+        <v>0300021</v>
       </c>
       <c r="B13" t="str">
-        <v>RAMESH ALAM</v>
+        <v>RAKESH TIWARI</v>
       </c>
       <c r="C13" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D13" t="str">
-        <v>03077</v>
+        <v>03020</v>
       </c>
       <c r="E13" t="str">
-        <v>Block Office Piprahi</v>
+        <v>Panchayat Bhawan Dumri Katsari</v>
       </c>
       <c r="F13" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G13" t="str">
-        <v>9003000097</v>
+        <v>9003000021</v>
       </c>
       <c r="H13" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I13" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J13" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K13" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L13" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M13" t="str">
-        <v>30000768143</v>
+        <v>30000166299</v>
       </c>
       <c r="N13" t="str">
         <v>State Bank of India</v>
@@ -2201,48 +2201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P13" t="str">
-        <v>SBIN0005356</v>
+        <v>SBIN0006244</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0300031</v>
+        <v>0300020</v>
       </c>
       <c r="B14" t="str">
-        <v>ASHA ALAM</v>
+        <v>SUNIL YADAV</v>
       </c>
       <c r="C14" t="str">
-        <v>Assistant Teacher</v>
+        <v>Headmaster</v>
       </c>
       <c r="D14" t="str">
-        <v>03027</v>
+        <v>03020</v>
       </c>
       <c r="E14" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Panchayat Bhawan Dumri Katsari</v>
       </c>
       <c r="F14" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G14" t="str">
-        <v>9003000031</v>
+        <v>9003000020</v>
       </c>
       <c r="H14" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I14" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J14" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K14" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L14" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M14" t="str">
-        <v>30000245489</v>
+        <v>30000158380</v>
       </c>
       <c r="N14" t="str">
         <v>State Bank of India</v>
@@ -2251,48 +2251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P14" t="str">
-        <v>SBIN0005421</v>
+        <v>SBIN0002891</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>0300007</v>
+        <v>0300123</v>
       </c>
       <c r="B15" t="str">
-        <v>ABDUL KALAM RAI</v>
+        <v>KIRAN RAI</v>
       </c>
       <c r="C15" t="str">
-        <v>Assistant Engineer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D15" t="str">
-        <v>03007</v>
+        <v>03096</v>
       </c>
       <c r="E15" t="str">
-        <v>Project Girls High School Piprahi No.3</v>
+        <v>UCO Bank, Purnahiya</v>
       </c>
       <c r="F15" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G15" t="str">
-        <v>9003000007</v>
+        <v>9003000123</v>
       </c>
       <c r="H15" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I15" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J15" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K15" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L15" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M15" t="str">
-        <v>30000055433</v>
+        <v>30000974037</v>
       </c>
       <c r="N15" t="str">
         <v>State Bank of India</v>
@@ -2301,33 +2301,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P15" t="str">
-        <v>SBIN0004521</v>
+        <v>SBIN0007445</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>0300045</v>
+        <v>0300029</v>
       </c>
       <c r="B16" t="str">
-        <v>DINESH SINHA</v>
+        <v>VIJAY MISHRA</v>
       </c>
       <c r="C16" t="str">
-        <v>Accountant</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D16" t="str">
-        <v>03041</v>
+        <v>03028</v>
       </c>
       <c r="E16" t="str">
-        <v>Panchayat Bhawan Tariyani No.4</v>
+        <v>Block Office Tariyani No.4</v>
       </c>
       <c r="F16" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G16" t="str">
-        <v>9003000045</v>
+        <v>9003000029</v>
       </c>
       <c r="H16" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I16" t="str">
         <v>0305</v>
@@ -2342,7 +2342,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M16" t="str">
-        <v>30000356355</v>
+        <v>30000229651</v>
       </c>
       <c r="N16" t="str">
         <v>State Bank of India</v>
@@ -2351,48 +2351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P16" t="str">
-        <v>SBIN0001444</v>
+        <v>SBIN0009241</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>0300023</v>
+        <v>0300047</v>
       </c>
       <c r="B17" t="str">
-        <v>VINOD VERMA</v>
+        <v>ALOK MAHTO</v>
       </c>
       <c r="C17" t="str">
-        <v>Head Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D17" t="str">
-        <v>03017</v>
+        <v>03040</v>
       </c>
       <c r="E17" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>Panchayat Bhawan Dumri Katsari No.4</v>
       </c>
       <c r="F17" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G17" t="str">
-        <v>9003000023</v>
+        <v>9003000047</v>
       </c>
       <c r="H17" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I17" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="J17" t="str">
-        <v>Others</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K17" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L17" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M17" t="str">
-        <v>30000182137</v>
+        <v>30000372193</v>
       </c>
       <c r="N17" t="str">
         <v>State Bank of India</v>
@@ -2401,48 +2401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P17" t="str">
-        <v>SBIN0007983</v>
+        <v>SBIN0004772</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>0300073</v>
+        <v>0300035</v>
       </c>
       <c r="B18" t="str">
-        <v>MD. SHAHID PANDEY</v>
+        <v>RINKU PASWAN</v>
       </c>
       <c r="C18" t="str">
-        <v>Clerk</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D18" t="str">
-        <v>03063</v>
+        <v>03033</v>
       </c>
       <c r="E18" t="str">
-        <v>Project Girls High School Piprahi No.2</v>
+        <v>High School Tariyani No.2</v>
       </c>
       <c r="F18" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G18" t="str">
-        <v>9003000073</v>
+        <v>9003000035</v>
       </c>
       <c r="H18" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I18" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J18" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K18" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L18" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M18" t="str">
-        <v>30000578087</v>
+        <v>30000277165</v>
       </c>
       <c r="N18" t="str">
         <v>State Bank of India</v>
@@ -2451,48 +2451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P18" t="str">
-        <v>SBIN0007843</v>
+        <v>SBIN0005903</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>0300015</v>
+        <v>0300001</v>
       </c>
       <c r="B19" t="str">
-        <v>SURESH THAKUR</v>
+        <v>ASHA OJHA</v>
       </c>
       <c r="C19" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D19" t="str">
-        <v>03015</v>
+        <v>03001</v>
       </c>
       <c r="E19" t="str">
-        <v>Block Education Office Dumri Katsari No.1</v>
+        <v>Primary School Purnahiya</v>
       </c>
       <c r="F19" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G19" t="str">
-        <v>9003000015</v>
+        <v>9003000001</v>
       </c>
       <c r="H19" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I19" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J19" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K19" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L19" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M19" t="str">
-        <v>30000118785</v>
+        <v>30000007919</v>
       </c>
       <c r="N19" t="str">
         <v>State Bank of India</v>
@@ -2501,15 +2501,15 @@
         <v>Sheohar</v>
       </c>
       <c r="P19" t="str">
-        <v>SBIN0008928</v>
+        <v>SBIN0002099</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>0300100</v>
+        <v>0300089</v>
       </c>
       <c r="B20" t="str">
-        <v>MD. SHAHID MAHTO</v>
+        <v>RINKU KUMAR</v>
       </c>
       <c r="C20" t="str">
         <v>Junior Engineer</v>
@@ -2518,31 +2518,31 @@
         <v>03074</v>
       </c>
       <c r="E20" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>Minor Irrigation Office Tariyani</v>
       </c>
       <c r="F20" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G20" t="str">
-        <v>9003000100</v>
+        <v>9003000089</v>
       </c>
       <c r="H20" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I20" t="str">
-        <v>0303</v>
+        <v>999999</v>
       </c>
       <c r="J20" t="str">
-        <v>Purnahiya</v>
+        <v>Others</v>
       </c>
       <c r="K20" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L20" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M20" t="str">
-        <v>30000791900</v>
+        <v>30000704791</v>
       </c>
       <c r="N20" t="str">
         <v>State Bank of India</v>
@@ -2551,48 +2551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P20" t="str">
-        <v>SBIN0004933</v>
+        <v>SBIN0009790</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>0300017</v>
+        <v>0300064</v>
       </c>
       <c r="B21" t="str">
-        <v>KUMARI ANJALI TIWARI</v>
+        <v>RINKU CHAUDHARY</v>
       </c>
       <c r="C21" t="str">
-        <v>Section Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D21" t="str">
-        <v>03017</v>
+        <v>03056</v>
       </c>
       <c r="E21" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>Primary School Tariyani No.4</v>
       </c>
       <c r="F21" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G21" t="str">
-        <v>9003000017</v>
+        <v>9003000064</v>
       </c>
       <c r="H21" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I21" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J21" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K21" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L21" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M21" t="str">
-        <v>30000134623</v>
+        <v>30000506816</v>
       </c>
       <c r="N21" t="str">
         <v>State Bank of India</v>
@@ -2601,48 +2601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P21" t="str">
-        <v>SBIN0009639</v>
+        <v>SBIN0008428</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>0300064</v>
+        <v>0300044</v>
       </c>
       <c r="B22" t="str">
-        <v>MUKESH OJHA</v>
+        <v>SANJAY GUPTA</v>
       </c>
       <c r="C22" t="str">
-        <v>Data Entry Operator</v>
+        <v>Teacher</v>
       </c>
       <c r="D22" t="str">
-        <v>03023</v>
+        <v>03017</v>
       </c>
       <c r="E22" t="str">
-        <v>Project Girls High School Tariyani No.1</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="F22" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G22" t="str">
-        <v>9003000064</v>
+        <v>9003000044</v>
       </c>
       <c r="H22" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I22" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J22" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K22" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L22" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M22" t="str">
-        <v>30000506816</v>
+        <v>30000348436</v>
       </c>
       <c r="N22" t="str">
         <v>State Bank of India</v>
@@ -2651,48 +2651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P22" t="str">
-        <v>SBIN0009403</v>
+        <v>SBIN0001253</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>0300079</v>
+        <v>0300098</v>
       </c>
       <c r="B23" t="str">
-        <v>FARHAT KUMAR</v>
+        <v>ASHA SHARMA</v>
       </c>
       <c r="C23" t="str">
-        <v>Teacher</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D23" t="str">
-        <v>03050</v>
+        <v>03078</v>
       </c>
       <c r="E23" t="str">
-        <v>Project Girls High School Tariyani</v>
+        <v>Minor Irrigation Office Sheohar</v>
       </c>
       <c r="F23" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G23" t="str">
-        <v>9003000079</v>
+        <v>9003000098</v>
       </c>
       <c r="H23" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I23" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J23" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K23" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L23" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M23" t="str">
-        <v>30000625601</v>
+        <v>30000776062</v>
       </c>
       <c r="N23" t="str">
         <v>State Bank of India</v>
@@ -2701,48 +2701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P23" t="str">
-        <v>SBIN0004649</v>
+        <v>SBIN0003117</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>0300082</v>
+        <v>0300118</v>
       </c>
       <c r="B24" t="str">
-        <v>MD. SHAHID SAH</v>
+        <v>KIRAN SAH</v>
       </c>
       <c r="C24" t="str">
-        <v>Office Assistant</v>
+        <v>Postmaster</v>
       </c>
       <c r="D24" t="str">
-        <v>03069</v>
+        <v>03094</v>
       </c>
       <c r="E24" t="str">
-        <v>Block Education Office Tariyani No.2</v>
+        <v>Central Bank of India, Piprahi</v>
       </c>
       <c r="F24" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G24" t="str">
-        <v>9003000082</v>
+        <v>9003000118</v>
       </c>
       <c r="H24" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I24" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J24" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K24" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L24" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M24" t="str">
-        <v>30000649358</v>
+        <v>30000934442</v>
       </c>
       <c r="N24" t="str">
         <v>State Bank of India</v>
@@ -2751,48 +2751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P24" t="str">
-        <v>SBIN0006652</v>
+        <v>SBIN0005227</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0300095</v>
+        <v>0300042</v>
       </c>
       <c r="B25" t="str">
-        <v>RAVI YADAV</v>
+        <v>UMESH OJHA</v>
       </c>
       <c r="C25" t="str">
-        <v>Revenue Officer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D25" t="str">
-        <v>03076</v>
+        <v>03036</v>
       </c>
       <c r="E25" t="str">
-        <v>Minor Irrigation Office Tariyani</v>
+        <v>CDPO Office Piprahi No.3</v>
       </c>
       <c r="F25" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G25" t="str">
-        <v>9003000095</v>
+        <v>9003000042</v>
       </c>
       <c r="H25" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I25" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J25" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K25" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L25" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M25" t="str">
-        <v>30000752305</v>
+        <v>30000332598</v>
       </c>
       <c r="N25" t="str">
         <v>State Bank of India</v>
@@ -2801,33 +2801,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P25" t="str">
-        <v>SBIN0006486</v>
+        <v>SBIN0003580</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>0300115</v>
+        <v>0300018</v>
       </c>
       <c r="B26" t="str">
-        <v>SURESH VERMA</v>
+        <v>REKHA YADAV</v>
       </c>
       <c r="C26" t="str">
-        <v>Postmaster</v>
+        <v>Section Officer</v>
       </c>
       <c r="D26" t="str">
-        <v>03091</v>
+        <v>03018</v>
       </c>
       <c r="E26" t="str">
-        <v>BSNL Exchange, Dumri Katsari</v>
+        <v>Block Office Dumri Katsari No.4</v>
       </c>
       <c r="F26" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G26" t="str">
-        <v>9003000115</v>
+        <v>9003000018</v>
       </c>
       <c r="H26" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I26" t="str">
         <v>0304</v>
@@ -2842,7 +2842,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M26" t="str">
-        <v>30000910685</v>
+        <v>30000142542</v>
       </c>
       <c r="N26" t="str">
         <v>State Bank of India</v>
@@ -2851,33 +2851,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P26" t="str">
-        <v>SBIN0002417</v>
+        <v>SBIN0006984</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>0300047</v>
+        <v>0300119</v>
       </c>
       <c r="B27" t="str">
-        <v>USHA RAM</v>
+        <v>MD. SHAHID KHATUN</v>
       </c>
       <c r="C27" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D27" t="str">
-        <v>03043</v>
+        <v>03095</v>
       </c>
       <c r="E27" t="str">
-        <v>Panchayat Bhawan Sheohar</v>
+        <v>Central Bank of India, Sheohar</v>
       </c>
       <c r="F27" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G27" t="str">
-        <v>9003000047</v>
+        <v>9003000119</v>
       </c>
       <c r="H27" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I27" t="str">
         <v>0301</v>
@@ -2892,7 +2892,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M27" t="str">
-        <v>30000372193</v>
+        <v>30000942361</v>
       </c>
       <c r="N27" t="str">
         <v>State Bank of India</v>
@@ -2901,48 +2901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P27" t="str">
-        <v>SBIN0004946</v>
+        <v>SBIN0009780</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>0300067</v>
+        <v>0300076</v>
       </c>
       <c r="B28" t="str">
-        <v>RAKESH OJHA</v>
+        <v>SURESH ALAM</v>
       </c>
       <c r="C28" t="str">
-        <v>Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D28" t="str">
-        <v>03057</v>
+        <v>03064</v>
       </c>
       <c r="E28" t="str">
-        <v>Panchayat Bhawan Piprahi</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F28" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G28" t="str">
-        <v>9003000067</v>
+        <v>9003000076</v>
       </c>
       <c r="H28" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I28" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J28" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K28" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L28" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M28" t="str">
-        <v>30000530573</v>
+        <v>30000601844</v>
       </c>
       <c r="N28" t="str">
         <v>State Bank of India</v>
@@ -2951,48 +2951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P28" t="str">
-        <v>SBIN0006413</v>
+        <v>SBIN0006430</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>0300112</v>
+        <v>0300030</v>
       </c>
       <c r="B29" t="str">
-        <v>RAJESH RAI</v>
+        <v>RAKESH ANSARI</v>
       </c>
       <c r="C29" t="str">
-        <v>Administrative Officer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D29" t="str">
-        <v>03089</v>
+        <v>03029</v>
       </c>
       <c r="E29" t="str">
-        <v>Central Bank of India, Purnahiya</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="F29" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G29" t="str">
-        <v>9003000112</v>
+        <v>9003000030</v>
       </c>
       <c r="H29" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I29" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J29" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K29" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L29" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M29" t="str">
-        <v>30000886928</v>
+        <v>30000237570</v>
       </c>
       <c r="N29" t="str">
         <v>State Bank of India</v>
@@ -3001,48 +3001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P29" t="str">
-        <v>SBIN0004350</v>
+        <v>SBIN0008493</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>0300038</v>
+        <v>0300010</v>
       </c>
       <c r="B30" t="str">
-        <v>DINESH RAM</v>
+        <v>RANJIT THAKUR</v>
       </c>
       <c r="C30" t="str">
-        <v>Senior Clerk</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D30" t="str">
-        <v>03034</v>
+        <v>03010</v>
       </c>
       <c r="E30" t="str">
-        <v>District Treasury Sheohar</v>
+        <v>Primary School Purnahiya No.3</v>
       </c>
       <c r="F30" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G30" t="str">
-        <v>9003000038</v>
+        <v>9003000010</v>
       </c>
       <c r="H30" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I30" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J30" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K30" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L30" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M30" t="str">
-        <v>30000300922</v>
+        <v>30000079190</v>
       </c>
       <c r="N30" t="str">
         <v>State Bank of India</v>
@@ -3051,48 +3051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P30" t="str">
-        <v>SBIN0007235</v>
+        <v>SBIN0003171</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>0300121</v>
+        <v>0300105</v>
       </c>
       <c r="B31" t="str">
-        <v>RAKESH TIWARI</v>
+        <v>MANOJ THAKUR</v>
       </c>
       <c r="C31" t="str">
-        <v>Branch Manager</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D31" t="str">
-        <v>03095</v>
+        <v>03075</v>
       </c>
       <c r="E31" t="str">
-        <v>Punjab National Bank, Piprahi</v>
+        <v>RWD Sub-Division Purnahiya</v>
       </c>
       <c r="F31" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G31" t="str">
-        <v>9003000121</v>
+        <v>9003000105</v>
       </c>
       <c r="H31" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I31" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J31" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K31" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L31" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M31" t="str">
-        <v>30000958199</v>
+        <v>30000831495</v>
       </c>
       <c r="N31" t="str">
         <v>State Bank of India</v>
@@ -3101,48 +3101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P31" t="str">
-        <v>SBIN0009242</v>
+        <v>SBIN0003073</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>0300034</v>
+        <v>0300045</v>
       </c>
       <c r="B32" t="str">
-        <v>REKHA ANSARI</v>
+        <v>FARHAT THAKUR</v>
       </c>
       <c r="C32" t="str">
-        <v>Head Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D32" t="str">
-        <v>03030</v>
+        <v>03038</v>
       </c>
       <c r="E32" t="str">
-        <v>Project Girls High School Sheohar No.3</v>
+        <v>Circle Office Tariyani No.2</v>
       </c>
       <c r="F32" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G32" t="str">
-        <v>9003000034</v>
+        <v>9003000045</v>
       </c>
       <c r="H32" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I32" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J32" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K32" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L32" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M32" t="str">
-        <v>30000269246</v>
+        <v>30000356355</v>
       </c>
       <c r="N32" t="str">
         <v>State Bank of India</v>
@@ -3151,39 +3151,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P32" t="str">
-        <v>SBIN0007918</v>
+        <v>SBIN0001358</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>0300108</v>
+        <v>0300036</v>
       </c>
       <c r="B33" t="str">
-        <v>SHAILESH SINGH</v>
+        <v>REKHA VERMA</v>
       </c>
       <c r="C33" t="str">
-        <v>Assistant Manager</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D33" t="str">
-        <v>03085</v>
+        <v>03034</v>
       </c>
       <c r="E33" t="str">
-        <v>Head Post Office, Sheohar</v>
+        <v>Primary School Sheohar No.4</v>
       </c>
       <c r="F33" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G33" t="str">
-        <v>9003000108</v>
+        <v>9003000036</v>
       </c>
       <c r="H33" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I33" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J33" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K33" t="str">
         <v>0301</v>
@@ -3192,7 +3192,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M33" t="str">
-        <v>30000855252</v>
+        <v>30000285084</v>
       </c>
       <c r="N33" t="str">
         <v>State Bank of India</v>
@@ -3201,48 +3201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P33" t="str">
-        <v>SBIN0006138</v>
+        <v>SBIN0007569</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>0300032</v>
+        <v>0300073</v>
       </c>
       <c r="B34" t="str">
-        <v>SUNITA YADAV</v>
+        <v>NITISH ALAM</v>
       </c>
       <c r="C34" t="str">
-        <v>Head Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D34" t="str">
-        <v>03028</v>
+        <v>03032</v>
       </c>
       <c r="E34" t="str">
-        <v>Panchayat Bhawan Dumri Katsari No.1</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F34" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G34" t="str">
-        <v>9003000032</v>
+        <v>9003000073</v>
       </c>
       <c r="H34" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I34" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J34" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K34" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L34" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M34" t="str">
-        <v>30000253408</v>
+        <v>30000578087</v>
       </c>
       <c r="N34" t="str">
         <v>State Bank of India</v>
@@ -3251,33 +3251,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P34" t="str">
-        <v>SBIN0004950</v>
+        <v>SBIN0007462</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>0300009</v>
+        <v>0300126</v>
       </c>
       <c r="B35" t="str">
-        <v>FARHAT SINGH</v>
+        <v>SUNITA KUMAR</v>
       </c>
       <c r="C35" t="str">
-        <v>Assistant Engineer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D35" t="str">
-        <v>03009</v>
+        <v>03098</v>
       </c>
       <c r="E35" t="str">
-        <v>High School Dumri Katsari No.3</v>
+        <v>Punjab National Bank, Piprahi</v>
       </c>
       <c r="F35" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G35" t="str">
-        <v>9003000009</v>
+        <v>9003000126</v>
       </c>
       <c r="H35" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I35" t="str">
         <v>0304</v>
@@ -3286,13 +3286,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K35" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L35" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M35" t="str">
-        <v>30000071271</v>
+        <v>30000997794</v>
       </c>
       <c r="N35" t="str">
         <v>State Bank of India</v>
@@ -3301,33 +3301,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P35" t="str">
-        <v>SBIN0003534</v>
+        <v>SBIN0003521</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>0300029</v>
+        <v>0300066</v>
       </c>
       <c r="B36" t="str">
-        <v>PRIYANKA PRASAD</v>
+        <v>AMIT MISHRA</v>
       </c>
       <c r="C36" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D36" t="str">
-        <v>03025</v>
+        <v>03058</v>
       </c>
       <c r="E36" t="str">
-        <v>Block Office Sheohar No.3</v>
+        <v>Project Girls High School Dumri Katsari No.1</v>
       </c>
       <c r="F36" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G36" t="str">
-        <v>9003000029</v>
+        <v>9003000066</v>
       </c>
       <c r="H36" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I36" t="str">
         <v>0301</v>
@@ -3336,13 +3336,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K36" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L36" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M36" t="str">
-        <v>30000229651</v>
+        <v>30000522654</v>
       </c>
       <c r="N36" t="str">
         <v>State Bank of India</v>
@@ -3351,21 +3351,21 @@
         <v>Sheohar</v>
       </c>
       <c r="P36" t="str">
-        <v>SBIN0009606</v>
+        <v>SBIN0006440</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>0300101</v>
+        <v>0300100</v>
       </c>
       <c r="B37" t="str">
-        <v>SANTOSH PRASAD</v>
+        <v>SANTOSH PASWAN</v>
       </c>
       <c r="C37" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D37" t="str">
-        <v>03079</v>
+        <v>03080</v>
       </c>
       <c r="E37" t="str">
         <v>Minor Irrigation Office Piprahi</v>
@@ -3374,16 +3374,16 @@
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G37" t="str">
-        <v>9003000101</v>
+        <v>9003000100</v>
       </c>
       <c r="H37" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I37" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J37" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K37" t="str">
         <v>0302</v>
@@ -3392,7 +3392,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M37" t="str">
-        <v>30000799819</v>
+        <v>30000791900</v>
       </c>
       <c r="N37" t="str">
         <v>State Bank of India</v>
@@ -3401,48 +3401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P37" t="str">
-        <v>SBIN0005802</v>
+        <v>SBIN0005969</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>0300072</v>
+        <v>0300084</v>
       </c>
       <c r="B38" t="str">
-        <v>RANJIT THAKUR</v>
+        <v>PRIYANKA ALAM D</v>
       </c>
       <c r="C38" t="str">
-        <v>Office Assistant</v>
+        <v>Clerk</v>
       </c>
       <c r="D38" t="str">
-        <v>03062</v>
+        <v>03045</v>
       </c>
       <c r="E38" t="str">
-        <v>Block Office Dumri Katsari No.3</v>
+        <v>PHC Tariyani</v>
       </c>
       <c r="F38" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G38" t="str">
-        <v>9003000072</v>
+        <v>9003000084</v>
       </c>
       <c r="H38" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I38" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J38" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K38" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L38" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M38" t="str">
-        <v>30000570168</v>
+        <v>30000665196</v>
       </c>
       <c r="N38" t="str">
         <v>State Bank of India</v>
@@ -3451,48 +3451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P38" t="str">
-        <v>SBIN0009704</v>
+        <v>SBIN0009875</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>0300005</v>
+        <v>0300096</v>
       </c>
       <c r="B39" t="str">
-        <v>PANKAJ RAM</v>
+        <v>RAVI PANDEY</v>
       </c>
       <c r="C39" t="str">
-        <v>Senior Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D39" t="str">
-        <v>03005</v>
+        <v>03077</v>
       </c>
       <c r="E39" t="str">
-        <v>Primary School Sheohar No.4</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="F39" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G39" t="str">
-        <v>9003000005</v>
+        <v>9003000096</v>
       </c>
       <c r="H39" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I39" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J39" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K39" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L39" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M39" t="str">
-        <v>30000039595</v>
+        <v>30000760224</v>
       </c>
       <c r="N39" t="str">
         <v>State Bank of India</v>
@@ -3501,48 +3501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P39" t="str">
-        <v>SBIN0002228</v>
+        <v>SBIN0001387</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>0300063</v>
+        <v>0300061</v>
       </c>
       <c r="B40" t="str">
-        <v>SUNITA SAH</v>
+        <v>MUKESH DEVI</v>
       </c>
       <c r="C40" t="str">
-        <v>Teacher</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D40" t="str">
-        <v>03021</v>
+        <v>03053</v>
       </c>
       <c r="E40" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>Panchayat Bhawan Piprahi No.2</v>
       </c>
       <c r="F40" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G40" t="str">
-        <v>9003000063</v>
+        <v>9003000061</v>
       </c>
       <c r="H40" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I40" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="J40" t="str">
-        <v>Dumri Katsari</v>
+        <v>Others</v>
       </c>
       <c r="K40" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L40" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M40" t="str">
-        <v>30000498897</v>
+        <v>30000483059</v>
       </c>
       <c r="N40" t="str">
         <v>State Bank of India</v>
@@ -3551,48 +3551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P40" t="str">
-        <v>SBIN0001246</v>
+        <v>SBIN0002042</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>0300006</v>
+        <v>0300082</v>
       </c>
       <c r="B41" t="str">
-        <v>RINKU VERMA</v>
+        <v>POONAM RAM</v>
       </c>
       <c r="C41" t="str">
-        <v>Senior Teacher</v>
+        <v>Teacher</v>
       </c>
       <c r="D41" t="str">
-        <v>03006</v>
+        <v>03069</v>
       </c>
       <c r="E41" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>Middle School Purnahiya No.2</v>
       </c>
       <c r="F41" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G41" t="str">
-        <v>9003000006</v>
+        <v>9003000082</v>
       </c>
       <c r="H41" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I41" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J41" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K41" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L41" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M41" t="str">
-        <v>30000047514</v>
+        <v>30000649358</v>
       </c>
       <c r="N41" t="str">
         <v>State Bank of India</v>
@@ -3601,48 +3601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P41" t="str">
-        <v>SBIN0009695</v>
+        <v>SBIN0006350</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>0300039</v>
+        <v>0300002</v>
       </c>
       <c r="B42" t="str">
-        <v>SURESH SAH</v>
+        <v>RAKESH SAH</v>
       </c>
       <c r="C42" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Lecturer</v>
       </c>
       <c r="D42" t="str">
-        <v>03035</v>
+        <v>03002</v>
       </c>
       <c r="E42" t="str">
-        <v>Block Education Office Dumri Katsari No.2</v>
+        <v>High School Piprahi</v>
       </c>
       <c r="F42" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G42" t="str">
-        <v>9003000039</v>
+        <v>9003000002</v>
       </c>
       <c r="H42" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I42" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J42" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K42" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L42" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M42" t="str">
-        <v>30000308841</v>
+        <v>30000015838</v>
       </c>
       <c r="N42" t="str">
         <v>State Bank of India</v>
@@ -3651,30 +3651,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P42" t="str">
-        <v>SBIN0002917</v>
+        <v>SBIN0002848</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>0300096</v>
+        <v>0300094</v>
       </c>
       <c r="B43" t="str">
-        <v>RANJIT TIWARI</v>
+        <v>PRIYANKA RAI</v>
       </c>
       <c r="C43" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D43" t="str">
-        <v>03072</v>
+        <v>03077</v>
       </c>
       <c r="E43" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="F43" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G43" t="str">
-        <v>9003000096</v>
+        <v>9003000094</v>
       </c>
       <c r="H43" t="str">
         <v>PATROLLING MAGISTRATE</v>
@@ -3686,13 +3686,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K43" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L43" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M43" t="str">
-        <v>30000760224</v>
+        <v>30000744386</v>
       </c>
       <c r="N43" t="str">
         <v>State Bank of India</v>
@@ -3701,48 +3701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P43" t="str">
-        <v>SBIN0009892</v>
+        <v>SBIN0003963</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>0300075</v>
+        <v>0300067</v>
       </c>
       <c r="B44" t="str">
-        <v>RINKU GUPTA</v>
+        <v>VINOD KHATUN</v>
       </c>
       <c r="C44" t="str">
-        <v>Office Assistant</v>
+        <v>Teacher</v>
       </c>
       <c r="D44" t="str">
-        <v>03024</v>
+        <v>03018</v>
       </c>
       <c r="E44" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Block Office Dumri Katsari No.4</v>
       </c>
       <c r="F44" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G44" t="str">
-        <v>9003000075</v>
+        <v>9003000067</v>
       </c>
       <c r="H44" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I44" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J44" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K44" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L44" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M44" t="str">
-        <v>30000593925</v>
+        <v>30000530573</v>
       </c>
       <c r="N44" t="str">
         <v>State Bank of India</v>
@@ -3751,48 +3751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P44" t="str">
-        <v>SBIN0003337</v>
+        <v>SBIN0003378</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>0300041</v>
+        <v>0300017</v>
       </c>
       <c r="B45" t="str">
-        <v>MAMTA THAKUR</v>
+        <v>SUNIL PRASAD</v>
       </c>
       <c r="C45" t="str">
-        <v>Senior Clerk</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D45" t="str">
-        <v>03037</v>
+        <v>03017</v>
       </c>
       <c r="E45" t="str">
-        <v>Project Girls High School Piprahi No.1</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="F45" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G45" t="str">
-        <v>9003000041</v>
+        <v>9003000017</v>
       </c>
       <c r="H45" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I45" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J45" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K45" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L45" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M45" t="str">
-        <v>30000324679</v>
+        <v>30000134623</v>
       </c>
       <c r="N45" t="str">
         <v>State Bank of India</v>
@@ -3801,48 +3801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P45" t="str">
-        <v>SBIN0001168</v>
+        <v>SBIN0002029</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>0300061</v>
+        <v>0300114</v>
       </c>
       <c r="B46" t="str">
-        <v>SUNIL THAKUR</v>
+        <v>MD. IRFAN CHAUDHARY</v>
       </c>
       <c r="C46" t="str">
-        <v>Accountant</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D46" t="str">
-        <v>03053</v>
+        <v>03091</v>
       </c>
       <c r="E46" t="str">
-        <v>Middle School Purnahiya No.1</v>
+        <v>BSNL Exchange, Sheohar</v>
       </c>
       <c r="F46" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G46" t="str">
-        <v>9003000061</v>
+        <v>9003000114</v>
       </c>
       <c r="H46" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I46" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J46" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K46" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L46" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M46" t="str">
-        <v>30000483059</v>
+        <v>30000902766</v>
       </c>
       <c r="N46" t="str">
         <v>State Bank of India</v>
@@ -3851,33 +3851,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P46" t="str">
-        <v>SBIN0003127</v>
+        <v>SBIN0009498</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0300066</v>
+        <v>0300121</v>
       </c>
       <c r="B47" t="str">
-        <v>REKHA JHA</v>
+        <v>MAMTA JHA</v>
       </c>
       <c r="C47" t="str">
-        <v>Clerk</v>
+        <v>Postmaster</v>
       </c>
       <c r="D47" t="str">
-        <v>03056</v>
+        <v>03088</v>
       </c>
       <c r="E47" t="str">
-        <v>PHC Tariyani No.2</v>
+        <v>Head Post Office, Purnahiya</v>
       </c>
       <c r="F47" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G47" t="str">
-        <v>9003000066</v>
+        <v>9003000121</v>
       </c>
       <c r="H47" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I47" t="str">
         <v>0305</v>
@@ -3886,13 +3886,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K47" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L47" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M47" t="str">
-        <v>30000522654</v>
+        <v>30000958199</v>
       </c>
       <c r="N47" t="str">
         <v>State Bank of India</v>
@@ -3901,48 +3901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P47" t="str">
-        <v>SBIN0006386</v>
+        <v>SBIN0006366</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0300107</v>
+        <v>0300048</v>
       </c>
       <c r="B48" t="str">
-        <v>RAMESH PASWAN</v>
+        <v>RAJESH SAH</v>
       </c>
       <c r="C48" t="str">
-        <v>Branch Manager</v>
+        <v>Accountant</v>
       </c>
       <c r="D48" t="str">
-        <v>03084</v>
+        <v>03041</v>
       </c>
       <c r="E48" t="str">
-        <v>Bank of India, Sheohar</v>
+        <v>Panchayat Bhawan Piprahi</v>
       </c>
       <c r="F48" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G48" t="str">
-        <v>9003000107</v>
+        <v>9003000048</v>
       </c>
       <c r="H48" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I48" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J48" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K48" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L48" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M48" t="str">
-        <v>30000847333</v>
+        <v>30000380112</v>
       </c>
       <c r="N48" t="str">
         <v>State Bank of India</v>
@@ -3951,18 +3951,18 @@
         <v>Sheohar</v>
       </c>
       <c r="P48" t="str">
-        <v>SBIN0009678</v>
+        <v>SBIN0008245</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0300090</v>
+        <v>0300088</v>
       </c>
       <c r="B49" t="str">
-        <v>NIRMALA MISHRA</v>
+        <v>RAKESH THAKUR</v>
       </c>
       <c r="C49" t="str">
-        <v>Junior Engineer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D49" t="str">
         <v>03073</v>
@@ -3974,16 +3974,16 @@
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G49" t="str">
-        <v>9003000090</v>
+        <v>9003000088</v>
       </c>
       <c r="H49" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I49" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J49" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K49" t="str">
         <v>0305</v>
@@ -3992,7 +3992,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M49" t="str">
-        <v>30000712710</v>
+        <v>30000696872</v>
       </c>
       <c r="N49" t="str">
         <v>State Bank of India</v>
@@ -4001,33 +4001,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P49" t="str">
-        <v>SBIN0009742</v>
+        <v>SBIN0005560</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0300052</v>
+        <v>0300034</v>
       </c>
       <c r="B50" t="str">
-        <v>MAMTA JHA</v>
+        <v>KIRAN VERMA</v>
       </c>
       <c r="C50" t="str">
-        <v>Clerk</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D50" t="str">
-        <v>03038</v>
+        <v>03032</v>
       </c>
       <c r="E50" t="str">
-        <v>Primary School Sheohar</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F50" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G50" t="str">
-        <v>9003000052</v>
+        <v>9003000034</v>
       </c>
       <c r="H50" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I50" t="str">
         <v>0301</v>
@@ -4042,7 +4042,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M50" t="str">
-        <v>30000411788</v>
+        <v>30000269246</v>
       </c>
       <c r="N50" t="str">
         <v>State Bank of India</v>
@@ -4051,39 +4051,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P50" t="str">
-        <v>SBIN0007064</v>
+        <v>SBIN0003169</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>0300060</v>
+        <v>0300091</v>
       </c>
       <c r="B51" t="str">
-        <v>SUNIL ALAM</v>
+        <v>NIRMALA SAH</v>
       </c>
       <c r="C51" t="str">
-        <v>Teacher</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D51" t="str">
-        <v>03052</v>
+        <v>03075</v>
       </c>
       <c r="E51" t="str">
-        <v>Kanya Middle School Purnahiya No.4</v>
+        <v>RWD Sub-Division Purnahiya</v>
       </c>
       <c r="F51" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G51" t="str">
-        <v>9003000060</v>
+        <v>9003000091</v>
       </c>
       <c r="H51" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I51" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J51" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K51" t="str">
         <v>0303</v>
@@ -4092,7 +4092,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M51" t="str">
-        <v>30000475140</v>
+        <v>30000720629</v>
       </c>
       <c r="N51" t="str">
         <v>State Bank of India</v>
@@ -4101,39 +4101,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P51" t="str">
-        <v>SBIN0001459</v>
+        <v>SBIN0001722</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>0300050</v>
+        <v>0300009</v>
       </c>
       <c r="B52" t="str">
-        <v>MD. IRFAN MISHRA</v>
+        <v>PRIYANKA ALAM</v>
       </c>
       <c r="C52" t="str">
-        <v>Teacher</v>
+        <v>Lecturer</v>
       </c>
       <c r="D52" t="str">
-        <v>03015</v>
+        <v>03009</v>
       </c>
       <c r="E52" t="str">
-        <v>Block Education Office Dumri Katsari No.1</v>
+        <v>High School Dumri Katsari</v>
       </c>
       <c r="F52" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G52" t="str">
-        <v>9003000050</v>
+        <v>9003000009</v>
       </c>
       <c r="H52" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I52" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J52" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K52" t="str">
         <v>0304</v>
@@ -4142,7 +4142,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M52" t="str">
-        <v>30000395950</v>
+        <v>30000071271</v>
       </c>
       <c r="N52" t="str">
         <v>State Bank of India</v>
@@ -4151,48 +4151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P52" t="str">
-        <v>SBIN0001663</v>
+        <v>SBIN0008749</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>0300077</v>
+        <v>0300052</v>
       </c>
       <c r="B53" t="str">
-        <v>UMESH RAM</v>
+        <v>ASHA RAM</v>
       </c>
       <c r="C53" t="str">
-        <v>Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D53" t="str">
-        <v>03066</v>
+        <v>03045</v>
       </c>
       <c r="E53" t="str">
-        <v>CDPO Office Dumri Katsari No.4</v>
+        <v>PHC Tariyani</v>
       </c>
       <c r="F53" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G53" t="str">
-        <v>9003000077</v>
+        <v>9003000052</v>
       </c>
       <c r="H53" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I53" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J53" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K53" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L53" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M53" t="str">
-        <v>30000609763</v>
+        <v>30000411788</v>
       </c>
       <c r="N53" t="str">
         <v>State Bank of India</v>
@@ -4201,48 +4201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P53" t="str">
-        <v>SBIN0006857</v>
+        <v>SBIN0008103</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>0300083</v>
+        <v>0300092</v>
       </c>
       <c r="B54" t="str">
-        <v>RAMESH SAH</v>
+        <v>FARHAT SINHA</v>
       </c>
       <c r="C54" t="str">
-        <v>Clerk</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D54" t="str">
-        <v>03024</v>
+        <v>03076</v>
       </c>
       <c r="E54" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>RWD Sub-Division Piprahi</v>
       </c>
       <c r="F54" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G54" t="str">
-        <v>9003000083</v>
+        <v>9003000092</v>
       </c>
       <c r="H54" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I54" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="J54" t="str">
-        <v>Others</v>
+        <v>Tariyani</v>
       </c>
       <c r="K54" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L54" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M54" t="str">
-        <v>30000657277</v>
+        <v>30000728548</v>
       </c>
       <c r="N54" t="str">
         <v>State Bank of India</v>
@@ -4251,33 +4251,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P54" t="str">
-        <v>SBIN0003128</v>
+        <v>SBIN0002933</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>0300024</v>
+        <v>0300008</v>
       </c>
       <c r="B55" t="str">
-        <v>SUNIL SHARMA</v>
+        <v>PRAMOD OJHA</v>
       </c>
       <c r="C55" t="str">
-        <v>Assistant Teacher</v>
+        <v>Headmaster</v>
       </c>
       <c r="D55" t="str">
-        <v>03021</v>
+        <v>03008</v>
       </c>
       <c r="E55" t="str">
-        <v>Collectorate Sheohar</v>
+        <v>Block Office Purnahiya No.3</v>
       </c>
       <c r="F55" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G55" t="str">
-        <v>9003000024</v>
+        <v>9003000008</v>
       </c>
       <c r="H55" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I55" t="str">
         <v>0303</v>
@@ -4286,13 +4286,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K55" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L55" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M55" t="str">
-        <v>30000190056</v>
+        <v>30000063352</v>
       </c>
       <c r="N55" t="str">
         <v>State Bank of India</v>
@@ -4301,48 +4301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P55" t="str">
-        <v>SBIN0008112</v>
+        <v>SBIN0003711</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>0300078</v>
+        <v>0300059</v>
       </c>
       <c r="B56" t="str">
-        <v>MUKESH DEVI</v>
+        <v>MD. SHAHID RAM</v>
       </c>
       <c r="C56" t="str">
-        <v>Data Entry Operator</v>
+        <v>Clerk</v>
       </c>
       <c r="D56" t="str">
-        <v>03067</v>
+        <v>03051</v>
       </c>
       <c r="E56" t="str">
-        <v>Middle School Dumri Katsari No.4</v>
+        <v>Block Office Sheohar No.1</v>
       </c>
       <c r="F56" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G56" t="str">
-        <v>9003000078</v>
+        <v>9003000059</v>
       </c>
       <c r="H56" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I56" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J56" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K56" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L56" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M56" t="str">
-        <v>30000617682</v>
+        <v>30000467221</v>
       </c>
       <c r="N56" t="str">
         <v>State Bank of India</v>
@@ -4351,39 +4351,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P56" t="str">
-        <v>SBIN0005975</v>
+        <v>SBIN0004755</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>0300116</v>
+        <v>0300022</v>
       </c>
       <c r="B57" t="str">
-        <v>SHAILESH CHAUDHARY</v>
+        <v>NASREEN MISHRA</v>
       </c>
       <c r="C57" t="str">
-        <v>Postmaster</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D57" t="str">
-        <v>03092</v>
+        <v>03021</v>
       </c>
       <c r="E57" t="str">
-        <v>Central Bank of India, Piprahi</v>
+        <v>CDPO Office Piprahi No.1</v>
       </c>
       <c r="F57" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G57" t="str">
-        <v>9003000116</v>
+        <v>9003000022</v>
       </c>
       <c r="H57" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I57" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J57" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K57" t="str">
         <v>0302</v>
@@ -4392,7 +4392,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M57" t="str">
-        <v>30000918604</v>
+        <v>30000174218</v>
       </c>
       <c r="N57" t="str">
         <v>State Bank of India</v>
@@ -4401,48 +4401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P57" t="str">
-        <v>SBIN0001814</v>
+        <v>SBIN0003676</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>0300065</v>
+        <v>0300013</v>
       </c>
       <c r="B58" t="str">
-        <v>RINKU THAKUR</v>
+        <v>RAKESH KHATUN</v>
       </c>
       <c r="C58" t="str">
-        <v>Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D58" t="str">
-        <v>03055</v>
+        <v>03013</v>
       </c>
       <c r="E58" t="str">
-        <v>Circle Office Dumri Katsari No.4</v>
+        <v>Panchayat Bhawan Sheohar No.1</v>
       </c>
       <c r="F58" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G58" t="str">
-        <v>9003000065</v>
+        <v>9003000013</v>
       </c>
       <c r="H58" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I58" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J58" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K58" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L58" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M58" t="str">
-        <v>30000514735</v>
+        <v>30000102947</v>
       </c>
       <c r="N58" t="str">
         <v>State Bank of India</v>
@@ -4451,48 +4451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P58" t="str">
-        <v>SBIN0005890</v>
+        <v>SBIN0003797</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>0300027</v>
+        <v>0300101</v>
       </c>
       <c r="B59" t="str">
-        <v>NIRMALA KHATUN</v>
+        <v>PRAMOD PRASAD</v>
       </c>
       <c r="C59" t="str">
-        <v>Senior Clerk</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D59" t="str">
-        <v>03023</v>
+        <v>03081</v>
       </c>
       <c r="E59" t="str">
-        <v>Project Girls High School Tariyani No.1</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="F59" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G59" t="str">
-        <v>9003000027</v>
+        <v>9003000101</v>
       </c>
       <c r="H59" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I59" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J59" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K59" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L59" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M59" t="str">
-        <v>30000213813</v>
+        <v>30000799819</v>
       </c>
       <c r="N59" t="str">
         <v>State Bank of India</v>
@@ -4501,48 +4501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P59" t="str">
-        <v>SBIN0005014</v>
+        <v>SBIN0009804</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>0300120</v>
+        <v>0300058</v>
       </c>
       <c r="B60" t="str">
-        <v>SURESH SAH V</v>
+        <v>KUMARI ANJALI PANDEY A</v>
       </c>
       <c r="C60" t="str">
-        <v>Postmaster</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D60" t="str">
-        <v>03086</v>
+        <v>03050</v>
       </c>
       <c r="E60" t="str">
-        <v>Punjab National Bank, Purnahiya</v>
+        <v>Block Education Office Dumri Katsari</v>
       </c>
       <c r="F60" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G60" t="str">
-        <v>9003000120</v>
+        <v>9003000058</v>
       </c>
       <c r="H60" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I60" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J60" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K60" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L60" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M60" t="str">
-        <v>30000950280</v>
+        <v>30000459302</v>
       </c>
       <c r="N60" t="str">
         <v>State Bank of India</v>
@@ -4551,33 +4551,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P60" t="str">
-        <v>SBIN0007443</v>
+        <v>SBIN0008091</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>0300070</v>
+        <v>0300023</v>
       </c>
       <c r="B61" t="str">
-        <v>MD. SHAHID SHARMA</v>
+        <v>SANJAY PANDEY</v>
       </c>
       <c r="C61" t="str">
-        <v>Office Assistant</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D61" t="str">
-        <v>03060</v>
+        <v>03022</v>
       </c>
       <c r="E61" t="str">
-        <v>CDPO Office Tariyani No.3</v>
+        <v>Panchayat Bhawan Tariyani</v>
       </c>
       <c r="F61" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G61" t="str">
-        <v>9003000070</v>
+        <v>9003000023</v>
       </c>
       <c r="H61" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I61" t="str">
         <v>0305</v>
@@ -4592,7 +4592,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M61" t="str">
-        <v>30000554330</v>
+        <v>30000182137</v>
       </c>
       <c r="N61" t="str">
         <v>State Bank of India</v>
@@ -4601,39 +4601,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P61" t="str">
-        <v>SBIN0002882</v>
+        <v>SBIN0005747</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>0300118</v>
+        <v>0300049</v>
       </c>
       <c r="B62" t="str">
-        <v>ANIL JHA</v>
+        <v>RAJESH CHAUDHARY</v>
       </c>
       <c r="C62" t="str">
-        <v>Administrative Officer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D62" t="str">
-        <v>03094</v>
+        <v>03042</v>
       </c>
       <c r="E62" t="str">
-        <v>BSNL Exchange, Sheohar</v>
+        <v>District Education Office Sheohar</v>
       </c>
       <c r="F62" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G62" t="str">
-        <v>9003000118</v>
+        <v>9003000049</v>
       </c>
       <c r="H62" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I62" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J62" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K62" t="str">
         <v>0301</v>
@@ -4642,7 +4642,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M62" t="str">
-        <v>30000934442</v>
+        <v>30000388031</v>
       </c>
       <c r="N62" t="str">
         <v>State Bank of India</v>
@@ -4651,39 +4651,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P62" t="str">
-        <v>SBIN0003896</v>
+        <v>SBIN0002886</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>0300058</v>
+        <v>0300037</v>
       </c>
       <c r="B63" t="str">
-        <v>KUMARI ANJALI KUMAR</v>
+        <v>ASHA MAHTO</v>
       </c>
       <c r="C63" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D63" t="str">
-        <v>03033</v>
+        <v>03005</v>
       </c>
       <c r="E63" t="str">
-        <v>Project Girls High School Dumri Katsari</v>
+        <v>Middle School Dumri Katsari No.4</v>
       </c>
       <c r="F63" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G63" t="str">
-        <v>9003000058</v>
+        <v>9003000037</v>
       </c>
       <c r="H63" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I63" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J63" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K63" t="str">
         <v>0304</v>
@@ -4692,7 +4692,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M63" t="str">
-        <v>30000459302</v>
+        <v>30000293003</v>
       </c>
       <c r="N63" t="str">
         <v>State Bank of India</v>
@@ -4701,33 +4701,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P63" t="str">
-        <v>SBIN0007956</v>
+        <v>SBIN0001456</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>0300037</v>
+        <v>0300016</v>
       </c>
       <c r="B64" t="str">
-        <v>USHA PANDEY</v>
+        <v>MAHESH CHAUDHARY</v>
       </c>
       <c r="C64" t="str">
-        <v>Assistant Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D64" t="str">
-        <v>03033</v>
+        <v>03016</v>
       </c>
       <c r="E64" t="str">
-        <v>Project Girls High School Dumri Katsari</v>
+        <v>CDPO Office Tariyani No.1</v>
       </c>
       <c r="F64" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G64" t="str">
-        <v>9003000037</v>
+        <v>9003000016</v>
       </c>
       <c r="H64" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I64" t="str">
         <v>0305</v>
@@ -4736,13 +4736,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K64" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L64" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M64" t="str">
-        <v>30000293003</v>
+        <v>30000126704</v>
       </c>
       <c r="N64" t="str">
         <v>State Bank of India</v>
@@ -4751,48 +4751,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P64" t="str">
-        <v>SBIN0004692</v>
+        <v>SBIN0007559</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>0300055</v>
+        <v>0300065</v>
       </c>
       <c r="B65" t="str">
-        <v>FARHAT PANDEY</v>
+        <v>ALOK GUPTA</v>
       </c>
       <c r="C65" t="str">
         <v>Clerk</v>
       </c>
       <c r="D65" t="str">
-        <v>03048</v>
+        <v>03057</v>
       </c>
       <c r="E65" t="str">
-        <v>Project Girls High School Piprahi No.4</v>
+        <v>Project Girls High School Dumri Katsari</v>
       </c>
       <c r="F65" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G65" t="str">
-        <v>9003000055</v>
+        <v>9003000065</v>
       </c>
       <c r="H65" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I65" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J65" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K65" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L65" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M65" t="str">
-        <v>30000435545</v>
+        <v>30000514735</v>
       </c>
       <c r="N65" t="str">
         <v>State Bank of India</v>
@@ -4801,48 +4801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P65" t="str">
-        <v>SBIN0007309</v>
+        <v>SBIN0004918</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>0300008</v>
+        <v>0300093</v>
       </c>
       <c r="B66" t="str">
-        <v>KIRAN DEVI</v>
+        <v>MD. SHAHID PASWAN</v>
       </c>
       <c r="C66" t="str">
-        <v>Section Officer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D66" t="str">
-        <v>03008</v>
+        <v>03066</v>
       </c>
       <c r="E66" t="str">
-        <v>Block Office Tariyani No.2</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F66" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G66" t="str">
-        <v>9003000008</v>
+        <v>9003000093</v>
       </c>
       <c r="H66" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I66" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J66" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K66" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L66" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M66" t="str">
-        <v>30000063352</v>
+        <v>30000736467</v>
       </c>
       <c r="N66" t="str">
         <v>State Bank of India</v>
@@ -4851,33 +4851,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P66" t="str">
-        <v>SBIN0007461</v>
+        <v>SBIN0003954</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>0300086</v>
+        <v>0300031</v>
       </c>
       <c r="B67" t="str">
-        <v>VINOD ALAM C</v>
+        <v>RAKESH JHA</v>
       </c>
       <c r="C67" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D67" t="str">
-        <v>03070</v>
+        <v>03012</v>
       </c>
       <c r="E67" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F67" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G67" t="str">
-        <v>9003000086</v>
+        <v>9003000031</v>
       </c>
       <c r="H67" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I67" t="str">
         <v>0303</v>
@@ -4892,7 +4892,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M67" t="str">
-        <v>30000681034</v>
+        <v>30000245489</v>
       </c>
       <c r="N67" t="str">
         <v>State Bank of India</v>
@@ -4901,30 +4901,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P67" t="str">
-        <v>SBIN0004377</v>
+        <v>SBIN0009843</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>0300019</v>
+        <v>0300011</v>
       </c>
       <c r="B68" t="str">
-        <v>ARVIND DEVI</v>
+        <v>SANTOSH CHAUDHARY</v>
       </c>
       <c r="C68" t="str">
-        <v>Assistant Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D68" t="str">
-        <v>03019</v>
+        <v>03011</v>
       </c>
       <c r="E68" t="str">
-        <v>High School Piprahi No.2</v>
+        <v>CDPO Office Purnahiya</v>
       </c>
       <c r="F68" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G68" t="str">
-        <v>9003000019</v>
+        <v>9003000011</v>
       </c>
       <c r="H68" t="str">
         <v>PRESIDING OFFICER</v>
@@ -4936,13 +4936,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K68" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L68" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M68" t="str">
-        <v>30000150461</v>
+        <v>30000087109</v>
       </c>
       <c r="N68" t="str">
         <v>State Bank of India</v>
@@ -4951,39 +4951,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P68" t="str">
-        <v>SBIN0008535</v>
+        <v>SBIN0007665</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>0300104</v>
+        <v>0300111</v>
       </c>
       <c r="B69" t="str">
-        <v>USHA ALAM</v>
+        <v>NEHA MISHRA</v>
       </c>
       <c r="C69" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D69" t="str">
-        <v>03082</v>
+        <v>03088</v>
       </c>
       <c r="E69" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>Head Post Office, Purnahiya</v>
       </c>
       <c r="F69" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G69" t="str">
-        <v>9003000104</v>
+        <v>9003000111</v>
       </c>
       <c r="H69" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I69" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J69" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K69" t="str">
         <v>0303</v>
@@ -4992,7 +4992,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M69" t="str">
-        <v>30000823576</v>
+        <v>30000879009</v>
       </c>
       <c r="N69" t="str">
         <v>State Bank of India</v>
@@ -5001,39 +5001,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P69" t="str">
-        <v>SBIN0005259</v>
+        <v>SBIN0008716</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>0300106</v>
+        <v>0300122</v>
       </c>
       <c r="B70" t="str">
-        <v>DINESH KHATUN</v>
+        <v>ANIL YADAV</v>
       </c>
       <c r="C70" t="str">
         <v>Branch Manager</v>
       </c>
       <c r="D70" t="str">
-        <v>03083</v>
+        <v>03093</v>
       </c>
       <c r="E70" t="str">
-        <v>LIC Branch Office, Tariyani</v>
+        <v>Head Post Office, Tariyani</v>
       </c>
       <c r="F70" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G70" t="str">
-        <v>9003000106</v>
+        <v>9003000122</v>
       </c>
       <c r="H70" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I70" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J70" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K70" t="str">
         <v>0305</v>
@@ -5042,7 +5042,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M70" t="str">
-        <v>30000839414</v>
+        <v>30000966118</v>
       </c>
       <c r="N70" t="str">
         <v>State Bank of India</v>
@@ -5051,48 +5051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P70" t="str">
-        <v>SBIN0005986</v>
+        <v>SBIN0004445</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>0300059</v>
+        <v>0300072</v>
       </c>
       <c r="B71" t="str">
-        <v>NASREEN PASWAN</v>
+        <v>RANJIT MISHRA</v>
       </c>
       <c r="C71" t="str">
-        <v>Accountant</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D71" t="str">
-        <v>03051</v>
+        <v>03062</v>
       </c>
       <c r="E71" t="str">
-        <v>Middle School Dumri Katsari</v>
+        <v>Project Girls High School Purnahiya</v>
       </c>
       <c r="F71" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G71" t="str">
-        <v>9003000059</v>
+        <v>9003000072</v>
       </c>
       <c r="H71" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I71" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J71" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K71" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L71" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M71" t="str">
-        <v>30000467221</v>
+        <v>30000570168</v>
       </c>
       <c r="N71" t="str">
         <v>State Bank of India</v>
@@ -5101,48 +5101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P71" t="str">
-        <v>SBIN0003781</v>
+        <v>SBIN0002020</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>0300089</v>
+        <v>0300124</v>
       </c>
       <c r="B72" t="str">
-        <v>PANKAJ VERMA</v>
+        <v>DINESH RAI</v>
       </c>
       <c r="C72" t="str">
-        <v>Revenue Officer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D72" t="str">
-        <v>03072</v>
+        <v>03093</v>
       </c>
       <c r="E72" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Head Post Office, Tariyani</v>
       </c>
       <c r="F72" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G72" t="str">
-        <v>9003000089</v>
+        <v>9003000124</v>
       </c>
       <c r="H72" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I72" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J72" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K72" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L72" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M72" t="str">
-        <v>30000704791</v>
+        <v>30000981956</v>
       </c>
       <c r="N72" t="str">
         <v>State Bank of India</v>
@@ -5151,48 +5151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P72" t="str">
-        <v>SBIN0009828</v>
+        <v>SBIN0002904</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>0300048</v>
+        <v>0300083</v>
       </c>
       <c r="B73" t="str">
-        <v>VINOD ALAM</v>
+        <v>SANTOSH KUMAR</v>
       </c>
       <c r="C73" t="str">
         <v>Teacher</v>
       </c>
       <c r="D73" t="str">
-        <v>03044</v>
+        <v>03055</v>
       </c>
       <c r="E73" t="str">
-        <v>Block Office Sheohar No.4</v>
+        <v>Collectorate (deputed from other district)</v>
       </c>
       <c r="F73" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G73" t="str">
-        <v>9003000048</v>
+        <v>9003000083</v>
       </c>
       <c r="H73" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I73" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J73" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K73" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="L73" t="str">
-        <v>Sheohar</v>
+        <v>Other District</v>
       </c>
       <c r="M73" t="str">
-        <v>30000380112</v>
+        <v>30000657277</v>
       </c>
       <c r="N73" t="str">
         <v>State Bank of India</v>
@@ -5201,48 +5201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P73" t="str">
-        <v>SBIN0001235</v>
+        <v>SBIN0008489</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>0300117</v>
+        <v>0300056</v>
       </c>
       <c r="B74" t="str">
-        <v>DINESH ALAM</v>
+        <v>NIRMALA KUMAR</v>
       </c>
       <c r="C74" t="str">
-        <v>Branch Manager</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D74" t="str">
-        <v>03093</v>
+        <v>03048</v>
       </c>
       <c r="E74" t="str">
-        <v>UCO Bank, Tariyani</v>
+        <v>CDPO Office Dumri Katsari No.4</v>
       </c>
       <c r="F74" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G74" t="str">
-        <v>9003000117</v>
+        <v>9003000056</v>
       </c>
       <c r="H74" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I74" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J74" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K74" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L74" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M74" t="str">
-        <v>30000926523</v>
+        <v>30000443464</v>
       </c>
       <c r="N74" t="str">
         <v>State Bank of India</v>
@@ -5251,39 +5251,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P74" t="str">
-        <v>SBIN0004177</v>
+        <v>SBIN0007488</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>0300122</v>
+        <v>0300108</v>
       </c>
       <c r="B75" t="str">
-        <v>ABDUL KALAM GUPTA</v>
+        <v>SAVITA GUPTA</v>
       </c>
       <c r="C75" t="str">
-        <v>Postmaster</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D75" t="str">
-        <v>03096</v>
+        <v>03084</v>
       </c>
       <c r="E75" t="str">
-        <v>UCO Bank, Dumri Katsari</v>
+        <v>LIC Branch Office, Dumri Katsari</v>
       </c>
       <c r="F75" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G75" t="str">
-        <v>9003000122</v>
+        <v>9003000108</v>
       </c>
       <c r="H75" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I75" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J75" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K75" t="str">
         <v>0304</v>
@@ -5292,7 +5292,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M75" t="str">
-        <v>30000966118</v>
+        <v>30000855252</v>
       </c>
       <c r="N75" t="str">
         <v>State Bank of India</v>
@@ -5301,48 +5301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P75" t="str">
-        <v>SBIN0005596</v>
+        <v>SBIN0008507</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>0300103</v>
+        <v>0300087</v>
       </c>
       <c r="B76" t="str">
-        <v>AJAY RAI</v>
+        <v>NEHA TIWARI</v>
       </c>
       <c r="C76" t="str">
-        <v>Revenue Officer</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D76" t="str">
-        <v>03081</v>
+        <v>03072</v>
       </c>
       <c r="E76" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>RWD Sub-Division Sheohar</v>
       </c>
       <c r="F76" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G76" t="str">
-        <v>9003000103</v>
+        <v>9003000087</v>
       </c>
       <c r="H76" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I76" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J76" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K76" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L76" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M76" t="str">
-        <v>30000815657</v>
+        <v>30000688953</v>
       </c>
       <c r="N76" t="str">
         <v>State Bank of India</v>
@@ -5351,48 +5351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P76" t="str">
-        <v>SBIN0006586</v>
+        <v>SBIN0001423</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>0300081</v>
+        <v>0300012</v>
       </c>
       <c r="B77" t="str">
-        <v>SANTOSH SHARMA</v>
+        <v>NIRMALA SINHA</v>
       </c>
       <c r="C77" t="str">
-        <v>Office Assistant</v>
+        <v>Section Officer</v>
       </c>
       <c r="D77" t="str">
-        <v>03068</v>
+        <v>03012</v>
       </c>
       <c r="E77" t="str">
-        <v>CDPO Office Dumri Katsari No.2</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F77" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G77" t="str">
-        <v>9003000081</v>
+        <v>9003000012</v>
       </c>
       <c r="H77" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I77" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J77" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K77" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L77" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M77" t="str">
-        <v>30000641439</v>
+        <v>30000095028</v>
       </c>
       <c r="N77" t="str">
         <v>State Bank of India</v>
@@ -5401,33 +5401,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P77" t="str">
-        <v>SBIN0006850</v>
+        <v>SBIN0003812</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>0300088</v>
+        <v>0300125</v>
       </c>
       <c r="B78" t="str">
-        <v>SHAILESH ALAM</v>
+        <v>ANITA SHARMA</v>
       </c>
       <c r="C78" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D78" t="str">
-        <v>03071</v>
+        <v>03097</v>
       </c>
       <c r="E78" t="str">
-        <v>RWD Sub-Division Sheohar</v>
+        <v>UCO Bank, Sheohar</v>
       </c>
       <c r="F78" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G78" t="str">
-        <v>9003000088</v>
+        <v>9003000125</v>
       </c>
       <c r="H78" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I78" t="str">
         <v>999999</v>
@@ -5442,7 +5442,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M78" t="str">
-        <v>30000696872</v>
+        <v>30000989875</v>
       </c>
       <c r="N78" t="str">
         <v>State Bank of India</v>
@@ -5451,15 +5451,15 @@
         <v>Sheohar</v>
       </c>
       <c r="P78" t="str">
-        <v>SBIN0001296</v>
+        <v>SBIN0006105</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0300028</v>
+        <v>0300025</v>
       </c>
       <c r="B79" t="str">
-        <v>VINOD ANSARI</v>
+        <v>NASREEN ALAM</v>
       </c>
       <c r="C79" t="str">
         <v>Senior Clerk</v>
@@ -5468,22 +5468,22 @@
         <v>03024</v>
       </c>
       <c r="E79" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Civil Surgeon Office Sheohar</v>
       </c>
       <c r="F79" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G79" t="str">
-        <v>9003000028</v>
+        <v>9003000025</v>
       </c>
       <c r="H79" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I79" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J79" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K79" t="str">
         <v>0301</v>
@@ -5492,7 +5492,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M79" t="str">
-        <v>30000221732</v>
+        <v>30000197975</v>
       </c>
       <c r="N79" t="str">
         <v>State Bank of India</v>
@@ -5501,48 +5501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P79" t="str">
-        <v>SBIN0003267</v>
+        <v>SBIN0004404</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>0300056</v>
+        <v>0300003</v>
       </c>
       <c r="B80" t="str">
-        <v>RAKESH SHARMA</v>
+        <v>ANITA JHA</v>
       </c>
       <c r="C80" t="str">
-        <v>Teacher</v>
+        <v>Lecturer</v>
       </c>
       <c r="D80" t="str">
-        <v>03049</v>
+        <v>03003</v>
       </c>
       <c r="E80" t="str">
-        <v>Block Office Purnahiya No.4</v>
+        <v>Panchayat Bhawan Piprahi No.4</v>
       </c>
       <c r="F80" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G80" t="str">
-        <v>9003000056</v>
+        <v>9003000003</v>
       </c>
       <c r="H80" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I80" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="J80" t="str">
-        <v>Others</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K80" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L80" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M80" t="str">
-        <v>30000443464</v>
+        <v>30000023757</v>
       </c>
       <c r="N80" t="str">
         <v>State Bank of India</v>
@@ -5551,48 +5551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P80" t="str">
-        <v>SBIN0004276</v>
+        <v>SBIN0002193</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>0300126</v>
+        <v>0300039</v>
       </c>
       <c r="B81" t="str">
-        <v>FARHAT MAHTO</v>
+        <v>RAKESH SINGH</v>
       </c>
       <c r="C81" t="str">
-        <v>Administrative Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D81" t="str">
-        <v>03099</v>
+        <v>03017</v>
       </c>
       <c r="E81" t="str">
-        <v>BSNL Exchange, Purnahiya</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="F81" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G81" t="str">
-        <v>9003000126</v>
+        <v>9003000039</v>
       </c>
       <c r="H81" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I81" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J81" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K81" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L81" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M81" t="str">
-        <v>30000997794</v>
+        <v>30000308841</v>
       </c>
       <c r="N81" t="str">
         <v>State Bank of India</v>
@@ -5601,48 +5601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P81" t="str">
-        <v>SBIN0007293</v>
+        <v>SBIN0009029</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>0300099</v>
+        <v>0300026</v>
       </c>
       <c r="B82" t="str">
-        <v>ASHA ALAM T</v>
+        <v>NEHA PANDEY</v>
       </c>
       <c r="C82" t="str">
-        <v>Assistant Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D82" t="str">
-        <v>03078</v>
+        <v>03025</v>
       </c>
       <c r="E82" t="str">
-        <v>Minor Irrigation Office Dumri Katsari</v>
+        <v>PHC Tariyani No.2</v>
       </c>
       <c r="F82" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G82" t="str">
-        <v>9003000099</v>
+        <v>9003000026</v>
       </c>
       <c r="H82" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I82" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J82" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K82" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L82" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M82" t="str">
-        <v>30000783981</v>
+        <v>30000205894</v>
       </c>
       <c r="N82" t="str">
         <v>State Bank of India</v>
@@ -5651,48 +5651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P82" t="str">
-        <v>SBIN0009105</v>
+        <v>SBIN0007961</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>0300125</v>
+        <v>0300090</v>
       </c>
       <c r="B83" t="str">
-        <v>SUNIL KHATUN</v>
+        <v>PRAMOD SINHA</v>
       </c>
       <c r="C83" t="str">
-        <v>Administrative Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D83" t="str">
-        <v>03096</v>
+        <v>03071</v>
       </c>
       <c r="E83" t="str">
-        <v>UCO Bank, Dumri Katsari</v>
+        <v>Circle Office Sheohar</v>
       </c>
       <c r="F83" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G83" t="str">
-        <v>9003000125</v>
+        <v>9003000090</v>
       </c>
       <c r="H83" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I83" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J83" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K83" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L83" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M83" t="str">
-        <v>30000989875</v>
+        <v>30000712710</v>
       </c>
       <c r="N83" t="str">
         <v>State Bank of India</v>
@@ -5701,39 +5701,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P83" t="str">
-        <v>SBIN0002152</v>
+        <v>SBIN0009975</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>0300114</v>
+        <v>0300019</v>
       </c>
       <c r="B84" t="str">
-        <v>NEHA VERMA</v>
+        <v>VIJAY OJHA</v>
       </c>
       <c r="C84" t="str">
-        <v>Administrative Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D84" t="str">
-        <v>03090</v>
+        <v>03019</v>
       </c>
       <c r="E84" t="str">
-        <v>State Bank of India, Piprahi</v>
+        <v>Block Education Office Piprahi No.3</v>
       </c>
       <c r="F84" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G84" t="str">
-        <v>9003000114</v>
+        <v>9003000019</v>
       </c>
       <c r="H84" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I84" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J84" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K84" t="str">
         <v>0302</v>
@@ -5742,7 +5742,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M84" t="str">
-        <v>30000902766</v>
+        <v>30000150461</v>
       </c>
       <c r="N84" t="str">
         <v>State Bank of India</v>
@@ -5751,39 +5751,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P84" t="str">
-        <v>SBIN0007919</v>
+        <v>SBIN0005080</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>0300002</v>
+        <v>0300112</v>
       </c>
       <c r="B85" t="str">
-        <v>ARVIND SINGH</v>
+        <v>RAJESH RAM</v>
       </c>
       <c r="C85" t="str">
-        <v>Headmaster</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D85" t="str">
-        <v>03002</v>
+        <v>03089</v>
       </c>
       <c r="E85" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>UCO Bank, Tariyani</v>
       </c>
       <c r="F85" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G85" t="str">
-        <v>9003000002</v>
+        <v>9003000112</v>
       </c>
       <c r="H85" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I85" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J85" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K85" t="str">
         <v>0305</v>
@@ -5792,7 +5792,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M85" t="str">
-        <v>30000015838</v>
+        <v>30000886928</v>
       </c>
       <c r="N85" t="str">
         <v>State Bank of India</v>
@@ -5801,33 +5801,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P85" t="str">
-        <v>SBIN0005659</v>
+        <v>SBIN0006645</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>0300124</v>
+        <v>0300027</v>
       </c>
       <c r="B86" t="str">
-        <v>SANJAY THAKUR</v>
+        <v>ANIL PRASAD</v>
       </c>
       <c r="C86" t="str">
-        <v>Assistant Manager</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D86" t="str">
-        <v>03098</v>
+        <v>03026</v>
       </c>
       <c r="E86" t="str">
-        <v>Head Post Office, Tariyani</v>
+        <v>Primary School Piprahi</v>
       </c>
       <c r="F86" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G86" t="str">
-        <v>9003000124</v>
+        <v>9003000027</v>
       </c>
       <c r="H86" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I86" t="str">
         <v>0304</v>
@@ -5836,13 +5836,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K86" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L86" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M86" t="str">
-        <v>30000981956</v>
+        <v>30000213813</v>
       </c>
       <c r="N86" t="str">
         <v>State Bank of India</v>
@@ -5851,48 +5851,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P86" t="str">
-        <v>SBIN0003498</v>
+        <v>SBIN0008679</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>0300110</v>
+        <v>0300070</v>
       </c>
       <c r="B87" t="str">
-        <v>USHA GUPTA</v>
+        <v>RAKESH OJHA</v>
       </c>
       <c r="C87" t="str">
-        <v>Assistant Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D87" t="str">
-        <v>03087</v>
+        <v>03061</v>
       </c>
       <c r="E87" t="str">
-        <v>Central Bank of India, Dumri Katsari</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F87" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G87" t="str">
-        <v>9003000110</v>
+        <v>9003000070</v>
       </c>
       <c r="H87" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I87" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J87" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K87" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L87" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M87" t="str">
-        <v>30000871090</v>
+        <v>30000554330</v>
       </c>
       <c r="N87" t="str">
         <v>State Bank of India</v>
@@ -5901,48 +5901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P87" t="str">
-        <v>SBIN0008781</v>
+        <v>SBIN0004789</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>0300026</v>
+        <v>0300075</v>
       </c>
       <c r="B88" t="str">
-        <v>KIRAN DEVI P</v>
+        <v>RANJIT ALAM</v>
       </c>
       <c r="C88" t="str">
-        <v>Assistant Teacher</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D88" t="str">
-        <v>03015</v>
+        <v>03063</v>
       </c>
       <c r="E88" t="str">
-        <v>Block Education Office Dumri Katsari No.1</v>
+        <v>Block Office Sheohar No.2</v>
       </c>
       <c r="F88" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G88" t="str">
-        <v>9003000026</v>
+        <v>9003000075</v>
       </c>
       <c r="H88" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I88" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J88" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K88" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L88" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M88" t="str">
-        <v>30000205894</v>
+        <v>30000593925</v>
       </c>
       <c r="N88" t="str">
         <v>State Bank of India</v>
@@ -5951,48 +5951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P88" t="str">
-        <v>SBIN0002883</v>
+        <v>SBIN0006389</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>0300069</v>
+        <v>0300071</v>
       </c>
       <c r="B89" t="str">
-        <v>VIJAY CHAUDHARY Q</v>
+        <v>MANOJ CHAUDHARY</v>
       </c>
       <c r="C89" t="str">
-        <v>Clerk</v>
+        <v>Teacher</v>
       </c>
       <c r="D89" t="str">
-        <v>03059</v>
+        <v>03055</v>
       </c>
       <c r="E89" t="str">
-        <v>Primary School Purnahiya No.3</v>
+        <v>Collectorate (deputed from other district)</v>
       </c>
       <c r="F89" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G89" t="str">
-        <v>9003000069</v>
+        <v>9003000071</v>
       </c>
       <c r="H89" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I89" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J89" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K89" t="str">
         <v>999999</v>
       </c>
-      <c r="J89" t="str">
-        <v>Others</v>
-      </c>
-      <c r="K89" t="str">
-        <v>0303</v>
-      </c>
       <c r="L89" t="str">
-        <v>Purnahiya</v>
+        <v>Other District</v>
       </c>
       <c r="M89" t="str">
-        <v>30000546411</v>
+        <v>30000562249</v>
       </c>
       <c r="N89" t="str">
         <v>State Bank of India</v>
@@ -6001,48 +6001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P89" t="str">
-        <v>SBIN0002001</v>
+        <v>SBIN0003465</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>0300109</v>
+        <v>0300081</v>
       </c>
       <c r="B90" t="str">
-        <v>PANKAJ KHATUN P</v>
+        <v>RAVI CHAUDHARY</v>
       </c>
       <c r="C90" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D90" t="str">
-        <v>03086</v>
+        <v>03048</v>
       </c>
       <c r="E90" t="str">
-        <v>Punjab National Bank, Purnahiya</v>
+        <v>CDPO Office Dumri Katsari No.4</v>
       </c>
       <c r="F90" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G90" t="str">
-        <v>9003000109</v>
+        <v>9003000081</v>
       </c>
       <c r="H90" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I90" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J90" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K90" t="str">
         <v>0304</v>
       </c>
-      <c r="J90" t="str">
+      <c r="L90" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="K90" t="str">
-        <v>0303</v>
-      </c>
-      <c r="L90" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="M90" t="str">
-        <v>30000863171</v>
+        <v>30000641439</v>
       </c>
       <c r="N90" t="str">
         <v>State Bank of India</v>
@@ -6051,48 +6051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P90" t="str">
-        <v>SBIN0002528</v>
+        <v>SBIN0004454</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>0300092</v>
+        <v>0300041</v>
       </c>
       <c r="B91" t="str">
-        <v>SUNITA KHATUN</v>
+        <v>PRAMOD OJHA P</v>
       </c>
       <c r="C91" t="str">
-        <v>Junior Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D91" t="str">
-        <v>03075</v>
+        <v>03035</v>
       </c>
       <c r="E91" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>Project Girls High School Piprahi</v>
       </c>
       <c r="F91" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G91" t="str">
-        <v>9003000092</v>
+        <v>9003000041</v>
       </c>
       <c r="H91" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I91" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J91" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K91" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L91" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M91" t="str">
-        <v>30000728548</v>
+        <v>30000324679</v>
       </c>
       <c r="N91" t="str">
         <v>State Bank of India</v>
@@ -6101,39 +6101,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P91" t="str">
-        <v>SBIN0003145</v>
+        <v>SBIN0005207</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>0300071</v>
+        <v>0300033</v>
       </c>
       <c r="B92" t="str">
-        <v>NITISH CHAUDHARY</v>
+        <v>RANJIT ANSARI</v>
       </c>
       <c r="C92" t="str">
-        <v>Clerk</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D92" t="str">
-        <v>03061</v>
+        <v>03031</v>
       </c>
       <c r="E92" t="str">
-        <v>Kanya Middle School Tariyani No.1</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="F92" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G92" t="str">
-        <v>9003000071</v>
+        <v>9003000033</v>
       </c>
       <c r="H92" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I92" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J92" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K92" t="str">
         <v>0305</v>
@@ -6142,7 +6142,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M92" t="str">
-        <v>30000562249</v>
+        <v>30000261327</v>
       </c>
       <c r="N92" t="str">
         <v>State Bank of India</v>
@@ -6151,39 +6151,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P92" t="str">
-        <v>SBIN0008181</v>
+        <v>SBIN0001926</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>0300051</v>
+        <v>0300097</v>
       </c>
       <c r="B93" t="str">
-        <v>NIRMALA SHARMA</v>
+        <v>MUKESH SHARMA</v>
       </c>
       <c r="C93" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D93" t="str">
-        <v>03005</v>
+        <v>03072</v>
       </c>
       <c r="E93" t="str">
-        <v>Primary School Sheohar No.4</v>
+        <v>RWD Sub-Division Sheohar</v>
       </c>
       <c r="F93" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G93" t="str">
-        <v>9003000051</v>
+        <v>9003000097</v>
       </c>
       <c r="H93" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I93" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J93" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K93" t="str">
         <v>0301</v>
@@ -6192,7 +6192,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M93" t="str">
-        <v>30000403869</v>
+        <v>30000768143</v>
       </c>
       <c r="N93" t="str">
         <v>State Bank of India</v>
@@ -6201,48 +6201,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P93" t="str">
-        <v>SBIN0001738</v>
+        <v>SBIN0005595</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>0300057</v>
+        <v>0300046</v>
       </c>
       <c r="B94" t="str">
-        <v>PRAMOD PASWAN</v>
+        <v>PRAMOD RAM</v>
       </c>
       <c r="C94" t="str">
-        <v>Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D94" t="str">
-        <v>03050</v>
+        <v>03039</v>
       </c>
       <c r="E94" t="str">
-        <v>Project Girls High School Tariyani</v>
+        <v>PHC Piprahi No.3</v>
       </c>
       <c r="F94" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G94" t="str">
-        <v>9003000057</v>
+        <v>9003000046</v>
       </c>
       <c r="H94" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I94" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J94" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K94" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L94" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M94" t="str">
-        <v>30000451383</v>
+        <v>30000364274</v>
       </c>
       <c r="N94" t="str">
         <v>State Bank of India</v>
@@ -6251,7 +6251,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P94" t="str">
-        <v>SBIN0004746</v>
+        <v>SBIN0004767</v>
       </c>
     </row>
     <row r="95">
@@ -6259,19 +6259,19 @@
         <v>0300102</v>
       </c>
       <c r="B95" t="str">
-        <v>SHAILESH KUMAR</v>
+        <v>POONAM SAH</v>
       </c>
       <c r="C95" t="str">
-        <v>Revenue Officer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D95" t="str">
-        <v>03080</v>
+        <v>03082</v>
       </c>
       <c r="E95" t="str">
-        <v>Minor Irrigation Office Sheohar</v>
+        <v>Minor Irrigation Office Dumri Katsari</v>
       </c>
       <c r="F95" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G95" t="str">
         <v>9003000102</v>
@@ -6280,16 +6280,16 @@
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I95" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J95" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K95" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L95" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M95" t="str">
         <v>30000807738</v>
@@ -6301,48 +6301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P95" t="str">
-        <v>SBIN0008078</v>
+        <v>SBIN0004369</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>0300018</v>
+        <v>0300107</v>
       </c>
       <c r="B96" t="str">
-        <v>SANJAY SINHA</v>
+        <v>KUMARI ANJALI OJHA</v>
       </c>
       <c r="C96" t="str">
-        <v>Section Officer</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D96" t="str">
-        <v>03018</v>
+        <v>03085</v>
       </c>
       <c r="E96" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>State Bank of India, Purnahiya</v>
       </c>
       <c r="F96" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G96" t="str">
-        <v>9003000018</v>
+        <v>9003000107</v>
       </c>
       <c r="H96" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I96" t="str">
-        <v>999999</v>
+        <v>0303</v>
       </c>
       <c r="J96" t="str">
-        <v>Others</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K96" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L96" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M96" t="str">
-        <v>30000142542</v>
+        <v>30000847333</v>
       </c>
       <c r="N96" t="str">
         <v>State Bank of India</v>
@@ -6351,48 +6351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P96" t="str">
-        <v>SBIN0009036</v>
+        <v>SBIN0006995</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0300022</v>
+        <v>0300120</v>
       </c>
       <c r="B97" t="str">
-        <v>SURESH KHATUN</v>
+        <v>DINESH ANSARI</v>
       </c>
       <c r="C97" t="str">
-        <v>Head Clerk</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D97" t="str">
-        <v>03020</v>
+        <v>03096</v>
       </c>
       <c r="E97" t="str">
-        <v>Kanya Middle School Sheohar No.4</v>
+        <v>UCO Bank, Purnahiya</v>
       </c>
       <c r="F97" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G97" t="str">
-        <v>9003000022</v>
+        <v>9003000120</v>
       </c>
       <c r="H97" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I97" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J97" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K97" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L97" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M97" t="str">
-        <v>30000174218</v>
+        <v>30000950280</v>
       </c>
       <c r="N97" t="str">
         <v>State Bank of India</v>
@@ -6401,48 +6401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P97" t="str">
-        <v>SBIN0004140</v>
+        <v>SBIN0003644</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>0300074</v>
+        <v>0300038</v>
       </c>
       <c r="B98" t="str">
-        <v>MAMTA OJHA</v>
+        <v>UMESH SINHA Y</v>
       </c>
       <c r="C98" t="str">
-        <v>Clerk</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D98" t="str">
-        <v>03064</v>
+        <v>03020</v>
       </c>
       <c r="E98" t="str">
-        <v>Block Agriculture Office Purnahiya No.4</v>
+        <v>Panchayat Bhawan Dumri Katsari</v>
       </c>
       <c r="F98" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G98" t="str">
-        <v>9003000074</v>
+        <v>9003000038</v>
       </c>
       <c r="H98" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I98" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J98" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K98" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L98" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M98" t="str">
-        <v>30000586006</v>
+        <v>30000300922</v>
       </c>
       <c r="N98" t="str">
         <v>State Bank of India</v>
@@ -6451,39 +6451,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P98" t="str">
-        <v>SBIN0004121</v>
+        <v>SBIN0005275</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>0300011</v>
+        <v>0300060</v>
       </c>
       <c r="B99" t="str">
-        <v>MAHESH OJHA</v>
+        <v>AMIT KHATUN</v>
       </c>
       <c r="C99" t="str">
-        <v>Section Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D99" t="str">
-        <v>03011</v>
+        <v>03052</v>
       </c>
       <c r="E99" t="str">
-        <v>High School Dumri Katsari No.2</v>
+        <v>Block Office Dumri Katsari</v>
       </c>
       <c r="F99" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G99" t="str">
-        <v>9003000011</v>
+        <v>9003000060</v>
       </c>
       <c r="H99" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I99" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J99" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K99" t="str">
         <v>0304</v>
@@ -6492,7 +6492,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M99" t="str">
-        <v>30000087109</v>
+        <v>30000475140</v>
       </c>
       <c r="N99" t="str">
         <v>State Bank of India</v>
@@ -6501,48 +6501,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P99" t="str">
-        <v>SBIN0002313</v>
+        <v>SBIN0003562</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>0300010</v>
+        <v>0300055</v>
       </c>
       <c r="B100" t="str">
-        <v>ABDUL KALAM SINHA</v>
+        <v>ALOK PASWAN</v>
       </c>
       <c r="C100" t="str">
-        <v>Assistant Engineer</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D100" t="str">
-        <v>03010</v>
+        <v>03047</v>
       </c>
       <c r="E100" t="str">
-        <v>Middle School Purnahiya No.2</v>
+        <v>Kanya Middle School Piprahi No.1</v>
       </c>
       <c r="F100" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G100" t="str">
-        <v>9003000010</v>
+        <v>9003000055</v>
       </c>
       <c r="H100" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I100" t="str">
-        <v>999999</v>
+        <v>0302</v>
       </c>
       <c r="J100" t="str">
-        <v>Others</v>
+        <v>Piprahi</v>
       </c>
       <c r="K100" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L100" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M100" t="str">
-        <v>30000079190</v>
+        <v>30000435545</v>
       </c>
       <c r="N100" t="str">
         <v>State Bank of India</v>
@@ -6551,48 +6551,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P100" t="str">
-        <v>SBIN0001036</v>
+        <v>SBIN0004884</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>0300025</v>
+        <v>0300110</v>
       </c>
       <c r="B101" t="str">
-        <v>AMIT TIWARI</v>
+        <v>DINESH ALAM</v>
       </c>
       <c r="C101" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D101" t="str">
-        <v>03022</v>
+        <v>03087</v>
       </c>
       <c r="E101" t="str">
-        <v>High School Purnahiya No.3</v>
+        <v>LIC Branch Office, Sheohar</v>
       </c>
       <c r="F101" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G101" t="str">
-        <v>9003000025</v>
+        <v>9003000110</v>
       </c>
       <c r="H101" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I101" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J101" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K101" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L101" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M101" t="str">
-        <v>30000197975</v>
+        <v>30000871090</v>
       </c>
       <c r="N101" t="str">
         <v>State Bank of India</v>
@@ -6601,48 +6601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P101" t="str">
-        <v>SBIN0002393</v>
+        <v>SBIN0003383</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>0300087</v>
+        <v>0300015</v>
       </c>
       <c r="B102" t="str">
-        <v>SUNIL MISHRA</v>
+        <v>UMESH SINHA</v>
       </c>
       <c r="C102" t="str">
-        <v>Assistant Engineer</v>
+        <v>Headmaster</v>
       </c>
       <c r="D102" t="str">
-        <v>03006</v>
+        <v>03015</v>
       </c>
       <c r="E102" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>Kanya Middle School Dumri Katsari</v>
       </c>
       <c r="F102" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G102" t="str">
-        <v>9003000087</v>
+        <v>9003000015</v>
       </c>
       <c r="H102" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I102" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J102" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K102" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L102" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M102" t="str">
-        <v>30000688953</v>
+        <v>30000118785</v>
       </c>
       <c r="N102" t="str">
         <v>State Bank of India</v>
@@ -6651,48 +6651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P102" t="str">
-        <v>SBIN0004844</v>
+        <v>SBIN0003100</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>0300042</v>
+        <v>0300051</v>
       </c>
       <c r="B103" t="str">
-        <v>MANOJ KHATUN</v>
+        <v>SUNITA TIWARI</v>
       </c>
       <c r="C103" t="str">
-        <v>Senior Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D103" t="str">
-        <v>03038</v>
+        <v>03044</v>
       </c>
       <c r="E103" t="str">
-        <v>Primary School Sheohar</v>
+        <v>Block Education Office Piprahi No.2</v>
       </c>
       <c r="F103" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G103" t="str">
-        <v>9003000042</v>
+        <v>9003000051</v>
       </c>
       <c r="H103" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I103" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J103" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K103" t="str">
         <v>0302</v>
       </c>
-      <c r="J103" t="str">
+      <c r="L103" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K103" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L103" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M103" t="str">
-        <v>30000332598</v>
+        <v>30000403869</v>
       </c>
       <c r="N103" t="str">
         <v>State Bank of India</v>
@@ -6701,48 +6701,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P103" t="str">
-        <v>SBIN0009030</v>
+        <v>SBIN0005463</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>0300054</v>
+        <v>0300004</v>
       </c>
       <c r="B104" t="str">
-        <v>SURESH RAI</v>
+        <v>MUKESH PRASAD</v>
       </c>
       <c r="C104" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Headmaster</v>
       </c>
       <c r="D104" t="str">
-        <v>03047</v>
+        <v>03004</v>
       </c>
       <c r="E104" t="str">
-        <v>CDPO Office Dumri Katsari No.3</v>
+        <v>Block Agriculture Office Tariyani No.4</v>
       </c>
       <c r="F104" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G104" t="str">
-        <v>9003000054</v>
+        <v>9003000004</v>
       </c>
       <c r="H104" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I104" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="J104" t="str">
-        <v>Others</v>
+        <v>Tariyani</v>
       </c>
       <c r="K104" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L104" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M104" t="str">
-        <v>30000427626</v>
+        <v>30000031676</v>
       </c>
       <c r="N104" t="str">
         <v>State Bank of India</v>
@@ -6751,33 +6751,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P104" t="str">
-        <v>SBIN0009023</v>
+        <v>SBIN0004849</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>0300012</v>
+        <v>0300063</v>
       </c>
       <c r="B105" t="str">
-        <v>POONAM KHATUN</v>
+        <v>SAVITA VERMA</v>
       </c>
       <c r="C105" t="str">
-        <v>Headmaster</v>
+        <v>Accountant</v>
       </c>
       <c r="D105" t="str">
-        <v>03012</v>
+        <v>03055</v>
       </c>
       <c r="E105" t="str">
-        <v>Block Office Sheohar</v>
+        <v>Collectorate (deputed from other district)</v>
       </c>
       <c r="F105" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G105" t="str">
-        <v>9003000012</v>
+        <v>9003000063</v>
       </c>
       <c r="H105" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I105" t="str">
         <v>0303</v>
@@ -6786,13 +6786,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K105" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="L105" t="str">
-        <v>Sheohar</v>
+        <v>Other District</v>
       </c>
       <c r="M105" t="str">
-        <v>30000095028</v>
+        <v>30000498897</v>
       </c>
       <c r="N105" t="str">
         <v>State Bank of India</v>
@@ -6801,33 +6801,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P105" t="str">
-        <v>SBIN0007689</v>
+        <v>SBIN0006546</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>0300085</v>
+        <v>0300113</v>
       </c>
       <c r="B106" t="str">
-        <v>RAJESH YADAV</v>
+        <v>USHA SINHA</v>
       </c>
       <c r="C106" t="str">
-        <v>Assistant Engineer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D106" t="str">
-        <v>03013</v>
+        <v>03090</v>
       </c>
       <c r="E106" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>State Bank of India, Piprahi</v>
       </c>
       <c r="F106" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G106" t="str">
-        <v>9003000085</v>
+        <v>9003000113</v>
       </c>
       <c r="H106" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I106" t="str">
         <v>999999</v>
@@ -6836,13 +6836,13 @@
         <v>Others</v>
       </c>
       <c r="K106" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L106" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M106" t="str">
-        <v>30000673115</v>
+        <v>30000894847</v>
       </c>
       <c r="N106" t="str">
         <v>State Bank of India</v>
@@ -6851,33 +6851,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P106" t="str">
-        <v>SBIN0005100</v>
+        <v>SBIN0007650</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>0300105</v>
+        <v>0300068</v>
       </c>
       <c r="B107" t="str">
-        <v>MUKESH SAH</v>
+        <v>ANIL DEVI</v>
       </c>
       <c r="C107" t="str">
-        <v>Assistant Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D107" t="str">
-        <v>03070</v>
+        <v>03059</v>
       </c>
       <c r="E107" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>PHC Purnahiya No.1</v>
       </c>
       <c r="F107" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G107" t="str">
-        <v>9003000105</v>
+        <v>9003000068</v>
       </c>
       <c r="H107" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I107" t="str">
         <v>0303</v>
@@ -6892,7 +6892,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M107" t="str">
-        <v>30000831495</v>
+        <v>30000538492</v>
       </c>
       <c r="N107" t="str">
         <v>State Bank of India</v>
@@ -6901,48 +6901,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P107" t="str">
-        <v>SBIN0003683</v>
+        <v>SBIN0001268</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>0300036</v>
+        <v>0300050</v>
       </c>
       <c r="B108" t="str">
-        <v>REKHA KHATUN</v>
+        <v>NIRMALA RAI</v>
       </c>
       <c r="C108" t="str">
-        <v>Assistant Teacher</v>
+        <v>Teacher</v>
       </c>
       <c r="D108" t="str">
-        <v>03032</v>
+        <v>03043</v>
       </c>
       <c r="E108" t="str">
-        <v>Primary School Purnahiya No.2</v>
+        <v>Block Office Piprahi No.2</v>
       </c>
       <c r="F108" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G108" t="str">
-        <v>9003000036</v>
+        <v>9003000050</v>
       </c>
       <c r="H108" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I108" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J108" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K108" t="str">
         <v>0302</v>
       </c>
-      <c r="J108" t="str">
+      <c r="L108" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K108" t="str">
-        <v>0303</v>
-      </c>
-      <c r="L108" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="M108" t="str">
-        <v>30000285084</v>
+        <v>30000395950</v>
       </c>
       <c r="N108" t="str">
         <v>State Bank of India</v>
@@ -6951,48 +6951,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P108" t="str">
-        <v>SBIN0007542</v>
+        <v>SBIN0002917</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>0300084</v>
+        <v>0300099</v>
       </c>
       <c r="B109" t="str">
-        <v>MAMTA JHA E</v>
+        <v>NITISH MISHRA</v>
       </c>
       <c r="C109" t="str">
-        <v>Data Entry Operator</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D109" t="str">
-        <v>03027</v>
+        <v>03079</v>
       </c>
       <c r="E109" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F109" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G109" t="str">
-        <v>9003000084</v>
+        <v>9003000099</v>
       </c>
       <c r="H109" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I109" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J109" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K109" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L109" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M109" t="str">
-        <v>30000665196</v>
+        <v>30000783981</v>
       </c>
       <c r="N109" t="str">
         <v>State Bank of India</v>
@@ -7001,48 +7001,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P109" t="str">
-        <v>SBIN0008276</v>
+        <v>SBIN0008924</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>0300080</v>
+        <v>0300032</v>
       </c>
       <c r="B110" t="str">
-        <v>MAMTA SAH</v>
+        <v>KIRAN OJHA</v>
       </c>
       <c r="C110" t="str">
-        <v>Teacher</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D110" t="str">
-        <v>03033</v>
+        <v>03030</v>
       </c>
       <c r="E110" t="str">
-        <v>Project Girls High School Dumri Katsari</v>
+        <v>Panchayat Bhawan Piprahi No.3</v>
       </c>
       <c r="F110" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G110" t="str">
-        <v>9003000080</v>
+        <v>9003000032</v>
       </c>
       <c r="H110" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I110" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J110" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K110" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L110" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M110" t="str">
-        <v>30000633520</v>
+        <v>30000253408</v>
       </c>
       <c r="N110" t="str">
         <v>State Bank of India</v>
@@ -7051,48 +7051,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P110" t="str">
-        <v>SBIN0009353</v>
+        <v>SBIN0006118</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>0300094</v>
+        <v>0300069</v>
       </c>
       <c r="B111" t="str">
-        <v>FARHAT SINGH U</v>
+        <v>ABDUL KALAM TIWARI</v>
       </c>
       <c r="C111" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Teacher</v>
       </c>
       <c r="D111" t="str">
-        <v>03013</v>
+        <v>03060</v>
       </c>
       <c r="E111" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>Primary School Dumri Katsari No.4</v>
       </c>
       <c r="F111" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G111" t="str">
-        <v>9003000094</v>
+        <v>9003000069</v>
       </c>
       <c r="H111" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I111" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J111" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K111" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L111" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M111" t="str">
-        <v>30000744386</v>
+        <v>30000546411</v>
       </c>
       <c r="N111" t="str">
         <v>State Bank of India</v>
@@ -7101,48 +7101,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P111" t="str">
-        <v>SBIN0004075</v>
+        <v>SBIN0004108</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>0300111</v>
+        <v>0300077</v>
       </c>
       <c r="B112" t="str">
-        <v>NITISH PASWAN</v>
+        <v>ARVIND ANSARI</v>
       </c>
       <c r="C112" t="str">
-        <v>Administrative Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D112" t="str">
-        <v>03088</v>
+        <v>03065</v>
       </c>
       <c r="E112" t="str">
-        <v>Head Post Office, Piprahi</v>
+        <v>Primary School Tariyani No.1</v>
       </c>
       <c r="F112" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G112" t="str">
-        <v>9003000111</v>
+        <v>9003000077</v>
       </c>
       <c r="H112" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I112" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J112" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K112" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L112" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M112" t="str">
-        <v>30000879009</v>
+        <v>30000609763</v>
       </c>
       <c r="N112" t="str">
         <v>State Bank of India</v>
@@ -7151,48 +7151,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P112" t="str">
-        <v>SBIN0002407</v>
+        <v>SBIN0004722</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>0300123</v>
+        <v>0300079</v>
       </c>
       <c r="B113" t="str">
-        <v>FARHAT VERMA</v>
+        <v>NITISH SHARMA</v>
       </c>
       <c r="C113" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Teacher</v>
       </c>
       <c r="D113" t="str">
-        <v>03097</v>
+        <v>03067</v>
       </c>
       <c r="E113" t="str">
-        <v>UCO Bank, Purnahiya</v>
+        <v>High School Piprahi No.1</v>
       </c>
       <c r="F113" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G113" t="str">
-        <v>9003000123</v>
+        <v>9003000079</v>
       </c>
       <c r="H113" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I113" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J113" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K113" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L113" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M113" t="str">
-        <v>30000974037</v>
+        <v>30000625601</v>
       </c>
       <c r="N113" t="str">
         <v>State Bank of India</v>
@@ -7201,33 +7201,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P113" t="str">
-        <v>SBIN0007993</v>
+        <v>SBIN0005793</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>0300004</v>
+        <v>0300095</v>
       </c>
       <c r="B114" t="str">
-        <v>NEHA YADAV</v>
+        <v>NASREEN RAI</v>
       </c>
       <c r="C114" t="str">
-        <v>Headmaster</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D114" t="str">
-        <v>03004</v>
+        <v>03076</v>
       </c>
       <c r="E114" t="str">
-        <v>Kanya Middle School Piprahi No.1</v>
+        <v>RWD Sub-Division Piprahi</v>
       </c>
       <c r="F114" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G114" t="str">
-        <v>9003000004</v>
+        <v>9003000095</v>
       </c>
       <c r="H114" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I114" t="str">
         <v>0302</v>
@@ -7242,7 +7242,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M114" t="str">
-        <v>30000031676</v>
+        <v>30000752305</v>
       </c>
       <c r="N114" t="str">
         <v>State Bank of India</v>
@@ -7251,48 +7251,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P114" t="str">
-        <v>SBIN0004874</v>
+        <v>SBIN0001346</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>0300035</v>
+        <v>0300080</v>
       </c>
       <c r="B115" t="str">
-        <v>VIJAY CHAUDHARY</v>
+        <v>ARVIND KUMAR</v>
       </c>
       <c r="C115" t="str">
-        <v>Head Clerk</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D115" t="str">
-        <v>03031</v>
+        <v>03068</v>
       </c>
       <c r="E115" t="str">
-        <v>Middle School Tariyani No.4</v>
+        <v>Block Agriculture Office Dumri Katsari No.4</v>
       </c>
       <c r="F115" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G115" t="str">
-        <v>9003000035</v>
+        <v>9003000080</v>
       </c>
       <c r="H115" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I115" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J115" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K115" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L115" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M115" t="str">
-        <v>30000277165</v>
+        <v>30000633520</v>
       </c>
       <c r="N115" t="str">
         <v>State Bank of India</v>
@@ -7301,48 +7301,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P115" t="str">
-        <v>SBIN0005083</v>
+        <v>SBIN0005197</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>0300098</v>
+        <v>0300007</v>
       </c>
       <c r="B116" t="str">
-        <v>SURESH CHAUDHARY</v>
+        <v>SAVITA THAKUR</v>
       </c>
       <c r="C116" t="str">
-        <v>Junior Engineer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D116" t="str">
-        <v>03070</v>
+        <v>03007</v>
       </c>
       <c r="E116" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>PHED Division Sheohar</v>
       </c>
       <c r="F116" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G116" t="str">
-        <v>9003000098</v>
+        <v>9003000007</v>
       </c>
       <c r="H116" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I116" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J116" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K116" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L116" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M116" t="str">
-        <v>30000776062</v>
+        <v>30000055433</v>
       </c>
       <c r="N116" t="str">
         <v>State Bank of India</v>
@@ -7351,48 +7351,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P116" t="str">
-        <v>SBIN0001601</v>
+        <v>SBIN0007222</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>0300049</v>
+        <v>0300043</v>
       </c>
       <c r="B117" t="str">
-        <v>ABDUL KALAM SINHA M</v>
+        <v>ARVIND ALAM</v>
       </c>
       <c r="C117" t="str">
         <v>Clerk</v>
       </c>
       <c r="D117" t="str">
-        <v>03045</v>
+        <v>03037</v>
       </c>
       <c r="E117" t="str">
-        <v>High School Tariyani No.2</v>
+        <v>Block Agriculture Office Piprahi No.4</v>
       </c>
       <c r="F117" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G117" t="str">
-        <v>9003000049</v>
+        <v>9003000043</v>
       </c>
       <c r="H117" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I117" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J117" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K117" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L117" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M117" t="str">
-        <v>30000388031</v>
+        <v>30000340517</v>
       </c>
       <c r="N117" t="str">
         <v>State Bank of India</v>
@@ -7401,48 +7401,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P117" t="str">
-        <v>SBIN0006530</v>
+        <v>SBIN0004129</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>0300033</v>
+        <v>0300014</v>
       </c>
       <c r="B118" t="str">
-        <v>SUNITA OJHA</v>
+        <v>SAVITA JHA</v>
       </c>
       <c r="C118" t="str">
-        <v>Senior Clerk</v>
+        <v>Headmaster</v>
       </c>
       <c r="D118" t="str">
-        <v>03029</v>
+        <v>03014</v>
       </c>
       <c r="E118" t="str">
-        <v>Middle School Dumri Katsari No.2</v>
+        <v>Block Agriculture Office Tariyani No.3</v>
       </c>
       <c r="F118" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G118" t="str">
-        <v>9003000033</v>
+        <v>9003000014</v>
       </c>
       <c r="H118" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I118" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J118" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K118" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L118" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M118" t="str">
-        <v>30000261327</v>
+        <v>30000110866</v>
       </c>
       <c r="N118" t="str">
         <v>State Bank of India</v>
@@ -7451,48 +7451,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P118" t="str">
-        <v>SBIN0001765</v>
+        <v>SBIN0003394</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>0300046</v>
+        <v>0300005</v>
       </c>
       <c r="B119" t="str">
-        <v>ALOK VERMA</v>
+        <v>KUMARI ANJALI PANDEY</v>
       </c>
       <c r="C119" t="str">
-        <v>Teacher</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D119" t="str">
-        <v>03042</v>
+        <v>03005</v>
       </c>
       <c r="E119" t="str">
-        <v>Block Education Office Purnahiya No.4</v>
+        <v>Middle School Dumri Katsari No.4</v>
       </c>
       <c r="F119" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G119" t="str">
-        <v>9003000046</v>
+        <v>9003000005</v>
       </c>
       <c r="H119" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I119" t="str">
+        <v>0305</v>
+      </c>
+      <c r="J119" t="str">
+        <v>Tariyani</v>
+      </c>
+      <c r="K119" t="str">
         <v>0304</v>
       </c>
-      <c r="J119" t="str">
+      <c r="L119" t="str">
         <v>Dumri Katsari</v>
       </c>
-      <c r="K119" t="str">
-        <v>0303</v>
-      </c>
-      <c r="L119" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="M119" t="str">
-        <v>30000364274</v>
+        <v>30000039595</v>
       </c>
       <c r="N119" t="str">
         <v>State Bank of India</v>
@@ -7501,33 +7501,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P119" t="str">
-        <v>SBIN0008960</v>
+        <v>SBIN0007893</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>0300014</v>
+        <v>0300028</v>
       </c>
       <c r="B120" t="str">
-        <v>RAVI MISHRA</v>
+        <v>RANJIT KUMAR</v>
       </c>
       <c r="C120" t="str">
-        <v>Assistant Engineer</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D120" t="str">
-        <v>03014</v>
+        <v>03027</v>
       </c>
       <c r="E120" t="str">
-        <v>Block Education Office Sheohar No.2</v>
+        <v>Block Agriculture Office Tariyani No.2</v>
       </c>
       <c r="F120" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G120" t="str">
-        <v>9003000014</v>
+        <v>9003000028</v>
       </c>
       <c r="H120" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I120" t="str">
         <v>0301</v>
@@ -7536,13 +7536,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K120" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L120" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M120" t="str">
-        <v>30000110866</v>
+        <v>30000221732</v>
       </c>
       <c r="N120" t="str">
         <v>State Bank of India</v>
@@ -7551,33 +7551,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P120" t="str">
-        <v>SBIN0002617</v>
+        <v>SBIN0003910</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>0300091</v>
+        <v>0300078</v>
       </c>
       <c r="B121" t="str">
-        <v>RINKU PASWAN</v>
+        <v>MD. SHAHID RAI</v>
       </c>
       <c r="C121" t="str">
-        <v>Assistant Engineer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D121" t="str">
-        <v>03074</v>
+        <v>03066</v>
       </c>
       <c r="E121" t="str">
-        <v>Circle Office Piprahi</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F121" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G121" t="str">
-        <v>9003000091</v>
+        <v>9003000078</v>
       </c>
       <c r="H121" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I121" t="str">
         <v>0302</v>
@@ -7586,13 +7586,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K121" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L121" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M121" t="str">
-        <v>30000720629</v>
+        <v>30000617682</v>
       </c>
       <c r="N121" t="str">
         <v>State Bank of India</v>
@@ -7601,48 +7601,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P121" t="str">
-        <v>SBIN0006038</v>
+        <v>SBIN0001846</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>0300113</v>
+        <v>0300103</v>
       </c>
       <c r="B122" t="str">
-        <v>SHAILESH THAKUR</v>
+        <v>SURESH VERMA</v>
       </c>
       <c r="C122" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D122" t="str">
-        <v>03085</v>
+        <v>03083</v>
       </c>
       <c r="E122" t="str">
-        <v>Head Post Office, Sheohar</v>
+        <v>Block Office Purnahiya</v>
       </c>
       <c r="F122" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G122" t="str">
-        <v>9003000113</v>
+        <v>9003000103</v>
       </c>
       <c r="H122" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I122" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J122" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K122" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L122" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M122" t="str">
-        <v>30000894847</v>
+        <v>30000815657</v>
       </c>
       <c r="N122" t="str">
         <v>State Bank of India</v>
@@ -7651,48 +7651,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P122" t="str">
-        <v>SBIN0009155</v>
+        <v>SBIN0003303</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>0300003</v>
+        <v>0300117</v>
       </c>
       <c r="B123" t="str">
-        <v>FARHAT PASWAN</v>
+        <v>USHA SINHA V</v>
       </c>
       <c r="C123" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D123" t="str">
-        <v>03003</v>
+        <v>03093</v>
       </c>
       <c r="E123" t="str">
-        <v>PHC Purnahiya</v>
+        <v>Head Post Office, Tariyani</v>
       </c>
       <c r="F123" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G123" t="str">
-        <v>9003000003</v>
+        <v>9003000117</v>
       </c>
       <c r="H123" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I123" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J123" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K123" t="str">
         <v>0305</v>
       </c>
-      <c r="J123" t="str">
+      <c r="L123" t="str">
         <v>Tariyani</v>
       </c>
-      <c r="K123" t="str">
-        <v>0303</v>
-      </c>
-      <c r="L123" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="M123" t="str">
-        <v>30000023757</v>
+        <v>30000926523</v>
       </c>
       <c r="N123" t="str">
         <v>State Bank of India</v>
@@ -7701,39 +7701,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P123" t="str">
-        <v>SBIN0007923</v>
+        <v>SBIN0004887</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>0300119</v>
+        <v>0300053</v>
       </c>
       <c r="B124" t="str">
-        <v>ASHA RAM</v>
+        <v>RINKU PANDEY</v>
       </c>
       <c r="C124" t="str">
-        <v>Administrative Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D124" t="str">
-        <v>03093</v>
+        <v>03046</v>
       </c>
       <c r="E124" t="str">
-        <v>UCO Bank, Tariyani</v>
+        <v>CDPO Office Tariyani</v>
       </c>
       <c r="F124" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G124" t="str">
-        <v>9003000119</v>
+        <v>9003000053</v>
       </c>
       <c r="H124" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I124" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J124" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K124" t="str">
         <v>0305</v>
@@ -7742,7 +7742,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M124" t="str">
-        <v>30000942361</v>
+        <v>30000419707</v>
       </c>
       <c r="N124" t="str">
         <v>State Bank of India</v>
@@ -7751,39 +7751,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P124" t="str">
-        <v>SBIN0007464</v>
+        <v>SBIN0002439</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>0300013</v>
+        <v>0300115</v>
       </c>
       <c r="B125" t="str">
-        <v>MAMTA VERMA</v>
+        <v>RAKESH VERMA</v>
       </c>
       <c r="C125" t="str">
-        <v>Lecturer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D125" t="str">
-        <v>03013</v>
+        <v>03092</v>
       </c>
       <c r="E125" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>LIC Branch Office, Purnahiya</v>
       </c>
       <c r="F125" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G125" t="str">
-        <v>9003000013</v>
+        <v>9003000115</v>
       </c>
       <c r="H125" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I125" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J125" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K125" t="str">
         <v>0303</v>
@@ -7792,7 +7792,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M125" t="str">
-        <v>30000102947</v>
+        <v>30000910685</v>
       </c>
       <c r="N125" t="str">
         <v>State Bank of India</v>
@@ -7801,48 +7801,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P125" t="str">
-        <v>SBIN0006750</v>
+        <v>SBIN0004053</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>0300016</v>
+        <v>0300062</v>
       </c>
       <c r="B126" t="str">
-        <v>RINKU VERMA G</v>
+        <v>RAMESH YADAV</v>
       </c>
       <c r="C126" t="str">
-        <v>Section Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D126" t="str">
-        <v>03016</v>
+        <v>03054</v>
       </c>
       <c r="E126" t="str">
-        <v>PHC Sheohar No.2</v>
+        <v>Middle School Dumri Katsari</v>
       </c>
       <c r="F126" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G126" t="str">
-        <v>9003000016</v>
+        <v>9003000062</v>
       </c>
       <c r="H126" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I126" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J126" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K126" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L126" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M126" t="str">
-        <v>30000126704</v>
+        <v>30000490978</v>
       </c>
       <c r="N126" t="str">
         <v>State Bank of India</v>
@@ -7851,39 +7851,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P126" t="str">
-        <v>SBIN0006468</v>
+        <v>SBIN0005630</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>0300076</v>
+        <v>0300054</v>
       </c>
       <c r="B127" t="str">
-        <v>SUNIL OJHA</v>
+        <v>SHAILESH JHA</v>
       </c>
       <c r="C127" t="str">
-        <v>Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D127" t="str">
-        <v>03065</v>
+        <v>03037</v>
       </c>
       <c r="E127" t="str">
-        <v>High School Piprahi No.1</v>
+        <v>Block Agriculture Office Piprahi No.4</v>
       </c>
       <c r="F127" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G127" t="str">
-        <v>9003000076</v>
+        <v>9003000054</v>
       </c>
       <c r="H127" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I127" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J127" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K127" t="str">
         <v>0302</v>
@@ -7892,7 +7892,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M127" t="str">
-        <v>30000601844</v>
+        <v>30000427626</v>
       </c>
       <c r="N127" t="str">
         <v>State Bank of India</v>
@@ -7901,7 +7901,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P127" t="str">
-        <v>SBIN0004740</v>
+        <v>SBIN0007782</v>
       </c>
     </row>
   </sheetData>
@@ -7954,7 +7954,7 @@
         <v>Main</v>
       </c>
       <c r="D2" t="str">
-        <v>Block Office Hall Sheohar, Room 2</v>
+        <v>High School Sheohar, Room 2</v>
       </c>
       <c r="E2" t="str">
         <v>0301</v>
@@ -8014,7 +8014,7 @@
         <v>Main</v>
       </c>
       <c r="D5" t="str">
-        <v>Middle School Dumri Katsari, Room 2</v>
+        <v>High School Dumri Katsari, Room 2</v>
       </c>
       <c r="E5" t="str">
         <v>0304</v>
@@ -8034,7 +8034,7 @@
         <v>Main</v>
       </c>
       <c r="D6" t="str">
-        <v>High School Tariyani, Room 3</v>
+        <v>Panchayat Bhawan Tariyani, Room 3</v>
       </c>
       <c r="E6" t="str">
         <v>0305</v>
@@ -8054,7 +8054,7 @@
         <v>Main</v>
       </c>
       <c r="D7" t="str">
-        <v>Panchayat Bhawan Sheohar, Room 1</v>
+        <v>High School Sheohar, Room 1</v>
       </c>
       <c r="E7" t="str">
         <v>0301</v>
@@ -8094,7 +8094,7 @@
         <v>Main</v>
       </c>
       <c r="D9" t="str">
-        <v>High School Dumri Katsari, Room 3</v>
+        <v>Block Office Hall Dumri Katsari, Room 3</v>
       </c>
       <c r="E9" t="str">
         <v>0304</v>
@@ -8114,7 +8114,7 @@
         <v>Main</v>
       </c>
       <c r="D10" t="str">
-        <v>Panchayat Bhawan Tariyani, Room 1</v>
+        <v>Kanya Middle School Tariyani, Room 1</v>
       </c>
       <c r="E10" t="str">
         <v>0305</v>
@@ -8134,7 +8134,7 @@
         <v>Main</v>
       </c>
       <c r="D11" t="str">
-        <v>Panchayat Bhawan Sheohar, Room 2</v>
+        <v>High School Sheohar, Room 2</v>
       </c>
       <c r="E11" t="str">
         <v>0301</v>
@@ -8154,7 +8154,7 @@
         <v>Main</v>
       </c>
       <c r="D12" t="str">
-        <v>Middle School Piprahi, Room 3</v>
+        <v>Kanya Middle School Piprahi, Room 3</v>
       </c>
       <c r="E12" t="str">
         <v>0302</v>
@@ -8174,7 +8174,7 @@
         <v>Main</v>
       </c>
       <c r="D13" t="str">
-        <v>High School Purnahiya, Room 1</v>
+        <v>Panchayat Bhawan Purnahiya, Room 1</v>
       </c>
       <c r="E13" t="str">
         <v>0303</v>

--- a/test-data/TEST_Sheohar_Project.xlsx
+++ b/test-data/TEST_Sheohar_Project.xlsx
@@ -17,7 +17,8 @@
     <sheet name="Final_Micro" sheetId="12" r:id="rId12"/>
     <sheet name="Status" sheetId="13" r:id="rId13"/>
     <sheet name="Exemptions" sheetId="14" r:id="rId14"/>
-    <sheet name="Audit_Log" sheetId="15" r:id="rId15"/>
+    <sheet name="Constituency_Fixed" sheetId="15" r:id="rId15"/>
+    <sheet name="Audit_Log" sheetId="16" r:id="rId16"/>
   </sheets>
 </workbook>
 </file>
@@ -613,7 +614,7 @@
         <v>Saved at</v>
       </c>
       <c r="B4" t="str">
-        <v>13-10-2026 17:30:35</v>
+        <v>13-10-2026 17:49:45</v>
       </c>
     </row>
     <row r="5">
@@ -776,6 +777,29 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B1"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PIN</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Constituency</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
@@ -792,7 +816,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>13-10-2026 17:30:35</v>
+        <v>13-10-2026 17:49:45</v>
       </c>
       <c r="B2" t="str">
         <v>Test data generated (Small — Sheohar style (5 blocks, 6 TC + 6 GC booths))</v>
@@ -1606,43 +1630,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0300074</v>
+        <v>0300051</v>
       </c>
       <c r="B2" t="str">
-        <v>RAMESH MISHRA</v>
+        <v>MAMTA VERMA</v>
       </c>
       <c r="C2" t="str">
-        <v>Data Entry Operator</v>
+        <v>Clerk</v>
       </c>
       <c r="D2" t="str">
-        <v>03032</v>
+        <v>03048</v>
       </c>
       <c r="E2" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Middle School Piprahi No.4</v>
       </c>
       <c r="F2" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G2" t="str">
-        <v>9003000074</v>
+        <v>9003000051</v>
       </c>
       <c r="H2" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I2" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J2" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K2" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L2" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M2" t="str">
-        <v>30000586006</v>
+        <v>30000403869</v>
       </c>
       <c r="N2" t="str">
         <v>State Bank of India</v>
@@ -1651,48 +1675,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P2" t="str">
-        <v>SBIN0007741</v>
+        <v>SBIN0002130</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0300006</v>
+        <v>0300080</v>
       </c>
       <c r="B3" t="str">
-        <v>RAKESH CHAUDHARY</v>
+        <v>NASREEN KHATUN</v>
       </c>
       <c r="C3" t="str">
-        <v>Assistant Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D3" t="str">
-        <v>03006</v>
+        <v>03004</v>
       </c>
       <c r="E3" t="str">
-        <v>Primary School Dumri Katsari No.3</v>
+        <v>Panchayat Bhawan Sheohar</v>
       </c>
       <c r="F3" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G3" t="str">
-        <v>9003000006</v>
+        <v>9003000080</v>
       </c>
       <c r="H3" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I3" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J3" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K3" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L3" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M3" t="str">
-        <v>30000047514</v>
+        <v>30000633520</v>
       </c>
       <c r="N3" t="str">
         <v>State Bank of India</v>
@@ -1701,48 +1725,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P3" t="str">
-        <v>SBIN0006526</v>
+        <v>SBIN0005849</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0300085</v>
+        <v>0300070</v>
       </c>
       <c r="B4" t="str">
-        <v>UMESH DEVI</v>
+        <v>ANIL SAH</v>
       </c>
       <c r="C4" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D4" t="str">
-        <v>03070</v>
+        <v>03062</v>
       </c>
       <c r="E4" t="str">
-        <v>RWD Sub-Division Tariyani</v>
+        <v>Block Office Sheohar No.3</v>
       </c>
       <c r="F4" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G4" t="str">
-        <v>9003000085</v>
+        <v>9003000070</v>
       </c>
       <c r="H4" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I4" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J4" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K4" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L4" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M4" t="str">
-        <v>30000673115</v>
+        <v>30000554330</v>
       </c>
       <c r="N4" t="str">
         <v>State Bank of India</v>
@@ -1751,48 +1775,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P4" t="str">
-        <v>SBIN0004680</v>
+        <v>SBIN0006774</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0300024</v>
+        <v>0300078</v>
       </c>
       <c r="B5" t="str">
-        <v>VINOD PASWAN</v>
+        <v>SUNIL OJHA</v>
       </c>
       <c r="C5" t="str">
-        <v>Assistant Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D5" t="str">
-        <v>03023</v>
+        <v>03068</v>
       </c>
       <c r="E5" t="str">
-        <v>Block Office Piprahi No.3</v>
+        <v>Block Office Tariyani No.4</v>
       </c>
       <c r="F5" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G5" t="str">
-        <v>9003000024</v>
+        <v>9003000078</v>
       </c>
       <c r="H5" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I5" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J5" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K5" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L5" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M5" t="str">
-        <v>30000190056</v>
+        <v>30000617682</v>
       </c>
       <c r="N5" t="str">
         <v>State Bank of India</v>
@@ -1801,30 +1825,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P5" t="str">
-        <v>SBIN0002842</v>
+        <v>SBIN0002850</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0300057</v>
+        <v>0300058</v>
       </c>
       <c r="B6" t="str">
-        <v>RANJIT PRASAD</v>
+        <v>SUNIL PASWAN</v>
       </c>
       <c r="C6" t="str">
-        <v>Accountant</v>
+        <v>Teacher</v>
       </c>
       <c r="D6" t="str">
-        <v>03049</v>
+        <v>03054</v>
       </c>
       <c r="E6" t="str">
-        <v>Middle School Sheohar No.2</v>
+        <v>Kanya Middle School Dumri Katsari No.4</v>
       </c>
       <c r="F6" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G6" t="str">
-        <v>9003000057</v>
+        <v>9003000058</v>
       </c>
       <c r="H6" t="str">
         <v>POLLING OFFICER-2</v>
@@ -1836,13 +1860,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K6" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L6" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M6" t="str">
-        <v>30000451383</v>
+        <v>30000459302</v>
       </c>
       <c r="N6" t="str">
         <v>State Bank of India</v>
@@ -1851,48 +1875,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P6" t="str">
-        <v>SBIN0008873</v>
+        <v>SBIN0001965</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>0300116</v>
+        <v>0300011</v>
       </c>
       <c r="B7" t="str">
-        <v>USHA ALAM</v>
+        <v>RINKU ALAM</v>
       </c>
       <c r="C7" t="str">
-        <v>Administrative Officer</v>
+        <v>Section Officer</v>
       </c>
       <c r="D7" t="str">
-        <v>03091</v>
+        <v>03011</v>
       </c>
       <c r="E7" t="str">
-        <v>BSNL Exchange, Sheohar</v>
+        <v>Block Office Dumri Katsari No.2</v>
       </c>
       <c r="F7" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G7" t="str">
-        <v>9003000116</v>
+        <v>9003000011</v>
       </c>
       <c r="H7" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I7" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J7" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K7" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L7" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M7" t="str">
-        <v>30000918604</v>
+        <v>30000087109</v>
       </c>
       <c r="N7" t="str">
         <v>State Bank of India</v>
@@ -1901,48 +1925,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P7" t="str">
-        <v>SBIN0002265</v>
+        <v>SBIN0008674</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0300086</v>
+        <v>0300105</v>
       </c>
       <c r="B8" t="str">
-        <v>AJAY ANSARI</v>
+        <v>AJAY JHA</v>
       </c>
       <c r="C8" t="str">
-        <v>Junior Engineer</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D8" t="str">
-        <v>03071</v>
+        <v>03072</v>
       </c>
       <c r="E8" t="str">
-        <v>Circle Office Sheohar</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F8" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G8" t="str">
-        <v>9003000086</v>
+        <v>9003000105</v>
       </c>
       <c r="H8" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I8" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J8" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K8" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L8" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M8" t="str">
-        <v>30000681034</v>
+        <v>30000831495</v>
       </c>
       <c r="N8" t="str">
         <v>State Bank of India</v>
@@ -1951,48 +1975,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P8" t="str">
-        <v>SBIN0007878</v>
+        <v>SBIN0001708</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0300109</v>
+        <v>0300107</v>
       </c>
       <c r="B9" t="str">
-        <v>USHA RAI</v>
+        <v>USHA PASWAN</v>
       </c>
       <c r="C9" t="str">
         <v>Branch Manager</v>
       </c>
       <c r="D9" t="str">
-        <v>03086</v>
+        <v>03082</v>
       </c>
       <c r="E9" t="str">
-        <v>State Bank of India, Dumri Katsari</v>
+        <v>Head Post Office, Sheohar</v>
       </c>
       <c r="F9" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G9" t="str">
-        <v>9003000109</v>
+        <v>9003000107</v>
       </c>
       <c r="H9" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I9" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J9" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K9" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L9" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M9" t="str">
-        <v>30000863171</v>
+        <v>30000847333</v>
       </c>
       <c r="N9" t="str">
         <v>State Bank of India</v>
@@ -2001,48 +2025,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P9" t="str">
-        <v>SBIN0007547</v>
+        <v>SBIN0001827</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0300106</v>
+        <v>0300066</v>
       </c>
       <c r="B10" t="str">
-        <v>NIRMALA KHATUN</v>
+        <v>RAJESH MISHRA</v>
       </c>
       <c r="C10" t="str">
-        <v>Assistant Manager</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D10" t="str">
-        <v>03084</v>
+        <v>03060</v>
       </c>
       <c r="E10" t="str">
-        <v>LIC Branch Office, Dumri Katsari</v>
+        <v>Middle School Piprahi No.1</v>
       </c>
       <c r="F10" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G10" t="str">
-        <v>9003000106</v>
+        <v>9003000066</v>
       </c>
       <c r="H10" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I10" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="J10" t="str">
-        <v>Others</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K10" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L10" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M10" t="str">
-        <v>30000839414</v>
+        <v>30000522654</v>
       </c>
       <c r="N10" t="str">
         <v>State Bank of India</v>
@@ -2051,7 +2075,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P10" t="str">
-        <v>SBIN0004673</v>
+        <v>SBIN0006779</v>
       </c>
     </row>
     <row r="11">
@@ -2059,19 +2083,19 @@
         <v>0300104</v>
       </c>
       <c r="B11" t="str">
-        <v>DINESH MAHTO</v>
+        <v>NIRMALA JHA</v>
       </c>
       <c r="C11" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D11" t="str">
-        <v>03076</v>
+        <v>03080</v>
       </c>
       <c r="E11" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>Block Agriculture Office Purnahiya</v>
       </c>
       <c r="F11" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G11" t="str">
         <v>9003000104</v>
@@ -2080,16 +2104,16 @@
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I11" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J11" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K11" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L11" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M11" t="str">
         <v>30000823576</v>
@@ -2101,48 +2125,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P11" t="str">
-        <v>SBIN0001523</v>
+        <v>SBIN0002071</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>0300040</v>
+        <v>0300022</v>
       </c>
       <c r="B12" t="str">
-        <v>KUMARI ANJALI GUPTA</v>
+        <v>DEEPAK JHA</v>
       </c>
       <c r="C12" t="str">
         <v>Senior Clerk</v>
       </c>
       <c r="D12" t="str">
-        <v>03007</v>
+        <v>03021</v>
       </c>
       <c r="E12" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>Panchayat Bhawan Purnahiya No.2</v>
       </c>
       <c r="F12" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G12" t="str">
-        <v>9003000040</v>
+        <v>9003000022</v>
       </c>
       <c r="H12" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I12" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J12" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K12" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L12" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M12" t="str">
-        <v>30000316760</v>
+        <v>30000174218</v>
       </c>
       <c r="N12" t="str">
         <v>State Bank of India</v>
@@ -2151,39 +2175,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P12" t="str">
-        <v>SBIN0004065</v>
+        <v>SBIN0003212</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0300021</v>
+        <v>0300102</v>
       </c>
       <c r="B13" t="str">
-        <v>RAKESH TIWARI</v>
+        <v>SUNITA THAKUR</v>
       </c>
       <c r="C13" t="str">
-        <v>Headmaster</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D13" t="str">
-        <v>03020</v>
+        <v>03036</v>
       </c>
       <c r="E13" t="str">
-        <v>Panchayat Bhawan Dumri Katsari</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="F13" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G13" t="str">
-        <v>9003000021</v>
+        <v>9003000102</v>
       </c>
       <c r="H13" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I13" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J13" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K13" t="str">
         <v>0304</v>
@@ -2192,7 +2216,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M13" t="str">
-        <v>30000166299</v>
+        <v>30000807738</v>
       </c>
       <c r="N13" t="str">
         <v>State Bank of India</v>
@@ -2201,48 +2225,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P13" t="str">
-        <v>SBIN0006244</v>
+        <v>SBIN0008988</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0300020</v>
+        <v>0300024</v>
       </c>
       <c r="B14" t="str">
-        <v>SUNIL YADAV</v>
+        <v>PRAMOD DEVI</v>
       </c>
       <c r="C14" t="str">
-        <v>Headmaster</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D14" t="str">
-        <v>03020</v>
+        <v>03023</v>
       </c>
       <c r="E14" t="str">
-        <v>Panchayat Bhawan Dumri Katsari</v>
+        <v>High School Piprahi No.2</v>
       </c>
       <c r="F14" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G14" t="str">
-        <v>9003000020</v>
+        <v>9003000024</v>
       </c>
       <c r="H14" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I14" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J14" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K14" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L14" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M14" t="str">
-        <v>30000158380</v>
+        <v>30000190056</v>
       </c>
       <c r="N14" t="str">
         <v>State Bank of India</v>
@@ -2251,48 +2275,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P14" t="str">
-        <v>SBIN0002891</v>
+        <v>SBIN0007249</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>0300123</v>
+        <v>0300034</v>
       </c>
       <c r="B15" t="str">
-        <v>KIRAN RAI</v>
+        <v>RINKU GUPTA</v>
       </c>
       <c r="C15" t="str">
-        <v>Assistant Manager</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D15" t="str">
-        <v>03096</v>
+        <v>03031</v>
       </c>
       <c r="E15" t="str">
-        <v>UCO Bank, Purnahiya</v>
+        <v>Panchayat Bhawan Piprahi</v>
       </c>
       <c r="F15" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G15" t="str">
-        <v>9003000123</v>
+        <v>9003000034</v>
       </c>
       <c r="H15" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I15" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J15" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K15" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L15" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M15" t="str">
-        <v>30000974037</v>
+        <v>30000269246</v>
       </c>
       <c r="N15" t="str">
         <v>State Bank of India</v>
@@ -2301,33 +2325,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P15" t="str">
-        <v>SBIN0007445</v>
+        <v>SBIN0006504</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>0300029</v>
+        <v>0300089</v>
       </c>
       <c r="B16" t="str">
-        <v>VIJAY MISHRA</v>
+        <v>SANTOSH PRASAD</v>
       </c>
       <c r="C16" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D16" t="str">
-        <v>03028</v>
+        <v>03013</v>
       </c>
       <c r="E16" t="str">
-        <v>Block Office Tariyani No.4</v>
+        <v>Circle Office Sheohar</v>
       </c>
       <c r="F16" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G16" t="str">
-        <v>9003000029</v>
+        <v>9003000089</v>
       </c>
       <c r="H16" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I16" t="str">
         <v>0305</v>
@@ -2336,13 +2360,13 @@
         <v>Tariyani</v>
       </c>
       <c r="K16" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L16" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M16" t="str">
-        <v>30000229651</v>
+        <v>30000704791</v>
       </c>
       <c r="N16" t="str">
         <v>State Bank of India</v>
@@ -2351,48 +2375,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P16" t="str">
-        <v>SBIN0009241</v>
+        <v>SBIN0002951</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>0300047</v>
+        <v>0300111</v>
       </c>
       <c r="B17" t="str">
-        <v>ALOK MAHTO</v>
+        <v>ASHA THAKUR</v>
       </c>
       <c r="C17" t="str">
-        <v>Teacher</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D17" t="str">
-        <v>03040</v>
+        <v>03086</v>
       </c>
       <c r="E17" t="str">
-        <v>Panchayat Bhawan Dumri Katsari No.4</v>
+        <v>Head Post Office, Purnahiya</v>
       </c>
       <c r="F17" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G17" t="str">
-        <v>9003000047</v>
+        <v>9003000111</v>
       </c>
       <c r="H17" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I17" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J17" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K17" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L17" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M17" t="str">
-        <v>30000372193</v>
+        <v>30000879009</v>
       </c>
       <c r="N17" t="str">
         <v>State Bank of India</v>
@@ -2401,48 +2425,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P17" t="str">
-        <v>SBIN0004772</v>
+        <v>SBIN0004466</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>0300035</v>
+        <v>0300087</v>
       </c>
       <c r="B18" t="str">
-        <v>RINKU PASWAN</v>
+        <v>KUMARI ANJALI ALAM</v>
       </c>
       <c r="C18" t="str">
-        <v>Head Clerk</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D18" t="str">
-        <v>03033</v>
+        <v>03072</v>
       </c>
       <c r="E18" t="str">
-        <v>High School Tariyani No.2</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F18" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G18" t="str">
-        <v>9003000035</v>
+        <v>9003000087</v>
       </c>
       <c r="H18" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I18" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J18" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K18" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L18" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M18" t="str">
-        <v>30000277165</v>
+        <v>30000688953</v>
       </c>
       <c r="N18" t="str">
         <v>State Bank of India</v>
@@ -2451,48 +2475,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P18" t="str">
-        <v>SBIN0005903</v>
+        <v>SBIN0005040</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>0300001</v>
+        <v>0300079</v>
       </c>
       <c r="B19" t="str">
-        <v>ASHA OJHA</v>
+        <v>ANIL PANDEY</v>
       </c>
       <c r="C19" t="str">
-        <v>Assistant Engineer</v>
+        <v>Clerk</v>
       </c>
       <c r="D19" t="str">
-        <v>03001</v>
+        <v>03004</v>
       </c>
       <c r="E19" t="str">
-        <v>Primary School Purnahiya</v>
+        <v>Panchayat Bhawan Sheohar</v>
       </c>
       <c r="F19" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G19" t="str">
-        <v>9003000001</v>
+        <v>9003000079</v>
       </c>
       <c r="H19" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I19" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J19" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K19" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L19" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M19" t="str">
-        <v>30000007919</v>
+        <v>30000625601</v>
       </c>
       <c r="N19" t="str">
         <v>State Bank of India</v>
@@ -2501,48 +2525,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P19" t="str">
-        <v>SBIN0002099</v>
+        <v>SBIN0007955</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>0300089</v>
+        <v>0300118</v>
       </c>
       <c r="B20" t="str">
-        <v>RINKU KUMAR</v>
+        <v>FARHAT KUMAR</v>
       </c>
       <c r="C20" t="str">
-        <v>Junior Engineer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D20" t="str">
-        <v>03074</v>
+        <v>03091</v>
       </c>
       <c r="E20" t="str">
-        <v>Minor Irrigation Office Tariyani</v>
+        <v>Punjab National Bank, Dumri Katsari</v>
       </c>
       <c r="F20" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G20" t="str">
-        <v>9003000089</v>
+        <v>9003000118</v>
       </c>
       <c r="H20" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I20" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="J20" t="str">
-        <v>Others</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K20" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L20" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M20" t="str">
-        <v>30000704791</v>
+        <v>30000934442</v>
       </c>
       <c r="N20" t="str">
         <v>State Bank of India</v>
@@ -2551,48 +2575,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P20" t="str">
-        <v>SBIN0009790</v>
+        <v>SBIN0009416</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>0300064</v>
+        <v>0300015</v>
       </c>
       <c r="B21" t="str">
-        <v>RINKU CHAUDHARY</v>
+        <v>ANITA DEVI</v>
       </c>
       <c r="C21" t="str">
-        <v>Teacher</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D21" t="str">
-        <v>03056</v>
+        <v>03014</v>
       </c>
       <c r="E21" t="str">
-        <v>Primary School Tariyani No.4</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F21" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G21" t="str">
-        <v>9003000064</v>
+        <v>9003000015</v>
       </c>
       <c r="H21" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I21" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J21" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K21" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L21" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M21" t="str">
-        <v>30000506816</v>
+        <v>30000118785</v>
       </c>
       <c r="N21" t="str">
         <v>State Bank of India</v>
@@ -2601,33 +2625,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P21" t="str">
-        <v>SBIN0008428</v>
+        <v>SBIN0004755</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>0300044</v>
+        <v>0300017</v>
       </c>
       <c r="B22" t="str">
-        <v>SANJAY GUPTA</v>
+        <v>PRAMOD MISHRA</v>
       </c>
       <c r="C22" t="str">
-        <v>Teacher</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D22" t="str">
-        <v>03017</v>
+        <v>03016</v>
       </c>
       <c r="E22" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>High School Sheohar No.3</v>
       </c>
       <c r="F22" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G22" t="str">
-        <v>9003000044</v>
+        <v>9003000017</v>
       </c>
       <c r="H22" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I22" t="str">
         <v>0301</v>
@@ -2642,7 +2666,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M22" t="str">
-        <v>30000348436</v>
+        <v>30000134623</v>
       </c>
       <c r="N22" t="str">
         <v>State Bank of India</v>
@@ -2651,33 +2675,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P22" t="str">
-        <v>SBIN0001253</v>
+        <v>SBIN0003186</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>0300098</v>
+        <v>0300059</v>
       </c>
       <c r="B23" t="str">
-        <v>ASHA SHARMA</v>
+        <v>SAVITA ANSARI</v>
       </c>
       <c r="C23" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Accountant</v>
       </c>
       <c r="D23" t="str">
-        <v>03078</v>
+        <v>03055</v>
       </c>
       <c r="E23" t="str">
-        <v>Minor Irrigation Office Sheohar</v>
+        <v>Kanya Middle School Tariyani No.3</v>
       </c>
       <c r="F23" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G23" t="str">
-        <v>9003000098</v>
+        <v>9003000059</v>
       </c>
       <c r="H23" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I23" t="str">
         <v>0301</v>
@@ -2686,13 +2710,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K23" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L23" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M23" t="str">
-        <v>30000776062</v>
+        <v>30000467221</v>
       </c>
       <c r="N23" t="str">
         <v>State Bank of India</v>
@@ -2701,48 +2725,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P23" t="str">
-        <v>SBIN0003117</v>
+        <v>SBIN0006760</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>0300118</v>
+        <v>0300009</v>
       </c>
       <c r="B24" t="str">
-        <v>KIRAN SAH</v>
+        <v>DINESH SHARMA</v>
       </c>
       <c r="C24" t="str">
-        <v>Postmaster</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D24" t="str">
-        <v>03094</v>
+        <v>03009</v>
       </c>
       <c r="E24" t="str">
-        <v>Central Bank of India, Piprahi</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F24" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G24" t="str">
-        <v>9003000118</v>
+        <v>9003000009</v>
       </c>
       <c r="H24" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I24" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="J24" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="K24" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L24" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M24" t="str">
-        <v>30000934442</v>
+        <v>30000071271</v>
       </c>
       <c r="N24" t="str">
         <v>State Bank of India</v>
@@ -2751,48 +2775,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P24" t="str">
-        <v>SBIN0005227</v>
+        <v>SBIN0002226</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0300042</v>
+        <v>0300092</v>
       </c>
       <c r="B25" t="str">
-        <v>UMESH OJHA</v>
+        <v>SURESH ANSARI</v>
       </c>
       <c r="C25" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D25" t="str">
-        <v>03036</v>
+        <v>03075</v>
       </c>
       <c r="E25" t="str">
-        <v>CDPO Office Piprahi No.3</v>
+        <v>Minor Irrigation Office Sheohar</v>
       </c>
       <c r="F25" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G25" t="str">
-        <v>9003000042</v>
+        <v>9003000092</v>
       </c>
       <c r="H25" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I25" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J25" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K25" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L25" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M25" t="str">
-        <v>30000332598</v>
+        <v>30000728548</v>
       </c>
       <c r="N25" t="str">
         <v>State Bank of India</v>
@@ -2801,48 +2825,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P25" t="str">
-        <v>SBIN0003580</v>
+        <v>SBIN0009780</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>0300018</v>
+        <v>0300014</v>
       </c>
       <c r="B26" t="str">
-        <v>REKHA YADAV</v>
+        <v>RAVI PASWAN</v>
       </c>
       <c r="C26" t="str">
-        <v>Section Officer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D26" t="str">
-        <v>03018</v>
+        <v>03013</v>
       </c>
       <c r="E26" t="str">
-        <v>Block Office Dumri Katsari No.4</v>
+        <v>Circle Office Sheohar</v>
       </c>
       <c r="F26" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G26" t="str">
-        <v>9003000018</v>
+        <v>9003000014</v>
       </c>
       <c r="H26" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I26" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J26" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K26" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L26" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M26" t="str">
-        <v>30000142542</v>
+        <v>30000110866</v>
       </c>
       <c r="N26" t="str">
         <v>State Bank of India</v>
@@ -2851,48 +2875,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P26" t="str">
-        <v>SBIN0006984</v>
+        <v>SBIN0008875</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>0300119</v>
+        <v>0300074</v>
       </c>
       <c r="B27" t="str">
-        <v>MD. SHAHID KHATUN</v>
+        <v>NEHA GUPTA N</v>
       </c>
       <c r="C27" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D27" t="str">
-        <v>03095</v>
+        <v>03005</v>
       </c>
       <c r="E27" t="str">
-        <v>Central Bank of India, Sheohar</v>
+        <v>Kanya Middle School Tariyani</v>
       </c>
       <c r="F27" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G27" t="str">
-        <v>9003000119</v>
+        <v>9003000074</v>
       </c>
       <c r="H27" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I27" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J27" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K27" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L27" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M27" t="str">
-        <v>30000942361</v>
+        <v>30000586006</v>
       </c>
       <c r="N27" t="str">
         <v>State Bank of India</v>
@@ -2901,33 +2925,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P27" t="str">
-        <v>SBIN0009780</v>
+        <v>SBIN0003064</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>0300076</v>
+        <v>0300126</v>
       </c>
       <c r="B28" t="str">
-        <v>SURESH ALAM</v>
+        <v>ANIL MISHRA</v>
       </c>
       <c r="C28" t="str">
-        <v>Teacher</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D28" t="str">
-        <v>03064</v>
+        <v>03096</v>
       </c>
       <c r="E28" t="str">
-        <v>Block Agriculture Office Dumri Katsari</v>
+        <v>State Bank of India, Purnahiya</v>
       </c>
       <c r="F28" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G28" t="str">
-        <v>9003000076</v>
+        <v>9003000126</v>
       </c>
       <c r="H28" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I28" t="str">
         <v>0303</v>
@@ -2936,13 +2960,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K28" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L28" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M28" t="str">
-        <v>30000601844</v>
+        <v>30000997794</v>
       </c>
       <c r="N28" t="str">
         <v>State Bank of India</v>
@@ -2951,48 +2975,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P28" t="str">
-        <v>SBIN0006430</v>
+        <v>SBIN0003032</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>0300030</v>
+        <v>0300112</v>
       </c>
       <c r="B29" t="str">
-        <v>RAKESH ANSARI</v>
+        <v>NIRMALA RAM</v>
       </c>
       <c r="C29" t="str">
-        <v>Senior Clerk</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D29" t="str">
-        <v>03029</v>
+        <v>03084</v>
       </c>
       <c r="E29" t="str">
-        <v>Circle Office Dumri Katsari</v>
+        <v>Head Post Office, Piprahi</v>
       </c>
       <c r="F29" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G29" t="str">
-        <v>9003000030</v>
+        <v>9003000112</v>
       </c>
       <c r="H29" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I29" t="str">
+        <v>0301</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Sheohar</v>
+      </c>
+      <c r="K29" t="str">
         <v>0302</v>
       </c>
-      <c r="J29" t="str">
+      <c r="L29" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K29" t="str">
-        <v>0304</v>
-      </c>
-      <c r="L29" t="str">
-        <v>Dumri Katsari</v>
-      </c>
       <c r="M29" t="str">
-        <v>30000237570</v>
+        <v>30000886928</v>
       </c>
       <c r="N29" t="str">
         <v>State Bank of India</v>
@@ -3001,48 +3025,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P29" t="str">
-        <v>SBIN0008493</v>
+        <v>SBIN0001402</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>0300010</v>
+        <v>0300075</v>
       </c>
       <c r="B30" t="str">
-        <v>RANJIT THAKUR</v>
+        <v>ARVIND SINHA</v>
       </c>
       <c r="C30" t="str">
-        <v>Block Agriculture Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D30" t="str">
-        <v>03010</v>
+        <v>03064</v>
       </c>
       <c r="E30" t="str">
-        <v>Primary School Purnahiya No.3</v>
+        <v>Panchayat Bhawan Sheohar No.1</v>
       </c>
       <c r="F30" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G30" t="str">
-        <v>9003000010</v>
+        <v>9003000075</v>
       </c>
       <c r="H30" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I30" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J30" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K30" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L30" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M30" t="str">
-        <v>30000079190</v>
+        <v>30000593925</v>
       </c>
       <c r="N30" t="str">
         <v>State Bank of India</v>
@@ -3051,39 +3075,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P30" t="str">
-        <v>SBIN0003171</v>
+        <v>SBIN0008273</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>0300105</v>
+        <v>0300020</v>
       </c>
       <c r="B31" t="str">
-        <v>MANOJ THAKUR</v>
+        <v>SANTOSH ALAM</v>
       </c>
       <c r="C31" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D31" t="str">
-        <v>03075</v>
+        <v>03019</v>
       </c>
       <c r="E31" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>Block Office Purnahiya No.1</v>
       </c>
       <c r="F31" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G31" t="str">
-        <v>9003000105</v>
+        <v>9003000020</v>
       </c>
       <c r="H31" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I31" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="J31" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K31" t="str">
         <v>0303</v>
@@ -3092,7 +3116,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M31" t="str">
-        <v>30000831495</v>
+        <v>30000158380</v>
       </c>
       <c r="N31" t="str">
         <v>State Bank of India</v>
@@ -3101,48 +3125,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P31" t="str">
-        <v>SBIN0003073</v>
+        <v>SBIN0005576</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>0300045</v>
+        <v>0300076</v>
       </c>
       <c r="B32" t="str">
-        <v>FARHAT THAKUR</v>
+        <v>ARVIND KHATUN</v>
       </c>
       <c r="C32" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D32" t="str">
-        <v>03038</v>
+        <v>03066</v>
       </c>
       <c r="E32" t="str">
-        <v>Circle Office Tariyani No.2</v>
+        <v>Project Girls High School Sheohar No.2</v>
       </c>
       <c r="F32" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G32" t="str">
-        <v>9003000045</v>
+        <v>9003000076</v>
       </c>
       <c r="H32" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I32" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J32" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K32" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L32" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M32" t="str">
-        <v>30000356355</v>
+        <v>30000601844</v>
       </c>
       <c r="N32" t="str">
         <v>State Bank of India</v>
@@ -3151,39 +3175,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P32" t="str">
-        <v>SBIN0001358</v>
+        <v>SBIN0005663</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>0300036</v>
+        <v>0300008</v>
       </c>
       <c r="B33" t="str">
-        <v>REKHA VERMA</v>
+        <v>SAVITA PRASAD</v>
       </c>
       <c r="C33" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D33" t="str">
-        <v>03034</v>
+        <v>03008</v>
       </c>
       <c r="E33" t="str">
-        <v>Primary School Sheohar No.4</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F33" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G33" t="str">
-        <v>9003000036</v>
+        <v>9003000008</v>
       </c>
       <c r="H33" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I33" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J33" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K33" t="str">
         <v>0301</v>
@@ -3192,7 +3216,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M33" t="str">
-        <v>30000285084</v>
+        <v>30000063352</v>
       </c>
       <c r="N33" t="str">
         <v>State Bank of India</v>
@@ -3201,39 +3225,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P33" t="str">
-        <v>SBIN0007569</v>
+        <v>SBIN0004445</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>0300073</v>
+        <v>0300063</v>
       </c>
       <c r="B34" t="str">
-        <v>NITISH ALAM</v>
+        <v>KIRAN SHARMA</v>
       </c>
       <c r="C34" t="str">
-        <v>Teacher</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D34" t="str">
-        <v>03032</v>
+        <v>03009</v>
       </c>
       <c r="E34" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Collectorate Sheohar</v>
       </c>
       <c r="F34" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G34" t="str">
-        <v>9003000073</v>
+        <v>9003000063</v>
       </c>
       <c r="H34" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I34" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J34" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K34" t="str">
         <v>0301</v>
@@ -3242,7 +3266,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M34" t="str">
-        <v>30000578087</v>
+        <v>30000498897</v>
       </c>
       <c r="N34" t="str">
         <v>State Bank of India</v>
@@ -3251,33 +3275,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P34" t="str">
-        <v>SBIN0007462</v>
+        <v>SBIN0008579</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>0300126</v>
+        <v>0300037</v>
       </c>
       <c r="B35" t="str">
-        <v>SUNITA KUMAR</v>
+        <v>RANJIT CHAUDHARY</v>
       </c>
       <c r="C35" t="str">
-        <v>Branch Manager</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D35" t="str">
-        <v>03098</v>
+        <v>03034</v>
       </c>
       <c r="E35" t="str">
-        <v>Punjab National Bank, Piprahi</v>
+        <v>High School Dumri Katsari No.4</v>
       </c>
       <c r="F35" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G35" t="str">
-        <v>9003000126</v>
+        <v>9003000037</v>
       </c>
       <c r="H35" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I35" t="str">
         <v>0304</v>
@@ -3286,13 +3310,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K35" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L35" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M35" t="str">
-        <v>30000997794</v>
+        <v>30000293003</v>
       </c>
       <c r="N35" t="str">
         <v>State Bank of India</v>
@@ -3301,39 +3325,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P35" t="str">
-        <v>SBIN0003521</v>
+        <v>SBIN0003774</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>0300066</v>
+        <v>0300098</v>
       </c>
       <c r="B36" t="str">
-        <v>AMIT MISHRA</v>
+        <v>UMESH SINHA</v>
       </c>
       <c r="C36" t="str">
-        <v>Office Assistant</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D36" t="str">
-        <v>03058</v>
+        <v>03078</v>
       </c>
       <c r="E36" t="str">
-        <v>Project Girls High School Dumri Katsari No.1</v>
+        <v>RWD Sub-Division Dumri Katsari</v>
       </c>
       <c r="F36" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G36" t="str">
-        <v>9003000066</v>
+        <v>9003000098</v>
       </c>
       <c r="H36" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I36" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J36" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K36" t="str">
         <v>0304</v>
@@ -3342,7 +3366,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M36" t="str">
-        <v>30000522654</v>
+        <v>30000776062</v>
       </c>
       <c r="N36" t="str">
         <v>State Bank of India</v>
@@ -3351,33 +3375,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P36" t="str">
-        <v>SBIN0006440</v>
+        <v>SBIN0008306</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>0300100</v>
+        <v>0300041</v>
       </c>
       <c r="B37" t="str">
-        <v>SANTOSH PASWAN</v>
+        <v>RAJESH GUPTA</v>
       </c>
       <c r="C37" t="str">
-        <v>Assistant Engineer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D37" t="str">
-        <v>03080</v>
+        <v>03038</v>
       </c>
       <c r="E37" t="str">
-        <v>Minor Irrigation Office Piprahi</v>
+        <v>Kanya Middle School Dumri Katsari</v>
       </c>
       <c r="F37" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G37" t="str">
-        <v>9003000100</v>
+        <v>9003000041</v>
       </c>
       <c r="H37" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I37" t="str">
         <v>0304</v>
@@ -3386,13 +3410,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K37" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L37" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M37" t="str">
-        <v>30000791900</v>
+        <v>30000324679</v>
       </c>
       <c r="N37" t="str">
         <v>State Bank of India</v>
@@ -3401,33 +3425,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P37" t="str">
-        <v>SBIN0005969</v>
+        <v>SBIN0006244</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>0300084</v>
+        <v>0300043</v>
       </c>
       <c r="B38" t="str">
-        <v>PRIYANKA ALAM D</v>
+        <v>NEHA ANSARI</v>
       </c>
       <c r="C38" t="str">
-        <v>Clerk</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D38" t="str">
-        <v>03045</v>
+        <v>03040</v>
       </c>
       <c r="E38" t="str">
-        <v>PHC Tariyani</v>
+        <v>PHC Dumri Katsari No.3</v>
       </c>
       <c r="F38" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G38" t="str">
-        <v>9003000084</v>
+        <v>9003000043</v>
       </c>
       <c r="H38" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I38" t="str">
         <v>0304</v>
@@ -3436,13 +3460,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K38" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L38" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M38" t="str">
-        <v>30000665196</v>
+        <v>30000340517</v>
       </c>
       <c r="N38" t="str">
         <v>State Bank of India</v>
@@ -3451,15 +3475,15 @@
         <v>Sheohar</v>
       </c>
       <c r="P38" t="str">
-        <v>SBIN0009875</v>
+        <v>SBIN0009132</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>0300096</v>
+        <v>0300095</v>
       </c>
       <c r="B39" t="str">
-        <v>RAVI PANDEY</v>
+        <v>SAVITA DEVI</v>
       </c>
       <c r="C39" t="str">
         <v>Assistant Engineer</v>
@@ -3468,31 +3492,31 @@
         <v>03077</v>
       </c>
       <c r="E39" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>Collectorate (deputed from other district)</v>
       </c>
       <c r="F39" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G39" t="str">
-        <v>9003000096</v>
+        <v>9003000095</v>
       </c>
       <c r="H39" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I39" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J39" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K39" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="L39" t="str">
-        <v>Tariyani</v>
+        <v>Other District</v>
       </c>
       <c r="M39" t="str">
-        <v>30000760224</v>
+        <v>30000752305</v>
       </c>
       <c r="N39" t="str">
         <v>State Bank of India</v>
@@ -3501,48 +3525,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P39" t="str">
-        <v>SBIN0001387</v>
+        <v>SBIN0009555</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>0300061</v>
+        <v>0300056</v>
       </c>
       <c r="B40" t="str">
-        <v>MUKESH DEVI</v>
+        <v>SANJAY RAM</v>
       </c>
       <c r="C40" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Clerk</v>
       </c>
       <c r="D40" t="str">
-        <v>03053</v>
+        <v>03052</v>
       </c>
       <c r="E40" t="str">
-        <v>Panchayat Bhawan Piprahi No.2</v>
+        <v>Circle Office Tariyani No.2</v>
       </c>
       <c r="F40" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G40" t="str">
-        <v>9003000061</v>
+        <v>9003000056</v>
       </c>
       <c r="H40" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I40" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="J40" t="str">
-        <v>Others</v>
+        <v>Tariyani</v>
       </c>
       <c r="K40" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="L40" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="M40" t="str">
-        <v>30000483059</v>
+        <v>30000443464</v>
       </c>
       <c r="N40" t="str">
         <v>State Bank of India</v>
@@ -3551,39 +3575,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P40" t="str">
-        <v>SBIN0002042</v>
+        <v>SBIN0006699</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>0300082</v>
+        <v>0300044</v>
       </c>
       <c r="B41" t="str">
-        <v>POONAM RAM</v>
+        <v>ANITA ALAM</v>
       </c>
       <c r="C41" t="str">
         <v>Teacher</v>
       </c>
       <c r="D41" t="str">
-        <v>03069</v>
+        <v>03041</v>
       </c>
       <c r="E41" t="str">
-        <v>Middle School Purnahiya No.2</v>
+        <v>Kanya Middle School Purnahiya No.4</v>
       </c>
       <c r="F41" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G41" t="str">
-        <v>9003000082</v>
+        <v>9003000044</v>
       </c>
       <c r="H41" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I41" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J41" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K41" t="str">
         <v>0303</v>
@@ -3592,7 +3616,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M41" t="str">
-        <v>30000649358</v>
+        <v>30000348436</v>
       </c>
       <c r="N41" t="str">
         <v>State Bank of India</v>
@@ -3601,30 +3625,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P41" t="str">
-        <v>SBIN0006350</v>
+        <v>SBIN0002977</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>0300002</v>
+        <v>0300018</v>
       </c>
       <c r="B42" t="str">
-        <v>RAKESH SAH</v>
+        <v>MD. SHAHID KUMAR</v>
       </c>
       <c r="C42" t="str">
-        <v>Lecturer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D42" t="str">
-        <v>03002</v>
+        <v>03017</v>
       </c>
       <c r="E42" t="str">
-        <v>High School Piprahi</v>
+        <v>District Agriculture Office Sheohar</v>
       </c>
       <c r="F42" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G42" t="str">
-        <v>9003000002</v>
+        <v>9003000018</v>
       </c>
       <c r="H42" t="str">
         <v>PRESIDING OFFICER</v>
@@ -3636,13 +3660,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K42" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L42" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M42" t="str">
-        <v>30000015838</v>
+        <v>30000142542</v>
       </c>
       <c r="N42" t="str">
         <v>State Bank of India</v>
@@ -3651,48 +3675,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P42" t="str">
-        <v>SBIN0002848</v>
+        <v>SBIN0007870</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>0300094</v>
+        <v>0300012</v>
       </c>
       <c r="B43" t="str">
-        <v>PRIYANKA RAI</v>
+        <v>POONAM PASWAN</v>
       </c>
       <c r="C43" t="str">
-        <v>Assistant Engineer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D43" t="str">
-        <v>03077</v>
+        <v>03012</v>
       </c>
       <c r="E43" t="str">
-        <v>Block Agriculture Office Tariyani</v>
+        <v>CDPO Office Sheohar No.1</v>
       </c>
       <c r="F43" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G43" t="str">
-        <v>9003000094</v>
+        <v>9003000012</v>
       </c>
       <c r="H43" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I43" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J43" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K43" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L43" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M43" t="str">
-        <v>30000744386</v>
+        <v>30000095028</v>
       </c>
       <c r="N43" t="str">
         <v>State Bank of India</v>
@@ -3701,48 +3725,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P43" t="str">
-        <v>SBIN0003963</v>
+        <v>SBIN0008782</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>0300067</v>
+        <v>0300068</v>
       </c>
       <c r="B44" t="str">
-        <v>VINOD KHATUN</v>
+        <v>VIJAY RAI</v>
       </c>
       <c r="C44" t="str">
-        <v>Teacher</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D44" t="str">
-        <v>03018</v>
+        <v>03061</v>
       </c>
       <c r="E44" t="str">
-        <v>Block Office Dumri Katsari No.4</v>
+        <v>High School Purnahiya No.4</v>
       </c>
       <c r="F44" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G44" t="str">
-        <v>9003000067</v>
+        <v>9003000068</v>
       </c>
       <c r="H44" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I44" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J44" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K44" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L44" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M44" t="str">
-        <v>30000530573</v>
+        <v>30000538492</v>
       </c>
       <c r="N44" t="str">
         <v>State Bank of India</v>
@@ -3751,48 +3775,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P44" t="str">
-        <v>SBIN0003378</v>
+        <v>SBIN0004043</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>0300017</v>
+        <v>0300060</v>
       </c>
       <c r="B45" t="str">
-        <v>SUNIL PRASAD</v>
+        <v>SUNITA PRASAD</v>
       </c>
       <c r="C45" t="str">
-        <v>Senior Teacher</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D45" t="str">
-        <v>03017</v>
+        <v>03056</v>
       </c>
       <c r="E45" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Block Agriculture Office Dumri Katsari No.3</v>
       </c>
       <c r="F45" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G45" t="str">
-        <v>9003000017</v>
+        <v>9003000060</v>
       </c>
       <c r="H45" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I45" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J45" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K45" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L45" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M45" t="str">
-        <v>30000134623</v>
+        <v>30000475140</v>
       </c>
       <c r="N45" t="str">
         <v>State Bank of India</v>
@@ -3801,48 +3825,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P45" t="str">
-        <v>SBIN0002029</v>
+        <v>SBIN0003171</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>0300114</v>
+        <v>0300047</v>
       </c>
       <c r="B46" t="str">
-        <v>MD. IRFAN CHAUDHARY</v>
+        <v>MD. IRFAN TIWARI</v>
       </c>
       <c r="C46" t="str">
-        <v>Branch Manager</v>
+        <v>Teacher</v>
       </c>
       <c r="D46" t="str">
-        <v>03091</v>
+        <v>03044</v>
       </c>
       <c r="E46" t="str">
-        <v>BSNL Exchange, Sheohar</v>
+        <v>High School Purnahiya</v>
       </c>
       <c r="F46" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G46" t="str">
-        <v>9003000114</v>
+        <v>9003000047</v>
       </c>
       <c r="H46" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I46" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="J46" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K46" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L46" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M46" t="str">
-        <v>30000902766</v>
+        <v>30000372193</v>
       </c>
       <c r="N46" t="str">
         <v>State Bank of India</v>
@@ -3851,48 +3875,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P46" t="str">
-        <v>SBIN0009498</v>
+        <v>SBIN0001932</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>0300121</v>
+        <v>0300028</v>
       </c>
       <c r="B47" t="str">
-        <v>MAMTA JHA</v>
+        <v>MAMTA SHARMA</v>
       </c>
       <c r="C47" t="str">
-        <v>Postmaster</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D47" t="str">
-        <v>03088</v>
+        <v>03027</v>
       </c>
       <c r="E47" t="str">
-        <v>Head Post Office, Purnahiya</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F47" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G47" t="str">
-        <v>9003000121</v>
+        <v>9003000028</v>
       </c>
       <c r="H47" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I47" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J47" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K47" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L47" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M47" t="str">
-        <v>30000958199</v>
+        <v>30000221732</v>
       </c>
       <c r="N47" t="str">
         <v>State Bank of India</v>
@@ -3901,39 +3925,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P47" t="str">
-        <v>SBIN0006366</v>
+        <v>SBIN0002862</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>0300048</v>
+        <v>0300038</v>
       </c>
       <c r="B48" t="str">
-        <v>RAJESH SAH</v>
+        <v>SAVITA PANDEY</v>
       </c>
       <c r="C48" t="str">
-        <v>Accountant</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D48" t="str">
-        <v>03041</v>
+        <v>03035</v>
       </c>
       <c r="E48" t="str">
-        <v>Panchayat Bhawan Piprahi</v>
+        <v>Primary School Piprahi</v>
       </c>
       <c r="F48" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G48" t="str">
-        <v>9003000048</v>
+        <v>9003000038</v>
       </c>
       <c r="H48" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I48" t="str">
-        <v>999999</v>
+        <v>0303</v>
       </c>
       <c r="J48" t="str">
-        <v>Others</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K48" t="str">
         <v>0302</v>
@@ -3942,7 +3966,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M48" t="str">
-        <v>30000380112</v>
+        <v>30000300922</v>
       </c>
       <c r="N48" t="str">
         <v>State Bank of India</v>
@@ -3951,48 +3975,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P48" t="str">
-        <v>SBIN0008245</v>
+        <v>SBIN0001695</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>0300088</v>
+        <v>0300116</v>
       </c>
       <c r="B49" t="str">
-        <v>RAKESH THAKUR</v>
+        <v>RAVI YADAV</v>
       </c>
       <c r="C49" t="str">
-        <v>Assistant Engineer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D49" t="str">
-        <v>03073</v>
+        <v>03089</v>
       </c>
       <c r="E49" t="str">
-        <v>Block Office Tariyani</v>
+        <v>Punjab National Bank, Sheohar</v>
       </c>
       <c r="F49" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G49" t="str">
-        <v>9003000088</v>
+        <v>9003000116</v>
       </c>
       <c r="H49" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I49" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J49" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K49" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L49" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M49" t="str">
-        <v>30000696872</v>
+        <v>30000918604</v>
       </c>
       <c r="N49" t="str">
         <v>State Bank of India</v>
@@ -4001,39 +4025,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P49" t="str">
-        <v>SBIN0005560</v>
+        <v>SBIN0002187</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>0300034</v>
+        <v>0300055</v>
       </c>
       <c r="B50" t="str">
-        <v>KIRAN VERMA</v>
+        <v>RINKU JHA</v>
       </c>
       <c r="C50" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Teacher</v>
       </c>
       <c r="D50" t="str">
-        <v>03032</v>
+        <v>03051</v>
       </c>
       <c r="E50" t="str">
-        <v>District Welfare Office Sheohar</v>
+        <v>Project Girls High School Sheohar</v>
       </c>
       <c r="F50" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G50" t="str">
-        <v>9003000034</v>
+        <v>9003000055</v>
       </c>
       <c r="H50" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I50" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J50" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K50" t="str">
         <v>0301</v>
@@ -4042,7 +4066,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M50" t="str">
-        <v>30000269246</v>
+        <v>30000435545</v>
       </c>
       <c r="N50" t="str">
         <v>State Bank of India</v>
@@ -4051,33 +4075,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P50" t="str">
-        <v>SBIN0003169</v>
+        <v>SBIN0005002</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>0300091</v>
+        <v>0300122</v>
       </c>
       <c r="B51" t="str">
-        <v>NIRMALA SAH</v>
+        <v>RINKU SINHA</v>
       </c>
       <c r="C51" t="str">
-        <v>Revenue Officer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D51" t="str">
-        <v>03075</v>
+        <v>03094</v>
       </c>
       <c r="E51" t="str">
-        <v>RWD Sub-Division Purnahiya</v>
+        <v>BSNL Exchange, Purnahiya</v>
       </c>
       <c r="F51" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G51" t="str">
-        <v>9003000091</v>
+        <v>9003000122</v>
       </c>
       <c r="H51" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I51" t="str">
         <v>0302</v>
@@ -4092,7 +4116,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M51" t="str">
-        <v>30000720629</v>
+        <v>30000966118</v>
       </c>
       <c r="N51" t="str">
         <v>State Bank of India</v>
@@ -4101,48 +4125,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P51" t="str">
-        <v>SBIN0001722</v>
+        <v>SBIN0003769</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>0300009</v>
+        <v>0300002</v>
       </c>
       <c r="B52" t="str">
-        <v>PRIYANKA ALAM</v>
+        <v>REKHA ALAM</v>
       </c>
       <c r="C52" t="str">
-        <v>Lecturer</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D52" t="str">
-        <v>03009</v>
+        <v>03002</v>
       </c>
       <c r="E52" t="str">
-        <v>High School Dumri Katsari</v>
+        <v>Block Education Office Piprahi</v>
       </c>
       <c r="F52" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G52" t="str">
-        <v>9003000009</v>
+        <v>9003000002</v>
       </c>
       <c r="H52" t="str">
         <v>PRESIDING OFFICER</v>
       </c>
       <c r="I52" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J52" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K52" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L52" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M52" t="str">
-        <v>30000071271</v>
+        <v>30000015838</v>
       </c>
       <c r="N52" t="str">
         <v>State Bank of India</v>
@@ -4151,48 +4175,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P52" t="str">
-        <v>SBIN0008749</v>
+        <v>SBIN0003858</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>0300052</v>
+        <v>0300003</v>
       </c>
       <c r="B53" t="str">
-        <v>ASHA RAM</v>
+        <v>NITISH SHARMA</v>
       </c>
       <c r="C53" t="str">
-        <v>Teacher</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D53" t="str">
-        <v>03045</v>
+        <v>03003</v>
       </c>
       <c r="E53" t="str">
-        <v>PHC Tariyani</v>
+        <v>Kanya Middle School Sheohar</v>
       </c>
       <c r="F53" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G53" t="str">
-        <v>9003000052</v>
+        <v>9003000003</v>
       </c>
       <c r="H53" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I53" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K53" t="str">
         <v>0301</v>
       </c>
-      <c r="J53" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K53" t="str">
-        <v>0305</v>
-      </c>
       <c r="L53" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M53" t="str">
-        <v>30000411788</v>
+        <v>30000023757</v>
       </c>
       <c r="N53" t="str">
         <v>State Bank of India</v>
@@ -4201,48 +4225,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P53" t="str">
-        <v>SBIN0008103</v>
+        <v>SBIN0002611</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>0300092</v>
+        <v>0300085</v>
       </c>
       <c r="B54" t="str">
-        <v>FARHAT SINHA</v>
+        <v>MAMTA DEVI</v>
       </c>
       <c r="C54" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D54" t="str">
-        <v>03076</v>
+        <v>03070</v>
       </c>
       <c r="E54" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>RWD Sub-Division Sheohar</v>
       </c>
       <c r="F54" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G54" t="str">
-        <v>9003000092</v>
+        <v>9003000085</v>
       </c>
       <c r="H54" t="str">
         <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I54" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J54" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K54" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L54" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M54" t="str">
-        <v>30000728548</v>
+        <v>30000673115</v>
       </c>
       <c r="N54" t="str">
         <v>State Bank of India</v>
@@ -4251,48 +4275,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P54" t="str">
-        <v>SBIN0002933</v>
+        <v>SBIN0007678</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>0300008</v>
+        <v>0300035</v>
       </c>
       <c r="B55" t="str">
-        <v>PRAMOD OJHA</v>
+        <v>AMIT SAH</v>
       </c>
       <c r="C55" t="str">
-        <v>Headmaster</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D55" t="str">
-        <v>03008</v>
+        <v>03032</v>
       </c>
       <c r="E55" t="str">
-        <v>Block Office Purnahiya No.3</v>
+        <v>Block Office Tariyani No.3</v>
       </c>
       <c r="F55" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G55" t="str">
-        <v>9003000008</v>
+        <v>9003000035</v>
       </c>
       <c r="H55" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I55" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J55" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K55" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L55" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M55" t="str">
-        <v>30000063352</v>
+        <v>30000277165</v>
       </c>
       <c r="N55" t="str">
         <v>State Bank of India</v>
@@ -4301,48 +4325,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P55" t="str">
-        <v>SBIN0003711</v>
+        <v>SBIN0009033</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>0300059</v>
+        <v>0300071</v>
       </c>
       <c r="B56" t="str">
-        <v>MD. SHAHID RAM</v>
+        <v>SUNIL MISHRA</v>
       </c>
       <c r="C56" t="str">
-        <v>Clerk</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D56" t="str">
-        <v>03051</v>
+        <v>03063</v>
       </c>
       <c r="E56" t="str">
-        <v>Block Office Sheohar No.1</v>
+        <v>Primary School Purnahiya No.2</v>
       </c>
       <c r="F56" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G56" t="str">
-        <v>9003000059</v>
+        <v>9003000071</v>
       </c>
       <c r="H56" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I56" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="K56" t="str">
         <v>0303</v>
       </c>
-      <c r="J56" t="str">
+      <c r="L56" t="str">
         <v>Purnahiya</v>
       </c>
-      <c r="K56" t="str">
-        <v>0301</v>
-      </c>
-      <c r="L56" t="str">
-        <v>Sheohar</v>
-      </c>
       <c r="M56" t="str">
-        <v>30000467221</v>
+        <v>30000562249</v>
       </c>
       <c r="N56" t="str">
         <v>State Bank of India</v>
@@ -4351,48 +4375,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P56" t="str">
-        <v>SBIN0004755</v>
+        <v>SBIN0005428</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>0300022</v>
+        <v>0300001</v>
       </c>
       <c r="B57" t="str">
-        <v>NASREEN MISHRA</v>
+        <v>SANTOSH THAKUR</v>
       </c>
       <c r="C57" t="str">
-        <v>Assistant Teacher</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D57" t="str">
-        <v>03021</v>
+        <v>03001</v>
       </c>
       <c r="E57" t="str">
-        <v>CDPO Office Piprahi No.1</v>
+        <v>High School Sheohar No.2</v>
       </c>
       <c r="F57" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G57" t="str">
-        <v>9003000022</v>
+        <v>9003000001</v>
       </c>
       <c r="H57" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I57" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J57" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K57" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L57" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M57" t="str">
-        <v>30000174218</v>
+        <v>30000007919</v>
       </c>
       <c r="N57" t="str">
         <v>State Bank of India</v>
@@ -4401,33 +4425,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P57" t="str">
-        <v>SBIN0003676</v>
+        <v>SBIN0001303</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>0300013</v>
+        <v>0300064</v>
       </c>
       <c r="B58" t="str">
-        <v>RAKESH KHATUN</v>
+        <v>DINESH RAM</v>
       </c>
       <c r="C58" t="str">
-        <v>Assistant Engineer</v>
+        <v>Teacher</v>
       </c>
       <c r="D58" t="str">
-        <v>03013</v>
+        <v>03058</v>
       </c>
       <c r="E58" t="str">
-        <v>Panchayat Bhawan Sheohar No.1</v>
+        <v>Block Education Office Sheohar No.1</v>
       </c>
       <c r="F58" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G58" t="str">
-        <v>9003000013</v>
+        <v>9003000064</v>
       </c>
       <c r="H58" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I58" t="str">
         <v>0301</v>
@@ -4442,7 +4466,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M58" t="str">
-        <v>30000102947</v>
+        <v>30000506816</v>
       </c>
       <c r="N58" t="str">
         <v>State Bank of India</v>
@@ -4451,48 +4475,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P58" t="str">
-        <v>SBIN0003797</v>
+        <v>SBIN0008614</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>0300101</v>
+        <v>0300021</v>
       </c>
       <c r="B59" t="str">
-        <v>PRAMOD PRASAD</v>
+        <v>SUNIL THAKUR</v>
       </c>
       <c r="C59" t="str">
-        <v>Junior Engineer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D59" t="str">
-        <v>03081</v>
+        <v>03020</v>
       </c>
       <c r="E59" t="str">
-        <v>Block Agriculture Office Sheohar</v>
+        <v>High School Piprahi No.3</v>
       </c>
       <c r="F59" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G59" t="str">
-        <v>9003000101</v>
+        <v>9003000021</v>
       </c>
       <c r="H59" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I59" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J59" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K59" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L59" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M59" t="str">
-        <v>30000799819</v>
+        <v>30000166299</v>
       </c>
       <c r="N59" t="str">
         <v>State Bank of India</v>
@@ -4501,30 +4525,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P59" t="str">
-        <v>SBIN0009804</v>
+        <v>SBIN0003633</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>0300058</v>
+        <v>0300062</v>
       </c>
       <c r="B60" t="str">
-        <v>KUMARI ANJALI PANDEY A</v>
+        <v>AMIT SHARMA</v>
       </c>
       <c r="C60" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Accountant</v>
       </c>
       <c r="D60" t="str">
-        <v>03050</v>
+        <v>03057</v>
       </c>
       <c r="E60" t="str">
-        <v>Block Education Office Dumri Katsari</v>
+        <v>Block Education Office Piprahi No.1</v>
       </c>
       <c r="F60" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G60" t="str">
-        <v>9003000058</v>
+        <v>9003000062</v>
       </c>
       <c r="H60" t="str">
         <v>POLLING OFFICER-2</v>
@@ -4536,13 +4560,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K60" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L60" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M60" t="str">
-        <v>30000459302</v>
+        <v>30000490978</v>
       </c>
       <c r="N60" t="str">
         <v>State Bank of India</v>
@@ -4551,48 +4575,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P60" t="str">
-        <v>SBIN0008091</v>
+        <v>SBIN0005926</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>0300023</v>
+        <v>0300109</v>
       </c>
       <c r="B61" t="str">
-        <v>SANJAY PANDEY</v>
+        <v>SANJAY ALAM</v>
       </c>
       <c r="C61" t="str">
-        <v>Head Clerk</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D61" t="str">
-        <v>03022</v>
+        <v>03084</v>
       </c>
       <c r="E61" t="str">
-        <v>Panchayat Bhawan Tariyani</v>
+        <v>Head Post Office, Piprahi</v>
       </c>
       <c r="F61" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G61" t="str">
-        <v>9003000023</v>
+        <v>9003000109</v>
       </c>
       <c r="H61" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I61" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J61" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K61" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="L61" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="M61" t="str">
-        <v>30000182137</v>
+        <v>30000863171</v>
       </c>
       <c r="N61" t="str">
         <v>State Bank of India</v>
@@ -4601,48 +4625,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P61" t="str">
-        <v>SBIN0005747</v>
+        <v>SBIN0007274</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>0300049</v>
+        <v>0300113</v>
       </c>
       <c r="B62" t="str">
-        <v>RAJESH CHAUDHARY</v>
+        <v>SANJAY VERMA</v>
       </c>
       <c r="C62" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D62" t="str">
-        <v>03042</v>
+        <v>03087</v>
       </c>
       <c r="E62" t="str">
-        <v>District Education Office Sheohar</v>
+        <v>Bank of India, Tariyani</v>
       </c>
       <c r="F62" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G62" t="str">
-        <v>9003000049</v>
+        <v>9003000113</v>
       </c>
       <c r="H62" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I62" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J62" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K62" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L62" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M62" t="str">
-        <v>30000388031</v>
+        <v>30000894847</v>
       </c>
       <c r="N62" t="str">
         <v>State Bank of India</v>
@@ -4651,39 +4675,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P62" t="str">
-        <v>SBIN0002886</v>
+        <v>SBIN0003492</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>0300037</v>
+        <v>0300101</v>
       </c>
       <c r="B63" t="str">
-        <v>ASHA MAHTO</v>
+        <v>MAHESH VERMA</v>
       </c>
       <c r="C63" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D63" t="str">
-        <v>03005</v>
+        <v>03078</v>
       </c>
       <c r="E63" t="str">
-        <v>Middle School Dumri Katsari No.4</v>
+        <v>RWD Sub-Division Dumri Katsari</v>
       </c>
       <c r="F63" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G63" t="str">
-        <v>9003000037</v>
+        <v>9003000101</v>
       </c>
       <c r="H63" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I63" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="J63" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K63" t="str">
         <v>0304</v>
@@ -4692,7 +4716,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M63" t="str">
-        <v>30000293003</v>
+        <v>30000799819</v>
       </c>
       <c r="N63" t="str">
         <v>State Bank of India</v>
@@ -4701,48 +4725,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P63" t="str">
-        <v>SBIN0001456</v>
+        <v>SBIN0001267</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>0300016</v>
+        <v>0300110</v>
       </c>
       <c r="B64" t="str">
-        <v>MAHESH CHAUDHARY</v>
+        <v>PRAMOD KUMAR</v>
       </c>
       <c r="C64" t="str">
-        <v>Assistant Engineer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D64" t="str">
-        <v>03016</v>
+        <v>03085</v>
       </c>
       <c r="E64" t="str">
-        <v>CDPO Office Tariyani No.1</v>
+        <v>Central Bank of India, Sheohar</v>
       </c>
       <c r="F64" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G64" t="str">
-        <v>9003000016</v>
+        <v>9003000110</v>
       </c>
       <c r="H64" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I64" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J64" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K64" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L64" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M64" t="str">
-        <v>30000126704</v>
+        <v>30000871090</v>
       </c>
       <c r="N64" t="str">
         <v>State Bank of India</v>
@@ -4751,48 +4775,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P64" t="str">
-        <v>SBIN0007559</v>
+        <v>SBIN0005546</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>0300065</v>
+        <v>0300061</v>
       </c>
       <c r="B65" t="str">
-        <v>ALOK GUPTA</v>
+        <v>SANJAY SAH</v>
       </c>
       <c r="C65" t="str">
         <v>Clerk</v>
       </c>
       <c r="D65" t="str">
-        <v>03057</v>
+        <v>03008</v>
       </c>
       <c r="E65" t="str">
-        <v>Project Girls High School Dumri Katsari</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F65" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G65" t="str">
-        <v>9003000065</v>
+        <v>9003000061</v>
       </c>
       <c r="H65" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I65" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="J65" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="K65" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L65" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M65" t="str">
-        <v>30000514735</v>
+        <v>30000483059</v>
       </c>
       <c r="N65" t="str">
         <v>State Bank of India</v>
@@ -4801,48 +4825,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P65" t="str">
-        <v>SBIN0004918</v>
+        <v>SBIN0008567</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>0300093</v>
+        <v>0300039</v>
       </c>
       <c r="B66" t="str">
-        <v>MD. SHAHID PASWAN</v>
+        <v>MUKESH PRASAD</v>
       </c>
       <c r="C66" t="str">
-        <v>Labour Enforcement Officer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D66" t="str">
-        <v>03066</v>
+        <v>03036</v>
       </c>
       <c r="E66" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>Circle Office Dumri Katsari</v>
       </c>
       <c r="F66" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G66" t="str">
-        <v>9003000093</v>
+        <v>9003000039</v>
       </c>
       <c r="H66" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I66" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J66" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K66" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L66" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M66" t="str">
-        <v>30000736467</v>
+        <v>30000308841</v>
       </c>
       <c r="N66" t="str">
         <v>State Bank of India</v>
@@ -4851,39 +4875,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P66" t="str">
-        <v>SBIN0003954</v>
+        <v>SBIN0005231</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>0300031</v>
+        <v>0300048</v>
       </c>
       <c r="B67" t="str">
-        <v>RAKESH JHA</v>
+        <v>NEHA GUPTA</v>
       </c>
       <c r="C67" t="str">
-        <v>Assistant Teacher</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D67" t="str">
-        <v>03012</v>
+        <v>03045</v>
       </c>
       <c r="E67" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>Project Girls High School Purnahiya No.2</v>
       </c>
       <c r="F67" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G67" t="str">
-        <v>9003000031</v>
+        <v>9003000048</v>
       </c>
       <c r="H67" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I67" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J67" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K67" t="str">
         <v>0303</v>
@@ -4892,7 +4916,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M67" t="str">
-        <v>30000245489</v>
+        <v>30000380112</v>
       </c>
       <c r="N67" t="str">
         <v>State Bank of India</v>
@@ -4901,48 +4925,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P67" t="str">
-        <v>SBIN0009843</v>
+        <v>SBIN0004239</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>0300011</v>
+        <v>0300086</v>
       </c>
       <c r="B68" t="str">
-        <v>SANTOSH CHAUDHARY</v>
+        <v>RANJIT KHATUN</v>
       </c>
       <c r="C68" t="str">
-        <v>Headmaster</v>
+        <v>Labour Enforcement Officer</v>
       </c>
       <c r="D68" t="str">
-        <v>03011</v>
+        <v>03071</v>
       </c>
       <c r="E68" t="str">
-        <v>CDPO Office Purnahiya</v>
+        <v>Block Office Tariyani</v>
       </c>
       <c r="F68" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G68" t="str">
-        <v>9003000011</v>
+        <v>9003000086</v>
       </c>
       <c r="H68" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I68" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J68" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K68" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L68" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M68" t="str">
-        <v>30000087109</v>
+        <v>30000681034</v>
       </c>
       <c r="N68" t="str">
         <v>State Bank of India</v>
@@ -4951,48 +4975,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P68" t="str">
-        <v>SBIN0007665</v>
+        <v>SBIN0001010</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>0300111</v>
+        <v>0300123</v>
       </c>
       <c r="B69" t="str">
-        <v>NEHA MISHRA</v>
+        <v>AMIT SHARMA K</v>
       </c>
       <c r="C69" t="str">
-        <v>Administrative Officer</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D69" t="str">
-        <v>03088</v>
+        <v>03095</v>
       </c>
       <c r="E69" t="str">
-        <v>Head Post Office, Purnahiya</v>
+        <v>State Bank of India, Dumri Katsari</v>
       </c>
       <c r="F69" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G69" t="str">
-        <v>9003000111</v>
+        <v>9003000123</v>
       </c>
       <c r="H69" t="str">
         <v>MICRO OBSERVER</v>
       </c>
       <c r="I69" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J69" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K69" t="str">
-        <v>0303</v>
+        <v>0304</v>
       </c>
       <c r="L69" t="str">
-        <v>Purnahiya</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M69" t="str">
-        <v>30000879009</v>
+        <v>30000974037</v>
       </c>
       <c r="N69" t="str">
         <v>State Bank of India</v>
@@ -5001,48 +5025,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P69" t="str">
-        <v>SBIN0008716</v>
+        <v>SBIN0009955</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>0300122</v>
+        <v>0300004</v>
       </c>
       <c r="B70" t="str">
-        <v>ANIL YADAV</v>
+        <v>RAMESH SINGH</v>
       </c>
       <c r="C70" t="str">
-        <v>Branch Manager</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D70" t="str">
-        <v>03093</v>
+        <v>03004</v>
       </c>
       <c r="E70" t="str">
-        <v>Head Post Office, Tariyani</v>
+        <v>Panchayat Bhawan Sheohar</v>
       </c>
       <c r="F70" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G70" t="str">
-        <v>9003000122</v>
+        <v>9003000004</v>
       </c>
       <c r="H70" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I70" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J70" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K70" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L70" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M70" t="str">
-        <v>30000966118</v>
+        <v>30000031676</v>
       </c>
       <c r="N70" t="str">
         <v>State Bank of India</v>
@@ -5051,48 +5075,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P70" t="str">
-        <v>SBIN0004445</v>
+        <v>SBIN0005023</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>0300072</v>
+        <v>0300030</v>
       </c>
       <c r="B71" t="str">
-        <v>RANJIT MISHRA</v>
+        <v>RAJESH SINHA</v>
       </c>
       <c r="C71" t="str">
-        <v>Office Assistant</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D71" t="str">
-        <v>03062</v>
+        <v>03027</v>
       </c>
       <c r="E71" t="str">
-        <v>Project Girls High School Purnahiya</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F71" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G71" t="str">
-        <v>9003000072</v>
+        <v>9003000030</v>
       </c>
       <c r="H71" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I71" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J71" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K71" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L71" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M71" t="str">
-        <v>30000570168</v>
+        <v>30000237570</v>
       </c>
       <c r="N71" t="str">
         <v>State Bank of India</v>
@@ -5101,48 +5125,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P71" t="str">
-        <v>SBIN0002020</v>
+        <v>SBIN0005481</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>0300124</v>
+        <v>0300027</v>
       </c>
       <c r="B72" t="str">
-        <v>DINESH RAI</v>
+        <v>SANTOSH PANDEY</v>
       </c>
       <c r="C72" t="str">
-        <v>Assistant Manager</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D72" t="str">
-        <v>03093</v>
+        <v>03026</v>
       </c>
       <c r="E72" t="str">
-        <v>Head Post Office, Tariyani</v>
+        <v>Middle School Purnahiya</v>
       </c>
       <c r="F72" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G72" t="str">
-        <v>9003000124</v>
+        <v>9003000027</v>
       </c>
       <c r="H72" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I72" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J72" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K72" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="L72" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M72" t="str">
-        <v>30000981956</v>
+        <v>30000213813</v>
       </c>
       <c r="N72" t="str">
         <v>State Bank of India</v>
@@ -5151,48 +5175,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P72" t="str">
-        <v>SBIN0002904</v>
+        <v>SBIN0001140</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>0300083</v>
+        <v>0300125</v>
       </c>
       <c r="B73" t="str">
-        <v>SANTOSH KUMAR</v>
+        <v>PRAMOD SAH T</v>
       </c>
       <c r="C73" t="str">
-        <v>Teacher</v>
+        <v>Branch Manager</v>
       </c>
       <c r="D73" t="str">
-        <v>03055</v>
+        <v>03083</v>
       </c>
       <c r="E73" t="str">
-        <v>Collectorate (deputed from other district)</v>
+        <v>Bank of India, Dumri Katsari</v>
       </c>
       <c r="F73" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G73" t="str">
-        <v>9003000083</v>
+        <v>9003000125</v>
       </c>
       <c r="H73" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I73" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J73" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K73" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="L73" t="str">
-        <v>Other District</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M73" t="str">
-        <v>30000657277</v>
+        <v>30000989875</v>
       </c>
       <c r="N73" t="str">
         <v>State Bank of India</v>
@@ -5201,48 +5225,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P73" t="str">
-        <v>SBIN0008489</v>
+        <v>SBIN0004040</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>0300056</v>
+        <v>0300057</v>
       </c>
       <c r="B74" t="str">
-        <v>NIRMALA KUMAR</v>
+        <v>MAHESH SINHA</v>
       </c>
       <c r="C74" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Teacher</v>
       </c>
       <c r="D74" t="str">
-        <v>03048</v>
+        <v>03053</v>
       </c>
       <c r="E74" t="str">
-        <v>CDPO Office Dumri Katsari No.4</v>
+        <v>Primary School Tariyani</v>
       </c>
       <c r="F74" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G74" t="str">
-        <v>9003000056</v>
+        <v>9003000057</v>
       </c>
       <c r="H74" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I74" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J74" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K74" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L74" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M74" t="str">
-        <v>30000443464</v>
+        <v>30000451383</v>
       </c>
       <c r="N74" t="str">
         <v>State Bank of India</v>
@@ -5251,48 +5275,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P74" t="str">
-        <v>SBIN0007488</v>
+        <v>SBIN0001318</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>0300108</v>
+        <v>0300100</v>
       </c>
       <c r="B75" t="str">
-        <v>SAVITA GUPTA</v>
+        <v>RANJIT THAKUR</v>
       </c>
       <c r="C75" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D75" t="str">
-        <v>03084</v>
+        <v>03072</v>
       </c>
       <c r="E75" t="str">
-        <v>LIC Branch Office, Dumri Katsari</v>
+        <v>Circle Office Piprahi</v>
       </c>
       <c r="F75" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G75" t="str">
-        <v>9003000108</v>
+        <v>9003000100</v>
       </c>
       <c r="H75" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I75" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="J75" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="K75" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="L75" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="M75" t="str">
-        <v>30000855252</v>
+        <v>30000791900</v>
       </c>
       <c r="N75" t="str">
         <v>State Bank of India</v>
@@ -5301,48 +5325,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P75" t="str">
-        <v>SBIN0008507</v>
+        <v>SBIN0003522</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>0300087</v>
+        <v>0300006</v>
       </c>
       <c r="B76" t="str">
-        <v>NEHA TIWARI</v>
+        <v>SANTOSH SINHA</v>
       </c>
       <c r="C76" t="str">
-        <v>Block Panchayat Raj Officer</v>
+        <v>Lecturer</v>
       </c>
       <c r="D76" t="str">
-        <v>03072</v>
+        <v>03006</v>
       </c>
       <c r="E76" t="str">
-        <v>RWD Sub-Division Sheohar</v>
+        <v>Primary School Piprahi No.2</v>
       </c>
       <c r="F76" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G76" t="str">
-        <v>9003000087</v>
+        <v>9003000006</v>
       </c>
       <c r="H76" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I76" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J76" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K76" t="str">
-        <v>0301</v>
+        <v>0302</v>
       </c>
       <c r="L76" t="str">
-        <v>Sheohar</v>
+        <v>Piprahi</v>
       </c>
       <c r="M76" t="str">
-        <v>30000688953</v>
+        <v>30000047514</v>
       </c>
       <c r="N76" t="str">
         <v>State Bank of India</v>
@@ -5351,33 +5375,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P76" t="str">
-        <v>SBIN0001423</v>
+        <v>SBIN0001936</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>0300012</v>
+        <v>0300083</v>
       </c>
       <c r="B77" t="str">
-        <v>NIRMALA SINHA</v>
+        <v>VIJAY DEVI</v>
       </c>
       <c r="C77" t="str">
-        <v>Section Officer</v>
+        <v>Clerk</v>
       </c>
       <c r="D77" t="str">
-        <v>03012</v>
+        <v>03069</v>
       </c>
       <c r="E77" t="str">
-        <v>Block Agriculture Office Purnahiya</v>
+        <v>Primary School Purnahiya No.1</v>
       </c>
       <c r="F77" t="str">
         <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G77" t="str">
-        <v>9003000012</v>
+        <v>9003000083</v>
       </c>
       <c r="H77" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I77" t="str">
         <v>999999</v>
@@ -5392,7 +5416,7 @@
         <v>Purnahiya</v>
       </c>
       <c r="M77" t="str">
-        <v>30000095028</v>
+        <v>30000657277</v>
       </c>
       <c r="N77" t="str">
         <v>State Bank of India</v>
@@ -5401,39 +5425,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P77" t="str">
-        <v>SBIN0003812</v>
+        <v>SBIN0003657</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>0300125</v>
+        <v>0300023</v>
       </c>
       <c r="B78" t="str">
-        <v>ANITA SHARMA</v>
+        <v>AMIT KHATUN</v>
       </c>
       <c r="C78" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Assistant Teacher</v>
       </c>
       <c r="D78" t="str">
-        <v>03097</v>
+        <v>03022</v>
       </c>
       <c r="E78" t="str">
-        <v>UCO Bank, Sheohar</v>
+        <v>Primary School Sheohar</v>
       </c>
       <c r="F78" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G78" t="str">
-        <v>9003000125</v>
+        <v>9003000023</v>
       </c>
       <c r="H78" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I78" t="str">
-        <v>999999</v>
+        <v>0301</v>
       </c>
       <c r="J78" t="str">
-        <v>Others</v>
+        <v>Sheohar</v>
       </c>
       <c r="K78" t="str">
         <v>0301</v>
@@ -5442,7 +5466,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M78" t="str">
-        <v>30000989875</v>
+        <v>30000182137</v>
       </c>
       <c r="N78" t="str">
         <v>State Bank of India</v>
@@ -5451,48 +5475,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P78" t="str">
-        <v>SBIN0006105</v>
+        <v>SBIN0008935</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>0300025</v>
+        <v>0300114</v>
       </c>
       <c r="B79" t="str">
-        <v>NASREEN ALAM</v>
+        <v>MAMTA SINHA</v>
       </c>
       <c r="C79" t="str">
-        <v>Senior Clerk</v>
+        <v>Sub Divisional Engineer</v>
       </c>
       <c r="D79" t="str">
-        <v>03024</v>
+        <v>03088</v>
       </c>
       <c r="E79" t="str">
-        <v>Civil Surgeon Office Sheohar</v>
+        <v>Central Bank of India, Dumri Katsari</v>
       </c>
       <c r="F79" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G79" t="str">
-        <v>9003000025</v>
+        <v>9003000114</v>
       </c>
       <c r="H79" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I79" t="str">
-        <v>0301</v>
+        <v>999999</v>
       </c>
       <c r="J79" t="str">
-        <v>Sheohar</v>
+        <v>Others</v>
       </c>
       <c r="K79" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L79" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M79" t="str">
-        <v>30000197975</v>
+        <v>30000902766</v>
       </c>
       <c r="N79" t="str">
         <v>State Bank of India</v>
@@ -5501,48 +5525,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P79" t="str">
-        <v>SBIN0004404</v>
+        <v>SBIN0006971</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>0300003</v>
+        <v>0300077</v>
       </c>
       <c r="B80" t="str">
-        <v>ANITA JHA</v>
+        <v>NASREEN PASWAN</v>
       </c>
       <c r="C80" t="str">
-        <v>Lecturer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D80" t="str">
-        <v>03003</v>
+        <v>03067</v>
       </c>
       <c r="E80" t="str">
-        <v>Panchayat Bhawan Piprahi No.4</v>
+        <v>Primary School Purnahiya</v>
       </c>
       <c r="F80" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G80" t="str">
-        <v>9003000003</v>
+        <v>9003000077</v>
       </c>
       <c r="H80" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I80" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="J80" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K80" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L80" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M80" t="str">
-        <v>30000023757</v>
+        <v>30000609763</v>
       </c>
       <c r="N80" t="str">
         <v>State Bank of India</v>
@@ -5551,39 +5575,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P80" t="str">
-        <v>SBIN0002193</v>
+        <v>SBIN0002165</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>0300039</v>
+        <v>0300096</v>
       </c>
       <c r="B81" t="str">
-        <v>RAKESH SINGH</v>
+        <v>ARVIND GUPTA</v>
       </c>
       <c r="C81" t="str">
-        <v>Assistant Teacher</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D81" t="str">
-        <v>03017</v>
+        <v>03075</v>
       </c>
       <c r="E81" t="str">
-        <v>District Agriculture Office Sheohar</v>
+        <v>Minor Irrigation Office Sheohar</v>
       </c>
       <c r="F81" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G81" t="str">
-        <v>9003000039</v>
+        <v>9003000096</v>
       </c>
       <c r="H81" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I81" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J81" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K81" t="str">
         <v>0301</v>
@@ -5592,7 +5616,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M81" t="str">
-        <v>30000308841</v>
+        <v>30000760224</v>
       </c>
       <c r="N81" t="str">
         <v>State Bank of India</v>
@@ -5601,33 +5625,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P81" t="str">
-        <v>SBIN0009029</v>
+        <v>SBIN0003836</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>0300026</v>
+        <v>0300124</v>
       </c>
       <c r="B82" t="str">
-        <v>NEHA PANDEY</v>
+        <v>DINESH SINHA</v>
       </c>
       <c r="C82" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D82" t="str">
-        <v>03025</v>
+        <v>03081</v>
       </c>
       <c r="E82" t="str">
-        <v>PHC Tariyani No.2</v>
+        <v>LIC Branch Office, Sheohar</v>
       </c>
       <c r="F82" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G82" t="str">
-        <v>9003000026</v>
+        <v>9003000124</v>
       </c>
       <c r="H82" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I82" t="str">
         <v>0301</v>
@@ -5636,13 +5660,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K82" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L82" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M82" t="str">
-        <v>30000205894</v>
+        <v>30000981956</v>
       </c>
       <c r="N82" t="str">
         <v>State Bank of India</v>
@@ -5651,33 +5675,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P82" t="str">
-        <v>SBIN0007961</v>
+        <v>SBIN0005388</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>0300090</v>
+        <v>0300069</v>
       </c>
       <c r="B83" t="str">
-        <v>PRAMOD SINHA</v>
+        <v>PRIYANKA PANDEY</v>
       </c>
       <c r="C83" t="str">
-        <v>Assistant Engineer</v>
+        <v>Teacher</v>
       </c>
       <c r="D83" t="str">
-        <v>03071</v>
+        <v>03026</v>
       </c>
       <c r="E83" t="str">
-        <v>Circle Office Sheohar</v>
+        <v>Middle School Purnahiya</v>
       </c>
       <c r="F83" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G83" t="str">
-        <v>9003000090</v>
+        <v>9003000069</v>
       </c>
       <c r="H83" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I83" t="str">
         <v>0303</v>
@@ -5686,13 +5710,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K83" t="str">
-        <v>0301</v>
+        <v>0303</v>
       </c>
       <c r="L83" t="str">
-        <v>Sheohar</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M83" t="str">
-        <v>30000712710</v>
+        <v>30000546411</v>
       </c>
       <c r="N83" t="str">
         <v>State Bank of India</v>
@@ -5701,48 +5725,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P83" t="str">
-        <v>SBIN0009975</v>
+        <v>SBIN0004221</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>0300019</v>
+        <v>0300106</v>
       </c>
       <c r="B84" t="str">
-        <v>VIJAY OJHA</v>
+        <v>NEHA RAI</v>
       </c>
       <c r="C84" t="str">
-        <v>Assistant Engineer</v>
+        <v>Assistant Manager</v>
       </c>
       <c r="D84" t="str">
-        <v>03019</v>
+        <v>03081</v>
       </c>
       <c r="E84" t="str">
-        <v>Block Education Office Piprahi No.3</v>
+        <v>LIC Branch Office, Sheohar</v>
       </c>
       <c r="F84" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G84" t="str">
-        <v>9003000019</v>
+        <v>9003000106</v>
       </c>
       <c r="H84" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I84" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J84" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K84" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L84" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M84" t="str">
-        <v>30000150461</v>
+        <v>30000839414</v>
       </c>
       <c r="N84" t="str">
         <v>State Bank of India</v>
@@ -5751,48 +5775,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P84" t="str">
-        <v>SBIN0005080</v>
+        <v>SBIN0006751</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>0300112</v>
+        <v>0300013</v>
       </c>
       <c r="B85" t="str">
-        <v>RAJESH RAM</v>
+        <v>SUNITA ALAM</v>
       </c>
       <c r="C85" t="str">
-        <v>Branch Manager</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D85" t="str">
-        <v>03089</v>
+        <v>03008</v>
       </c>
       <c r="E85" t="str">
-        <v>UCO Bank, Tariyani</v>
+        <v>District Welfare Office Sheohar</v>
       </c>
       <c r="F85" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G85" t="str">
-        <v>9003000112</v>
+        <v>9003000013</v>
       </c>
       <c r="H85" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I85" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J85" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K85" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L85" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M85" t="str">
-        <v>30000886928</v>
+        <v>30000102947</v>
       </c>
       <c r="N85" t="str">
         <v>State Bank of India</v>
@@ -5801,48 +5825,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P85" t="str">
-        <v>SBIN0006645</v>
+        <v>SBIN0005013</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>0300027</v>
+        <v>0300042</v>
       </c>
       <c r="B86" t="str">
-        <v>ANIL PRASAD</v>
+        <v>MD. IRFAN PASWAN</v>
       </c>
       <c r="C86" t="str">
-        <v>Head Clerk</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D86" t="str">
-        <v>03026</v>
+        <v>03039</v>
       </c>
       <c r="E86" t="str">
-        <v>Primary School Piprahi</v>
+        <v>Kanya Middle School Sheohar No.3</v>
       </c>
       <c r="F86" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G86" t="str">
-        <v>9003000027</v>
+        <v>9003000042</v>
       </c>
       <c r="H86" t="str">
         <v>POLLING OFFICER-1</v>
       </c>
       <c r="I86" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J86" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K86" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L86" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M86" t="str">
-        <v>30000213813</v>
+        <v>30000332598</v>
       </c>
       <c r="N86" t="str">
         <v>State Bank of India</v>
@@ -5851,48 +5875,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P86" t="str">
-        <v>SBIN0008679</v>
+        <v>SBIN0009688</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>0300070</v>
+        <v>0300082</v>
       </c>
       <c r="B87" t="str">
-        <v>RAKESH OJHA</v>
+        <v>ANITA PASWAN</v>
       </c>
       <c r="C87" t="str">
-        <v>Teacher</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D87" t="str">
-        <v>03061</v>
+        <v>03053</v>
       </c>
       <c r="E87" t="str">
-        <v>RWD Division Sheohar</v>
+        <v>Primary School Tariyani</v>
       </c>
       <c r="F87" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G87" t="str">
-        <v>9003000070</v>
+        <v>9003000082</v>
       </c>
       <c r="H87" t="str">
         <v>POLLING OFFICER-3</v>
       </c>
       <c r="I87" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J87" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K87" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L87" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M87" t="str">
-        <v>30000554330</v>
+        <v>30000649358</v>
       </c>
       <c r="N87" t="str">
         <v>State Bank of India</v>
@@ -5901,33 +5925,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P87" t="str">
-        <v>SBIN0004789</v>
+        <v>SBIN0004370</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>0300075</v>
+        <v>0300026</v>
       </c>
       <c r="B88" t="str">
-        <v>RANJIT ALAM</v>
+        <v>SURESH VERMA</v>
       </c>
       <c r="C88" t="str">
-        <v>Office Assistant</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D88" t="str">
-        <v>03063</v>
+        <v>03025</v>
       </c>
       <c r="E88" t="str">
-        <v>Block Office Sheohar No.2</v>
+        <v>PHC Dumri Katsari</v>
       </c>
       <c r="F88" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G88" t="str">
-        <v>9003000075</v>
+        <v>9003000026</v>
       </c>
       <c r="H88" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I88" t="str">
         <v>0301</v>
@@ -5936,13 +5960,13 @@
         <v>Sheohar</v>
       </c>
       <c r="K88" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L88" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M88" t="str">
-        <v>30000593925</v>
+        <v>30000205894</v>
       </c>
       <c r="N88" t="str">
         <v>State Bank of India</v>
@@ -5951,48 +5975,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P88" t="str">
-        <v>SBIN0006389</v>
+        <v>SBIN0009814</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>0300071</v>
+        <v>0300052</v>
       </c>
       <c r="B89" t="str">
-        <v>MANOJ CHAUDHARY</v>
+        <v>MD. IRFAN KUMAR</v>
       </c>
       <c r="C89" t="str">
-        <v>Teacher</v>
+        <v>Accountant</v>
       </c>
       <c r="D89" t="str">
-        <v>03055</v>
+        <v>03049</v>
       </c>
       <c r="E89" t="str">
-        <v>Collectorate (deputed from other district)</v>
+        <v>Panchayat Bhawan Dumri Katsari No.2</v>
       </c>
       <c r="F89" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G89" t="str">
-        <v>9003000071</v>
+        <v>9003000052</v>
       </c>
       <c r="H89" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I89" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="J89" t="str">
-        <v>Piprahi</v>
+        <v>Others</v>
       </c>
       <c r="K89" t="str">
-        <v>999999</v>
+        <v>0304</v>
       </c>
       <c r="L89" t="str">
-        <v>Other District</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M89" t="str">
-        <v>30000562249</v>
+        <v>30000411788</v>
       </c>
       <c r="N89" t="str">
         <v>State Bank of India</v>
@@ -6001,48 +6025,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P89" t="str">
-        <v>SBIN0003465</v>
+        <v>SBIN0004661</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>0300081</v>
+        <v>0300010</v>
       </c>
       <c r="B90" t="str">
-        <v>RAVI CHAUDHARY</v>
+        <v>SHAILESH SHARMA</v>
       </c>
       <c r="C90" t="str">
-        <v>Office Assistant</v>
+        <v>Senior Teacher</v>
       </c>
       <c r="D90" t="str">
-        <v>03048</v>
+        <v>03010</v>
       </c>
       <c r="E90" t="str">
-        <v>CDPO Office Dumri Katsari No.4</v>
+        <v>PHED Division Sheohar</v>
       </c>
       <c r="F90" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G90" t="str">
-        <v>9003000081</v>
+        <v>9003000010</v>
       </c>
       <c r="H90" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I90" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J90" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K90" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L90" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M90" t="str">
-        <v>30000641439</v>
+        <v>30000079190</v>
       </c>
       <c r="N90" t="str">
         <v>State Bank of India</v>
@@ -6051,48 +6075,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P90" t="str">
-        <v>SBIN0004454</v>
+        <v>SBIN0005237</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>0300041</v>
+        <v>0300019</v>
       </c>
       <c r="B91" t="str">
-        <v>PRAMOD OJHA P</v>
+        <v>PRIYANKA TIWARI</v>
       </c>
       <c r="C91" t="str">
-        <v>Panchayat Secretary</v>
+        <v>Headmaster</v>
       </c>
       <c r="D91" t="str">
-        <v>03035</v>
+        <v>03018</v>
       </c>
       <c r="E91" t="str">
-        <v>Project Girls High School Piprahi</v>
+        <v>Block Office Sheohar No.4</v>
       </c>
       <c r="F91" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G91" t="str">
-        <v>9003000041</v>
+        <v>9003000019</v>
       </c>
       <c r="H91" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I91" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J91" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K91" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L91" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M91" t="str">
-        <v>30000324679</v>
+        <v>30000150461</v>
       </c>
       <c r="N91" t="str">
         <v>State Bank of India</v>
@@ -6101,48 +6125,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P91" t="str">
-        <v>SBIN0005207</v>
+        <v>SBIN0003017</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>0300033</v>
+        <v>0300084</v>
       </c>
       <c r="B92" t="str">
-        <v>RANJIT ANSARI</v>
+        <v>SHAILESH MAHTO</v>
       </c>
       <c r="C92" t="str">
-        <v>Head Clerk</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D92" t="str">
-        <v>03031</v>
+        <v>03027</v>
       </c>
       <c r="E92" t="str">
-        <v>Circle Office Tariyani</v>
+        <v>RWD Division Sheohar</v>
       </c>
       <c r="F92" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G92" t="str">
-        <v>9003000033</v>
+        <v>9003000084</v>
       </c>
       <c r="H92" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I92" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J92" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K92" t="str">
-        <v>0305</v>
+        <v>0301</v>
       </c>
       <c r="L92" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M92" t="str">
-        <v>30000261327</v>
+        <v>30000665196</v>
       </c>
       <c r="N92" t="str">
         <v>State Bank of India</v>
@@ -6151,39 +6175,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P92" t="str">
-        <v>SBIN0001926</v>
+        <v>SBIN0007077</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>0300097</v>
+        <v>0300032</v>
       </c>
       <c r="B93" t="str">
-        <v>MUKESH SHARMA</v>
+        <v>PRAMOD JHA</v>
       </c>
       <c r="C93" t="str">
-        <v>Junior Engineer</v>
+        <v>Head Clerk</v>
       </c>
       <c r="D93" t="str">
-        <v>03072</v>
+        <v>03029</v>
       </c>
       <c r="E93" t="str">
-        <v>RWD Sub-Division Sheohar</v>
+        <v>Middle School Sheohar</v>
       </c>
       <c r="F93" t="str">
         <v>Sheohar, Sheohar</v>
       </c>
       <c r="G93" t="str">
-        <v>9003000097</v>
+        <v>9003000032</v>
       </c>
       <c r="H93" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I93" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J93" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K93" t="str">
         <v>0301</v>
@@ -6192,7 +6216,7 @@
         <v>Sheohar</v>
       </c>
       <c r="M93" t="str">
-        <v>30000768143</v>
+        <v>30000253408</v>
       </c>
       <c r="N93" t="str">
         <v>State Bank of India</v>
@@ -6201,39 +6225,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P93" t="str">
-        <v>SBIN0005595</v>
+        <v>SBIN0004353</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>0300046</v>
+        <v>0300090</v>
       </c>
       <c r="B94" t="str">
-        <v>PRAMOD RAM</v>
+        <v>FARHAT SINHA</v>
       </c>
       <c r="C94" t="str">
-        <v>Accountant</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D94" t="str">
-        <v>03039</v>
+        <v>03047</v>
       </c>
       <c r="E94" t="str">
-        <v>PHC Piprahi No.3</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="F94" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G94" t="str">
-        <v>9003000046</v>
+        <v>9003000090</v>
       </c>
       <c r="H94" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I94" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J94" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K94" t="str">
         <v>0302</v>
@@ -6242,7 +6266,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M94" t="str">
-        <v>30000364274</v>
+        <v>30000712710</v>
       </c>
       <c r="N94" t="str">
         <v>State Bank of India</v>
@@ -6251,48 +6275,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P94" t="str">
-        <v>SBIN0004767</v>
+        <v>SBIN0003832</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>0300102</v>
+        <v>0300029</v>
       </c>
       <c r="B95" t="str">
-        <v>POONAM SAH</v>
+        <v>MAMTA YADAV</v>
       </c>
       <c r="C95" t="str">
-        <v>Assistant Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D95" t="str">
-        <v>03082</v>
+        <v>03026</v>
       </c>
       <c r="E95" t="str">
-        <v>Minor Irrigation Office Dumri Katsari</v>
+        <v>Middle School Purnahiya</v>
       </c>
       <c r="F95" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G95" t="str">
-        <v>9003000102</v>
+        <v>9003000029</v>
       </c>
       <c r="H95" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I95" t="str">
-        <v>0304</v>
+        <v>999999</v>
       </c>
       <c r="J95" t="str">
-        <v>Dumri Katsari</v>
+        <v>Others</v>
       </c>
       <c r="K95" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L95" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M95" t="str">
-        <v>30000807738</v>
+        <v>30000229651</v>
       </c>
       <c r="N95" t="str">
         <v>State Bank of India</v>
@@ -6301,48 +6325,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P95" t="str">
-        <v>SBIN0004369</v>
+        <v>SBIN0008684</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>0300107</v>
+        <v>0300067</v>
       </c>
       <c r="B96" t="str">
-        <v>KUMARI ANJALI OJHA</v>
+        <v>RINKU MAHTO</v>
       </c>
       <c r="C96" t="str">
-        <v>Sub Divisional Engineer</v>
+        <v>Data Entry Operator</v>
       </c>
       <c r="D96" t="str">
-        <v>03085</v>
+        <v>03012</v>
       </c>
       <c r="E96" t="str">
-        <v>State Bank of India, Purnahiya</v>
+        <v>CDPO Office Sheohar No.1</v>
       </c>
       <c r="F96" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G96" t="str">
-        <v>9003000107</v>
+        <v>9003000067</v>
       </c>
       <c r="H96" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I96" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J96" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K96" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="L96" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="M96" t="str">
-        <v>30000847333</v>
+        <v>30000530573</v>
       </c>
       <c r="N96" t="str">
         <v>State Bank of India</v>
@@ -6351,48 +6375,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P96" t="str">
-        <v>SBIN0006995</v>
+        <v>SBIN0005417</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>0300120</v>
+        <v>0300065</v>
       </c>
       <c r="B97" t="str">
-        <v>DINESH ANSARI</v>
+        <v>ANITA TIWARI</v>
       </c>
       <c r="C97" t="str">
-        <v>Administrative Officer</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D97" t="str">
-        <v>03096</v>
+        <v>03059</v>
       </c>
       <c r="E97" t="str">
-        <v>UCO Bank, Purnahiya</v>
+        <v>PHED Division (deputed from other district)</v>
       </c>
       <c r="F97" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G97" t="str">
-        <v>9003000120</v>
+        <v>9003000065</v>
       </c>
       <c r="H97" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I97" t="str">
+        <v>0302</v>
+      </c>
+      <c r="J97" t="str">
+        <v>Piprahi</v>
+      </c>
+      <c r="K97" t="str">
         <v>999999</v>
       </c>
-      <c r="J97" t="str">
-        <v>Others</v>
-      </c>
-      <c r="K97" t="str">
-        <v>0303</v>
-      </c>
       <c r="L97" t="str">
-        <v>Purnahiya</v>
+        <v>Other District</v>
       </c>
       <c r="M97" t="str">
-        <v>30000950280</v>
+        <v>30000514735</v>
       </c>
       <c r="N97" t="str">
         <v>State Bank of India</v>
@@ -6401,48 +6425,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P97" t="str">
-        <v>SBIN0003644</v>
+        <v>SBIN0006782</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>0300038</v>
+        <v>0300121</v>
       </c>
       <c r="B98" t="str">
-        <v>UMESH SINHA Y</v>
+        <v>SHAILESH PANDEY</v>
       </c>
       <c r="C98" t="str">
-        <v>Assistant Teacher</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D98" t="str">
-        <v>03020</v>
+        <v>03093</v>
       </c>
       <c r="E98" t="str">
-        <v>Panchayat Bhawan Dumri Katsari</v>
+        <v>State Bank of India, Sheohar</v>
       </c>
       <c r="F98" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G98" t="str">
-        <v>9003000038</v>
+        <v>9003000121</v>
       </c>
       <c r="H98" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I98" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J98" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K98" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="L98" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="M98" t="str">
-        <v>30000300922</v>
+        <v>30000958199</v>
       </c>
       <c r="N98" t="str">
         <v>State Bank of India</v>
@@ -6451,48 +6475,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P98" t="str">
-        <v>SBIN0005275</v>
+        <v>SBIN0005319</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>0300060</v>
+        <v>0300040</v>
       </c>
       <c r="B99" t="str">
-        <v>AMIT KHATUN</v>
+        <v>PRIYANKA SINGH</v>
       </c>
       <c r="C99" t="str">
-        <v>Teacher</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D99" t="str">
-        <v>03052</v>
+        <v>03037</v>
       </c>
       <c r="E99" t="str">
-        <v>Block Office Dumri Katsari</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="F99" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G99" t="str">
-        <v>9003000060</v>
+        <v>9003000040</v>
       </c>
       <c r="H99" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I99" t="str">
-        <v>0304</v>
+        <v>0302</v>
       </c>
       <c r="J99" t="str">
-        <v>Dumri Katsari</v>
+        <v>Piprahi</v>
       </c>
       <c r="K99" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L99" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M99" t="str">
-        <v>30000475140</v>
+        <v>30000316760</v>
       </c>
       <c r="N99" t="str">
         <v>State Bank of India</v>
@@ -6501,48 +6525,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P99" t="str">
-        <v>SBIN0003562</v>
+        <v>SBIN0007452</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>0300055</v>
+        <v>0300091</v>
       </c>
       <c r="B100" t="str">
-        <v>ALOK PASWAN</v>
+        <v>MAHESH TIWARI</v>
       </c>
       <c r="C100" t="str">
-        <v>Revenue Karmachari</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D100" t="str">
-        <v>03047</v>
+        <v>03074</v>
       </c>
       <c r="E100" t="str">
-        <v>Kanya Middle School Piprahi No.1</v>
+        <v>Block Agriculture Office Sheohar</v>
       </c>
       <c r="F100" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G100" t="str">
-        <v>9003000055</v>
+        <v>9003000091</v>
       </c>
       <c r="H100" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I100" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J100" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K100" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L100" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M100" t="str">
-        <v>30000435545</v>
+        <v>30000720629</v>
       </c>
       <c r="N100" t="str">
         <v>State Bank of India</v>
@@ -6551,48 +6575,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P100" t="str">
-        <v>SBIN0004884</v>
+        <v>SBIN0006548</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>0300110</v>
+        <v>0300007</v>
       </c>
       <c r="B101" t="str">
-        <v>DINESH ALAM</v>
+        <v>DINESH GUPTA</v>
       </c>
       <c r="C101" t="str">
-        <v>Assistant Manager</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D101" t="str">
-        <v>03087</v>
+        <v>03007</v>
       </c>
       <c r="E101" t="str">
-        <v>LIC Branch Office, Sheohar</v>
+        <v>CDPO Office Dumri Katsari</v>
       </c>
       <c r="F101" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G101" t="str">
-        <v>9003000110</v>
+        <v>9003000007</v>
       </c>
       <c r="H101" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I101" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="J101" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K101" t="str">
-        <v>0301</v>
+        <v>0304</v>
       </c>
       <c r="L101" t="str">
-        <v>Sheohar</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M101" t="str">
-        <v>30000871090</v>
+        <v>30000055433</v>
       </c>
       <c r="N101" t="str">
         <v>State Bank of India</v>
@@ -6601,48 +6625,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P101" t="str">
-        <v>SBIN0003383</v>
+        <v>SBIN0007992</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>0300015</v>
+        <v>0300036</v>
       </c>
       <c r="B102" t="str">
-        <v>UMESH SINHA</v>
+        <v>KUMARI ANJALI MISHRA</v>
       </c>
       <c r="C102" t="str">
-        <v>Headmaster</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D102" t="str">
-        <v>03015</v>
+        <v>03033</v>
       </c>
       <c r="E102" t="str">
-        <v>Kanya Middle School Dumri Katsari</v>
+        <v>Primary School Tariyani No.4</v>
       </c>
       <c r="F102" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G102" t="str">
-        <v>9003000015</v>
+        <v>9003000036</v>
       </c>
       <c r="H102" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I102" t="str">
-        <v>0302</v>
+        <v>0305</v>
       </c>
       <c r="J102" t="str">
-        <v>Piprahi</v>
+        <v>Tariyani</v>
       </c>
       <c r="K102" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="L102" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="M102" t="str">
-        <v>30000118785</v>
+        <v>30000285084</v>
       </c>
       <c r="N102" t="str">
         <v>State Bank of India</v>
@@ -6651,39 +6675,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P102" t="str">
-        <v>SBIN0003100</v>
+        <v>SBIN0002468</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>0300051</v>
+        <v>0300050</v>
       </c>
       <c r="B103" t="str">
-        <v>SUNITA TIWARI</v>
+        <v>ABDUL KALAM ALAM</v>
       </c>
       <c r="C103" t="str">
-        <v>Accountant</v>
+        <v>Teacher</v>
       </c>
       <c r="D103" t="str">
-        <v>03044</v>
+        <v>03047</v>
       </c>
       <c r="E103" t="str">
-        <v>Block Education Office Piprahi No.2</v>
+        <v>Block Office Piprahi</v>
       </c>
       <c r="F103" t="str">
         <v>Piprahi, Sheohar</v>
       </c>
       <c r="G103" t="str">
-        <v>9003000051</v>
+        <v>9003000050</v>
       </c>
       <c r="H103" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I103" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J103" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K103" t="str">
         <v>0302</v>
@@ -6692,7 +6716,7 @@
         <v>Piprahi</v>
       </c>
       <c r="M103" t="str">
-        <v>30000403869</v>
+        <v>30000395950</v>
       </c>
       <c r="N103" t="str">
         <v>State Bank of India</v>
@@ -6701,33 +6725,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P103" t="str">
-        <v>SBIN0005463</v>
+        <v>SBIN0001275</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>0300004</v>
+        <v>0300045</v>
       </c>
       <c r="B104" t="str">
-        <v>MUKESH PRASAD</v>
+        <v>NEHA MAHTO</v>
       </c>
       <c r="C104" t="str">
-        <v>Headmaster</v>
+        <v>Revenue Karmachari</v>
       </c>
       <c r="D104" t="str">
-        <v>03004</v>
+        <v>03042</v>
       </c>
       <c r="E104" t="str">
-        <v>Block Agriculture Office Tariyani No.4</v>
+        <v>Middle School Tariyani No.4</v>
       </c>
       <c r="F104" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G104" t="str">
-        <v>9003000004</v>
+        <v>9003000045</v>
       </c>
       <c r="H104" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I104" t="str">
         <v>0305</v>
@@ -6742,7 +6766,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M104" t="str">
-        <v>30000031676</v>
+        <v>30000356355</v>
       </c>
       <c r="N104" t="str">
         <v>State Bank of India</v>
@@ -6751,48 +6775,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P104" t="str">
-        <v>SBIN0004849</v>
+        <v>SBIN0003475</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>0300063</v>
+        <v>0300094</v>
       </c>
       <c r="B105" t="str">
-        <v>SAVITA VERMA</v>
+        <v>NITISH RAI</v>
       </c>
       <c r="C105" t="str">
-        <v>Accountant</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D105" t="str">
-        <v>03055</v>
+        <v>03076</v>
       </c>
       <c r="E105" t="str">
-        <v>Collectorate (deputed from other district)</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="F105" t="str">
-        <v>Other District, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G105" t="str">
-        <v>9003000063</v>
+        <v>9003000094</v>
       </c>
       <c r="H105" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I105" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="J105" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="K105" t="str">
-        <v>999999</v>
+        <v>0305</v>
       </c>
       <c r="L105" t="str">
-        <v>Other District</v>
+        <v>Tariyani</v>
       </c>
       <c r="M105" t="str">
-        <v>30000498897</v>
+        <v>30000744386</v>
       </c>
       <c r="N105" t="str">
         <v>State Bank of India</v>
@@ -6801,48 +6825,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P105" t="str">
-        <v>SBIN0006546</v>
+        <v>SBIN0008787</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>0300113</v>
+        <v>0300081</v>
       </c>
       <c r="B106" t="str">
-        <v>USHA SINHA</v>
+        <v>RAJESH PRASAD</v>
       </c>
       <c r="C106" t="str">
-        <v>Postmaster</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D106" t="str">
-        <v>03090</v>
+        <v>03014</v>
       </c>
       <c r="E106" t="str">
-        <v>State Bank of India, Piprahi</v>
+        <v>Circle Office Purnahiya</v>
       </c>
       <c r="F106" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G106" t="str">
-        <v>9003000113</v>
+        <v>9003000081</v>
       </c>
       <c r="H106" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I106" t="str">
-        <v>999999</v>
+        <v>0303</v>
       </c>
       <c r="J106" t="str">
-        <v>Others</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K106" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L106" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M106" t="str">
-        <v>30000894847</v>
+        <v>30000641439</v>
       </c>
       <c r="N106" t="str">
         <v>State Bank of India</v>
@@ -6851,48 +6875,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P106" t="str">
-        <v>SBIN0007650</v>
+        <v>SBIN0007411</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>0300068</v>
+        <v>0300033</v>
       </c>
       <c r="B107" t="str">
-        <v>ANIL DEVI</v>
+        <v>SANJAY MAHTO</v>
       </c>
       <c r="C107" t="str">
-        <v>Data Entry Operator</v>
+        <v>Senior Clerk</v>
       </c>
       <c r="D107" t="str">
-        <v>03059</v>
+        <v>03030</v>
       </c>
       <c r="E107" t="str">
-        <v>PHC Purnahiya No.1</v>
+        <v>Block Agriculture Office Tariyani No.4</v>
       </c>
       <c r="F107" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G107" t="str">
-        <v>9003000068</v>
+        <v>9003000033</v>
       </c>
       <c r="H107" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I107" t="str">
-        <v>0303</v>
+        <v>0301</v>
       </c>
       <c r="J107" t="str">
-        <v>Purnahiya</v>
+        <v>Sheohar</v>
       </c>
       <c r="K107" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="L107" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="M107" t="str">
-        <v>30000538492</v>
+        <v>30000261327</v>
       </c>
       <c r="N107" t="str">
         <v>State Bank of India</v>
@@ -6901,33 +6925,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P107" t="str">
-        <v>SBIN0001268</v>
+        <v>SBIN0003313</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>0300050</v>
+        <v>0300073</v>
       </c>
       <c r="B108" t="str">
-        <v>NIRMALA RAI</v>
+        <v>SAVITA RAM</v>
       </c>
       <c r="C108" t="str">
-        <v>Teacher</v>
+        <v>Office Assistant</v>
       </c>
       <c r="D108" t="str">
-        <v>03043</v>
+        <v>03065</v>
       </c>
       <c r="E108" t="str">
-        <v>Block Office Piprahi No.2</v>
+        <v>District Treasury Sheohar</v>
       </c>
       <c r="F108" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G108" t="str">
-        <v>9003000050</v>
+        <v>9003000073</v>
       </c>
       <c r="H108" t="str">
-        <v>POLLING OFFICER-2</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I108" t="str">
         <v>0303</v>
@@ -6936,13 +6960,13 @@
         <v>Purnahiya</v>
       </c>
       <c r="K108" t="str">
-        <v>0302</v>
+        <v>0301</v>
       </c>
       <c r="L108" t="str">
-        <v>Piprahi</v>
+        <v>Sheohar</v>
       </c>
       <c r="M108" t="str">
-        <v>30000395950</v>
+        <v>30000578087</v>
       </c>
       <c r="N108" t="str">
         <v>State Bank of India</v>
@@ -6951,33 +6975,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P108" t="str">
-        <v>SBIN0002917</v>
+        <v>SBIN0009213</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>0300099</v>
+        <v>0300119</v>
       </c>
       <c r="B109" t="str">
-        <v>NITISH MISHRA</v>
+        <v>KIRAN YADAV</v>
       </c>
       <c r="C109" t="str">
-        <v>Revenue Officer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D109" t="str">
-        <v>03079</v>
+        <v>03092</v>
       </c>
       <c r="E109" t="str">
-        <v>Block Agriculture Office Piprahi</v>
+        <v>LIC Branch Office, Dumri Katsari</v>
       </c>
       <c r="F109" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G109" t="str">
-        <v>9003000099</v>
+        <v>9003000119</v>
       </c>
       <c r="H109" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I109" t="str">
         <v>0302</v>
@@ -6986,13 +7010,13 @@
         <v>Piprahi</v>
       </c>
       <c r="K109" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L109" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M109" t="str">
-        <v>30000783981</v>
+        <v>30000942361</v>
       </c>
       <c r="N109" t="str">
         <v>State Bank of India</v>
@@ -7001,48 +7025,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P109" t="str">
-        <v>SBIN0008924</v>
+        <v>SBIN0003988</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>0300032</v>
+        <v>0300016</v>
       </c>
       <c r="B110" t="str">
-        <v>KIRAN OJHA</v>
+        <v>PRIYANKA MISHRA</v>
       </c>
       <c r="C110" t="str">
-        <v>Senior Clerk</v>
+        <v>Block Agriculture Officer</v>
       </c>
       <c r="D110" t="str">
-        <v>03030</v>
+        <v>03015</v>
       </c>
       <c r="E110" t="str">
-        <v>Panchayat Bhawan Piprahi No.3</v>
+        <v>Primary School Dumri Katsari No.3</v>
       </c>
       <c r="F110" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G110" t="str">
-        <v>9003000032</v>
+        <v>9003000016</v>
       </c>
       <c r="H110" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I110" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J110" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K110" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="L110" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M110" t="str">
-        <v>30000253408</v>
+        <v>30000126704</v>
       </c>
       <c r="N110" t="str">
         <v>State Bank of India</v>
@@ -7051,39 +7075,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P110" t="str">
-        <v>SBIN0006118</v>
+        <v>SBIN0008031</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>0300069</v>
+        <v>0300088</v>
       </c>
       <c r="B111" t="str">
-        <v>ABDUL KALAM TIWARI</v>
+        <v>MD. SHAHID CHAUDHARY</v>
       </c>
       <c r="C111" t="str">
-        <v>Teacher</v>
+        <v>Junior Engineer</v>
       </c>
       <c r="D111" t="str">
-        <v>03060</v>
+        <v>03073</v>
       </c>
       <c r="E111" t="str">
-        <v>Primary School Dumri Katsari No.4</v>
+        <v>Block Agriculture Office Dumri Katsari</v>
       </c>
       <c r="F111" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G111" t="str">
-        <v>9003000069</v>
+        <v>9003000088</v>
       </c>
       <c r="H111" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I111" t="str">
-        <v>0304</v>
+        <v>0301</v>
       </c>
       <c r="J111" t="str">
-        <v>Dumri Katsari</v>
+        <v>Sheohar</v>
       </c>
       <c r="K111" t="str">
         <v>0304</v>
@@ -7092,7 +7116,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M111" t="str">
-        <v>30000546411</v>
+        <v>30000696872</v>
       </c>
       <c r="N111" t="str">
         <v>State Bank of India</v>
@@ -7101,33 +7125,33 @@
         <v>Sheohar</v>
       </c>
       <c r="P111" t="str">
-        <v>SBIN0004108</v>
+        <v>SBIN0009615</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>0300077</v>
+        <v>0300108</v>
       </c>
       <c r="B112" t="str">
-        <v>ARVIND ANSARI</v>
+        <v>MANOJ SINGH</v>
       </c>
       <c r="C112" t="str">
-        <v>Office Assistant</v>
+        <v>Postmaster</v>
       </c>
       <c r="D112" t="str">
-        <v>03065</v>
+        <v>03083</v>
       </c>
       <c r="E112" t="str">
-        <v>Primary School Tariyani No.1</v>
+        <v>Bank of India, Dumri Katsari</v>
       </c>
       <c r="F112" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G112" t="str">
-        <v>9003000077</v>
+        <v>9003000108</v>
       </c>
       <c r="H112" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I112" t="str">
         <v>0304</v>
@@ -7136,13 +7160,13 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="K112" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L112" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M112" t="str">
-        <v>30000609763</v>
+        <v>30000855252</v>
       </c>
       <c r="N112" t="str">
         <v>State Bank of India</v>
@@ -7151,48 +7175,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P112" t="str">
-        <v>SBIN0004722</v>
+        <v>SBIN0003885</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>0300079</v>
+        <v>0300120</v>
       </c>
       <c r="B113" t="str">
-        <v>NITISH SHARMA</v>
+        <v>SUNIL OJHA U</v>
       </c>
       <c r="C113" t="str">
-        <v>Teacher</v>
+        <v>Postmaster</v>
       </c>
       <c r="D113" t="str">
-        <v>03067</v>
+        <v>03086</v>
       </c>
       <c r="E113" t="str">
-        <v>High School Piprahi No.1</v>
+        <v>Head Post Office, Purnahiya</v>
       </c>
       <c r="F113" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G113" t="str">
-        <v>9003000079</v>
+        <v>9003000120</v>
       </c>
       <c r="H113" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I113" t="str">
-        <v>0305</v>
+        <v>0303</v>
       </c>
       <c r="J113" t="str">
-        <v>Tariyani</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K113" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L113" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M113" t="str">
-        <v>30000625601</v>
+        <v>30000950280</v>
       </c>
       <c r="N113" t="str">
         <v>State Bank of India</v>
@@ -7201,48 +7225,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P113" t="str">
-        <v>SBIN0005793</v>
+        <v>SBIN0006436</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>0300095</v>
+        <v>0300025</v>
       </c>
       <c r="B114" t="str">
-        <v>NASREEN RAI</v>
+        <v>NASREEN ANSARI</v>
       </c>
       <c r="C114" t="str">
-        <v>Assistant Engineer</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D114" t="str">
-        <v>03076</v>
+        <v>03024</v>
       </c>
       <c r="E114" t="str">
-        <v>RWD Sub-Division Piprahi</v>
+        <v>Circle Office Purnahiya No.2</v>
       </c>
       <c r="F114" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G114" t="str">
-        <v>9003000095</v>
+        <v>9003000025</v>
       </c>
       <c r="H114" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I114" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="J114" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="K114" t="str">
-        <v>0302</v>
+        <v>0303</v>
       </c>
       <c r="L114" t="str">
-        <v>Piprahi</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M114" t="str">
-        <v>30000752305</v>
+        <v>30000197975</v>
       </c>
       <c r="N114" t="str">
         <v>State Bank of India</v>
@@ -7251,48 +7275,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P114" t="str">
-        <v>SBIN0001346</v>
+        <v>SBIN0006245</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>0300080</v>
+        <v>0300031</v>
       </c>
       <c r="B115" t="str">
-        <v>ARVIND KUMAR</v>
+        <v>VINOD SHARMA</v>
       </c>
       <c r="C115" t="str">
-        <v>Data Entry Operator</v>
+        <v>Panchayat Secretary</v>
       </c>
       <c r="D115" t="str">
-        <v>03068</v>
+        <v>03028</v>
       </c>
       <c r="E115" t="str">
-        <v>Block Agriculture Office Dumri Katsari No.4</v>
+        <v>Project Girls High School Purnahiya No.4</v>
       </c>
       <c r="F115" t="str">
-        <v>Dumri Katsari, Sheohar</v>
+        <v>Purnahiya, Sheohar</v>
       </c>
       <c r="G115" t="str">
-        <v>9003000080</v>
+        <v>9003000031</v>
       </c>
       <c r="H115" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>POLLING OFFICER-1</v>
       </c>
       <c r="I115" t="str">
-        <v>0304</v>
+        <v>0305</v>
       </c>
       <c r="J115" t="str">
-        <v>Dumri Katsari</v>
+        <v>Tariyani</v>
       </c>
       <c r="K115" t="str">
-        <v>0304</v>
+        <v>0303</v>
       </c>
       <c r="L115" t="str">
-        <v>Dumri Katsari</v>
+        <v>Purnahiya</v>
       </c>
       <c r="M115" t="str">
-        <v>30000633520</v>
+        <v>30000245489</v>
       </c>
       <c r="N115" t="str">
         <v>State Bank of India</v>
@@ -7301,48 +7325,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P115" t="str">
-        <v>SBIN0005197</v>
+        <v>SBIN0006171</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>0300007</v>
+        <v>0300097</v>
       </c>
       <c r="B116" t="str">
-        <v>SAVITA THAKUR</v>
+        <v>ANIL ANSARI</v>
       </c>
       <c r="C116" t="str">
-        <v>Lecturer</v>
+        <v>Revenue Officer</v>
       </c>
       <c r="D116" t="str">
-        <v>03007</v>
+        <v>03076</v>
       </c>
       <c r="E116" t="str">
-        <v>PHED Division Sheohar</v>
+        <v>Circle Office Tariyani</v>
       </c>
       <c r="F116" t="str">
-        <v>Sheohar, Sheohar</v>
+        <v>Tariyani, Sheohar</v>
       </c>
       <c r="G116" t="str">
-        <v>9003000007</v>
+        <v>9003000097</v>
       </c>
       <c r="H116" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I116" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J116" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K116" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="L116" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="M116" t="str">
-        <v>30000055433</v>
+        <v>30000768143</v>
       </c>
       <c r="N116" t="str">
         <v>State Bank of India</v>
@@ -7351,48 +7375,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P116" t="str">
-        <v>SBIN0007222</v>
+        <v>SBIN0009501</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>0300043</v>
+        <v>0300046</v>
       </c>
       <c r="B117" t="str">
-        <v>ARVIND ALAM</v>
+        <v>PRAMOD SAH</v>
       </c>
       <c r="C117" t="str">
-        <v>Clerk</v>
+        <v>Accountant</v>
       </c>
       <c r="D117" t="str">
-        <v>03037</v>
+        <v>03043</v>
       </c>
       <c r="E117" t="str">
-        <v>Block Agriculture Office Piprahi No.4</v>
+        <v>District Agriculture Office (deputed from other district)</v>
       </c>
       <c r="F117" t="str">
-        <v>Piprahi, Sheohar</v>
+        <v>Other District, Sheohar</v>
       </c>
       <c r="G117" t="str">
-        <v>9003000043</v>
+        <v>9003000046</v>
       </c>
       <c r="H117" t="str">
         <v>POLLING OFFICER-2</v>
       </c>
       <c r="I117" t="str">
-        <v>0302</v>
+        <v>0304</v>
       </c>
       <c r="J117" t="str">
-        <v>Piprahi</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="K117" t="str">
-        <v>0302</v>
+        <v>999999</v>
       </c>
       <c r="L117" t="str">
-        <v>Piprahi</v>
+        <v>Other District</v>
       </c>
       <c r="M117" t="str">
-        <v>30000340517</v>
+        <v>30000364274</v>
       </c>
       <c r="N117" t="str">
         <v>State Bank of India</v>
@@ -7401,39 +7425,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P117" t="str">
-        <v>SBIN0004129</v>
+        <v>SBIN0001579</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>0300014</v>
+        <v>0300099</v>
       </c>
       <c r="B118" t="str">
-        <v>SAVITA JHA</v>
+        <v>RAMESH THAKUR</v>
       </c>
       <c r="C118" t="str">
-        <v>Headmaster</v>
+        <v>Block Panchayat Raj Officer</v>
       </c>
       <c r="D118" t="str">
-        <v>03014</v>
+        <v>03037</v>
       </c>
       <c r="E118" t="str">
-        <v>Block Agriculture Office Tariyani No.3</v>
+        <v>Block Agriculture Office Tariyani</v>
       </c>
       <c r="F118" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G118" t="str">
-        <v>9003000014</v>
+        <v>9003000099</v>
       </c>
       <c r="H118" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I118" t="str">
-        <v>0303</v>
+        <v>0305</v>
       </c>
       <c r="J118" t="str">
-        <v>Purnahiya</v>
+        <v>Tariyani</v>
       </c>
       <c r="K118" t="str">
         <v>0305</v>
@@ -7442,7 +7466,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M118" t="str">
-        <v>30000110866</v>
+        <v>30000783981</v>
       </c>
       <c r="N118" t="str">
         <v>State Bank of India</v>
@@ -7451,39 +7475,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P118" t="str">
-        <v>SBIN0003394</v>
+        <v>SBIN0004636</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>0300005</v>
+        <v>0300054</v>
       </c>
       <c r="B119" t="str">
-        <v>KUMARI ANJALI PANDEY</v>
+        <v>SAVITA SINHA</v>
       </c>
       <c r="C119" t="str">
-        <v>Senior Teacher</v>
+        <v>Clerk</v>
       </c>
       <c r="D119" t="str">
-        <v>03005</v>
+        <v>03050</v>
       </c>
       <c r="E119" t="str">
-        <v>Middle School Dumri Katsari No.4</v>
+        <v>PHC Dumri Katsari No.4</v>
       </c>
       <c r="F119" t="str">
         <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G119" t="str">
-        <v>9003000005</v>
+        <v>9003000054</v>
       </c>
       <c r="H119" t="str">
-        <v>PRESIDING OFFICER</v>
+        <v>POLLING OFFICER-2</v>
       </c>
       <c r="I119" t="str">
-        <v>0305</v>
+        <v>999999</v>
       </c>
       <c r="J119" t="str">
-        <v>Tariyani</v>
+        <v>Others</v>
       </c>
       <c r="K119" t="str">
         <v>0304</v>
@@ -7492,7 +7516,7 @@
         <v>Dumri Katsari</v>
       </c>
       <c r="M119" t="str">
-        <v>30000039595</v>
+        <v>30000427626</v>
       </c>
       <c r="N119" t="str">
         <v>State Bank of India</v>
@@ -7501,39 +7525,39 @@
         <v>Sheohar</v>
       </c>
       <c r="P119" t="str">
-        <v>SBIN0007893</v>
+        <v>SBIN0006256</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>0300028</v>
+        <v>0300005</v>
       </c>
       <c r="B120" t="str">
-        <v>RANJIT KUMAR</v>
+        <v>MAMTA GUPTA</v>
       </c>
       <c r="C120" t="str">
-        <v>Senior Clerk</v>
+        <v>Headmaster</v>
       </c>
       <c r="D120" t="str">
-        <v>03027</v>
+        <v>03005</v>
       </c>
       <c r="E120" t="str">
-        <v>Block Agriculture Office Tariyani No.2</v>
+        <v>Kanya Middle School Tariyani</v>
       </c>
       <c r="F120" t="str">
         <v>Tariyani, Sheohar</v>
       </c>
       <c r="G120" t="str">
-        <v>9003000028</v>
+        <v>9003000005</v>
       </c>
       <c r="H120" t="str">
-        <v>POLLING OFFICER-1</v>
+        <v>PRESIDING OFFICER</v>
       </c>
       <c r="I120" t="str">
-        <v>0301</v>
+        <v>0305</v>
       </c>
       <c r="J120" t="str">
-        <v>Sheohar</v>
+        <v>Tariyani</v>
       </c>
       <c r="K120" t="str">
         <v>0305</v>
@@ -7542,7 +7566,7 @@
         <v>Tariyani</v>
       </c>
       <c r="M120" t="str">
-        <v>30000221732</v>
+        <v>30000039595</v>
       </c>
       <c r="N120" t="str">
         <v>State Bank of India</v>
@@ -7551,48 +7575,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P120" t="str">
-        <v>SBIN0003910</v>
+        <v>SBIN0007577</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>0300078</v>
+        <v>0300103</v>
       </c>
       <c r="B121" t="str">
-        <v>MD. SHAHID RAI</v>
+        <v>VINOD ALAM</v>
       </c>
       <c r="C121" t="str">
-        <v>Office Assistant</v>
+        <v>Assistant Engineer</v>
       </c>
       <c r="D121" t="str">
-        <v>03066</v>
+        <v>03079</v>
       </c>
       <c r="E121" t="str">
-        <v>Circle Office Purnahiya</v>
+        <v>Block Agriculture Office Piprahi</v>
       </c>
       <c r="F121" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G121" t="str">
-        <v>9003000078</v>
+        <v>9003000103</v>
       </c>
       <c r="H121" t="str">
-        <v>POLLING OFFICER-3</v>
+        <v>PATROLLING MAGISTRATE</v>
       </c>
       <c r="I121" t="str">
+        <v>0304</v>
+      </c>
+      <c r="J121" t="str">
+        <v>Dumri Katsari</v>
+      </c>
+      <c r="K121" t="str">
         <v>0302</v>
       </c>
-      <c r="J121" t="str">
+      <c r="L121" t="str">
         <v>Piprahi</v>
       </c>
-      <c r="K121" t="str">
-        <v>0303</v>
-      </c>
-      <c r="L121" t="str">
-        <v>Purnahiya</v>
-      </c>
       <c r="M121" t="str">
-        <v>30000617682</v>
+        <v>30000815657</v>
       </c>
       <c r="N121" t="str">
         <v>State Bank of India</v>
@@ -7601,48 +7625,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P121" t="str">
-        <v>SBIN0001846</v>
+        <v>SBIN0008600</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>0300103</v>
+        <v>0300115</v>
       </c>
       <c r="B122" t="str">
-        <v>SURESH VERMA</v>
+        <v>SAVITA RAM X</v>
       </c>
       <c r="C122" t="str">
-        <v>Revenue Officer</v>
+        <v>Administrative Officer</v>
       </c>
       <c r="D122" t="str">
-        <v>03083</v>
+        <v>03084</v>
       </c>
       <c r="E122" t="str">
-        <v>Block Office Purnahiya</v>
+        <v>Head Post Office, Piprahi</v>
       </c>
       <c r="F122" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
       </c>
       <c r="G122" t="str">
-        <v>9003000103</v>
+        <v>9003000115</v>
       </c>
       <c r="H122" t="str">
-        <v>PATROLLING MAGISTRATE</v>
+        <v>MICRO OBSERVER</v>
       </c>
       <c r="I122" t="str">
-        <v>0305</v>
+        <v>0302</v>
       </c>
       <c r="J122" t="str">
-        <v>Tariyani</v>
+        <v>Piprahi</v>
       </c>
       <c r="K122" t="str">
-        <v>0303</v>
+        <v>0302</v>
       </c>
       <c r="L122" t="str">
-        <v>Purnahiya</v>
+        <v>Piprahi</v>
       </c>
       <c r="M122" t="str">
-        <v>30000815657</v>
+        <v>30000910685</v>
       </c>
       <c r="N122" t="str">
         <v>State Bank of India</v>
@@ -7651,48 +7675,48 @@
         <v>Sheohar</v>
       </c>
       <c r="P122" t="str">
-        <v>SBIN0003303</v>
+        <v>SBIN0001596</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>0300117</v>
+        <v>0300072</v>
       </c>
       <c r="B123" t="str">
-        <v>USHA SINHA V</v>
+        <v>MUKESH SAH</v>
       </c>
       <c r="C123" t="str">
-        <v>Postmaster</v>
+        <v>Clerk</v>
       </c>
       <c r="D123" t="str">
-        <v>03093</v>
+        <v>03064</v>
       </c>
       <c r="E123" t="str">
-        <v>Head Post Office, Tariyani</v>
+        <v>Panchayat Bhawan Sheohar No.1</v>
       </c>
       <c r="F123" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Sheohar, Sheohar</v>
       </c>
       <c r="G123" t="str">
-        <v>9003000117</v>
+        <v>9003000072</v>
       </c>
       <c r="H123" t="str">
-        <v>MICRO OBSERVER</v>
+        <v>POLLING OFFICER-3</v>
       </c>
       <c r="I123" t="str">
+        <v>0303</v>
+      </c>
+      <c r="J123" t="str">
+        <v>Purnahiya</v>
+      </c>
+      <c r="K123" t="str">
         <v>0301</v>
       </c>
-      <c r="J123" t="str">
-        <v>Sheohar</v>
-      </c>
-      <c r="K123" t="str">
-        <v>0305</v>
-      </c>
       <c r="L123" t="str">
-        <v>Tariyani</v>
+        <v>Sheohar</v>
       </c>
       <c r="M123" t="str">
-        <v>30000926523</v>
+        <v>30000570168</v>
       </c>
       <c r="N123" t="str">
         <v>State Bank of India</v>
@@ -7701,7 +7725,7 @@
         <v>Sheohar</v>
       </c>
       <c r="P123" t="str">
-        <v>SBIN0004887</v>
+        <v>SBIN0003487</v>
       </c>
     </row>
     <row r="124">
@@ -7709,19 +7733,19 @@
         <v>0300053</v>
       </c>
       <c r="B124" t="str">
-        <v>RINKU PANDEY</v>
+        <v>AMIT MAHTO</v>
       </c>
       <c r="C124" t="str">
-        <v>Accountant</v>
+        <v>Clerk</v>
       </c>
       <c r="D124" t="str">
-        <v>03046</v>
+        <v>03038</v>
       </c>
       <c r="E124" t="str">
-        <v>CDPO Office Tariyani</v>
+        <v>Kanya Middle School Dumri Katsari</v>
       </c>
       <c r="F124" t="str">
-        <v>Tariyani, Sheohar</v>
+        <v>Dumri Katsari, Sheohar</v>
       </c>
       <c r="G124" t="str">
         <v>9003000053</v>
@@ -7736,10 +7760,10 @@
         <v>Tariyani</v>
       </c>
       <c r="K124" t="str">
-        <v>0305</v>
+        <v>0304</v>
       </c>
       <c r="L124" t="str">
-        <v>Tariyani</v>
+        <v>Dumri Katsari</v>
       </c>
       <c r="M124" t="str">
         <v>30000419707</v>
@@ -7751,30 +7775,30 @@
         <v>Sheohar</v>
       </c>
       <c r="P124" t="str">
-        <v>SBIN0002439</v>
+        <v>SBIN0009020</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>0300115</v>
+        <v>0300117</v>
       </c>
       <c r="B125" t="str">
-        <v>RAKESH VERMA</v>
+        <v>MANOJ JHA</v>
       </c>
       <c r="C125" t="str">
-        <v>Administrative Officer</v>
+        <v>Postmaster</v>
       </c>
       <c r="D125" t="str">
-        <v>03092</v>
+        <v>03090</v>
       </c>
       <c r="E125" t="str">
-        <v>LIC Branch Office, Purnahiya</v>
+        <v>UCO Bank, Piprahi</v>
       </c>
       <c r="F125" t="str">
-        <v>Purnahiya, Sheohar</v>
+        <v>Piprahi, Sheohar</v>
     